--- a/Engagement Rankings 2026-07.xlsx
+++ b/Engagement Rankings 2026-07.xlsx
@@ -419,13 +419,13 @@
         <v>peacegrappler</v>
       </c>
       <c r="B2">
-        <v>13380</v>
+        <v>13381</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>12115</v>
+        <v>12116</v>
       </c>
     </row>
     <row r="3">
@@ -475,13 +475,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B6">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="C6">
         <v>14</v>
       </c>
       <c r="D6">
-        <v>711</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -13667,10 +13667,53 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetData/>
+  <dimension ref="A1:D3"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Username</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Text</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Emoji</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Early</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>peacegrappler</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>quemuel_ottoni</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Engagement Rankings 2026-07.xlsx
+++ b/Engagement Rankings 2026-07.xlsx
@@ -419,13 +419,13 @@
         <v>peacegrappler</v>
       </c>
       <c r="B2">
-        <v>13381</v>
+        <v>13387</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>12116</v>
+        <v>12122</v>
       </c>
     </row>
     <row r="3">
@@ -433,13 +433,13 @@
         <v>pedr00jj</v>
       </c>
       <c r="B3">
-        <v>3663</v>
+        <v>3667</v>
       </c>
       <c r="C3">
         <v>6</v>
       </c>
       <c r="D3">
-        <v>1554</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="4">
@@ -461,13 +461,13 @@
         <v>enzocardoso.bjj</v>
       </c>
       <c r="B5">
-        <v>2177</v>
+        <v>2182</v>
       </c>
       <c r="C5">
         <v>30</v>
       </c>
       <c r="D5">
-        <v>983</v>
+        <v>988</v>
       </c>
     </row>
     <row r="6">
@@ -475,13 +475,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B6">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="C6">
         <v>14</v>
       </c>
       <c r="D6">
-        <v>712</v>
+        <v>713</v>
       </c>
     </row>
     <row r="7">
@@ -13667,7 +13667,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -13688,32 +13688,60 @@
         <v>peacegrappler</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
+        <v>enzocardoso.bjj</v>
+      </c>
+      <c r="B3">
+        <v>5</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>pedr00jj</v>
+      </c>
+      <c r="B4">
+        <v>4</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
         <v>quemuel_ottoni</v>
       </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Engagement Rankings 2026-07.xlsx
+++ b/Engagement Rankings 2026-07.xlsx
@@ -461,13 +461,13 @@
         <v>enzocardoso.bjj</v>
       </c>
       <c r="B5">
-        <v>2182</v>
+        <v>2183</v>
       </c>
       <c r="C5">
         <v>30</v>
       </c>
       <c r="D5">
-        <v>988</v>
+        <v>989</v>
       </c>
     </row>
     <row r="6">
@@ -475,13 +475,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B6">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="C6">
         <v>14</v>
       </c>
       <c r="D6">
-        <v>713</v>
+        <v>714</v>
       </c>
     </row>
     <row r="7">
@@ -1970,27 +1970,27 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>psi_pedro.madeira</v>
+        <v>natanborges001</v>
       </c>
       <c r="B113">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C113">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D113">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>cayan.pascoalbjj</v>
+        <v>psi_pedro.madeira</v>
       </c>
       <c r="B114">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C114">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D114">
         <v>2</v>
@@ -1998,63 +1998,63 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>luigimoraess</v>
+        <v>cayan.pascoalbjj</v>
       </c>
       <c r="B115">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C115">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D115">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>bruno_murata</v>
+        <v>luigimoraess</v>
       </c>
       <c r="B116">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C116">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D116">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>juniordiasmma</v>
+        <v>bruno_murata</v>
       </c>
       <c r="B117">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C117">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D117">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>janders0202</v>
+        <v>juniordiasmma</v>
       </c>
       <c r="B118">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C118">
         <v>0</v>
       </c>
       <c r="D118">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>fabio_gb_</v>
+        <v>janders0202</v>
       </c>
       <c r="B119">
         <v>5</v>
@@ -2063,91 +2063,91 @@
         <v>0</v>
       </c>
       <c r="D119">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>carlosalbertobarretojr</v>
+        <v>fabio_gb_</v>
       </c>
       <c r="B120">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C120">
         <v>0</v>
       </c>
       <c r="D120">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>jorgeantoniopba</v>
+        <v>carlosalbertobarretojr</v>
       </c>
       <c r="B121">
         <v>8</v>
       </c>
       <c r="C121">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D121">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>alfredo_miras</v>
+        <v>jorgeantoniopba</v>
       </c>
       <c r="B122">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C122">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D122">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>mimuniz.bjj</v>
+        <v>alfredo_miras</v>
       </c>
       <c r="B123">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C123">
         <v>0</v>
       </c>
       <c r="D123">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>lucascardosol__</v>
+        <v>mimuniz.bjj</v>
       </c>
       <c r="B124">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C124">
         <v>0</v>
       </c>
       <c r="D124">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>natanborges001</v>
+        <v>lucascardosol__</v>
       </c>
       <c r="B125">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C125">
+        <v>0</v>
+      </c>
+      <c r="D125">
         <v>3</v>
-      </c>
-      <c r="D125">
-        <v>6</v>
       </c>
     </row>
     <row r="126">
@@ -13667,7 +13667,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -13702,13 +13702,13 @@
         <v>enzocardoso.bjj</v>
       </c>
       <c r="B3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -13730,18 +13730,32 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>natanborges001</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D6"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Engagement Rankings 2026-07.xlsx
+++ b/Engagement Rankings 2026-07.xlsx
@@ -433,7 +433,7 @@
         <v>pedr00jj</v>
       </c>
       <c r="B3">
-        <v>3667</v>
+        <v>3668</v>
       </c>
       <c r="C3">
         <v>6</v>
@@ -447,7 +447,7 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B4">
-        <v>3379</v>
+        <v>3380</v>
       </c>
       <c r="C4">
         <v>17</v>
@@ -461,13 +461,13 @@
         <v>enzocardoso.bjj</v>
       </c>
       <c r="B5">
-        <v>2183</v>
+        <v>2185</v>
       </c>
       <c r="C5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D5">
-        <v>989</v>
+        <v>992</v>
       </c>
     </row>
     <row r="6">
@@ -475,7 +475,7 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B6">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="C6">
         <v>14</v>
@@ -545,7 +545,7 @@
         <v>combintel</v>
       </c>
       <c r="B11">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C11">
         <v>2</v>
@@ -629,7 +629,7 @@
         <v>mmmarc20</v>
       </c>
       <c r="B17">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -643,7 +643,7 @@
         <v>johnmma9</v>
       </c>
       <c r="B18">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -657,7 +657,7 @@
         <v>masonharper_mma</v>
       </c>
       <c r="B19">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -1480,44 +1480,44 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>danielcarmonaconsultor</v>
+        <v>kelly_ottoni</v>
       </c>
       <c r="B78">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C78">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D78">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>jvxz______</v>
+        <v>danielcarmonaconsultor</v>
       </c>
       <c r="B79">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C79">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D79">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>kelly_ottoni</v>
+        <v>jvxz______</v>
       </c>
       <c r="B80">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C80">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D80">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="81">
@@ -13667,7 +13667,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D12"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -13702,13 +13702,13 @@
         <v>enzocardoso.bjj</v>
       </c>
       <c r="B3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -13716,7 +13716,7 @@
         <v>pedr00jj</v>
       </c>
       <c r="B4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -13730,7 +13730,7 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -13753,9 +13753,93 @@
         <v>1</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>combintel</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>masonharper_mma</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>johnmma9</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>mmmarc20</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>pablofiorindi</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>kelly_ottoni</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D12"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Engagement Rankings 2026-07.xlsx
+++ b/Engagement Rankings 2026-07.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D947"/>
+  <dimension ref="A1:D948"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -433,7 +433,7 @@
         <v>pedr00jj</v>
       </c>
       <c r="B3">
-        <v>3668</v>
+        <v>3671</v>
       </c>
       <c r="C3">
         <v>6</v>
@@ -461,10 +461,10 @@
         <v>enzocardoso.bjj</v>
       </c>
       <c r="B5">
-        <v>2185</v>
+        <v>2187</v>
       </c>
       <c r="C5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D5">
         <v>992</v>
@@ -475,13 +475,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B6">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C6">
         <v>14</v>
       </c>
       <c r="D6">
-        <v>714</v>
+        <v>715</v>
       </c>
     </row>
     <row r="7">
@@ -685,10 +685,10 @@
         <v>sirleneferreiradiasdias</v>
       </c>
       <c r="B21">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C21">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D21">
         <v>64</v>
@@ -853,13 +853,13 @@
         <v>washington_cassisno</v>
       </c>
       <c r="B33">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C33">
         <v>18</v>
       </c>
       <c r="D33">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="34">
@@ -1004,30 +1004,30 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>kamile_oliveria_10</v>
+        <v>anayachiottoni</v>
       </c>
       <c r="B44">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C44">
         <v>0</v>
       </c>
       <c r="D44">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>anayachiottoni</v>
+        <v>kamile_oliveria_10</v>
       </c>
       <c r="B45">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C45">
         <v>0</v>
       </c>
       <c r="D45">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="46">
@@ -1228,114 +1228,114 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>thiagoauper</v>
+        <v>grapplerfight</v>
       </c>
       <c r="B60">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="C60">
         <v>0</v>
       </c>
       <c r="D60">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>mar_iarmaria</v>
+        <v>thiagoauper</v>
       </c>
       <c r="B61">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C61">
         <v>0</v>
       </c>
       <c r="D61">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>eliassilverio</v>
+        <v>mar_iarmaria</v>
       </c>
       <c r="B62">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C62">
+        <v>0</v>
+      </c>
+      <c r="D62">
         <v>14</v>
-      </c>
-      <c r="D62">
-        <v>9</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>grapplerfight</v>
+        <v>eliassilverio</v>
       </c>
       <c r="B63">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="C63">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D63">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>gra_jpereira</v>
+        <v>thundergrapple</v>
       </c>
       <c r="B64">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C64">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D64">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>thundergrapple</v>
+        <v>galler_peace</v>
       </c>
       <c r="B65">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C65">
         <v>0</v>
       </c>
       <c r="D65">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>galler_peace</v>
+        <v>figh_grappler</v>
       </c>
       <c r="B66">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C66">
         <v>0</v>
       </c>
       <c r="D66">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>figh_grappler</v>
+        <v>gra_jpereira</v>
       </c>
       <c r="B67">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C67">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D67">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="68">
@@ -1466,30 +1466,30 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>tawanregismma</v>
+        <v>kelly_ottoni</v>
       </c>
       <c r="B77">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C77">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D77">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>kelly_ottoni</v>
+        <v>tawanregismma</v>
       </c>
       <c r="B78">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C78">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D78">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="79">
@@ -2152,10 +2152,10 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>biabasiliojj</v>
+        <v>erickdiaseds</v>
       </c>
       <c r="B126">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C126">
         <v>0</v>
@@ -2166,10 +2166,10 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>deboralvesoficial</v>
+        <v>biabasiliojj</v>
       </c>
       <c r="B127">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C127">
         <v>0</v>
@@ -2180,69 +2180,69 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>aj_mma_</v>
+        <v>deboralvesoficial</v>
       </c>
       <c r="B128">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C128">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D128">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>__bielgg</v>
+        <v>aj_mma_</v>
       </c>
       <c r="B129">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C129">
+        <v>1</v>
+      </c>
+      <c r="D129">
         <v>3</v>
-      </c>
-      <c r="D129">
-        <v>1</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>juanx.pontes</v>
+        <v>__bielgg</v>
       </c>
       <c r="B130">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C130">
         <v>3</v>
       </c>
       <c r="D130">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>paxlucta</v>
+        <v>juanx.pontes</v>
       </c>
       <c r="B131">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C131">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D131">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>muricunha</v>
+        <v>paxlucta</v>
       </c>
       <c r="B132">
         <v>5</v>
       </c>
       <c r="C132">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D132">
         <v>1</v>
@@ -2250,7 +2250,7 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>erickdiaseds</v>
+        <v>muricunha</v>
       </c>
       <c r="B133">
         <v>5</v>
@@ -2726,80 +2726,80 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>pitbullandrade</v>
+        <v>leobahiamma</v>
       </c>
       <c r="B167">
+        <v>2</v>
+      </c>
+      <c r="C167">
+        <v>1</v>
+      </c>
+      <c r="D167">
         <v>3</v>
-      </c>
-      <c r="C167">
-        <v>1</v>
-      </c>
-      <c r="D167">
-        <v>2</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>zedelano</v>
+        <v>pitbullandrade</v>
       </c>
       <c r="B168">
         <v>3</v>
       </c>
       <c r="C168">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D168">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>salost.ofc</v>
+        <v>zedelano</v>
       </c>
       <c r="B169">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C169">
         <v>0</v>
       </c>
       <c r="D169">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>gabrielsouzamma</v>
+        <v>salost.ofc</v>
       </c>
       <c r="B170">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C170">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D170">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>wilson_n_janjacomo</v>
+        <v>gabrielsouzamma</v>
       </c>
       <c r="B171">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C171">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D171">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>y.arthur_01</v>
+        <v>wilson_n_janjacomo</v>
       </c>
       <c r="B172">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C172">
         <v>0</v>
@@ -2810,16 +2810,16 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>leobahiamma</v>
+        <v>y.arthur_01</v>
       </c>
       <c r="B173">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C173">
         <v>0</v>
       </c>
       <c r="D173">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="174">
@@ -3006,27 +3006,27 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>mah__vergueiro</v>
+        <v>cristianpsicologo</v>
       </c>
       <c r="B187">
+        <v>2</v>
+      </c>
+      <c r="C187">
+        <v>4</v>
+      </c>
+      <c r="D187">
         <v>3</v>
-      </c>
-      <c r="C187">
-        <v>0</v>
-      </c>
-      <c r="D187">
-        <v>0</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>pizzaria.bambina_</v>
+        <v>mah__vergueiro</v>
       </c>
       <c r="B188">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C188">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D188">
         <v>0</v>
@@ -3034,35 +3034,35 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>h.codasqueves</v>
+        <v>pizzaria.bambina_</v>
       </c>
       <c r="B189">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C189">
         <v>1</v>
       </c>
       <c r="D189">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>alexandreconsentino</v>
+        <v>h.codasqueves</v>
       </c>
       <c r="B190">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C190">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D190">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>lipe.ftt</v>
+        <v>alexandreconsentino</v>
       </c>
       <c r="B191">
         <v>4</v>
@@ -3076,7 +3076,7 @@
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>fau_gfs</v>
+        <v>lipe.ftt</v>
       </c>
       <c r="B192">
         <v>4</v>
@@ -3090,21 +3090,21 @@
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>vitorpetrino</v>
+        <v>fau_gfs</v>
       </c>
       <c r="B193">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C193">
         <v>0</v>
       </c>
       <c r="D193">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>thompsonborralho</v>
+        <v>vitorpetrino</v>
       </c>
       <c r="B194">
         <v>3</v>
@@ -3118,7 +3118,7 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>devessonjj</v>
+        <v>thompsonborralho</v>
       </c>
       <c r="B195">
         <v>3</v>
@@ -3132,63 +3132,63 @@
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>espaco_jhayoliveira</v>
+        <v>devessonjj</v>
       </c>
       <c r="B196">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C196">
         <v>0</v>
       </c>
       <c r="D196">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>artewebpersonalizados</v>
+        <v>espaco_jhayoliveira</v>
       </c>
       <c r="B197">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C197">
         <v>0</v>
       </c>
       <c r="D197">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>marcosferreira.ofc1</v>
+        <v>artewebpersonalizados</v>
       </c>
       <c r="B198">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C198">
         <v>0</v>
       </c>
       <c r="D198">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>npb.enterprise</v>
+        <v>marcosferreira.ofc1</v>
       </c>
       <c r="B199">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C199">
         <v>0</v>
       </c>
       <c r="D199">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>victorhenriquebjj</v>
+        <v>npb.enterprise</v>
       </c>
       <c r="B200">
         <v>2</v>
@@ -3197,12 +3197,12 @@
         <v>0</v>
       </c>
       <c r="D200">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>eduardorobjj</v>
+        <v>victorhenriquebjj</v>
       </c>
       <c r="B201">
         <v>2</v>
@@ -3216,7 +3216,7 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>diego.dieguito.3914</v>
+        <v>eduardorobjj</v>
       </c>
       <c r="B202">
         <v>2</v>
@@ -3230,7 +3230,7 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>aerowellsports</v>
+        <v>diego.dieguito.3914</v>
       </c>
       <c r="B203">
         <v>2</v>
@@ -3244,7 +3244,7 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>royrosiano</v>
+        <v>aerowellsports</v>
       </c>
       <c r="B204">
         <v>2</v>
@@ -3258,7 +3258,7 @@
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>febrancatti</v>
+        <v>royrosiano</v>
       </c>
       <c r="B205">
         <v>2</v>
@@ -3272,7 +3272,7 @@
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>sensei_rogerio_baltazar</v>
+        <v>febrancatti</v>
       </c>
       <c r="B206">
         <v>2</v>
@@ -3286,7 +3286,7 @@
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>jpaulo.mma</v>
+        <v>sensei_rogerio_baltazar</v>
       </c>
       <c r="B207">
         <v>2</v>
@@ -3300,7 +3300,7 @@
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>william_beckett12345</v>
+        <v>jpaulo.mma</v>
       </c>
       <c r="B208">
         <v>2</v>
@@ -3314,7 +3314,7 @@
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>_falcao95_</v>
+        <v>william_beckett12345</v>
       </c>
       <c r="B209">
         <v>2</v>
@@ -3328,7 +3328,7 @@
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>janyson.s</v>
+        <v>_falcao95_</v>
       </c>
       <c r="B210">
         <v>2</v>
@@ -3342,7 +3342,7 @@
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>rodrigo.personal.muaythai</v>
+        <v>janyson.s</v>
       </c>
       <c r="B211">
         <v>2</v>
@@ -3356,7 +3356,7 @@
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>andre_cr_daniel</v>
+        <v>rodrigo.personal.muaythai</v>
       </c>
       <c r="B212">
         <v>2</v>
@@ -3370,7 +3370,7 @@
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>wilsinho.campos</v>
+        <v>andre_cr_daniel</v>
       </c>
       <c r="B213">
         <v>2</v>
@@ -3384,7 +3384,7 @@
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>jheffzao</v>
+        <v>wilsinho.campos</v>
       </c>
       <c r="B214">
         <v>2</v>
@@ -3398,41 +3398,41 @@
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>felipedasilvalucas.bjj</v>
+        <v>jheffzao</v>
       </c>
       <c r="B215">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C215">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D215">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>motumbo_jr</v>
+        <v>felipedasilvalucas.bjj</v>
       </c>
       <c r="B216">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C216">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D216">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>julianoalicate</v>
+        <v>motumbo_jr</v>
       </c>
       <c r="B217">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C217">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D217">
         <v>1</v>
@@ -3440,13 +3440,13 @@
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>cairorochamma</v>
+        <v>julianoalicate</v>
       </c>
       <c r="B218">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C218">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D218">
         <v>1</v>
@@ -3454,41 +3454,41 @@
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>victus_torquatus</v>
+        <v>cairorochamma</v>
       </c>
       <c r="B219">
         <v>2</v>
       </c>
       <c r="C219">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D219">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>alexsandra_kairos</v>
+        <v>victus_torquatus</v>
       </c>
       <c r="B220">
         <v>2</v>
       </c>
       <c r="C220">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D220">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>tuizainocenciorodrigues</v>
+        <v>alexsandra_kairos</v>
       </c>
       <c r="B221">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C221">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D221">
         <v>0</v>
@@ -3496,7 +3496,7 @@
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>jocyrefan_bjj_mma</v>
+        <v>tuizainocenciorodrigues</v>
       </c>
       <c r="B222">
         <v>3</v>
@@ -3510,7 +3510,7 @@
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>multiplicaaba</v>
+        <v>jocyrefan_bjj_mma</v>
       </c>
       <c r="B223">
         <v>3</v>
@@ -3524,13 +3524,13 @@
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>disk_egg</v>
+        <v>multiplicaaba</v>
       </c>
       <c r="B224">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C224">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D224">
         <v>0</v>
@@ -3538,80 +3538,80 @@
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>joandersontubarao_ufc</v>
+        <v>disk_egg</v>
       </c>
       <c r="B225">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C225">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D225">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>jean_ferreira_br</v>
+        <v>joandersontubarao_ufc</v>
       </c>
       <c r="B226">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C226">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D226">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>jose_luiz_thome</v>
+        <v>jean_ferreira_br</v>
       </c>
       <c r="B227">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C227">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D227">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>efsantos.oficial</v>
+        <v>jose_luiz_thome</v>
       </c>
       <c r="B228">
         <v>1</v>
       </c>
       <c r="C228">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D228">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>ufc_paramountsports</v>
+        <v>efsantos.oficial</v>
       </c>
       <c r="B229">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C229">
         <v>1</v>
       </c>
       <c r="D229">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>marifferreirac</v>
+        <v>ufc_paramountsports</v>
       </c>
       <c r="B230">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C230">
         <v>1</v>
@@ -3622,35 +3622,35 @@
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>pauloserrati</v>
+        <v>marifferreirac</v>
       </c>
       <c r="B231">
         <v>1</v>
       </c>
       <c r="C231">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D231">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>mineirinho_jj</v>
+        <v>pauloserrati</v>
       </c>
       <c r="B232">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C232">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D232">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>juliochagasmma</v>
+        <v>mineirinho_jj</v>
       </c>
       <c r="B233">
         <v>2</v>
@@ -3664,35 +3664,35 @@
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>orafao1</v>
+        <v>juliochagasmma</v>
       </c>
       <c r="B234">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C234">
         <v>0</v>
       </c>
       <c r="D234">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>lopesbrunao</v>
+        <v>orafao1</v>
       </c>
       <c r="B235">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C235">
         <v>0</v>
       </c>
       <c r="D235">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>claudiaottoni19</v>
+        <v>lopesbrunao</v>
       </c>
       <c r="B236">
         <v>2</v>
@@ -3706,7 +3706,7 @@
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>sr.valter</v>
+        <v>claudiaottoni19</v>
       </c>
       <c r="B237">
         <v>2</v>
@@ -3720,7 +3720,7 @@
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>marcos.jordao.bjj</v>
+        <v>sr.valter</v>
       </c>
       <c r="B238">
         <v>2</v>
@@ -3734,49 +3734,49 @@
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>meol.socialmidia</v>
+        <v>marcos.jordao.bjj</v>
       </c>
       <c r="B239">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C239">
         <v>0</v>
       </c>
       <c r="D239">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>yamasakinhobjj</v>
+        <v>meol.socialmidia</v>
       </c>
       <c r="B240">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C240">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D240">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>mestreviniciusreviravolta</v>
+        <v>yamasakinhobjj</v>
       </c>
       <c r="B241">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C241">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D241">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>cami28_l</v>
+        <v>mestreviniciusreviravolta</v>
       </c>
       <c r="B242">
         <v>3</v>
@@ -3790,7 +3790,7 @@
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>flaviakaena</v>
+        <v>cami28_l</v>
       </c>
       <c r="B243">
         <v>3</v>
@@ -3804,133 +3804,133 @@
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>chrislima____</v>
+        <v>flaviakaena</v>
       </c>
       <c r="B244">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C244">
         <v>0</v>
       </c>
       <c r="D244">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>c.m_figth</v>
+        <v>chrislima____</v>
       </c>
       <c r="B245">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C245">
         <v>0</v>
       </c>
       <c r="D245">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>leo.ribeiro.bjj</v>
+        <v>c.m_figth</v>
       </c>
       <c r="B246">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C246">
         <v>0</v>
       </c>
       <c r="D246">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>e_car.doso</v>
+        <v>leo.ribeiro.bjj</v>
       </c>
       <c r="B247">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C247">
         <v>0</v>
       </c>
       <c r="D247">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>dgswillian</v>
+        <v>e_car.doso</v>
       </c>
       <c r="B248">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C248">
         <v>0</v>
       </c>
       <c r="D248">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>couragemma</v>
+        <v>dgswillian</v>
       </c>
       <c r="B249">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C249">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D249">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>kaua_limaofc</v>
+        <v>couragemma</v>
       </c>
       <c r="B250">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C250">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D250">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>ruangzk</v>
+        <v>kaua_limaofc</v>
       </c>
       <c r="B251">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C251">
         <v>0</v>
       </c>
       <c r="D251">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>emerson_lucaszx</v>
+        <v>ruangzk</v>
       </c>
       <c r="B252">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C252">
         <v>0</v>
       </c>
       <c r="D252">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>clouddhidden</v>
+        <v>emerson_lucaszx</v>
       </c>
       <c r="B253">
         <v>2</v>
@@ -3944,21 +3944,21 @@
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>_matheusifernandes</v>
+        <v>clouddhidden</v>
       </c>
       <c r="B254">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C254">
         <v>0</v>
       </c>
       <c r="D254">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>bryantank_</v>
+        <v>_matheusifernandes</v>
       </c>
       <c r="B255">
         <v>1</v>
@@ -3972,7 +3972,7 @@
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>ruan.arcanjo01</v>
+        <v>bryantank_</v>
       </c>
       <c r="B256">
         <v>1</v>
@@ -3986,7 +3986,7 @@
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>coyote_style_hair</v>
+        <v>ruan.arcanjo01</v>
       </c>
       <c r="B257">
         <v>1</v>
@@ -4000,83 +4000,83 @@
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>sueli_ferreira48</v>
+        <v>coyote_style_hair</v>
       </c>
       <c r="B258">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C258">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D258">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>edsoncostateixeirabjj</v>
+        <v>sueli_ferreira48</v>
       </c>
       <c r="B259">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C259">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D259">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>klein_hila</v>
+        <v>edsoncostateixeirabjj</v>
       </c>
       <c r="B260">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C260">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D260">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>jhonatas_ricardo</v>
+        <v>klein_hila</v>
       </c>
       <c r="B261">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C261">
         <v>1</v>
       </c>
       <c r="D261">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>vnciuss__df</v>
+        <v>jhonatas_ricardo</v>
       </c>
       <c r="B262">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C262">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D262">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>jhee_dias</v>
+        <v>vnciuss__df</v>
       </c>
       <c r="B263">
         <v>2</v>
       </c>
       <c r="C263">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D263">
         <v>0</v>
@@ -4084,7 +4084,7 @@
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>tassiogiloficial</v>
+        <v>jhee_dias</v>
       </c>
       <c r="B264">
         <v>2</v>
@@ -4098,35 +4098,35 @@
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>nicolasmarretabjj</v>
+        <v>tassiogiloficial</v>
       </c>
       <c r="B265">
         <v>2</v>
       </c>
       <c r="C265">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D265">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>richards_brusen</v>
+        <v>nicolasmarretabjj</v>
       </c>
       <c r="B266">
         <v>2</v>
       </c>
       <c r="C266">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D266">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>natalan_wilgner</v>
+        <v>richards_brusen</v>
       </c>
       <c r="B267">
         <v>2</v>
@@ -4140,7 +4140,7 @@
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>leticiamartinspro</v>
+        <v>natalan_wilgner</v>
       </c>
       <c r="B268">
         <v>2</v>
@@ -4154,69 +4154,69 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>danilo_marquesc</v>
+        <v>leticiamartinspro</v>
       </c>
       <c r="B269">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C269">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D269">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>lucasspaulista</v>
+        <v>danilo_marquesc</v>
       </c>
       <c r="B270">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C270">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D270">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>eltonqueirozpereira</v>
+        <v>lucasspaulista</v>
       </c>
       <c r="B271">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C271">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D271">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>elderdiascaneladeaco</v>
+        <v>eltonqueirozpereira</v>
       </c>
       <c r="B272">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C272">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D272">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>select_from_joao</v>
+        <v>elderdiascaneladeaco</v>
       </c>
       <c r="B273">
         <v>2</v>
       </c>
       <c r="C273">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D273">
         <v>0</v>
@@ -4224,16 +4224,16 @@
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>cristianpsicologo</v>
+        <v>select_from_joao</v>
       </c>
       <c r="B274">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C274">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D274">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="275">
@@ -5162,7 +5162,7 @@
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>ellen.cristinaaa</v>
+        <v>_jullianadacruz</v>
       </c>
       <c r="B341">
         <v>2</v>
@@ -5176,21 +5176,21 @@
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>fabiieju</v>
+        <v>ellen.cristinaaa</v>
       </c>
       <c r="B342">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C342">
         <v>0</v>
       </c>
       <c r="D342">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>marqueswanderson</v>
+        <v>fabiieju</v>
       </c>
       <c r="B343">
         <v>1</v>
@@ -5204,7 +5204,7 @@
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>adauto2505</v>
+        <v>marqueswanderson</v>
       </c>
       <c r="B344">
         <v>1</v>
@@ -5218,7 +5218,7 @@
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>joaogagoarta</v>
+        <v>adauto2505</v>
       </c>
       <c r="B345">
         <v>1</v>
@@ -5232,27 +5232,27 @@
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>dr.daniloduartefisio</v>
+        <v>joaogagoarta</v>
       </c>
       <c r="B346">
         <v>1</v>
       </c>
       <c r="C346">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D346">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>pablo_bvg</v>
+        <v>brcks4breakfast</v>
       </c>
       <c r="B347">
         <v>1</v>
       </c>
       <c r="C347">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D347">
         <v>1</v>
@@ -5260,63 +5260,63 @@
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>marceloscorzato</v>
+        <v>dr.daniloduartefisio</v>
       </c>
       <c r="B348">
         <v>1</v>
       </c>
       <c r="C348">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D348">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>sergio_alves_bjj</v>
+        <v>pablo_bvg</v>
       </c>
       <c r="B349">
         <v>1</v>
       </c>
       <c r="C349">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D349">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>treinaadorrafael</v>
+        <v>marceloscorzato</v>
       </c>
       <c r="B350">
         <v>1</v>
       </c>
       <c r="C350">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D350">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>estevaotoledo</v>
+        <v>sergio_alves_bjj</v>
       </c>
       <c r="B351">
         <v>1</v>
       </c>
       <c r="C351">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D351">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>ismael.marreta_ufc</v>
+        <v>treinaadorrafael</v>
       </c>
       <c r="B352">
         <v>1</v>
@@ -5330,13 +5330,13 @@
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>djsagatoficial</v>
+        <v>estevaotoledo</v>
       </c>
       <c r="B353">
         <v>1</v>
       </c>
       <c r="C353">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D353">
         <v>0</v>
@@ -5344,13 +5344,13 @@
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>yurimartins1_</v>
+        <v>ismael.marreta_ufc</v>
       </c>
       <c r="B354">
         <v>1</v>
       </c>
       <c r="C354">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D354">
         <v>0</v>
@@ -5358,13 +5358,13 @@
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>matheusteodoro_1</v>
+        <v>djsagatoficial</v>
       </c>
       <c r="B355">
         <v>1</v>
       </c>
       <c r="C355">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D355">
         <v>0</v>
@@ -5372,7 +5372,7 @@
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>maria.pereiradeoliveira.5283</v>
+        <v>yurimartins1_</v>
       </c>
       <c r="B356">
         <v>1</v>
@@ -5386,13 +5386,13 @@
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>kael_lyto</v>
+        <v>matheusteodoro_1</v>
       </c>
       <c r="B357">
         <v>1</v>
       </c>
       <c r="C357">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D357">
         <v>0</v>
@@ -5400,7 +5400,7 @@
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>kawannsenaboxe</v>
+        <v>maria.pereiradeoliveira.5283</v>
       </c>
       <c r="B358">
         <v>1</v>
@@ -5414,13 +5414,13 @@
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>guiiviieira_</v>
+        <v>kael_lyto</v>
       </c>
       <c r="B359">
         <v>1</v>
       </c>
       <c r="C359">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D359">
         <v>0</v>
@@ -5428,7 +5428,7 @@
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>cshigueo</v>
+        <v>kawannsenaboxe</v>
       </c>
       <c r="B360">
         <v>1</v>
@@ -5442,7 +5442,7 @@
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>vitorhugo_vtr</v>
+        <v>guiiviieira_</v>
       </c>
       <c r="B361">
         <v>1</v>
@@ -5456,7 +5456,7 @@
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>danni_goncalves12</v>
+        <v>cshigueo</v>
       </c>
       <c r="B362">
         <v>1</v>
@@ -5470,7 +5470,7 @@
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>mttsm._</v>
+        <v>vitorhugo_vtr</v>
       </c>
       <c r="B363">
         <v>1</v>
@@ -5484,7 +5484,7 @@
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>andrealvess02</v>
+        <v>danni_goncalves12</v>
       </c>
       <c r="B364">
         <v>1</v>
@@ -5498,7 +5498,7 @@
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>gildojiu</v>
+        <v>mttsm._</v>
       </c>
       <c r="B365">
         <v>1</v>
@@ -5512,13 +5512,13 @@
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>fagnerosensei</v>
+        <v>andrealvess02</v>
       </c>
       <c r="B366">
         <v>1</v>
       </c>
       <c r="C366">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D366">
         <v>0</v>
@@ -5526,13 +5526,13 @@
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>flavio.dequeiroz</v>
+        <v>gildojiu</v>
       </c>
       <c r="B367">
         <v>1</v>
       </c>
       <c r="C367">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D367">
         <v>0</v>
@@ -5540,13 +5540,13 @@
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>030sami</v>
+        <v>fagnerosensei</v>
       </c>
       <c r="B368">
         <v>1</v>
       </c>
       <c r="C368">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D368">
         <v>0</v>
@@ -5554,21 +5554,21 @@
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>giulia.fasolato</v>
+        <v>flavio.dequeiroz</v>
       </c>
       <c r="B369">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C369">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D369">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>selipereirapereira</v>
+        <v>030sami</v>
       </c>
       <c r="B370">
         <v>1</v>
@@ -5582,21 +5582,21 @@
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>d.silvamma</v>
+        <v>giulia.fasolato</v>
       </c>
       <c r="B371">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C371">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D371">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>kalindrafaria</v>
+        <v>selipereirapereira</v>
       </c>
       <c r="B372">
         <v>1</v>
@@ -5610,21 +5610,21 @@
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>igorsiqueiramma57</v>
+        <v>d.silvamma</v>
       </c>
       <c r="B373">
         <v>1</v>
       </c>
       <c r="C373">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D373">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>manoelwilliamdejesus</v>
+        <v>kalindrafaria</v>
       </c>
       <c r="B374">
         <v>1</v>
@@ -5638,21 +5638,21 @@
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>oniszczuk_ko</v>
+        <v>igorsiqueiramma57</v>
       </c>
       <c r="B375">
         <v>1</v>
       </c>
       <c r="C375">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D375">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>andreibjj</v>
+        <v>manoelwilliamdejesus</v>
       </c>
       <c r="B376">
         <v>1</v>
@@ -5666,7 +5666,7 @@
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>killemquick</v>
+        <v>oniszczuk_ko</v>
       </c>
       <c r="B377">
         <v>1</v>
@@ -5680,7 +5680,7 @@
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>chuck_tlp</v>
+        <v>andreibjj</v>
       </c>
       <c r="B378">
         <v>1</v>
@@ -5694,7 +5694,7 @@
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>henriquemmunhoz</v>
+        <v>killemquick</v>
       </c>
       <c r="B379">
         <v>1</v>
@@ -5708,7 +5708,7 @@
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>flavio_tuba8</v>
+        <v>chuck_tlp</v>
       </c>
       <c r="B380">
         <v>1</v>
@@ -5722,13 +5722,13 @@
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>koliseu.br</v>
+        <v>henriquemmunhoz</v>
       </c>
       <c r="B381">
         <v>1</v>
       </c>
       <c r="C381">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D381">
         <v>0</v>
@@ -5736,27 +5736,27 @@
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>aida_dos_sonhos</v>
+        <v>flavio_tuba8</v>
       </c>
       <c r="B382">
         <v>1</v>
       </c>
       <c r="C382">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D382">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>plmoreiraz</v>
+        <v>koliseu.br</v>
       </c>
       <c r="B383">
         <v>1</v>
       </c>
       <c r="C383">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D383">
         <v>0</v>
@@ -5764,21 +5764,21 @@
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>marianappedro</v>
+        <v>aida_dos_sonhos</v>
       </c>
       <c r="B384">
         <v>1</v>
       </c>
       <c r="C384">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D384">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>morena_ramos</v>
+        <v>plmoreiraz</v>
       </c>
       <c r="B385">
         <v>1</v>
@@ -5792,13 +5792,13 @@
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>yeslifeacademia</v>
+        <v>marianappedro</v>
       </c>
       <c r="B386">
         <v>1</v>
       </c>
       <c r="C386">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D386">
         <v>0</v>
@@ -5806,13 +5806,13 @@
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>ojaimerocha</v>
+        <v>morena_ramos</v>
       </c>
       <c r="B387">
         <v>1</v>
       </c>
       <c r="C387">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D387">
         <v>0</v>
@@ -5820,7 +5820,7 @@
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>percepcar</v>
+        <v>yeslifeacademia</v>
       </c>
       <c r="B388">
         <v>1</v>
@@ -5834,7 +5834,7 @@
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>edergama.mma</v>
+        <v>ojaimerocha</v>
       </c>
       <c r="B389">
         <v>1</v>
@@ -5848,21 +5848,21 @@
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>pedro_pavin_</v>
+        <v>percepcar</v>
       </c>
       <c r="B390">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C390">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D390">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>eliandropires</v>
+        <v>edergama.mma</v>
       </c>
       <c r="B391">
         <v>1</v>
@@ -5876,21 +5876,21 @@
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>_gabrielpego</v>
+        <v>pedro_pavin_</v>
       </c>
       <c r="B392">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C392">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D392">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>motumbo_team</v>
+        <v>eliandropires</v>
       </c>
       <c r="B393">
         <v>1</v>
@@ -5904,7 +5904,7 @@
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>eusoufernandosaito</v>
+        <v>_gabrielpego</v>
       </c>
       <c r="B394">
         <v>1</v>
@@ -5918,7 +5918,7 @@
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>jenifer.ciborg</v>
+        <v>motumbo_team</v>
       </c>
       <c r="B395">
         <v>1</v>
@@ -5932,7 +5932,7 @@
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>beabmendes_</v>
+        <v>eusoufernandosaito</v>
       </c>
       <c r="B396">
         <v>1</v>
@@ -5946,7 +5946,7 @@
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>felipefrancoufc</v>
+        <v>jenifer.ciborg</v>
       </c>
       <c r="B397">
         <v>1</v>
@@ -5960,7 +5960,7 @@
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>leonardoo_paixao</v>
+        <v>beabmendes_</v>
       </c>
       <c r="B398">
         <v>1</v>
@@ -5974,21 +5974,21 @@
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>antonioemanuel.13</v>
+        <v>felipefrancoufc</v>
       </c>
       <c r="B399">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C399">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D399">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>gasparjr1983</v>
+        <v>leonardoo_paixao</v>
       </c>
       <c r="B400">
         <v>1</v>
@@ -6002,21 +6002,21 @@
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>magnoddias</v>
+        <v>antonioemanuel.13</v>
       </c>
       <c r="B401">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C401">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D401">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>ballestarbosa</v>
+        <v>gasparjr1983</v>
       </c>
       <c r="B402">
         <v>1</v>
@@ -6030,7 +6030,7 @@
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>marcioticotobarbosa</v>
+        <v>magnoddias</v>
       </c>
       <c r="B403">
         <v>1</v>
@@ -6044,7 +6044,7 @@
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>renan.dniz</v>
+        <v>ballestarbosa</v>
       </c>
       <c r="B404">
         <v>1</v>
@@ -6058,7 +6058,7 @@
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>nunesjanjacomo</v>
+        <v>marcioticotobarbosa</v>
       </c>
       <c r="B405">
         <v>1</v>
@@ -6072,7 +6072,7 @@
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>eumarianojr</v>
+        <v>renan.dniz</v>
       </c>
       <c r="B406">
         <v>1</v>
@@ -6086,7 +6086,7 @@
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>cathya_ferreira</v>
+        <v>nunesjanjacomo</v>
       </c>
       <c r="B407">
         <v>1</v>
@@ -6100,7 +6100,7 @@
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>mmapalpitex</v>
+        <v>eumarianojr</v>
       </c>
       <c r="B408">
         <v>1</v>
@@ -6114,7 +6114,7 @@
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>george.laroque</v>
+        <v>cathya_ferreira</v>
       </c>
       <c r="B409">
         <v>1</v>
@@ -6128,7 +6128,7 @@
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>chillyfit007</v>
+        <v>mmapalpitex</v>
       </c>
       <c r="B410">
         <v>1</v>
@@ -6142,13 +6142,13 @@
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>rafaela_duaartee</v>
+        <v>george.laroque</v>
       </c>
       <c r="B411">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C411">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D411">
         <v>0</v>
@@ -6156,13 +6156,13 @@
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>wagner_alexandre_w_a</v>
+        <v>chillyfit007</v>
       </c>
       <c r="B412">
         <v>1</v>
       </c>
       <c r="C412">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D412">
         <v>0</v>
@@ -6170,13 +6170,13 @@
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>andre.legendre.10</v>
+        <v>rafaela_duaartee</v>
       </c>
       <c r="B413">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C413">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D413">
         <v>0</v>
@@ -6184,7 +6184,7 @@
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>phillipe.harry</v>
+        <v>wagner_alexandre_w_a</v>
       </c>
       <c r="B414">
         <v>1</v>
@@ -6198,7 +6198,7 @@
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>andrejetx</v>
+        <v>andre.legendre.10</v>
       </c>
       <c r="B415">
         <v>1</v>
@@ -6212,7 +6212,7 @@
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>leandro_motiv4</v>
+        <v>phillipe.harry</v>
       </c>
       <c r="B416">
         <v>1</v>
@@ -6226,7 +6226,7 @@
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>olga.oliveira013</v>
+        <v>andrejetx</v>
       </c>
       <c r="B417">
         <v>1</v>
@@ -6240,7 +6240,7 @@
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>vinyrodriguesoficial</v>
+        <v>leandro_motiv4</v>
       </c>
       <c r="B418">
         <v>1</v>
@@ -6254,7 +6254,7 @@
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>leosacraa</v>
+        <v>olga.oliveira013</v>
       </c>
       <c r="B419">
         <v>1</v>
@@ -6268,7 +6268,7 @@
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>gutocriativo</v>
+        <v>vinyrodriguesoficial</v>
       </c>
       <c r="B420">
         <v>1</v>
@@ -6282,7 +6282,7 @@
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>igorfso_</v>
+        <v>leosacraa</v>
       </c>
       <c r="B421">
         <v>1</v>
@@ -6296,7 +6296,7 @@
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>gabrielsilva_mma</v>
+        <v>gutocriativo</v>
       </c>
       <c r="B422">
         <v>1</v>
@@ -6310,7 +6310,7 @@
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>lay_roqs</v>
+        <v>igorfso_</v>
       </c>
       <c r="B423">
         <v>1</v>
@@ -6324,7 +6324,7 @@
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>bigjota.music</v>
+        <v>gabrielsilva_mma</v>
       </c>
       <c r="B424">
         <v>1</v>
@@ -6338,7 +6338,7 @@
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>jhoninhaoficial031</v>
+        <v>lay_roqs</v>
       </c>
       <c r="B425">
         <v>1</v>
@@ -6352,7 +6352,7 @@
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>mth_fernandes031</v>
+        <v>bigjota.music</v>
       </c>
       <c r="B426">
         <v>1</v>
@@ -6366,7 +6366,7 @@
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>cezary_oleksiejczuk</v>
+        <v>jhoninhaoficial031</v>
       </c>
       <c r="B427">
         <v>1</v>
@@ -6380,7 +6380,7 @@
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>_alcantara.bru</v>
+        <v>mth_fernandes031</v>
       </c>
       <c r="B428">
         <v>1</v>
@@ -6394,7 +6394,7 @@
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>_puroosso88</v>
+        <v>cezary_oleksiejczuk</v>
       </c>
       <c r="B429">
         <v>1</v>
@@ -6408,7 +6408,7 @@
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>_rayysp</v>
+        <v>_alcantara.bru</v>
       </c>
       <c r="B430">
         <v>1</v>
@@ -6422,7 +6422,7 @@
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>cami.terra_</v>
+        <v>_puroosso88</v>
       </c>
       <c r="B431">
         <v>1</v>
@@ -6436,7 +6436,7 @@
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>gabicardoson</v>
+        <v>_rayysp</v>
       </c>
       <c r="B432">
         <v>1</v>
@@ -6450,7 +6450,7 @@
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>pietroshz</v>
+        <v>cami.terra_</v>
       </c>
       <c r="B433">
         <v>1</v>
@@ -6464,7 +6464,7 @@
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>___neller</v>
+        <v>gabicardoson</v>
       </c>
       <c r="B434">
         <v>1</v>
@@ -6478,7 +6478,7 @@
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>guilhermeefelix__</v>
+        <v>pietroshz</v>
       </c>
       <c r="B435">
         <v>1</v>
@@ -6492,7 +6492,7 @@
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>pativinisf</v>
+        <v>___neller</v>
       </c>
       <c r="B436">
         <v>1</v>
@@ -6506,7 +6506,7 @@
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>judadany</v>
+        <v>guilhermeefelix__</v>
       </c>
       <c r="B437">
         <v>1</v>
@@ -6520,7 +6520,7 @@
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>andre_alcausa</v>
+        <v>pativinisf</v>
       </c>
       <c r="B438">
         <v>1</v>
@@ -6534,7 +6534,7 @@
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>_fernunes</v>
+        <v>judadany</v>
       </c>
       <c r="B439">
         <v>1</v>
@@ -6548,7 +6548,7 @@
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>aloirmarcal</v>
+        <v>andre_alcausa</v>
       </c>
       <c r="B440">
         <v>1</v>
@@ -6562,7 +6562,7 @@
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>gilberto_7606</v>
+        <v>_fernunes</v>
       </c>
       <c r="B441">
         <v>1</v>
@@ -6576,7 +6576,7 @@
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>flazuera14</v>
+        <v>aloirmarcal</v>
       </c>
       <c r="B442">
         <v>1</v>
@@ -6590,7 +6590,7 @@
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>camii_bonfim</v>
+        <v>gilberto_7606</v>
       </c>
       <c r="B443">
         <v>1</v>
@@ -6604,7 +6604,7 @@
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>danlouiz.jj</v>
+        <v>flazuera14</v>
       </c>
       <c r="B444">
         <v>1</v>
@@ -6618,7 +6618,7 @@
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>gabriel_trevelin</v>
+        <v>camii_bonfim</v>
       </c>
       <c r="B445">
         <v>1</v>
@@ -6632,7 +6632,7 @@
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>_lsanchess_</v>
+        <v>danlouiz.jj</v>
       </c>
       <c r="B446">
         <v>1</v>
@@ -6646,7 +6646,7 @@
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>mr__rlk01</v>
+        <v>gabriel_trevelin</v>
       </c>
       <c r="B447">
         <v>1</v>
@@ -6660,7 +6660,7 @@
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>vitor_buck</v>
+        <v>_lsanchess_</v>
       </c>
       <c r="B448">
         <v>1</v>
@@ -6674,7 +6674,7 @@
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>fran.ruys</v>
+        <v>mr__rlk01</v>
       </c>
       <c r="B449">
         <v>1</v>
@@ -6688,7 +6688,7 @@
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>arthurhenrique.sx</v>
+        <v>vitor_buck</v>
       </c>
       <c r="B450">
         <v>1</v>
@@ -6702,7 +6702,7 @@
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>draanapaulaponceano</v>
+        <v>fran.ruys</v>
       </c>
       <c r="B451">
         <v>1</v>
@@ -6716,7 +6716,7 @@
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>saj_photo_miami</v>
+        <v>arthurhenrique.sx</v>
       </c>
       <c r="B452">
         <v>1</v>
@@ -6730,7 +6730,7 @@
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>alternativaremocoes</v>
+        <v>draanapaulaponceano</v>
       </c>
       <c r="B453">
         <v>1</v>
@@ -6744,7 +6744,7 @@
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>benivalentinn</v>
+        <v>saj_photo_miami</v>
       </c>
       <c r="B454">
         <v>1</v>
@@ -6758,7 +6758,7 @@
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>miguelrodriguesbjj</v>
+        <v>alternativaremocoes</v>
       </c>
       <c r="B455">
         <v>1</v>
@@ -6772,7 +6772,7 @@
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>navarro_9430</v>
+        <v>benivalentinn</v>
       </c>
       <c r="B456">
         <v>1</v>
@@ -6786,7 +6786,7 @@
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>charlesanthony2466</v>
+        <v>miguelrodriguesbjj</v>
       </c>
       <c r="B457">
         <v>1</v>
@@ -6800,7 +6800,7 @@
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>xavyeroficial</v>
+        <v>navarro_9430</v>
       </c>
       <c r="B458">
         <v>1</v>
@@ -6814,7 +6814,7 @@
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>maryanagandra</v>
+        <v>charlesanthony2466</v>
       </c>
       <c r="B459">
         <v>1</v>
@@ -6828,7 +6828,7 @@
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>katiaecarreraf</v>
+        <v>xavyeroficial</v>
       </c>
       <c r="B460">
         <v>1</v>
@@ -6842,7 +6842,7 @@
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>geraldocnetomma</v>
+        <v>maryanagandra</v>
       </c>
       <c r="B461">
         <v>1</v>
@@ -6856,13 +6856,13 @@
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>marinealcausa</v>
+        <v>katiaecarreraf</v>
       </c>
       <c r="B462">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C462">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D462">
         <v>0</v>
@@ -6870,7 +6870,7 @@
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>artemio_bjj</v>
+        <v>geraldocnetomma</v>
       </c>
       <c r="B463">
         <v>1</v>
@@ -6884,13 +6884,13 @@
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>carolinne.xwp</v>
+        <v>marinealcausa</v>
       </c>
       <c r="B464">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C464">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D464">
         <v>0</v>
@@ -6898,7 +6898,7 @@
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>isaac.bah_starinazzo</v>
+        <v>artemio_bjj</v>
       </c>
       <c r="B465">
         <v>1</v>
@@ -6912,7 +6912,7 @@
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>lara.rpr</v>
+        <v>carolinne.xwp</v>
       </c>
       <c r="B466">
         <v>1</v>
@@ -6926,7 +6926,7 @@
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>codasqueves</v>
+        <v>isaac.bah_starinazzo</v>
       </c>
       <c r="B467">
         <v>1</v>
@@ -6940,7 +6940,7 @@
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>yan_touro_.7766</v>
+        <v>lara.rpr</v>
       </c>
       <c r="B468">
         <v>1</v>
@@ -6954,7 +6954,7 @@
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>brothers_of_life</v>
+        <v>codasqueves</v>
       </c>
       <c r="B469">
         <v>1</v>
@@ -6968,7 +6968,7 @@
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>teacherthalesyouplus</v>
+        <v>yan_touro_.7766</v>
       </c>
       <c r="B470">
         <v>1</v>
@@ -6982,7 +6982,7 @@
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>minotaurinho</v>
+        <v>brothers_of_life</v>
       </c>
       <c r="B471">
         <v>1</v>
@@ -6996,7 +6996,7 @@
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>anahangelica</v>
+        <v>teacherthalesyouplus</v>
       </c>
       <c r="B472">
         <v>1</v>
@@ -7010,7 +7010,7 @@
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>frankikolimabjj</v>
+        <v>minotaurinho</v>
       </c>
       <c r="B473">
         <v>1</v>
@@ -7024,7 +7024,7 @@
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>tonketjudes</v>
+        <v>anahangelica</v>
       </c>
       <c r="B474">
         <v>1</v>
@@ -7038,7 +7038,7 @@
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>_eliasffx</v>
+        <v>frankikolimabjj</v>
       </c>
       <c r="B475">
         <v>1</v>
@@ -7052,7 +7052,7 @@
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>pdfiv</v>
+        <v>tonketjudes</v>
       </c>
       <c r="B476">
         <v>1</v>
@@ -7066,7 +7066,7 @@
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>mariaraimundad940</v>
+        <v>_eliasffx</v>
       </c>
       <c r="B477">
         <v>1</v>
@@ -7080,7 +7080,7 @@
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>gabesantos.13</v>
+        <v>pdfiv</v>
       </c>
       <c r="B478">
         <v>1</v>
@@ -7094,7 +7094,7 @@
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>euvitormirandaa</v>
+        <v>mariaraimundad940</v>
       </c>
       <c r="B479">
         <v>1</v>
@@ -7108,7 +7108,7 @@
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>gandra.julya</v>
+        <v>gabesantos.13</v>
       </c>
       <c r="B480">
         <v>1</v>
@@ -7122,7 +7122,7 @@
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>espacomarcialino</v>
+        <v>euvitormirandaa</v>
       </c>
       <c r="B481">
         <v>1</v>
@@ -7136,7 +7136,7 @@
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>azulcapoeirabjj</v>
+        <v>gandra.julya</v>
       </c>
       <c r="B482">
         <v>1</v>
@@ -7150,7 +7150,7 @@
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>andreiaatleta</v>
+        <v>espacomarcialino</v>
       </c>
       <c r="B483">
         <v>1</v>
@@ -7164,7 +7164,7 @@
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>luhluhm</v>
+        <v>azulcapoeirabjj</v>
       </c>
       <c r="B484">
         <v>1</v>
@@ -7178,7 +7178,7 @@
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>jack_hashimoto</v>
+        <v>andreiaatleta</v>
       </c>
       <c r="B485">
         <v>1</v>
@@ -7192,7 +7192,7 @@
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>do_caex_wandel</v>
+        <v>luhluhm</v>
       </c>
       <c r="B486">
         <v>1</v>
@@ -7206,7 +7206,7 @@
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>eu_felipe_leite</v>
+        <v>jack_hashimoto</v>
       </c>
       <c r="B487">
         <v>1</v>
@@ -7220,7 +7220,7 @@
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>selma.ribeirotr</v>
+        <v>do_caex_wandel</v>
       </c>
       <c r="B488">
         <v>1</v>
@@ -7234,7 +7234,7 @@
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>valqsm</v>
+        <v>eu_felipe_leite</v>
       </c>
       <c r="B489">
         <v>1</v>
@@ -7248,7 +7248,7 @@
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>nutrivan.alves</v>
+        <v>selma.ribeirotr</v>
       </c>
       <c r="B490">
         <v>1</v>
@@ -7262,7 +7262,7 @@
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>allisonestuchi_fisioterapeuta</v>
+        <v>valqsm</v>
       </c>
       <c r="B491">
         <v>1</v>
@@ -7276,7 +7276,7 @@
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>sidneibabu</v>
+        <v>nutrivan.alves</v>
       </c>
       <c r="B492">
         <v>1</v>
@@ -7290,7 +7290,7 @@
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>muriloo__ferreira</v>
+        <v>allisonestuchi_fisioterapeuta</v>
       </c>
       <c r="B493">
         <v>1</v>
@@ -7304,7 +7304,7 @@
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>drfelipeoliveira_adv</v>
+        <v>sidneibabu</v>
       </c>
       <c r="B494">
         <v>1</v>
@@ -7318,7 +7318,7 @@
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>turmanmma</v>
+        <v>muriloo__ferreira</v>
       </c>
       <c r="B495">
         <v>1</v>
@@ -7332,7 +7332,7 @@
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>andre_luizdj</v>
+        <v>drfelipeoliveira_adv</v>
       </c>
       <c r="B496">
         <v>1</v>
@@ -7346,7 +7346,7 @@
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>lumarasantosjj</v>
+        <v>turmanmma</v>
       </c>
       <c r="B497">
         <v>1</v>
@@ -7360,7 +7360,7 @@
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>donrey_42</v>
+        <v>andre_luizdj</v>
       </c>
       <c r="B498">
         <v>1</v>
@@ -7374,7 +7374,7 @@
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>personalmaju</v>
+        <v>lumarasantosjj</v>
       </c>
       <c r="B499">
         <v>1</v>
@@ -7388,7 +7388,7 @@
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>itsmayraregina</v>
+        <v>donrey_42</v>
       </c>
       <c r="B500">
         <v>1</v>
@@ -7402,7 +7402,7 @@
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>fototatico</v>
+        <v>personalmaju</v>
       </c>
       <c r="B501">
         <v>1</v>
@@ -7416,7 +7416,7 @@
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>michel.juliano.barbershop</v>
+        <v>itsmayraregina</v>
       </c>
       <c r="B502">
         <v>1</v>
@@ -7430,7 +7430,7 @@
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>ruperto_696</v>
+        <v>fototatico</v>
       </c>
       <c r="B503">
         <v>1</v>
@@ -7444,7 +7444,7 @@
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>diegomoisesribeiro</v>
+        <v>michel.juliano.barbershop</v>
       </c>
       <c r="B504">
         <v>1</v>
@@ -7458,7 +7458,7 @@
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>lucca_bjj_01</v>
+        <v>ruperto_696</v>
       </c>
       <c r="B505">
         <v>1</v>
@@ -7472,7 +7472,7 @@
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>calebe1000grau</v>
+        <v>diegomoisesribeiro</v>
       </c>
       <c r="B506">
         <v>1</v>
@@ -7486,7 +7486,7 @@
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>brunito_bernardo</v>
+        <v>lucca_bjj_01</v>
       </c>
       <c r="B507">
         <v>1</v>
@@ -7500,7 +7500,7 @@
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>clarianavillasboasoficial</v>
+        <v>calebe1000grau</v>
       </c>
       <c r="B508">
         <v>1</v>
@@ -7514,7 +7514,7 @@
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>gladyador_do_asa</v>
+        <v>brunito_bernardo</v>
       </c>
       <c r="B509">
         <v>1</v>
@@ -7528,7 +7528,7 @@
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>aureooficial</v>
+        <v>clarianavillasboasoficial</v>
       </c>
       <c r="B510">
         <v>1</v>
@@ -7542,7 +7542,7 @@
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>williamjanser</v>
+        <v>gladyador_do_asa</v>
       </c>
       <c r="B511">
         <v>1</v>
@@ -7556,7 +7556,7 @@
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>jeremyericjacobs</v>
+        <v>aureooficial</v>
       </c>
       <c r="B512">
         <v>1</v>
@@ -7570,7 +7570,7 @@
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>chicinvancity</v>
+        <v>williamjanser</v>
       </c>
       <c r="B513">
         <v>1</v>
@@ -7584,7 +7584,7 @@
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>susiemelchionda</v>
+        <v>jeremyericjacobs</v>
       </c>
       <c r="B514">
         <v>1</v>
@@ -7598,7 +7598,7 @@
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>satsangbjj</v>
+        <v>chicinvancity</v>
       </c>
       <c r="B515">
         <v>1</v>
@@ -7612,7 +7612,7 @@
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>gallupistrengthconditioning</v>
+        <v>susiemelchionda</v>
       </c>
       <c r="B516">
         <v>1</v>
@@ -7626,7 +7626,7 @@
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>danibastiaan</v>
+        <v>satsangbjj</v>
       </c>
       <c r="B517">
         <v>1</v>
@@ -7640,7 +7640,7 @@
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>gilcilenecristina</v>
+        <v>gallupistrengthconditioning</v>
       </c>
       <c r="B518">
         <v>1</v>
@@ -7654,7 +7654,7 @@
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>andreaapurinaoficial</v>
+        <v>danibastiaan</v>
       </c>
       <c r="B519">
         <v>1</v>
@@ -7668,7 +7668,7 @@
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>alehh_novaes</v>
+        <v>gilcilenecristina</v>
       </c>
       <c r="B520">
         <v>1</v>
@@ -7682,7 +7682,7 @@
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>franklinamaral</v>
+        <v>andreaapurinaoficial</v>
       </c>
       <c r="B521">
         <v>1</v>
@@ -7696,7 +7696,7 @@
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>valbersonsantoss</v>
+        <v>alehh_novaes</v>
       </c>
       <c r="B522">
         <v>1</v>
@@ -7710,7 +7710,7 @@
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>j.borgespz</v>
+        <v>franklinamaral</v>
       </c>
       <c r="B523">
         <v>1</v>
@@ -7724,7 +7724,7 @@
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>gpedroza1</v>
+        <v>valbersonsantoss</v>
       </c>
       <c r="B524">
         <v>1</v>
@@ -7738,7 +7738,7 @@
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>almir_gdf</v>
+        <v>j.borgespz</v>
       </c>
       <c r="B525">
         <v>1</v>
@@ -7752,7 +7752,7 @@
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>renancarlini</v>
+        <v>gpedroza1</v>
       </c>
       <c r="B526">
         <v>1</v>
@@ -7766,7 +7766,7 @@
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>lucaswallaceftt</v>
+        <v>almir_gdf</v>
       </c>
       <c r="B527">
         <v>1</v>
@@ -7780,7 +7780,7 @@
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>lilianvillaca_</v>
+        <v>renancarlini</v>
       </c>
       <c r="B528">
         <v>1</v>
@@ -7794,7 +7794,7 @@
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>jose_carlos_baixote</v>
+        <v>lucaswallaceftt</v>
       </c>
       <c r="B529">
         <v>1</v>
@@ -7808,7 +7808,7 @@
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>projeto_amigos_de_ouro</v>
+        <v>lilianvillaca_</v>
       </c>
       <c r="B530">
         <v>1</v>
@@ -7822,7 +7822,7 @@
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>gratidao_jesus2026</v>
+        <v>jose_carlos_baixote</v>
       </c>
       <c r="B531">
         <v>1</v>
@@ -7836,7 +7836,7 @@
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>sabe_de_uma_coisa2026</v>
+        <v>projeto_amigos_de_ouro</v>
       </c>
       <c r="B532">
         <v>1</v>
@@ -7850,7 +7850,7 @@
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>alinedoprojeto</v>
+        <v>gratidao_jesus2026</v>
       </c>
       <c r="B533">
         <v>1</v>
@@ -7864,7 +7864,7 @@
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>dani120690</v>
+        <v>sabe_de_uma_coisa2026</v>
       </c>
       <c r="B534">
         <v>1</v>
@@ -7878,7 +7878,7 @@
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>raonasthai</v>
+        <v>alinedoprojeto</v>
       </c>
       <c r="B535">
         <v>1</v>
@@ -7892,7 +7892,7 @@
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>adonaibjj_grip</v>
+        <v>dani120690</v>
       </c>
       <c r="B536">
         <v>1</v>
@@ -7906,7 +7906,7 @@
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>arturbambam</v>
+        <v>raonasthai</v>
       </c>
       <c r="B537">
         <v>1</v>
@@ -7920,7 +7920,7 @@
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>cebolajj167</v>
+        <v>adonaibjj_grip</v>
       </c>
       <c r="B538">
         <v>1</v>
@@ -7934,7 +7934,7 @@
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>danieljsantoss_</v>
+        <v>arturbambam</v>
       </c>
       <c r="B539">
         <v>1</v>
@@ -7948,7 +7948,7 @@
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>hermaan10_</v>
+        <v>cebolajj167</v>
       </c>
       <c r="B540">
         <v>1</v>
@@ -7962,7 +7962,7 @@
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>markakasocks</v>
+        <v>danieljsantoss_</v>
       </c>
       <c r="B541">
         <v>1</v>
@@ -7976,7 +7976,7 @@
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>hunter.mccrary</v>
+        <v>hermaan10_</v>
       </c>
       <c r="B542">
         <v>1</v>
@@ -7990,7 +7990,7 @@
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>davidpina_047</v>
+        <v>markakasocks</v>
       </c>
       <c r="B543">
         <v>1</v>
@@ -8004,7 +8004,7 @@
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>odivaldo_lobo</v>
+        <v>hunter.mccrary</v>
       </c>
       <c r="B544">
         <v>1</v>
@@ -8018,7 +8018,7 @@
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>rodrigojansen_</v>
+        <v>davidpina_047</v>
       </c>
       <c r="B545">
         <v>1</v>
@@ -8032,7 +8032,7 @@
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>flavia_gomes_29</v>
+        <v>odivaldo_lobo</v>
       </c>
       <c r="B546">
         <v>1</v>
@@ -8046,7 +8046,7 @@
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>pelevermelha.uniformes</v>
+        <v>rodrigojansen_</v>
       </c>
       <c r="B547">
         <v>1</v>
@@ -8060,7 +8060,7 @@
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>joao_lins_muaythai</v>
+        <v>flavia_gomes_29</v>
       </c>
       <c r="B548">
         <v>1</v>
@@ -8074,7 +8074,7 @@
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>omarcotomaz</v>
+        <v>pelevermelha.uniformes</v>
       </c>
       <c r="B549">
         <v>1</v>
@@ -8088,7 +8088,7 @@
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>alphavillesup</v>
+        <v>joao_lins_muaythai</v>
       </c>
       <c r="B550">
         <v>1</v>
@@ -8102,7 +8102,7 @@
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>ricieritonan</v>
+        <v>omarcotomaz</v>
       </c>
       <c r="B551">
         <v>1</v>
@@ -8116,7 +8116,7 @@
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>lucasampaio</v>
+        <v>alphavillesup</v>
       </c>
       <c r="B552">
         <v>1</v>
@@ -8130,7 +8130,7 @@
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>manmoska</v>
+        <v>ricieritonan</v>
       </c>
       <c r="B553">
         <v>1</v>
@@ -8144,7 +8144,7 @@
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>renatoevangelistaa</v>
+        <v>lucasampaio</v>
       </c>
       <c r="B554">
         <v>1</v>
@@ -8158,7 +8158,7 @@
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>cassius.paula</v>
+        <v>manmoska</v>
       </c>
       <c r="B555">
         <v>1</v>
@@ -8172,7 +8172,7 @@
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>ctt.casaestopteam</v>
+        <v>renatoevangelistaa</v>
       </c>
       <c r="B556">
         <v>1</v>
@@ -8186,7 +8186,7 @@
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>moisespira</v>
+        <v>cassius.paula</v>
       </c>
       <c r="B557">
         <v>1</v>
@@ -8200,7 +8200,7 @@
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>rodrigolidiosales</v>
+        <v>ctt.casaestopteam</v>
       </c>
       <c r="B558">
         <v>1</v>
@@ -8214,7 +8214,7 @@
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>claudioribeiro_ufc</v>
+        <v>moisespira</v>
       </c>
       <c r="B559">
         <v>1</v>
@@ -8228,7 +8228,7 @@
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>marciocatenacci</v>
+        <v>rodrigolidiosales</v>
       </c>
       <c r="B560">
         <v>1</v>
@@ -8242,7 +8242,7 @@
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>cristiane.c.santana</v>
+        <v>claudioribeiro_ufc</v>
       </c>
       <c r="B561">
         <v>1</v>
@@ -8256,7 +8256,7 @@
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>ariel_alvees</v>
+        <v>marciocatenacci</v>
       </c>
       <c r="B562">
         <v>1</v>
@@ -8270,7 +8270,7 @@
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>flahvinhotreinador</v>
+        <v>cristiane.c.santana</v>
       </c>
       <c r="B563">
         <v>1</v>
@@ -8284,7 +8284,7 @@
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>selma.oscar12</v>
+        <v>ariel_alvees</v>
       </c>
       <c r="B564">
         <v>1</v>
@@ -8298,7 +8298,7 @@
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>romulobelarmino</v>
+        <v>flahvinhotreinador</v>
       </c>
       <c r="B565">
         <v>1</v>
@@ -8312,7 +8312,7 @@
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>alberto_garcia_queiroz_junior</v>
+        <v>selma.oscar12</v>
       </c>
       <c r="B566">
         <v>1</v>
@@ -8326,7 +8326,7 @@
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>isasantos1404</v>
+        <v>romulobelarmino</v>
       </c>
       <c r="B567">
         <v>1</v>
@@ -8340,7 +8340,7 @@
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>fernandamourabjj</v>
+        <v>alberto_garcia_queiroz_junior</v>
       </c>
       <c r="B568">
         <v>1</v>
@@ -8354,7 +8354,7 @@
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>larissamartinsbjj</v>
+        <v>isasantos1404</v>
       </c>
       <c r="B569">
         <v>1</v>
@@ -8368,7 +8368,7 @@
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>gabrielsoaresbjj</v>
+        <v>fernandamourabjj</v>
       </c>
       <c r="B570">
         <v>1</v>
@@ -8382,7 +8382,7 @@
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>leitefelippez</v>
+        <v>larissamartinsbjj</v>
       </c>
       <c r="B571">
         <v>1</v>
@@ -8396,7 +8396,7 @@
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>israelbahiensebraz</v>
+        <v>gabrielsoaresbjj</v>
       </c>
       <c r="B572">
         <v>1</v>
@@ -8410,7 +8410,7 @@
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>titosbjj</v>
+        <v>leitefelippez</v>
       </c>
       <c r="B573">
         <v>1</v>
@@ -8424,7 +8424,7 @@
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>aldomanuel1994</v>
+        <v>israelbahiensebraz</v>
       </c>
       <c r="B574">
         <v>1</v>
@@ -8438,7 +8438,7 @@
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>x_xpatto</v>
+        <v>titosbjj</v>
       </c>
       <c r="B575">
         <v>1</v>
@@ -8452,7 +8452,7 @@
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>keep.itpushinnn</v>
+        <v>aldomanuel1994</v>
       </c>
       <c r="B576">
         <v>1</v>
@@ -8466,7 +8466,7 @@
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>johnnydesinfluencer</v>
+        <v>x_xpatto</v>
       </c>
       <c r="B577">
         <v>1</v>
@@ -8480,7 +8480,7 @@
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>ana.cristina.uno</v>
+        <v>keep.itpushinnn</v>
       </c>
       <c r="B578">
         <v>1</v>
@@ -8494,7 +8494,7 @@
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>pbmoments_</v>
+        <v>johnnydesinfluencer</v>
       </c>
       <c r="B579">
         <v>1</v>
@@ -8508,7 +8508,7 @@
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>rick.santosz</v>
+        <v>ana.cristina.uno</v>
       </c>
       <c r="B580">
         <v>1</v>
@@ -8522,7 +8522,7 @@
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>eriikdossantoos</v>
+        <v>pbmoments_</v>
       </c>
       <c r="B581">
         <v>1</v>
@@ -8536,7 +8536,7 @@
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>sp__theus</v>
+        <v>rick.santosz</v>
       </c>
       <c r="B582">
         <v>1</v>
@@ -8550,7 +8550,7 @@
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>guihs_cardoso</v>
+        <v>eriikdossantoos</v>
       </c>
       <c r="B583">
         <v>1</v>
@@ -8564,7 +8564,7 @@
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>jeffersonliu2022</v>
+        <v>sp__theus</v>
       </c>
       <c r="B584">
         <v>1</v>
@@ -8578,7 +8578,7 @@
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>pettys2298</v>
+        <v>guihs_cardoso</v>
       </c>
       <c r="B585">
         <v>1</v>
@@ -8592,7 +8592,7 @@
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>jhonny.2302_aritamma</v>
+        <v>jeffersonliu2022</v>
       </c>
       <c r="B586">
         <v>1</v>
@@ -8606,7 +8606,7 @@
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>ph_castroh</v>
+        <v>pettys2298</v>
       </c>
       <c r="B587">
         <v>1</v>
@@ -8620,7 +8620,7 @@
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>paulokami.mma</v>
+        <v>jhonny.2302_aritamma</v>
       </c>
       <c r="B588">
         <v>1</v>
@@ -8634,7 +8634,7 @@
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>generaldantas</v>
+        <v>ph_castroh</v>
       </c>
       <c r="B589">
         <v>1</v>
@@ -8648,7 +8648,7 @@
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>gi.liimaa_</v>
+        <v>paulokami.mma</v>
       </c>
       <c r="B590">
         <v>1</v>
@@ -8662,7 +8662,7 @@
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>_murilo_06</v>
+        <v>generaldantas</v>
       </c>
       <c r="B591">
         <v>1</v>
@@ -8676,7 +8676,7 @@
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>biabezerra88</v>
+        <v>gi.liimaa_</v>
       </c>
       <c r="B592">
         <v>1</v>
@@ -8690,7 +8690,7 @@
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>geovannaalc_</v>
+        <v>_murilo_06</v>
       </c>
       <c r="B593">
         <v>1</v>
@@ -8704,7 +8704,7 @@
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>joselia_1980</v>
+        <v>biabezerra88</v>
       </c>
       <c r="B594">
         <v>1</v>
@@ -8718,7 +8718,7 @@
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>silva_junior1979</v>
+        <v>geovannaalc_</v>
       </c>
       <c r="B595">
         <v>1</v>
@@ -8732,7 +8732,7 @@
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>andreloliva12</v>
+        <v>joselia_1980</v>
       </c>
       <c r="B596">
         <v>1</v>
@@ -8746,7 +8746,7 @@
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>soniarochaco</v>
+        <v>silva_junior1979</v>
       </c>
       <c r="B597">
         <v>1</v>
@@ -8760,7 +8760,7 @@
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>leandro_pedro7</v>
+        <v>andreloliva12</v>
       </c>
       <c r="B598">
         <v>1</v>
@@ -8774,7 +8774,7 @@
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>camillinhamma</v>
+        <v>soniarochaco</v>
       </c>
       <c r="B599">
         <v>1</v>
@@ -8788,7 +8788,7 @@
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>martins.rauanee</v>
+        <v>leandro_pedro7</v>
       </c>
       <c r="B600">
         <v>1</v>
@@ -8802,7 +8802,7 @@
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>ever.soulson</v>
+        <v>camillinhamma</v>
       </c>
       <c r="B601">
         <v>1</v>
@@ -8816,7 +8816,7 @@
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>mestrevascobento</v>
+        <v>martins.rauanee</v>
       </c>
       <c r="B602">
         <v>1</v>
@@ -8830,7 +8830,7 @@
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>bernardocavalcanti1</v>
+        <v>ever.soulson</v>
       </c>
       <c r="B603">
         <v>1</v>
@@ -8844,7 +8844,7 @@
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>terapeuta_moniquedias</v>
+        <v>mestrevascobento</v>
       </c>
       <c r="B604">
         <v>1</v>
@@ -8858,7 +8858,7 @@
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>santos39roger</v>
+        <v>bernardocavalcanti1</v>
       </c>
       <c r="B605">
         <v>1</v>
@@ -8872,7 +8872,7 @@
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>dcoops2</v>
+        <v>terapeuta_moniquedias</v>
       </c>
       <c r="B606">
         <v>1</v>
@@ -8886,7 +8886,7 @@
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>ricardosousa811</v>
+        <v>santos39roger</v>
       </c>
       <c r="B607">
         <v>1</v>
@@ -8900,7 +8900,7 @@
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>ludelmaraujo</v>
+        <v>dcoops2</v>
       </c>
       <c r="B608">
         <v>1</v>
@@ -8914,7 +8914,7 @@
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>homemdeita</v>
+        <v>ricardosousa811</v>
       </c>
       <c r="B609">
         <v>1</v>
@@ -8928,7 +8928,7 @@
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>victorxferreira</v>
+        <v>ludelmaraujo</v>
       </c>
       <c r="B610">
         <v>1</v>
@@ -8942,7 +8942,7 @@
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>eimysalazar</v>
+        <v>homemdeita</v>
       </c>
       <c r="B611">
         <v>1</v>
@@ -8956,7 +8956,7 @@
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>oficialrichardsilva_ice_men</v>
+        <v>victorxferreira</v>
       </c>
       <c r="B612">
         <v>1</v>
@@ -8970,7 +8970,7 @@
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>axiaaly</v>
+        <v>eimysalazar</v>
       </c>
       <c r="B613">
         <v>1</v>
@@ -8984,7 +8984,7 @@
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>renatogomes769</v>
+        <v>oficialrichardsilva_ice_men</v>
       </c>
       <c r="B614">
         <v>1</v>
@@ -8998,7 +8998,7 @@
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>adrianoblessed89</v>
+        <v>axiaaly</v>
       </c>
       <c r="B615">
         <v>1</v>
@@ -9012,7 +9012,7 @@
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>dinhomoraisoficial</v>
+        <v>renatogomes769</v>
       </c>
       <c r="B616">
         <v>1</v>
@@ -9026,7 +9026,7 @@
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>santosriveiros18737383</v>
+        <v>adrianoblessed89</v>
       </c>
       <c r="B617">
         <v>1</v>
@@ -9040,7 +9040,7 @@
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>sr.dpaula10</v>
+        <v>dinhomoraisoficial</v>
       </c>
       <c r="B618">
         <v>1</v>
@@ -9054,7 +9054,7 @@
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>pazzini__</v>
+        <v>santosriveiros18737383</v>
       </c>
       <c r="B619">
         <v>1</v>
@@ -9068,7 +9068,7 @@
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>thiagomoisesmma</v>
+        <v>sr.dpaula10</v>
       </c>
       <c r="B620">
         <v>1</v>
@@ -9082,7 +9082,7 @@
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>dobby_1968</v>
+        <v>pazzini__</v>
       </c>
       <c r="B621">
         <v>1</v>
@@ -9096,7 +9096,7 @@
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>ricardogabriel.sr</v>
+        <v>thiagomoisesmma</v>
       </c>
       <c r="B622">
         <v>1</v>
@@ -9110,7 +9110,7 @@
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>indiopersonalfight</v>
+        <v>dobby_1968</v>
       </c>
       <c r="B623">
         <v>1</v>
@@ -9124,7 +9124,7 @@
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>_samu35</v>
+        <v>ricardogabriel.sr</v>
       </c>
       <c r="B624">
         <v>1</v>
@@ -9138,7 +9138,7 @@
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>1felipe.bjj</v>
+        <v>indiopersonalfight</v>
       </c>
       <c r="B625">
         <v>1</v>
@@ -9152,7 +9152,7 @@
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>odennismagalhaes</v>
+        <v>_samu35</v>
       </c>
       <c r="B626">
         <v>1</v>
@@ -9166,7 +9166,7 @@
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>remarchina</v>
+        <v>1felipe.bjj</v>
       </c>
       <c r="B627">
         <v>1</v>
@@ -9180,7 +9180,7 @@
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>blesed578</v>
+        <v>odennismagalhaes</v>
       </c>
       <c r="B628">
         <v>1</v>
@@ -9194,7 +9194,7 @@
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>yago_08k</v>
+        <v>remarchina</v>
       </c>
       <c r="B629">
         <v>1</v>
@@ -9208,7 +9208,7 @@
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>maribrittos22</v>
+        <v>blesed578</v>
       </c>
       <c r="B630">
         <v>1</v>
@@ -9222,7 +9222,7 @@
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>grupoohplanooficial</v>
+        <v>yago_08k</v>
       </c>
       <c r="B631">
         <v>1</v>
@@ -9236,7 +9236,7 @@
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>rxdi_mns</v>
+        <v>maribrittos22</v>
       </c>
       <c r="B632">
         <v>1</v>
@@ -9250,7 +9250,7 @@
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>almeida_.e7</v>
+        <v>grupoohplanooficial</v>
       </c>
       <c r="B633">
         <v>1</v>
@@ -9264,7 +9264,7 @@
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>dyrodriguesohplano</v>
+        <v>rxdi_mns</v>
       </c>
       <c r="B634">
         <v>1</v>
@@ -9278,7 +9278,7 @@
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>lucianatpiccelli</v>
+        <v>almeida_.e7</v>
       </c>
       <c r="B635">
         <v>1</v>
@@ -9292,7 +9292,7 @@
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>fe_.faggi</v>
+        <v>dyrodriguesohplano</v>
       </c>
       <c r="B636">
         <v>1</v>
@@ -9306,7 +9306,7 @@
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>allves___46</v>
+        <v>lucianatpiccelli</v>
       </c>
       <c r="B637">
         <v>1</v>
@@ -9320,7 +9320,7 @@
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>ottoniisrael</v>
+        <v>fe_.faggi</v>
       </c>
       <c r="B638">
         <v>1</v>
@@ -9334,7 +9334,7 @@
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>_.carlos.2x._</v>
+        <v>allves___46</v>
       </c>
       <c r="B639">
         <v>1</v>
@@ -9348,7 +9348,7 @@
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>guilherme.duartesilva</v>
+        <v>ottoniisrael</v>
       </c>
       <c r="B640">
         <v>1</v>
@@ -9362,7 +9362,7 @@
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>davi.cb</v>
+        <v>_.carlos.2x._</v>
       </c>
       <c r="B641">
         <v>1</v>
@@ -9376,7 +9376,7 @@
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>abbasrizvi2204</v>
+        <v>guilherme.duartesilva</v>
       </c>
       <c r="B642">
         <v>1</v>
@@ -9390,7 +9390,7 @@
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>nulife2day</v>
+        <v>davi.cb</v>
       </c>
       <c r="B643">
         <v>1</v>
@@ -9404,7 +9404,7 @@
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>elnaggar_85</v>
+        <v>abbasrizvi2204</v>
       </c>
       <c r="B644">
         <v>1</v>
@@ -9418,7 +9418,7 @@
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>bammer2026</v>
+        <v>nulife2day</v>
       </c>
       <c r="B645">
         <v>1</v>
@@ -9432,7 +9432,7 @@
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>yon0sab0</v>
+        <v>elnaggar_85</v>
       </c>
       <c r="B646">
         <v>1</v>
@@ -9446,7 +9446,7 @@
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>thizzlenik</v>
+        <v>bammer2026</v>
       </c>
       <c r="B647">
         <v>1</v>
@@ -9460,7 +9460,7 @@
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>dogodoy</v>
+        <v>yon0sab0</v>
       </c>
       <c r="B648">
         <v>1</v>
@@ -9474,7 +9474,7 @@
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>cinemarianophoto</v>
+        <v>thizzlenik</v>
       </c>
       <c r="B649">
         <v>1</v>
@@ -9488,7 +9488,7 @@
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>nati.monteiro</v>
+        <v>dogodoy</v>
       </c>
       <c r="B650">
         <v>1</v>
@@ -9502,7 +9502,7 @@
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>boeno_rafael</v>
+        <v>cinemarianophoto</v>
       </c>
       <c r="B651">
         <v>1</v>
@@ -9516,7 +9516,7 @@
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>claudio_tikar</v>
+        <v>nati.monteiro</v>
       </c>
       <c r="B652">
         <v>1</v>
@@ -9530,7 +9530,7 @@
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>mauricio_dutra_m</v>
+        <v>boeno_rafael</v>
       </c>
       <c r="B653">
         <v>1</v>
@@ -9544,7 +9544,7 @@
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>s_giofe</v>
+        <v>claudio_tikar</v>
       </c>
       <c r="B654">
         <v>1</v>
@@ -9558,7 +9558,7 @@
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>1tiagomonteiro</v>
+        <v>mauricio_dutra_m</v>
       </c>
       <c r="B655">
         <v>1</v>
@@ -9572,7 +9572,7 @@
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>nautinhor7</v>
+        <v>s_giofe</v>
       </c>
       <c r="B656">
         <v>1</v>
@@ -9586,7 +9586,7 @@
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>lucaspaes047</v>
+        <v>1tiagomonteiro</v>
       </c>
       <c r="B657">
         <v>1</v>
@@ -9600,7 +9600,7 @@
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>bmarinhorogerio</v>
+        <v>nautinhor7</v>
       </c>
       <c r="B658">
         <v>1</v>
@@ -9614,7 +9614,7 @@
     </row>
     <row r="659">
       <c r="A659" t="str">
-        <v>klaiver.027xx</v>
+        <v>lucaspaes047</v>
       </c>
       <c r="B659">
         <v>1</v>
@@ -9628,7 +9628,7 @@
     </row>
     <row r="660">
       <c r="A660" t="str">
-        <v>jefte_jizreel</v>
+        <v>bmarinhorogerio</v>
       </c>
       <c r="B660">
         <v>1</v>
@@ -9642,7 +9642,7 @@
     </row>
     <row r="661">
       <c r="A661" t="str">
-        <v>clinicaikiro</v>
+        <v>klaiver.027xx</v>
       </c>
       <c r="B661">
         <v>1</v>
@@ -9656,7 +9656,7 @@
     </row>
     <row r="662">
       <c r="A662" t="str">
-        <v>cabreuvamma</v>
+        <v>jefte_jizreel</v>
       </c>
       <c r="B662">
         <v>1</v>
@@ -9670,7 +9670,7 @@
     </row>
     <row r="663">
       <c r="A663" t="str">
-        <v>use.ellasfit</v>
+        <v>clinicaikiro</v>
       </c>
       <c r="B663">
         <v>1</v>
@@ -9684,7 +9684,7 @@
     </row>
     <row r="664">
       <c r="A664" t="str">
-        <v>patriciarichteroficial</v>
+        <v>cabreuvamma</v>
       </c>
       <c r="B664">
         <v>1</v>
@@ -9698,7 +9698,7 @@
     </row>
     <row r="665">
       <c r="A665" t="str">
-        <v>kauan_mantas</v>
+        <v>use.ellasfit</v>
       </c>
       <c r="B665">
         <v>1</v>
@@ -9712,7 +9712,7 @@
     </row>
     <row r="666">
       <c r="A666" t="str">
-        <v>emersonapache</v>
+        <v>patriciarichteroficial</v>
       </c>
       <c r="B666">
         <v>1</v>
@@ -9726,7 +9726,7 @@
     </row>
     <row r="667">
       <c r="A667" t="str">
-        <v>nataliavidal965</v>
+        <v>kauan_mantas</v>
       </c>
       <c r="B667">
         <v>1</v>
@@ -9740,7 +9740,7 @@
     </row>
     <row r="668">
       <c r="A668" t="str">
-        <v>ruanpantojanutricionista</v>
+        <v>emersonapache</v>
       </c>
       <c r="B668">
         <v>1</v>
@@ -9754,7 +9754,7 @@
     </row>
     <row r="669">
       <c r="A669" t="str">
-        <v>luizpaulomma</v>
+        <v>nataliavidal965</v>
       </c>
       <c r="B669">
         <v>1</v>
@@ -9768,7 +9768,7 @@
     </row>
     <row r="670">
       <c r="A670" t="str">
-        <v>epicjoel2022</v>
+        <v>ruanpantojanutricionista</v>
       </c>
       <c r="B670">
         <v>1</v>
@@ -9782,7 +9782,7 @@
     </row>
     <row r="671">
       <c r="A671" t="str">
-        <v>tvlinsoficial</v>
+        <v>luizpaulomma</v>
       </c>
       <c r="B671">
         <v>1</v>
@@ -9796,7 +9796,7 @@
     </row>
     <row r="672">
       <c r="A672" t="str">
-        <v>_itamar_maximo</v>
+        <v>epicjoel2022</v>
       </c>
       <c r="B672">
         <v>1</v>
@@ -9810,7 +9810,7 @@
     </row>
     <row r="673">
       <c r="A673" t="str">
-        <v>mg._silvaa_</v>
+        <v>tvlinsoficial</v>
       </c>
       <c r="B673">
         <v>1</v>
@@ -9824,7 +9824,7 @@
     </row>
     <row r="674">
       <c r="A674" t="str">
-        <v>desativado_no_off33</v>
+        <v>_itamar_maximo</v>
       </c>
       <c r="B674">
         <v>1</v>
@@ -9838,21 +9838,21 @@
     </row>
     <row r="675">
       <c r="A675" t="str">
-        <v>lucasbaddoure</v>
+        <v>mg._silvaa_</v>
       </c>
       <c r="B675">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C675">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D675">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="str">
-        <v>paulo_rafa_personal</v>
+        <v>desativado_no_off33</v>
       </c>
       <c r="B676">
         <v>1</v>
@@ -9866,21 +9866,21 @@
     </row>
     <row r="677">
       <c r="A677" t="str">
-        <v>endurance_guia</v>
+        <v>lucasbaddoure</v>
       </c>
       <c r="B677">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C677">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D677">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="str">
-        <v>cadupereirss</v>
+        <v>paulo_rafa_personal</v>
       </c>
       <c r="B678">
         <v>1</v>
@@ -9894,7 +9894,7 @@
     </row>
     <row r="679">
       <c r="A679" t="str">
-        <v>instrutorindiovs</v>
+        <v>endurance_guia</v>
       </c>
       <c r="B679">
         <v>1</v>
@@ -9908,7 +9908,7 @@
     </row>
     <row r="680">
       <c r="A680" t="str">
-        <v>lopes.felipe13</v>
+        <v>cadupereirss</v>
       </c>
       <c r="B680">
         <v>1</v>
@@ -9922,7 +9922,7 @@
     </row>
     <row r="681">
       <c r="A681" t="str">
-        <v>_jullianadacruz</v>
+        <v>instrutorindiovs</v>
       </c>
       <c r="B681">
         <v>1</v>
@@ -9936,7 +9936,7 @@
     </row>
     <row r="682">
       <c r="A682" t="str">
-        <v>marchi_vinicius</v>
+        <v>lopes.felipe13</v>
       </c>
       <c r="B682">
         <v>1</v>
@@ -9950,7 +9950,7 @@
     </row>
     <row r="683">
       <c r="A683" t="str">
-        <v>rafa_speda</v>
+        <v>marchi_vinicius</v>
       </c>
       <c r="B683">
         <v>1</v>
@@ -9964,7 +9964,7 @@
     </row>
     <row r="684">
       <c r="A684" t="str">
-        <v>m1guelmolina</v>
+        <v>rafa_speda</v>
       </c>
       <c r="B684">
         <v>1</v>
@@ -9978,7 +9978,7 @@
     </row>
     <row r="685">
       <c r="A685" t="str">
-        <v>rosantos83</v>
+        <v>m1guelmolina</v>
       </c>
       <c r="B685">
         <v>1</v>
@@ -9992,7 +9992,7 @@
     </row>
     <row r="686">
       <c r="A686" t="str">
-        <v>caiogoularts</v>
+        <v>rosantos83</v>
       </c>
       <c r="B686">
         <v>1</v>
@@ -10006,7 +10006,7 @@
     </row>
     <row r="687">
       <c r="A687" t="str">
-        <v>cassiolee013</v>
+        <v>caiogoularts</v>
       </c>
       <c r="B687">
         <v>1</v>
@@ -10020,7 +10020,7 @@
     </row>
     <row r="688">
       <c r="A688" t="str">
-        <v>alinefurlann</v>
+        <v>cassiolee013</v>
       </c>
       <c r="B688">
         <v>1</v>
@@ -10034,7 +10034,7 @@
     </row>
     <row r="689">
       <c r="A689" t="str">
-        <v>programaparadois</v>
+        <v>alinefurlann</v>
       </c>
       <c r="B689">
         <v>1</v>
@@ -10048,7 +10048,7 @@
     </row>
     <row r="690">
       <c r="A690" t="str">
-        <v>cotty_bigmonster</v>
+        <v>programaparadois</v>
       </c>
       <c r="B690">
         <v>1</v>
@@ -10062,7 +10062,7 @@
     </row>
     <row r="691">
       <c r="A691" t="str">
-        <v>alissonlayza</v>
+        <v>cotty_bigmonster</v>
       </c>
       <c r="B691">
         <v>1</v>
@@ -10076,7 +10076,7 @@
     </row>
     <row r="692">
       <c r="A692" t="str">
-        <v>perninhakickboxing</v>
+        <v>alissonlayza</v>
       </c>
       <c r="B692">
         <v>1</v>
@@ -10090,7 +10090,7 @@
     </row>
     <row r="693">
       <c r="A693" t="str">
-        <v>rodrigo.nsx</v>
+        <v>perninhakickboxing</v>
       </c>
       <c r="B693">
         <v>1</v>
@@ -10104,35 +10104,35 @@
     </row>
     <row r="694">
       <c r="A694" t="str">
-        <v>luizcosta_mma</v>
+        <v>rodrigo.nsx</v>
       </c>
       <c r="B694">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C694">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D694">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="str">
-        <v>taylor_71kg</v>
+        <v>luizcosta_mma</v>
       </c>
       <c r="B695">
         <v>0</v>
       </c>
       <c r="C695">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D695">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="str">
-        <v>_vpft</v>
+        <v>taylor_71kg</v>
       </c>
       <c r="B696">
         <v>0</v>
@@ -10146,21 +10146,21 @@
     </row>
     <row r="697">
       <c r="A697" t="str">
-        <v>viniciustbf</v>
+        <v>_vpft</v>
       </c>
       <c r="B697">
         <v>0</v>
       </c>
       <c r="C697">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D697">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="str">
-        <v>dayanaa1511</v>
+        <v>viniciustbf</v>
       </c>
       <c r="B698">
         <v>0</v>
@@ -10169,40 +10169,40 @@
         <v>2</v>
       </c>
       <c r="D698">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="str">
-        <v>danielfranzesilva</v>
+        <v>dayanaa1511</v>
       </c>
       <c r="B699">
         <v>0</v>
       </c>
       <c r="C699">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D699">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="str">
-        <v>ednilsonkaicai</v>
+        <v>danielfranzesilva</v>
       </c>
       <c r="B700">
         <v>0</v>
       </c>
       <c r="C700">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D700">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="str">
-        <v>vanessamelomma</v>
+        <v>ednilsonkaicai</v>
       </c>
       <c r="B701">
         <v>0</v>
@@ -10216,21 +10216,21 @@
     </row>
     <row r="702">
       <c r="A702" t="str">
-        <v>michelle_mirele</v>
+        <v>vanessamelomma</v>
       </c>
       <c r="B702">
         <v>0</v>
       </c>
       <c r="C702">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D702">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="str">
-        <v>geyziellsouza</v>
+        <v>michelle_mirele</v>
       </c>
       <c r="B703">
         <v>0</v>
@@ -10244,21 +10244,21 @@
     </row>
     <row r="704">
       <c r="A704" t="str">
-        <v>guerreirammaofc</v>
+        <v>geyziellsouza</v>
       </c>
       <c r="B704">
         <v>0</v>
       </c>
       <c r="C704">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D704">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="str">
-        <v>kalaga_vito</v>
+        <v>guerreirammaofc</v>
       </c>
       <c r="B705">
         <v>0</v>
@@ -10272,7 +10272,7 @@
     </row>
     <row r="706">
       <c r="A706" t="str">
-        <v>dudaadantass</v>
+        <v>kalaga_vito</v>
       </c>
       <c r="B706">
         <v>0</v>
@@ -10286,7 +10286,7 @@
     </row>
     <row r="707">
       <c r="A707" t="str">
-        <v>vitorshowman</v>
+        <v>dudaadantass</v>
       </c>
       <c r="B707">
         <v>0</v>
@@ -10295,12 +10295,12 @@
         <v>2</v>
       </c>
       <c r="D707">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="708">
       <c r="A708" t="str">
-        <v>4lissson</v>
+        <v>vitorshowman</v>
       </c>
       <c r="B708">
         <v>0</v>
@@ -10314,21 +10314,21 @@
     </row>
     <row r="709">
       <c r="A709" t="str">
-        <v>danilofernandescf</v>
+        <v>4lissson</v>
       </c>
       <c r="B709">
         <v>0</v>
       </c>
       <c r="C709">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D709">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="710">
       <c r="A710" t="str">
-        <v>bryandazuera</v>
+        <v>danilofernandescf</v>
       </c>
       <c r="B710">
         <v>0</v>
@@ -10342,21 +10342,21 @@
     </row>
     <row r="711">
       <c r="A711" t="str">
-        <v>orlando_alfa09</v>
+        <v>bryandazuera</v>
       </c>
       <c r="B711">
         <v>0</v>
       </c>
       <c r="C711">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D711">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="712">
       <c r="A712" t="str">
-        <v>jhonnatanboxe_</v>
+        <v>orlando_alfa09</v>
       </c>
       <c r="B712">
         <v>0</v>
@@ -10370,7 +10370,7 @@
     </row>
     <row r="713">
       <c r="A713" t="str">
-        <v>manumito.oficial</v>
+        <v>jhonnatanboxe_</v>
       </c>
       <c r="B713">
         <v>0</v>
@@ -10384,63 +10384,63 @@
     </row>
     <row r="714">
       <c r="A714" t="str">
-        <v>coutz11</v>
+        <v>manumito.oficial</v>
       </c>
       <c r="B714">
         <v>0</v>
       </c>
       <c r="C714">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D714">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="715">
       <c r="A715" t="str">
-        <v>eglaudiomma</v>
+        <v>coutz11</v>
       </c>
       <c r="B715">
         <v>0</v>
       </c>
       <c r="C715">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D715">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="716">
       <c r="A716" t="str">
-        <v>lokomemo_protetores</v>
+        <v>eglaudiomma</v>
       </c>
       <c r="B716">
         <v>0</v>
       </c>
       <c r="C716">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D716">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="717">
       <c r="A717" t="str">
-        <v>carlosnoelblack</v>
+        <v>lokomemo_protetores</v>
       </c>
       <c r="B717">
         <v>0</v>
       </c>
       <c r="C717">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D717">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="718">
       <c r="A718" t="str">
-        <v>rafaelcmjj</v>
+        <v>carlosnoelblack</v>
       </c>
       <c r="B718">
         <v>0</v>
@@ -10454,21 +10454,21 @@
     </row>
     <row r="719">
       <c r="A719" t="str">
-        <v>rahikikhalid</v>
+        <v>rafaelcmjj</v>
       </c>
       <c r="B719">
         <v>0</v>
       </c>
       <c r="C719">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D719">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="720">
       <c r="A720" t="str">
-        <v>leonardopateira</v>
+        <v>rahikikhalid</v>
       </c>
       <c r="B720">
         <v>0</v>
@@ -10482,21 +10482,21 @@
     </row>
     <row r="721">
       <c r="A721" t="str">
-        <v>thalytabjj</v>
+        <v>leonardopateira</v>
       </c>
       <c r="B721">
         <v>0</v>
       </c>
       <c r="C721">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D721">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="722">
       <c r="A722" t="str">
-        <v>rafaelantonio.rj</v>
+        <v>thalytabjj</v>
       </c>
       <c r="B722">
         <v>0</v>
@@ -10510,35 +10510,35 @@
     </row>
     <row r="723">
       <c r="A723" t="str">
-        <v>yasminreis_oficiall</v>
+        <v>rafaelantonio.rj</v>
       </c>
       <c r="B723">
         <v>0</v>
       </c>
       <c r="C723">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D723">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="724">
       <c r="A724" t="str">
-        <v>dnoxsport</v>
+        <v>yasminreis_oficiall</v>
       </c>
       <c r="B724">
         <v>0</v>
       </c>
       <c r="C724">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D724">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="725">
       <c r="A725" t="str">
-        <v>armysenju</v>
+        <v>dnoxsport</v>
       </c>
       <c r="B725">
         <v>0</v>
@@ -10552,7 +10552,7 @@
     </row>
     <row r="726">
       <c r="A726" t="str">
-        <v>kamtalksmma</v>
+        <v>armysenju</v>
       </c>
       <c r="B726">
         <v>0</v>
@@ -10566,49 +10566,49 @@
     </row>
     <row r="727">
       <c r="A727" t="str">
-        <v>arleyleboss</v>
+        <v>kamtalksmma</v>
       </c>
       <c r="B727">
         <v>0</v>
       </c>
       <c r="C727">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D727">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="728">
       <c r="A728" t="str">
-        <v>jj_miguel05</v>
+        <v>arleyleboss</v>
       </c>
       <c r="B728">
         <v>0</v>
       </c>
       <c r="C728">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D728">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="729">
       <c r="A729" t="str">
-        <v>dra.izabeldelfino_</v>
+        <v>jj_miguel05</v>
       </c>
       <c r="B729">
         <v>0</v>
       </c>
       <c r="C729">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D729">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="730">
       <c r="A730" t="str">
-        <v>janjaovix</v>
+        <v>dra.izabeldelfino_</v>
       </c>
       <c r="B730">
         <v>0</v>
@@ -10622,7 +10622,7 @@
     </row>
     <row r="731">
       <c r="A731" t="str">
-        <v>joaolucasmma.rocha</v>
+        <v>janjaovix</v>
       </c>
       <c r="B731">
         <v>0</v>
@@ -10636,7 +10636,7 @@
     </row>
     <row r="732">
       <c r="A732" t="str">
-        <v>edsonbahienseb</v>
+        <v>joaolucasmma.rocha</v>
       </c>
       <c r="B732">
         <v>0</v>
@@ -10650,7 +10650,7 @@
     </row>
     <row r="733">
       <c r="A733" t="str">
-        <v>paulomartins.mma</v>
+        <v>edsonbahienseb</v>
       </c>
       <c r="B733">
         <v>0</v>
@@ -10664,27 +10664,27 @@
     </row>
     <row r="734">
       <c r="A734" t="str">
-        <v>daniel_natel</v>
+        <v>paulomartins.mma</v>
       </c>
       <c r="B734">
         <v>0</v>
       </c>
       <c r="C734">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D734">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="735">
       <c r="A735" t="str">
-        <v>dhuks11</v>
+        <v>daniel_natel</v>
       </c>
       <c r="B735">
         <v>0</v>
       </c>
       <c r="C735">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D735">
         <v>0</v>
@@ -10692,7 +10692,7 @@
     </row>
     <row r="736">
       <c r="A736" t="str">
-        <v>macksomlee</v>
+        <v>dhuks11</v>
       </c>
       <c r="B736">
         <v>0</v>
@@ -10701,40 +10701,40 @@
         <v>1</v>
       </c>
       <c r="D736">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="737">
       <c r="A737" t="str">
-        <v>y_nichimura</v>
+        <v>macksomlee</v>
       </c>
       <c r="B737">
         <v>0</v>
       </c>
       <c r="C737">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D737">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="738">
       <c r="A738" t="str">
-        <v>mayconzilli</v>
+        <v>y_nichimura</v>
       </c>
       <c r="B738">
         <v>0</v>
       </c>
       <c r="C738">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D738">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="739">
       <c r="A739" t="str">
-        <v>patascubo</v>
+        <v>mayconzilli</v>
       </c>
       <c r="B739">
         <v>0</v>
@@ -10748,7 +10748,7 @@
     </row>
     <row r="740">
       <c r="A740" t="str">
-        <v>jeffesonmeirelles</v>
+        <v>patascubo</v>
       </c>
       <c r="B740">
         <v>0</v>
@@ -10762,7 +10762,7 @@
     </row>
     <row r="741">
       <c r="A741" t="str">
-        <v>denilson.unit</v>
+        <v>jeffesonmeirelles</v>
       </c>
       <c r="B741">
         <v>0</v>
@@ -10776,7 +10776,7 @@
     </row>
     <row r="742">
       <c r="A742" t="str">
-        <v>vieirabjj____</v>
+        <v>denilson.unit</v>
       </c>
       <c r="B742">
         <v>0</v>
@@ -10790,7 +10790,7 @@
     </row>
     <row r="743">
       <c r="A743" t="str">
-        <v>canalgolpebaixo</v>
+        <v>vieirabjj____</v>
       </c>
       <c r="B743">
         <v>0</v>
@@ -10804,7 +10804,7 @@
     </row>
     <row r="744">
       <c r="A744" t="str">
-        <v>leandro__parpinelli</v>
+        <v>canalgolpebaixo</v>
       </c>
       <c r="B744">
         <v>0</v>
@@ -10818,7 +10818,7 @@
     </row>
     <row r="745">
       <c r="A745" t="str">
-        <v>bruno_pontes1992</v>
+        <v>leandro__parpinelli</v>
       </c>
       <c r="B745">
         <v>0</v>
@@ -10832,7 +10832,7 @@
     </row>
     <row r="746">
       <c r="A746" t="str">
-        <v>_pedro0h</v>
+        <v>bruno_pontes1992</v>
       </c>
       <c r="B746">
         <v>0</v>
@@ -10846,7 +10846,7 @@
     </row>
     <row r="747">
       <c r="A747" t="str">
-        <v>alineanne_</v>
+        <v>_pedro0h</v>
       </c>
       <c r="B747">
         <v>0</v>
@@ -10855,12 +10855,12 @@
         <v>1</v>
       </c>
       <c r="D747">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="748">
       <c r="A748" t="str">
-        <v>julckreis</v>
+        <v>alineanne_</v>
       </c>
       <c r="B748">
         <v>0</v>
@@ -10874,7 +10874,7 @@
     </row>
     <row r="749">
       <c r="A749" t="str">
-        <v>andreza.thais.1</v>
+        <v>julckreis</v>
       </c>
       <c r="B749">
         <v>0</v>
@@ -10888,7 +10888,7 @@
     </row>
     <row r="750">
       <c r="A750" t="str">
-        <v>benicius_edu</v>
+        <v>andreza.thais.1</v>
       </c>
       <c r="B750">
         <v>0</v>
@@ -10902,7 +10902,7 @@
     </row>
     <row r="751">
       <c r="A751" t="str">
-        <v>nataliaemanuela.personal</v>
+        <v>benicius_edu</v>
       </c>
       <c r="B751">
         <v>0</v>
@@ -10916,7 +10916,7 @@
     </row>
     <row r="752">
       <c r="A752" t="str">
-        <v>michele_mixa</v>
+        <v>nataliaemanuela.personal</v>
       </c>
       <c r="B752">
         <v>0</v>
@@ -10930,7 +10930,7 @@
     </row>
     <row r="753">
       <c r="A753" t="str">
-        <v>joaolauar_</v>
+        <v>michele_mixa</v>
       </c>
       <c r="B753">
         <v>0</v>
@@ -10944,7 +10944,7 @@
     </row>
     <row r="754">
       <c r="A754" t="str">
-        <v>igorbrasileiro01</v>
+        <v>joaolauar_</v>
       </c>
       <c r="B754">
         <v>0</v>
@@ -10958,7 +10958,7 @@
     </row>
     <row r="755">
       <c r="A755" t="str">
-        <v>felipeocalmon</v>
+        <v>igorbrasileiro01</v>
       </c>
       <c r="B755">
         <v>0</v>
@@ -10972,7 +10972,7 @@
     </row>
     <row r="756">
       <c r="A756" t="str">
-        <v>rejr_mma</v>
+        <v>felipeocalmon</v>
       </c>
       <c r="B756">
         <v>0</v>
@@ -10986,7 +10986,7 @@
     </row>
     <row r="757">
       <c r="A757" t="str">
-        <v>deivssonmanin</v>
+        <v>rejr_mma</v>
       </c>
       <c r="B757">
         <v>0</v>
@@ -11000,7 +11000,7 @@
     </row>
     <row r="758">
       <c r="A758" t="str">
-        <v>andrey_m_s_</v>
+        <v>deivssonmanin</v>
       </c>
       <c r="B758">
         <v>0</v>
@@ -11014,7 +11014,7 @@
     </row>
     <row r="759">
       <c r="A759" t="str">
-        <v>vidaldanin</v>
+        <v>andrey_m_s_</v>
       </c>
       <c r="B759">
         <v>0</v>
@@ -11028,7 +11028,7 @@
     </row>
     <row r="760">
       <c r="A760" t="str">
-        <v>barbaracontadora</v>
+        <v>vidaldanin</v>
       </c>
       <c r="B760">
         <v>0</v>
@@ -11042,7 +11042,7 @@
     </row>
     <row r="761">
       <c r="A761" t="str">
-        <v>natalves5</v>
+        <v>barbaracontadora</v>
       </c>
       <c r="B761">
         <v>0</v>
@@ -11056,7 +11056,7 @@
     </row>
     <row r="762">
       <c r="A762" t="str">
-        <v>marlon_bodybuilding</v>
+        <v>natalves5</v>
       </c>
       <c r="B762">
         <v>0</v>
@@ -11070,7 +11070,7 @@
     </row>
     <row r="763">
       <c r="A763" t="str">
-        <v>boradepodcastoficial</v>
+        <v>marlon_bodybuilding</v>
       </c>
       <c r="B763">
         <v>0</v>
@@ -11084,7 +11084,7 @@
     </row>
     <row r="764">
       <c r="A764" t="str">
-        <v>audizioandrade</v>
+        <v>boradepodcastoficial</v>
       </c>
       <c r="B764">
         <v>0</v>
@@ -11098,7 +11098,7 @@
     </row>
     <row r="765">
       <c r="A765" t="str">
-        <v>isadoragolimpio</v>
+        <v>audizioandrade</v>
       </c>
       <c r="B765">
         <v>0</v>
@@ -11112,7 +11112,7 @@
     </row>
     <row r="766">
       <c r="A766" t="str">
-        <v>dudu.acabamentos</v>
+        <v>isadoragolimpio</v>
       </c>
       <c r="B766">
         <v>0</v>
@@ -11126,7 +11126,7 @@
     </row>
     <row r="767">
       <c r="A767" t="str">
-        <v>katlembrenda</v>
+        <v>dudu.acabamentos</v>
       </c>
       <c r="B767">
         <v>0</v>
@@ -11140,7 +11140,7 @@
     </row>
     <row r="768">
       <c r="A768" t="str">
-        <v>aline.amaral21</v>
+        <v>katlembrenda</v>
       </c>
       <c r="B768">
         <v>0</v>
@@ -11154,7 +11154,7 @@
     </row>
     <row r="769">
       <c r="A769" t="str">
-        <v>tamysregina</v>
+        <v>aline.amaral21</v>
       </c>
       <c r="B769">
         <v>0</v>
@@ -11168,7 +11168,7 @@
     </row>
     <row r="770">
       <c r="A770" t="str">
-        <v>guilhermews1994</v>
+        <v>tamysregina</v>
       </c>
       <c r="B770">
         <v>0</v>
@@ -11182,7 +11182,7 @@
     </row>
     <row r="771">
       <c r="A771" t="str">
-        <v>kevin.mota95</v>
+        <v>guilhermews1994</v>
       </c>
       <c r="B771">
         <v>0</v>
@@ -11196,7 +11196,7 @@
     </row>
     <row r="772">
       <c r="A772" t="str">
-        <v>douglas_vitor8</v>
+        <v>kevin.mota95</v>
       </c>
       <c r="B772">
         <v>0</v>
@@ -11210,7 +11210,7 @@
     </row>
     <row r="773">
       <c r="A773" t="str">
-        <v>gemeaslauraebrenda</v>
+        <v>douglas_vitor8</v>
       </c>
       <c r="B773">
         <v>0</v>
@@ -11224,7 +11224,7 @@
     </row>
     <row r="774">
       <c r="A774" t="str">
-        <v>raulcarvalho1010</v>
+        <v>gemeaslauraebrenda</v>
       </c>
       <c r="B774">
         <v>0</v>
@@ -11238,7 +11238,7 @@
     </row>
     <row r="775">
       <c r="A775" t="str">
-        <v>roginbrito</v>
+        <v>raulcarvalho1010</v>
       </c>
       <c r="B775">
         <v>0</v>
@@ -11252,7 +11252,7 @@
     </row>
     <row r="776">
       <c r="A776" t="str">
-        <v>romulerasilva</v>
+        <v>roginbrito</v>
       </c>
       <c r="B776">
         <v>0</v>
@@ -11266,7 +11266,7 @@
     </row>
     <row r="777">
       <c r="A777" t="str">
-        <v>higorsaantana</v>
+        <v>romulerasilva</v>
       </c>
       <c r="B777">
         <v>0</v>
@@ -11280,7 +11280,7 @@
     </row>
     <row r="778">
       <c r="A778" t="str">
-        <v>vitorcosta_mma</v>
+        <v>higorsaantana</v>
       </c>
       <c r="B778">
         <v>0</v>
@@ -11294,7 +11294,7 @@
     </row>
     <row r="779">
       <c r="A779" t="str">
-        <v>paulo.titoo</v>
+        <v>vitorcosta_mma</v>
       </c>
       <c r="B779">
         <v>0</v>
@@ -11308,7 +11308,7 @@
     </row>
     <row r="780">
       <c r="A780" t="str">
-        <v>1000ton_n</v>
+        <v>paulo.titoo</v>
       </c>
       <c r="B780">
         <v>0</v>
@@ -11322,7 +11322,7 @@
     </row>
     <row r="781">
       <c r="A781" t="str">
-        <v>strong_stg_oficial</v>
+        <v>1000ton_n</v>
       </c>
       <c r="B781">
         <v>0</v>
@@ -11336,7 +11336,7 @@
     </row>
     <row r="782">
       <c r="A782" t="str">
-        <v>ricardotofanello</v>
+        <v>strong_stg_oficial</v>
       </c>
       <c r="B782">
         <v>0</v>
@@ -11350,7 +11350,7 @@
     </row>
     <row r="783">
       <c r="A783" t="str">
-        <v>taporondebruno</v>
+        <v>ricardotofanello</v>
       </c>
       <c r="B783">
         <v>0</v>
@@ -11364,7 +11364,7 @@
     </row>
     <row r="784">
       <c r="A784" t="str">
-        <v>anamatias.m</v>
+        <v>taporondebruno</v>
       </c>
       <c r="B784">
         <v>0</v>
@@ -11378,7 +11378,7 @@
     </row>
     <row r="785">
       <c r="A785" t="str">
-        <v>claudio_marchese_7</v>
+        <v>anamatias.m</v>
       </c>
       <c r="B785">
         <v>0</v>
@@ -11392,7 +11392,7 @@
     </row>
     <row r="786">
       <c r="A786" t="str">
-        <v>caioparangole</v>
+        <v>claudio_marchese_7</v>
       </c>
       <c r="B786">
         <v>0</v>
@@ -11406,7 +11406,7 @@
     </row>
     <row r="787">
       <c r="A787" t="str">
-        <v>sabrinaalsilva</v>
+        <v>caioparangole</v>
       </c>
       <c r="B787">
         <v>0</v>
@@ -11420,7 +11420,7 @@
     </row>
     <row r="788">
       <c r="A788" t="str">
-        <v>nuncadesistir.nd</v>
+        <v>sabrinaalsilva</v>
       </c>
       <c r="B788">
         <v>0</v>
@@ -11434,7 +11434,7 @@
     </row>
     <row r="789">
       <c r="A789" t="str">
-        <v>marcilio.silva.71404</v>
+        <v>nuncadesistir.nd</v>
       </c>
       <c r="B789">
         <v>0</v>
@@ -11448,7 +11448,7 @@
     </row>
     <row r="790">
       <c r="A790" t="str">
-        <v>doraasivla</v>
+        <v>marcilio.silva.71404</v>
       </c>
       <c r="B790">
         <v>0</v>
@@ -11462,7 +11462,7 @@
     </row>
     <row r="791">
       <c r="A791" t="str">
-        <v>pe.mirandas</v>
+        <v>doraasivla</v>
       </c>
       <c r="B791">
         <v>0</v>
@@ -11476,7 +11476,7 @@
     </row>
     <row r="792">
       <c r="A792" t="str">
-        <v>leaoanaalice</v>
+        <v>pe.mirandas</v>
       </c>
       <c r="B792">
         <v>0</v>
@@ -11490,7 +11490,7 @@
     </row>
     <row r="793">
       <c r="A793" t="str">
-        <v>cristianomarcello</v>
+        <v>leaoanaalice</v>
       </c>
       <c r="B793">
         <v>0</v>
@@ -11504,7 +11504,7 @@
     </row>
     <row r="794">
       <c r="A794" t="str">
-        <v>dandraco_</v>
+        <v>cristianomarcello</v>
       </c>
       <c r="B794">
         <v>0</v>
@@ -11518,7 +11518,7 @@
     </row>
     <row r="795">
       <c r="A795" t="str">
-        <v>oliveiraandiarabjj</v>
+        <v>dandraco_</v>
       </c>
       <c r="B795">
         <v>0</v>
@@ -11532,7 +11532,7 @@
     </row>
     <row r="796">
       <c r="A796" t="str">
-        <v>sejamotivadorofc</v>
+        <v>oliveiraandiarabjj</v>
       </c>
       <c r="B796">
         <v>0</v>
@@ -11546,7 +11546,7 @@
     </row>
     <row r="797">
       <c r="A797" t="str">
-        <v>tpapereira</v>
+        <v>sejamotivadorofc</v>
       </c>
       <c r="B797">
         <v>0</v>
@@ -11560,7 +11560,7 @@
     </row>
     <row r="798">
       <c r="A798" t="str">
-        <v>kfcampeoes</v>
+        <v>tpapereira</v>
       </c>
       <c r="B798">
         <v>0</v>
@@ -11574,7 +11574,7 @@
     </row>
     <row r="799">
       <c r="A799" t="str">
-        <v>herrickmarinho</v>
+        <v>kfcampeoes</v>
       </c>
       <c r="B799">
         <v>0</v>
@@ -11588,7 +11588,7 @@
     </row>
     <row r="800">
       <c r="A800" t="str">
-        <v>geanne_franca_</v>
+        <v>herrickmarinho</v>
       </c>
       <c r="B800">
         <v>0</v>
@@ -11602,7 +11602,7 @@
     </row>
     <row r="801">
       <c r="A801" t="str">
-        <v>vanemessina</v>
+        <v>geanne_franca_</v>
       </c>
       <c r="B801">
         <v>0</v>
@@ -11616,7 +11616,7 @@
     </row>
     <row r="802">
       <c r="A802" t="str">
-        <v>dadwillians</v>
+        <v>vanemessina</v>
       </c>
       <c r="B802">
         <v>0</v>
@@ -11630,7 +11630,7 @@
     </row>
     <row r="803">
       <c r="A803" t="str">
-        <v>esteticaluharruda</v>
+        <v>dadwillians</v>
       </c>
       <c r="B803">
         <v>0</v>
@@ -11644,7 +11644,7 @@
     </row>
     <row r="804">
       <c r="A804" t="str">
-        <v>chubotaru_lilu</v>
+        <v>esteticaluharruda</v>
       </c>
       <c r="B804">
         <v>0</v>
@@ -11658,7 +11658,7 @@
     </row>
     <row r="805">
       <c r="A805" t="str">
-        <v>_kainanlima</v>
+        <v>chubotaru_lilu</v>
       </c>
       <c r="B805">
         <v>0</v>
@@ -11672,7 +11672,7 @@
     </row>
     <row r="806">
       <c r="A806" t="str">
-        <v>jimmy_indioap</v>
+        <v>_kainanlima</v>
       </c>
       <c r="B806">
         <v>0</v>
@@ -11686,7 +11686,7 @@
     </row>
     <row r="807">
       <c r="A807" t="str">
-        <v>omar_alneaimi</v>
+        <v>jimmy_indioap</v>
       </c>
       <c r="B807">
         <v>0</v>
@@ -11700,7 +11700,7 @@
     </row>
     <row r="808">
       <c r="A808" t="str">
-        <v>victor_brunopersonal</v>
+        <v>omar_alneaimi</v>
       </c>
       <c r="B808">
         <v>0</v>
@@ -11714,7 +11714,7 @@
     </row>
     <row r="809">
       <c r="A809" t="str">
-        <v>mariacleusa.lopes</v>
+        <v>victor_brunopersonal</v>
       </c>
       <c r="B809">
         <v>0</v>
@@ -11728,7 +11728,7 @@
     </row>
     <row r="810">
       <c r="A810" t="str">
-        <v>rafaelbipolarufc</v>
+        <v>mariacleusa.lopes</v>
       </c>
       <c r="B810">
         <v>0</v>
@@ -11742,7 +11742,7 @@
     </row>
     <row r="811">
       <c r="A811" t="str">
-        <v>martinpakciarz</v>
+        <v>rafaelbipolarufc</v>
       </c>
       <c r="B811">
         <v>0</v>
@@ -11756,7 +11756,7 @@
     </row>
     <row r="812">
       <c r="A812" t="str">
-        <v>andrearschack</v>
+        <v>martinpakciarz</v>
       </c>
       <c r="B812">
         <v>0</v>
@@ -11770,7 +11770,7 @@
     </row>
     <row r="813">
       <c r="A813" t="str">
-        <v>leziamorbeck50</v>
+        <v>andrearschack</v>
       </c>
       <c r="B813">
         <v>0</v>
@@ -11784,7 +11784,7 @@
     </row>
     <row r="814">
       <c r="A814" t="str">
-        <v>meirelesmma</v>
+        <v>leziamorbeck50</v>
       </c>
       <c r="B814">
         <v>0</v>
@@ -11798,7 +11798,7 @@
     </row>
     <row r="815">
       <c r="A815" t="str">
-        <v>teamsilverio</v>
+        <v>meirelesmma</v>
       </c>
       <c r="B815">
         <v>0</v>
@@ -11812,7 +11812,7 @@
     </row>
     <row r="816">
       <c r="A816" t="str">
-        <v>tatiaradias</v>
+        <v>teamsilverio</v>
       </c>
       <c r="B816">
         <v>0</v>
@@ -11826,7 +11826,7 @@
     </row>
     <row r="817">
       <c r="A817" t="str">
-        <v>daniloacordeon_oficial</v>
+        <v>tatiaradias</v>
       </c>
       <c r="B817">
         <v>0</v>
@@ -11840,7 +11840,7 @@
     </row>
     <row r="818">
       <c r="A818" t="str">
-        <v>thiagopssantos</v>
+        <v>daniloacordeon_oficial</v>
       </c>
       <c r="B818">
         <v>0</v>
@@ -11854,7 +11854,7 @@
     </row>
     <row r="819">
       <c r="A819" t="str">
-        <v>leafarlemos</v>
+        <v>thiagopssantos</v>
       </c>
       <c r="B819">
         <v>0</v>
@@ -11868,7 +11868,7 @@
     </row>
     <row r="820">
       <c r="A820" t="str">
-        <v>miltoncjr28</v>
+        <v>leafarlemos</v>
       </c>
       <c r="B820">
         <v>0</v>
@@ -11882,7 +11882,7 @@
     </row>
     <row r="821">
       <c r="A821" t="str">
-        <v>almeidajjwk</v>
+        <v>miltoncjr28</v>
       </c>
       <c r="B821">
         <v>0</v>
@@ -11896,7 +11896,7 @@
     </row>
     <row r="822">
       <c r="A822" t="str">
-        <v>soniarmurata</v>
+        <v>almeidajjwk</v>
       </c>
       <c r="B822">
         <v>0</v>
@@ -11910,7 +11910,7 @@
     </row>
     <row r="823">
       <c r="A823" t="str">
-        <v>foryousaudeespecializada</v>
+        <v>soniarmurata</v>
       </c>
       <c r="B823">
         <v>0</v>
@@ -11924,7 +11924,7 @@
     </row>
     <row r="824">
       <c r="A824" t="str">
-        <v>marques.__bjj</v>
+        <v>foryousaudeespecializada</v>
       </c>
       <c r="B824">
         <v>0</v>
@@ -11938,7 +11938,7 @@
     </row>
     <row r="825">
       <c r="A825" t="str">
-        <v>ryu_artes_marciais</v>
+        <v>marques.__bjj</v>
       </c>
       <c r="B825">
         <v>0</v>
@@ -11952,7 +11952,7 @@
     </row>
     <row r="826">
       <c r="A826" t="str">
-        <v>dorgivan13_bjj</v>
+        <v>ryu_artes_marciais</v>
       </c>
       <c r="B826">
         <v>0</v>
@@ -11966,7 +11966,7 @@
     </row>
     <row r="827">
       <c r="A827" t="str">
-        <v>ayman__falil_06</v>
+        <v>dorgivan13_bjj</v>
       </c>
       <c r="B827">
         <v>0</v>
@@ -11980,7 +11980,7 @@
     </row>
     <row r="828">
       <c r="A828" t="str">
-        <v>otaviocarneiromma</v>
+        <v>ayman__falil_06</v>
       </c>
       <c r="B828">
         <v>0</v>
@@ -11994,7 +11994,7 @@
     </row>
     <row r="829">
       <c r="A829" t="str">
-        <v>dvlucc2k26_</v>
+        <v>otaviocarneiromma</v>
       </c>
       <c r="B829">
         <v>0</v>
@@ -12008,7 +12008,7 @@
     </row>
     <row r="830">
       <c r="A830" t="str">
-        <v>thayanne_rodrigues_bjj</v>
+        <v>dvlucc2k26_</v>
       </c>
       <c r="B830">
         <v>0</v>
@@ -12022,7 +12022,7 @@
     </row>
     <row r="831">
       <c r="A831" t="str">
-        <v>lurochachef</v>
+        <v>thayanne_rodrigues_bjj</v>
       </c>
       <c r="B831">
         <v>0</v>
@@ -12036,7 +12036,7 @@
     </row>
     <row r="832">
       <c r="A832" t="str">
-        <v>viniciusmorais.bjj</v>
+        <v>lurochachef</v>
       </c>
       <c r="B832">
         <v>0</v>
@@ -12050,7 +12050,7 @@
     </row>
     <row r="833">
       <c r="A833" t="str">
-        <v>mauriciogeorge</v>
+        <v>viniciusmorais.bjj</v>
       </c>
       <c r="B833">
         <v>0</v>
@@ -12064,7 +12064,7 @@
     </row>
     <row r="834">
       <c r="A834" t="str">
-        <v>gisbedejose</v>
+        <v>mauriciogeorge</v>
       </c>
       <c r="B834">
         <v>0</v>
@@ -12078,7 +12078,7 @@
     </row>
     <row r="835">
       <c r="A835" t="str">
-        <v>laureanucalvo</v>
+        <v>gisbedejose</v>
       </c>
       <c r="B835">
         <v>0</v>
@@ -12092,7 +12092,7 @@
     </row>
     <row r="836">
       <c r="A836" t="str">
-        <v>galindofrontado</v>
+        <v>laureanucalvo</v>
       </c>
       <c r="B836">
         <v>0</v>
@@ -12106,7 +12106,7 @@
     </row>
     <row r="837">
       <c r="A837" t="str">
-        <v>chalakakavinda</v>
+        <v>galindofrontado</v>
       </c>
       <c r="B837">
         <v>0</v>
@@ -12120,7 +12120,7 @@
     </row>
     <row r="838">
       <c r="A838" t="str">
-        <v>gandrapaulino</v>
+        <v>chalakakavinda</v>
       </c>
       <c r="B838">
         <v>0</v>
@@ -12134,7 +12134,7 @@
     </row>
     <row r="839">
       <c r="A839" t="str">
-        <v>pgmarquesantos</v>
+        <v>gandrapaulino</v>
       </c>
       <c r="B839">
         <v>0</v>
@@ -12148,7 +12148,7 @@
     </row>
     <row r="840">
       <c r="A840" t="str">
-        <v>uluukyrgyz_tima</v>
+        <v>pgmarquesantos</v>
       </c>
       <c r="B840">
         <v>0</v>
@@ -12162,7 +12162,7 @@
     </row>
     <row r="841">
       <c r="A841" t="str">
-        <v>kells2vallone</v>
+        <v>uluukyrgyz_tima</v>
       </c>
       <c r="B841">
         <v>0</v>
@@ -12176,7 +12176,7 @@
     </row>
     <row r="842">
       <c r="A842" t="str">
-        <v>personaljakeline</v>
+        <v>kells2vallone</v>
       </c>
       <c r="B842">
         <v>0</v>
@@ -12190,7 +12190,7 @@
     </row>
     <row r="843">
       <c r="A843" t="str">
-        <v>bjjfalkenberg</v>
+        <v>personaljakeline</v>
       </c>
       <c r="B843">
         <v>0</v>
@@ -12204,7 +12204,7 @@
     </row>
     <row r="844">
       <c r="A844" t="str">
-        <v>sergiorenatocruz1</v>
+        <v>bjjfalkenberg</v>
       </c>
       <c r="B844">
         <v>0</v>
@@ -12218,7 +12218,7 @@
     </row>
     <row r="845">
       <c r="A845" t="str">
-        <v>marcaojudobjjmaster</v>
+        <v>sergiorenatocruz1</v>
       </c>
       <c r="B845">
         <v>0</v>
@@ -12232,7 +12232,7 @@
     </row>
     <row r="846">
       <c r="A846" t="str">
-        <v>indio_mma</v>
+        <v>marcaojudobjjmaster</v>
       </c>
       <c r="B846">
         <v>0</v>
@@ -12246,7 +12246,7 @@
     </row>
     <row r="847">
       <c r="A847" t="str">
-        <v>covil.045</v>
+        <v>indio_mma</v>
       </c>
       <c r="B847">
         <v>0</v>
@@ -12260,7 +12260,7 @@
     </row>
     <row r="848">
       <c r="A848" t="str">
-        <v>allandelano</v>
+        <v>covil.045</v>
       </c>
       <c r="B848">
         <v>0</v>
@@ -12274,7 +12274,7 @@
     </row>
     <row r="849">
       <c r="A849" t="str">
-        <v>alomaraujo</v>
+        <v>allandelano</v>
       </c>
       <c r="B849">
         <v>0</v>
@@ -12288,7 +12288,7 @@
     </row>
     <row r="850">
       <c r="A850" t="str">
-        <v>theanimallifemovement</v>
+        <v>alomaraujo</v>
       </c>
       <c r="B850">
         <v>0</v>
@@ -12302,7 +12302,7 @@
     </row>
     <row r="851">
       <c r="A851" t="str">
-        <v>tombg_64</v>
+        <v>theanimallifemovement</v>
       </c>
       <c r="B851">
         <v>0</v>
@@ -12316,7 +12316,7 @@
     </row>
     <row r="852">
       <c r="A852" t="str">
-        <v>michaeloliveiramma</v>
+        <v>tombg_64</v>
       </c>
       <c r="B852">
         <v>0</v>
@@ -12330,7 +12330,7 @@
     </row>
     <row r="853">
       <c r="A853" t="str">
-        <v>andreichubotaru94</v>
+        <v>michaeloliveiramma</v>
       </c>
       <c r="B853">
         <v>0</v>
@@ -12344,7 +12344,7 @@
     </row>
     <row r="854">
       <c r="A854" t="str">
-        <v>carinhakkz</v>
+        <v>andreichubotaru94</v>
       </c>
       <c r="B854">
         <v>0</v>
@@ -12358,7 +12358,7 @@
     </row>
     <row r="855">
       <c r="A855" t="str">
-        <v>helaynecrisl</v>
+        <v>carinhakkz</v>
       </c>
       <c r="B855">
         <v>0</v>
@@ -12372,7 +12372,7 @@
     </row>
     <row r="856">
       <c r="A856" t="str">
-        <v>oliveiraa_00.11</v>
+        <v>helaynecrisl</v>
       </c>
       <c r="B856">
         <v>0</v>
@@ -12386,7 +12386,7 @@
     </row>
     <row r="857">
       <c r="A857" t="str">
-        <v>udilimaheroi</v>
+        <v>oliveiraa_00.11</v>
       </c>
       <c r="B857">
         <v>0</v>
@@ -12400,7 +12400,7 @@
     </row>
     <row r="858">
       <c r="A858" t="str">
-        <v>mirnacaroline</v>
+        <v>udilimaheroi</v>
       </c>
       <c r="B858">
         <v>0</v>
@@ -12414,7 +12414,7 @@
     </row>
     <row r="859">
       <c r="A859" t="str">
-        <v>lmk_sport</v>
+        <v>mirnacaroline</v>
       </c>
       <c r="B859">
         <v>0</v>
@@ -12428,7 +12428,7 @@
     </row>
     <row r="860">
       <c r="A860" t="str">
-        <v>fher.nando_</v>
+        <v>lmk_sport</v>
       </c>
       <c r="B860">
         <v>0</v>
@@ -12442,7 +12442,7 @@
     </row>
     <row r="861">
       <c r="A861" t="str">
-        <v>cristiannogueira.vtt</v>
+        <v>fher.nando_</v>
       </c>
       <c r="B861">
         <v>0</v>
@@ -12456,7 +12456,7 @@
     </row>
     <row r="862">
       <c r="A862" t="str">
-        <v>adrianaramosalvesribeiro</v>
+        <v>cristiannogueira.vtt</v>
       </c>
       <c r="B862">
         <v>0</v>
@@ -12470,7 +12470,7 @@
     </row>
     <row r="863">
       <c r="A863" t="str">
-        <v>djuliaarianamma</v>
+        <v>adrianaramosalvesribeiro</v>
       </c>
       <c r="B863">
         <v>0</v>
@@ -12484,7 +12484,7 @@
     </row>
     <row r="864">
       <c r="A864" t="str">
-        <v>raulbasilioo</v>
+        <v>djuliaarianamma</v>
       </c>
       <c r="B864">
         <v>0</v>
@@ -12498,7 +12498,7 @@
     </row>
     <row r="865">
       <c r="A865" t="str">
-        <v>heloisa_elohim</v>
+        <v>raulbasilioo</v>
       </c>
       <c r="B865">
         <v>0</v>
@@ -12512,7 +12512,7 @@
     </row>
     <row r="866">
       <c r="A866" t="str">
-        <v>hostonhugo</v>
+        <v>heloisa_elohim</v>
       </c>
       <c r="B866">
         <v>0</v>
@@ -12526,7 +12526,7 @@
     </row>
     <row r="867">
       <c r="A867" t="str">
-        <v>ellida_guimaraes</v>
+        <v>hostonhugo</v>
       </c>
       <c r="B867">
         <v>0</v>
@@ -12540,7 +12540,7 @@
     </row>
     <row r="868">
       <c r="A868" t="str">
-        <v>massoterapeuta_bemestarr</v>
+        <v>ellida_guimaraes</v>
       </c>
       <c r="B868">
         <v>0</v>
@@ -12554,7 +12554,7 @@
     </row>
     <row r="869">
       <c r="A869" t="str">
-        <v>alexandrefideliis</v>
+        <v>massoterapeuta_bemestarr</v>
       </c>
       <c r="B869">
         <v>0</v>
@@ -12568,7 +12568,7 @@
     </row>
     <row r="870">
       <c r="A870" t="str">
-        <v>pammygaryo</v>
+        <v>alexandrefideliis</v>
       </c>
       <c r="B870">
         <v>0</v>
@@ -12582,7 +12582,7 @@
     </row>
     <row r="871">
       <c r="A871" t="str">
-        <v>beatrizosilveira</v>
+        <v>pammygaryo</v>
       </c>
       <c r="B871">
         <v>0</v>
@@ -12596,7 +12596,7 @@
     </row>
     <row r="872">
       <c r="A872" t="str">
-        <v>bastazinifilho</v>
+        <v>beatrizosilveira</v>
       </c>
       <c r="B872">
         <v>0</v>
@@ -12610,7 +12610,7 @@
     </row>
     <row r="873">
       <c r="A873" t="str">
-        <v>sem_saida.12</v>
+        <v>bastazinifilho</v>
       </c>
       <c r="B873">
         <v>0</v>
@@ -12624,7 +12624,7 @@
     </row>
     <row r="874">
       <c r="A874" t="str">
-        <v>sougustavorosa</v>
+        <v>sem_saida.12</v>
       </c>
       <c r="B874">
         <v>0</v>
@@ -12638,7 +12638,7 @@
     </row>
     <row r="875">
       <c r="A875" t="str">
-        <v>lincoln__puig77</v>
+        <v>sougustavorosa</v>
       </c>
       <c r="B875">
         <v>0</v>
@@ -12652,7 +12652,7 @@
     </row>
     <row r="876">
       <c r="A876" t="str">
-        <v>anselmo.azevedo</v>
+        <v>lincoln__puig77</v>
       </c>
       <c r="B876">
         <v>0</v>
@@ -12666,7 +12666,7 @@
     </row>
     <row r="877">
       <c r="A877" t="str">
-        <v>marcotulio_matuto</v>
+        <v>anselmo.azevedo</v>
       </c>
       <c r="B877">
         <v>0</v>
@@ -12680,7 +12680,7 @@
     </row>
     <row r="878">
       <c r="A878" t="str">
-        <v>ianrochaf</v>
+        <v>marcotulio_matuto</v>
       </c>
       <c r="B878">
         <v>0</v>
@@ -12694,7 +12694,7 @@
     </row>
     <row r="879">
       <c r="A879" t="str">
-        <v>ale.lagonegro</v>
+        <v>ianrochaf</v>
       </c>
       <c r="B879">
         <v>0</v>
@@ -12708,7 +12708,7 @@
     </row>
     <row r="880">
       <c r="A880" t="str">
-        <v>ganemfelipe</v>
+        <v>ale.lagonegro</v>
       </c>
       <c r="B880">
         <v>0</v>
@@ -12722,7 +12722,7 @@
     </row>
     <row r="881">
       <c r="A881" t="str">
-        <v>marcusvgsz</v>
+        <v>ganemfelipe</v>
       </c>
       <c r="B881">
         <v>0</v>
@@ -12736,7 +12736,7 @@
     </row>
     <row r="882">
       <c r="A882" t="str">
-        <v>fabio.sampaio.90260</v>
+        <v>marcusvgsz</v>
       </c>
       <c r="B882">
         <v>0</v>
@@ -12750,7 +12750,7 @@
     </row>
     <row r="883">
       <c r="A883" t="str">
-        <v>kaynankruschewsky_ufc</v>
+        <v>fabio.sampaio.90260</v>
       </c>
       <c r="B883">
         <v>0</v>
@@ -12764,7 +12764,7 @@
     </row>
     <row r="884">
       <c r="A884" t="str">
-        <v>vitorpaes_personalfight</v>
+        <v>kaynankruschewsky_ufc</v>
       </c>
       <c r="B884">
         <v>0</v>
@@ -12778,7 +12778,7 @@
     </row>
     <row r="885">
       <c r="A885" t="str">
-        <v>zeferinomma</v>
+        <v>vitorpaes_personalfight</v>
       </c>
       <c r="B885">
         <v>0</v>
@@ -12792,7 +12792,7 @@
     </row>
     <row r="886">
       <c r="A886" t="str">
-        <v>tavaresguu</v>
+        <v>zeferinomma</v>
       </c>
       <c r="B886">
         <v>0</v>
@@ -12806,7 +12806,7 @@
     </row>
     <row r="887">
       <c r="A887" t="str">
-        <v>ildemarmarajo</v>
+        <v>tavaresguu</v>
       </c>
       <c r="B887">
         <v>0</v>
@@ -12820,7 +12820,7 @@
     </row>
     <row r="888">
       <c r="A888" t="str">
-        <v>pepefightteam</v>
+        <v>ildemarmarajo</v>
       </c>
       <c r="B888">
         <v>0</v>
@@ -12834,7 +12834,7 @@
     </row>
     <row r="889">
       <c r="A889" t="str">
-        <v>danieldias7s</v>
+        <v>pepefightteam</v>
       </c>
       <c r="B889">
         <v>0</v>
@@ -12848,7 +12848,7 @@
     </row>
     <row r="890">
       <c r="A890" t="str">
-        <v>ohanna.anselmo</v>
+        <v>danieldias7s</v>
       </c>
       <c r="B890">
         <v>0</v>
@@ -12862,7 +12862,7 @@
     </row>
     <row r="891">
       <c r="A891" t="str">
-        <v>brun_oguerreiro</v>
+        <v>ohanna.anselmo</v>
       </c>
       <c r="B891">
         <v>0</v>
@@ -12876,7 +12876,7 @@
     </row>
     <row r="892">
       <c r="A892" t="str">
-        <v>helman_mma70</v>
+        <v>brun_oguerreiro</v>
       </c>
       <c r="B892">
         <v>0</v>
@@ -12890,7 +12890,7 @@
     </row>
     <row r="893">
       <c r="A893" t="str">
-        <v>macio.almeida_89</v>
+        <v>helman_mma70</v>
       </c>
       <c r="B893">
         <v>0</v>
@@ -12904,7 +12904,7 @@
     </row>
     <row r="894">
       <c r="A894" t="str">
-        <v>lyviaestherbjj</v>
+        <v>macio.almeida_89</v>
       </c>
       <c r="B894">
         <v>0</v>
@@ -12918,7 +12918,7 @@
     </row>
     <row r="895">
       <c r="A895" t="str">
-        <v>mma.fisio</v>
+        <v>lyviaestherbjj</v>
       </c>
       <c r="B895">
         <v>0</v>
@@ -12932,7 +12932,7 @@
     </row>
     <row r="896">
       <c r="A896" t="str">
-        <v>thaynara_victoria_</v>
+        <v>mma.fisio</v>
       </c>
       <c r="B896">
         <v>0</v>
@@ -12946,7 +12946,7 @@
     </row>
     <row r="897">
       <c r="A897" t="str">
-        <v>tamarapq</v>
+        <v>thaynara_victoria_</v>
       </c>
       <c r="B897">
         <v>0</v>
@@ -12960,7 +12960,7 @@
     </row>
     <row r="898">
       <c r="A898" t="str">
-        <v>wendel_bjj14</v>
+        <v>tamarapq</v>
       </c>
       <c r="B898">
         <v>0</v>
@@ -12974,7 +12974,7 @@
     </row>
     <row r="899">
       <c r="A899" t="str">
-        <v>karine_killer_ufc</v>
+        <v>wendel_bjj14</v>
       </c>
       <c r="B899">
         <v>0</v>
@@ -12988,7 +12988,7 @@
     </row>
     <row r="900">
       <c r="A900" t="str">
-        <v>andressa_bjj_</v>
+        <v>karine_killer_ufc</v>
       </c>
       <c r="B900">
         <v>0</v>
@@ -13002,7 +13002,7 @@
     </row>
     <row r="901">
       <c r="A901" t="str">
-        <v>dreamartpro</v>
+        <v>andressa_bjj_</v>
       </c>
       <c r="B901">
         <v>0</v>
@@ -13016,7 +13016,7 @@
     </row>
     <row r="902">
       <c r="A902" t="str">
-        <v>makelele_bjj</v>
+        <v>dreamartpro</v>
       </c>
       <c r="B902">
         <v>0</v>
@@ -13030,7 +13030,7 @@
     </row>
     <row r="903">
       <c r="A903" t="str">
-        <v>fdanieljj</v>
+        <v>makelele_bjj</v>
       </c>
       <c r="B903">
         <v>0</v>
@@ -13044,7 +13044,7 @@
     </row>
     <row r="904">
       <c r="A904" t="str">
-        <v>jeferson_tijolo1</v>
+        <v>fdanieljj</v>
       </c>
       <c r="B904">
         <v>0</v>
@@ -13058,7 +13058,7 @@
     </row>
     <row r="905">
       <c r="A905" t="str">
-        <v>caioleonjj</v>
+        <v>jeferson_tijolo1</v>
       </c>
       <c r="B905">
         <v>0</v>
@@ -13072,7 +13072,7 @@
     </row>
     <row r="906">
       <c r="A906" t="str">
-        <v>kevinlopes_bjj</v>
+        <v>caioleonjj</v>
       </c>
       <c r="B906">
         <v>0</v>
@@ -13086,7 +13086,7 @@
     </row>
     <row r="907">
       <c r="A907" t="str">
-        <v>malene_elleen</v>
+        <v>kevinlopes_bjj</v>
       </c>
       <c r="B907">
         <v>0</v>
@@ -13100,7 +13100,7 @@
     </row>
     <row r="908">
       <c r="A908" t="str">
-        <v>danielplayboymt</v>
+        <v>malene_elleen</v>
       </c>
       <c r="B908">
         <v>0</v>
@@ -13114,7 +13114,7 @@
     </row>
     <row r="909">
       <c r="A909" t="str">
-        <v>fix.pec</v>
+        <v>danielplayboymt</v>
       </c>
       <c r="B909">
         <v>0</v>
@@ -13128,7 +13128,7 @@
     </row>
     <row r="910">
       <c r="A910" t="str">
-        <v>chunco_424</v>
+        <v>fix.pec</v>
       </c>
       <c r="B910">
         <v>0</v>
@@ -13142,7 +13142,7 @@
     </row>
     <row r="911">
       <c r="A911" t="str">
-        <v>denisalagoanobjj</v>
+        <v>chunco_424</v>
       </c>
       <c r="B911">
         <v>0</v>
@@ -13156,7 +13156,7 @@
     </row>
     <row r="912">
       <c r="A912" t="str">
-        <v>priscilaapbatista</v>
+        <v>denisalagoanobjj</v>
       </c>
       <c r="B912">
         <v>0</v>
@@ -13170,7 +13170,7 @@
     </row>
     <row r="913">
       <c r="A913" t="str">
-        <v>josita_bjj</v>
+        <v>priscilaapbatista</v>
       </c>
       <c r="B913">
         <v>0</v>
@@ -13184,7 +13184,7 @@
     </row>
     <row r="914">
       <c r="A914" t="str">
-        <v>roxostrike</v>
+        <v>josita_bjj</v>
       </c>
       <c r="B914">
         <v>0</v>
@@ -13198,7 +13198,7 @@
     </row>
     <row r="915">
       <c r="A915" t="str">
-        <v>shirleypalestrina6</v>
+        <v>roxostrike</v>
       </c>
       <c r="B915">
         <v>0</v>
@@ -13212,7 +13212,7 @@
     </row>
     <row r="916">
       <c r="A916" t="str">
-        <v>flipebiano</v>
+        <v>shirleypalestrina6</v>
       </c>
       <c r="B916">
         <v>0</v>
@@ -13226,7 +13226,7 @@
     </row>
     <row r="917">
       <c r="A917" t="str">
-        <v>ruanmiqueias</v>
+        <v>flipebiano</v>
       </c>
       <c r="B917">
         <v>0</v>
@@ -13240,7 +13240,7 @@
     </row>
     <row r="918">
       <c r="A918" t="str">
-        <v>babimaciel1</v>
+        <v>ruanmiqueias</v>
       </c>
       <c r="B918">
         <v>0</v>
@@ -13254,7 +13254,7 @@
     </row>
     <row r="919">
       <c r="A919" t="str">
-        <v>manoel.brum</v>
+        <v>babimaciel1</v>
       </c>
       <c r="B919">
         <v>0</v>
@@ -13268,7 +13268,7 @@
     </row>
     <row r="920">
       <c r="A920" t="str">
-        <v>horadopower</v>
+        <v>manoel.brum</v>
       </c>
       <c r="B920">
         <v>0</v>
@@ -13282,7 +13282,7 @@
     </row>
     <row r="921">
       <c r="A921" t="str">
-        <v>lyvia_genuina</v>
+        <v>horadopower</v>
       </c>
       <c r="B921">
         <v>0</v>
@@ -13296,7 +13296,7 @@
     </row>
     <row r="922">
       <c r="A922" t="str">
-        <v>delariva_belem</v>
+        <v>lyvia_genuina</v>
       </c>
       <c r="B922">
         <v>0</v>
@@ -13310,7 +13310,7 @@
     </row>
     <row r="923">
       <c r="A923" t="str">
-        <v>juugxmes</v>
+        <v>delariva_belem</v>
       </c>
       <c r="B923">
         <v>0</v>
@@ -13324,7 +13324,7 @@
     </row>
     <row r="924">
       <c r="A924" t="str">
-        <v>gabrielsantosufc_</v>
+        <v>juugxmes</v>
       </c>
       <c r="B924">
         <v>0</v>
@@ -13338,7 +13338,7 @@
     </row>
     <row r="925">
       <c r="A925" t="str">
-        <v>_matheustiberio</v>
+        <v>gabrielsantosufc_</v>
       </c>
       <c r="B925">
         <v>0</v>
@@ -13352,7 +13352,7 @@
     </row>
     <row r="926">
       <c r="A926" t="str">
-        <v>sthefany_ochoao</v>
+        <v>_matheustiberio</v>
       </c>
       <c r="B926">
         <v>0</v>
@@ -13366,7 +13366,7 @@
     </row>
     <row r="927">
       <c r="A927" t="str">
-        <v>reynitaoblitasbustamante</v>
+        <v>sthefany_ochoao</v>
       </c>
       <c r="B927">
         <v>0</v>
@@ -13380,7 +13380,7 @@
     </row>
     <row r="928">
       <c r="A928" t="str">
-        <v>joseochoa.mma</v>
+        <v>reynitaoblitasbustamante</v>
       </c>
       <c r="B928">
         <v>0</v>
@@ -13394,7 +13394,7 @@
     </row>
     <row r="929">
       <c r="A929" t="str">
-        <v>gabriellb.andrade</v>
+        <v>joseochoa.mma</v>
       </c>
       <c r="B929">
         <v>0</v>
@@ -13408,7 +13408,7 @@
     </row>
     <row r="930">
       <c r="A930" t="str">
-        <v>romelluistro</v>
+        <v>gabriellb.andrade</v>
       </c>
       <c r="B930">
         <v>0</v>
@@ -13422,7 +13422,7 @@
     </row>
     <row r="931">
       <c r="A931" t="str">
-        <v>yuricapelasso</v>
+        <v>romelluistro</v>
       </c>
       <c r="B931">
         <v>0</v>
@@ -13436,7 +13436,7 @@
     </row>
     <row r="932">
       <c r="A932" t="str">
-        <v>lucasfenomeno_ufc</v>
+        <v>yuricapelasso</v>
       </c>
       <c r="B932">
         <v>0</v>
@@ -13450,7 +13450,7 @@
     </row>
     <row r="933">
       <c r="A933" t="str">
-        <v>gabriell_marcus</v>
+        <v>lucasfenomeno_ufc</v>
       </c>
       <c r="B933">
         <v>0</v>
@@ -13464,7 +13464,7 @@
     </row>
     <row r="934">
       <c r="A934" t="str">
-        <v>lazyboy.ufc</v>
+        <v>gabriell_marcus</v>
       </c>
       <c r="B934">
         <v>0</v>
@@ -13478,7 +13478,7 @@
     </row>
     <row r="935">
       <c r="A935" t="str">
-        <v>matheusdouradomma</v>
+        <v>lazyboy.ufc</v>
       </c>
       <c r="B935">
         <v>0</v>
@@ -13492,7 +13492,7 @@
     </row>
     <row r="936">
       <c r="A936" t="str">
-        <v>rafaelsouza7586</v>
+        <v>matheusdouradomma</v>
       </c>
       <c r="B936">
         <v>0</v>
@@ -13506,7 +13506,7 @@
     </row>
     <row r="937">
       <c r="A937" t="str">
-        <v>land_on_martelo_308</v>
+        <v>rafaelsouza7586</v>
       </c>
       <c r="B937">
         <v>0</v>
@@ -13520,7 +13520,7 @@
     </row>
     <row r="938">
       <c r="A938" t="str">
-        <v>dodge_big_johnson29</v>
+        <v>land_on_martelo_308</v>
       </c>
       <c r="B938">
         <v>0</v>
@@ -13534,7 +13534,7 @@
     </row>
     <row r="939">
       <c r="A939" t="str">
-        <v>dj__freckles</v>
+        <v>dodge_big_johnson29</v>
       </c>
       <c r="B939">
         <v>0</v>
@@ -13548,7 +13548,7 @@
     </row>
     <row r="940">
       <c r="A940" t="str">
-        <v>regis18vieira</v>
+        <v>dj__freckles</v>
       </c>
       <c r="B940">
         <v>0</v>
@@ -13562,7 +13562,7 @@
     </row>
     <row r="941">
       <c r="A941" t="str">
-        <v>andy.techera.12</v>
+        <v>regis18vieira</v>
       </c>
       <c r="B941">
         <v>0</v>
@@ -13576,7 +13576,7 @@
     </row>
     <row r="942">
       <c r="A942" t="str">
-        <v>celiogarcia6</v>
+        <v>andy.techera.12</v>
       </c>
       <c r="B942">
         <v>0</v>
@@ -13590,7 +13590,7 @@
     </row>
     <row r="943">
       <c r="A943" t="str">
-        <v>luluakio</v>
+        <v>celiogarcia6</v>
       </c>
       <c r="B943">
         <v>0</v>
@@ -13604,7 +13604,7 @@
     </row>
     <row r="944">
       <c r="A944" t="str">
-        <v>barreto.boxe</v>
+        <v>luluakio</v>
       </c>
       <c r="B944">
         <v>0</v>
@@ -13618,7 +13618,7 @@
     </row>
     <row r="945">
       <c r="A945" t="str">
-        <v>lusoaresjj</v>
+        <v>barreto.boxe</v>
       </c>
       <c r="B945">
         <v>0</v>
@@ -13632,7 +13632,7 @@
     </row>
     <row r="946">
       <c r="A946" t="str">
-        <v>sharingan_mma</v>
+        <v>lusoaresjj</v>
       </c>
       <c r="B946">
         <v>0</v>
@@ -13646,28 +13646,42 @@
     </row>
     <row r="947">
       <c r="A947" t="str">
+        <v>sharingan_mma</v>
+      </c>
+      <c r="B947">
+        <v>0</v>
+      </c>
+      <c r="C947">
+        <v>1</v>
+      </c>
+      <c r="D947">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="str">
         <v>thaisadantas</v>
       </c>
-      <c r="B947">
-        <v>0</v>
-      </c>
-      <c r="C947">
-        <v>1</v>
-      </c>
-      <c r="D947">
+      <c r="B948">
+        <v>0</v>
+      </c>
+      <c r="C948">
+        <v>1</v>
+      </c>
+      <c r="D948">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D947"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D948"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D24"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -13702,10 +13716,10 @@
         <v>enzocardoso.bjj</v>
       </c>
       <c r="B3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3">
         <v>9</v>
@@ -13716,7 +13730,7 @@
         <v>pedr00jj</v>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -13730,21 +13744,21 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
         <v>4</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>natanborges001</v>
+        <v>kelly_ottoni</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -13755,7 +13769,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>combintel</v>
+        <v>natanborges001</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -13764,12 +13778,12 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>masonharper_mma</v>
+        <v>cristianpsicologo</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -13778,12 +13792,12 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>johnmma9</v>
+        <v>brcks4breakfast</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -13792,12 +13806,12 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>mmmarc20</v>
+        <v>washington_cassisno</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -13806,12 +13820,12 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>pablofiorindi</v>
+        <v>grapplerfight</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -13820,12 +13834,12 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>kelly_ottoni</v>
+        <v>galler_peace</v>
       </c>
       <c r="B12">
         <v>1</v>
@@ -13834,12 +13848,180 @@
         <v>0</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>thundergrapple</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>figh_grappler</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>anayachiottoni</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>sirleneferreiradiasdias</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>combintel</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>masonharper_mma</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>johnmma9</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>mmmarc20</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>pablofiorindi</v>
+      </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>_jullianadacruz</v>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>erickdiaseds</v>
+      </c>
+      <c r="B23">
+        <v>1</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>leobahiamma</v>
+      </c>
+      <c r="B24">
+        <v>0</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D24"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Engagement Rankings 2026-07.xlsx
+++ b/Engagement Rankings 2026-07.xlsx
@@ -419,13 +419,13 @@
         <v>peacegrappler</v>
       </c>
       <c r="B2">
-        <v>13387</v>
+        <v>13388</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>12122</v>
+        <v>12123</v>
       </c>
     </row>
     <row r="3">
@@ -475,13 +475,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B6">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="C6">
         <v>14</v>
       </c>
       <c r="D6">
-        <v>715</v>
+        <v>716</v>
       </c>
     </row>
     <row r="7">
@@ -856,10 +856,10 @@
         <v>39</v>
       </c>
       <c r="C33">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D33">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="34">
@@ -1102,44 +1102,44 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>leandrosolano_mma</v>
+        <v>propeace_fight</v>
       </c>
       <c r="B51">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C51">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="D51">
-        <v>9</v>
+        <v>22</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>cleyton_jesuss</v>
+        <v>leandrosolano_mma</v>
       </c>
       <c r="B52">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C52">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="D52">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>propeace_fight</v>
+        <v>cleyton_jesuss</v>
       </c>
       <c r="B53">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C53">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D53">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="54">
@@ -1438,44 +1438,44 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>_alvezbjj__</v>
+        <v>kelly_ottoni</v>
       </c>
       <c r="B75">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C75">
         <v>3</v>
       </c>
       <c r="D75">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>gustavomohallem</v>
+        <v>_alvezbjj__</v>
       </c>
       <c r="B76">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C76">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D76">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>kelly_ottoni</v>
+        <v>gustavomohallem</v>
       </c>
       <c r="B77">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C77">
+        <v>1</v>
+      </c>
+      <c r="D77">
         <v>3</v>
-      </c>
-      <c r="D77">
-        <v>10</v>
       </c>
     </row>
     <row r="78">
@@ -13681,7 +13681,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D25"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -13702,13 +13702,13 @@
         <v>peacegrappler</v>
       </c>
       <c r="B2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -13744,13 +13744,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B5">
+        <v>6</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
         <v>5</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -13758,32 +13758,32 @@
         <v>kelly_ottoni</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>natanborges001</v>
+        <v>washington_cassisno</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>cristianpsicologo</v>
+        <v>natanborges001</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -13797,7 +13797,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>brcks4breakfast</v>
+        <v>cristianpsicologo</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -13811,7 +13811,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>washington_cassisno</v>
+        <v>brcks4breakfast</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -13895,27 +13895,27 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>sirleneferreiradiasdias</v>
+        <v>propeace_fight</v>
       </c>
       <c r="B16">
         <v>1</v>
       </c>
       <c r="C16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>combintel</v>
+        <v>sirleneferreiradiasdias</v>
       </c>
       <c r="B17">
         <v>1</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -13923,7 +13923,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>masonharper_mma</v>
+        <v>combintel</v>
       </c>
       <c r="B18">
         <v>1</v>
@@ -13937,7 +13937,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>johnmma9</v>
+        <v>masonharper_mma</v>
       </c>
       <c r="B19">
         <v>1</v>
@@ -13951,7 +13951,7 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>mmmarc20</v>
+        <v>johnmma9</v>
       </c>
       <c r="B20">
         <v>1</v>
@@ -13965,7 +13965,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>pablofiorindi</v>
+        <v>mmmarc20</v>
       </c>
       <c r="B21">
         <v>1</v>
@@ -13979,7 +13979,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>_jullianadacruz</v>
+        <v>pablofiorindi</v>
       </c>
       <c r="B22">
         <v>1</v>
@@ -13993,7 +13993,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>erickdiaseds</v>
+        <v>_jullianadacruz</v>
       </c>
       <c r="B23">
         <v>1</v>
@@ -14007,21 +14007,35 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
+        <v>erickdiaseds</v>
+      </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
         <v>leobahiamma</v>
       </c>
-      <c r="B24">
-        <v>0</v>
-      </c>
-      <c r="C24">
-        <v>1</v>
-      </c>
-      <c r="D24">
+      <c r="B25">
+        <v>0</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="D25">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D24"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D25"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Engagement Rankings 2026-07.xlsx
+++ b/Engagement Rankings 2026-07.xlsx
@@ -419,13 +419,13 @@
         <v>peacegrappler</v>
       </c>
       <c r="B2">
-        <v>13388</v>
+        <v>13392</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>12123</v>
+        <v>12127</v>
       </c>
     </row>
     <row r="3">
@@ -461,13 +461,13 @@
         <v>enzocardoso.bjj</v>
       </c>
       <c r="B5">
-        <v>2187</v>
+        <v>2188</v>
       </c>
       <c r="C5">
         <v>32</v>
       </c>
       <c r="D5">
-        <v>992</v>
+        <v>993</v>
       </c>
     </row>
     <row r="6">
@@ -475,7 +475,7 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B6">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="C6">
         <v>14</v>
@@ -559,13 +559,13 @@
         <v>rm.nicki</v>
       </c>
       <c r="B12">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C12">
         <v>7</v>
       </c>
       <c r="D12">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="13">
@@ -856,7 +856,7 @@
         <v>39</v>
       </c>
       <c r="C33">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D33">
         <v>36</v>
@@ -1886,83 +1886,83 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>pedro_giraldi</v>
+        <v>natanborges001</v>
       </c>
       <c r="B107">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C107">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D107">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>brodschack_</v>
+        <v>pedro_giraldi</v>
       </c>
       <c r="B108">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C108">
+        <v>14</v>
+      </c>
+      <c r="D108">
         <v>5</v>
-      </c>
-      <c r="D108">
-        <v>3</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>vitor_dx_mma</v>
+        <v>brodschack_</v>
       </c>
       <c r="B109">
         <v>9</v>
       </c>
       <c r="C109">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D109">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>rosiortega</v>
+        <v>vitor_dx_mma</v>
       </c>
       <c r="B110">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C110">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D110">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>_oliveira09_</v>
+        <v>rosiortega</v>
       </c>
       <c r="B111">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C111">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D111">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>badboykillermma</v>
+        <v>_oliveira09_</v>
       </c>
       <c r="B112">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C112">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D112">
         <v>4</v>
@@ -1970,16 +1970,16 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>natanborges001</v>
+        <v>badboykillermma</v>
       </c>
       <c r="B113">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C113">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D113">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="114">
@@ -2208,55 +2208,55 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>__bielgg</v>
+        <v>mma.idiot</v>
       </c>
       <c r="B130">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C130">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D130">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>juanx.pontes</v>
+        <v>__bielgg</v>
       </c>
       <c r="B131">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C131">
         <v>3</v>
       </c>
       <c r="D131">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>paxlucta</v>
+        <v>juanx.pontes</v>
       </c>
       <c r="B132">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C132">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D132">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>muricunha</v>
+        <v>paxlucta</v>
       </c>
       <c r="B133">
         <v>5</v>
       </c>
       <c r="C133">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D133">
         <v>1</v>
@@ -2264,21 +2264,21 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>maria_bonita_kairos</v>
+        <v>muricunha</v>
       </c>
       <c r="B134">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C134">
         <v>0</v>
       </c>
       <c r="D134">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>f.luan_11</v>
+        <v>maria_bonita_kairos</v>
       </c>
       <c r="B135">
         <v>7</v>
@@ -2292,35 +2292,35 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>dennerfenomeno</v>
+        <v>f.luan_11</v>
       </c>
       <c r="B136">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C136">
         <v>0</v>
       </c>
       <c r="D136">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>hellenzinha.alves</v>
+        <v>dennerfenomeno</v>
       </c>
       <c r="B137">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C137">
         <v>0</v>
       </c>
       <c r="D137">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>hollenberg.personal</v>
+        <v>hellenzinha.alves</v>
       </c>
       <c r="B138">
         <v>7</v>
@@ -2334,55 +2334,55 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>fredoctmma</v>
+        <v>hollenberg.personal</v>
       </c>
       <c r="B139">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C139">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D139">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>thiagodossantossilvasantos</v>
+        <v>fredoctmma</v>
       </c>
       <c r="B140">
+        <v>3</v>
+      </c>
+      <c r="C140">
+        <v>3</v>
+      </c>
+      <c r="D140">
         <v>4</v>
-      </c>
-      <c r="C140">
-        <v>0</v>
-      </c>
-      <c r="D140">
-        <v>2</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>elienelucindo_oficial</v>
+        <v>thiagodossantossilvasantos</v>
       </c>
       <c r="B141">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C141">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D141">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>edinalvajanjacomo</v>
+        <v>elienelucindo_oficial</v>
       </c>
       <c r="B142">
         <v>6</v>
       </c>
       <c r="C142">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D142">
         <v>0</v>
@@ -2390,13 +2390,13 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>combatclubsp</v>
+        <v>edinalvajanjacomo</v>
       </c>
       <c r="B143">
         <v>6</v>
       </c>
       <c r="C143">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D143">
         <v>0</v>
@@ -2404,77 +2404,77 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>eric.shpritz</v>
+        <v>combatclubsp</v>
       </c>
       <c r="B144">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C144">
         <v>2</v>
       </c>
       <c r="D144">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>edaregiao</v>
+        <v>eric.shpritz</v>
       </c>
       <c r="B145">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C145">
         <v>2</v>
       </c>
       <c r="D145">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>f.ostini</v>
+        <v>edaregiao</v>
       </c>
       <c r="B146">
         <v>4</v>
       </c>
       <c r="C146">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D146">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>adrianoams7</v>
+        <v>f.ostini</v>
       </c>
       <c r="B147">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C147">
         <v>1</v>
       </c>
       <c r="D147">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>dagestan0920</v>
+        <v>adrianoams7</v>
       </c>
       <c r="B148">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C148">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D148">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>cesar.boanerges</v>
+        <v>dagestan0920</v>
       </c>
       <c r="B149">
         <v>5</v>
@@ -2488,35 +2488,35 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>tatibscardoso</v>
+        <v>cesar.boanerges</v>
       </c>
       <c r="B150">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C150">
         <v>0</v>
       </c>
       <c r="D150">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>olifrankiw</v>
+        <v>tatibscardoso</v>
       </c>
       <c r="B151">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C151">
         <v>0</v>
       </c>
       <c r="D151">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>mayarinhafreestyle</v>
+        <v>olifrankiw</v>
       </c>
       <c r="B152">
         <v>6</v>
@@ -2530,16 +2530,16 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>mma.idiot</v>
+        <v>mayarinhafreestyle</v>
       </c>
       <c r="B153">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C153">
         <v>0</v>
       </c>
       <c r="D153">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154">
@@ -13681,7 +13681,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D27"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -13702,13 +13702,13 @@
         <v>peacegrappler</v>
       </c>
       <c r="B2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -13716,41 +13716,41 @@
         <v>enzocardoso.bjj</v>
       </c>
       <c r="B3">
+        <v>11</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
         <v>10</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>pedr00jj</v>
+        <v>quemuel_ottoni</v>
       </c>
       <c r="B4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C4">
         <v>0</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>quemuel_ottoni</v>
+        <v>pedr00jj</v>
       </c>
       <c r="B5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -13769,13 +13769,13 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>washington_cassisno</v>
+        <v>natanborges001</v>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7">
         <v>2</v>
@@ -13783,16 +13783,16 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>natanborges001</v>
+        <v>washington_cassisno</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -13909,21 +13909,21 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>sirleneferreiradiasdias</v>
+        <v>rm.nicki</v>
       </c>
       <c r="B17">
         <v>1</v>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>combintel</v>
+        <v>mma.idiot</v>
       </c>
       <c r="B18">
         <v>1</v>
@@ -13932,18 +13932,18 @@
         <v>0</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>masonharper_mma</v>
+        <v>sirleneferreiradiasdias</v>
       </c>
       <c r="B19">
         <v>1</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -13951,7 +13951,7 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>johnmma9</v>
+        <v>combintel</v>
       </c>
       <c r="B20">
         <v>1</v>
@@ -13965,7 +13965,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>mmmarc20</v>
+        <v>masonharper_mma</v>
       </c>
       <c r="B21">
         <v>1</v>
@@ -13979,7 +13979,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>pablofiorindi</v>
+        <v>johnmma9</v>
       </c>
       <c r="B22">
         <v>1</v>
@@ -13993,7 +13993,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>_jullianadacruz</v>
+        <v>mmmarc20</v>
       </c>
       <c r="B23">
         <v>1</v>
@@ -14007,7 +14007,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>erickdiaseds</v>
+        <v>pablofiorindi</v>
       </c>
       <c r="B24">
         <v>1</v>
@@ -14021,21 +14021,49 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
+        <v>_jullianadacruz</v>
+      </c>
+      <c r="B25">
+        <v>1</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>erickdiaseds</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
         <v>leobahiamma</v>
       </c>
-      <c r="B25">
-        <v>0</v>
-      </c>
-      <c r="C25">
-        <v>1</v>
-      </c>
-      <c r="D25">
+      <c r="B27">
+        <v>0</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D25"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D27"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Engagement Rankings 2026-07.xlsx
+++ b/Engagement Rankings 2026-07.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D964"/>
+  <dimension ref="A1:D969"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -475,13 +475,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B6">
-        <v>889</v>
+        <v>895</v>
       </c>
       <c r="C6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D6">
-        <v>727</v>
+        <v>734</v>
       </c>
     </row>
     <row r="7">
@@ -1298,100 +1298,100 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>mar_iarmaria</v>
+        <v>kelly_ottoni</v>
       </c>
       <c r="B65">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C65">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D65">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>eliassilverio</v>
+        <v>mar_iarmaria</v>
       </c>
       <c r="B66">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C66">
+        <v>0</v>
+      </c>
+      <c r="D66">
         <v>14</v>
-      </c>
-      <c r="D66">
-        <v>9</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>gra_jpereira</v>
+        <v>eliassilverio</v>
       </c>
       <c r="B67">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C67">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D67">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>alvesmidih</v>
+        <v>gra_jpereira</v>
       </c>
       <c r="B68">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C68">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D68">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>marcelogabrielmma</v>
+        <v>alvesmidih</v>
       </c>
       <c r="B69">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C69">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D69">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>vndcardoso</v>
+        <v>marcelogabrielmma</v>
       </c>
       <c r="B70">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C70">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D70">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>kelly_ottoni</v>
+        <v>vndcardoso</v>
       </c>
       <c r="B71">
         <v>20</v>
       </c>
       <c r="C71">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D71">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="72">
@@ -1704,13 +1704,13 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>edebetim_</v>
+        <v>natanborges001</v>
       </c>
       <c r="B94">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C94">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D94">
         <v>9</v>
@@ -1718,13 +1718,13 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>natanborges001</v>
+        <v>edebetim_</v>
       </c>
       <c r="B95">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C95">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D95">
         <v>9</v>
@@ -3258,7 +3258,7 @@
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>victorhenriquebjj</v>
+        <v>helenmacielmma</v>
       </c>
       <c r="B205">
         <v>2</v>
@@ -3267,12 +3267,12 @@
         <v>0</v>
       </c>
       <c r="D205">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>eduardorobjj</v>
+        <v>victorhenriquebjj</v>
       </c>
       <c r="B206">
         <v>2</v>
@@ -3286,7 +3286,7 @@
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>diego.dieguito.3914</v>
+        <v>eduardorobjj</v>
       </c>
       <c r="B207">
         <v>2</v>
@@ -3300,7 +3300,7 @@
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>aerowellsports</v>
+        <v>diego.dieguito.3914</v>
       </c>
       <c r="B208">
         <v>2</v>
@@ -3314,7 +3314,7 @@
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>royrosiano</v>
+        <v>aerowellsports</v>
       </c>
       <c r="B209">
         <v>2</v>
@@ -3328,7 +3328,7 @@
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>febrancatti</v>
+        <v>royrosiano</v>
       </c>
       <c r="B210">
         <v>2</v>
@@ -3342,7 +3342,7 @@
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>sensei_rogerio_baltazar</v>
+        <v>febrancatti</v>
       </c>
       <c r="B211">
         <v>2</v>
@@ -3356,7 +3356,7 @@
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>jpaulo.mma</v>
+        <v>sensei_rogerio_baltazar</v>
       </c>
       <c r="B212">
         <v>2</v>
@@ -3370,7 +3370,7 @@
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>william_beckett12345</v>
+        <v>jpaulo.mma</v>
       </c>
       <c r="B213">
         <v>2</v>
@@ -3384,7 +3384,7 @@
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>_falcao95_</v>
+        <v>william_beckett12345</v>
       </c>
       <c r="B214">
         <v>2</v>
@@ -3398,7 +3398,7 @@
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>janyson.s</v>
+        <v>_falcao95_</v>
       </c>
       <c r="B215">
         <v>2</v>
@@ -3412,7 +3412,7 @@
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>rodrigo.personal.muaythai</v>
+        <v>janyson.s</v>
       </c>
       <c r="B216">
         <v>2</v>
@@ -3426,7 +3426,7 @@
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>andre_cr_daniel</v>
+        <v>rodrigo.personal.muaythai</v>
       </c>
       <c r="B217">
         <v>2</v>
@@ -3440,7 +3440,7 @@
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>wilsinho.campos</v>
+        <v>andre_cr_daniel</v>
       </c>
       <c r="B218">
         <v>2</v>
@@ -3454,7 +3454,7 @@
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>jheffzao</v>
+        <v>wilsinho.campos</v>
       </c>
       <c r="B219">
         <v>2</v>
@@ -3468,55 +3468,55 @@
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>joandersontubarao_ufc</v>
+        <v>jheffzao</v>
       </c>
       <c r="B220">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C220">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D220">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>felipedasilvalucas.bjj</v>
+        <v>joandersontubarao_ufc</v>
       </c>
       <c r="B221">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C221">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D221">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>motumbo_jr</v>
+        <v>felipedasilvalucas.bjj</v>
       </c>
       <c r="B222">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C222">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D222">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>julianoalicate</v>
+        <v>motumbo_jr</v>
       </c>
       <c r="B223">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C223">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D223">
         <v>1</v>
@@ -3524,13 +3524,13 @@
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>cairorochamma</v>
+        <v>julianoalicate</v>
       </c>
       <c r="B224">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C224">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D224">
         <v>1</v>
@@ -3538,41 +3538,41 @@
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>victus_torquatus</v>
+        <v>cairorochamma</v>
       </c>
       <c r="B225">
         <v>2</v>
       </c>
       <c r="C225">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D225">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>alexsandra_kairos</v>
+        <v>victus_torquatus</v>
       </c>
       <c r="B226">
         <v>2</v>
       </c>
       <c r="C226">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D226">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>tuizainocenciorodrigues</v>
+        <v>alexsandra_kairos</v>
       </c>
       <c r="B227">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C227">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D227">
         <v>0</v>
@@ -3580,7 +3580,7 @@
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>jocyrefan_bjj_mma</v>
+        <v>tuizainocenciorodrigues</v>
       </c>
       <c r="B228">
         <v>3</v>
@@ -3594,7 +3594,7 @@
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>multiplicaaba</v>
+        <v>jocyrefan_bjj_mma</v>
       </c>
       <c r="B229">
         <v>3</v>
@@ -3608,13 +3608,13 @@
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>disk_egg</v>
+        <v>multiplicaaba</v>
       </c>
       <c r="B230">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C230">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D230">
         <v>0</v>
@@ -3622,52 +3622,52 @@
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>jose_luiz_thome</v>
+        <v>disk_egg</v>
       </c>
       <c r="B231">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C231">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D231">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>efsantos.oficial</v>
+        <v>jose_luiz_thome</v>
       </c>
       <c r="B232">
         <v>1</v>
       </c>
       <c r="C232">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D232">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>ufc_paramountsports</v>
+        <v>efsantos.oficial</v>
       </c>
       <c r="B233">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C233">
         <v>1</v>
       </c>
       <c r="D233">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>marifferreirac</v>
+        <v>ufc_paramountsports</v>
       </c>
       <c r="B234">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C234">
         <v>1</v>
@@ -3678,13 +3678,13 @@
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>mineirinho_jj</v>
+        <v>marifferreirac</v>
       </c>
       <c r="B235">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C235">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D235">
         <v>1</v>
@@ -3692,7 +3692,7 @@
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>juliochagasmma</v>
+        <v>mineirinho_jj</v>
       </c>
       <c r="B236">
         <v>2</v>
@@ -3706,35 +3706,35 @@
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>orafao1</v>
+        <v>juliochagasmma</v>
       </c>
       <c r="B237">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C237">
         <v>0</v>
       </c>
       <c r="D237">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>lopesbrunao</v>
+        <v>orafao1</v>
       </c>
       <c r="B238">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C238">
         <v>0</v>
       </c>
       <c r="D238">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>claudiaottoni19</v>
+        <v>lopesbrunao</v>
       </c>
       <c r="B239">
         <v>2</v>
@@ -3748,7 +3748,7 @@
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>sr.valter</v>
+        <v>claudiaottoni19</v>
       </c>
       <c r="B240">
         <v>2</v>
@@ -3762,7 +3762,7 @@
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>marcos.jordao.bjj</v>
+        <v>sr.valter</v>
       </c>
       <c r="B241">
         <v>2</v>
@@ -3776,49 +3776,49 @@
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>meol.socialmidia</v>
+        <v>marcos.jordao.bjj</v>
       </c>
       <c r="B242">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C242">
         <v>0</v>
       </c>
       <c r="D242">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>yamasakinhobjj</v>
+        <v>meol.socialmidia</v>
       </c>
       <c r="B243">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C243">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D243">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>mestreviniciusreviravolta</v>
+        <v>yamasakinhobjj</v>
       </c>
       <c r="B244">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C244">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D244">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>cami28_l</v>
+        <v>mestreviniciusreviravolta</v>
       </c>
       <c r="B245">
         <v>3</v>
@@ -3832,7 +3832,7 @@
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>flaviakaena</v>
+        <v>cami28_l</v>
       </c>
       <c r="B246">
         <v>3</v>
@@ -3846,63 +3846,63 @@
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>chrislima____</v>
+        <v>flaviakaena</v>
       </c>
       <c r="B247">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C247">
         <v>0</v>
       </c>
       <c r="D247">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>c.m_figth</v>
+        <v>chrislima____</v>
       </c>
       <c r="B248">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C248">
         <v>0</v>
       </c>
       <c r="D248">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>leo.ribeiro.bjj</v>
+        <v>c.m_figth</v>
       </c>
       <c r="B249">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C249">
         <v>0</v>
       </c>
       <c r="D249">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>e_car.doso</v>
+        <v>leo.ribeiro.bjj</v>
       </c>
       <c r="B250">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C250">
         <v>0</v>
       </c>
       <c r="D250">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>ellen.cristinaaa</v>
+        <v>e_car.doso</v>
       </c>
       <c r="B251">
         <v>3</v>
@@ -3916,77 +3916,77 @@
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>dgswillian</v>
+        <v>ellen.cristinaaa</v>
       </c>
       <c r="B252">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C252">
         <v>0</v>
       </c>
       <c r="D252">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>couragemma</v>
+        <v>dgswillian</v>
       </c>
       <c r="B253">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C253">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D253">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>kaua_limaofc</v>
+        <v>couragemma</v>
       </c>
       <c r="B254">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C254">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D254">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>ruangzk</v>
+        <v>kaua_limaofc</v>
       </c>
       <c r="B255">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C255">
         <v>0</v>
       </c>
       <c r="D255">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>emerson_lucaszx</v>
+        <v>ruangzk</v>
       </c>
       <c r="B256">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C256">
         <v>0</v>
       </c>
       <c r="D256">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>clouddhidden</v>
+        <v>emerson_lucaszx</v>
       </c>
       <c r="B257">
         <v>2</v>
@@ -4000,21 +4000,21 @@
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>_matheusifernandes</v>
+        <v>clouddhidden</v>
       </c>
       <c r="B258">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C258">
         <v>0</v>
       </c>
       <c r="D258">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>bryantank_</v>
+        <v>_matheusifernandes</v>
       </c>
       <c r="B259">
         <v>1</v>
@@ -4028,7 +4028,7 @@
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>ruan.arcanjo01</v>
+        <v>bryantank_</v>
       </c>
       <c r="B260">
         <v>1</v>
@@ -4042,7 +4042,7 @@
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>coyote_style_hair</v>
+        <v>ruan.arcanjo01</v>
       </c>
       <c r="B261">
         <v>1</v>
@@ -4056,7 +4056,7 @@
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>edsoncostateixeirabjj</v>
+        <v>coyote_style_hair</v>
       </c>
       <c r="B262">
         <v>1</v>
@@ -4070,55 +4070,55 @@
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>klein_hila</v>
+        <v>edsoncostateixeirabjj</v>
       </c>
       <c r="B263">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C263">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D263">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>jhonatas_ricardo</v>
+        <v>klein_hila</v>
       </c>
       <c r="B264">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C264">
         <v>1</v>
       </c>
       <c r="D264">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>vnciuss__df</v>
+        <v>jhonatas_ricardo</v>
       </c>
       <c r="B265">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C265">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D265">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>jhee_dias</v>
+        <v>vnciuss__df</v>
       </c>
       <c r="B266">
         <v>2</v>
       </c>
       <c r="C266">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D266">
         <v>0</v>
@@ -4126,35 +4126,35 @@
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>tassiogiloficial</v>
+        <v>diegosilvabjjoficial</v>
       </c>
       <c r="B267">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C267">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D267">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>nicolasmarretabjj</v>
+        <v>jhee_dias</v>
       </c>
       <c r="B268">
         <v>2</v>
       </c>
       <c r="C268">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D268">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>richards_brusen</v>
+        <v>tassiogiloficial</v>
       </c>
       <c r="B269">
         <v>2</v>
@@ -4168,21 +4168,21 @@
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>natalan_wilgner</v>
+        <v>nicolasmarretabjj</v>
       </c>
       <c r="B270">
         <v>2</v>
       </c>
       <c r="C270">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D270">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>leticiamartinspro</v>
+        <v>richards_brusen</v>
       </c>
       <c r="B271">
         <v>2</v>
@@ -4196,21 +4196,21 @@
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>danilo_marquesc</v>
+        <v>natalan_wilgner</v>
       </c>
       <c r="B272">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C272">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D272">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>lucasspaulista</v>
+        <v>leticiamartinspro</v>
       </c>
       <c r="B273">
         <v>2</v>
@@ -4224,7 +4224,7 @@
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>eltonqueirozpereira</v>
+        <v>danilo_marquesc</v>
       </c>
       <c r="B274">
         <v>1</v>
@@ -4238,7 +4238,7 @@
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>elderdiascaneladeaco</v>
+        <v>lucasspaulista</v>
       </c>
       <c r="B275">
         <v>2</v>
@@ -4252,49 +4252,49 @@
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>select_from_joao</v>
+        <v>eltonqueirozpereira</v>
       </c>
       <c r="B276">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C276">
         <v>1</v>
       </c>
       <c r="D276">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>fabaotipster</v>
+        <v>elderdiascaneladeaco</v>
       </c>
       <c r="B277">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C277">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D277">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>luanlacerda_ufc_61kg</v>
+        <v>select_from_joao</v>
       </c>
       <c r="B278">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C278">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D278">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>helenaseveribjj</v>
+        <v>fabaotipster</v>
       </c>
       <c r="B279">
         <v>1</v>
@@ -4308,41 +4308,41 @@
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>marciokeske</v>
+        <v>luanlacerda_ufc_61kg</v>
       </c>
       <c r="B280">
         <v>1</v>
       </c>
       <c r="C280">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D280">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>ommariotti</v>
+        <v>helenaseveribjj</v>
       </c>
       <c r="B281">
         <v>1</v>
       </c>
       <c r="C281">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D281">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>felipebunesufc</v>
+        <v>marciokeske</v>
       </c>
       <c r="B282">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C282">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D282">
         <v>0</v>
@@ -4350,35 +4350,35 @@
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>icarohilton</v>
+        <v>ommariotti</v>
       </c>
       <c r="B283">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C283">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D283">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>jesabelmelo9</v>
+        <v>felipebunesufc</v>
       </c>
       <c r="B284">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C284">
         <v>1</v>
       </c>
       <c r="D284">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>iranbez</v>
+        <v>icarohilton</v>
       </c>
       <c r="B285">
         <v>2</v>
@@ -4392,27 +4392,27 @@
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>sthe._.araujo</v>
+        <v>jesabelmelo9</v>
       </c>
       <c r="B286">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C286">
         <v>1</v>
       </c>
       <c r="D286">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>clayton77silva</v>
+        <v>iranbez</v>
       </c>
       <c r="B287">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C287">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D287">
         <v>0</v>
@@ -4420,7 +4420,7 @@
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>raycon_mma</v>
+        <v>sthe._.araujo</v>
       </c>
       <c r="B288">
         <v>2</v>
@@ -4434,13 +4434,13 @@
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>sarahfmaia</v>
+        <v>clayton77silva</v>
       </c>
       <c r="B289">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C289">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D289">
         <v>0</v>
@@ -4448,27 +4448,27 @@
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>rosacostasousa36</v>
+        <v>raycon_mma</v>
       </c>
       <c r="B290">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C290">
         <v>1</v>
       </c>
       <c r="D290">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>erivan_sousa_tico</v>
+        <v>sarahfmaia</v>
       </c>
       <c r="B291">
         <v>2</v>
       </c>
       <c r="C291">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D291">
         <v>0</v>
@@ -4476,13 +4476,13 @@
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>fernando.nogueira.7792</v>
+        <v>rosacostasousa36</v>
       </c>
       <c r="B292">
         <v>1</v>
       </c>
       <c r="C292">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D292">
         <v>1</v>
@@ -4490,7 +4490,7 @@
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>aliferpaulo_</v>
+        <v>erivan_sousa_tico</v>
       </c>
       <c r="B293">
         <v>2</v>
@@ -4504,35 +4504,35 @@
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>sambagabrieloficial</v>
+        <v>fernando.nogueira.7792</v>
       </c>
       <c r="B294">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C294">
         <v>0</v>
       </c>
       <c r="D294">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>raelduraes</v>
+        <v>aliferpaulo_</v>
       </c>
       <c r="B295">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C295">
         <v>0</v>
       </c>
       <c r="D295">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>martta.mariah</v>
+        <v>sambagabrieloficial</v>
       </c>
       <c r="B296">
         <v>2</v>
@@ -4546,21 +4546,21 @@
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>wlt_miguel</v>
+        <v>raelduraes</v>
       </c>
       <c r="B297">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C297">
         <v>0</v>
       </c>
       <c r="D297">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>_bety_marcal</v>
+        <v>martta.mariah</v>
       </c>
       <c r="B298">
         <v>2</v>
@@ -4574,13 +4574,13 @@
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>diegosilvabjjoficial</v>
+        <v>wlt_miguel</v>
       </c>
       <c r="B299">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C299">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D299">
         <v>0</v>
@@ -4588,7 +4588,7 @@
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>wesley_bjjvc</v>
+        <v>_bety_marcal</v>
       </c>
       <c r="B300">
         <v>2</v>
@@ -4602,7 +4602,7 @@
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>guga.llisboa_bjj</v>
+        <v>wesley_bjjvc</v>
       </c>
       <c r="B301">
         <v>2</v>
@@ -4616,21 +4616,21 @@
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>marcosmeireles_pqd_</v>
+        <v>guga.llisboa_bjj</v>
       </c>
       <c r="B302">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C302">
         <v>0</v>
       </c>
       <c r="D302">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>gabriel.junior20bjj</v>
+        <v>marcosmeireles_pqd_</v>
       </c>
       <c r="B303">
         <v>1</v>
@@ -4644,21 +4644,21 @@
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>fabi.godooy</v>
+        <v>gabriel.junior20bjj</v>
       </c>
       <c r="B304">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C304">
         <v>0</v>
       </c>
       <c r="D304">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>davicorbella</v>
+        <v>fabi.godooy</v>
       </c>
       <c r="B305">
         <v>2</v>
@@ -4672,7 +4672,7 @@
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>joegam3r</v>
+        <v>davicorbella</v>
       </c>
       <c r="B306">
         <v>2</v>
@@ -4686,35 +4686,35 @@
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>graalino</v>
+        <v>joegam3r</v>
       </c>
       <c r="B307">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C307">
         <v>0</v>
       </c>
       <c r="D307">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>ramanatoscanellibjj</v>
+        <v>graalino</v>
       </c>
       <c r="B308">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C308">
         <v>0</v>
       </c>
       <c r="D308">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>mariabeltapagani</v>
+        <v>ramanatoscanellibjj</v>
       </c>
       <c r="B309">
         <v>2</v>
@@ -4728,7 +4728,7 @@
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>auriceliaribeiro_</v>
+        <v>mariabeltapagani</v>
       </c>
       <c r="B310">
         <v>2</v>
@@ -4742,7 +4742,7 @@
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>craig_cohen1</v>
+        <v>auriceliaribeiro_</v>
       </c>
       <c r="B311">
         <v>2</v>
@@ -4756,35 +4756,35 @@
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>glessios_silva</v>
+        <v>craig_cohen1</v>
       </c>
       <c r="B312">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C312">
         <v>0</v>
       </c>
       <c r="D312">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>fabioincalado</v>
+        <v>glessios_silva</v>
       </c>
       <c r="B313">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C313">
         <v>0</v>
       </c>
       <c r="D313">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>vanderleiamellogois</v>
+        <v>fabioincalado</v>
       </c>
       <c r="B314">
         <v>2</v>
@@ -4798,91 +4798,91 @@
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>pedrinhosbjj</v>
+        <v>vanderleiamellogois</v>
       </c>
       <c r="B315">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C315">
         <v>0</v>
       </c>
       <c r="D315">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>_jaquealms</v>
+        <v>pedrinhosbjj</v>
       </c>
       <c r="B316">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C316">
         <v>0</v>
       </c>
       <c r="D316">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>caio.fermianoo</v>
+        <v>_jaquealms</v>
       </c>
       <c r="B317">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C317">
         <v>0</v>
       </c>
       <c r="D317">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>corrozzzive</v>
+        <v>caio.fermianoo</v>
       </c>
       <c r="B318">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C318">
         <v>0</v>
       </c>
       <c r="D318">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>araujojonaspenhade</v>
+        <v>corrozzzive</v>
       </c>
       <c r="B319">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C319">
         <v>0</v>
       </c>
       <c r="D319">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>duuleitee</v>
+        <v>araujojonaspenhade</v>
       </c>
       <c r="B320">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C320">
         <v>0</v>
       </c>
       <c r="D320">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>pvd_._dudis</v>
+        <v>duuleitee</v>
       </c>
       <c r="B321">
         <v>2</v>
@@ -4896,7 +4896,7 @@
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>boia_capoeira</v>
+        <v>pvd_._dudis</v>
       </c>
       <c r="B322">
         <v>2</v>
@@ -4910,27 +4910,27 @@
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>tatianeaguiarp</v>
+        <v>boia_capoeira</v>
       </c>
       <c r="B323">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C323">
         <v>0</v>
       </c>
       <c r="D323">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>ismael.marreta_ufc</v>
+        <v>tatianeaguiarp</v>
       </c>
       <c r="B324">
         <v>1</v>
       </c>
       <c r="C324">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D324">
         <v>1</v>
@@ -4938,13 +4938,13 @@
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>ottonhona</v>
+        <v>ismael.marreta_ufc</v>
       </c>
       <c r="B325">
         <v>1</v>
       </c>
       <c r="C325">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D325">
         <v>1</v>
@@ -4952,7 +4952,7 @@
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>alcateiaartesmarciais</v>
+        <v>ottonhona</v>
       </c>
       <c r="B326">
         <v>1</v>
@@ -4966,49 +4966,49 @@
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>marcov__7</v>
+        <v>alcateiaartesmarciais</v>
       </c>
       <c r="B327">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C327">
         <v>0</v>
       </c>
       <c r="D327">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>anachierico_</v>
+        <v>marcov__7</v>
       </c>
       <c r="B328">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C328">
         <v>0</v>
       </c>
       <c r="D328">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>toraostreet</v>
+        <v>anachierico_</v>
       </c>
       <c r="B329">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C329">
         <v>0</v>
       </c>
       <c r="D329">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>bears635</v>
+        <v>toraostreet</v>
       </c>
       <c r="B330">
         <v>2</v>
@@ -5022,7 +5022,7 @@
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>vivi_fitnees</v>
+        <v>bears635</v>
       </c>
       <c r="B331">
         <v>2</v>
@@ -5036,7 +5036,7 @@
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>shockmonteiro</v>
+        <v>vivi_fitnees</v>
       </c>
       <c r="B332">
         <v>2</v>
@@ -5050,7 +5050,7 @@
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>murilomuaythai</v>
+        <v>shockmonteiro</v>
       </c>
       <c r="B333">
         <v>2</v>
@@ -5064,35 +5064,35 @@
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>suel.f1270</v>
+        <v>murilomuaythai</v>
       </c>
       <c r="B334">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C334">
         <v>0</v>
       </c>
       <c r="D334">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>thiagoxavier13</v>
+        <v>suel.f1270</v>
       </c>
       <c r="B335">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C335">
         <v>0</v>
       </c>
       <c r="D335">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>fatima_trindade_</v>
+        <v>thiagoxavier13</v>
       </c>
       <c r="B336">
         <v>2</v>
@@ -5106,21 +5106,21 @@
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>gillesarquitetura</v>
+        <v>fatima_trindade_</v>
       </c>
       <c r="B337">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C337">
         <v>0</v>
       </c>
       <c r="D337">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>alvestank</v>
+        <v>gillesarquitetura</v>
       </c>
       <c r="B338">
         <v>1</v>
@@ -5134,35 +5134,35 @@
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>marciooangelo</v>
+        <v>alvestank</v>
       </c>
       <c r="B339">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C339">
         <v>0</v>
       </c>
       <c r="D339">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>adevaldojr_</v>
+        <v>marciooangelo</v>
       </c>
       <c r="B340">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C340">
         <v>0</v>
       </c>
       <c r="D340">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>manucanecorso.bjj</v>
+        <v>adevaldojr_</v>
       </c>
       <c r="B341">
         <v>1</v>
@@ -5176,63 +5176,63 @@
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>claudiaottoni2025</v>
+        <v>manucanecorso.bjj</v>
       </c>
       <c r="B342">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C342">
         <v>0</v>
       </c>
       <c r="D342">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>tavin.mendes</v>
+        <v>claudiaottoni2025</v>
       </c>
       <c r="B343">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C343">
         <v>0</v>
       </c>
       <c r="D343">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>_jullianadacruz</v>
+        <v>tavin.mendes</v>
       </c>
       <c r="B344">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C344">
         <v>0</v>
       </c>
       <c r="D344">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>fabiieju</v>
+        <v>_jullianadacruz</v>
       </c>
       <c r="B345">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C345">
         <v>0</v>
       </c>
       <c r="D345">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>marqueswanderson</v>
+        <v>fabiieju</v>
       </c>
       <c r="B346">
         <v>1</v>
@@ -5246,7 +5246,7 @@
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>adauto2505</v>
+        <v>marqueswanderson</v>
       </c>
       <c r="B347">
         <v>1</v>
@@ -5260,7 +5260,7 @@
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>joaogagoarta</v>
+        <v>adauto2505</v>
       </c>
       <c r="B348">
         <v>1</v>
@@ -5274,7 +5274,7 @@
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>brcks4breakfast</v>
+        <v>joaogagoarta</v>
       </c>
       <c r="B349">
         <v>1</v>
@@ -5288,7 +5288,7 @@
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>lili.munix</v>
+        <v>brcks4breakfast</v>
       </c>
       <c r="B350">
         <v>1</v>
@@ -5302,7 +5302,7 @@
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>carlos_hm_iglesias</v>
+        <v>lili.munix</v>
       </c>
       <c r="B351">
         <v>1</v>
@@ -5316,7 +5316,7 @@
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>roger_santosmma</v>
+        <v>carlos_hm_iglesias</v>
       </c>
       <c r="B352">
         <v>1</v>
@@ -5330,7 +5330,7 @@
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>murata_profight</v>
+        <v>roger_santosmma</v>
       </c>
       <c r="B353">
         <v>1</v>
@@ -5344,7 +5344,7 @@
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>helenmacielmma</v>
+        <v>murata_profight</v>
       </c>
       <c r="B354">
         <v>1</v>
@@ -5358,41 +5358,41 @@
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>dr.daniloduartefisio</v>
+        <v>zackdos</v>
       </c>
       <c r="B355">
         <v>1</v>
       </c>
       <c r="C355">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D355">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>pablo_bvg</v>
+        <v>dr.daniloduartefisio</v>
       </c>
       <c r="B356">
         <v>1</v>
       </c>
       <c r="C356">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D356">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>marceloscorzato</v>
+        <v>pablo_bvg</v>
       </c>
       <c r="B357">
         <v>1</v>
       </c>
       <c r="C357">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D357">
         <v>1</v>
@@ -5400,49 +5400,49 @@
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>sergio_alves_bjj</v>
+        <v>marceloscorzato</v>
       </c>
       <c r="B358">
         <v>1</v>
       </c>
       <c r="C358">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D358">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>pedro_pavin_</v>
+        <v>sergio_alves_bjj</v>
       </c>
       <c r="B359">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C359">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D359">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>treinaadorrafael</v>
+        <v>pedro_pavin_</v>
       </c>
       <c r="B360">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C360">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D360">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>estevaotoledo</v>
+        <v>treinaadorrafael</v>
       </c>
       <c r="B361">
         <v>1</v>
@@ -5456,13 +5456,13 @@
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>djsagatoficial</v>
+        <v>estevaotoledo</v>
       </c>
       <c r="B362">
         <v>1</v>
       </c>
       <c r="C362">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D362">
         <v>0</v>
@@ -5470,13 +5470,13 @@
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>yurimartins1_</v>
+        <v>djsagatoficial</v>
       </c>
       <c r="B363">
         <v>1</v>
       </c>
       <c r="C363">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D363">
         <v>0</v>
@@ -5484,7 +5484,7 @@
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>matheusteodoro_1</v>
+        <v>yurimartins1_</v>
       </c>
       <c r="B364">
         <v>1</v>
@@ -5498,7 +5498,7 @@
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>maria.pereiradeoliveira.5283</v>
+        <v>matheusteodoro_1</v>
       </c>
       <c r="B365">
         <v>1</v>
@@ -5512,13 +5512,13 @@
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>kael_lyto</v>
+        <v>maria.pereiradeoliveira.5283</v>
       </c>
       <c r="B366">
         <v>1</v>
       </c>
       <c r="C366">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D366">
         <v>0</v>
@@ -5526,13 +5526,13 @@
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>kawannsenaboxe</v>
+        <v>kael_lyto</v>
       </c>
       <c r="B367">
         <v>1</v>
       </c>
       <c r="C367">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D367">
         <v>0</v>
@@ -5540,7 +5540,7 @@
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>guiiviieira_</v>
+        <v>kawannsenaboxe</v>
       </c>
       <c r="B368">
         <v>1</v>
@@ -5554,7 +5554,7 @@
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>cshigueo</v>
+        <v>guiiviieira_</v>
       </c>
       <c r="B369">
         <v>1</v>
@@ -5568,7 +5568,7 @@
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>vitorhugo_vtr</v>
+        <v>cshigueo</v>
       </c>
       <c r="B370">
         <v>1</v>
@@ -5582,7 +5582,7 @@
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>danni_goncalves12</v>
+        <v>vitorhugo_vtr</v>
       </c>
       <c r="B371">
         <v>1</v>
@@ -5596,7 +5596,7 @@
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>mttsm._</v>
+        <v>danni_goncalves12</v>
       </c>
       <c r="B372">
         <v>1</v>
@@ -5610,7 +5610,7 @@
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>andrealvess02</v>
+        <v>mttsm._</v>
       </c>
       <c r="B373">
         <v>1</v>
@@ -5624,7 +5624,7 @@
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>gildojiu</v>
+        <v>andrealvess02</v>
       </c>
       <c r="B374">
         <v>1</v>
@@ -5638,13 +5638,13 @@
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>fagnerosensei</v>
+        <v>gildojiu</v>
       </c>
       <c r="B375">
         <v>1</v>
       </c>
       <c r="C375">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D375">
         <v>0</v>
@@ -5652,7 +5652,7 @@
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>flavio.dequeiroz</v>
+        <v>fagnerosensei</v>
       </c>
       <c r="B376">
         <v>1</v>
@@ -5666,13 +5666,13 @@
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>030sami</v>
+        <v>flavio.dequeiroz</v>
       </c>
       <c r="B377">
         <v>1</v>
       </c>
       <c r="C377">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D377">
         <v>0</v>
@@ -5680,35 +5680,35 @@
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>giulia.fasolato</v>
+        <v>030sami</v>
       </c>
       <c r="B378">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C378">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D378">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>selipereirapereira</v>
+        <v>giulia.fasolato</v>
       </c>
       <c r="B379">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C379">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D379">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>d.silvamma</v>
+        <v>selipereirapereira</v>
       </c>
       <c r="B380">
         <v>1</v>
@@ -5722,7 +5722,7 @@
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>kalindrafaria</v>
+        <v>d.silvamma</v>
       </c>
       <c r="B381">
         <v>1</v>
@@ -5736,35 +5736,35 @@
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>igorsiqueiramma57</v>
+        <v>kalindrafaria</v>
       </c>
       <c r="B382">
         <v>1</v>
       </c>
       <c r="C382">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D382">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>manoelwilliamdejesus</v>
+        <v>igorsiqueiramma57</v>
       </c>
       <c r="B383">
         <v>1</v>
       </c>
       <c r="C383">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D383">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>oniszczuk_ko</v>
+        <v>manoelwilliamdejesus</v>
       </c>
       <c r="B384">
         <v>1</v>
@@ -5778,7 +5778,7 @@
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>andreibjj</v>
+        <v>oniszczuk_ko</v>
       </c>
       <c r="B385">
         <v>1</v>
@@ -5792,7 +5792,7 @@
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>killemquick</v>
+        <v>andreibjj</v>
       </c>
       <c r="B386">
         <v>1</v>
@@ -5806,7 +5806,7 @@
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>chuck_tlp</v>
+        <v>killemquick</v>
       </c>
       <c r="B387">
         <v>1</v>
@@ -5820,7 +5820,7 @@
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>henriquemmunhoz</v>
+        <v>chuck_tlp</v>
       </c>
       <c r="B388">
         <v>1</v>
@@ -5834,7 +5834,7 @@
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>flavio_tuba8</v>
+        <v>henriquemmunhoz</v>
       </c>
       <c r="B389">
         <v>1</v>
@@ -5848,13 +5848,13 @@
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>koliseu.br</v>
+        <v>flavio_tuba8</v>
       </c>
       <c r="B390">
         <v>1</v>
       </c>
       <c r="C390">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D390">
         <v>0</v>
@@ -5862,41 +5862,41 @@
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>aida_dos_sonhos</v>
+        <v>koliseu.br</v>
       </c>
       <c r="B391">
         <v>1</v>
       </c>
       <c r="C391">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D391">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>plmoreiraz</v>
+        <v>aida_dos_sonhos</v>
       </c>
       <c r="B392">
         <v>1</v>
       </c>
       <c r="C392">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D392">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>cathya_ferreira</v>
+        <v>plmoreiraz</v>
       </c>
       <c r="B393">
         <v>1</v>
       </c>
       <c r="C393">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D393">
         <v>0</v>
@@ -5904,13 +5904,13 @@
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>marianappedro</v>
+        <v>cathya_ferreira</v>
       </c>
       <c r="B394">
         <v>1</v>
       </c>
       <c r="C394">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D394">
         <v>0</v>
@@ -5918,7 +5918,7 @@
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>morena_ramos</v>
+        <v>marianappedro</v>
       </c>
       <c r="B395">
         <v>1</v>
@@ -5932,21 +5932,21 @@
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>_pedro0h</v>
+        <v>morena_ramos</v>
       </c>
       <c r="B396">
         <v>1</v>
       </c>
       <c r="C396">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D396">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>yeslifeacademia</v>
+        <v>_pedro0h</v>
       </c>
       <c r="B397">
         <v>1</v>
@@ -5955,12 +5955,12 @@
         <v>1</v>
       </c>
       <c r="D397">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>ojaimerocha</v>
+        <v>yeslifeacademia</v>
       </c>
       <c r="B398">
         <v>1</v>
@@ -5974,7 +5974,7 @@
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>percepcar</v>
+        <v>ojaimerocha</v>
       </c>
       <c r="B399">
         <v>1</v>
@@ -5988,7 +5988,7 @@
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>edergama.mma</v>
+        <v>percepcar</v>
       </c>
       <c r="B400">
         <v>1</v>
@@ -6002,7 +6002,7 @@
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>eliandropires</v>
+        <v>edergama.mma</v>
       </c>
       <c r="B401">
         <v>1</v>
@@ -6016,7 +6016,7 @@
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>_gabrielpego</v>
+        <v>eliandropires</v>
       </c>
       <c r="B402">
         <v>1</v>
@@ -6030,7 +6030,7 @@
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>motumbo_team</v>
+        <v>_gabrielpego</v>
       </c>
       <c r="B403">
         <v>1</v>
@@ -6044,7 +6044,7 @@
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>eusoufernandosaito</v>
+        <v>motumbo_team</v>
       </c>
       <c r="B404">
         <v>1</v>
@@ -6058,7 +6058,7 @@
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>jenifer.ciborg</v>
+        <v>eusoufernandosaito</v>
       </c>
       <c r="B405">
         <v>1</v>
@@ -6072,7 +6072,7 @@
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>beabmendes_</v>
+        <v>jenifer.ciborg</v>
       </c>
       <c r="B406">
         <v>1</v>
@@ -6086,7 +6086,7 @@
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>felipefrancoufc</v>
+        <v>beabmendes_</v>
       </c>
       <c r="B407">
         <v>1</v>
@@ -6100,7 +6100,7 @@
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>leonardoo_paixao</v>
+        <v>felipefrancoufc</v>
       </c>
       <c r="B408">
         <v>1</v>
@@ -6114,35 +6114,35 @@
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>antonioemanuel.13</v>
+        <v>leonardoo_paixao</v>
       </c>
       <c r="B409">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C409">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D409">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>gasparjr1983</v>
+        <v>antonioemanuel.13</v>
       </c>
       <c r="B410">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C410">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D410">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>magnoddias</v>
+        <v>gasparjr1983</v>
       </c>
       <c r="B411">
         <v>1</v>
@@ -6156,7 +6156,7 @@
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>ballestarbosa</v>
+        <v>magnoddias</v>
       </c>
       <c r="B412">
         <v>1</v>
@@ -6170,7 +6170,7 @@
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>marcioticotobarbosa</v>
+        <v>ballestarbosa</v>
       </c>
       <c r="B413">
         <v>1</v>
@@ -6184,7 +6184,7 @@
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>renan.dniz</v>
+        <v>marcioticotobarbosa</v>
       </c>
       <c r="B414">
         <v>1</v>
@@ -6198,7 +6198,7 @@
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>nunesjanjacomo</v>
+        <v>renan.dniz</v>
       </c>
       <c r="B415">
         <v>1</v>
@@ -6212,7 +6212,7 @@
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>eumarianojr</v>
+        <v>nunesjanjacomo</v>
       </c>
       <c r="B416">
         <v>1</v>
@@ -6226,7 +6226,7 @@
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>mmapalpitex</v>
+        <v>eumarianojr</v>
       </c>
       <c r="B417">
         <v>1</v>
@@ -6240,7 +6240,7 @@
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>george.laroque</v>
+        <v>mmapalpitex</v>
       </c>
       <c r="B418">
         <v>1</v>
@@ -6254,7 +6254,7 @@
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>chillyfit007</v>
+        <v>george.laroque</v>
       </c>
       <c r="B419">
         <v>1</v>
@@ -6268,7 +6268,7 @@
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>cassiosants__</v>
+        <v>chillyfit007</v>
       </c>
       <c r="B420">
         <v>1</v>
@@ -6282,13 +6282,13 @@
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>rafaela_duaartee</v>
+        <v>cassiosants__</v>
       </c>
       <c r="B421">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C421">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D421">
         <v>0</v>
@@ -6296,13 +6296,13 @@
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>wagner_alexandre_w_a</v>
+        <v>rafaela_duaartee</v>
       </c>
       <c r="B422">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C422">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D422">
         <v>0</v>
@@ -6310,7 +6310,7 @@
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>andre.legendre.10</v>
+        <v>wagner_alexandre_w_a</v>
       </c>
       <c r="B423">
         <v>1</v>
@@ -6324,7 +6324,7 @@
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>phillipe.harry</v>
+        <v>andre.legendre.10</v>
       </c>
       <c r="B424">
         <v>1</v>
@@ -6338,7 +6338,7 @@
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>andrejetx</v>
+        <v>phillipe.harry</v>
       </c>
       <c r="B425">
         <v>1</v>
@@ -6352,7 +6352,7 @@
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>leandro_motiv4</v>
+        <v>andrejetx</v>
       </c>
       <c r="B426">
         <v>1</v>
@@ -6366,7 +6366,7 @@
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>olga.oliveira013</v>
+        <v>leandro_motiv4</v>
       </c>
       <c r="B427">
         <v>1</v>
@@ -6380,7 +6380,7 @@
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>vinyrodriguesoficial</v>
+        <v>olga.oliveira013</v>
       </c>
       <c r="B428">
         <v>1</v>
@@ -6394,7 +6394,7 @@
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>leosacraa</v>
+        <v>vinyrodriguesoficial</v>
       </c>
       <c r="B429">
         <v>1</v>
@@ -6408,7 +6408,7 @@
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>gutocriativo</v>
+        <v>leosacraa</v>
       </c>
       <c r="B430">
         <v>1</v>
@@ -6422,7 +6422,7 @@
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>igorfso_</v>
+        <v>gutocriativo</v>
       </c>
       <c r="B431">
         <v>1</v>
@@ -6436,7 +6436,7 @@
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>gabrielsilva_mma</v>
+        <v>igorfso_</v>
       </c>
       <c r="B432">
         <v>1</v>
@@ -6450,7 +6450,7 @@
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>lay_roqs</v>
+        <v>gabrielsilva_mma</v>
       </c>
       <c r="B433">
         <v>1</v>
@@ -6464,7 +6464,7 @@
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>bigjota.music</v>
+        <v>lay_roqs</v>
       </c>
       <c r="B434">
         <v>1</v>
@@ -6478,7 +6478,7 @@
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>jhoninhaoficial031</v>
+        <v>bigjota.music</v>
       </c>
       <c r="B435">
         <v>1</v>
@@ -6492,7 +6492,7 @@
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>mth_fernandes031</v>
+        <v>jhoninhaoficial031</v>
       </c>
       <c r="B436">
         <v>1</v>
@@ -6506,7 +6506,7 @@
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>cezary_oleksiejczuk</v>
+        <v>mth_fernandes031</v>
       </c>
       <c r="B437">
         <v>1</v>
@@ -6520,7 +6520,7 @@
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>_alcantara.bru</v>
+        <v>cezary_oleksiejczuk</v>
       </c>
       <c r="B438">
         <v>1</v>
@@ -6534,7 +6534,7 @@
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>_puroosso88</v>
+        <v>_alcantara.bru</v>
       </c>
       <c r="B439">
         <v>1</v>
@@ -6548,7 +6548,7 @@
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>_rayysp</v>
+        <v>_puroosso88</v>
       </c>
       <c r="B440">
         <v>1</v>
@@ -6562,7 +6562,7 @@
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>cami.terra_</v>
+        <v>_rayysp</v>
       </c>
       <c r="B441">
         <v>1</v>
@@ -6576,7 +6576,7 @@
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>gabicardoson</v>
+        <v>cami.terra_</v>
       </c>
       <c r="B442">
         <v>1</v>
@@ -6590,7 +6590,7 @@
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>pietroshz</v>
+        <v>gabicardoson</v>
       </c>
       <c r="B443">
         <v>1</v>
@@ -6604,7 +6604,7 @@
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>___neller</v>
+        <v>pietroshz</v>
       </c>
       <c r="B444">
         <v>1</v>
@@ -6618,7 +6618,7 @@
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>guilhermeefelix__</v>
+        <v>___neller</v>
       </c>
       <c r="B445">
         <v>1</v>
@@ -6632,7 +6632,7 @@
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>pativinisf</v>
+        <v>guilhermeefelix__</v>
       </c>
       <c r="B446">
         <v>1</v>
@@ -6646,7 +6646,7 @@
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>judadany</v>
+        <v>pativinisf</v>
       </c>
       <c r="B447">
         <v>1</v>
@@ -6660,7 +6660,7 @@
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>andre_alcausa</v>
+        <v>judadany</v>
       </c>
       <c r="B448">
         <v>1</v>
@@ -6674,7 +6674,7 @@
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>_fernunes</v>
+        <v>andre_alcausa</v>
       </c>
       <c r="B449">
         <v>1</v>
@@ -6688,7 +6688,7 @@
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>aloirmarcal</v>
+        <v>_fernunes</v>
       </c>
       <c r="B450">
         <v>1</v>
@@ -6702,7 +6702,7 @@
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>gilberto_7606</v>
+        <v>aloirmarcal</v>
       </c>
       <c r="B451">
         <v>1</v>
@@ -6716,7 +6716,7 @@
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>flazuera14</v>
+        <v>gilberto_7606</v>
       </c>
       <c r="B452">
         <v>1</v>
@@ -6730,7 +6730,7 @@
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>camii_bonfim</v>
+        <v>flazuera14</v>
       </c>
       <c r="B453">
         <v>1</v>
@@ -6744,7 +6744,7 @@
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>danlouiz.jj</v>
+        <v>camii_bonfim</v>
       </c>
       <c r="B454">
         <v>1</v>
@@ -6758,7 +6758,7 @@
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>gabriel_trevelin</v>
+        <v>danlouiz.jj</v>
       </c>
       <c r="B455">
         <v>1</v>
@@ -6772,7 +6772,7 @@
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>_lsanchess_</v>
+        <v>gabriel_trevelin</v>
       </c>
       <c r="B456">
         <v>1</v>
@@ -6786,7 +6786,7 @@
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>mr__rlk01</v>
+        <v>_lsanchess_</v>
       </c>
       <c r="B457">
         <v>1</v>
@@ -6800,7 +6800,7 @@
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>vitor_buck</v>
+        <v>mr__rlk01</v>
       </c>
       <c r="B458">
         <v>1</v>
@@ -6814,7 +6814,7 @@
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>fran.ruys</v>
+        <v>vitor_buck</v>
       </c>
       <c r="B459">
         <v>1</v>
@@ -6828,7 +6828,7 @@
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>arthurhenrique.sx</v>
+        <v>fran.ruys</v>
       </c>
       <c r="B460">
         <v>1</v>
@@ -6842,7 +6842,7 @@
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>draanapaulaponceano</v>
+        <v>arthurhenrique.sx</v>
       </c>
       <c r="B461">
         <v>1</v>
@@ -6856,7 +6856,7 @@
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>saj_photo_miami</v>
+        <v>draanapaulaponceano</v>
       </c>
       <c r="B462">
         <v>1</v>
@@ -6870,7 +6870,7 @@
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>alternativaremocoes</v>
+        <v>saj_photo_miami</v>
       </c>
       <c r="B463">
         <v>1</v>
@@ -6884,7 +6884,7 @@
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>benivalentinn</v>
+        <v>alternativaremocoes</v>
       </c>
       <c r="B464">
         <v>1</v>
@@ -6898,7 +6898,7 @@
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>miguelrodriguesbjj</v>
+        <v>benivalentinn</v>
       </c>
       <c r="B465">
         <v>1</v>
@@ -6912,7 +6912,7 @@
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>navarro_9430</v>
+        <v>miguelrodriguesbjj</v>
       </c>
       <c r="B466">
         <v>1</v>
@@ -6926,7 +6926,7 @@
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>charlesanthony2466</v>
+        <v>navarro_9430</v>
       </c>
       <c r="B467">
         <v>1</v>
@@ -6940,7 +6940,7 @@
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>xavyeroficial</v>
+        <v>charlesanthony2466</v>
       </c>
       <c r="B468">
         <v>1</v>
@@ -6954,7 +6954,7 @@
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>maryanagandra</v>
+        <v>xavyeroficial</v>
       </c>
       <c r="B469">
         <v>1</v>
@@ -6968,7 +6968,7 @@
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>katiaecarreraf</v>
+        <v>maryanagandra</v>
       </c>
       <c r="B470">
         <v>1</v>
@@ -6982,7 +6982,7 @@
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>geraldocnetomma</v>
+        <v>katiaecarreraf</v>
       </c>
       <c r="B471">
         <v>1</v>
@@ -6996,13 +6996,13 @@
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>marinealcausa</v>
+        <v>geraldocnetomma</v>
       </c>
       <c r="B472">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C472">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D472">
         <v>0</v>
@@ -7010,13 +7010,13 @@
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>artemio_bjj</v>
+        <v>marinealcausa</v>
       </c>
       <c r="B473">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C473">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D473">
         <v>0</v>
@@ -7024,7 +7024,7 @@
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>carolinne.xwp</v>
+        <v>artemio_bjj</v>
       </c>
       <c r="B474">
         <v>1</v>
@@ -7038,7 +7038,7 @@
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>isaac.bah_starinazzo</v>
+        <v>carolinne.xwp</v>
       </c>
       <c r="B475">
         <v>1</v>
@@ -7052,7 +7052,7 @@
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>lara.rpr</v>
+        <v>isaac.bah_starinazzo</v>
       </c>
       <c r="B476">
         <v>1</v>
@@ -7066,7 +7066,7 @@
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>codasqueves</v>
+        <v>lara.rpr</v>
       </c>
       <c r="B477">
         <v>1</v>
@@ -7080,7 +7080,7 @@
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>yan_touro_.7766</v>
+        <v>codasqueves</v>
       </c>
       <c r="B478">
         <v>1</v>
@@ -7094,7 +7094,7 @@
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>brothers_of_life</v>
+        <v>yan_touro_.7766</v>
       </c>
       <c r="B479">
         <v>1</v>
@@ -7108,7 +7108,7 @@
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>teacherthalesyouplus</v>
+        <v>brothers_of_life</v>
       </c>
       <c r="B480">
         <v>1</v>
@@ -7122,7 +7122,7 @@
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>minotaurinho</v>
+        <v>teacherthalesyouplus</v>
       </c>
       <c r="B481">
         <v>1</v>
@@ -7136,7 +7136,7 @@
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>anahangelica</v>
+        <v>minotaurinho</v>
       </c>
       <c r="B482">
         <v>1</v>
@@ -7150,7 +7150,7 @@
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>frankikolimabjj</v>
+        <v>anahangelica</v>
       </c>
       <c r="B483">
         <v>1</v>
@@ -7164,7 +7164,7 @@
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>tonketjudes</v>
+        <v>frankikolimabjj</v>
       </c>
       <c r="B484">
         <v>1</v>
@@ -7178,7 +7178,7 @@
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>_eliasffx</v>
+        <v>tonketjudes</v>
       </c>
       <c r="B485">
         <v>1</v>
@@ -7192,7 +7192,7 @@
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>pdfiv</v>
+        <v>_eliasffx</v>
       </c>
       <c r="B486">
         <v>1</v>
@@ -7206,7 +7206,7 @@
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>mariaraimundad940</v>
+        <v>pdfiv</v>
       </c>
       <c r="B487">
         <v>1</v>
@@ -7220,7 +7220,7 @@
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>gabesantos.13</v>
+        <v>mariaraimundad940</v>
       </c>
       <c r="B488">
         <v>1</v>
@@ -7234,7 +7234,7 @@
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>euvitormirandaa</v>
+        <v>gabesantos.13</v>
       </c>
       <c r="B489">
         <v>1</v>
@@ -7248,7 +7248,7 @@
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>gandra.julya</v>
+        <v>euvitormirandaa</v>
       </c>
       <c r="B490">
         <v>1</v>
@@ -7262,7 +7262,7 @@
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>espacomarcialino</v>
+        <v>gandra.julya</v>
       </c>
       <c r="B491">
         <v>1</v>
@@ -7276,7 +7276,7 @@
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>azulcapoeirabjj</v>
+        <v>espacomarcialino</v>
       </c>
       <c r="B492">
         <v>1</v>
@@ -7290,7 +7290,7 @@
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>andreiaatleta</v>
+        <v>azulcapoeirabjj</v>
       </c>
       <c r="B493">
         <v>1</v>
@@ -7304,7 +7304,7 @@
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>luhluhm</v>
+        <v>andreiaatleta</v>
       </c>
       <c r="B494">
         <v>1</v>
@@ -7318,7 +7318,7 @@
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>jack_hashimoto</v>
+        <v>luhluhm</v>
       </c>
       <c r="B495">
         <v>1</v>
@@ -7332,7 +7332,7 @@
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>do_caex_wandel</v>
+        <v>jack_hashimoto</v>
       </c>
       <c r="B496">
         <v>1</v>
@@ -7346,7 +7346,7 @@
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>eu_felipe_leite</v>
+        <v>do_caex_wandel</v>
       </c>
       <c r="B497">
         <v>1</v>
@@ -7360,7 +7360,7 @@
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>selma.ribeirotr</v>
+        <v>eu_felipe_leite</v>
       </c>
       <c r="B498">
         <v>1</v>
@@ -7374,7 +7374,7 @@
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>valqsm</v>
+        <v>selma.ribeirotr</v>
       </c>
       <c r="B499">
         <v>1</v>
@@ -7388,7 +7388,7 @@
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>nutrivan.alves</v>
+        <v>valqsm</v>
       </c>
       <c r="B500">
         <v>1</v>
@@ -7402,7 +7402,7 @@
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>allisonestuchi_fisioterapeuta</v>
+        <v>nutrivan.alves</v>
       </c>
       <c r="B501">
         <v>1</v>
@@ -7416,7 +7416,7 @@
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>sidneibabu</v>
+        <v>allisonestuchi_fisioterapeuta</v>
       </c>
       <c r="B502">
         <v>1</v>
@@ -7430,7 +7430,7 @@
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>muriloo__ferreira</v>
+        <v>sidneibabu</v>
       </c>
       <c r="B503">
         <v>1</v>
@@ -7444,7 +7444,7 @@
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>drfelipeoliveira_adv</v>
+        <v>muriloo__ferreira</v>
       </c>
       <c r="B504">
         <v>1</v>
@@ -7458,7 +7458,7 @@
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>turmanmma</v>
+        <v>drfelipeoliveira_adv</v>
       </c>
       <c r="B505">
         <v>1</v>
@@ -7472,7 +7472,7 @@
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>andre_luizdj</v>
+        <v>turmanmma</v>
       </c>
       <c r="B506">
         <v>1</v>
@@ -7486,7 +7486,7 @@
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>lumarasantosjj</v>
+        <v>andre_luizdj</v>
       </c>
       <c r="B507">
         <v>1</v>
@@ -7500,7 +7500,7 @@
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>donrey_42</v>
+        <v>lumarasantosjj</v>
       </c>
       <c r="B508">
         <v>1</v>
@@ -7514,7 +7514,7 @@
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>personalmaju</v>
+        <v>donrey_42</v>
       </c>
       <c r="B509">
         <v>1</v>
@@ -7528,7 +7528,7 @@
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>itsmayraregina</v>
+        <v>personalmaju</v>
       </c>
       <c r="B510">
         <v>1</v>
@@ -7542,7 +7542,7 @@
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>fototatico</v>
+        <v>itsmayraregina</v>
       </c>
       <c r="B511">
         <v>1</v>
@@ -7556,7 +7556,7 @@
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>michel.juliano.barbershop</v>
+        <v>fototatico</v>
       </c>
       <c r="B512">
         <v>1</v>
@@ -7570,7 +7570,7 @@
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>ruperto_696</v>
+        <v>michel.juliano.barbershop</v>
       </c>
       <c r="B513">
         <v>1</v>
@@ -7584,7 +7584,7 @@
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>diegomoisesribeiro</v>
+        <v>ruperto_696</v>
       </c>
       <c r="B514">
         <v>1</v>
@@ -7598,7 +7598,7 @@
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>lucca_bjj_01</v>
+        <v>diegomoisesribeiro</v>
       </c>
       <c r="B515">
         <v>1</v>
@@ -7612,7 +7612,7 @@
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>calebe1000grau</v>
+        <v>lucca_bjj_01</v>
       </c>
       <c r="B516">
         <v>1</v>
@@ -7626,7 +7626,7 @@
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>brunito_bernardo</v>
+        <v>calebe1000grau</v>
       </c>
       <c r="B517">
         <v>1</v>
@@ -7640,7 +7640,7 @@
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>clarianavillasboasoficial</v>
+        <v>brunito_bernardo</v>
       </c>
       <c r="B518">
         <v>1</v>
@@ -7654,7 +7654,7 @@
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>gladyador_do_asa</v>
+        <v>clarianavillasboasoficial</v>
       </c>
       <c r="B519">
         <v>1</v>
@@ -7668,7 +7668,7 @@
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>aureooficial</v>
+        <v>gladyador_do_asa</v>
       </c>
       <c r="B520">
         <v>1</v>
@@ -7682,7 +7682,7 @@
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>williamjanser</v>
+        <v>aureooficial</v>
       </c>
       <c r="B521">
         <v>1</v>
@@ -7696,7 +7696,7 @@
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>jeremyericjacobs</v>
+        <v>williamjanser</v>
       </c>
       <c r="B522">
         <v>1</v>
@@ -7710,7 +7710,7 @@
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>chicinvancity</v>
+        <v>jeremyericjacobs</v>
       </c>
       <c r="B523">
         <v>1</v>
@@ -7724,7 +7724,7 @@
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>susiemelchionda</v>
+        <v>chicinvancity</v>
       </c>
       <c r="B524">
         <v>1</v>
@@ -7738,7 +7738,7 @@
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>satsangbjj</v>
+        <v>susiemelchionda</v>
       </c>
       <c r="B525">
         <v>1</v>
@@ -7752,7 +7752,7 @@
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>gallupistrengthconditioning</v>
+        <v>satsangbjj</v>
       </c>
       <c r="B526">
         <v>1</v>
@@ -7766,7 +7766,7 @@
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>danibastiaan</v>
+        <v>gallupistrengthconditioning</v>
       </c>
       <c r="B527">
         <v>1</v>
@@ -7780,7 +7780,7 @@
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>gilcilenecristina</v>
+        <v>danibastiaan</v>
       </c>
       <c r="B528">
         <v>1</v>
@@ -7794,7 +7794,7 @@
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>andreaapurinaoficial</v>
+        <v>gilcilenecristina</v>
       </c>
       <c r="B529">
         <v>1</v>
@@ -7808,7 +7808,7 @@
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>alehh_novaes</v>
+        <v>andreaapurinaoficial</v>
       </c>
       <c r="B530">
         <v>1</v>
@@ -7822,7 +7822,7 @@
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>franklinamaral</v>
+        <v>alehh_novaes</v>
       </c>
       <c r="B531">
         <v>1</v>
@@ -7836,7 +7836,7 @@
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>valbersonsantoss</v>
+        <v>franklinamaral</v>
       </c>
       <c r="B532">
         <v>1</v>
@@ -7850,7 +7850,7 @@
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>j.borgespz</v>
+        <v>valbersonsantoss</v>
       </c>
       <c r="B533">
         <v>1</v>
@@ -7864,7 +7864,7 @@
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>gpedroza1</v>
+        <v>j.borgespz</v>
       </c>
       <c r="B534">
         <v>1</v>
@@ -7878,7 +7878,7 @@
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>almir_gdf</v>
+        <v>gpedroza1</v>
       </c>
       <c r="B535">
         <v>1</v>
@@ -7892,7 +7892,7 @@
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>renancarlini</v>
+        <v>almir_gdf</v>
       </c>
       <c r="B536">
         <v>1</v>
@@ -7906,7 +7906,7 @@
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>lucaswallaceftt</v>
+        <v>renancarlini</v>
       </c>
       <c r="B537">
         <v>1</v>
@@ -7920,7 +7920,7 @@
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>lilianvillaca_</v>
+        <v>lucaswallaceftt</v>
       </c>
       <c r="B538">
         <v>1</v>
@@ -7934,7 +7934,7 @@
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>jose_carlos_baixote</v>
+        <v>lilianvillaca_</v>
       </c>
       <c r="B539">
         <v>1</v>
@@ -7948,7 +7948,7 @@
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>projeto_amigos_de_ouro</v>
+        <v>jose_carlos_baixote</v>
       </c>
       <c r="B540">
         <v>1</v>
@@ -7962,7 +7962,7 @@
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>gratidao_jesus2026</v>
+        <v>projeto_amigos_de_ouro</v>
       </c>
       <c r="B541">
         <v>1</v>
@@ -7976,7 +7976,7 @@
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>sabe_de_uma_coisa2026</v>
+        <v>gratidao_jesus2026</v>
       </c>
       <c r="B542">
         <v>1</v>
@@ -7990,7 +7990,7 @@
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>alinedoprojeto</v>
+        <v>sabe_de_uma_coisa2026</v>
       </c>
       <c r="B543">
         <v>1</v>
@@ -8004,7 +8004,7 @@
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>dani120690</v>
+        <v>alinedoprojeto</v>
       </c>
       <c r="B544">
         <v>1</v>
@@ -8018,7 +8018,7 @@
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>raonasthai</v>
+        <v>dani120690</v>
       </c>
       <c r="B545">
         <v>1</v>
@@ -8032,7 +8032,7 @@
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>adonaibjj_grip</v>
+        <v>raonasthai</v>
       </c>
       <c r="B546">
         <v>1</v>
@@ -8046,7 +8046,7 @@
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>arturbambam</v>
+        <v>adonaibjj_grip</v>
       </c>
       <c r="B547">
         <v>1</v>
@@ -8060,7 +8060,7 @@
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>cebolajj167</v>
+        <v>arturbambam</v>
       </c>
       <c r="B548">
         <v>1</v>
@@ -8074,7 +8074,7 @@
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>danieljsantoss_</v>
+        <v>cebolajj167</v>
       </c>
       <c r="B549">
         <v>1</v>
@@ -8088,7 +8088,7 @@
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>hermaan10_</v>
+        <v>danieljsantoss_</v>
       </c>
       <c r="B550">
         <v>1</v>
@@ -8102,7 +8102,7 @@
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>markakasocks</v>
+        <v>hermaan10_</v>
       </c>
       <c r="B551">
         <v>1</v>
@@ -8116,7 +8116,7 @@
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>hunter.mccrary</v>
+        <v>markakasocks</v>
       </c>
       <c r="B552">
         <v>1</v>
@@ -8130,7 +8130,7 @@
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>davidpina_047</v>
+        <v>hunter.mccrary</v>
       </c>
       <c r="B553">
         <v>1</v>
@@ -8144,7 +8144,7 @@
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>odivaldo_lobo</v>
+        <v>davidpina_047</v>
       </c>
       <c r="B554">
         <v>1</v>
@@ -8158,7 +8158,7 @@
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>rodrigojansen_</v>
+        <v>odivaldo_lobo</v>
       </c>
       <c r="B555">
         <v>1</v>
@@ -8172,7 +8172,7 @@
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>flavia_gomes_29</v>
+        <v>rodrigojansen_</v>
       </c>
       <c r="B556">
         <v>1</v>
@@ -8186,7 +8186,7 @@
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>pelevermelha.uniformes</v>
+        <v>flavia_gomes_29</v>
       </c>
       <c r="B557">
         <v>1</v>
@@ -8200,7 +8200,7 @@
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>joao_lins_muaythai</v>
+        <v>pelevermelha.uniformes</v>
       </c>
       <c r="B558">
         <v>1</v>
@@ -8214,7 +8214,7 @@
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>omarcotomaz</v>
+        <v>joao_lins_muaythai</v>
       </c>
       <c r="B559">
         <v>1</v>
@@ -8228,7 +8228,7 @@
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>alphavillesup</v>
+        <v>omarcotomaz</v>
       </c>
       <c r="B560">
         <v>1</v>
@@ -8242,7 +8242,7 @@
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>ricieritonan</v>
+        <v>alphavillesup</v>
       </c>
       <c r="B561">
         <v>1</v>
@@ -8256,7 +8256,7 @@
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>lucasampaio</v>
+        <v>ricieritonan</v>
       </c>
       <c r="B562">
         <v>1</v>
@@ -8270,7 +8270,7 @@
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>manmoska</v>
+        <v>lucasampaio</v>
       </c>
       <c r="B563">
         <v>1</v>
@@ -8284,7 +8284,7 @@
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>renatoevangelistaa</v>
+        <v>manmoska</v>
       </c>
       <c r="B564">
         <v>1</v>
@@ -8298,7 +8298,7 @@
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>cassius.paula</v>
+        <v>renatoevangelistaa</v>
       </c>
       <c r="B565">
         <v>1</v>
@@ -8312,7 +8312,7 @@
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>ctt.casaestopteam</v>
+        <v>cassius.paula</v>
       </c>
       <c r="B566">
         <v>1</v>
@@ -8326,7 +8326,7 @@
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>moisespira</v>
+        <v>ctt.casaestopteam</v>
       </c>
       <c r="B567">
         <v>1</v>
@@ -8340,7 +8340,7 @@
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>rodrigolidiosales</v>
+        <v>moisespira</v>
       </c>
       <c r="B568">
         <v>1</v>
@@ -8354,7 +8354,7 @@
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>claudioribeiro_ufc</v>
+        <v>rodrigolidiosales</v>
       </c>
       <c r="B569">
         <v>1</v>
@@ -8368,7 +8368,7 @@
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>marciocatenacci</v>
+        <v>claudioribeiro_ufc</v>
       </c>
       <c r="B570">
         <v>1</v>
@@ -8382,7 +8382,7 @@
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>cristiane.c.santana</v>
+        <v>marciocatenacci</v>
       </c>
       <c r="B571">
         <v>1</v>
@@ -8396,7 +8396,7 @@
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>ariel_alvees</v>
+        <v>cristiane.c.santana</v>
       </c>
       <c r="B572">
         <v>1</v>
@@ -8410,7 +8410,7 @@
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>flahvinhotreinador</v>
+        <v>ariel_alvees</v>
       </c>
       <c r="B573">
         <v>1</v>
@@ -8424,7 +8424,7 @@
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>selma.oscar12</v>
+        <v>flahvinhotreinador</v>
       </c>
       <c r="B574">
         <v>1</v>
@@ -8438,7 +8438,7 @@
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>romulobelarmino</v>
+        <v>selma.oscar12</v>
       </c>
       <c r="B575">
         <v>1</v>
@@ -8452,7 +8452,7 @@
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>alberto_garcia_queiroz_junior</v>
+        <v>romulobelarmino</v>
       </c>
       <c r="B576">
         <v>1</v>
@@ -8466,7 +8466,7 @@
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>isasantos1404</v>
+        <v>alberto_garcia_queiroz_junior</v>
       </c>
       <c r="B577">
         <v>1</v>
@@ -8480,7 +8480,7 @@
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>fernandamourabjj</v>
+        <v>isasantos1404</v>
       </c>
       <c r="B578">
         <v>1</v>
@@ -8494,7 +8494,7 @@
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>larissamartinsbjj</v>
+        <v>fernandamourabjj</v>
       </c>
       <c r="B579">
         <v>1</v>
@@ -8508,7 +8508,7 @@
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>gabrielsoaresbjj</v>
+        <v>larissamartinsbjj</v>
       </c>
       <c r="B580">
         <v>1</v>
@@ -8522,7 +8522,7 @@
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>leitefelippez</v>
+        <v>gabrielsoaresbjj</v>
       </c>
       <c r="B581">
         <v>1</v>
@@ -8536,7 +8536,7 @@
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>israelbahiensebraz</v>
+        <v>leitefelippez</v>
       </c>
       <c r="B582">
         <v>1</v>
@@ -8550,7 +8550,7 @@
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>titosbjj</v>
+        <v>israelbahiensebraz</v>
       </c>
       <c r="B583">
         <v>1</v>
@@ -8564,7 +8564,7 @@
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>aldomanuel1994</v>
+        <v>titosbjj</v>
       </c>
       <c r="B584">
         <v>1</v>
@@ -8578,7 +8578,7 @@
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>x_xpatto</v>
+        <v>aldomanuel1994</v>
       </c>
       <c r="B585">
         <v>1</v>
@@ -8592,7 +8592,7 @@
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>keep.itpushinnn</v>
+        <v>x_xpatto</v>
       </c>
       <c r="B586">
         <v>1</v>
@@ -8606,7 +8606,7 @@
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>johnnydesinfluencer</v>
+        <v>keep.itpushinnn</v>
       </c>
       <c r="B587">
         <v>1</v>
@@ -8620,7 +8620,7 @@
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>ana.cristina.uno</v>
+        <v>johnnydesinfluencer</v>
       </c>
       <c r="B588">
         <v>1</v>
@@ -8634,7 +8634,7 @@
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>pbmoments_</v>
+        <v>ana.cristina.uno</v>
       </c>
       <c r="B589">
         <v>1</v>
@@ -8648,7 +8648,7 @@
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>rick.santosz</v>
+        <v>pbmoments_</v>
       </c>
       <c r="B590">
         <v>1</v>
@@ -8662,7 +8662,7 @@
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>eriikdossantoos</v>
+        <v>rick.santosz</v>
       </c>
       <c r="B591">
         <v>1</v>
@@ -8676,7 +8676,7 @@
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>sp__theus</v>
+        <v>eriikdossantoos</v>
       </c>
       <c r="B592">
         <v>1</v>
@@ -8690,7 +8690,7 @@
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>guihs_cardoso</v>
+        <v>sp__theus</v>
       </c>
       <c r="B593">
         <v>1</v>
@@ -8704,7 +8704,7 @@
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>jeffersonliu2022</v>
+        <v>guihs_cardoso</v>
       </c>
       <c r="B594">
         <v>1</v>
@@ -8718,7 +8718,7 @@
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>pettys2298</v>
+        <v>jeffersonliu2022</v>
       </c>
       <c r="B595">
         <v>1</v>
@@ -8732,7 +8732,7 @@
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>jhonny.2302_aritamma</v>
+        <v>pettys2298</v>
       </c>
       <c r="B596">
         <v>1</v>
@@ -8746,7 +8746,7 @@
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>ph_castroh</v>
+        <v>jhonny.2302_aritamma</v>
       </c>
       <c r="B597">
         <v>1</v>
@@ -8760,7 +8760,7 @@
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>paulokami.mma</v>
+        <v>ph_castroh</v>
       </c>
       <c r="B598">
         <v>1</v>
@@ -8774,7 +8774,7 @@
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>generaldantas</v>
+        <v>paulokami.mma</v>
       </c>
       <c r="B599">
         <v>1</v>
@@ -8788,7 +8788,7 @@
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>gi.liimaa_</v>
+        <v>generaldantas</v>
       </c>
       <c r="B600">
         <v>1</v>
@@ -8802,7 +8802,7 @@
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>_murilo_06</v>
+        <v>gi.liimaa_</v>
       </c>
       <c r="B601">
         <v>1</v>
@@ -8816,7 +8816,7 @@
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>biabezerra88</v>
+        <v>_murilo_06</v>
       </c>
       <c r="B602">
         <v>1</v>
@@ -8830,7 +8830,7 @@
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>geovannaalc_</v>
+        <v>biabezerra88</v>
       </c>
       <c r="B603">
         <v>1</v>
@@ -8844,7 +8844,7 @@
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>joselia_1980</v>
+        <v>geovannaalc_</v>
       </c>
       <c r="B604">
         <v>1</v>
@@ -8858,7 +8858,7 @@
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>silva_junior1979</v>
+        <v>joselia_1980</v>
       </c>
       <c r="B605">
         <v>1</v>
@@ -8872,7 +8872,7 @@
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>andreloliva12</v>
+        <v>silva_junior1979</v>
       </c>
       <c r="B606">
         <v>1</v>
@@ -8886,7 +8886,7 @@
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>soniarochaco</v>
+        <v>andreloliva12</v>
       </c>
       <c r="B607">
         <v>1</v>
@@ -8900,7 +8900,7 @@
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>leandro_pedro7</v>
+        <v>soniarochaco</v>
       </c>
       <c r="B608">
         <v>1</v>
@@ -8914,7 +8914,7 @@
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>camillinhamma</v>
+        <v>leandro_pedro7</v>
       </c>
       <c r="B609">
         <v>1</v>
@@ -8928,7 +8928,7 @@
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>martins.rauanee</v>
+        <v>camillinhamma</v>
       </c>
       <c r="B610">
         <v>1</v>
@@ -8942,7 +8942,7 @@
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>ever.soulson</v>
+        <v>martins.rauanee</v>
       </c>
       <c r="B611">
         <v>1</v>
@@ -8956,7 +8956,7 @@
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>mestrevascobento</v>
+        <v>ever.soulson</v>
       </c>
       <c r="B612">
         <v>1</v>
@@ -8970,7 +8970,7 @@
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>bernardocavalcanti1</v>
+        <v>mestrevascobento</v>
       </c>
       <c r="B613">
         <v>1</v>
@@ -8984,7 +8984,7 @@
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>terapeuta_moniquedias</v>
+        <v>bernardocavalcanti1</v>
       </c>
       <c r="B614">
         <v>1</v>
@@ -8998,7 +8998,7 @@
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>santos39roger</v>
+        <v>terapeuta_moniquedias</v>
       </c>
       <c r="B615">
         <v>1</v>
@@ -9012,7 +9012,7 @@
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>dcoops2</v>
+        <v>santos39roger</v>
       </c>
       <c r="B616">
         <v>1</v>
@@ -9026,7 +9026,7 @@
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>ricardosousa811</v>
+        <v>dcoops2</v>
       </c>
       <c r="B617">
         <v>1</v>
@@ -9040,7 +9040,7 @@
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>ludelmaraujo</v>
+        <v>ricardosousa811</v>
       </c>
       <c r="B618">
         <v>1</v>
@@ -9054,7 +9054,7 @@
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>homemdeita</v>
+        <v>ludelmaraujo</v>
       </c>
       <c r="B619">
         <v>1</v>
@@ -9068,7 +9068,7 @@
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>victorxferreira</v>
+        <v>homemdeita</v>
       </c>
       <c r="B620">
         <v>1</v>
@@ -9082,7 +9082,7 @@
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>eimysalazar</v>
+        <v>victorxferreira</v>
       </c>
       <c r="B621">
         <v>1</v>
@@ -9096,7 +9096,7 @@
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>oficialrichardsilva_ice_men</v>
+        <v>eimysalazar</v>
       </c>
       <c r="B622">
         <v>1</v>
@@ -9110,7 +9110,7 @@
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>axiaaly</v>
+        <v>oficialrichardsilva_ice_men</v>
       </c>
       <c r="B623">
         <v>1</v>
@@ -9124,7 +9124,7 @@
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>renatogomes769</v>
+        <v>axiaaly</v>
       </c>
       <c r="B624">
         <v>1</v>
@@ -9138,7 +9138,7 @@
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>adrianoblessed89</v>
+        <v>renatogomes769</v>
       </c>
       <c r="B625">
         <v>1</v>
@@ -9152,7 +9152,7 @@
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>dinhomoraisoficial</v>
+        <v>adrianoblessed89</v>
       </c>
       <c r="B626">
         <v>1</v>
@@ -9166,7 +9166,7 @@
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>santosriveiros18737383</v>
+        <v>dinhomoraisoficial</v>
       </c>
       <c r="B627">
         <v>1</v>
@@ -9180,7 +9180,7 @@
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>sr.dpaula10</v>
+        <v>santosriveiros18737383</v>
       </c>
       <c r="B628">
         <v>1</v>
@@ -9194,7 +9194,7 @@
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>pazzini__</v>
+        <v>sr.dpaula10</v>
       </c>
       <c r="B629">
         <v>1</v>
@@ -9208,7 +9208,7 @@
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>thiagomoisesmma</v>
+        <v>pazzini__</v>
       </c>
       <c r="B630">
         <v>1</v>
@@ -9222,7 +9222,7 @@
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>dobby_1968</v>
+        <v>thiagomoisesmma</v>
       </c>
       <c r="B631">
         <v>1</v>
@@ -9236,7 +9236,7 @@
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>ricardogabriel.sr</v>
+        <v>dobby_1968</v>
       </c>
       <c r="B632">
         <v>1</v>
@@ -9250,7 +9250,7 @@
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>indiopersonalfight</v>
+        <v>ricardogabriel.sr</v>
       </c>
       <c r="B633">
         <v>1</v>
@@ -9264,7 +9264,7 @@
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>_samu35</v>
+        <v>indiopersonalfight</v>
       </c>
       <c r="B634">
         <v>1</v>
@@ -9278,7 +9278,7 @@
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>1felipe.bjj</v>
+        <v>_samu35</v>
       </c>
       <c r="B635">
         <v>1</v>
@@ -9292,7 +9292,7 @@
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>odennismagalhaes</v>
+        <v>1felipe.bjj</v>
       </c>
       <c r="B636">
         <v>1</v>
@@ -9306,7 +9306,7 @@
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>remarchina</v>
+        <v>odennismagalhaes</v>
       </c>
       <c r="B637">
         <v>1</v>
@@ -9320,7 +9320,7 @@
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>blesed578</v>
+        <v>remarchina</v>
       </c>
       <c r="B638">
         <v>1</v>
@@ -9334,7 +9334,7 @@
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>yago_08k</v>
+        <v>blesed578</v>
       </c>
       <c r="B639">
         <v>1</v>
@@ -9348,7 +9348,7 @@
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>maribrittos22</v>
+        <v>yago_08k</v>
       </c>
       <c r="B640">
         <v>1</v>
@@ -9362,7 +9362,7 @@
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>grupoohplanooficial</v>
+        <v>maribrittos22</v>
       </c>
       <c r="B641">
         <v>1</v>
@@ -9376,7 +9376,7 @@
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>rxdi_mns</v>
+        <v>grupoohplanooficial</v>
       </c>
       <c r="B642">
         <v>1</v>
@@ -9390,7 +9390,7 @@
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>almeida_.e7</v>
+        <v>rxdi_mns</v>
       </c>
       <c r="B643">
         <v>1</v>
@@ -9404,7 +9404,7 @@
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>dyrodriguesohplano</v>
+        <v>almeida_.e7</v>
       </c>
       <c r="B644">
         <v>1</v>
@@ -9418,7 +9418,7 @@
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>lucianatpiccelli</v>
+        <v>dyrodriguesohplano</v>
       </c>
       <c r="B645">
         <v>1</v>
@@ -9432,7 +9432,7 @@
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>fe_.faggi</v>
+        <v>lucianatpiccelli</v>
       </c>
       <c r="B646">
         <v>1</v>
@@ -9446,7 +9446,7 @@
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>allves___46</v>
+        <v>fe_.faggi</v>
       </c>
       <c r="B647">
         <v>1</v>
@@ -9460,7 +9460,7 @@
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>ottoniisrael</v>
+        <v>allves___46</v>
       </c>
       <c r="B648">
         <v>1</v>
@@ -9474,7 +9474,7 @@
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>_.carlos.2x._</v>
+        <v>ottoniisrael</v>
       </c>
       <c r="B649">
         <v>1</v>
@@ -9488,7 +9488,7 @@
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>guilherme.duartesilva</v>
+        <v>_.carlos.2x._</v>
       </c>
       <c r="B650">
         <v>1</v>
@@ -9502,7 +9502,7 @@
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>davi.cb</v>
+        <v>guilherme.duartesilva</v>
       </c>
       <c r="B651">
         <v>1</v>
@@ -9516,7 +9516,7 @@
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>abbasrizvi2204</v>
+        <v>davi.cb</v>
       </c>
       <c r="B652">
         <v>1</v>
@@ -9530,7 +9530,7 @@
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>nulife2day</v>
+        <v>abbasrizvi2204</v>
       </c>
       <c r="B653">
         <v>1</v>
@@ -9544,7 +9544,7 @@
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>elnaggar_85</v>
+        <v>nulife2day</v>
       </c>
       <c r="B654">
         <v>1</v>
@@ -9558,7 +9558,7 @@
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>bammer2026</v>
+        <v>elnaggar_85</v>
       </c>
       <c r="B655">
         <v>1</v>
@@ -9572,7 +9572,7 @@
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>yon0sab0</v>
+        <v>bammer2026</v>
       </c>
       <c r="B656">
         <v>1</v>
@@ -9586,7 +9586,7 @@
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>thizzlenik</v>
+        <v>yon0sab0</v>
       </c>
       <c r="B657">
         <v>1</v>
@@ -9600,7 +9600,7 @@
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>dogodoy</v>
+        <v>thizzlenik</v>
       </c>
       <c r="B658">
         <v>1</v>
@@ -9614,7 +9614,7 @@
     </row>
     <row r="659">
       <c r="A659" t="str">
-        <v>cinemarianophoto</v>
+        <v>dogodoy</v>
       </c>
       <c r="B659">
         <v>1</v>
@@ -9628,7 +9628,7 @@
     </row>
     <row r="660">
       <c r="A660" t="str">
-        <v>nati.monteiro</v>
+        <v>cinemarianophoto</v>
       </c>
       <c r="B660">
         <v>1</v>
@@ -9642,7 +9642,7 @@
     </row>
     <row r="661">
       <c r="A661" t="str">
-        <v>boeno_rafael</v>
+        <v>nati.monteiro</v>
       </c>
       <c r="B661">
         <v>1</v>
@@ -9656,7 +9656,7 @@
     </row>
     <row r="662">
       <c r="A662" t="str">
-        <v>claudio_tikar</v>
+        <v>boeno_rafael</v>
       </c>
       <c r="B662">
         <v>1</v>
@@ -9670,7 +9670,7 @@
     </row>
     <row r="663">
       <c r="A663" t="str">
-        <v>mauricio_dutra_m</v>
+        <v>claudio_tikar</v>
       </c>
       <c r="B663">
         <v>1</v>
@@ -9684,7 +9684,7 @@
     </row>
     <row r="664">
       <c r="A664" t="str">
-        <v>s_giofe</v>
+        <v>mauricio_dutra_m</v>
       </c>
       <c r="B664">
         <v>1</v>
@@ -9698,7 +9698,7 @@
     </row>
     <row r="665">
       <c r="A665" t="str">
-        <v>1tiagomonteiro</v>
+        <v>s_giofe</v>
       </c>
       <c r="B665">
         <v>1</v>
@@ -9712,7 +9712,7 @@
     </row>
     <row r="666">
       <c r="A666" t="str">
-        <v>nautinhor7</v>
+        <v>1tiagomonteiro</v>
       </c>
       <c r="B666">
         <v>1</v>
@@ -9726,7 +9726,7 @@
     </row>
     <row r="667">
       <c r="A667" t="str">
-        <v>lucaspaes047</v>
+        <v>nautinhor7</v>
       </c>
       <c r="B667">
         <v>1</v>
@@ -9740,7 +9740,7 @@
     </row>
     <row r="668">
       <c r="A668" t="str">
-        <v>bmarinhorogerio</v>
+        <v>lucaspaes047</v>
       </c>
       <c r="B668">
         <v>1</v>
@@ -9754,7 +9754,7 @@
     </row>
     <row r="669">
       <c r="A669" t="str">
-        <v>klaiver.027xx</v>
+        <v>bmarinhorogerio</v>
       </c>
       <c r="B669">
         <v>1</v>
@@ -9768,7 +9768,7 @@
     </row>
     <row r="670">
       <c r="A670" t="str">
-        <v>jefte_jizreel</v>
+        <v>klaiver.027xx</v>
       </c>
       <c r="B670">
         <v>1</v>
@@ -9782,7 +9782,7 @@
     </row>
     <row r="671">
       <c r="A671" t="str">
-        <v>clinicaikiro</v>
+        <v>jefte_jizreel</v>
       </c>
       <c r="B671">
         <v>1</v>
@@ -9796,7 +9796,7 @@
     </row>
     <row r="672">
       <c r="A672" t="str">
-        <v>cabreuvamma</v>
+        <v>clinicaikiro</v>
       </c>
       <c r="B672">
         <v>1</v>
@@ -9810,7 +9810,7 @@
     </row>
     <row r="673">
       <c r="A673" t="str">
-        <v>use.ellasfit</v>
+        <v>cabreuvamma</v>
       </c>
       <c r="B673">
         <v>1</v>
@@ -9824,7 +9824,7 @@
     </row>
     <row r="674">
       <c r="A674" t="str">
-        <v>patriciarichteroficial</v>
+        <v>use.ellasfit</v>
       </c>
       <c r="B674">
         <v>1</v>
@@ -9838,7 +9838,7 @@
     </row>
     <row r="675">
       <c r="A675" t="str">
-        <v>kauan_mantas</v>
+        <v>patriciarichteroficial</v>
       </c>
       <c r="B675">
         <v>1</v>
@@ -9852,7 +9852,7 @@
     </row>
     <row r="676">
       <c r="A676" t="str">
-        <v>emersonapache</v>
+        <v>kauan_mantas</v>
       </c>
       <c r="B676">
         <v>1</v>
@@ -9866,7 +9866,7 @@
     </row>
     <row r="677">
       <c r="A677" t="str">
-        <v>nataliavidal965</v>
+        <v>emersonapache</v>
       </c>
       <c r="B677">
         <v>1</v>
@@ -9880,7 +9880,7 @@
     </row>
     <row r="678">
       <c r="A678" t="str">
-        <v>ruanpantojanutricionista</v>
+        <v>nataliavidal965</v>
       </c>
       <c r="B678">
         <v>1</v>
@@ -9894,7 +9894,7 @@
     </row>
     <row r="679">
       <c r="A679" t="str">
-        <v>luizpaulomma</v>
+        <v>ruanpantojanutricionista</v>
       </c>
       <c r="B679">
         <v>1</v>
@@ -9908,7 +9908,7 @@
     </row>
     <row r="680">
       <c r="A680" t="str">
-        <v>epicjoel2022</v>
+        <v>luizpaulomma</v>
       </c>
       <c r="B680">
         <v>1</v>
@@ -9922,7 +9922,7 @@
     </row>
     <row r="681">
       <c r="A681" t="str">
-        <v>tvlinsoficial</v>
+        <v>epicjoel2022</v>
       </c>
       <c r="B681">
         <v>1</v>
@@ -9936,7 +9936,7 @@
     </row>
     <row r="682">
       <c r="A682" t="str">
-        <v>_itamar_maximo</v>
+        <v>tvlinsoficial</v>
       </c>
       <c r="B682">
         <v>1</v>
@@ -9950,7 +9950,7 @@
     </row>
     <row r="683">
       <c r="A683" t="str">
-        <v>mg._silvaa_</v>
+        <v>_itamar_maximo</v>
       </c>
       <c r="B683">
         <v>1</v>
@@ -9964,7 +9964,7 @@
     </row>
     <row r="684">
       <c r="A684" t="str">
-        <v>desativado_no_off33</v>
+        <v>mg._silvaa_</v>
       </c>
       <c r="B684">
         <v>1</v>
@@ -9978,35 +9978,35 @@
     </row>
     <row r="685">
       <c r="A685" t="str">
-        <v>lucasbaddoure</v>
+        <v>desativado_no_off33</v>
       </c>
       <c r="B685">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C685">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D685">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="str">
-        <v>paulo_rafa_personal</v>
+        <v>lucasbaddoure</v>
       </c>
       <c r="B686">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C686">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D686">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="str">
-        <v>endurance_guia</v>
+        <v>paulo_rafa_personal</v>
       </c>
       <c r="B687">
         <v>1</v>
@@ -10020,7 +10020,7 @@
     </row>
     <row r="688">
       <c r="A688" t="str">
-        <v>cadupereirss</v>
+        <v>endurance_guia</v>
       </c>
       <c r="B688">
         <v>1</v>
@@ -10034,7 +10034,7 @@
     </row>
     <row r="689">
       <c r="A689" t="str">
-        <v>instrutorindiovs</v>
+        <v>cadupereirss</v>
       </c>
       <c r="B689">
         <v>1</v>
@@ -10048,7 +10048,7 @@
     </row>
     <row r="690">
       <c r="A690" t="str">
-        <v>lopes.felipe13</v>
+        <v>instrutorindiovs</v>
       </c>
       <c r="B690">
         <v>1</v>
@@ -10062,7 +10062,7 @@
     </row>
     <row r="691">
       <c r="A691" t="str">
-        <v>marchi_vinicius</v>
+        <v>lopes.felipe13</v>
       </c>
       <c r="B691">
         <v>1</v>
@@ -10076,7 +10076,7 @@
     </row>
     <row r="692">
       <c r="A692" t="str">
-        <v>rafa_speda</v>
+        <v>marchi_vinicius</v>
       </c>
       <c r="B692">
         <v>1</v>
@@ -10090,7 +10090,7 @@
     </row>
     <row r="693">
       <c r="A693" t="str">
-        <v>m1guelmolina</v>
+        <v>rafa_speda</v>
       </c>
       <c r="B693">
         <v>1</v>
@@ -10104,7 +10104,7 @@
     </row>
     <row r="694">
       <c r="A694" t="str">
-        <v>rosantos83</v>
+        <v>m1guelmolina</v>
       </c>
       <c r="B694">
         <v>1</v>
@@ -10118,7 +10118,7 @@
     </row>
     <row r="695">
       <c r="A695" t="str">
-        <v>caiogoularts</v>
+        <v>rosantos83</v>
       </c>
       <c r="B695">
         <v>1</v>
@@ -10132,7 +10132,7 @@
     </row>
     <row r="696">
       <c r="A696" t="str">
-        <v>cassiolee013</v>
+        <v>caiogoularts</v>
       </c>
       <c r="B696">
         <v>1</v>
@@ -10146,7 +10146,7 @@
     </row>
     <row r="697">
       <c r="A697" t="str">
-        <v>alinefurlann</v>
+        <v>cassiolee013</v>
       </c>
       <c r="B697">
         <v>1</v>
@@ -10160,7 +10160,7 @@
     </row>
     <row r="698">
       <c r="A698" t="str">
-        <v>programaparadois</v>
+        <v>alinefurlann</v>
       </c>
       <c r="B698">
         <v>1</v>
@@ -10174,7 +10174,7 @@
     </row>
     <row r="699">
       <c r="A699" t="str">
-        <v>cotty_bigmonster</v>
+        <v>programaparadois</v>
       </c>
       <c r="B699">
         <v>1</v>
@@ -10188,7 +10188,7 @@
     </row>
     <row r="700">
       <c r="A700" t="str">
-        <v>alissonlayza</v>
+        <v>cotty_bigmonster</v>
       </c>
       <c r="B700">
         <v>1</v>
@@ -10202,7 +10202,7 @@
     </row>
     <row r="701">
       <c r="A701" t="str">
-        <v>perninhakickboxing</v>
+        <v>alissonlayza</v>
       </c>
       <c r="B701">
         <v>1</v>
@@ -10216,7 +10216,7 @@
     </row>
     <row r="702">
       <c r="A702" t="str">
-        <v>rodrigo.nsx</v>
+        <v>perninhakickboxing</v>
       </c>
       <c r="B702">
         <v>1</v>
@@ -10230,7 +10230,7 @@
     </row>
     <row r="703">
       <c r="A703" t="str">
-        <v>_hygor.soares</v>
+        <v>rodrigo.nsx</v>
       </c>
       <c r="B703">
         <v>1</v>
@@ -10244,7 +10244,7 @@
     </row>
     <row r="704">
       <c r="A704" t="str">
-        <v>enzorkbjj</v>
+        <v>_hygor.soares</v>
       </c>
       <c r="B704">
         <v>1</v>
@@ -10258,7 +10258,7 @@
     </row>
     <row r="705">
       <c r="A705" t="str">
-        <v>lorenzojjts</v>
+        <v>enzorkbjj</v>
       </c>
       <c r="B705">
         <v>1</v>
@@ -10272,97 +10272,97 @@
     </row>
     <row r="706">
       <c r="A706" t="str">
-        <v>luizcosta_mma</v>
+        <v>lorenzojjts</v>
       </c>
       <c r="B706">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C706">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D706">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="707">
       <c r="A707" t="str">
-        <v>taylor_71kg</v>
+        <v>i_am_mauispunjahchick</v>
       </c>
       <c r="B707">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C707">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D707">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="708">
       <c r="A708" t="str">
-        <v>_vpft</v>
+        <v>808.chaz</v>
       </c>
       <c r="B708">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C708">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D708">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="709">
       <c r="A709" t="str">
-        <v>viniciustbf</v>
+        <v>k_costa68</v>
       </c>
       <c r="B709">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C709">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D709">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="710">
       <c r="A710" t="str">
-        <v>dayanaa1511</v>
+        <v>leomvgomes</v>
       </c>
       <c r="B710">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C710">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D710">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="711">
       <c r="A711" t="str">
-        <v>danielfranzesilva</v>
+        <v>luizcosta_mma</v>
       </c>
       <c r="B711">
         <v>0</v>
       </c>
       <c r="C711">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D711">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="712">
       <c r="A712" t="str">
-        <v>ednilsonkaicai</v>
+        <v>taylor_71kg</v>
       </c>
       <c r="B712">
         <v>0</v>
       </c>
       <c r="C712">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D712">
         <v>1</v>
@@ -10370,13 +10370,13 @@
     </row>
     <row r="713">
       <c r="A713" t="str">
-        <v>vanessamelomma</v>
+        <v>_vpft</v>
       </c>
       <c r="B713">
         <v>0</v>
       </c>
       <c r="C713">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D713">
         <v>1</v>
@@ -10384,49 +10384,49 @@
     </row>
     <row r="714">
       <c r="A714" t="str">
-        <v>michelle_mirele</v>
+        <v>viniciustbf</v>
       </c>
       <c r="B714">
         <v>0</v>
       </c>
       <c r="C714">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D714">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="715">
       <c r="A715" t="str">
-        <v>geyziellsouza</v>
+        <v>dayanaa1511</v>
       </c>
       <c r="B715">
         <v>0</v>
       </c>
       <c r="C715">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D715">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="716">
       <c r="A716" t="str">
-        <v>guerreirammaofc</v>
+        <v>danielfranzesilva</v>
       </c>
       <c r="B716">
         <v>0</v>
       </c>
       <c r="C716">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D716">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="717">
       <c r="A717" t="str">
-        <v>kalaga_vito</v>
+        <v>ednilsonkaicai</v>
       </c>
       <c r="B717">
         <v>0</v>
@@ -10440,7 +10440,7 @@
     </row>
     <row r="718">
       <c r="A718" t="str">
-        <v>dudaadantass</v>
+        <v>vanessamelomma</v>
       </c>
       <c r="B718">
         <v>0</v>
@@ -10454,13 +10454,13 @@
     </row>
     <row r="719">
       <c r="A719" t="str">
-        <v>vitorshowman</v>
+        <v>michelle_mirele</v>
       </c>
       <c r="B719">
         <v>0</v>
       </c>
       <c r="C719">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D719">
         <v>0</v>
@@ -10468,13 +10468,13 @@
     </row>
     <row r="720">
       <c r="A720" t="str">
-        <v>4lissson</v>
+        <v>geyziellsouza</v>
       </c>
       <c r="B720">
         <v>0</v>
       </c>
       <c r="C720">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D720">
         <v>0</v>
@@ -10482,13 +10482,13 @@
     </row>
     <row r="721">
       <c r="A721" t="str">
-        <v>danilofernandescf</v>
+        <v>guerreirammaofc</v>
       </c>
       <c r="B721">
         <v>0</v>
       </c>
       <c r="C721">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D721">
         <v>1</v>
@@ -10496,13 +10496,13 @@
     </row>
     <row r="722">
       <c r="A722" t="str">
-        <v>bryandazuera</v>
+        <v>kalaga_vito</v>
       </c>
       <c r="B722">
         <v>0</v>
       </c>
       <c r="C722">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D722">
         <v>1</v>
@@ -10510,7 +10510,7 @@
     </row>
     <row r="723">
       <c r="A723" t="str">
-        <v>orlando_alfa09</v>
+        <v>dudaadantass</v>
       </c>
       <c r="B723">
         <v>0</v>
@@ -10519,12 +10519,12 @@
         <v>2</v>
       </c>
       <c r="D723">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="724">
       <c r="A724" t="str">
-        <v>jhonnatanboxe_</v>
+        <v>vitorshowman</v>
       </c>
       <c r="B724">
         <v>0</v>
@@ -10538,7 +10538,7 @@
     </row>
     <row r="725">
       <c r="A725" t="str">
-        <v>manumito.oficial</v>
+        <v>4lissson</v>
       </c>
       <c r="B725">
         <v>0</v>
@@ -10552,7 +10552,7 @@
     </row>
     <row r="726">
       <c r="A726" t="str">
-        <v>coutz11</v>
+        <v>danilofernandescf</v>
       </c>
       <c r="B726">
         <v>0</v>
@@ -10566,35 +10566,35 @@
     </row>
     <row r="727">
       <c r="A727" t="str">
-        <v>eglaudiomma</v>
+        <v>bryandazuera</v>
       </c>
       <c r="B727">
         <v>0</v>
       </c>
       <c r="C727">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D727">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="728">
       <c r="A728" t="str">
-        <v>lokomemo_protetores</v>
+        <v>orlando_alfa09</v>
       </c>
       <c r="B728">
         <v>0</v>
       </c>
       <c r="C728">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D728">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="729">
       <c r="A729" t="str">
-        <v>carlosnoelblack</v>
+        <v>jhonnatanboxe_</v>
       </c>
       <c r="B729">
         <v>0</v>
@@ -10608,7 +10608,7 @@
     </row>
     <row r="730">
       <c r="A730" t="str">
-        <v>rafaelcmjj</v>
+        <v>manumito.oficial</v>
       </c>
       <c r="B730">
         <v>0</v>
@@ -10622,7 +10622,7 @@
     </row>
     <row r="731">
       <c r="A731" t="str">
-        <v>rahikikhalid</v>
+        <v>coutz11</v>
       </c>
       <c r="B731">
         <v>0</v>
@@ -10636,35 +10636,35 @@
     </row>
     <row r="732">
       <c r="A732" t="str">
-        <v>leonardopateira</v>
+        <v>eglaudiomma</v>
       </c>
       <c r="B732">
         <v>0</v>
       </c>
       <c r="C732">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D732">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="733">
       <c r="A733" t="str">
-        <v>thalytabjj</v>
+        <v>lokomemo_protetores</v>
       </c>
       <c r="B733">
         <v>0</v>
       </c>
       <c r="C733">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D733">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="734">
       <c r="A734" t="str">
-        <v>rafaelantonio.rj</v>
+        <v>carlosnoelblack</v>
       </c>
       <c r="B734">
         <v>0</v>
@@ -10678,49 +10678,49 @@
     </row>
     <row r="735">
       <c r="A735" t="str">
-        <v>yasminreis_oficiall</v>
+        <v>rafaelcmjj</v>
       </c>
       <c r="B735">
         <v>0</v>
       </c>
       <c r="C735">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D735">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="736">
       <c r="A736" t="str">
-        <v>dnoxsport</v>
+        <v>rahikikhalid</v>
       </c>
       <c r="B736">
         <v>0</v>
       </c>
       <c r="C736">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D736">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="737">
       <c r="A737" t="str">
-        <v>armysenju</v>
+        <v>leonardopateira</v>
       </c>
       <c r="B737">
         <v>0</v>
       </c>
       <c r="C737">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D737">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="738">
       <c r="A738" t="str">
-        <v>kamtalksmma</v>
+        <v>thalytabjj</v>
       </c>
       <c r="B738">
         <v>0</v>
@@ -10734,77 +10734,77 @@
     </row>
     <row r="739">
       <c r="A739" t="str">
-        <v>arleyleboss</v>
+        <v>rafaelantonio.rj</v>
       </c>
       <c r="B739">
         <v>0</v>
       </c>
       <c r="C739">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D739">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="740">
       <c r="A740" t="str">
-        <v>jj_miguel05</v>
+        <v>yasminreis_oficiall</v>
       </c>
       <c r="B740">
         <v>0</v>
       </c>
       <c r="C740">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D740">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="741">
       <c r="A741" t="str">
-        <v>dra.izabeldelfino_</v>
+        <v>dnoxsport</v>
       </c>
       <c r="B741">
         <v>0</v>
       </c>
       <c r="C741">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D741">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="742">
       <c r="A742" t="str">
-        <v>janjaovix</v>
+        <v>armysenju</v>
       </c>
       <c r="B742">
         <v>0</v>
       </c>
       <c r="C742">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D742">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="743">
       <c r="A743" t="str">
-        <v>joaolucasmma.rocha</v>
+        <v>kamtalksmma</v>
       </c>
       <c r="B743">
         <v>0</v>
       </c>
       <c r="C743">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D743">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="744">
       <c r="A744" t="str">
-        <v>edsonbahienseb</v>
+        <v>arleyleboss</v>
       </c>
       <c r="B744">
         <v>0</v>
@@ -10818,35 +10818,35 @@
     </row>
     <row r="745">
       <c r="A745" t="str">
-        <v>paulomartins.mma</v>
+        <v>jj_miguel05</v>
       </c>
       <c r="B745">
         <v>0</v>
       </c>
       <c r="C745">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D745">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="746">
       <c r="A746" t="str">
-        <v>daniel_natel</v>
+        <v>dra.izabeldelfino_</v>
       </c>
       <c r="B746">
         <v>0</v>
       </c>
       <c r="C746">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D746">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="747">
       <c r="A747" t="str">
-        <v>dhuks11</v>
+        <v>janjaovix</v>
       </c>
       <c r="B747">
         <v>0</v>
@@ -10855,12 +10855,12 @@
         <v>1</v>
       </c>
       <c r="D747">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="748">
       <c r="A748" t="str">
-        <v>macksomlee</v>
+        <v>joaolucasmma.rocha</v>
       </c>
       <c r="B748">
         <v>0</v>
@@ -10874,21 +10874,21 @@
     </row>
     <row r="749">
       <c r="A749" t="str">
-        <v>y_nichimura</v>
+        <v>edsonbahienseb</v>
       </c>
       <c r="B749">
         <v>0</v>
       </c>
       <c r="C749">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D749">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="750">
       <c r="A750" t="str">
-        <v>mayconzilli</v>
+        <v>paulomartins.mma</v>
       </c>
       <c r="B750">
         <v>0</v>
@@ -10902,21 +10902,21 @@
     </row>
     <row r="751">
       <c r="A751" t="str">
-        <v>patascubo</v>
+        <v>daniel_natel</v>
       </c>
       <c r="B751">
         <v>0</v>
       </c>
       <c r="C751">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D751">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="752">
       <c r="A752" t="str">
-        <v>jeffesonmeirelles</v>
+        <v>dhuks11</v>
       </c>
       <c r="B752">
         <v>0</v>
@@ -10925,12 +10925,12 @@
         <v>1</v>
       </c>
       <c r="D752">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="753">
       <c r="A753" t="str">
-        <v>denilson.unit</v>
+        <v>macksomlee</v>
       </c>
       <c r="B753">
         <v>0</v>
@@ -10944,21 +10944,21 @@
     </row>
     <row r="754">
       <c r="A754" t="str">
-        <v>vieirabjj____</v>
+        <v>y_nichimura</v>
       </c>
       <c r="B754">
         <v>0</v>
       </c>
       <c r="C754">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D754">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="755">
       <c r="A755" t="str">
-        <v>canalgolpebaixo</v>
+        <v>mayconzilli</v>
       </c>
       <c r="B755">
         <v>0</v>
@@ -10972,7 +10972,7 @@
     </row>
     <row r="756">
       <c r="A756" t="str">
-        <v>leandro__parpinelli</v>
+        <v>patascubo</v>
       </c>
       <c r="B756">
         <v>0</v>
@@ -10986,7 +10986,7 @@
     </row>
     <row r="757">
       <c r="A757" t="str">
-        <v>bruno_pontes1992</v>
+        <v>jeffesonmeirelles</v>
       </c>
       <c r="B757">
         <v>0</v>
@@ -11000,7 +11000,7 @@
     </row>
     <row r="758">
       <c r="A758" t="str">
-        <v>allan10adm</v>
+        <v>denilson.unit</v>
       </c>
       <c r="B758">
         <v>0</v>
@@ -11014,7 +11014,7 @@
     </row>
     <row r="759">
       <c r="A759" t="str">
-        <v>gaby_alves07</v>
+        <v>vieirabjj____</v>
       </c>
       <c r="B759">
         <v>0</v>
@@ -11028,7 +11028,7 @@
     </row>
     <row r="760">
       <c r="A760" t="str">
-        <v>alineanne_</v>
+        <v>canalgolpebaixo</v>
       </c>
       <c r="B760">
         <v>0</v>
@@ -11037,12 +11037,12 @@
         <v>1</v>
       </c>
       <c r="D760">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="761">
       <c r="A761" t="str">
-        <v>julckreis</v>
+        <v>leandro__parpinelli</v>
       </c>
       <c r="B761">
         <v>0</v>
@@ -11051,12 +11051,12 @@
         <v>1</v>
       </c>
       <c r="D761">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="762">
       <c r="A762" t="str">
-        <v>andreza.thais.1</v>
+        <v>bruno_pontes1992</v>
       </c>
       <c r="B762">
         <v>0</v>
@@ -11065,12 +11065,12 @@
         <v>1</v>
       </c>
       <c r="D762">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="763">
       <c r="A763" t="str">
-        <v>benicius_edu</v>
+        <v>allan10adm</v>
       </c>
       <c r="B763">
         <v>0</v>
@@ -11079,12 +11079,12 @@
         <v>1</v>
       </c>
       <c r="D763">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="764">
       <c r="A764" t="str">
-        <v>nataliaemanuela.personal</v>
+        <v>gaby_alves07</v>
       </c>
       <c r="B764">
         <v>0</v>
@@ -11093,12 +11093,12 @@
         <v>1</v>
       </c>
       <c r="D764">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="765">
       <c r="A765" t="str">
-        <v>michele_mixa</v>
+        <v>alineanne_</v>
       </c>
       <c r="B765">
         <v>0</v>
@@ -11112,7 +11112,7 @@
     </row>
     <row r="766">
       <c r="A766" t="str">
-        <v>joaolauar_</v>
+        <v>julckreis</v>
       </c>
       <c r="B766">
         <v>0</v>
@@ -11126,7 +11126,7 @@
     </row>
     <row r="767">
       <c r="A767" t="str">
-        <v>igorbrasileiro01</v>
+        <v>andreza.thais.1</v>
       </c>
       <c r="B767">
         <v>0</v>
@@ -11140,7 +11140,7 @@
     </row>
     <row r="768">
       <c r="A768" t="str">
-        <v>felipeocalmon</v>
+        <v>benicius_edu</v>
       </c>
       <c r="B768">
         <v>0</v>
@@ -11154,7 +11154,7 @@
     </row>
     <row r="769">
       <c r="A769" t="str">
-        <v>rejr_mma</v>
+        <v>nataliaemanuela.personal</v>
       </c>
       <c r="B769">
         <v>0</v>
@@ -11168,7 +11168,7 @@
     </row>
     <row r="770">
       <c r="A770" t="str">
-        <v>deivssonmanin</v>
+        <v>michele_mixa</v>
       </c>
       <c r="B770">
         <v>0</v>
@@ -11182,7 +11182,7 @@
     </row>
     <row r="771">
       <c r="A771" t="str">
-        <v>andrey_m_s_</v>
+        <v>joaolauar_</v>
       </c>
       <c r="B771">
         <v>0</v>
@@ -11196,7 +11196,7 @@
     </row>
     <row r="772">
       <c r="A772" t="str">
-        <v>vidaldanin</v>
+        <v>igorbrasileiro01</v>
       </c>
       <c r="B772">
         <v>0</v>
@@ -11210,7 +11210,7 @@
     </row>
     <row r="773">
       <c r="A773" t="str">
-        <v>barbaracontadora</v>
+        <v>felipeocalmon</v>
       </c>
       <c r="B773">
         <v>0</v>
@@ -11224,7 +11224,7 @@
     </row>
     <row r="774">
       <c r="A774" t="str">
-        <v>natalves5</v>
+        <v>rejr_mma</v>
       </c>
       <c r="B774">
         <v>0</v>
@@ -11238,7 +11238,7 @@
     </row>
     <row r="775">
       <c r="A775" t="str">
-        <v>marlon_bodybuilding</v>
+        <v>deivssonmanin</v>
       </c>
       <c r="B775">
         <v>0</v>
@@ -11252,7 +11252,7 @@
     </row>
     <row r="776">
       <c r="A776" t="str">
-        <v>boradepodcastoficial</v>
+        <v>andrey_m_s_</v>
       </c>
       <c r="B776">
         <v>0</v>
@@ -11266,7 +11266,7 @@
     </row>
     <row r="777">
       <c r="A777" t="str">
-        <v>audizioandrade</v>
+        <v>vidaldanin</v>
       </c>
       <c r="B777">
         <v>0</v>
@@ -11280,7 +11280,7 @@
     </row>
     <row r="778">
       <c r="A778" t="str">
-        <v>isadoragolimpio</v>
+        <v>barbaracontadora</v>
       </c>
       <c r="B778">
         <v>0</v>
@@ -11294,7 +11294,7 @@
     </row>
     <row r="779">
       <c r="A779" t="str">
-        <v>dudu.acabamentos</v>
+        <v>natalves5</v>
       </c>
       <c r="B779">
         <v>0</v>
@@ -11308,7 +11308,7 @@
     </row>
     <row r="780">
       <c r="A780" t="str">
-        <v>katlembrenda</v>
+        <v>marlon_bodybuilding</v>
       </c>
       <c r="B780">
         <v>0</v>
@@ -11322,7 +11322,7 @@
     </row>
     <row r="781">
       <c r="A781" t="str">
-        <v>aline.amaral21</v>
+        <v>boradepodcastoficial</v>
       </c>
       <c r="B781">
         <v>0</v>
@@ -11336,7 +11336,7 @@
     </row>
     <row r="782">
       <c r="A782" t="str">
-        <v>tamysregina</v>
+        <v>audizioandrade</v>
       </c>
       <c r="B782">
         <v>0</v>
@@ -11350,7 +11350,7 @@
     </row>
     <row r="783">
       <c r="A783" t="str">
-        <v>guilhermews1994</v>
+        <v>isadoragolimpio</v>
       </c>
       <c r="B783">
         <v>0</v>
@@ -11364,7 +11364,7 @@
     </row>
     <row r="784">
       <c r="A784" t="str">
-        <v>kevin.mota95</v>
+        <v>dudu.acabamentos</v>
       </c>
       <c r="B784">
         <v>0</v>
@@ -11378,7 +11378,7 @@
     </row>
     <row r="785">
       <c r="A785" t="str">
-        <v>douglas_vitor8</v>
+        <v>katlembrenda</v>
       </c>
       <c r="B785">
         <v>0</v>
@@ -11392,7 +11392,7 @@
     </row>
     <row r="786">
       <c r="A786" t="str">
-        <v>gemeaslauraebrenda</v>
+        <v>aline.amaral21</v>
       </c>
       <c r="B786">
         <v>0</v>
@@ -11406,7 +11406,7 @@
     </row>
     <row r="787">
       <c r="A787" t="str">
-        <v>raulcarvalho1010</v>
+        <v>tamysregina</v>
       </c>
       <c r="B787">
         <v>0</v>
@@ -11420,7 +11420,7 @@
     </row>
     <row r="788">
       <c r="A788" t="str">
-        <v>roginbrito</v>
+        <v>guilhermews1994</v>
       </c>
       <c r="B788">
         <v>0</v>
@@ -11434,7 +11434,7 @@
     </row>
     <row r="789">
       <c r="A789" t="str">
-        <v>romulerasilva</v>
+        <v>kevin.mota95</v>
       </c>
       <c r="B789">
         <v>0</v>
@@ -11448,7 +11448,7 @@
     </row>
     <row r="790">
       <c r="A790" t="str">
-        <v>higorsaantana</v>
+        <v>douglas_vitor8</v>
       </c>
       <c r="B790">
         <v>0</v>
@@ -11462,7 +11462,7 @@
     </row>
     <row r="791">
       <c r="A791" t="str">
-        <v>vitorcosta_mma</v>
+        <v>gemeaslauraebrenda</v>
       </c>
       <c r="B791">
         <v>0</v>
@@ -11476,7 +11476,7 @@
     </row>
     <row r="792">
       <c r="A792" t="str">
-        <v>paulo.titoo</v>
+        <v>raulcarvalho1010</v>
       </c>
       <c r="B792">
         <v>0</v>
@@ -11490,7 +11490,7 @@
     </row>
     <row r="793">
       <c r="A793" t="str">
-        <v>1000ton_n</v>
+        <v>roginbrito</v>
       </c>
       <c r="B793">
         <v>0</v>
@@ -11504,7 +11504,7 @@
     </row>
     <row r="794">
       <c r="A794" t="str">
-        <v>strong_stg_oficial</v>
+        <v>romulerasilva</v>
       </c>
       <c r="B794">
         <v>0</v>
@@ -11518,7 +11518,7 @@
     </row>
     <row r="795">
       <c r="A795" t="str">
-        <v>ricardotofanello</v>
+        <v>higorsaantana</v>
       </c>
       <c r="B795">
         <v>0</v>
@@ -11532,7 +11532,7 @@
     </row>
     <row r="796">
       <c r="A796" t="str">
-        <v>taporondebruno</v>
+        <v>vitorcosta_mma</v>
       </c>
       <c r="B796">
         <v>0</v>
@@ -11546,7 +11546,7 @@
     </row>
     <row r="797">
       <c r="A797" t="str">
-        <v>anamatias.m</v>
+        <v>paulo.titoo</v>
       </c>
       <c r="B797">
         <v>0</v>
@@ -11560,7 +11560,7 @@
     </row>
     <row r="798">
       <c r="A798" t="str">
-        <v>claudio_marchese_7</v>
+        <v>1000ton_n</v>
       </c>
       <c r="B798">
         <v>0</v>
@@ -11574,7 +11574,7 @@
     </row>
     <row r="799">
       <c r="A799" t="str">
-        <v>caioparangole</v>
+        <v>strong_stg_oficial</v>
       </c>
       <c r="B799">
         <v>0</v>
@@ -11588,7 +11588,7 @@
     </row>
     <row r="800">
       <c r="A800" t="str">
-        <v>sabrinaalsilva</v>
+        <v>ricardotofanello</v>
       </c>
       <c r="B800">
         <v>0</v>
@@ -11602,7 +11602,7 @@
     </row>
     <row r="801">
       <c r="A801" t="str">
-        <v>nuncadesistir.nd</v>
+        <v>taporondebruno</v>
       </c>
       <c r="B801">
         <v>0</v>
@@ -11616,7 +11616,7 @@
     </row>
     <row r="802">
       <c r="A802" t="str">
-        <v>marcilio.silva.71404</v>
+        <v>anamatias.m</v>
       </c>
       <c r="B802">
         <v>0</v>
@@ -11630,7 +11630,7 @@
     </row>
     <row r="803">
       <c r="A803" t="str">
-        <v>doraasivla</v>
+        <v>claudio_marchese_7</v>
       </c>
       <c r="B803">
         <v>0</v>
@@ -11644,7 +11644,7 @@
     </row>
     <row r="804">
       <c r="A804" t="str">
-        <v>pe.mirandas</v>
+        <v>caioparangole</v>
       </c>
       <c r="B804">
         <v>0</v>
@@ -11658,7 +11658,7 @@
     </row>
     <row r="805">
       <c r="A805" t="str">
-        <v>leaoanaalice</v>
+        <v>sabrinaalsilva</v>
       </c>
       <c r="B805">
         <v>0</v>
@@ -11672,7 +11672,7 @@
     </row>
     <row r="806">
       <c r="A806" t="str">
-        <v>cristianomarcello</v>
+        <v>nuncadesistir.nd</v>
       </c>
       <c r="B806">
         <v>0</v>
@@ -11686,7 +11686,7 @@
     </row>
     <row r="807">
       <c r="A807" t="str">
-        <v>dandraco_</v>
+        <v>marcilio.silva.71404</v>
       </c>
       <c r="B807">
         <v>0</v>
@@ -11700,7 +11700,7 @@
     </row>
     <row r="808">
       <c r="A808" t="str">
-        <v>oliveiraandiarabjj</v>
+        <v>doraasivla</v>
       </c>
       <c r="B808">
         <v>0</v>
@@ -11714,7 +11714,7 @@
     </row>
     <row r="809">
       <c r="A809" t="str">
-        <v>sejamotivadorofc</v>
+        <v>pe.mirandas</v>
       </c>
       <c r="B809">
         <v>0</v>
@@ -11728,7 +11728,7 @@
     </row>
     <row r="810">
       <c r="A810" t="str">
-        <v>tpapereira</v>
+        <v>leaoanaalice</v>
       </c>
       <c r="B810">
         <v>0</v>
@@ -11742,7 +11742,7 @@
     </row>
     <row r="811">
       <c r="A811" t="str">
-        <v>kfcampeoes</v>
+        <v>cristianomarcello</v>
       </c>
       <c r="B811">
         <v>0</v>
@@ -11756,7 +11756,7 @@
     </row>
     <row r="812">
       <c r="A812" t="str">
-        <v>herrickmarinho</v>
+        <v>dandraco_</v>
       </c>
       <c r="B812">
         <v>0</v>
@@ -11770,7 +11770,7 @@
     </row>
     <row r="813">
       <c r="A813" t="str">
-        <v>geanne_franca_</v>
+        <v>oliveiraandiarabjj</v>
       </c>
       <c r="B813">
         <v>0</v>
@@ -11784,7 +11784,7 @@
     </row>
     <row r="814">
       <c r="A814" t="str">
-        <v>vanemessina</v>
+        <v>sejamotivadorofc</v>
       </c>
       <c r="B814">
         <v>0</v>
@@ -11798,7 +11798,7 @@
     </row>
     <row r="815">
       <c r="A815" t="str">
-        <v>dadwillians</v>
+        <v>tpapereira</v>
       </c>
       <c r="B815">
         <v>0</v>
@@ -11812,7 +11812,7 @@
     </row>
     <row r="816">
       <c r="A816" t="str">
-        <v>esteticaluharruda</v>
+        <v>kfcampeoes</v>
       </c>
       <c r="B816">
         <v>0</v>
@@ -11826,7 +11826,7 @@
     </row>
     <row r="817">
       <c r="A817" t="str">
-        <v>chubotaru_lilu</v>
+        <v>herrickmarinho</v>
       </c>
       <c r="B817">
         <v>0</v>
@@ -11840,7 +11840,7 @@
     </row>
     <row r="818">
       <c r="A818" t="str">
-        <v>_kainanlima</v>
+        <v>geanne_franca_</v>
       </c>
       <c r="B818">
         <v>0</v>
@@ -11854,7 +11854,7 @@
     </row>
     <row r="819">
       <c r="A819" t="str">
-        <v>jimmy_indioap</v>
+        <v>vanemessina</v>
       </c>
       <c r="B819">
         <v>0</v>
@@ -11868,7 +11868,7 @@
     </row>
     <row r="820">
       <c r="A820" t="str">
-        <v>omar_alneaimi</v>
+        <v>dadwillians</v>
       </c>
       <c r="B820">
         <v>0</v>
@@ -11882,7 +11882,7 @@
     </row>
     <row r="821">
       <c r="A821" t="str">
-        <v>victor_brunopersonal</v>
+        <v>esteticaluharruda</v>
       </c>
       <c r="B821">
         <v>0</v>
@@ -11896,7 +11896,7 @@
     </row>
     <row r="822">
       <c r="A822" t="str">
-        <v>mariacleusa.lopes</v>
+        <v>chubotaru_lilu</v>
       </c>
       <c r="B822">
         <v>0</v>
@@ -11910,7 +11910,7 @@
     </row>
     <row r="823">
       <c r="A823" t="str">
-        <v>rafaelbipolarufc</v>
+        <v>_kainanlima</v>
       </c>
       <c r="B823">
         <v>0</v>
@@ -11924,7 +11924,7 @@
     </row>
     <row r="824">
       <c r="A824" t="str">
-        <v>martinpakciarz</v>
+        <v>jimmy_indioap</v>
       </c>
       <c r="B824">
         <v>0</v>
@@ -11938,7 +11938,7 @@
     </row>
     <row r="825">
       <c r="A825" t="str">
-        <v>andrearschack</v>
+        <v>omar_alneaimi</v>
       </c>
       <c r="B825">
         <v>0</v>
@@ -11952,7 +11952,7 @@
     </row>
     <row r="826">
       <c r="A826" t="str">
-        <v>leziamorbeck50</v>
+        <v>victor_brunopersonal</v>
       </c>
       <c r="B826">
         <v>0</v>
@@ -11966,7 +11966,7 @@
     </row>
     <row r="827">
       <c r="A827" t="str">
-        <v>meirelesmma</v>
+        <v>mariacleusa.lopes</v>
       </c>
       <c r="B827">
         <v>0</v>
@@ -11980,7 +11980,7 @@
     </row>
     <row r="828">
       <c r="A828" t="str">
-        <v>teamsilverio</v>
+        <v>rafaelbipolarufc</v>
       </c>
       <c r="B828">
         <v>0</v>
@@ -11994,7 +11994,7 @@
     </row>
     <row r="829">
       <c r="A829" t="str">
-        <v>tatiaradias</v>
+        <v>martinpakciarz</v>
       </c>
       <c r="B829">
         <v>0</v>
@@ -12008,7 +12008,7 @@
     </row>
     <row r="830">
       <c r="A830" t="str">
-        <v>daniloacordeon_oficial</v>
+        <v>andrearschack</v>
       </c>
       <c r="B830">
         <v>0</v>
@@ -12022,7 +12022,7 @@
     </row>
     <row r="831">
       <c r="A831" t="str">
-        <v>thiagopssantos</v>
+        <v>leziamorbeck50</v>
       </c>
       <c r="B831">
         <v>0</v>
@@ -12036,7 +12036,7 @@
     </row>
     <row r="832">
       <c r="A832" t="str">
-        <v>leafarlemos</v>
+        <v>meirelesmma</v>
       </c>
       <c r="B832">
         <v>0</v>
@@ -12050,7 +12050,7 @@
     </row>
     <row r="833">
       <c r="A833" t="str">
-        <v>miltoncjr28</v>
+        <v>teamsilverio</v>
       </c>
       <c r="B833">
         <v>0</v>
@@ -12064,7 +12064,7 @@
     </row>
     <row r="834">
       <c r="A834" t="str">
-        <v>almeidajjwk</v>
+        <v>tatiaradias</v>
       </c>
       <c r="B834">
         <v>0</v>
@@ -12078,7 +12078,7 @@
     </row>
     <row r="835">
       <c r="A835" t="str">
-        <v>soniarmurata</v>
+        <v>daniloacordeon_oficial</v>
       </c>
       <c r="B835">
         <v>0</v>
@@ -12092,7 +12092,7 @@
     </row>
     <row r="836">
       <c r="A836" t="str">
-        <v>foryousaudeespecializada</v>
+        <v>thiagopssantos</v>
       </c>
       <c r="B836">
         <v>0</v>
@@ -12106,7 +12106,7 @@
     </row>
     <row r="837">
       <c r="A837" t="str">
-        <v>marques.__bjj</v>
+        <v>leafarlemos</v>
       </c>
       <c r="B837">
         <v>0</v>
@@ -12120,7 +12120,7 @@
     </row>
     <row r="838">
       <c r="A838" t="str">
-        <v>ryu_artes_marciais</v>
+        <v>miltoncjr28</v>
       </c>
       <c r="B838">
         <v>0</v>
@@ -12134,7 +12134,7 @@
     </row>
     <row r="839">
       <c r="A839" t="str">
-        <v>dorgivan13_bjj</v>
+        <v>almeidajjwk</v>
       </c>
       <c r="B839">
         <v>0</v>
@@ -12148,7 +12148,7 @@
     </row>
     <row r="840">
       <c r="A840" t="str">
-        <v>ayman__falil_06</v>
+        <v>soniarmurata</v>
       </c>
       <c r="B840">
         <v>0</v>
@@ -12162,7 +12162,7 @@
     </row>
     <row r="841">
       <c r="A841" t="str">
-        <v>otaviocarneiromma</v>
+        <v>foryousaudeespecializada</v>
       </c>
       <c r="B841">
         <v>0</v>
@@ -12176,7 +12176,7 @@
     </row>
     <row r="842">
       <c r="A842" t="str">
-        <v>dvlucc2k26_</v>
+        <v>marques.__bjj</v>
       </c>
       <c r="B842">
         <v>0</v>
@@ -12190,7 +12190,7 @@
     </row>
     <row r="843">
       <c r="A843" t="str">
-        <v>thayanne_rodrigues_bjj</v>
+        <v>ryu_artes_marciais</v>
       </c>
       <c r="B843">
         <v>0</v>
@@ -12204,7 +12204,7 @@
     </row>
     <row r="844">
       <c r="A844" t="str">
-        <v>lurochachef</v>
+        <v>dorgivan13_bjj</v>
       </c>
       <c r="B844">
         <v>0</v>
@@ -12218,7 +12218,7 @@
     </row>
     <row r="845">
       <c r="A845" t="str">
-        <v>viniciusmorais.bjj</v>
+        <v>ayman__falil_06</v>
       </c>
       <c r="B845">
         <v>0</v>
@@ -12232,7 +12232,7 @@
     </row>
     <row r="846">
       <c r="A846" t="str">
-        <v>mauriciogeorge</v>
+        <v>otaviocarneiromma</v>
       </c>
       <c r="B846">
         <v>0</v>
@@ -12246,7 +12246,7 @@
     </row>
     <row r="847">
       <c r="A847" t="str">
-        <v>gisbedejose</v>
+        <v>dvlucc2k26_</v>
       </c>
       <c r="B847">
         <v>0</v>
@@ -12260,7 +12260,7 @@
     </row>
     <row r="848">
       <c r="A848" t="str">
-        <v>laureanucalvo</v>
+        <v>thayanne_rodrigues_bjj</v>
       </c>
       <c r="B848">
         <v>0</v>
@@ -12274,7 +12274,7 @@
     </row>
     <row r="849">
       <c r="A849" t="str">
-        <v>galindofrontado</v>
+        <v>lurochachef</v>
       </c>
       <c r="B849">
         <v>0</v>
@@ -12288,7 +12288,7 @@
     </row>
     <row r="850">
       <c r="A850" t="str">
-        <v>chalakakavinda</v>
+        <v>viniciusmorais.bjj</v>
       </c>
       <c r="B850">
         <v>0</v>
@@ -12302,7 +12302,7 @@
     </row>
     <row r="851">
       <c r="A851" t="str">
-        <v>gandrapaulino</v>
+        <v>mauriciogeorge</v>
       </c>
       <c r="B851">
         <v>0</v>
@@ -12316,7 +12316,7 @@
     </row>
     <row r="852">
       <c r="A852" t="str">
-        <v>pgmarquesantos</v>
+        <v>gisbedejose</v>
       </c>
       <c r="B852">
         <v>0</v>
@@ -12330,7 +12330,7 @@
     </row>
     <row r="853">
       <c r="A853" t="str">
-        <v>uluukyrgyz_tima</v>
+        <v>laureanucalvo</v>
       </c>
       <c r="B853">
         <v>0</v>
@@ -12344,7 +12344,7 @@
     </row>
     <row r="854">
       <c r="A854" t="str">
-        <v>kells2vallone</v>
+        <v>galindofrontado</v>
       </c>
       <c r="B854">
         <v>0</v>
@@ -12358,7 +12358,7 @@
     </row>
     <row r="855">
       <c r="A855" t="str">
-        <v>personaljakeline</v>
+        <v>chalakakavinda</v>
       </c>
       <c r="B855">
         <v>0</v>
@@ -12372,7 +12372,7 @@
     </row>
     <row r="856">
       <c r="A856" t="str">
-        <v>bjjfalkenberg</v>
+        <v>gandrapaulino</v>
       </c>
       <c r="B856">
         <v>0</v>
@@ -12386,7 +12386,7 @@
     </row>
     <row r="857">
       <c r="A857" t="str">
-        <v>sergiorenatocruz1</v>
+        <v>pgmarquesantos</v>
       </c>
       <c r="B857">
         <v>0</v>
@@ -12400,7 +12400,7 @@
     </row>
     <row r="858">
       <c r="A858" t="str">
-        <v>marcaojudobjjmaster</v>
+        <v>uluukyrgyz_tima</v>
       </c>
       <c r="B858">
         <v>0</v>
@@ -12414,7 +12414,7 @@
     </row>
     <row r="859">
       <c r="A859" t="str">
-        <v>indio_mma</v>
+        <v>kells2vallone</v>
       </c>
       <c r="B859">
         <v>0</v>
@@ -12428,7 +12428,7 @@
     </row>
     <row r="860">
       <c r="A860" t="str">
-        <v>covil.045</v>
+        <v>personaljakeline</v>
       </c>
       <c r="B860">
         <v>0</v>
@@ -12442,7 +12442,7 @@
     </row>
     <row r="861">
       <c r="A861" t="str">
-        <v>allandelano</v>
+        <v>bjjfalkenberg</v>
       </c>
       <c r="B861">
         <v>0</v>
@@ -12456,7 +12456,7 @@
     </row>
     <row r="862">
       <c r="A862" t="str">
-        <v>alomaraujo</v>
+        <v>sergiorenatocruz1</v>
       </c>
       <c r="B862">
         <v>0</v>
@@ -12470,7 +12470,7 @@
     </row>
     <row r="863">
       <c r="A863" t="str">
-        <v>theanimallifemovement</v>
+        <v>marcaojudobjjmaster</v>
       </c>
       <c r="B863">
         <v>0</v>
@@ -12484,7 +12484,7 @@
     </row>
     <row r="864">
       <c r="A864" t="str">
-        <v>tombg_64</v>
+        <v>indio_mma</v>
       </c>
       <c r="B864">
         <v>0</v>
@@ -12498,7 +12498,7 @@
     </row>
     <row r="865">
       <c r="A865" t="str">
-        <v>michaeloliveiramma</v>
+        <v>covil.045</v>
       </c>
       <c r="B865">
         <v>0</v>
@@ -12512,7 +12512,7 @@
     </row>
     <row r="866">
       <c r="A866" t="str">
-        <v>andreichubotaru94</v>
+        <v>allandelano</v>
       </c>
       <c r="B866">
         <v>0</v>
@@ -12526,7 +12526,7 @@
     </row>
     <row r="867">
       <c r="A867" t="str">
-        <v>carinhakkz</v>
+        <v>alomaraujo</v>
       </c>
       <c r="B867">
         <v>0</v>
@@ -12540,7 +12540,7 @@
     </row>
     <row r="868">
       <c r="A868" t="str">
-        <v>helaynecrisl</v>
+        <v>theanimallifemovement</v>
       </c>
       <c r="B868">
         <v>0</v>
@@ -12554,7 +12554,7 @@
     </row>
     <row r="869">
       <c r="A869" t="str">
-        <v>oliveiraa_00.11</v>
+        <v>tombg_64</v>
       </c>
       <c r="B869">
         <v>0</v>
@@ -12568,7 +12568,7 @@
     </row>
     <row r="870">
       <c r="A870" t="str">
-        <v>udilimaheroi</v>
+        <v>michaeloliveiramma</v>
       </c>
       <c r="B870">
         <v>0</v>
@@ -12582,7 +12582,7 @@
     </row>
     <row r="871">
       <c r="A871" t="str">
-        <v>mirnacaroline</v>
+        <v>andreichubotaru94</v>
       </c>
       <c r="B871">
         <v>0</v>
@@ -12596,7 +12596,7 @@
     </row>
     <row r="872">
       <c r="A872" t="str">
-        <v>lmk_sport</v>
+        <v>carinhakkz</v>
       </c>
       <c r="B872">
         <v>0</v>
@@ -12610,7 +12610,7 @@
     </row>
     <row r="873">
       <c r="A873" t="str">
-        <v>fher.nando_</v>
+        <v>helaynecrisl</v>
       </c>
       <c r="B873">
         <v>0</v>
@@ -12624,7 +12624,7 @@
     </row>
     <row r="874">
       <c r="A874" t="str">
-        <v>cristiannogueira.vtt</v>
+        <v>oliveiraa_00.11</v>
       </c>
       <c r="B874">
         <v>0</v>
@@ -12638,7 +12638,7 @@
     </row>
     <row r="875">
       <c r="A875" t="str">
-        <v>adrianaramosalvesribeiro</v>
+        <v>udilimaheroi</v>
       </c>
       <c r="B875">
         <v>0</v>
@@ -12652,7 +12652,7 @@
     </row>
     <row r="876">
       <c r="A876" t="str">
-        <v>djuliaarianamma</v>
+        <v>mirnacaroline</v>
       </c>
       <c r="B876">
         <v>0</v>
@@ -12666,7 +12666,7 @@
     </row>
     <row r="877">
       <c r="A877" t="str">
-        <v>raulbasilioo</v>
+        <v>lmk_sport</v>
       </c>
       <c r="B877">
         <v>0</v>
@@ -12680,7 +12680,7 @@
     </row>
     <row r="878">
       <c r="A878" t="str">
-        <v>heloisa_elohim</v>
+        <v>fher.nando_</v>
       </c>
       <c r="B878">
         <v>0</v>
@@ -12694,7 +12694,7 @@
     </row>
     <row r="879">
       <c r="A879" t="str">
-        <v>hostonhugo</v>
+        <v>cristiannogueira.vtt</v>
       </c>
       <c r="B879">
         <v>0</v>
@@ -12708,7 +12708,7 @@
     </row>
     <row r="880">
       <c r="A880" t="str">
-        <v>ellida_guimaraes</v>
+        <v>adrianaramosalvesribeiro</v>
       </c>
       <c r="B880">
         <v>0</v>
@@ -12722,7 +12722,7 @@
     </row>
     <row r="881">
       <c r="A881" t="str">
-        <v>massoterapeuta_bemestarr</v>
+        <v>djuliaarianamma</v>
       </c>
       <c r="B881">
         <v>0</v>
@@ -12736,7 +12736,7 @@
     </row>
     <row r="882">
       <c r="A882" t="str">
-        <v>alexandrefideliis</v>
+        <v>raulbasilioo</v>
       </c>
       <c r="B882">
         <v>0</v>
@@ -12750,7 +12750,7 @@
     </row>
     <row r="883">
       <c r="A883" t="str">
-        <v>pammygaryo</v>
+        <v>heloisa_elohim</v>
       </c>
       <c r="B883">
         <v>0</v>
@@ -12764,7 +12764,7 @@
     </row>
     <row r="884">
       <c r="A884" t="str">
-        <v>beatrizosilveira</v>
+        <v>hostonhugo</v>
       </c>
       <c r="B884">
         <v>0</v>
@@ -12778,7 +12778,7 @@
     </row>
     <row r="885">
       <c r="A885" t="str">
-        <v>bastazinifilho</v>
+        <v>ellida_guimaraes</v>
       </c>
       <c r="B885">
         <v>0</v>
@@ -12792,7 +12792,7 @@
     </row>
     <row r="886">
       <c r="A886" t="str">
-        <v>sem_saida.12</v>
+        <v>massoterapeuta_bemestarr</v>
       </c>
       <c r="B886">
         <v>0</v>
@@ -12806,7 +12806,7 @@
     </row>
     <row r="887">
       <c r="A887" t="str">
-        <v>sougustavorosa</v>
+        <v>alexandrefideliis</v>
       </c>
       <c r="B887">
         <v>0</v>
@@ -12820,7 +12820,7 @@
     </row>
     <row r="888">
       <c r="A888" t="str">
-        <v>lincoln__puig77</v>
+        <v>pammygaryo</v>
       </c>
       <c r="B888">
         <v>0</v>
@@ -12834,7 +12834,7 @@
     </row>
     <row r="889">
       <c r="A889" t="str">
-        <v>anselmo.azevedo</v>
+        <v>beatrizosilveira</v>
       </c>
       <c r="B889">
         <v>0</v>
@@ -12848,7 +12848,7 @@
     </row>
     <row r="890">
       <c r="A890" t="str">
-        <v>marcotulio_matuto</v>
+        <v>bastazinifilho</v>
       </c>
       <c r="B890">
         <v>0</v>
@@ -12862,7 +12862,7 @@
     </row>
     <row r="891">
       <c r="A891" t="str">
-        <v>ianrochaf</v>
+        <v>sem_saida.12</v>
       </c>
       <c r="B891">
         <v>0</v>
@@ -12876,7 +12876,7 @@
     </row>
     <row r="892">
       <c r="A892" t="str">
-        <v>ale.lagonegro</v>
+        <v>sougustavorosa</v>
       </c>
       <c r="B892">
         <v>0</v>
@@ -12890,7 +12890,7 @@
     </row>
     <row r="893">
       <c r="A893" t="str">
-        <v>ganemfelipe</v>
+        <v>lincoln__puig77</v>
       </c>
       <c r="B893">
         <v>0</v>
@@ -12904,7 +12904,7 @@
     </row>
     <row r="894">
       <c r="A894" t="str">
-        <v>marcusvgsz</v>
+        <v>anselmo.azevedo</v>
       </c>
       <c r="B894">
         <v>0</v>
@@ -12918,7 +12918,7 @@
     </row>
     <row r="895">
       <c r="A895" t="str">
-        <v>fabio.sampaio.90260</v>
+        <v>marcotulio_matuto</v>
       </c>
       <c r="B895">
         <v>0</v>
@@ -12932,7 +12932,7 @@
     </row>
     <row r="896">
       <c r="A896" t="str">
-        <v>kaynankruschewsky_ufc</v>
+        <v>ianrochaf</v>
       </c>
       <c r="B896">
         <v>0</v>
@@ -12946,7 +12946,7 @@
     </row>
     <row r="897">
       <c r="A897" t="str">
-        <v>vitorpaes_personalfight</v>
+        <v>ale.lagonegro</v>
       </c>
       <c r="B897">
         <v>0</v>
@@ -12960,7 +12960,7 @@
     </row>
     <row r="898">
       <c r="A898" t="str">
-        <v>zeferinomma</v>
+        <v>ganemfelipe</v>
       </c>
       <c r="B898">
         <v>0</v>
@@ -12974,7 +12974,7 @@
     </row>
     <row r="899">
       <c r="A899" t="str">
-        <v>tavaresguu</v>
+        <v>marcusvgsz</v>
       </c>
       <c r="B899">
         <v>0</v>
@@ -12988,7 +12988,7 @@
     </row>
     <row r="900">
       <c r="A900" t="str">
-        <v>ildemarmarajo</v>
+        <v>fabio.sampaio.90260</v>
       </c>
       <c r="B900">
         <v>0</v>
@@ -13002,7 +13002,7 @@
     </row>
     <row r="901">
       <c r="A901" t="str">
-        <v>pepefightteam</v>
+        <v>kaynankruschewsky_ufc</v>
       </c>
       <c r="B901">
         <v>0</v>
@@ -13016,7 +13016,7 @@
     </row>
     <row r="902">
       <c r="A902" t="str">
-        <v>danieldias7s</v>
+        <v>vitorpaes_personalfight</v>
       </c>
       <c r="B902">
         <v>0</v>
@@ -13030,7 +13030,7 @@
     </row>
     <row r="903">
       <c r="A903" t="str">
-        <v>ohanna.anselmo</v>
+        <v>zeferinomma</v>
       </c>
       <c r="B903">
         <v>0</v>
@@ -13044,7 +13044,7 @@
     </row>
     <row r="904">
       <c r="A904" t="str">
-        <v>brun_oguerreiro</v>
+        <v>tavaresguu</v>
       </c>
       <c r="B904">
         <v>0</v>
@@ -13058,7 +13058,7 @@
     </row>
     <row r="905">
       <c r="A905" t="str">
-        <v>helman_mma70</v>
+        <v>ildemarmarajo</v>
       </c>
       <c r="B905">
         <v>0</v>
@@ -13072,7 +13072,7 @@
     </row>
     <row r="906">
       <c r="A906" t="str">
-        <v>macio.almeida_89</v>
+        <v>pepefightteam</v>
       </c>
       <c r="B906">
         <v>0</v>
@@ -13086,7 +13086,7 @@
     </row>
     <row r="907">
       <c r="A907" t="str">
-        <v>lyviaestherbjj</v>
+        <v>danieldias7s</v>
       </c>
       <c r="B907">
         <v>0</v>
@@ -13100,7 +13100,7 @@
     </row>
     <row r="908">
       <c r="A908" t="str">
-        <v>mma.fisio</v>
+        <v>ohanna.anselmo</v>
       </c>
       <c r="B908">
         <v>0</v>
@@ -13114,7 +13114,7 @@
     </row>
     <row r="909">
       <c r="A909" t="str">
-        <v>thaynara_victoria_</v>
+        <v>brun_oguerreiro</v>
       </c>
       <c r="B909">
         <v>0</v>
@@ -13128,7 +13128,7 @@
     </row>
     <row r="910">
       <c r="A910" t="str">
-        <v>tamarapq</v>
+        <v>helman_mma70</v>
       </c>
       <c r="B910">
         <v>0</v>
@@ -13142,7 +13142,7 @@
     </row>
     <row r="911">
       <c r="A911" t="str">
-        <v>wendel_bjj14</v>
+        <v>macio.almeida_89</v>
       </c>
       <c r="B911">
         <v>0</v>
@@ -13156,7 +13156,7 @@
     </row>
     <row r="912">
       <c r="A912" t="str">
-        <v>karine_killer_ufc</v>
+        <v>lyviaestherbjj</v>
       </c>
       <c r="B912">
         <v>0</v>
@@ -13170,7 +13170,7 @@
     </row>
     <row r="913">
       <c r="A913" t="str">
-        <v>andressa_bjj_</v>
+        <v>mma.fisio</v>
       </c>
       <c r="B913">
         <v>0</v>
@@ -13184,7 +13184,7 @@
     </row>
     <row r="914">
       <c r="A914" t="str">
-        <v>dreamartpro</v>
+        <v>thaynara_victoria_</v>
       </c>
       <c r="B914">
         <v>0</v>
@@ -13198,7 +13198,7 @@
     </row>
     <row r="915">
       <c r="A915" t="str">
-        <v>makelele_bjj</v>
+        <v>tamarapq</v>
       </c>
       <c r="B915">
         <v>0</v>
@@ -13212,7 +13212,7 @@
     </row>
     <row r="916">
       <c r="A916" t="str">
-        <v>fdanieljj</v>
+        <v>wendel_bjj14</v>
       </c>
       <c r="B916">
         <v>0</v>
@@ -13226,7 +13226,7 @@
     </row>
     <row r="917">
       <c r="A917" t="str">
-        <v>jeferson_tijolo1</v>
+        <v>karine_killer_ufc</v>
       </c>
       <c r="B917">
         <v>0</v>
@@ -13240,7 +13240,7 @@
     </row>
     <row r="918">
       <c r="A918" t="str">
-        <v>caioleonjj</v>
+        <v>andressa_bjj_</v>
       </c>
       <c r="B918">
         <v>0</v>
@@ -13254,7 +13254,7 @@
     </row>
     <row r="919">
       <c r="A919" t="str">
-        <v>kevinlopes_bjj</v>
+        <v>dreamartpro</v>
       </c>
       <c r="B919">
         <v>0</v>
@@ -13268,7 +13268,7 @@
     </row>
     <row r="920">
       <c r="A920" t="str">
-        <v>malene_elleen</v>
+        <v>makelele_bjj</v>
       </c>
       <c r="B920">
         <v>0</v>
@@ -13282,7 +13282,7 @@
     </row>
     <row r="921">
       <c r="A921" t="str">
-        <v>danielplayboymt</v>
+        <v>fdanieljj</v>
       </c>
       <c r="B921">
         <v>0</v>
@@ -13296,7 +13296,7 @@
     </row>
     <row r="922">
       <c r="A922" t="str">
-        <v>fix.pec</v>
+        <v>jeferson_tijolo1</v>
       </c>
       <c r="B922">
         <v>0</v>
@@ -13310,7 +13310,7 @@
     </row>
     <row r="923">
       <c r="A923" t="str">
-        <v>chunco_424</v>
+        <v>caioleonjj</v>
       </c>
       <c r="B923">
         <v>0</v>
@@ -13324,7 +13324,7 @@
     </row>
     <row r="924">
       <c r="A924" t="str">
-        <v>denisalagoanobjj</v>
+        <v>kevinlopes_bjj</v>
       </c>
       <c r="B924">
         <v>0</v>
@@ -13338,7 +13338,7 @@
     </row>
     <row r="925">
       <c r="A925" t="str">
-        <v>priscilaapbatista</v>
+        <v>malene_elleen</v>
       </c>
       <c r="B925">
         <v>0</v>
@@ -13352,7 +13352,7 @@
     </row>
     <row r="926">
       <c r="A926" t="str">
-        <v>josita_bjj</v>
+        <v>danielplayboymt</v>
       </c>
       <c r="B926">
         <v>0</v>
@@ -13366,7 +13366,7 @@
     </row>
     <row r="927">
       <c r="A927" t="str">
-        <v>roxostrike</v>
+        <v>fix.pec</v>
       </c>
       <c r="B927">
         <v>0</v>
@@ -13380,7 +13380,7 @@
     </row>
     <row r="928">
       <c r="A928" t="str">
-        <v>shirleypalestrina6</v>
+        <v>chunco_424</v>
       </c>
       <c r="B928">
         <v>0</v>
@@ -13394,7 +13394,7 @@
     </row>
     <row r="929">
       <c r="A929" t="str">
-        <v>flipebiano</v>
+        <v>denisalagoanobjj</v>
       </c>
       <c r="B929">
         <v>0</v>
@@ -13408,7 +13408,7 @@
     </row>
     <row r="930">
       <c r="A930" t="str">
-        <v>ruanmiqueias</v>
+        <v>priscilaapbatista</v>
       </c>
       <c r="B930">
         <v>0</v>
@@ -13422,7 +13422,7 @@
     </row>
     <row r="931">
       <c r="A931" t="str">
-        <v>babimaciel1</v>
+        <v>josita_bjj</v>
       </c>
       <c r="B931">
         <v>0</v>
@@ -13436,7 +13436,7 @@
     </row>
     <row r="932">
       <c r="A932" t="str">
-        <v>manoel.brum</v>
+        <v>roxostrike</v>
       </c>
       <c r="B932">
         <v>0</v>
@@ -13450,7 +13450,7 @@
     </row>
     <row r="933">
       <c r="A933" t="str">
-        <v>horadopower</v>
+        <v>shirleypalestrina6</v>
       </c>
       <c r="B933">
         <v>0</v>
@@ -13464,7 +13464,7 @@
     </row>
     <row r="934">
       <c r="A934" t="str">
-        <v>lyvia_genuina</v>
+        <v>flipebiano</v>
       </c>
       <c r="B934">
         <v>0</v>
@@ -13478,7 +13478,7 @@
     </row>
     <row r="935">
       <c r="A935" t="str">
-        <v>delariva_belem</v>
+        <v>ruanmiqueias</v>
       </c>
       <c r="B935">
         <v>0</v>
@@ -13492,7 +13492,7 @@
     </row>
     <row r="936">
       <c r="A936" t="str">
-        <v>juugxmes</v>
+        <v>babimaciel1</v>
       </c>
       <c r="B936">
         <v>0</v>
@@ -13506,7 +13506,7 @@
     </row>
     <row r="937">
       <c r="A937" t="str">
-        <v>gabrielsantosufc_</v>
+        <v>manoel.brum</v>
       </c>
       <c r="B937">
         <v>0</v>
@@ -13520,7 +13520,7 @@
     </row>
     <row r="938">
       <c r="A938" t="str">
-        <v>_matheustiberio</v>
+        <v>horadopower</v>
       </c>
       <c r="B938">
         <v>0</v>
@@ -13534,7 +13534,7 @@
     </row>
     <row r="939">
       <c r="A939" t="str">
-        <v>sthefany_ochoao</v>
+        <v>lyvia_genuina</v>
       </c>
       <c r="B939">
         <v>0</v>
@@ -13548,7 +13548,7 @@
     </row>
     <row r="940">
       <c r="A940" t="str">
-        <v>reynitaoblitasbustamante</v>
+        <v>delariva_belem</v>
       </c>
       <c r="B940">
         <v>0</v>
@@ -13562,7 +13562,7 @@
     </row>
     <row r="941">
       <c r="A941" t="str">
-        <v>joseochoa.mma</v>
+        <v>juugxmes</v>
       </c>
       <c r="B941">
         <v>0</v>
@@ -13576,7 +13576,7 @@
     </row>
     <row r="942">
       <c r="A942" t="str">
-        <v>gabriellb.andrade</v>
+        <v>gabrielsantosufc_</v>
       </c>
       <c r="B942">
         <v>0</v>
@@ -13590,7 +13590,7 @@
     </row>
     <row r="943">
       <c r="A943" t="str">
-        <v>romelluistro</v>
+        <v>_matheustiberio</v>
       </c>
       <c r="B943">
         <v>0</v>
@@ -13604,7 +13604,7 @@
     </row>
     <row r="944">
       <c r="A944" t="str">
-        <v>yuricapelasso</v>
+        <v>sthefany_ochoao</v>
       </c>
       <c r="B944">
         <v>0</v>
@@ -13618,7 +13618,7 @@
     </row>
     <row r="945">
       <c r="A945" t="str">
-        <v>lucasfenomeno_ufc</v>
+        <v>reynitaoblitasbustamante</v>
       </c>
       <c r="B945">
         <v>0</v>
@@ -13632,7 +13632,7 @@
     </row>
     <row r="946">
       <c r="A946" t="str">
-        <v>gabriell_marcus</v>
+        <v>joseochoa.mma</v>
       </c>
       <c r="B946">
         <v>0</v>
@@ -13646,7 +13646,7 @@
     </row>
     <row r="947">
       <c r="A947" t="str">
-        <v>lazyboy.ufc</v>
+        <v>gabriellb.andrade</v>
       </c>
       <c r="B947">
         <v>0</v>
@@ -13660,7 +13660,7 @@
     </row>
     <row r="948">
       <c r="A948" t="str">
-        <v>matheusdouradomma</v>
+        <v>romelluistro</v>
       </c>
       <c r="B948">
         <v>0</v>
@@ -13674,7 +13674,7 @@
     </row>
     <row r="949">
       <c r="A949" t="str">
-        <v>rafaelsouza7586</v>
+        <v>yuricapelasso</v>
       </c>
       <c r="B949">
         <v>0</v>
@@ -13688,7 +13688,7 @@
     </row>
     <row r="950">
       <c r="A950" t="str">
-        <v>land_on_martelo_308</v>
+        <v>lucasfenomeno_ufc</v>
       </c>
       <c r="B950">
         <v>0</v>
@@ -13702,7 +13702,7 @@
     </row>
     <row r="951">
       <c r="A951" t="str">
-        <v>dodge_big_johnson29</v>
+        <v>gabriell_marcus</v>
       </c>
       <c r="B951">
         <v>0</v>
@@ -13716,7 +13716,7 @@
     </row>
     <row r="952">
       <c r="A952" t="str">
-        <v>dj__freckles</v>
+        <v>lazyboy.ufc</v>
       </c>
       <c r="B952">
         <v>0</v>
@@ -13730,7 +13730,7 @@
     </row>
     <row r="953">
       <c r="A953" t="str">
-        <v>regis18vieira</v>
+        <v>matheusdouradomma</v>
       </c>
       <c r="B953">
         <v>0</v>
@@ -13744,7 +13744,7 @@
     </row>
     <row r="954">
       <c r="A954" t="str">
-        <v>andy.techera.12</v>
+        <v>rafaelsouza7586</v>
       </c>
       <c r="B954">
         <v>0</v>
@@ -13758,7 +13758,7 @@
     </row>
     <row r="955">
       <c r="A955" t="str">
-        <v>celiogarcia6</v>
+        <v>land_on_martelo_308</v>
       </c>
       <c r="B955">
         <v>0</v>
@@ -13772,7 +13772,7 @@
     </row>
     <row r="956">
       <c r="A956" t="str">
-        <v>luluakio</v>
+        <v>dodge_big_johnson29</v>
       </c>
       <c r="B956">
         <v>0</v>
@@ -13786,7 +13786,7 @@
     </row>
     <row r="957">
       <c r="A957" t="str">
-        <v>barreto.boxe</v>
+        <v>dj__freckles</v>
       </c>
       <c r="B957">
         <v>0</v>
@@ -13800,7 +13800,7 @@
     </row>
     <row r="958">
       <c r="A958" t="str">
-        <v>lusoaresjj</v>
+        <v>regis18vieira</v>
       </c>
       <c r="B958">
         <v>0</v>
@@ -13814,7 +13814,7 @@
     </row>
     <row r="959">
       <c r="A959" t="str">
-        <v>sharingan_mma</v>
+        <v>andy.techera.12</v>
       </c>
       <c r="B959">
         <v>0</v>
@@ -13828,7 +13828,7 @@
     </row>
     <row r="960">
       <c r="A960" t="str">
-        <v>thaisadantas</v>
+        <v>celiogarcia6</v>
       </c>
       <c r="B960">
         <v>0</v>
@@ -13842,7 +13842,7 @@
     </row>
     <row r="961">
       <c r="A961" t="str">
-        <v>pulsepro.nutrition</v>
+        <v>luluakio</v>
       </c>
       <c r="B961">
         <v>0</v>
@@ -13856,7 +13856,7 @@
     </row>
     <row r="962">
       <c r="A962" t="str">
-        <v>herbeth_indiomma</v>
+        <v>barreto.boxe</v>
       </c>
       <c r="B962">
         <v>0</v>
@@ -13870,7 +13870,7 @@
     </row>
     <row r="963">
       <c r="A963" t="str">
-        <v>danielbzk_</v>
+        <v>lusoaresjj</v>
       </c>
       <c r="B963">
         <v>0</v>
@@ -13884,28 +13884,98 @@
     </row>
     <row r="964">
       <c r="A964" t="str">
+        <v>sharingan_mma</v>
+      </c>
+      <c r="B964">
+        <v>0</v>
+      </c>
+      <c r="C964">
+        <v>1</v>
+      </c>
+      <c r="D964">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="str">
+        <v>thaisadantas</v>
+      </c>
+      <c r="B965">
+        <v>0</v>
+      </c>
+      <c r="C965">
+        <v>1</v>
+      </c>
+      <c r="D965">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="str">
+        <v>pulsepro.nutrition</v>
+      </c>
+      <c r="B966">
+        <v>0</v>
+      </c>
+      <c r="C966">
+        <v>1</v>
+      </c>
+      <c r="D966">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="str">
+        <v>herbeth_indiomma</v>
+      </c>
+      <c r="B967">
+        <v>0</v>
+      </c>
+      <c r="C967">
+        <v>1</v>
+      </c>
+      <c r="D967">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="str">
+        <v>danielbzk_</v>
+      </c>
+      <c r="B968">
+        <v>0</v>
+      </c>
+      <c r="C968">
+        <v>1</v>
+      </c>
+      <c r="D968">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="str">
         <v>jp.mdc</v>
       </c>
-      <c r="B964">
-        <v>0</v>
-      </c>
-      <c r="C964">
-        <v>1</v>
-      </c>
-      <c r="D964">
+      <c r="B969">
+        <v>0</v>
+      </c>
+      <c r="C969">
+        <v>1</v>
+      </c>
+      <c r="D969">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D964"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D969"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D69"/>
+  <dimension ref="A1:D75"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -13940,13 +14010,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
@@ -13965,30 +14035,30 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>pedr00jj</v>
+        <v>kelly_ottoni</v>
       </c>
       <c r="B5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D5">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>kelly_ottoni</v>
+        <v>pedr00jj</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -13996,7 +14066,7 @@
         <v>natanborges001</v>
       </c>
       <c r="B7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -14133,7 +14203,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>sueli_ferreira48</v>
+        <v>helenmacielmma</v>
       </c>
       <c r="B17">
         <v>2</v>
@@ -14142,15 +14212,15 @@
         <v>0</v>
       </c>
       <c r="D17">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>cristianpsicologo</v>
+        <v>sueli_ferreira48</v>
       </c>
       <c r="B18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -14161,7 +14231,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>brcks4breakfast</v>
+        <v>cristianpsicologo</v>
       </c>
       <c r="B19">
         <v>1</v>
@@ -14175,7 +14245,7 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>rm.nicki</v>
+        <v>brcks4breakfast</v>
       </c>
       <c r="B20">
         <v>1</v>
@@ -14189,7 +14259,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>mma.idiot</v>
+        <v>rm.nicki</v>
       </c>
       <c r="B21">
         <v>1</v>
@@ -14203,7 +14273,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>lili.munix</v>
+        <v>mma.idiot</v>
       </c>
       <c r="B22">
         <v>1</v>
@@ -14217,7 +14287,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>carlos_hm_iglesias</v>
+        <v>lili.munix</v>
       </c>
       <c r="B23">
         <v>1</v>
@@ -14231,7 +14301,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>roger_santosmma</v>
+        <v>carlos_hm_iglesias</v>
       </c>
       <c r="B24">
         <v>1</v>
@@ -14245,7 +14315,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>murata_profight</v>
+        <v>roger_santosmma</v>
       </c>
       <c r="B25">
         <v>1</v>
@@ -14259,7 +14329,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>rayn.avaro</v>
+        <v>murata_profight</v>
       </c>
       <c r="B26">
         <v>1</v>
@@ -14273,7 +14343,7 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>arafight_pesc</v>
+        <v>rayn.avaro</v>
       </c>
       <c r="B27">
         <v>1</v>
@@ -14287,7 +14357,7 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>kamile_oliveria_10</v>
+        <v>arafight_pesc</v>
       </c>
       <c r="B28">
         <v>1</v>
@@ -14301,7 +14371,7 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>malu832757</v>
+        <v>kamile_oliveria_10</v>
       </c>
       <c r="B29">
         <v>1</v>
@@ -14315,7 +14385,7 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>vndcardoso</v>
+        <v>malu832757</v>
       </c>
       <c r="B30">
         <v>1</v>
@@ -14329,7 +14399,7 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>ninjatheorist</v>
+        <v>vndcardoso</v>
       </c>
       <c r="B31">
         <v>1</v>
@@ -14343,7 +14413,7 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>gdazuera</v>
+        <v>ninjatheorist</v>
       </c>
       <c r="B32">
         <v>1</v>
@@ -14357,7 +14427,7 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>helenmacielmma</v>
+        <v>gdazuera</v>
       </c>
       <c r="B33">
         <v>1</v>
@@ -14371,21 +14441,21 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>adriano.trator</v>
+        <v>zackdos</v>
       </c>
       <c r="B34">
         <v>1</v>
       </c>
       <c r="C34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>cassiosants__</v>
+        <v>adriano.trator</v>
       </c>
       <c r="B35">
         <v>1</v>
@@ -14399,13 +14469,13 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>combintel</v>
+        <v>cassiosants__</v>
       </c>
       <c r="B36">
         <v>1</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -14413,7 +14483,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>masonharper_mma</v>
+        <v>combintel</v>
       </c>
       <c r="B37">
         <v>1</v>
@@ -14427,7 +14497,7 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>johnmma9</v>
+        <v>masonharper_mma</v>
       </c>
       <c r="B38">
         <v>1</v>
@@ -14441,7 +14511,7 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>mmmarc20</v>
+        <v>johnmma9</v>
       </c>
       <c r="B39">
         <v>1</v>
@@ -14455,7 +14525,7 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>pablofiorindi</v>
+        <v>mmmarc20</v>
       </c>
       <c r="B40">
         <v>1</v>
@@ -14469,7 +14539,7 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>_jullianadacruz</v>
+        <v>pablofiorindi</v>
       </c>
       <c r="B41">
         <v>1</v>
@@ -14483,7 +14553,7 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>erickdiaseds</v>
+        <v>_jullianadacruz</v>
       </c>
       <c r="B42">
         <v>1</v>
@@ -14497,7 +14567,7 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>ottonimestre</v>
+        <v>erickdiaseds</v>
       </c>
       <c r="B43">
         <v>1</v>
@@ -14511,7 +14581,7 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>adrianoams7</v>
+        <v>ottonimestre</v>
       </c>
       <c r="B44">
         <v>1</v>
@@ -14525,7 +14595,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>_hygor.soares</v>
+        <v>adrianoams7</v>
       </c>
       <c r="B45">
         <v>1</v>
@@ -14539,7 +14609,7 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>enzorkbjj</v>
+        <v>_hygor.soares</v>
       </c>
       <c r="B46">
         <v>1</v>
@@ -14553,7 +14623,7 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>emersonriosmma</v>
+        <v>enzorkbjj</v>
       </c>
       <c r="B47">
         <v>1</v>
@@ -14567,7 +14637,7 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>_pedro0h</v>
+        <v>emersonriosmma</v>
       </c>
       <c r="B48">
         <v>1</v>
@@ -14581,7 +14651,7 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>lorenzojjts</v>
+        <v>_pedro0h</v>
       </c>
       <c r="B49">
         <v>1</v>
@@ -14595,7 +14665,7 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>pauloserrati</v>
+        <v>lorenzojjts</v>
       </c>
       <c r="B50">
         <v>1</v>
@@ -14609,7 +14679,7 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>karen.ottoni</v>
+        <v>pauloserrati</v>
       </c>
       <c r="B51">
         <v>1</v>
@@ -14623,7 +14693,7 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>thiagoauper</v>
+        <v>karen.ottoni</v>
       </c>
       <c r="B52">
         <v>1</v>
@@ -14637,7 +14707,7 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>ellen.cristinaaa</v>
+        <v>thiagoauper</v>
       </c>
       <c r="B53">
         <v>1</v>
@@ -14651,7 +14721,7 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>albertoleandromoco</v>
+        <v>ellen.cristinaaa</v>
       </c>
       <c r="B54">
         <v>1</v>
@@ -14665,7 +14735,7 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>god.motivacao</v>
+        <v>albertoleandromoco</v>
       </c>
       <c r="B55">
         <v>1</v>
@@ -14679,7 +14749,7 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>jean_ferreira_br</v>
+        <v>god.motivacao</v>
       </c>
       <c r="B56">
         <v>1</v>
@@ -14693,7 +14763,7 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>ismaeldaniell</v>
+        <v>jean_ferreira_br</v>
       </c>
       <c r="B57">
         <v>1</v>
@@ -14707,83 +14777,83 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>leobahiamma</v>
+        <v>ismaeldaniell</v>
       </c>
       <c r="B58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C58">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D58">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>pedro_pavin_</v>
+        <v>i_am_mauispunjahchick</v>
       </c>
       <c r="B59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C59">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D59">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>allan10adm</v>
+        <v>808.chaz</v>
       </c>
       <c r="B60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C60">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D60">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>ismael.marreta_ufc</v>
+        <v>k_costa68</v>
       </c>
       <c r="B61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C61">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D61">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>joandersontubarao_ufc</v>
+        <v>leomvgomes</v>
       </c>
       <c r="B62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C62">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D62">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>gaby_alves07</v>
+        <v>leobahiamma</v>
       </c>
       <c r="B63">
         <v>0</v>
       </c>
       <c r="C63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D63">
         <v>1</v>
@@ -14791,7 +14861,7 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>pulsepro.nutrition</v>
+        <v>pedro_pavin_</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -14800,12 +14870,12 @@
         <v>1</v>
       </c>
       <c r="D64">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>herbeth_indiomma</v>
+        <v>allan10adm</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -14814,12 +14884,12 @@
         <v>1</v>
       </c>
       <c r="D65">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>danielbzk_</v>
+        <v>ismael.marreta_ufc</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -14828,12 +14898,12 @@
         <v>1</v>
       </c>
       <c r="D66">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>jp.mdc</v>
+        <v>joandersontubarao_ufc</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -14842,12 +14912,12 @@
         <v>1</v>
       </c>
       <c r="D67">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>rosacostasousa36</v>
+        <v>gaby_alves07</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -14856,26 +14926,110 @@
         <v>1</v>
       </c>
       <c r="D68">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
+        <v>diegosilvabjjoficial</v>
+      </c>
+      <c r="B69">
+        <v>0</v>
+      </c>
+      <c r="C69">
+        <v>1</v>
+      </c>
+      <c r="D69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>pulsepro.nutrition</v>
+      </c>
+      <c r="B70">
+        <v>0</v>
+      </c>
+      <c r="C70">
+        <v>1</v>
+      </c>
+      <c r="D70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>herbeth_indiomma</v>
+      </c>
+      <c r="B71">
+        <v>0</v>
+      </c>
+      <c r="C71">
+        <v>1</v>
+      </c>
+      <c r="D71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>danielbzk_</v>
+      </c>
+      <c r="B72">
+        <v>0</v>
+      </c>
+      <c r="C72">
+        <v>1</v>
+      </c>
+      <c r="D72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>jp.mdc</v>
+      </c>
+      <c r="B73">
+        <v>0</v>
+      </c>
+      <c r="C73">
+        <v>1</v>
+      </c>
+      <c r="D73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>rosacostasousa36</v>
+      </c>
+      <c r="B74">
+        <v>0</v>
+      </c>
+      <c r="C74">
+        <v>1</v>
+      </c>
+      <c r="D74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
         <v>cathya_ferreira</v>
       </c>
-      <c r="B69">
-        <v>0</v>
-      </c>
-      <c r="C69">
-        <v>1</v>
-      </c>
-      <c r="D69">
+      <c r="B75">
+        <v>0</v>
+      </c>
+      <c r="C75">
+        <v>1</v>
+      </c>
+      <c r="D75">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D69"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D75"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Engagement Rankings 2026-07.xlsx
+++ b/Engagement Rankings 2026-07.xlsx
@@ -478,10 +478,10 @@
         <v>895</v>
       </c>
       <c r="C6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D6">
-        <v>734</v>
+        <v>735</v>
       </c>
     </row>
     <row r="7">
@@ -545,13 +545,13 @@
         <v>combintel</v>
       </c>
       <c r="B11">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C11">
         <v>2</v>
       </c>
       <c r="D11">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12">
@@ -856,10 +856,10 @@
         <v>40</v>
       </c>
       <c r="C33">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D33">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="34">
@@ -1158,35 +1158,35 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>shawlin13oficial</v>
+        <v>ninjatheorist</v>
       </c>
       <c r="B55">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="C55">
         <v>0</v>
       </c>
       <c r="D55">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>pedromadeira.s</v>
+        <v>shawlin13oficial</v>
       </c>
       <c r="B56">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C56">
         <v>0</v>
       </c>
       <c r="D56">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>_cardoso_caio_</v>
+        <v>pedromadeira.s</v>
       </c>
       <c r="B57">
         <v>31</v>
@@ -1195,21 +1195,21 @@
         <v>0</v>
       </c>
       <c r="D57">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>ninjatheorist</v>
+        <v>_cardoso_caio_</v>
       </c>
       <c r="B58">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C58">
         <v>0</v>
       </c>
       <c r="D58">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="59">
@@ -14013,10 +14013,10 @@
         <v>25</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4">
@@ -14083,10 +14083,10 @@
         <v>2</v>
       </c>
       <c r="C8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D8">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -14231,10 +14231,10 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>cristianpsicologo</v>
+        <v>combintel</v>
       </c>
       <c r="B19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -14245,10 +14245,10 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>brcks4breakfast</v>
+        <v>ninjatheorist</v>
       </c>
       <c r="B20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -14259,7 +14259,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>rm.nicki</v>
+        <v>cristianpsicologo</v>
       </c>
       <c r="B21">
         <v>1</v>
@@ -14273,7 +14273,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>mma.idiot</v>
+        <v>brcks4breakfast</v>
       </c>
       <c r="B22">
         <v>1</v>
@@ -14287,7 +14287,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>lili.munix</v>
+        <v>rm.nicki</v>
       </c>
       <c r="B23">
         <v>1</v>
@@ -14301,7 +14301,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>carlos_hm_iglesias</v>
+        <v>mma.idiot</v>
       </c>
       <c r="B24">
         <v>1</v>
@@ -14315,7 +14315,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>roger_santosmma</v>
+        <v>lili.munix</v>
       </c>
       <c r="B25">
         <v>1</v>
@@ -14329,7 +14329,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>murata_profight</v>
+        <v>carlos_hm_iglesias</v>
       </c>
       <c r="B26">
         <v>1</v>
@@ -14343,7 +14343,7 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>rayn.avaro</v>
+        <v>roger_santosmma</v>
       </c>
       <c r="B27">
         <v>1</v>
@@ -14357,7 +14357,7 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>arafight_pesc</v>
+        <v>murata_profight</v>
       </c>
       <c r="B28">
         <v>1</v>
@@ -14371,7 +14371,7 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>kamile_oliveria_10</v>
+        <v>rayn.avaro</v>
       </c>
       <c r="B29">
         <v>1</v>
@@ -14385,7 +14385,7 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>malu832757</v>
+        <v>arafight_pesc</v>
       </c>
       <c r="B30">
         <v>1</v>
@@ -14399,7 +14399,7 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>vndcardoso</v>
+        <v>kamile_oliveria_10</v>
       </c>
       <c r="B31">
         <v>1</v>
@@ -14413,7 +14413,7 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>ninjatheorist</v>
+        <v>malu832757</v>
       </c>
       <c r="B32">
         <v>1</v>
@@ -14427,7 +14427,7 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>gdazuera</v>
+        <v>vndcardoso</v>
       </c>
       <c r="B33">
         <v>1</v>
@@ -14441,7 +14441,7 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>zackdos</v>
+        <v>gdazuera</v>
       </c>
       <c r="B34">
         <v>1</v>
@@ -14455,21 +14455,21 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>adriano.trator</v>
+        <v>zackdos</v>
       </c>
       <c r="B35">
         <v>1</v>
       </c>
       <c r="C35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>cassiosants__</v>
+        <v>adriano.trator</v>
       </c>
       <c r="B36">
         <v>1</v>
@@ -14483,13 +14483,13 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>combintel</v>
+        <v>cassiosants__</v>
       </c>
       <c r="B37">
         <v>1</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D37">
         <v>0</v>

--- a/Engagement Rankings 2026-07.xlsx
+++ b/Engagement Rankings 2026-07.xlsx
@@ -419,13 +419,13 @@
         <v>peacegrappler</v>
       </c>
       <c r="B2">
-        <v>13442</v>
+        <v>13447</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>12176</v>
+        <v>12178</v>
       </c>
     </row>
     <row r="3">
@@ -475,13 +475,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B6">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="C6">
         <v>16</v>
       </c>
       <c r="D6">
-        <v>735</v>
+        <v>736</v>
       </c>
     </row>
     <row r="7">
@@ -853,10 +853,10 @@
         <v>washington_cassisno</v>
       </c>
       <c r="B33">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C33">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D33">
         <v>39</v>
@@ -1228,49 +1228,49 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>jujua_maral1</v>
+        <v>kelly_ottoni</v>
       </c>
       <c r="B60">
         <v>23</v>
       </c>
       <c r="C60">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D60">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>thiagoauper</v>
+        <v>jujua_maral1</v>
       </c>
       <c r="B61">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C61">
         <v>0</v>
       </c>
       <c r="D61">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>thundergrapple</v>
+        <v>thiagoauper</v>
       </c>
       <c r="B62">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="C62">
         <v>0</v>
       </c>
       <c r="D62">
-        <v>18</v>
+        <v>7</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>galler_peace</v>
+        <v>thundergrapple</v>
       </c>
       <c r="B63">
         <v>22</v>
@@ -1284,7 +1284,7 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>figh_grappler</v>
+        <v>galler_peace</v>
       </c>
       <c r="B64">
         <v>22</v>
@@ -1298,13 +1298,13 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>kelly_ottoni</v>
+        <v>figh_grappler</v>
       </c>
       <c r="B65">
         <v>22</v>
       </c>
       <c r="C65">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D65">
         <v>18</v>
@@ -1312,30 +1312,30 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>mar_iarmaria</v>
+        <v>eliassilverio</v>
       </c>
       <c r="B66">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C66">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D66">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>eliassilverio</v>
+        <v>mar_iarmaria</v>
       </c>
       <c r="B67">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C67">
+        <v>0</v>
+      </c>
+      <c r="D67">
         <v>14</v>
-      </c>
-      <c r="D67">
-        <v>9</v>
       </c>
     </row>
     <row r="68">
@@ -1634,86 +1634,86 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>cjrnavalhaoficial</v>
+        <v>natanborges001</v>
       </c>
       <c r="B89">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C89">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D89">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>macamariotti</v>
+        <v>cjrnavalhaoficial</v>
       </c>
       <c r="B90">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C90">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D90">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>guilhermemirandamma</v>
+        <v>macamariotti</v>
       </c>
       <c r="B91">
         <v>7</v>
       </c>
       <c r="C91">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D91">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>luizalaguerabjj</v>
+        <v>guilhermemirandamma</v>
       </c>
       <c r="B92">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D92">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>cpetemma248</v>
+        <v>luizalaguerabjj</v>
       </c>
       <c r="B93">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C93">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D93">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>natanborges001</v>
+        <v>cpetemma248</v>
       </c>
       <c r="B94">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C94">
         <v>3</v>
       </c>
       <c r="D94">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="95">
@@ -2586,13 +2586,13 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>ailtonjuniorbarbeiro</v>
+        <v>npb.enterprise</v>
       </c>
       <c r="B157">
         <v>3</v>
       </c>
       <c r="C157">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D157">
         <v>3</v>
@@ -2600,105 +2600,105 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>rafaelmacapa_</v>
+        <v>ailtonjuniorbarbeiro</v>
       </c>
       <c r="B158">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C158">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D158">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>daniezzyy</v>
+        <v>rafaelmacapa_</v>
       </c>
       <c r="B159">
         <v>4</v>
       </c>
       <c r="C159">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D159">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>glm.barbosa</v>
+        <v>daniezzyy</v>
       </c>
       <c r="B160">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C160">
         <v>0</v>
       </c>
       <c r="D160">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>fernando.mma</v>
+        <v>glm.barbosa</v>
       </c>
       <c r="B161">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C161">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D161">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>davizoka_mascote</v>
+        <v>fernando.mma</v>
       </c>
       <c r="B162">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C162">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D162">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>enzo_henrik</v>
+        <v>davizoka_mascote</v>
       </c>
       <c r="B163">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C163">
         <v>0</v>
       </c>
       <c r="D163">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>douglasoct_mma</v>
+        <v>enzo_henrik</v>
       </c>
       <c r="B164">
         <v>2</v>
       </c>
       <c r="C164">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D164">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>leobahiamma</v>
+        <v>douglasoct_mma</v>
       </c>
       <c r="B165">
         <v>2</v>
@@ -2712,122 +2712,122 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>marcocanatelli</v>
+        <v>leobahiamma</v>
       </c>
       <c r="B166">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C166">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D166">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>benjafloripabjj</v>
+        <v>marcocanatelli</v>
       </c>
       <c r="B167">
         <v>4</v>
       </c>
       <c r="C167">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D167">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>heltoncm2002</v>
+        <v>benjafloripabjj</v>
       </c>
       <c r="B168">
         <v>4</v>
       </c>
       <c r="C168">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D168">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>pitbullandrade</v>
+        <v>heltoncm2002</v>
       </c>
       <c r="B169">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C169">
         <v>1</v>
       </c>
       <c r="D169">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>zedelano</v>
+        <v>pitbullandrade</v>
       </c>
       <c r="B170">
         <v>3</v>
       </c>
       <c r="C170">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D170">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>salost.ofc</v>
+        <v>zedelano</v>
       </c>
       <c r="B171">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C171">
         <v>0</v>
       </c>
       <c r="D171">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>gabrielsouzamma</v>
+        <v>salost.ofc</v>
       </c>
       <c r="B172">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C172">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D172">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>wilson_n_janjacomo</v>
+        <v>gabrielsouzamma</v>
       </c>
       <c r="B173">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C173">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D173">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>y.arthur_01</v>
+        <v>wilson_n_janjacomo</v>
       </c>
       <c r="B174">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C174">
         <v>0</v>
@@ -2838,49 +2838,49 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>s__simone__</v>
+        <v>y.arthur_01</v>
       </c>
       <c r="B175">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C175">
         <v>0</v>
       </c>
       <c r="D175">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>maxbjj_0</v>
+        <v>s__simone__</v>
       </c>
       <c r="B176">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C176">
         <v>0</v>
       </c>
       <c r="D176">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>vincenzo_pit_monster</v>
+        <v>maxbjj_0</v>
       </c>
       <c r="B177">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C177">
         <v>0</v>
       </c>
       <c r="D177">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>rian.vitorjj</v>
+        <v>vincenzo_pit_monster</v>
       </c>
       <c r="B178">
         <v>2</v>
@@ -2894,7 +2894,7 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>danielrodrigues1000</v>
+        <v>rian.vitorjj</v>
       </c>
       <c r="B179">
         <v>2</v>
@@ -2908,7 +2908,7 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>lonbradao__777</v>
+        <v>danielrodrigues1000</v>
       </c>
       <c r="B180">
         <v>2</v>
@@ -2922,7 +2922,7 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>wesleysepulveda__mma</v>
+        <v>lonbradao__777</v>
       </c>
       <c r="B181">
         <v>2</v>
@@ -2936,63 +2936,63 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>fabinho_falcao_</v>
+        <v>wesleysepulveda__mma</v>
       </c>
       <c r="B182">
         <v>2</v>
       </c>
       <c r="C182">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D182">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>odeivisoncardoso</v>
+        <v>fabinho_falcao_</v>
       </c>
       <c r="B183">
         <v>2</v>
       </c>
       <c r="C183">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D183">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>fabiomarcelinopersonal</v>
+        <v>odeivisoncardoso</v>
       </c>
       <c r="B184">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C184">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D184">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>peacegrappler_archive</v>
+        <v>fabiomarcelinopersonal</v>
       </c>
       <c r="B185">
         <v>3</v>
       </c>
       <c r="C185">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D185">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>reifernandes</v>
+        <v>peacegrappler_archive</v>
       </c>
       <c r="B186">
         <v>3</v>
@@ -3006,69 +3006,69 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>daniel_dias_214</v>
+        <v>reifernandes</v>
       </c>
       <c r="B187">
         <v>3</v>
       </c>
       <c r="C187">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D187">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>mauriciomouraprev</v>
+        <v>daniel_dias_214</v>
       </c>
       <c r="B188">
         <v>3</v>
       </c>
       <c r="C188">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D188">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>cristianpsicologo</v>
+        <v>mauriciomouraprev</v>
       </c>
       <c r="B189">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C189">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D189">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>mah__vergueiro</v>
+        <v>cristianpsicologo</v>
       </c>
       <c r="B190">
+        <v>2</v>
+      </c>
+      <c r="C190">
+        <v>4</v>
+      </c>
+      <c r="D190">
         <v>3</v>
-      </c>
-      <c r="C190">
-        <v>0</v>
-      </c>
-      <c r="D190">
-        <v>0</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>pizzaria.bambina_</v>
+        <v>mah__vergueiro</v>
       </c>
       <c r="B191">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C191">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D191">
         <v>0</v>
@@ -3076,7 +3076,7 @@
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>jean_ferreira_br</v>
+        <v>pizzaria.bambina_</v>
       </c>
       <c r="B192">
         <v>4</v>
@@ -3090,49 +3090,49 @@
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>h.codasqueves</v>
+        <v>jean_ferreira_br</v>
       </c>
       <c r="B193">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C193">
         <v>1</v>
       </c>
       <c r="D193">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>pauloserrati</v>
+        <v>h.codasqueves</v>
       </c>
       <c r="B194">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C194">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D194">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>alexandreconsentino</v>
+        <v>pauloserrati</v>
       </c>
       <c r="B195">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C195">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D195">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>lipe.ftt</v>
+        <v>alexandreconsentino</v>
       </c>
       <c r="B196">
         <v>4</v>
@@ -3146,7 +3146,7 @@
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>fau_gfs</v>
+        <v>lipe.ftt</v>
       </c>
       <c r="B197">
         <v>4</v>
@@ -3160,21 +3160,21 @@
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>vitorpetrino</v>
+        <v>fau_gfs</v>
       </c>
       <c r="B198">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C198">
         <v>0</v>
       </c>
       <c r="D198">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>thompsonborralho</v>
+        <v>vitorpetrino</v>
       </c>
       <c r="B199">
         <v>3</v>
@@ -3188,7 +3188,7 @@
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>devessonjj</v>
+        <v>thompsonborralho</v>
       </c>
       <c r="B200">
         <v>3</v>
@@ -3202,58 +3202,58 @@
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>espaco_jhayoliveira</v>
+        <v>devessonjj</v>
       </c>
       <c r="B201">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C201">
         <v>0</v>
       </c>
       <c r="D201">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>artewebpersonalizados</v>
+        <v>espaco_jhayoliveira</v>
       </c>
       <c r="B202">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C202">
         <v>0</v>
       </c>
       <c r="D202">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>marcosferreira.ofc1</v>
+        <v>artewebpersonalizados</v>
       </c>
       <c r="B203">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C203">
         <v>0</v>
       </c>
       <c r="D203">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>npb.enterprise</v>
+        <v>marcosferreira.ofc1</v>
       </c>
       <c r="B204">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C204">
         <v>0</v>
       </c>
       <c r="D204">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="205">
@@ -4280,41 +4280,41 @@
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>select_from_joao</v>
+        <v>canalgolpebaixo</v>
       </c>
       <c r="B278">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C278">
         <v>1</v>
       </c>
       <c r="D278">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>fabaotipster</v>
+        <v>select_from_joao</v>
       </c>
       <c r="B279">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C279">
         <v>1</v>
       </c>
       <c r="D279">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>luanlacerda_ufc_61kg</v>
+        <v>fabaotipster</v>
       </c>
       <c r="B280">
         <v>1</v>
       </c>
       <c r="C280">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D280">
         <v>1</v>
@@ -4322,13 +4322,13 @@
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>helenaseveribjj</v>
+        <v>luanlacerda_ufc_61kg</v>
       </c>
       <c r="B281">
         <v>1</v>
       </c>
       <c r="C281">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D281">
         <v>1</v>
@@ -4336,49 +4336,49 @@
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>marciokeske</v>
+        <v>helenaseveribjj</v>
       </c>
       <c r="B282">
         <v>1</v>
       </c>
       <c r="C282">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D282">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>ommariotti</v>
+        <v>marciokeske</v>
       </c>
       <c r="B283">
         <v>1</v>
       </c>
       <c r="C283">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D283">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>felipebunesufc</v>
+        <v>ommariotti</v>
       </c>
       <c r="B284">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C284">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D284">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>icarohilton</v>
+        <v>felipebunesufc</v>
       </c>
       <c r="B285">
         <v>2</v>
@@ -4392,35 +4392,35 @@
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>jesabelmelo9</v>
+        <v>icarohilton</v>
       </c>
       <c r="B286">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C286">
         <v>1</v>
       </c>
       <c r="D286">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>iranbez</v>
+        <v>jesabelmelo9</v>
       </c>
       <c r="B287">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C287">
         <v>1</v>
       </c>
       <c r="D287">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>sthe._.araujo</v>
+        <v>iranbez</v>
       </c>
       <c r="B288">
         <v>2</v>
@@ -4434,13 +4434,13 @@
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>clayton77silva</v>
+        <v>sthe._.araujo</v>
       </c>
       <c r="B289">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C289">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D289">
         <v>0</v>
@@ -4448,13 +4448,13 @@
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>raycon_mma</v>
+        <v>clayton77silva</v>
       </c>
       <c r="B290">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C290">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D290">
         <v>0</v>
@@ -4462,7 +4462,7 @@
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>sarahfmaia</v>
+        <v>raycon_mma</v>
       </c>
       <c r="B291">
         <v>2</v>
@@ -4476,63 +4476,63 @@
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>rosacostasousa36</v>
+        <v>sarahfmaia</v>
       </c>
       <c r="B292">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C292">
         <v>1</v>
       </c>
       <c r="D292">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>erivan_sousa_tico</v>
+        <v>rosacostasousa36</v>
       </c>
       <c r="B293">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C293">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D293">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>fernando.nogueira.7792</v>
+        <v>erivan_sousa_tico</v>
       </c>
       <c r="B294">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C294">
         <v>0</v>
       </c>
       <c r="D294">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>aliferpaulo_</v>
+        <v>fernando.nogueira.7792</v>
       </c>
       <c r="B295">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C295">
         <v>0</v>
       </c>
       <c r="D295">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>sambagabrieloficial</v>
+        <v>aliferpaulo_</v>
       </c>
       <c r="B296">
         <v>2</v>
@@ -4546,35 +4546,35 @@
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>raelduraes</v>
+        <v>sambagabrieloficial</v>
       </c>
       <c r="B297">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C297">
         <v>0</v>
       </c>
       <c r="D297">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>martta.mariah</v>
+        <v>raelduraes</v>
       </c>
       <c r="B298">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C298">
         <v>0</v>
       </c>
       <c r="D298">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>wlt_miguel</v>
+        <v>martta.mariah</v>
       </c>
       <c r="B299">
         <v>2</v>
@@ -4588,7 +4588,7 @@
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>_bety_marcal</v>
+        <v>wlt_miguel</v>
       </c>
       <c r="B300">
         <v>2</v>
@@ -4602,7 +4602,7 @@
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>wesley_bjjvc</v>
+        <v>_bety_marcal</v>
       </c>
       <c r="B301">
         <v>2</v>
@@ -4616,7 +4616,7 @@
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>guga.llisboa_bjj</v>
+        <v>wesley_bjjvc</v>
       </c>
       <c r="B302">
         <v>2</v>
@@ -4630,21 +4630,21 @@
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>marcosmeireles_pqd_</v>
+        <v>guga.llisboa_bjj</v>
       </c>
       <c r="B303">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C303">
         <v>0</v>
       </c>
       <c r="D303">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>gabriel.junior20bjj</v>
+        <v>marcosmeireles_pqd_</v>
       </c>
       <c r="B304">
         <v>1</v>
@@ -4658,21 +4658,21 @@
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>fabi.godooy</v>
+        <v>gabriel.junior20bjj</v>
       </c>
       <c r="B305">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C305">
         <v>0</v>
       </c>
       <c r="D305">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>davicorbella</v>
+        <v>fabi.godooy</v>
       </c>
       <c r="B306">
         <v>2</v>
@@ -4686,7 +4686,7 @@
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>joegam3r</v>
+        <v>davicorbella</v>
       </c>
       <c r="B307">
         <v>2</v>
@@ -4700,35 +4700,35 @@
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>graalino</v>
+        <v>joegam3r</v>
       </c>
       <c r="B308">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C308">
         <v>0</v>
       </c>
       <c r="D308">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>ramanatoscanellibjj</v>
+        <v>graalino</v>
       </c>
       <c r="B309">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C309">
         <v>0</v>
       </c>
       <c r="D309">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>mariabeltapagani</v>
+        <v>ramanatoscanellibjj</v>
       </c>
       <c r="B310">
         <v>2</v>
@@ -4742,7 +4742,7 @@
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>auriceliaribeiro_</v>
+        <v>mariabeltapagani</v>
       </c>
       <c r="B311">
         <v>2</v>
@@ -4756,7 +4756,7 @@
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>craig_cohen1</v>
+        <v>auriceliaribeiro_</v>
       </c>
       <c r="B312">
         <v>2</v>
@@ -4770,35 +4770,35 @@
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>glessios_silva</v>
+        <v>craig_cohen1</v>
       </c>
       <c r="B313">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C313">
         <v>0</v>
       </c>
       <c r="D313">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>fabioincalado</v>
+        <v>glessios_silva</v>
       </c>
       <c r="B314">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C314">
         <v>0</v>
       </c>
       <c r="D314">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>vanderleiamellogois</v>
+        <v>fabioincalado</v>
       </c>
       <c r="B315">
         <v>2</v>
@@ -4812,91 +4812,91 @@
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>pedrinhosbjj</v>
+        <v>vanderleiamellogois</v>
       </c>
       <c r="B316">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C316">
         <v>0</v>
       </c>
       <c r="D316">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>_jaquealms</v>
+        <v>pedrinhosbjj</v>
       </c>
       <c r="B317">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C317">
         <v>0</v>
       </c>
       <c r="D317">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>caio.fermianoo</v>
+        <v>_jaquealms</v>
       </c>
       <c r="B318">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C318">
         <v>0</v>
       </c>
       <c r="D318">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>corrozzzive</v>
+        <v>caio.fermianoo</v>
       </c>
       <c r="B319">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C319">
         <v>0</v>
       </c>
       <c r="D319">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>araujojonaspenhade</v>
+        <v>corrozzzive</v>
       </c>
       <c r="B320">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C320">
         <v>0</v>
       </c>
       <c r="D320">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>duuleitee</v>
+        <v>araujojonaspenhade</v>
       </c>
       <c r="B321">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C321">
         <v>0</v>
       </c>
       <c r="D321">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>pvd_._dudis</v>
+        <v>duuleitee</v>
       </c>
       <c r="B322">
         <v>2</v>
@@ -4910,7 +4910,7 @@
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>boia_capoeira</v>
+        <v>pvd_._dudis</v>
       </c>
       <c r="B323">
         <v>2</v>
@@ -4924,27 +4924,27 @@
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>tatianeaguiarp</v>
+        <v>boia_capoeira</v>
       </c>
       <c r="B324">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C324">
         <v>0</v>
       </c>
       <c r="D324">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>ismael.marreta_ufc</v>
+        <v>tatianeaguiarp</v>
       </c>
       <c r="B325">
         <v>1</v>
       </c>
       <c r="C325">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D325">
         <v>1</v>
@@ -4952,13 +4952,13 @@
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>ottonhona</v>
+        <v>ismael.marreta_ufc</v>
       </c>
       <c r="B326">
         <v>1</v>
       </c>
       <c r="C326">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D326">
         <v>1</v>
@@ -4966,7 +4966,7 @@
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>alcateiaartesmarciais</v>
+        <v>ottonhona</v>
       </c>
       <c r="B327">
         <v>1</v>
@@ -4980,49 +4980,49 @@
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>marcov__7</v>
+        <v>alcateiaartesmarciais</v>
       </c>
       <c r="B328">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C328">
         <v>0</v>
       </c>
       <c r="D328">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>anachierico_</v>
+        <v>marcov__7</v>
       </c>
       <c r="B329">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C329">
         <v>0</v>
       </c>
       <c r="D329">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>toraostreet</v>
+        <v>anachierico_</v>
       </c>
       <c r="B330">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C330">
         <v>0</v>
       </c>
       <c r="D330">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>bears635</v>
+        <v>toraostreet</v>
       </c>
       <c r="B331">
         <v>2</v>
@@ -5036,7 +5036,7 @@
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>vivi_fitnees</v>
+        <v>bears635</v>
       </c>
       <c r="B332">
         <v>2</v>
@@ -5050,7 +5050,7 @@
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>shockmonteiro</v>
+        <v>vivi_fitnees</v>
       </c>
       <c r="B333">
         <v>2</v>
@@ -5064,7 +5064,7 @@
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>murilomuaythai</v>
+        <v>shockmonteiro</v>
       </c>
       <c r="B334">
         <v>2</v>
@@ -5078,35 +5078,35 @@
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>suel.f1270</v>
+        <v>murilomuaythai</v>
       </c>
       <c r="B335">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C335">
         <v>0</v>
       </c>
       <c r="D335">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>thiagoxavier13</v>
+        <v>suel.f1270</v>
       </c>
       <c r="B336">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C336">
         <v>0</v>
       </c>
       <c r="D336">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>fatima_trindade_</v>
+        <v>thiagoxavier13</v>
       </c>
       <c r="B337">
         <v>2</v>
@@ -5120,21 +5120,21 @@
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>gillesarquitetura</v>
+        <v>fatima_trindade_</v>
       </c>
       <c r="B338">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C338">
         <v>0</v>
       </c>
       <c r="D338">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>alvestank</v>
+        <v>gillesarquitetura</v>
       </c>
       <c r="B339">
         <v>1</v>
@@ -5148,35 +5148,35 @@
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>marciooangelo</v>
+        <v>alvestank</v>
       </c>
       <c r="B340">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C340">
         <v>0</v>
       </c>
       <c r="D340">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>adevaldojr_</v>
+        <v>marciooangelo</v>
       </c>
       <c r="B341">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C341">
         <v>0</v>
       </c>
       <c r="D341">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>manucanecorso.bjj</v>
+        <v>adevaldojr_</v>
       </c>
       <c r="B342">
         <v>1</v>
@@ -5190,63 +5190,63 @@
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>claudiaottoni2025</v>
+        <v>manucanecorso.bjj</v>
       </c>
       <c r="B343">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C343">
         <v>0</v>
       </c>
       <c r="D343">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>tavin.mendes</v>
+        <v>claudiaottoni2025</v>
       </c>
       <c r="B344">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C344">
         <v>0</v>
       </c>
       <c r="D344">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>_jullianadacruz</v>
+        <v>tavin.mendes</v>
       </c>
       <c r="B345">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C345">
         <v>0</v>
       </c>
       <c r="D345">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>fabiieju</v>
+        <v>_jullianadacruz</v>
       </c>
       <c r="B346">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C346">
         <v>0</v>
       </c>
       <c r="D346">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>marqueswanderson</v>
+        <v>fabiieju</v>
       </c>
       <c r="B347">
         <v>1</v>
@@ -5260,7 +5260,7 @@
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>adauto2505</v>
+        <v>marqueswanderson</v>
       </c>
       <c r="B348">
         <v>1</v>
@@ -5274,7 +5274,7 @@
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>joaogagoarta</v>
+        <v>adauto2505</v>
       </c>
       <c r="B349">
         <v>1</v>
@@ -5288,7 +5288,7 @@
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>brcks4breakfast</v>
+        <v>joaogagoarta</v>
       </c>
       <c r="B350">
         <v>1</v>
@@ -5302,7 +5302,7 @@
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>lili.munix</v>
+        <v>brcks4breakfast</v>
       </c>
       <c r="B351">
         <v>1</v>
@@ -5316,7 +5316,7 @@
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>carlos_hm_iglesias</v>
+        <v>lili.munix</v>
       </c>
       <c r="B352">
         <v>1</v>
@@ -5330,7 +5330,7 @@
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>roger_santosmma</v>
+        <v>carlos_hm_iglesias</v>
       </c>
       <c r="B353">
         <v>1</v>
@@ -5344,7 +5344,7 @@
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>murata_profight</v>
+        <v>roger_santosmma</v>
       </c>
       <c r="B354">
         <v>1</v>
@@ -5358,7 +5358,7 @@
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>zackdos</v>
+        <v>murata_profight</v>
       </c>
       <c r="B355">
         <v>1</v>
@@ -5372,41 +5372,41 @@
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>dr.daniloduartefisio</v>
+        <v>zackdos</v>
       </c>
       <c r="B356">
         <v>1</v>
       </c>
       <c r="C356">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D356">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>pablo_bvg</v>
+        <v>dr.daniloduartefisio</v>
       </c>
       <c r="B357">
         <v>1</v>
       </c>
       <c r="C357">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D357">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>marceloscorzato</v>
+        <v>pablo_bvg</v>
       </c>
       <c r="B358">
         <v>1</v>
       </c>
       <c r="C358">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D358">
         <v>1</v>
@@ -5414,49 +5414,49 @@
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>sergio_alves_bjj</v>
+        <v>marceloscorzato</v>
       </c>
       <c r="B359">
         <v>1</v>
       </c>
       <c r="C359">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D359">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>pedro_pavin_</v>
+        <v>sergio_alves_bjj</v>
       </c>
       <c r="B360">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C360">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D360">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>treinaadorrafael</v>
+        <v>pedro_pavin_</v>
       </c>
       <c r="B361">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C361">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D361">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>estevaotoledo</v>
+        <v>treinaadorrafael</v>
       </c>
       <c r="B362">
         <v>1</v>
@@ -5470,13 +5470,13 @@
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>djsagatoficial</v>
+        <v>estevaotoledo</v>
       </c>
       <c r="B363">
         <v>1</v>
       </c>
       <c r="C363">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D363">
         <v>0</v>
@@ -5484,13 +5484,13 @@
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>yurimartins1_</v>
+        <v>djsagatoficial</v>
       </c>
       <c r="B364">
         <v>1</v>
       </c>
       <c r="C364">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D364">
         <v>0</v>
@@ -5498,7 +5498,7 @@
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>matheusteodoro_1</v>
+        <v>yurimartins1_</v>
       </c>
       <c r="B365">
         <v>1</v>
@@ -5512,7 +5512,7 @@
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>maria.pereiradeoliveira.5283</v>
+        <v>matheusteodoro_1</v>
       </c>
       <c r="B366">
         <v>1</v>
@@ -5526,13 +5526,13 @@
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>kael_lyto</v>
+        <v>maria.pereiradeoliveira.5283</v>
       </c>
       <c r="B367">
         <v>1</v>
       </c>
       <c r="C367">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D367">
         <v>0</v>
@@ -5540,13 +5540,13 @@
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>kawannsenaboxe</v>
+        <v>kael_lyto</v>
       </c>
       <c r="B368">
         <v>1</v>
       </c>
       <c r="C368">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D368">
         <v>0</v>
@@ -5554,7 +5554,7 @@
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>guiiviieira_</v>
+        <v>kawannsenaboxe</v>
       </c>
       <c r="B369">
         <v>1</v>
@@ -5568,7 +5568,7 @@
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>cshigueo</v>
+        <v>guiiviieira_</v>
       </c>
       <c r="B370">
         <v>1</v>
@@ -5582,7 +5582,7 @@
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>vitorhugo_vtr</v>
+        <v>cshigueo</v>
       </c>
       <c r="B371">
         <v>1</v>
@@ -5596,7 +5596,7 @@
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>danni_goncalves12</v>
+        <v>vitorhugo_vtr</v>
       </c>
       <c r="B372">
         <v>1</v>
@@ -5610,7 +5610,7 @@
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>mttsm._</v>
+        <v>danni_goncalves12</v>
       </c>
       <c r="B373">
         <v>1</v>
@@ -5624,7 +5624,7 @@
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>andrealvess02</v>
+        <v>mttsm._</v>
       </c>
       <c r="B374">
         <v>1</v>
@@ -5638,7 +5638,7 @@
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>gildojiu</v>
+        <v>andrealvess02</v>
       </c>
       <c r="B375">
         <v>1</v>
@@ -5652,13 +5652,13 @@
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>fagnerosensei</v>
+        <v>gildojiu</v>
       </c>
       <c r="B376">
         <v>1</v>
       </c>
       <c r="C376">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D376">
         <v>0</v>
@@ -5666,7 +5666,7 @@
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>flavio.dequeiroz</v>
+        <v>fagnerosensei</v>
       </c>
       <c r="B377">
         <v>1</v>
@@ -5680,13 +5680,13 @@
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>030sami</v>
+        <v>flavio.dequeiroz</v>
       </c>
       <c r="B378">
         <v>1</v>
       </c>
       <c r="C378">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D378">
         <v>0</v>
@@ -5694,35 +5694,35 @@
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>giulia.fasolato</v>
+        <v>030sami</v>
       </c>
       <c r="B379">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C379">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D379">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>selipereirapereira</v>
+        <v>giulia.fasolato</v>
       </c>
       <c r="B380">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C380">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D380">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>d.silvamma</v>
+        <v>selipereirapereira</v>
       </c>
       <c r="B381">
         <v>1</v>
@@ -5736,7 +5736,7 @@
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>kalindrafaria</v>
+        <v>d.silvamma</v>
       </c>
       <c r="B382">
         <v>1</v>
@@ -5750,35 +5750,35 @@
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>igorsiqueiramma57</v>
+        <v>kalindrafaria</v>
       </c>
       <c r="B383">
         <v>1</v>
       </c>
       <c r="C383">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D383">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>manoelwilliamdejesus</v>
+        <v>igorsiqueiramma57</v>
       </c>
       <c r="B384">
         <v>1</v>
       </c>
       <c r="C384">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D384">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>oniszczuk_ko</v>
+        <v>manoelwilliamdejesus</v>
       </c>
       <c r="B385">
         <v>1</v>
@@ -5792,7 +5792,7 @@
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>andreibjj</v>
+        <v>oniszczuk_ko</v>
       </c>
       <c r="B386">
         <v>1</v>
@@ -5806,7 +5806,7 @@
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>killemquick</v>
+        <v>andreibjj</v>
       </c>
       <c r="B387">
         <v>1</v>
@@ -5820,7 +5820,7 @@
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>chuck_tlp</v>
+        <v>killemquick</v>
       </c>
       <c r="B388">
         <v>1</v>
@@ -5834,7 +5834,7 @@
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>henriquemmunhoz</v>
+        <v>chuck_tlp</v>
       </c>
       <c r="B389">
         <v>1</v>
@@ -5848,7 +5848,7 @@
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>flavio_tuba8</v>
+        <v>henriquemmunhoz</v>
       </c>
       <c r="B390">
         <v>1</v>
@@ -5862,13 +5862,13 @@
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>koliseu.br</v>
+        <v>flavio_tuba8</v>
       </c>
       <c r="B391">
         <v>1</v>
       </c>
       <c r="C391">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D391">
         <v>0</v>
@@ -5876,41 +5876,41 @@
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>aida_dos_sonhos</v>
+        <v>koliseu.br</v>
       </c>
       <c r="B392">
         <v>1</v>
       </c>
       <c r="C392">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D392">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>plmoreiraz</v>
+        <v>aida_dos_sonhos</v>
       </c>
       <c r="B393">
         <v>1</v>
       </c>
       <c r="C393">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D393">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>cathya_ferreira</v>
+        <v>plmoreiraz</v>
       </c>
       <c r="B394">
         <v>1</v>
       </c>
       <c r="C394">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D394">
         <v>0</v>
@@ -5918,13 +5918,13 @@
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>marianappedro</v>
+        <v>cathya_ferreira</v>
       </c>
       <c r="B395">
         <v>1</v>
       </c>
       <c r="C395">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D395">
         <v>0</v>
@@ -5932,7 +5932,7 @@
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>morena_ramos</v>
+        <v>marianappedro</v>
       </c>
       <c r="B396">
         <v>1</v>
@@ -5946,21 +5946,21 @@
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>_pedro0h</v>
+        <v>morena_ramos</v>
       </c>
       <c r="B397">
         <v>1</v>
       </c>
       <c r="C397">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D397">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>yeslifeacademia</v>
+        <v>_pedro0h</v>
       </c>
       <c r="B398">
         <v>1</v>
@@ -5969,12 +5969,12 @@
         <v>1</v>
       </c>
       <c r="D398">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>ojaimerocha</v>
+        <v>yeslifeacademia</v>
       </c>
       <c r="B399">
         <v>1</v>
@@ -5988,7 +5988,7 @@
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>percepcar</v>
+        <v>ojaimerocha</v>
       </c>
       <c r="B400">
         <v>1</v>
@@ -6002,7 +6002,7 @@
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>edergama.mma</v>
+        <v>percepcar</v>
       </c>
       <c r="B401">
         <v>1</v>
@@ -6016,7 +6016,7 @@
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>eliandropires</v>
+        <v>edergama.mma</v>
       </c>
       <c r="B402">
         <v>1</v>
@@ -6030,7 +6030,7 @@
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>_gabrielpego</v>
+        <v>eliandropires</v>
       </c>
       <c r="B403">
         <v>1</v>
@@ -6044,7 +6044,7 @@
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>motumbo_team</v>
+        <v>_gabrielpego</v>
       </c>
       <c r="B404">
         <v>1</v>
@@ -6058,7 +6058,7 @@
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>eusoufernandosaito</v>
+        <v>motumbo_team</v>
       </c>
       <c r="B405">
         <v>1</v>
@@ -6072,7 +6072,7 @@
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>jenifer.ciborg</v>
+        <v>eusoufernandosaito</v>
       </c>
       <c r="B406">
         <v>1</v>
@@ -6086,7 +6086,7 @@
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>beabmendes_</v>
+        <v>jenifer.ciborg</v>
       </c>
       <c r="B407">
         <v>1</v>
@@ -6100,7 +6100,7 @@
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>felipefrancoufc</v>
+        <v>beabmendes_</v>
       </c>
       <c r="B408">
         <v>1</v>
@@ -6114,7 +6114,7 @@
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>leonardoo_paixao</v>
+        <v>felipefrancoufc</v>
       </c>
       <c r="B409">
         <v>1</v>
@@ -6128,35 +6128,35 @@
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>antonioemanuel.13</v>
+        <v>leonardoo_paixao</v>
       </c>
       <c r="B410">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C410">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D410">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>gasparjr1983</v>
+        <v>antonioemanuel.13</v>
       </c>
       <c r="B411">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C411">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D411">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>magnoddias</v>
+        <v>gasparjr1983</v>
       </c>
       <c r="B412">
         <v>1</v>
@@ -6170,7 +6170,7 @@
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>ballestarbosa</v>
+        <v>magnoddias</v>
       </c>
       <c r="B413">
         <v>1</v>
@@ -6184,7 +6184,7 @@
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>marcioticotobarbosa</v>
+        <v>ballestarbosa</v>
       </c>
       <c r="B414">
         <v>1</v>
@@ -6198,7 +6198,7 @@
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>renan.dniz</v>
+        <v>marcioticotobarbosa</v>
       </c>
       <c r="B415">
         <v>1</v>
@@ -6212,7 +6212,7 @@
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>nunesjanjacomo</v>
+        <v>renan.dniz</v>
       </c>
       <c r="B416">
         <v>1</v>
@@ -6226,7 +6226,7 @@
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>eumarianojr</v>
+        <v>nunesjanjacomo</v>
       </c>
       <c r="B417">
         <v>1</v>
@@ -6240,7 +6240,7 @@
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>mmapalpitex</v>
+        <v>eumarianojr</v>
       </c>
       <c r="B418">
         <v>1</v>
@@ -6254,7 +6254,7 @@
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>george.laroque</v>
+        <v>mmapalpitex</v>
       </c>
       <c r="B419">
         <v>1</v>
@@ -6268,7 +6268,7 @@
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>chillyfit007</v>
+        <v>george.laroque</v>
       </c>
       <c r="B420">
         <v>1</v>
@@ -6282,7 +6282,7 @@
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>cassiosants__</v>
+        <v>chillyfit007</v>
       </c>
       <c r="B421">
         <v>1</v>
@@ -6296,13 +6296,13 @@
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>rafaela_duaartee</v>
+        <v>cassiosants__</v>
       </c>
       <c r="B422">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C422">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D422">
         <v>0</v>
@@ -6310,13 +6310,13 @@
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>wagner_alexandre_w_a</v>
+        <v>rafaela_duaartee</v>
       </c>
       <c r="B423">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C423">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D423">
         <v>0</v>
@@ -6324,7 +6324,7 @@
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>andre.legendre.10</v>
+        <v>wagner_alexandre_w_a</v>
       </c>
       <c r="B424">
         <v>1</v>
@@ -6338,7 +6338,7 @@
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>phillipe.harry</v>
+        <v>andre.legendre.10</v>
       </c>
       <c r="B425">
         <v>1</v>
@@ -6352,7 +6352,7 @@
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>andrejetx</v>
+        <v>phillipe.harry</v>
       </c>
       <c r="B426">
         <v>1</v>
@@ -6366,7 +6366,7 @@
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>leandro_motiv4</v>
+        <v>andrejetx</v>
       </c>
       <c r="B427">
         <v>1</v>
@@ -6380,7 +6380,7 @@
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>olga.oliveira013</v>
+        <v>leandro_motiv4</v>
       </c>
       <c r="B428">
         <v>1</v>
@@ -6394,7 +6394,7 @@
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>vinyrodriguesoficial</v>
+        <v>olga.oliveira013</v>
       </c>
       <c r="B429">
         <v>1</v>
@@ -6408,7 +6408,7 @@
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>leosacraa</v>
+        <v>vinyrodriguesoficial</v>
       </c>
       <c r="B430">
         <v>1</v>
@@ -6422,7 +6422,7 @@
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>gutocriativo</v>
+        <v>leosacraa</v>
       </c>
       <c r="B431">
         <v>1</v>
@@ -6436,7 +6436,7 @@
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>igorfso_</v>
+        <v>gutocriativo</v>
       </c>
       <c r="B432">
         <v>1</v>
@@ -6450,7 +6450,7 @@
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>gabrielsilva_mma</v>
+        <v>igorfso_</v>
       </c>
       <c r="B433">
         <v>1</v>
@@ -6464,7 +6464,7 @@
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>lay_roqs</v>
+        <v>gabrielsilva_mma</v>
       </c>
       <c r="B434">
         <v>1</v>
@@ -6478,7 +6478,7 @@
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>bigjota.music</v>
+        <v>lay_roqs</v>
       </c>
       <c r="B435">
         <v>1</v>
@@ -6492,7 +6492,7 @@
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>jhoninhaoficial031</v>
+        <v>bigjota.music</v>
       </c>
       <c r="B436">
         <v>1</v>
@@ -6506,7 +6506,7 @@
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>mth_fernandes031</v>
+        <v>jhoninhaoficial031</v>
       </c>
       <c r="B437">
         <v>1</v>
@@ -6520,7 +6520,7 @@
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>cezary_oleksiejczuk</v>
+        <v>mth_fernandes031</v>
       </c>
       <c r="B438">
         <v>1</v>
@@ -6534,7 +6534,7 @@
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>_alcantara.bru</v>
+        <v>cezary_oleksiejczuk</v>
       </c>
       <c r="B439">
         <v>1</v>
@@ -6548,7 +6548,7 @@
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>_puroosso88</v>
+        <v>_alcantara.bru</v>
       </c>
       <c r="B440">
         <v>1</v>
@@ -6562,7 +6562,7 @@
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>_rayysp</v>
+        <v>_puroosso88</v>
       </c>
       <c r="B441">
         <v>1</v>
@@ -6576,7 +6576,7 @@
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>cami.terra_</v>
+        <v>_rayysp</v>
       </c>
       <c r="B442">
         <v>1</v>
@@ -6590,7 +6590,7 @@
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>gabicardoson</v>
+        <v>cami.terra_</v>
       </c>
       <c r="B443">
         <v>1</v>
@@ -6604,7 +6604,7 @@
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>pietroshz</v>
+        <v>gabicardoson</v>
       </c>
       <c r="B444">
         <v>1</v>
@@ -6618,7 +6618,7 @@
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>___neller</v>
+        <v>pietroshz</v>
       </c>
       <c r="B445">
         <v>1</v>
@@ -6632,7 +6632,7 @@
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>guilhermeefelix__</v>
+        <v>___neller</v>
       </c>
       <c r="B446">
         <v>1</v>
@@ -6646,7 +6646,7 @@
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>pativinisf</v>
+        <v>guilhermeefelix__</v>
       </c>
       <c r="B447">
         <v>1</v>
@@ -6660,7 +6660,7 @@
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>judadany</v>
+        <v>pativinisf</v>
       </c>
       <c r="B448">
         <v>1</v>
@@ -6674,7 +6674,7 @@
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>andre_alcausa</v>
+        <v>judadany</v>
       </c>
       <c r="B449">
         <v>1</v>
@@ -6688,7 +6688,7 @@
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>_fernunes</v>
+        <v>andre_alcausa</v>
       </c>
       <c r="B450">
         <v>1</v>
@@ -6702,7 +6702,7 @@
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>aloirmarcal</v>
+        <v>_fernunes</v>
       </c>
       <c r="B451">
         <v>1</v>
@@ -6716,7 +6716,7 @@
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>gilberto_7606</v>
+        <v>aloirmarcal</v>
       </c>
       <c r="B452">
         <v>1</v>
@@ -6730,7 +6730,7 @@
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>flazuera14</v>
+        <v>gilberto_7606</v>
       </c>
       <c r="B453">
         <v>1</v>
@@ -6744,7 +6744,7 @@
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>camii_bonfim</v>
+        <v>flazuera14</v>
       </c>
       <c r="B454">
         <v>1</v>
@@ -6758,7 +6758,7 @@
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>danlouiz.jj</v>
+        <v>camii_bonfim</v>
       </c>
       <c r="B455">
         <v>1</v>
@@ -6772,7 +6772,7 @@
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>gabriel_trevelin</v>
+        <v>danlouiz.jj</v>
       </c>
       <c r="B456">
         <v>1</v>
@@ -6786,7 +6786,7 @@
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>_lsanchess_</v>
+        <v>gabriel_trevelin</v>
       </c>
       <c r="B457">
         <v>1</v>
@@ -6800,7 +6800,7 @@
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>mr__rlk01</v>
+        <v>_lsanchess_</v>
       </c>
       <c r="B458">
         <v>1</v>
@@ -6814,7 +6814,7 @@
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>vitor_buck</v>
+        <v>mr__rlk01</v>
       </c>
       <c r="B459">
         <v>1</v>
@@ -6828,7 +6828,7 @@
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>fran.ruys</v>
+        <v>vitor_buck</v>
       </c>
       <c r="B460">
         <v>1</v>
@@ -6842,7 +6842,7 @@
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>arthurhenrique.sx</v>
+        <v>fran.ruys</v>
       </c>
       <c r="B461">
         <v>1</v>
@@ -6856,7 +6856,7 @@
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>draanapaulaponceano</v>
+        <v>arthurhenrique.sx</v>
       </c>
       <c r="B462">
         <v>1</v>
@@ -6870,7 +6870,7 @@
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>saj_photo_miami</v>
+        <v>draanapaulaponceano</v>
       </c>
       <c r="B463">
         <v>1</v>
@@ -6884,7 +6884,7 @@
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>alternativaremocoes</v>
+        <v>saj_photo_miami</v>
       </c>
       <c r="B464">
         <v>1</v>
@@ -6898,7 +6898,7 @@
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>benivalentinn</v>
+        <v>alternativaremocoes</v>
       </c>
       <c r="B465">
         <v>1</v>
@@ -6912,7 +6912,7 @@
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>miguelrodriguesbjj</v>
+        <v>benivalentinn</v>
       </c>
       <c r="B466">
         <v>1</v>
@@ -6926,7 +6926,7 @@
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>navarro_9430</v>
+        <v>miguelrodriguesbjj</v>
       </c>
       <c r="B467">
         <v>1</v>
@@ -6940,7 +6940,7 @@
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>charlesanthony2466</v>
+        <v>navarro_9430</v>
       </c>
       <c r="B468">
         <v>1</v>
@@ -6954,7 +6954,7 @@
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>xavyeroficial</v>
+        <v>charlesanthony2466</v>
       </c>
       <c r="B469">
         <v>1</v>
@@ -6968,7 +6968,7 @@
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>maryanagandra</v>
+        <v>xavyeroficial</v>
       </c>
       <c r="B470">
         <v>1</v>
@@ -6982,7 +6982,7 @@
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>katiaecarreraf</v>
+        <v>maryanagandra</v>
       </c>
       <c r="B471">
         <v>1</v>
@@ -6996,7 +6996,7 @@
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>geraldocnetomma</v>
+        <v>katiaecarreraf</v>
       </c>
       <c r="B472">
         <v>1</v>
@@ -7010,13 +7010,13 @@
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>marinealcausa</v>
+        <v>geraldocnetomma</v>
       </c>
       <c r="B473">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C473">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D473">
         <v>0</v>
@@ -7024,13 +7024,13 @@
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>artemio_bjj</v>
+        <v>marinealcausa</v>
       </c>
       <c r="B474">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C474">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D474">
         <v>0</v>
@@ -7038,7 +7038,7 @@
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>carolinne.xwp</v>
+        <v>artemio_bjj</v>
       </c>
       <c r="B475">
         <v>1</v>
@@ -7052,7 +7052,7 @@
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>isaac.bah_starinazzo</v>
+        <v>carolinne.xwp</v>
       </c>
       <c r="B476">
         <v>1</v>
@@ -7066,7 +7066,7 @@
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>lara.rpr</v>
+        <v>isaac.bah_starinazzo</v>
       </c>
       <c r="B477">
         <v>1</v>
@@ -7080,7 +7080,7 @@
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>codasqueves</v>
+        <v>lara.rpr</v>
       </c>
       <c r="B478">
         <v>1</v>
@@ -7094,7 +7094,7 @@
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>yan_touro_.7766</v>
+        <v>codasqueves</v>
       </c>
       <c r="B479">
         <v>1</v>
@@ -7108,7 +7108,7 @@
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>brothers_of_life</v>
+        <v>yan_touro_.7766</v>
       </c>
       <c r="B480">
         <v>1</v>
@@ -7122,7 +7122,7 @@
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>teacherthalesyouplus</v>
+        <v>brothers_of_life</v>
       </c>
       <c r="B481">
         <v>1</v>
@@ -7136,7 +7136,7 @@
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>minotaurinho</v>
+        <v>teacherthalesyouplus</v>
       </c>
       <c r="B482">
         <v>1</v>
@@ -7150,7 +7150,7 @@
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>anahangelica</v>
+        <v>minotaurinho</v>
       </c>
       <c r="B483">
         <v>1</v>
@@ -7164,7 +7164,7 @@
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>frankikolimabjj</v>
+        <v>anahangelica</v>
       </c>
       <c r="B484">
         <v>1</v>
@@ -7178,7 +7178,7 @@
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>tonketjudes</v>
+        <v>frankikolimabjj</v>
       </c>
       <c r="B485">
         <v>1</v>
@@ -7192,7 +7192,7 @@
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>_eliasffx</v>
+        <v>tonketjudes</v>
       </c>
       <c r="B486">
         <v>1</v>
@@ -7206,7 +7206,7 @@
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>pdfiv</v>
+        <v>_eliasffx</v>
       </c>
       <c r="B487">
         <v>1</v>
@@ -7220,7 +7220,7 @@
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>mariaraimundad940</v>
+        <v>pdfiv</v>
       </c>
       <c r="B488">
         <v>1</v>
@@ -7234,7 +7234,7 @@
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>gabesantos.13</v>
+        <v>mariaraimundad940</v>
       </c>
       <c r="B489">
         <v>1</v>
@@ -7248,7 +7248,7 @@
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>euvitormirandaa</v>
+        <v>gabesantos.13</v>
       </c>
       <c r="B490">
         <v>1</v>
@@ -7262,7 +7262,7 @@
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>gandra.julya</v>
+        <v>euvitormirandaa</v>
       </c>
       <c r="B491">
         <v>1</v>
@@ -7276,7 +7276,7 @@
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>espacomarcialino</v>
+        <v>gandra.julya</v>
       </c>
       <c r="B492">
         <v>1</v>
@@ -7290,7 +7290,7 @@
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>azulcapoeirabjj</v>
+        <v>espacomarcialino</v>
       </c>
       <c r="B493">
         <v>1</v>
@@ -7304,7 +7304,7 @@
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>andreiaatleta</v>
+        <v>azulcapoeirabjj</v>
       </c>
       <c r="B494">
         <v>1</v>
@@ -7318,7 +7318,7 @@
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>luhluhm</v>
+        <v>andreiaatleta</v>
       </c>
       <c r="B495">
         <v>1</v>
@@ -7332,7 +7332,7 @@
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>jack_hashimoto</v>
+        <v>luhluhm</v>
       </c>
       <c r="B496">
         <v>1</v>
@@ -7346,7 +7346,7 @@
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>do_caex_wandel</v>
+        <v>jack_hashimoto</v>
       </c>
       <c r="B497">
         <v>1</v>
@@ -7360,7 +7360,7 @@
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>eu_felipe_leite</v>
+        <v>do_caex_wandel</v>
       </c>
       <c r="B498">
         <v>1</v>
@@ -7374,7 +7374,7 @@
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>selma.ribeirotr</v>
+        <v>eu_felipe_leite</v>
       </c>
       <c r="B499">
         <v>1</v>
@@ -7388,7 +7388,7 @@
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>valqsm</v>
+        <v>selma.ribeirotr</v>
       </c>
       <c r="B500">
         <v>1</v>
@@ -7402,7 +7402,7 @@
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>nutrivan.alves</v>
+        <v>valqsm</v>
       </c>
       <c r="B501">
         <v>1</v>
@@ -7416,7 +7416,7 @@
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>allisonestuchi_fisioterapeuta</v>
+        <v>nutrivan.alves</v>
       </c>
       <c r="B502">
         <v>1</v>
@@ -7430,7 +7430,7 @@
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>sidneibabu</v>
+        <v>allisonestuchi_fisioterapeuta</v>
       </c>
       <c r="B503">
         <v>1</v>
@@ -7444,7 +7444,7 @@
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>muriloo__ferreira</v>
+        <v>sidneibabu</v>
       </c>
       <c r="B504">
         <v>1</v>
@@ -7458,7 +7458,7 @@
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>drfelipeoliveira_adv</v>
+        <v>muriloo__ferreira</v>
       </c>
       <c r="B505">
         <v>1</v>
@@ -7472,7 +7472,7 @@
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>turmanmma</v>
+        <v>drfelipeoliveira_adv</v>
       </c>
       <c r="B506">
         <v>1</v>
@@ -7486,7 +7486,7 @@
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>andre_luizdj</v>
+        <v>turmanmma</v>
       </c>
       <c r="B507">
         <v>1</v>
@@ -7500,7 +7500,7 @@
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>lumarasantosjj</v>
+        <v>andre_luizdj</v>
       </c>
       <c r="B508">
         <v>1</v>
@@ -7514,7 +7514,7 @@
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>donrey_42</v>
+        <v>lumarasantosjj</v>
       </c>
       <c r="B509">
         <v>1</v>
@@ -7528,7 +7528,7 @@
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>personalmaju</v>
+        <v>donrey_42</v>
       </c>
       <c r="B510">
         <v>1</v>
@@ -7542,7 +7542,7 @@
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>itsmayraregina</v>
+        <v>personalmaju</v>
       </c>
       <c r="B511">
         <v>1</v>
@@ -7556,7 +7556,7 @@
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>fototatico</v>
+        <v>itsmayraregina</v>
       </c>
       <c r="B512">
         <v>1</v>
@@ -7570,7 +7570,7 @@
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>michel.juliano.barbershop</v>
+        <v>fototatico</v>
       </c>
       <c r="B513">
         <v>1</v>
@@ -7584,7 +7584,7 @@
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>ruperto_696</v>
+        <v>michel.juliano.barbershop</v>
       </c>
       <c r="B514">
         <v>1</v>
@@ -7598,7 +7598,7 @@
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>diegomoisesribeiro</v>
+        <v>ruperto_696</v>
       </c>
       <c r="B515">
         <v>1</v>
@@ -7612,7 +7612,7 @@
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>lucca_bjj_01</v>
+        <v>diegomoisesribeiro</v>
       </c>
       <c r="B516">
         <v>1</v>
@@ -7626,7 +7626,7 @@
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>calebe1000grau</v>
+        <v>lucca_bjj_01</v>
       </c>
       <c r="B517">
         <v>1</v>
@@ -7640,7 +7640,7 @@
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>brunito_bernardo</v>
+        <v>calebe1000grau</v>
       </c>
       <c r="B518">
         <v>1</v>
@@ -7654,7 +7654,7 @@
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>clarianavillasboasoficial</v>
+        <v>brunito_bernardo</v>
       </c>
       <c r="B519">
         <v>1</v>
@@ -7668,7 +7668,7 @@
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>gladyador_do_asa</v>
+        <v>clarianavillasboasoficial</v>
       </c>
       <c r="B520">
         <v>1</v>
@@ -7682,7 +7682,7 @@
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>aureooficial</v>
+        <v>gladyador_do_asa</v>
       </c>
       <c r="B521">
         <v>1</v>
@@ -7696,7 +7696,7 @@
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>williamjanser</v>
+        <v>aureooficial</v>
       </c>
       <c r="B522">
         <v>1</v>
@@ -7710,7 +7710,7 @@
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>jeremyericjacobs</v>
+        <v>williamjanser</v>
       </c>
       <c r="B523">
         <v>1</v>
@@ -7724,7 +7724,7 @@
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>chicinvancity</v>
+        <v>jeremyericjacobs</v>
       </c>
       <c r="B524">
         <v>1</v>
@@ -7738,7 +7738,7 @@
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>susiemelchionda</v>
+        <v>chicinvancity</v>
       </c>
       <c r="B525">
         <v>1</v>
@@ -7752,7 +7752,7 @@
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>satsangbjj</v>
+        <v>susiemelchionda</v>
       </c>
       <c r="B526">
         <v>1</v>
@@ -7766,7 +7766,7 @@
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>gallupistrengthconditioning</v>
+        <v>satsangbjj</v>
       </c>
       <c r="B527">
         <v>1</v>
@@ -7780,7 +7780,7 @@
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>danibastiaan</v>
+        <v>gallupistrengthconditioning</v>
       </c>
       <c r="B528">
         <v>1</v>
@@ -7794,7 +7794,7 @@
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>gilcilenecristina</v>
+        <v>danibastiaan</v>
       </c>
       <c r="B529">
         <v>1</v>
@@ -7808,7 +7808,7 @@
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>andreaapurinaoficial</v>
+        <v>gilcilenecristina</v>
       </c>
       <c r="B530">
         <v>1</v>
@@ -7822,7 +7822,7 @@
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>alehh_novaes</v>
+        <v>andreaapurinaoficial</v>
       </c>
       <c r="B531">
         <v>1</v>
@@ -7836,7 +7836,7 @@
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>franklinamaral</v>
+        <v>alehh_novaes</v>
       </c>
       <c r="B532">
         <v>1</v>
@@ -7850,7 +7850,7 @@
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>valbersonsantoss</v>
+        <v>franklinamaral</v>
       </c>
       <c r="B533">
         <v>1</v>
@@ -7864,7 +7864,7 @@
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>j.borgespz</v>
+        <v>valbersonsantoss</v>
       </c>
       <c r="B534">
         <v>1</v>
@@ -7878,7 +7878,7 @@
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>gpedroza1</v>
+        <v>j.borgespz</v>
       </c>
       <c r="B535">
         <v>1</v>
@@ -7892,7 +7892,7 @@
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>almir_gdf</v>
+        <v>gpedroza1</v>
       </c>
       <c r="B536">
         <v>1</v>
@@ -7906,7 +7906,7 @@
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>renancarlini</v>
+        <v>almir_gdf</v>
       </c>
       <c r="B537">
         <v>1</v>
@@ -7920,7 +7920,7 @@
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>lucaswallaceftt</v>
+        <v>renancarlini</v>
       </c>
       <c r="B538">
         <v>1</v>
@@ -7934,7 +7934,7 @@
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>lilianvillaca_</v>
+        <v>lucaswallaceftt</v>
       </c>
       <c r="B539">
         <v>1</v>
@@ -7948,7 +7948,7 @@
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>jose_carlos_baixote</v>
+        <v>lilianvillaca_</v>
       </c>
       <c r="B540">
         <v>1</v>
@@ -7962,7 +7962,7 @@
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>projeto_amigos_de_ouro</v>
+        <v>jose_carlos_baixote</v>
       </c>
       <c r="B541">
         <v>1</v>
@@ -7976,7 +7976,7 @@
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>gratidao_jesus2026</v>
+        <v>projeto_amigos_de_ouro</v>
       </c>
       <c r="B542">
         <v>1</v>
@@ -7990,7 +7990,7 @@
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>sabe_de_uma_coisa2026</v>
+        <v>gratidao_jesus2026</v>
       </c>
       <c r="B543">
         <v>1</v>
@@ -8004,7 +8004,7 @@
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>alinedoprojeto</v>
+        <v>sabe_de_uma_coisa2026</v>
       </c>
       <c r="B544">
         <v>1</v>
@@ -8018,7 +8018,7 @@
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>dani120690</v>
+        <v>alinedoprojeto</v>
       </c>
       <c r="B545">
         <v>1</v>
@@ -8032,7 +8032,7 @@
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>raonasthai</v>
+        <v>dani120690</v>
       </c>
       <c r="B546">
         <v>1</v>
@@ -8046,7 +8046,7 @@
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>adonaibjj_grip</v>
+        <v>raonasthai</v>
       </c>
       <c r="B547">
         <v>1</v>
@@ -8060,7 +8060,7 @@
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>arturbambam</v>
+        <v>adonaibjj_grip</v>
       </c>
       <c r="B548">
         <v>1</v>
@@ -8074,7 +8074,7 @@
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>cebolajj167</v>
+        <v>arturbambam</v>
       </c>
       <c r="B549">
         <v>1</v>
@@ -8088,7 +8088,7 @@
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>danieljsantoss_</v>
+        <v>cebolajj167</v>
       </c>
       <c r="B550">
         <v>1</v>
@@ -8102,7 +8102,7 @@
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>hermaan10_</v>
+        <v>danieljsantoss_</v>
       </c>
       <c r="B551">
         <v>1</v>
@@ -8116,7 +8116,7 @@
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>markakasocks</v>
+        <v>hermaan10_</v>
       </c>
       <c r="B552">
         <v>1</v>
@@ -8130,7 +8130,7 @@
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>hunter.mccrary</v>
+        <v>markakasocks</v>
       </c>
       <c r="B553">
         <v>1</v>
@@ -8144,7 +8144,7 @@
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>davidpina_047</v>
+        <v>hunter.mccrary</v>
       </c>
       <c r="B554">
         <v>1</v>
@@ -8158,7 +8158,7 @@
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>odivaldo_lobo</v>
+        <v>davidpina_047</v>
       </c>
       <c r="B555">
         <v>1</v>
@@ -8172,7 +8172,7 @@
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>rodrigojansen_</v>
+        <v>odivaldo_lobo</v>
       </c>
       <c r="B556">
         <v>1</v>
@@ -8186,7 +8186,7 @@
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>flavia_gomes_29</v>
+        <v>rodrigojansen_</v>
       </c>
       <c r="B557">
         <v>1</v>
@@ -8200,7 +8200,7 @@
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>pelevermelha.uniformes</v>
+        <v>flavia_gomes_29</v>
       </c>
       <c r="B558">
         <v>1</v>
@@ -8214,7 +8214,7 @@
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>joao_lins_muaythai</v>
+        <v>pelevermelha.uniformes</v>
       </c>
       <c r="B559">
         <v>1</v>
@@ -8228,7 +8228,7 @@
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>omarcotomaz</v>
+        <v>joao_lins_muaythai</v>
       </c>
       <c r="B560">
         <v>1</v>
@@ -8242,7 +8242,7 @@
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>alphavillesup</v>
+        <v>omarcotomaz</v>
       </c>
       <c r="B561">
         <v>1</v>
@@ -8256,7 +8256,7 @@
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>ricieritonan</v>
+        <v>alphavillesup</v>
       </c>
       <c r="B562">
         <v>1</v>
@@ -8270,7 +8270,7 @@
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>lucasampaio</v>
+        <v>ricieritonan</v>
       </c>
       <c r="B563">
         <v>1</v>
@@ -8284,7 +8284,7 @@
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>manmoska</v>
+        <v>lucasampaio</v>
       </c>
       <c r="B564">
         <v>1</v>
@@ -8298,7 +8298,7 @@
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>renatoevangelistaa</v>
+        <v>manmoska</v>
       </c>
       <c r="B565">
         <v>1</v>
@@ -8312,7 +8312,7 @@
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>cassius.paula</v>
+        <v>renatoevangelistaa</v>
       </c>
       <c r="B566">
         <v>1</v>
@@ -8326,7 +8326,7 @@
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>ctt.casaestopteam</v>
+        <v>cassius.paula</v>
       </c>
       <c r="B567">
         <v>1</v>
@@ -8340,7 +8340,7 @@
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>moisespira</v>
+        <v>ctt.casaestopteam</v>
       </c>
       <c r="B568">
         <v>1</v>
@@ -8354,7 +8354,7 @@
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>rodrigolidiosales</v>
+        <v>moisespira</v>
       </c>
       <c r="B569">
         <v>1</v>
@@ -8368,7 +8368,7 @@
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>claudioribeiro_ufc</v>
+        <v>rodrigolidiosales</v>
       </c>
       <c r="B570">
         <v>1</v>
@@ -8382,7 +8382,7 @@
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>marciocatenacci</v>
+        <v>claudioribeiro_ufc</v>
       </c>
       <c r="B571">
         <v>1</v>
@@ -8396,7 +8396,7 @@
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>cristiane.c.santana</v>
+        <v>marciocatenacci</v>
       </c>
       <c r="B572">
         <v>1</v>
@@ -8410,7 +8410,7 @@
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>ariel_alvees</v>
+        <v>cristiane.c.santana</v>
       </c>
       <c r="B573">
         <v>1</v>
@@ -8424,7 +8424,7 @@
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>flahvinhotreinador</v>
+        <v>ariel_alvees</v>
       </c>
       <c r="B574">
         <v>1</v>
@@ -8438,7 +8438,7 @@
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>selma.oscar12</v>
+        <v>flahvinhotreinador</v>
       </c>
       <c r="B575">
         <v>1</v>
@@ -8452,7 +8452,7 @@
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>romulobelarmino</v>
+        <v>selma.oscar12</v>
       </c>
       <c r="B576">
         <v>1</v>
@@ -8466,7 +8466,7 @@
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>alberto_garcia_queiroz_junior</v>
+        <v>romulobelarmino</v>
       </c>
       <c r="B577">
         <v>1</v>
@@ -8480,7 +8480,7 @@
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>isasantos1404</v>
+        <v>alberto_garcia_queiroz_junior</v>
       </c>
       <c r="B578">
         <v>1</v>
@@ -8494,7 +8494,7 @@
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>fernandamourabjj</v>
+        <v>isasantos1404</v>
       </c>
       <c r="B579">
         <v>1</v>
@@ -8508,7 +8508,7 @@
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>larissamartinsbjj</v>
+        <v>fernandamourabjj</v>
       </c>
       <c r="B580">
         <v>1</v>
@@ -8522,7 +8522,7 @@
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>gabrielsoaresbjj</v>
+        <v>larissamartinsbjj</v>
       </c>
       <c r="B581">
         <v>1</v>
@@ -8536,7 +8536,7 @@
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>leitefelippez</v>
+        <v>gabrielsoaresbjj</v>
       </c>
       <c r="B582">
         <v>1</v>
@@ -8550,7 +8550,7 @@
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>israelbahiensebraz</v>
+        <v>leitefelippez</v>
       </c>
       <c r="B583">
         <v>1</v>
@@ -8564,7 +8564,7 @@
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>titosbjj</v>
+        <v>israelbahiensebraz</v>
       </c>
       <c r="B584">
         <v>1</v>
@@ -8578,7 +8578,7 @@
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>aldomanuel1994</v>
+        <v>titosbjj</v>
       </c>
       <c r="B585">
         <v>1</v>
@@ -8592,7 +8592,7 @@
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>x_xpatto</v>
+        <v>aldomanuel1994</v>
       </c>
       <c r="B586">
         <v>1</v>
@@ -8606,7 +8606,7 @@
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>keep.itpushinnn</v>
+        <v>x_xpatto</v>
       </c>
       <c r="B587">
         <v>1</v>
@@ -8620,7 +8620,7 @@
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>johnnydesinfluencer</v>
+        <v>keep.itpushinnn</v>
       </c>
       <c r="B588">
         <v>1</v>
@@ -8634,7 +8634,7 @@
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>ana.cristina.uno</v>
+        <v>johnnydesinfluencer</v>
       </c>
       <c r="B589">
         <v>1</v>
@@ -8648,7 +8648,7 @@
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>pbmoments_</v>
+        <v>ana.cristina.uno</v>
       </c>
       <c r="B590">
         <v>1</v>
@@ -8662,7 +8662,7 @@
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>rick.santosz</v>
+        <v>pbmoments_</v>
       </c>
       <c r="B591">
         <v>1</v>
@@ -8676,7 +8676,7 @@
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>eriikdossantoos</v>
+        <v>rick.santosz</v>
       </c>
       <c r="B592">
         <v>1</v>
@@ -8690,7 +8690,7 @@
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>sp__theus</v>
+        <v>eriikdossantoos</v>
       </c>
       <c r="B593">
         <v>1</v>
@@ -8704,7 +8704,7 @@
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>guihs_cardoso</v>
+        <v>sp__theus</v>
       </c>
       <c r="B594">
         <v>1</v>
@@ -8718,7 +8718,7 @@
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>jeffersonliu2022</v>
+        <v>guihs_cardoso</v>
       </c>
       <c r="B595">
         <v>1</v>
@@ -8732,7 +8732,7 @@
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>pettys2298</v>
+        <v>jeffersonliu2022</v>
       </c>
       <c r="B596">
         <v>1</v>
@@ -8746,7 +8746,7 @@
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>jhonny.2302_aritamma</v>
+        <v>pettys2298</v>
       </c>
       <c r="B597">
         <v>1</v>
@@ -8760,7 +8760,7 @@
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>ph_castroh</v>
+        <v>jhonny.2302_aritamma</v>
       </c>
       <c r="B598">
         <v>1</v>
@@ -8774,7 +8774,7 @@
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>paulokami.mma</v>
+        <v>ph_castroh</v>
       </c>
       <c r="B599">
         <v>1</v>
@@ -8788,7 +8788,7 @@
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>generaldantas</v>
+        <v>paulokami.mma</v>
       </c>
       <c r="B600">
         <v>1</v>
@@ -8802,7 +8802,7 @@
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>gi.liimaa_</v>
+        <v>generaldantas</v>
       </c>
       <c r="B601">
         <v>1</v>
@@ -8816,7 +8816,7 @@
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>_murilo_06</v>
+        <v>gi.liimaa_</v>
       </c>
       <c r="B602">
         <v>1</v>
@@ -8830,7 +8830,7 @@
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>biabezerra88</v>
+        <v>_murilo_06</v>
       </c>
       <c r="B603">
         <v>1</v>
@@ -8844,7 +8844,7 @@
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>geovannaalc_</v>
+        <v>biabezerra88</v>
       </c>
       <c r="B604">
         <v>1</v>
@@ -8858,7 +8858,7 @@
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>joselia_1980</v>
+        <v>geovannaalc_</v>
       </c>
       <c r="B605">
         <v>1</v>
@@ -8872,7 +8872,7 @@
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>silva_junior1979</v>
+        <v>joselia_1980</v>
       </c>
       <c r="B606">
         <v>1</v>
@@ -8886,7 +8886,7 @@
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>andreloliva12</v>
+        <v>silva_junior1979</v>
       </c>
       <c r="B607">
         <v>1</v>
@@ -8900,7 +8900,7 @@
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>soniarochaco</v>
+        <v>andreloliva12</v>
       </c>
       <c r="B608">
         <v>1</v>
@@ -8914,7 +8914,7 @@
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>leandro_pedro7</v>
+        <v>soniarochaco</v>
       </c>
       <c r="B609">
         <v>1</v>
@@ -8928,7 +8928,7 @@
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>camillinhamma</v>
+        <v>leandro_pedro7</v>
       </c>
       <c r="B610">
         <v>1</v>
@@ -8942,7 +8942,7 @@
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>martins.rauanee</v>
+        <v>camillinhamma</v>
       </c>
       <c r="B611">
         <v>1</v>
@@ -8956,7 +8956,7 @@
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>ever.soulson</v>
+        <v>martins.rauanee</v>
       </c>
       <c r="B612">
         <v>1</v>
@@ -8970,7 +8970,7 @@
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>mestrevascobento</v>
+        <v>ever.soulson</v>
       </c>
       <c r="B613">
         <v>1</v>
@@ -8984,7 +8984,7 @@
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>bernardocavalcanti1</v>
+        <v>mestrevascobento</v>
       </c>
       <c r="B614">
         <v>1</v>
@@ -8998,7 +8998,7 @@
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>terapeuta_moniquedias</v>
+        <v>bernardocavalcanti1</v>
       </c>
       <c r="B615">
         <v>1</v>
@@ -9012,7 +9012,7 @@
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>santos39roger</v>
+        <v>terapeuta_moniquedias</v>
       </c>
       <c r="B616">
         <v>1</v>
@@ -9026,7 +9026,7 @@
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>dcoops2</v>
+        <v>santos39roger</v>
       </c>
       <c r="B617">
         <v>1</v>
@@ -9040,7 +9040,7 @@
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>ricardosousa811</v>
+        <v>dcoops2</v>
       </c>
       <c r="B618">
         <v>1</v>
@@ -9054,7 +9054,7 @@
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>ludelmaraujo</v>
+        <v>ricardosousa811</v>
       </c>
       <c r="B619">
         <v>1</v>
@@ -9068,7 +9068,7 @@
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>homemdeita</v>
+        <v>ludelmaraujo</v>
       </c>
       <c r="B620">
         <v>1</v>
@@ -9082,7 +9082,7 @@
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>victorxferreira</v>
+        <v>homemdeita</v>
       </c>
       <c r="B621">
         <v>1</v>
@@ -9096,7 +9096,7 @@
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>eimysalazar</v>
+        <v>victorxferreira</v>
       </c>
       <c r="B622">
         <v>1</v>
@@ -9110,7 +9110,7 @@
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>oficialrichardsilva_ice_men</v>
+        <v>eimysalazar</v>
       </c>
       <c r="B623">
         <v>1</v>
@@ -9124,7 +9124,7 @@
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>axiaaly</v>
+        <v>oficialrichardsilva_ice_men</v>
       </c>
       <c r="B624">
         <v>1</v>
@@ -9138,7 +9138,7 @@
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>renatogomes769</v>
+        <v>axiaaly</v>
       </c>
       <c r="B625">
         <v>1</v>
@@ -9152,7 +9152,7 @@
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>adrianoblessed89</v>
+        <v>renatogomes769</v>
       </c>
       <c r="B626">
         <v>1</v>
@@ -9166,7 +9166,7 @@
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>dinhomoraisoficial</v>
+        <v>adrianoblessed89</v>
       </c>
       <c r="B627">
         <v>1</v>
@@ -9180,7 +9180,7 @@
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>santosriveiros18737383</v>
+        <v>dinhomoraisoficial</v>
       </c>
       <c r="B628">
         <v>1</v>
@@ -9194,7 +9194,7 @@
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>sr.dpaula10</v>
+        <v>santosriveiros18737383</v>
       </c>
       <c r="B629">
         <v>1</v>
@@ -9208,7 +9208,7 @@
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>pazzini__</v>
+        <v>sr.dpaula10</v>
       </c>
       <c r="B630">
         <v>1</v>
@@ -9222,7 +9222,7 @@
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>thiagomoisesmma</v>
+        <v>pazzini__</v>
       </c>
       <c r="B631">
         <v>1</v>
@@ -9236,7 +9236,7 @@
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>dobby_1968</v>
+        <v>thiagomoisesmma</v>
       </c>
       <c r="B632">
         <v>1</v>
@@ -9250,7 +9250,7 @@
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>ricardogabriel.sr</v>
+        <v>dobby_1968</v>
       </c>
       <c r="B633">
         <v>1</v>
@@ -9264,7 +9264,7 @@
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>indiopersonalfight</v>
+        <v>ricardogabriel.sr</v>
       </c>
       <c r="B634">
         <v>1</v>
@@ -9278,7 +9278,7 @@
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>_samu35</v>
+        <v>indiopersonalfight</v>
       </c>
       <c r="B635">
         <v>1</v>
@@ -9292,7 +9292,7 @@
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>1felipe.bjj</v>
+        <v>_samu35</v>
       </c>
       <c r="B636">
         <v>1</v>
@@ -9306,7 +9306,7 @@
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>odennismagalhaes</v>
+        <v>1felipe.bjj</v>
       </c>
       <c r="B637">
         <v>1</v>
@@ -9320,7 +9320,7 @@
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>remarchina</v>
+        <v>odennismagalhaes</v>
       </c>
       <c r="B638">
         <v>1</v>
@@ -9334,7 +9334,7 @@
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>blesed578</v>
+        <v>remarchina</v>
       </c>
       <c r="B639">
         <v>1</v>
@@ -9348,7 +9348,7 @@
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>yago_08k</v>
+        <v>blesed578</v>
       </c>
       <c r="B640">
         <v>1</v>
@@ -9362,7 +9362,7 @@
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>maribrittos22</v>
+        <v>yago_08k</v>
       </c>
       <c r="B641">
         <v>1</v>
@@ -9376,7 +9376,7 @@
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>grupoohplanooficial</v>
+        <v>maribrittos22</v>
       </c>
       <c r="B642">
         <v>1</v>
@@ -9390,7 +9390,7 @@
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>rxdi_mns</v>
+        <v>grupoohplanooficial</v>
       </c>
       <c r="B643">
         <v>1</v>
@@ -9404,7 +9404,7 @@
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>almeida_.e7</v>
+        <v>rxdi_mns</v>
       </c>
       <c r="B644">
         <v>1</v>
@@ -9418,7 +9418,7 @@
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>dyrodriguesohplano</v>
+        <v>almeida_.e7</v>
       </c>
       <c r="B645">
         <v>1</v>
@@ -9432,7 +9432,7 @@
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>lucianatpiccelli</v>
+        <v>dyrodriguesohplano</v>
       </c>
       <c r="B646">
         <v>1</v>
@@ -9446,7 +9446,7 @@
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>fe_.faggi</v>
+        <v>lucianatpiccelli</v>
       </c>
       <c r="B647">
         <v>1</v>
@@ -9460,7 +9460,7 @@
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>allves___46</v>
+        <v>fe_.faggi</v>
       </c>
       <c r="B648">
         <v>1</v>
@@ -9474,7 +9474,7 @@
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>ottoniisrael</v>
+        <v>allves___46</v>
       </c>
       <c r="B649">
         <v>1</v>
@@ -9488,7 +9488,7 @@
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>_.carlos.2x._</v>
+        <v>ottoniisrael</v>
       </c>
       <c r="B650">
         <v>1</v>
@@ -9502,7 +9502,7 @@
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>guilherme.duartesilva</v>
+        <v>_.carlos.2x._</v>
       </c>
       <c r="B651">
         <v>1</v>
@@ -9516,7 +9516,7 @@
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>davi.cb</v>
+        <v>guilherme.duartesilva</v>
       </c>
       <c r="B652">
         <v>1</v>
@@ -9530,7 +9530,7 @@
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>abbasrizvi2204</v>
+        <v>davi.cb</v>
       </c>
       <c r="B653">
         <v>1</v>
@@ -9544,7 +9544,7 @@
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>nulife2day</v>
+        <v>abbasrizvi2204</v>
       </c>
       <c r="B654">
         <v>1</v>
@@ -9558,7 +9558,7 @@
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>elnaggar_85</v>
+        <v>nulife2day</v>
       </c>
       <c r="B655">
         <v>1</v>
@@ -9572,7 +9572,7 @@
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>bammer2026</v>
+        <v>elnaggar_85</v>
       </c>
       <c r="B656">
         <v>1</v>
@@ -9586,7 +9586,7 @@
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>yon0sab0</v>
+        <v>bammer2026</v>
       </c>
       <c r="B657">
         <v>1</v>
@@ -9600,7 +9600,7 @@
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>thizzlenik</v>
+        <v>yon0sab0</v>
       </c>
       <c r="B658">
         <v>1</v>
@@ -9614,7 +9614,7 @@
     </row>
     <row r="659">
       <c r="A659" t="str">
-        <v>dogodoy</v>
+        <v>thizzlenik</v>
       </c>
       <c r="B659">
         <v>1</v>
@@ -9628,7 +9628,7 @@
     </row>
     <row r="660">
       <c r="A660" t="str">
-        <v>cinemarianophoto</v>
+        <v>dogodoy</v>
       </c>
       <c r="B660">
         <v>1</v>
@@ -9642,7 +9642,7 @@
     </row>
     <row r="661">
       <c r="A661" t="str">
-        <v>nati.monteiro</v>
+        <v>cinemarianophoto</v>
       </c>
       <c r="B661">
         <v>1</v>
@@ -9656,7 +9656,7 @@
     </row>
     <row r="662">
       <c r="A662" t="str">
-        <v>boeno_rafael</v>
+        <v>nati.monteiro</v>
       </c>
       <c r="B662">
         <v>1</v>
@@ -9670,7 +9670,7 @@
     </row>
     <row r="663">
       <c r="A663" t="str">
-        <v>claudio_tikar</v>
+        <v>boeno_rafael</v>
       </c>
       <c r="B663">
         <v>1</v>
@@ -9684,7 +9684,7 @@
     </row>
     <row r="664">
       <c r="A664" t="str">
-        <v>mauricio_dutra_m</v>
+        <v>claudio_tikar</v>
       </c>
       <c r="B664">
         <v>1</v>
@@ -9698,7 +9698,7 @@
     </row>
     <row r="665">
       <c r="A665" t="str">
-        <v>s_giofe</v>
+        <v>mauricio_dutra_m</v>
       </c>
       <c r="B665">
         <v>1</v>
@@ -9712,7 +9712,7 @@
     </row>
     <row r="666">
       <c r="A666" t="str">
-        <v>1tiagomonteiro</v>
+        <v>s_giofe</v>
       </c>
       <c r="B666">
         <v>1</v>
@@ -9726,7 +9726,7 @@
     </row>
     <row r="667">
       <c r="A667" t="str">
-        <v>nautinhor7</v>
+        <v>1tiagomonteiro</v>
       </c>
       <c r="B667">
         <v>1</v>
@@ -9740,7 +9740,7 @@
     </row>
     <row r="668">
       <c r="A668" t="str">
-        <v>lucaspaes047</v>
+        <v>nautinhor7</v>
       </c>
       <c r="B668">
         <v>1</v>
@@ -9754,7 +9754,7 @@
     </row>
     <row r="669">
       <c r="A669" t="str">
-        <v>bmarinhorogerio</v>
+        <v>lucaspaes047</v>
       </c>
       <c r="B669">
         <v>1</v>
@@ -9768,7 +9768,7 @@
     </row>
     <row r="670">
       <c r="A670" t="str">
-        <v>klaiver.027xx</v>
+        <v>bmarinhorogerio</v>
       </c>
       <c r="B670">
         <v>1</v>
@@ -9782,7 +9782,7 @@
     </row>
     <row r="671">
       <c r="A671" t="str">
-        <v>jefte_jizreel</v>
+        <v>klaiver.027xx</v>
       </c>
       <c r="B671">
         <v>1</v>
@@ -9796,7 +9796,7 @@
     </row>
     <row r="672">
       <c r="A672" t="str">
-        <v>clinicaikiro</v>
+        <v>jefte_jizreel</v>
       </c>
       <c r="B672">
         <v>1</v>
@@ -9810,7 +9810,7 @@
     </row>
     <row r="673">
       <c r="A673" t="str">
-        <v>cabreuvamma</v>
+        <v>clinicaikiro</v>
       </c>
       <c r="B673">
         <v>1</v>
@@ -9824,7 +9824,7 @@
     </row>
     <row r="674">
       <c r="A674" t="str">
-        <v>use.ellasfit</v>
+        <v>cabreuvamma</v>
       </c>
       <c r="B674">
         <v>1</v>
@@ -9838,7 +9838,7 @@
     </row>
     <row r="675">
       <c r="A675" t="str">
-        <v>patriciarichteroficial</v>
+        <v>use.ellasfit</v>
       </c>
       <c r="B675">
         <v>1</v>
@@ -9852,7 +9852,7 @@
     </row>
     <row r="676">
       <c r="A676" t="str">
-        <v>kauan_mantas</v>
+        <v>patriciarichteroficial</v>
       </c>
       <c r="B676">
         <v>1</v>
@@ -9866,7 +9866,7 @@
     </row>
     <row r="677">
       <c r="A677" t="str">
-        <v>emersonapache</v>
+        <v>kauan_mantas</v>
       </c>
       <c r="B677">
         <v>1</v>
@@ -9880,7 +9880,7 @@
     </row>
     <row r="678">
       <c r="A678" t="str">
-        <v>nataliavidal965</v>
+        <v>emersonapache</v>
       </c>
       <c r="B678">
         <v>1</v>
@@ -9894,7 +9894,7 @@
     </row>
     <row r="679">
       <c r="A679" t="str">
-        <v>ruanpantojanutricionista</v>
+        <v>nataliavidal965</v>
       </c>
       <c r="B679">
         <v>1</v>
@@ -9908,7 +9908,7 @@
     </row>
     <row r="680">
       <c r="A680" t="str">
-        <v>luizpaulomma</v>
+        <v>ruanpantojanutricionista</v>
       </c>
       <c r="B680">
         <v>1</v>
@@ -9922,7 +9922,7 @@
     </row>
     <row r="681">
       <c r="A681" t="str">
-        <v>epicjoel2022</v>
+        <v>luizpaulomma</v>
       </c>
       <c r="B681">
         <v>1</v>
@@ -9936,7 +9936,7 @@
     </row>
     <row r="682">
       <c r="A682" t="str">
-        <v>tvlinsoficial</v>
+        <v>epicjoel2022</v>
       </c>
       <c r="B682">
         <v>1</v>
@@ -9950,7 +9950,7 @@
     </row>
     <row r="683">
       <c r="A683" t="str">
-        <v>_itamar_maximo</v>
+        <v>tvlinsoficial</v>
       </c>
       <c r="B683">
         <v>1</v>
@@ -9964,7 +9964,7 @@
     </row>
     <row r="684">
       <c r="A684" t="str">
-        <v>mg._silvaa_</v>
+        <v>_itamar_maximo</v>
       </c>
       <c r="B684">
         <v>1</v>
@@ -9978,7 +9978,7 @@
     </row>
     <row r="685">
       <c r="A685" t="str">
-        <v>desativado_no_off33</v>
+        <v>mg._silvaa_</v>
       </c>
       <c r="B685">
         <v>1</v>
@@ -9992,35 +9992,35 @@
     </row>
     <row r="686">
       <c r="A686" t="str">
-        <v>lucasbaddoure</v>
+        <v>desativado_no_off33</v>
       </c>
       <c r="B686">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C686">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D686">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="str">
-        <v>paulo_rafa_personal</v>
+        <v>lucasbaddoure</v>
       </c>
       <c r="B687">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C687">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D687">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="str">
-        <v>endurance_guia</v>
+        <v>paulo_rafa_personal</v>
       </c>
       <c r="B688">
         <v>1</v>
@@ -10034,7 +10034,7 @@
     </row>
     <row r="689">
       <c r="A689" t="str">
-        <v>cadupereirss</v>
+        <v>endurance_guia</v>
       </c>
       <c r="B689">
         <v>1</v>
@@ -10048,7 +10048,7 @@
     </row>
     <row r="690">
       <c r="A690" t="str">
-        <v>instrutorindiovs</v>
+        <v>cadupereirss</v>
       </c>
       <c r="B690">
         <v>1</v>
@@ -10062,7 +10062,7 @@
     </row>
     <row r="691">
       <c r="A691" t="str">
-        <v>lopes.felipe13</v>
+        <v>instrutorindiovs</v>
       </c>
       <c r="B691">
         <v>1</v>
@@ -10076,7 +10076,7 @@
     </row>
     <row r="692">
       <c r="A692" t="str">
-        <v>marchi_vinicius</v>
+        <v>lopes.felipe13</v>
       </c>
       <c r="B692">
         <v>1</v>
@@ -10090,7 +10090,7 @@
     </row>
     <row r="693">
       <c r="A693" t="str">
-        <v>rafa_speda</v>
+        <v>marchi_vinicius</v>
       </c>
       <c r="B693">
         <v>1</v>
@@ -10104,7 +10104,7 @@
     </row>
     <row r="694">
       <c r="A694" t="str">
-        <v>m1guelmolina</v>
+        <v>rafa_speda</v>
       </c>
       <c r="B694">
         <v>1</v>
@@ -10118,7 +10118,7 @@
     </row>
     <row r="695">
       <c r="A695" t="str">
-        <v>rosantos83</v>
+        <v>m1guelmolina</v>
       </c>
       <c r="B695">
         <v>1</v>
@@ -10132,7 +10132,7 @@
     </row>
     <row r="696">
       <c r="A696" t="str">
-        <v>caiogoularts</v>
+        <v>rosantos83</v>
       </c>
       <c r="B696">
         <v>1</v>
@@ -10146,7 +10146,7 @@
     </row>
     <row r="697">
       <c r="A697" t="str">
-        <v>cassiolee013</v>
+        <v>caiogoularts</v>
       </c>
       <c r="B697">
         <v>1</v>
@@ -10160,7 +10160,7 @@
     </row>
     <row r="698">
       <c r="A698" t="str">
-        <v>alinefurlann</v>
+        <v>cassiolee013</v>
       </c>
       <c r="B698">
         <v>1</v>
@@ -10174,7 +10174,7 @@
     </row>
     <row r="699">
       <c r="A699" t="str">
-        <v>programaparadois</v>
+        <v>alinefurlann</v>
       </c>
       <c r="B699">
         <v>1</v>
@@ -10188,7 +10188,7 @@
     </row>
     <row r="700">
       <c r="A700" t="str">
-        <v>cotty_bigmonster</v>
+        <v>programaparadois</v>
       </c>
       <c r="B700">
         <v>1</v>
@@ -10202,7 +10202,7 @@
     </row>
     <row r="701">
       <c r="A701" t="str">
-        <v>alissonlayza</v>
+        <v>cotty_bigmonster</v>
       </c>
       <c r="B701">
         <v>1</v>
@@ -10216,7 +10216,7 @@
     </row>
     <row r="702">
       <c r="A702" t="str">
-        <v>perninhakickboxing</v>
+        <v>alissonlayza</v>
       </c>
       <c r="B702">
         <v>1</v>
@@ -10230,7 +10230,7 @@
     </row>
     <row r="703">
       <c r="A703" t="str">
-        <v>rodrigo.nsx</v>
+        <v>perninhakickboxing</v>
       </c>
       <c r="B703">
         <v>1</v>
@@ -10244,7 +10244,7 @@
     </row>
     <row r="704">
       <c r="A704" t="str">
-        <v>_hygor.soares</v>
+        <v>rodrigo.nsx</v>
       </c>
       <c r="B704">
         <v>1</v>
@@ -10258,7 +10258,7 @@
     </row>
     <row r="705">
       <c r="A705" t="str">
-        <v>enzorkbjj</v>
+        <v>_hygor.soares</v>
       </c>
       <c r="B705">
         <v>1</v>
@@ -10272,7 +10272,7 @@
     </row>
     <row r="706">
       <c r="A706" t="str">
-        <v>lorenzojjts</v>
+        <v>enzorkbjj</v>
       </c>
       <c r="B706">
         <v>1</v>
@@ -10286,7 +10286,7 @@
     </row>
     <row r="707">
       <c r="A707" t="str">
-        <v>i_am_mauispunjahchick</v>
+        <v>lorenzojjts</v>
       </c>
       <c r="B707">
         <v>1</v>
@@ -10300,7 +10300,7 @@
     </row>
     <row r="708">
       <c r="A708" t="str">
-        <v>808.chaz</v>
+        <v>i_am_mauispunjahchick</v>
       </c>
       <c r="B708">
         <v>1</v>
@@ -10314,7 +10314,7 @@
     </row>
     <row r="709">
       <c r="A709" t="str">
-        <v>k_costa68</v>
+        <v>808.chaz</v>
       </c>
       <c r="B709">
         <v>1</v>
@@ -10328,7 +10328,7 @@
     </row>
     <row r="710">
       <c r="A710" t="str">
-        <v>leomvgomes</v>
+        <v>k_costa68</v>
       </c>
       <c r="B710">
         <v>1</v>
@@ -10342,35 +10342,35 @@
     </row>
     <row r="711">
       <c r="A711" t="str">
-        <v>luizcosta_mma</v>
+        <v>leomvgomes</v>
       </c>
       <c r="B711">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C711">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D711">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="712">
       <c r="A712" t="str">
-        <v>taylor_71kg</v>
+        <v>luizcosta_mma</v>
       </c>
       <c r="B712">
         <v>0</v>
       </c>
       <c r="C712">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D712">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="713">
       <c r="A713" t="str">
-        <v>_vpft</v>
+        <v>taylor_71kg</v>
       </c>
       <c r="B713">
         <v>0</v>
@@ -10384,21 +10384,21 @@
     </row>
     <row r="714">
       <c r="A714" t="str">
-        <v>viniciustbf</v>
+        <v>_vpft</v>
       </c>
       <c r="B714">
         <v>0</v>
       </c>
       <c r="C714">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D714">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="715">
       <c r="A715" t="str">
-        <v>dayanaa1511</v>
+        <v>viniciustbf</v>
       </c>
       <c r="B715">
         <v>0</v>
@@ -10407,40 +10407,40 @@
         <v>2</v>
       </c>
       <c r="D715">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="716">
       <c r="A716" t="str">
-        <v>danielfranzesilva</v>
+        <v>dayanaa1511</v>
       </c>
       <c r="B716">
         <v>0</v>
       </c>
       <c r="C716">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D716">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="717">
       <c r="A717" t="str">
-        <v>ednilsonkaicai</v>
+        <v>danielfranzesilva</v>
       </c>
       <c r="B717">
         <v>0</v>
       </c>
       <c r="C717">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D717">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="718">
       <c r="A718" t="str">
-        <v>vanessamelomma</v>
+        <v>ednilsonkaicai</v>
       </c>
       <c r="B718">
         <v>0</v>
@@ -10454,21 +10454,21 @@
     </row>
     <row r="719">
       <c r="A719" t="str">
-        <v>michelle_mirele</v>
+        <v>vanessamelomma</v>
       </c>
       <c r="B719">
         <v>0</v>
       </c>
       <c r="C719">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D719">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="720">
       <c r="A720" t="str">
-        <v>geyziellsouza</v>
+        <v>michelle_mirele</v>
       </c>
       <c r="B720">
         <v>0</v>
@@ -10482,21 +10482,21 @@
     </row>
     <row r="721">
       <c r="A721" t="str">
-        <v>guerreirammaofc</v>
+        <v>geyziellsouza</v>
       </c>
       <c r="B721">
         <v>0</v>
       </c>
       <c r="C721">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D721">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="722">
       <c r="A722" t="str">
-        <v>kalaga_vito</v>
+        <v>guerreirammaofc</v>
       </c>
       <c r="B722">
         <v>0</v>
@@ -10510,7 +10510,7 @@
     </row>
     <row r="723">
       <c r="A723" t="str">
-        <v>dudaadantass</v>
+        <v>kalaga_vito</v>
       </c>
       <c r="B723">
         <v>0</v>
@@ -10524,7 +10524,7 @@
     </row>
     <row r="724">
       <c r="A724" t="str">
-        <v>vitorshowman</v>
+        <v>dudaadantass</v>
       </c>
       <c r="B724">
         <v>0</v>
@@ -10533,12 +10533,12 @@
         <v>2</v>
       </c>
       <c r="D724">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="725">
       <c r="A725" t="str">
-        <v>4lissson</v>
+        <v>vitorshowman</v>
       </c>
       <c r="B725">
         <v>0</v>
@@ -10552,21 +10552,21 @@
     </row>
     <row r="726">
       <c r="A726" t="str">
-        <v>danilofernandescf</v>
+        <v>4lissson</v>
       </c>
       <c r="B726">
         <v>0</v>
       </c>
       <c r="C726">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D726">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="727">
       <c r="A727" t="str">
-        <v>bryandazuera</v>
+        <v>danilofernandescf</v>
       </c>
       <c r="B727">
         <v>0</v>
@@ -10580,21 +10580,21 @@
     </row>
     <row r="728">
       <c r="A728" t="str">
-        <v>orlando_alfa09</v>
+        <v>bryandazuera</v>
       </c>
       <c r="B728">
         <v>0</v>
       </c>
       <c r="C728">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D728">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="729">
       <c r="A729" t="str">
-        <v>jhonnatanboxe_</v>
+        <v>orlando_alfa09</v>
       </c>
       <c r="B729">
         <v>0</v>
@@ -10608,7 +10608,7 @@
     </row>
     <row r="730">
       <c r="A730" t="str">
-        <v>manumito.oficial</v>
+        <v>jhonnatanboxe_</v>
       </c>
       <c r="B730">
         <v>0</v>
@@ -10622,63 +10622,63 @@
     </row>
     <row r="731">
       <c r="A731" t="str">
-        <v>coutz11</v>
+        <v>manumito.oficial</v>
       </c>
       <c r="B731">
         <v>0</v>
       </c>
       <c r="C731">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D731">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="732">
       <c r="A732" t="str">
-        <v>eglaudiomma</v>
+        <v>coutz11</v>
       </c>
       <c r="B732">
         <v>0</v>
       </c>
       <c r="C732">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D732">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="733">
       <c r="A733" t="str">
-        <v>lokomemo_protetores</v>
+        <v>eglaudiomma</v>
       </c>
       <c r="B733">
         <v>0</v>
       </c>
       <c r="C733">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D733">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="734">
       <c r="A734" t="str">
-        <v>carlosnoelblack</v>
+        <v>lokomemo_protetores</v>
       </c>
       <c r="B734">
         <v>0</v>
       </c>
       <c r="C734">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D734">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="735">
       <c r="A735" t="str">
-        <v>rafaelcmjj</v>
+        <v>carlosnoelblack</v>
       </c>
       <c r="B735">
         <v>0</v>
@@ -10692,21 +10692,21 @@
     </row>
     <row r="736">
       <c r="A736" t="str">
-        <v>rahikikhalid</v>
+        <v>rafaelcmjj</v>
       </c>
       <c r="B736">
         <v>0</v>
       </c>
       <c r="C736">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D736">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="737">
       <c r="A737" t="str">
-        <v>leonardopateira</v>
+        <v>rahikikhalid</v>
       </c>
       <c r="B737">
         <v>0</v>
@@ -10720,21 +10720,21 @@
     </row>
     <row r="738">
       <c r="A738" t="str">
-        <v>thalytabjj</v>
+        <v>leonardopateira</v>
       </c>
       <c r="B738">
         <v>0</v>
       </c>
       <c r="C738">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D738">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="739">
       <c r="A739" t="str">
-        <v>rafaelantonio.rj</v>
+        <v>thalytabjj</v>
       </c>
       <c r="B739">
         <v>0</v>
@@ -10748,35 +10748,35 @@
     </row>
     <row r="740">
       <c r="A740" t="str">
-        <v>yasminreis_oficiall</v>
+        <v>rafaelantonio.rj</v>
       </c>
       <c r="B740">
         <v>0</v>
       </c>
       <c r="C740">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D740">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="741">
       <c r="A741" t="str">
-        <v>dnoxsport</v>
+        <v>yasminreis_oficiall</v>
       </c>
       <c r="B741">
         <v>0</v>
       </c>
       <c r="C741">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D741">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="742">
       <c r="A742" t="str">
-        <v>armysenju</v>
+        <v>dnoxsport</v>
       </c>
       <c r="B742">
         <v>0</v>
@@ -10790,7 +10790,7 @@
     </row>
     <row r="743">
       <c r="A743" t="str">
-        <v>kamtalksmma</v>
+        <v>armysenju</v>
       </c>
       <c r="B743">
         <v>0</v>
@@ -10804,49 +10804,49 @@
     </row>
     <row r="744">
       <c r="A744" t="str">
-        <v>arleyleboss</v>
+        <v>kamtalksmma</v>
       </c>
       <c r="B744">
         <v>0</v>
       </c>
       <c r="C744">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D744">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="745">
       <c r="A745" t="str">
-        <v>jj_miguel05</v>
+        <v>arleyleboss</v>
       </c>
       <c r="B745">
         <v>0</v>
       </c>
       <c r="C745">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D745">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="746">
       <c r="A746" t="str">
-        <v>dra.izabeldelfino_</v>
+        <v>jj_miguel05</v>
       </c>
       <c r="B746">
         <v>0</v>
       </c>
       <c r="C746">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D746">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="747">
       <c r="A747" t="str">
-        <v>janjaovix</v>
+        <v>dra.izabeldelfino_</v>
       </c>
       <c r="B747">
         <v>0</v>
@@ -10860,7 +10860,7 @@
     </row>
     <row r="748">
       <c r="A748" t="str">
-        <v>joaolucasmma.rocha</v>
+        <v>janjaovix</v>
       </c>
       <c r="B748">
         <v>0</v>
@@ -10874,7 +10874,7 @@
     </row>
     <row r="749">
       <c r="A749" t="str">
-        <v>edsonbahienseb</v>
+        <v>joaolucasmma.rocha</v>
       </c>
       <c r="B749">
         <v>0</v>
@@ -10888,7 +10888,7 @@
     </row>
     <row r="750">
       <c r="A750" t="str">
-        <v>paulomartins.mma</v>
+        <v>edsonbahienseb</v>
       </c>
       <c r="B750">
         <v>0</v>
@@ -10902,27 +10902,27 @@
     </row>
     <row r="751">
       <c r="A751" t="str">
-        <v>daniel_natel</v>
+        <v>paulomartins.mma</v>
       </c>
       <c r="B751">
         <v>0</v>
       </c>
       <c r="C751">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D751">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="752">
       <c r="A752" t="str">
-        <v>dhuks11</v>
+        <v>daniel_natel</v>
       </c>
       <c r="B752">
         <v>0</v>
       </c>
       <c r="C752">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D752">
         <v>0</v>
@@ -10930,7 +10930,7 @@
     </row>
     <row r="753">
       <c r="A753" t="str">
-        <v>macksomlee</v>
+        <v>dhuks11</v>
       </c>
       <c r="B753">
         <v>0</v>
@@ -10939,40 +10939,40 @@
         <v>1</v>
       </c>
       <c r="D753">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="754">
       <c r="A754" t="str">
-        <v>y_nichimura</v>
+        <v>macksomlee</v>
       </c>
       <c r="B754">
         <v>0</v>
       </c>
       <c r="C754">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D754">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="755">
       <c r="A755" t="str">
-        <v>mayconzilli</v>
+        <v>y_nichimura</v>
       </c>
       <c r="B755">
         <v>0</v>
       </c>
       <c r="C755">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D755">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="756">
       <c r="A756" t="str">
-        <v>patascubo</v>
+        <v>mayconzilli</v>
       </c>
       <c r="B756">
         <v>0</v>
@@ -10986,7 +10986,7 @@
     </row>
     <row r="757">
       <c r="A757" t="str">
-        <v>jeffesonmeirelles</v>
+        <v>patascubo</v>
       </c>
       <c r="B757">
         <v>0</v>
@@ -11000,7 +11000,7 @@
     </row>
     <row r="758">
       <c r="A758" t="str">
-        <v>denilson.unit</v>
+        <v>jeffesonmeirelles</v>
       </c>
       <c r="B758">
         <v>0</v>
@@ -11014,7 +11014,7 @@
     </row>
     <row r="759">
       <c r="A759" t="str">
-        <v>vieirabjj____</v>
+        <v>denilson.unit</v>
       </c>
       <c r="B759">
         <v>0</v>
@@ -11028,7 +11028,7 @@
     </row>
     <row r="760">
       <c r="A760" t="str">
-        <v>canalgolpebaixo</v>
+        <v>vieirabjj____</v>
       </c>
       <c r="B760">
         <v>0</v>
@@ -13975,7 +13975,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D75"/>
+  <dimension ref="A1:D78"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -13996,13 +13996,13 @@
         <v>peacegrappler</v>
       </c>
       <c r="B2">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3">
@@ -14010,13 +14010,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
+        <v>26</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
         <v>25</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>24</v>
       </c>
     </row>
     <row r="4">
@@ -14038,13 +14038,13 @@
         <v>kelly_ottoni</v>
       </c>
       <c r="B5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5">
         <v>5</v>
       </c>
       <c r="D5">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -14066,13 +14066,13 @@
         <v>natanborges001</v>
       </c>
       <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
         <v>4</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -14080,10 +14080,10 @@
         <v>washington_cassisno</v>
       </c>
       <c r="B8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D8">
         <v>5</v>
@@ -14469,41 +14469,41 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>adriano.trator</v>
+        <v>canalgolpebaixo</v>
       </c>
       <c r="B36">
         <v>1</v>
       </c>
       <c r="C36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>cassiosants__</v>
+        <v>npb.enterprise</v>
       </c>
       <c r="B37">
         <v>1</v>
       </c>
       <c r="C37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>masonharper_mma</v>
+        <v>adriano.trator</v>
       </c>
       <c r="B38">
         <v>1</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -14511,13 +14511,13 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>johnmma9</v>
+        <v>cassiosants__</v>
       </c>
       <c r="B39">
         <v>1</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D39">
         <v>0</v>
@@ -14525,7 +14525,7 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>mmmarc20</v>
+        <v>masonharper_mma</v>
       </c>
       <c r="B40">
         <v>1</v>
@@ -14539,7 +14539,7 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>pablofiorindi</v>
+        <v>johnmma9</v>
       </c>
       <c r="B41">
         <v>1</v>
@@ -14553,7 +14553,7 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>_jullianadacruz</v>
+        <v>mmmarc20</v>
       </c>
       <c r="B42">
         <v>1</v>
@@ -14567,7 +14567,7 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>erickdiaseds</v>
+        <v>pablofiorindi</v>
       </c>
       <c r="B43">
         <v>1</v>
@@ -14581,7 +14581,7 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>ottonimestre</v>
+        <v>_jullianadacruz</v>
       </c>
       <c r="B44">
         <v>1</v>
@@ -14595,7 +14595,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>adrianoams7</v>
+        <v>erickdiaseds</v>
       </c>
       <c r="B45">
         <v>1</v>
@@ -14609,7 +14609,7 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>_hygor.soares</v>
+        <v>ottonimestre</v>
       </c>
       <c r="B46">
         <v>1</v>
@@ -14623,7 +14623,7 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>enzorkbjj</v>
+        <v>adrianoams7</v>
       </c>
       <c r="B47">
         <v>1</v>
@@ -14637,7 +14637,7 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>emersonriosmma</v>
+        <v>_hygor.soares</v>
       </c>
       <c r="B48">
         <v>1</v>
@@ -14651,7 +14651,7 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>_pedro0h</v>
+        <v>enzorkbjj</v>
       </c>
       <c r="B49">
         <v>1</v>
@@ -14665,7 +14665,7 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>lorenzojjts</v>
+        <v>emersonriosmma</v>
       </c>
       <c r="B50">
         <v>1</v>
@@ -14679,7 +14679,7 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>pauloserrati</v>
+        <v>_pedro0h</v>
       </c>
       <c r="B51">
         <v>1</v>
@@ -14693,7 +14693,7 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>karen.ottoni</v>
+        <v>lorenzojjts</v>
       </c>
       <c r="B52">
         <v>1</v>
@@ -14707,7 +14707,7 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>thiagoauper</v>
+        <v>pauloserrati</v>
       </c>
       <c r="B53">
         <v>1</v>
@@ -14721,7 +14721,7 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>ellen.cristinaaa</v>
+        <v>karen.ottoni</v>
       </c>
       <c r="B54">
         <v>1</v>
@@ -14735,7 +14735,7 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>albertoleandromoco</v>
+        <v>thiagoauper</v>
       </c>
       <c r="B55">
         <v>1</v>
@@ -14749,7 +14749,7 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>god.motivacao</v>
+        <v>ellen.cristinaaa</v>
       </c>
       <c r="B56">
         <v>1</v>
@@ -14763,7 +14763,7 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>jean_ferreira_br</v>
+        <v>albertoleandromoco</v>
       </c>
       <c r="B57">
         <v>1</v>
@@ -14777,7 +14777,7 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>ismaeldaniell</v>
+        <v>god.motivacao</v>
       </c>
       <c r="B58">
         <v>1</v>
@@ -14791,7 +14791,7 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>i_am_mauispunjahchick</v>
+        <v>jean_ferreira_br</v>
       </c>
       <c r="B59">
         <v>1</v>
@@ -14805,7 +14805,7 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>808.chaz</v>
+        <v>ismaeldaniell</v>
       </c>
       <c r="B60">
         <v>1</v>
@@ -14819,7 +14819,7 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>k_costa68</v>
+        <v>i_am_mauispunjahchick</v>
       </c>
       <c r="B61">
         <v>1</v>
@@ -14833,7 +14833,7 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>leomvgomes</v>
+        <v>808.chaz</v>
       </c>
       <c r="B62">
         <v>1</v>
@@ -14847,55 +14847,55 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>leobahiamma</v>
+        <v>k_costa68</v>
       </c>
       <c r="B63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C63">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D63">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>pedro_pavin_</v>
+        <v>leomvgomes</v>
       </c>
       <c r="B64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C64">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D64">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>allan10adm</v>
+        <v>eliassilverio</v>
       </c>
       <c r="B65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D65">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>ismael.marreta_ufc</v>
+        <v>leobahiamma</v>
       </c>
       <c r="B66">
         <v>0</v>
       </c>
       <c r="C66">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D66">
         <v>1</v>
@@ -14903,7 +14903,7 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>joandersontubarao_ufc</v>
+        <v>pedro_pavin_</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -14917,7 +14917,7 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>gaby_alves07</v>
+        <v>allan10adm</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -14931,7 +14931,7 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>diegosilvabjjoficial</v>
+        <v>ismael.marreta_ufc</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -14945,7 +14945,7 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>pulsepro.nutrition</v>
+        <v>joandersontubarao_ufc</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -14954,12 +14954,12 @@
         <v>1</v>
       </c>
       <c r="D70">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>herbeth_indiomma</v>
+        <v>gaby_alves07</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -14968,12 +14968,12 @@
         <v>1</v>
       </c>
       <c r="D71">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>danielbzk_</v>
+        <v>diegosilvabjjoficial</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -14982,12 +14982,12 @@
         <v>1</v>
       </c>
       <c r="D72">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>jp.mdc</v>
+        <v>pulsepro.nutrition</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -15001,7 +15001,7 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>rosacostasousa36</v>
+        <v>herbeth_indiomma</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -15015,21 +15015,63 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
+        <v>danielbzk_</v>
+      </c>
+      <c r="B75">
+        <v>0</v>
+      </c>
+      <c r="C75">
+        <v>1</v>
+      </c>
+      <c r="D75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>jp.mdc</v>
+      </c>
+      <c r="B76">
+        <v>0</v>
+      </c>
+      <c r="C76">
+        <v>1</v>
+      </c>
+      <c r="D76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>rosacostasousa36</v>
+      </c>
+      <c r="B77">
+        <v>0</v>
+      </c>
+      <c r="C77">
+        <v>1</v>
+      </c>
+      <c r="D77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
         <v>cathya_ferreira</v>
       </c>
-      <c r="B75">
-        <v>0</v>
-      </c>
-      <c r="C75">
-        <v>1</v>
-      </c>
-      <c r="D75">
+      <c r="B78">
+        <v>0</v>
+      </c>
+      <c r="C78">
+        <v>1</v>
+      </c>
+      <c r="D78">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D75"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D78"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Engagement Rankings 2026-07.xlsx
+++ b/Engagement Rankings 2026-07.xlsx
@@ -419,13 +419,13 @@
         <v>peacegrappler</v>
       </c>
       <c r="B2">
-        <v>13489</v>
+        <v>13502</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>12214</v>
+        <v>12224</v>
       </c>
     </row>
     <row r="3">
@@ -461,7 +461,7 @@
         <v>enzocardoso.bjj</v>
       </c>
       <c r="B5">
-        <v>2191</v>
+        <v>2192</v>
       </c>
       <c r="C5">
         <v>33</v>
@@ -475,13 +475,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B6">
-        <v>901</v>
+        <v>909</v>
       </c>
       <c r="C6">
         <v>16</v>
       </c>
       <c r="D6">
-        <v>740</v>
+        <v>745</v>
       </c>
     </row>
     <row r="7">
@@ -780,30 +780,30 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>cjrnavalha</v>
+        <v>god.motivacao</v>
       </c>
       <c r="B28">
-        <v>84</v>
+        <v>33</v>
       </c>
       <c r="C28">
-        <v>3</v>
+        <v>212</v>
       </c>
       <c r="D28">
-        <v>16</v>
+        <v>66</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>god.motivacao</v>
+        <v>cjrnavalha</v>
       </c>
       <c r="B29">
-        <v>32</v>
+        <v>84</v>
       </c>
       <c r="C29">
-        <v>212</v>
+        <v>3</v>
       </c>
       <c r="D29">
-        <v>66</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30">
@@ -856,10 +856,10 @@
         <v>41</v>
       </c>
       <c r="C33">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D33">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="34">
@@ -1172,13 +1172,13 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>grapplerfight</v>
+        <v>kelly_ottoni</v>
       </c>
       <c r="B56">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C56">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D56">
         <v>20</v>
@@ -1186,7 +1186,7 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>shawlin13oficial</v>
+        <v>grapplerfight</v>
       </c>
       <c r="B57">
         <v>24</v>
@@ -1195,21 +1195,21 @@
         <v>0</v>
       </c>
       <c r="D57">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>kelly_ottoni</v>
+        <v>shawlin13oficial</v>
       </c>
       <c r="B58">
         <v>24</v>
       </c>
       <c r="C58">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D58">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="59">
@@ -1539,10 +1539,10 @@
         <v>adriano.trator</v>
       </c>
       <c r="B82">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C82">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D82">
         <v>14</v>
@@ -1830,13 +1830,13 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>eolucasrosa</v>
+        <v>ismaeldaniell</v>
       </c>
       <c r="B103">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C103">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D103">
         <v>3</v>
@@ -1844,41 +1844,41 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>diegopaivajj</v>
+        <v>eolucasrosa</v>
       </c>
       <c r="B104">
         <v>9</v>
       </c>
       <c r="C104">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D104">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>anderson.logan.35</v>
+        <v>diegopaivajj</v>
       </c>
       <c r="B105">
         <v>9</v>
       </c>
       <c r="C105">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D105">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>__ottonii__</v>
+        <v>anderson.logan.35</v>
       </c>
       <c r="B106">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C106">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D106">
         <v>3</v>
@@ -1886,7 +1886,7 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>misskelsc</v>
+        <v>__ottonii__</v>
       </c>
       <c r="B107">
         <v>10</v>
@@ -1895,21 +1895,21 @@
         <v>1</v>
       </c>
       <c r="D107">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>ismaeldaniell</v>
+        <v>misskelsc</v>
       </c>
       <c r="B108">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C108">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D108">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109">
@@ -1976,7 +1976,7 @@
         <v>7</v>
       </c>
       <c r="C113">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D113">
         <v>4</v>
@@ -2810,13 +2810,13 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>salost.ofc</v>
+        <v>jean_ferreira_br</v>
       </c>
       <c r="B173">
         <v>5</v>
       </c>
       <c r="C173">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D173">
         <v>0</v>
@@ -2824,49 +2824,49 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>gabrielsouzamma</v>
+        <v>salost.ofc</v>
       </c>
       <c r="B174">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C174">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D174">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>wilson_n_janjacomo</v>
+        <v>gabrielsouzamma</v>
       </c>
       <c r="B175">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C175">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D175">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>helenmacielmma</v>
+        <v>wilson_n_janjacomo</v>
       </c>
       <c r="B176">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C176">
         <v>0</v>
       </c>
       <c r="D176">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>y.arthur_01</v>
+        <v>carlos_hm_iglesias</v>
       </c>
       <c r="B177">
         <v>3</v>
@@ -2875,26 +2875,26 @@
         <v>0</v>
       </c>
       <c r="D177">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>s__simone__</v>
+        <v>helenmacielmma</v>
       </c>
       <c r="B178">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C178">
         <v>0</v>
       </c>
       <c r="D178">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>maxbjj_0</v>
+        <v>y.arthur_01</v>
       </c>
       <c r="B179">
         <v>3</v>
@@ -2908,35 +2908,35 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>vincenzo_pit_monster</v>
+        <v>s__simone__</v>
       </c>
       <c r="B180">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C180">
         <v>0</v>
       </c>
       <c r="D180">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>rian.vitorjj</v>
+        <v>maxbjj_0</v>
       </c>
       <c r="B181">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C181">
         <v>0</v>
       </c>
       <c r="D181">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>lonbradao__777</v>
+        <v>vincenzo_pit_monster</v>
       </c>
       <c r="B182">
         <v>2</v>
@@ -2950,7 +2950,7 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>wesleysepulveda__mma</v>
+        <v>rian.vitorjj</v>
       </c>
       <c r="B183">
         <v>2</v>
@@ -2964,27 +2964,27 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>fabinho_falcao_</v>
+        <v>lonbradao__777</v>
       </c>
       <c r="B184">
         <v>2</v>
       </c>
       <c r="C184">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D184">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>odeivisoncardoso</v>
+        <v>wesleysepulveda__mma</v>
       </c>
       <c r="B185">
         <v>2</v>
       </c>
       <c r="C185">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D185">
         <v>2</v>
@@ -2992,13 +2992,13 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>fabiomarcelinopersonal</v>
+        <v>fabinho_falcao_</v>
       </c>
       <c r="B186">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C186">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D186">
         <v>1</v>
@@ -3006,13 +3006,13 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>peacegrappler_archive</v>
+        <v>odeivisoncardoso</v>
       </c>
       <c r="B187">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C187">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D187">
         <v>2</v>
@@ -3020,41 +3020,41 @@
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>reifernandes</v>
+        <v>fabiomarcelinopersonal</v>
       </c>
       <c r="B188">
         <v>3</v>
       </c>
       <c r="C188">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D188">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>daniel_dias_214</v>
+        <v>peacegrappler_archive</v>
       </c>
       <c r="B189">
         <v>3</v>
       </c>
       <c r="C189">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D189">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>mauriciomouraprev</v>
+        <v>reifernandes</v>
       </c>
       <c r="B190">
         <v>3</v>
       </c>
       <c r="C190">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D190">
         <v>2</v>
@@ -3062,55 +3062,55 @@
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>cristianpsicologo</v>
+        <v>daniel_dias_214</v>
       </c>
       <c r="B191">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C191">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D191">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>mah__vergueiro</v>
+        <v>mauriciomouraprev</v>
       </c>
       <c r="B192">
         <v>3</v>
       </c>
       <c r="C192">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D192">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>pizzaria.bambina_</v>
+        <v>cristianpsicologo</v>
       </c>
       <c r="B193">
+        <v>2</v>
+      </c>
+      <c r="C193">
         <v>4</v>
       </c>
-      <c r="C193">
-        <v>1</v>
-      </c>
       <c r="D193">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>jean_ferreira_br</v>
+        <v>mah__vergueiro</v>
       </c>
       <c r="B194">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C194">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D194">
         <v>0</v>
@@ -3118,49 +3118,49 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>h.codasqueves</v>
+        <v>pizzaria.bambina_</v>
       </c>
       <c r="B195">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C195">
         <v>1</v>
       </c>
       <c r="D195">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>pauloserrati</v>
+        <v>h.codasqueves</v>
       </c>
       <c r="B196">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C196">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D196">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>alexandreconsentino</v>
+        <v>pauloserrati</v>
       </c>
       <c r="B197">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C197">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D197">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>lipe.ftt</v>
+        <v>alexandreconsentino</v>
       </c>
       <c r="B198">
         <v>4</v>
@@ -3174,7 +3174,7 @@
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>fau_gfs</v>
+        <v>lipe.ftt</v>
       </c>
       <c r="B199">
         <v>4</v>
@@ -3188,21 +3188,21 @@
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>vitorpetrino</v>
+        <v>fau_gfs</v>
       </c>
       <c r="B200">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C200">
         <v>0</v>
       </c>
       <c r="D200">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>thompsonborralho</v>
+        <v>vitorpetrino</v>
       </c>
       <c r="B201">
         <v>3</v>
@@ -3216,7 +3216,7 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>devessonjj</v>
+        <v>thompsonborralho</v>
       </c>
       <c r="B202">
         <v>3</v>
@@ -3230,77 +3230,77 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>espaco_jhayoliveira</v>
+        <v>devessonjj</v>
       </c>
       <c r="B203">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C203">
         <v>0</v>
       </c>
       <c r="D203">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>artewebpersonalizados</v>
+        <v>espaco_jhayoliveira</v>
       </c>
       <c r="B204">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C204">
         <v>0</v>
       </c>
       <c r="D204">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>marcosferreira.ofc1</v>
+        <v>artewebpersonalizados</v>
       </c>
       <c r="B205">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C205">
         <v>0</v>
       </c>
       <c r="D205">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>lili.munix</v>
+        <v>marcosferreira.ofc1</v>
       </c>
       <c r="B206">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C206">
         <v>0</v>
       </c>
       <c r="D206">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>carlos_hm_iglesias</v>
+        <v>dgswillian</v>
       </c>
       <c r="B207">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C207">
         <v>0</v>
       </c>
       <c r="D207">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>victorhenriquebjj</v>
+        <v>lili.munix</v>
       </c>
       <c r="B208">
         <v>2</v>
@@ -3309,12 +3309,12 @@
         <v>0</v>
       </c>
       <c r="D208">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>eduardorobjj</v>
+        <v>victorhenriquebjj</v>
       </c>
       <c r="B209">
         <v>2</v>
@@ -3328,7 +3328,7 @@
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>diego.dieguito.3914</v>
+        <v>eduardorobjj</v>
       </c>
       <c r="B210">
         <v>2</v>
@@ -3342,7 +3342,7 @@
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>aerowellsports</v>
+        <v>diego.dieguito.3914</v>
       </c>
       <c r="B211">
         <v>2</v>
@@ -3356,7 +3356,7 @@
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>royrosiano</v>
+        <v>aerowellsports</v>
       </c>
       <c r="B212">
         <v>2</v>
@@ -3370,7 +3370,7 @@
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>febrancatti</v>
+        <v>royrosiano</v>
       </c>
       <c r="B213">
         <v>2</v>
@@ -3384,7 +3384,7 @@
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>sensei_rogerio_baltazar</v>
+        <v>febrancatti</v>
       </c>
       <c r="B214">
         <v>2</v>
@@ -3398,7 +3398,7 @@
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>jpaulo.mma</v>
+        <v>sensei_rogerio_baltazar</v>
       </c>
       <c r="B215">
         <v>2</v>
@@ -3412,7 +3412,7 @@
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>william_beckett12345</v>
+        <v>jpaulo.mma</v>
       </c>
       <c r="B216">
         <v>2</v>
@@ -3426,7 +3426,7 @@
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>_falcao95_</v>
+        <v>william_beckett12345</v>
       </c>
       <c r="B217">
         <v>2</v>
@@ -3440,7 +3440,7 @@
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>janyson.s</v>
+        <v>_falcao95_</v>
       </c>
       <c r="B218">
         <v>2</v>
@@ -3454,7 +3454,7 @@
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>rodrigo.personal.muaythai</v>
+        <v>janyson.s</v>
       </c>
       <c r="B219">
         <v>2</v>
@@ -3468,7 +3468,7 @@
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>andre_cr_daniel</v>
+        <v>rodrigo.personal.muaythai</v>
       </c>
       <c r="B220">
         <v>2</v>
@@ -3482,7 +3482,7 @@
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>wilsinho.campos</v>
+        <v>andre_cr_daniel</v>
       </c>
       <c r="B221">
         <v>2</v>
@@ -3496,7 +3496,7 @@
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>jheffzao</v>
+        <v>wilsinho.campos</v>
       </c>
       <c r="B222">
         <v>2</v>
@@ -3510,55 +3510,55 @@
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>joandersontubarao_ufc</v>
+        <v>jheffzao</v>
       </c>
       <c r="B223">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C223">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D223">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>felipedasilvalucas.bjj</v>
+        <v>joandersontubarao_ufc</v>
       </c>
       <c r="B224">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C224">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D224">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>motumbo_jr</v>
+        <v>felipedasilvalucas.bjj</v>
       </c>
       <c r="B225">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C225">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D225">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>julianoalicate</v>
+        <v>motumbo_jr</v>
       </c>
       <c r="B226">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C226">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D226">
         <v>1</v>
@@ -3566,69 +3566,69 @@
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>canalgolpebaixo</v>
+        <v>julianoalicate</v>
       </c>
       <c r="B227">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C227">
         <v>1</v>
       </c>
       <c r="D227">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>cairorochamma</v>
+        <v>canalgolpebaixo</v>
       </c>
       <c r="B228">
         <v>2</v>
       </c>
       <c r="C228">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D228">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>victus_torquatus</v>
+        <v>cairorochamma</v>
       </c>
       <c r="B229">
         <v>2</v>
       </c>
       <c r="C229">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D229">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>alexsandra_kairos</v>
+        <v>victus_torquatus</v>
       </c>
       <c r="B230">
         <v>2</v>
       </c>
       <c r="C230">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D230">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>tuizainocenciorodrigues</v>
+        <v>alexsandra_kairos</v>
       </c>
       <c r="B231">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C231">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D231">
         <v>0</v>
@@ -3636,7 +3636,7 @@
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>jocyrefan_bjj_mma</v>
+        <v>tuizainocenciorodrigues</v>
       </c>
       <c r="B232">
         <v>3</v>
@@ -3650,7 +3650,7 @@
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>multiplicaaba</v>
+        <v>jocyrefan_bjj_mma</v>
       </c>
       <c r="B233">
         <v>3</v>
@@ -3664,13 +3664,13 @@
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>disk_egg</v>
+        <v>multiplicaaba</v>
       </c>
       <c r="B234">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C234">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D234">
         <v>0</v>
@@ -3678,52 +3678,52 @@
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>jose_luiz_thome</v>
+        <v>disk_egg</v>
       </c>
       <c r="B235">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C235">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D235">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>efsantos.oficial</v>
+        <v>jose_luiz_thome</v>
       </c>
       <c r="B236">
         <v>1</v>
       </c>
       <c r="C236">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D236">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>ufc_paramountsports</v>
+        <v>efsantos.oficial</v>
       </c>
       <c r="B237">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C237">
         <v>1</v>
       </c>
       <c r="D237">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>marifferreirac</v>
+        <v>ufc_paramountsports</v>
       </c>
       <c r="B238">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C238">
         <v>1</v>
@@ -3734,13 +3734,13 @@
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>mineirinho_jj</v>
+        <v>marifferreirac</v>
       </c>
       <c r="B239">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C239">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D239">
         <v>1</v>
@@ -3748,7 +3748,7 @@
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>juliochagasmma</v>
+        <v>mineirinho_jj</v>
       </c>
       <c r="B240">
         <v>2</v>
@@ -3762,35 +3762,35 @@
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>orafao1</v>
+        <v>juliochagasmma</v>
       </c>
       <c r="B241">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C241">
         <v>0</v>
       </c>
       <c r="D241">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>lopesbrunao</v>
+        <v>orafao1</v>
       </c>
       <c r="B242">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C242">
         <v>0</v>
       </c>
       <c r="D242">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>claudiaottoni19</v>
+        <v>lopesbrunao</v>
       </c>
       <c r="B243">
         <v>2</v>
@@ -3804,7 +3804,7 @@
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>sr.valter</v>
+        <v>claudiaottoni19</v>
       </c>
       <c r="B244">
         <v>2</v>
@@ -3818,7 +3818,7 @@
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>marcos.jordao.bjj</v>
+        <v>sr.valter</v>
       </c>
       <c r="B245">
         <v>2</v>
@@ -3832,49 +3832,49 @@
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>meol.socialmidia</v>
+        <v>marcos.jordao.bjj</v>
       </c>
       <c r="B246">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C246">
         <v>0</v>
       </c>
       <c r="D246">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>yamasakinhobjj</v>
+        <v>meol.socialmidia</v>
       </c>
       <c r="B247">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C247">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D247">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>mestreviniciusreviravolta</v>
+        <v>yamasakinhobjj</v>
       </c>
       <c r="B248">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C248">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D248">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>cami28_l</v>
+        <v>mestreviniciusreviravolta</v>
       </c>
       <c r="B249">
         <v>3</v>
@@ -3888,7 +3888,7 @@
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>flaviakaena</v>
+        <v>cami28_l</v>
       </c>
       <c r="B250">
         <v>3</v>
@@ -3902,63 +3902,63 @@
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>chrislima____</v>
+        <v>flaviakaena</v>
       </c>
       <c r="B251">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C251">
         <v>0</v>
       </c>
       <c r="D251">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>c.m_figth</v>
+        <v>chrislima____</v>
       </c>
       <c r="B252">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C252">
         <v>0</v>
       </c>
       <c r="D252">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>leo.ribeiro.bjj</v>
+        <v>c.m_figth</v>
       </c>
       <c r="B253">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C253">
         <v>0</v>
       </c>
       <c r="D253">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>e_car.doso</v>
+        <v>leo.ribeiro.bjj</v>
       </c>
       <c r="B254">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C254">
         <v>0</v>
       </c>
       <c r="D254">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>ellen.cristinaaa</v>
+        <v>e_car.doso</v>
       </c>
       <c r="B255">
         <v>3</v>
@@ -3972,16 +3972,16 @@
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>dgswillian</v>
+        <v>ellen.cristinaaa</v>
       </c>
       <c r="B256">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C256">
         <v>0</v>
       </c>
       <c r="D256">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="257">
@@ -10188,21 +10188,21 @@
     </row>
     <row r="700">
       <c r="A700" t="str">
-        <v>rosantos83</v>
+        <v>dudaadantass</v>
       </c>
       <c r="B700">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C700">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D700">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="str">
-        <v>caiogoularts</v>
+        <v>rosantos83</v>
       </c>
       <c r="B701">
         <v>1</v>
@@ -10216,7 +10216,7 @@
     </row>
     <row r="702">
       <c r="A702" t="str">
-        <v>cassiolee013</v>
+        <v>caiogoularts</v>
       </c>
       <c r="B702">
         <v>1</v>
@@ -10230,7 +10230,7 @@
     </row>
     <row r="703">
       <c r="A703" t="str">
-        <v>alinefurlann</v>
+        <v>cassiolee013</v>
       </c>
       <c r="B703">
         <v>1</v>
@@ -10244,7 +10244,7 @@
     </row>
     <row r="704">
       <c r="A704" t="str">
-        <v>programaparadois</v>
+        <v>alinefurlann</v>
       </c>
       <c r="B704">
         <v>1</v>
@@ -10258,7 +10258,7 @@
     </row>
     <row r="705">
       <c r="A705" t="str">
-        <v>cotty_bigmonster</v>
+        <v>programaparadois</v>
       </c>
       <c r="B705">
         <v>1</v>
@@ -10272,7 +10272,7 @@
     </row>
     <row r="706">
       <c r="A706" t="str">
-        <v>alissonlayza</v>
+        <v>cotty_bigmonster</v>
       </c>
       <c r="B706">
         <v>1</v>
@@ -10286,7 +10286,7 @@
     </row>
     <row r="707">
       <c r="A707" t="str">
-        <v>perninhakickboxing</v>
+        <v>alissonlayza</v>
       </c>
       <c r="B707">
         <v>1</v>
@@ -10300,7 +10300,7 @@
     </row>
     <row r="708">
       <c r="A708" t="str">
-        <v>rodrigo.nsx</v>
+        <v>perninhakickboxing</v>
       </c>
       <c r="B708">
         <v>1</v>
@@ -10314,7 +10314,7 @@
     </row>
     <row r="709">
       <c r="A709" t="str">
-        <v>_hygor.soares</v>
+        <v>rodrigo.nsx</v>
       </c>
       <c r="B709">
         <v>1</v>
@@ -10328,7 +10328,7 @@
     </row>
     <row r="710">
       <c r="A710" t="str">
-        <v>enzorkbjj</v>
+        <v>_hygor.soares</v>
       </c>
       <c r="B710">
         <v>1</v>
@@ -10342,7 +10342,7 @@
     </row>
     <row r="711">
       <c r="A711" t="str">
-        <v>lorenzojjts</v>
+        <v>enzorkbjj</v>
       </c>
       <c r="B711">
         <v>1</v>
@@ -10356,7 +10356,7 @@
     </row>
     <row r="712">
       <c r="A712" t="str">
-        <v>i_am_mauispunjahchick</v>
+        <v>lorenzojjts</v>
       </c>
       <c r="B712">
         <v>1</v>
@@ -10370,7 +10370,7 @@
     </row>
     <row r="713">
       <c r="A713" t="str">
-        <v>808.chaz</v>
+        <v>i_am_mauispunjahchick</v>
       </c>
       <c r="B713">
         <v>1</v>
@@ -10384,7 +10384,7 @@
     </row>
     <row r="714">
       <c r="A714" t="str">
-        <v>k_costa68</v>
+        <v>808.chaz</v>
       </c>
       <c r="B714">
         <v>1</v>
@@ -10398,7 +10398,7 @@
     </row>
     <row r="715">
       <c r="A715" t="str">
-        <v>leomvgomes</v>
+        <v>k_costa68</v>
       </c>
       <c r="B715">
         <v>1</v>
@@ -10412,7 +10412,7 @@
     </row>
     <row r="716">
       <c r="A716" t="str">
-        <v>wagnermeneguelll</v>
+        <v>leomvgomes</v>
       </c>
       <c r="B716">
         <v>1</v>
@@ -10426,7 +10426,7 @@
     </row>
     <row r="717">
       <c r="A717" t="str">
-        <v>luizguilhermepaiva_</v>
+        <v>wagnermeneguelll</v>
       </c>
       <c r="B717">
         <v>1</v>
@@ -10440,7 +10440,7 @@
     </row>
     <row r="718">
       <c r="A718" t="str">
-        <v>corullapedro</v>
+        <v>luizguilhermepaiva_</v>
       </c>
       <c r="B718">
         <v>1</v>
@@ -10454,7 +10454,7 @@
     </row>
     <row r="719">
       <c r="A719" t="str">
-        <v>marcos_indio._</v>
+        <v>corullapedro</v>
       </c>
       <c r="B719">
         <v>1</v>
@@ -10468,35 +10468,35 @@
     </row>
     <row r="720">
       <c r="A720" t="str">
-        <v>luizcosta_mma</v>
+        <v>marcos_indio._</v>
       </c>
       <c r="B720">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C720">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D720">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="721">
       <c r="A721" t="str">
-        <v>taylor_71kg</v>
+        <v>luizcosta_mma</v>
       </c>
       <c r="B721">
         <v>0</v>
       </c>
       <c r="C721">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D721">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="722">
       <c r="A722" t="str">
-        <v>_vpft</v>
+        <v>taylor_71kg</v>
       </c>
       <c r="B722">
         <v>0</v>
@@ -10510,21 +10510,21 @@
     </row>
     <row r="723">
       <c r="A723" t="str">
-        <v>viniciustbf</v>
+        <v>_vpft</v>
       </c>
       <c r="B723">
         <v>0</v>
       </c>
       <c r="C723">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D723">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="724">
       <c r="A724" t="str">
-        <v>dayanaa1511</v>
+        <v>viniciustbf</v>
       </c>
       <c r="B724">
         <v>0</v>
@@ -10533,40 +10533,40 @@
         <v>2</v>
       </c>
       <c r="D724">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="725">
       <c r="A725" t="str">
-        <v>danielfranzesilva</v>
+        <v>dayanaa1511</v>
       </c>
       <c r="B725">
         <v>0</v>
       </c>
       <c r="C725">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D725">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="726">
       <c r="A726" t="str">
-        <v>ednilsonkaicai</v>
+        <v>danielfranzesilva</v>
       </c>
       <c r="B726">
         <v>0</v>
       </c>
       <c r="C726">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D726">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="727">
       <c r="A727" t="str">
-        <v>vanessamelomma</v>
+        <v>ednilsonkaicai</v>
       </c>
       <c r="B727">
         <v>0</v>
@@ -10580,21 +10580,21 @@
     </row>
     <row r="728">
       <c r="A728" t="str">
-        <v>michelle_mirele</v>
+        <v>vanessamelomma</v>
       </c>
       <c r="B728">
         <v>0</v>
       </c>
       <c r="C728">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D728">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="729">
       <c r="A729" t="str">
-        <v>geyziellsouza</v>
+        <v>michelle_mirele</v>
       </c>
       <c r="B729">
         <v>0</v>
@@ -10608,21 +10608,21 @@
     </row>
     <row r="730">
       <c r="A730" t="str">
-        <v>guerreirammaofc</v>
+        <v>geyziellsouza</v>
       </c>
       <c r="B730">
         <v>0</v>
       </c>
       <c r="C730">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D730">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="731">
       <c r="A731" t="str">
-        <v>kalaga_vito</v>
+        <v>guerreirammaofc</v>
       </c>
       <c r="B731">
         <v>0</v>
@@ -10636,7 +10636,7 @@
     </row>
     <row r="732">
       <c r="A732" t="str">
-        <v>dudaadantass</v>
+        <v>kalaga_vito</v>
       </c>
       <c r="B732">
         <v>0</v>
@@ -14115,7 +14115,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D94"/>
+  <dimension ref="A1:D97"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -14136,13 +14136,13 @@
         <v>peacegrappler</v>
       </c>
       <c r="B2">
+        <v>122</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
         <v>109</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>99</v>
       </c>
     </row>
     <row r="3">
@@ -14150,13 +14150,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C3">
         <v>2</v>
       </c>
       <c r="D3">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4">
@@ -14164,7 +14164,7 @@
         <v>enzocardoso.bjj</v>
       </c>
       <c r="B4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -14178,7 +14178,7 @@
         <v>kelly_ottoni</v>
       </c>
       <c r="B5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C5">
         <v>7</v>
@@ -14237,29 +14237,29 @@
         <v>3</v>
       </c>
       <c r="C9">
+        <v>13</v>
+      </c>
+      <c r="D9">
         <v>11</v>
-      </c>
-      <c r="D9">
-        <v>9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>grapplerfight</v>
+        <v>ismaeldaniell</v>
       </c>
       <c r="B10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>galler_peace</v>
+        <v>grapplerfight</v>
       </c>
       <c r="B11">
         <v>3</v>
@@ -14273,7 +14273,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>thundergrapple</v>
+        <v>galler_peace</v>
       </c>
       <c r="B12">
         <v>3</v>
@@ -14287,7 +14287,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>figh_grappler</v>
+        <v>thundergrapple</v>
       </c>
       <c r="B13">
         <v>3</v>
@@ -14301,7 +14301,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>anayachiottoni</v>
+        <v>figh_grappler</v>
       </c>
       <c r="B14">
         <v>3</v>
@@ -14315,7 +14315,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ismaeldaniell</v>
+        <v>anayachiottoni</v>
       </c>
       <c r="B15">
         <v>3</v>
@@ -14324,26 +14324,26 @@
         <v>0</v>
       </c>
       <c r="D15">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>ninjatheorist</v>
+        <v>god.motivacao</v>
       </c>
       <c r="B16">
         <v>3</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D16">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>helenmacielmma</v>
+        <v>carlos_hm_iglesias</v>
       </c>
       <c r="B17">
         <v>3</v>
@@ -14357,10 +14357,10 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>wesleysepulveda__mma</v>
+        <v>ninjatheorist</v>
       </c>
       <c r="B18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -14371,21 +14371,21 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>god.motivacao</v>
+        <v>helenmacielmma</v>
       </c>
       <c r="B19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C19">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D19">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>propeace_fight</v>
+        <v>wesleysepulveda__mma</v>
       </c>
       <c r="B20">
         <v>2</v>
@@ -14399,7 +14399,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>rm.nicki</v>
+        <v>propeace_fight</v>
       </c>
       <c r="B21">
         <v>2</v>
@@ -14413,7 +14413,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>lili.munix</v>
+        <v>rm.nicki</v>
       </c>
       <c r="B22">
         <v>2</v>
@@ -14427,7 +14427,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>carlos_hm_iglesias</v>
+        <v>lili.munix</v>
       </c>
       <c r="B23">
         <v>2</v>
@@ -14525,21 +14525,21 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>combintel</v>
+        <v>adriano.trator</v>
       </c>
       <c r="B30">
         <v>2</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D30">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>ottonimestre</v>
+        <v>combintel</v>
       </c>
       <c r="B31">
         <v>2</v>
@@ -14553,7 +14553,7 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>canalgolpebaixo</v>
+        <v>ottonimestre</v>
       </c>
       <c r="B32">
         <v>2</v>
@@ -14567,7 +14567,7 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>shawlinoficial</v>
+        <v>canalgolpebaixo</v>
       </c>
       <c r="B33">
         <v>2</v>
@@ -14581,10 +14581,10 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>og.mthx</v>
+        <v>shawlinoficial</v>
       </c>
       <c r="B34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C34">
         <v>0</v>
@@ -14595,7 +14595,7 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>danielcarmonaconsultor</v>
+        <v>og.mthx</v>
       </c>
       <c r="B35">
         <v>1</v>
@@ -14609,7 +14609,7 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>cristianpsicologo</v>
+        <v>danielcarmonaconsultor</v>
       </c>
       <c r="B36">
         <v>1</v>
@@ -14623,7 +14623,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>brcks4breakfast</v>
+        <v>cristianpsicologo</v>
       </c>
       <c r="B37">
         <v>1</v>
@@ -14637,7 +14637,7 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>mma.idiot</v>
+        <v>brcks4breakfast</v>
       </c>
       <c r="B38">
         <v>1</v>
@@ -14651,7 +14651,7 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>roger_santosmma</v>
+        <v>mma.idiot</v>
       </c>
       <c r="B39">
         <v>1</v>
@@ -14665,7 +14665,7 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>murata_profight</v>
+        <v>roger_santosmma</v>
       </c>
       <c r="B40">
         <v>1</v>
@@ -14679,7 +14679,7 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>vndcardoso</v>
+        <v>murata_profight</v>
       </c>
       <c r="B41">
         <v>1</v>
@@ -14693,7 +14693,7 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>zackdos</v>
+        <v>vndcardoso</v>
       </c>
       <c r="B42">
         <v>1</v>
@@ -14707,21 +14707,21 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>npb.enterprise</v>
+        <v>jean_ferreira_br</v>
       </c>
       <c r="B43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C43">
         <v>0</v>
       </c>
       <c r="D43">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>david_sfc19</v>
+        <v>zackdos</v>
       </c>
       <c r="B44">
         <v>1</v>
@@ -14735,7 +14735,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>danielrodrigues1000</v>
+        <v>npb.enterprise</v>
       </c>
       <c r="B45">
         <v>1</v>
@@ -14749,7 +14749,7 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>laisrebeiro10</v>
+        <v>david_sfc19</v>
       </c>
       <c r="B46">
         <v>1</v>
@@ -14763,7 +14763,7 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>claudineiscorrea</v>
+        <v>danielrodrigues1000</v>
       </c>
       <c r="B47">
         <v>1</v>
@@ -14777,7 +14777,7 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ottonianalivia</v>
+        <v>laisrebeiro10</v>
       </c>
       <c r="B48">
         <v>1</v>
@@ -14791,41 +14791,41 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>adriano.trator</v>
+        <v>claudineiscorrea</v>
       </c>
       <c r="B49">
         <v>1</v>
       </c>
       <c r="C49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D49">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>cassiosants__</v>
+        <v>ottonianalivia</v>
       </c>
       <c r="B50">
         <v>1</v>
       </c>
       <c r="C50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D50">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>masonharper_mma</v>
+        <v>cassiosants__</v>
       </c>
       <c r="B51">
         <v>1</v>
       </c>
       <c r="C51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D51">
         <v>0</v>
@@ -14833,7 +14833,7 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>johnmma9</v>
+        <v>masonharper_mma</v>
       </c>
       <c r="B52">
         <v>1</v>
@@ -14847,7 +14847,7 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>mmmarc20</v>
+        <v>johnmma9</v>
       </c>
       <c r="B53">
         <v>1</v>
@@ -14861,7 +14861,7 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>pablofiorindi</v>
+        <v>mmmarc20</v>
       </c>
       <c r="B54">
         <v>1</v>
@@ -14875,7 +14875,7 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>_jullianadacruz</v>
+        <v>pablofiorindi</v>
       </c>
       <c r="B55">
         <v>1</v>
@@ -14889,7 +14889,7 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>erickdiaseds</v>
+        <v>_jullianadacruz</v>
       </c>
       <c r="B56">
         <v>1</v>
@@ -14903,7 +14903,7 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>adrianoams7</v>
+        <v>erickdiaseds</v>
       </c>
       <c r="B57">
         <v>1</v>
@@ -14917,7 +14917,7 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>_hygor.soares</v>
+        <v>adrianoams7</v>
       </c>
       <c r="B58">
         <v>1</v>
@@ -14931,7 +14931,7 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>enzorkbjj</v>
+        <v>_hygor.soares</v>
       </c>
       <c r="B59">
         <v>1</v>
@@ -14945,7 +14945,7 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>emersonriosmma</v>
+        <v>enzorkbjj</v>
       </c>
       <c r="B60">
         <v>1</v>
@@ -14959,7 +14959,7 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>_pedro0h</v>
+        <v>emersonriosmma</v>
       </c>
       <c r="B61">
         <v>1</v>
@@ -14973,7 +14973,7 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>lorenzojjts</v>
+        <v>_pedro0h</v>
       </c>
       <c r="B62">
         <v>1</v>
@@ -14987,7 +14987,7 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>pauloserrati</v>
+        <v>lorenzojjts</v>
       </c>
       <c r="B63">
         <v>1</v>
@@ -15001,7 +15001,7 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>karen.ottoni</v>
+        <v>pauloserrati</v>
       </c>
       <c r="B64">
         <v>1</v>
@@ -15015,7 +15015,7 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>thiagoauper</v>
+        <v>karen.ottoni</v>
       </c>
       <c r="B65">
         <v>1</v>
@@ -15029,7 +15029,7 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>ellen.cristinaaa</v>
+        <v>thiagoauper</v>
       </c>
       <c r="B66">
         <v>1</v>
@@ -15043,7 +15043,7 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>albertoleandromoco</v>
+        <v>ellen.cristinaaa</v>
       </c>
       <c r="B67">
         <v>1</v>
@@ -15057,7 +15057,7 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>jean_ferreira_br</v>
+        <v>albertoleandromoco</v>
       </c>
       <c r="B68">
         <v>1</v>
@@ -15211,27 +15211,27 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>leobahiamma</v>
+        <v>dgswillian</v>
       </c>
       <c r="B79">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C79">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D79">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>pedro_pavin_</v>
+        <v>leobahiamma</v>
       </c>
       <c r="B80">
         <v>0</v>
       </c>
       <c r="C80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D80">
         <v>1</v>
@@ -15239,7 +15239,7 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>allan10adm</v>
+        <v>pedro_pavin_</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -15253,7 +15253,7 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>ismael.marreta_ufc</v>
+        <v>allan10adm</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -15267,7 +15267,7 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>joandersontubarao_ufc</v>
+        <v>ismael.marreta_ufc</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -15281,7 +15281,7 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>gaby_alves07</v>
+        <v>joandersontubarao_ufc</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -15295,7 +15295,7 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>diegosilvabjjoficial</v>
+        <v>gaby_alves07</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -15309,7 +15309,7 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>mvp_lutas</v>
+        <v>diegosilvabjjoficial</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -15323,7 +15323,7 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>pulsepro.nutrition</v>
+        <v>mvp_lutas</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -15332,12 +15332,12 @@
         <v>1</v>
       </c>
       <c r="D87">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>herbeth_indiomma</v>
+        <v>dudaadantass</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -15346,12 +15346,12 @@
         <v>1</v>
       </c>
       <c r="D88">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>danielbzk_</v>
+        <v>pulsepro.nutrition</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -15365,7 +15365,7 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>jp.mdc</v>
+        <v>herbeth_indiomma</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -15379,7 +15379,7 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>rosacostasousa36</v>
+        <v>danielbzk_</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -15393,7 +15393,7 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>cathya_ferreira</v>
+        <v>jp.mdc</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -15407,7 +15407,7 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>1210gi</v>
+        <v>rosacostasousa36</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -15421,21 +15421,63 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
+        <v>cathya_ferreira</v>
+      </c>
+      <c r="B94">
+        <v>0</v>
+      </c>
+      <c r="C94">
+        <v>1</v>
+      </c>
+      <c r="D94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>1210gi</v>
+      </c>
+      <c r="B95">
+        <v>0</v>
+      </c>
+      <c r="C95">
+        <v>1</v>
+      </c>
+      <c r="D95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
         <v>juanx.pontes</v>
       </c>
-      <c r="B94">
-        <v>0</v>
-      </c>
-      <c r="C94">
-        <v>1</v>
-      </c>
-      <c r="D94">
+      <c r="B96">
+        <v>0</v>
+      </c>
+      <c r="C96">
+        <v>1</v>
+      </c>
+      <c r="D96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>_oliveira09_</v>
+      </c>
+      <c r="B97">
+        <v>0</v>
+      </c>
+      <c r="C97">
+        <v>1</v>
+      </c>
+      <c r="D97">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D94"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D97"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Engagement Rankings 2026-07.xlsx
+++ b/Engagement Rankings 2026-07.xlsx
@@ -419,13 +419,13 @@
         <v>peacegrappler</v>
       </c>
       <c r="B2">
-        <v>13502</v>
+        <v>13513</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>12224</v>
+        <v>12235</v>
       </c>
     </row>
     <row r="3">
@@ -433,7 +433,7 @@
         <v>pedr00jj</v>
       </c>
       <c r="B3">
-        <v>3675</v>
+        <v>3676</v>
       </c>
       <c r="C3">
         <v>6</v>
@@ -492,10 +492,10 @@
         <v>1342</v>
       </c>
       <c r="C7">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D7">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="8">
@@ -685,13 +685,13 @@
         <v>sirleneferreiradiasdias</v>
       </c>
       <c r="B21">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C21">
         <v>51</v>
       </c>
       <c r="D21">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="22">
@@ -836,30 +836,30 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>maxgandra</v>
+        <v>washington_cassisno</v>
       </c>
       <c r="B32">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="C32">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D32">
-        <v>17</v>
+        <v>47</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>washington_cassisno</v>
+        <v>maxgandra</v>
       </c>
       <c r="B33">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="C33">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D33">
-        <v>45</v>
+        <v>17</v>
       </c>
     </row>
     <row r="34">
@@ -1178,7 +1178,7 @@
         <v>25</v>
       </c>
       <c r="C56">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D56">
         <v>20</v>
@@ -1539,7 +1539,7 @@
         <v>adriano.trator</v>
       </c>
       <c r="B82">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C82">
         <v>47</v>
@@ -1735,7 +1735,7 @@
         <v>edebetim_</v>
       </c>
       <c r="B96">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C96">
         <v>20</v>
@@ -3692,52 +3692,52 @@
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>jose_luiz_thome</v>
+        <v>mestreviniciusreviravolta</v>
       </c>
       <c r="B236">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C236">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D236">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>efsantos.oficial</v>
+        <v>jose_luiz_thome</v>
       </c>
       <c r="B237">
         <v>1</v>
       </c>
       <c r="C237">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D237">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>ufc_paramountsports</v>
+        <v>efsantos.oficial</v>
       </c>
       <c r="B238">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C238">
         <v>1</v>
       </c>
       <c r="D238">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>marifferreirac</v>
+        <v>ufc_paramountsports</v>
       </c>
       <c r="B239">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C239">
         <v>1</v>
@@ -3748,13 +3748,13 @@
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>mineirinho_jj</v>
+        <v>marifferreirac</v>
       </c>
       <c r="B240">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C240">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D240">
         <v>1</v>
@@ -3762,7 +3762,7 @@
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>juliochagasmma</v>
+        <v>mineirinho_jj</v>
       </c>
       <c r="B241">
         <v>2</v>
@@ -3776,35 +3776,35 @@
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>orafao1</v>
+        <v>juliochagasmma</v>
       </c>
       <c r="B242">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C242">
         <v>0</v>
       </c>
       <c r="D242">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>lopesbrunao</v>
+        <v>orafao1</v>
       </c>
       <c r="B243">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C243">
         <v>0</v>
       </c>
       <c r="D243">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>claudiaottoni19</v>
+        <v>lopesbrunao</v>
       </c>
       <c r="B244">
         <v>2</v>
@@ -3818,7 +3818,7 @@
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>sr.valter</v>
+        <v>claudiaottoni19</v>
       </c>
       <c r="B245">
         <v>2</v>
@@ -3832,7 +3832,7 @@
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>marcos.jordao.bjj</v>
+        <v>sr.valter</v>
       </c>
       <c r="B246">
         <v>2</v>
@@ -3846,44 +3846,44 @@
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>meol.socialmidia</v>
+        <v>marcos.jordao.bjj</v>
       </c>
       <c r="B247">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C247">
         <v>0</v>
       </c>
       <c r="D247">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>yamasakinhobjj</v>
+        <v>meol.socialmidia</v>
       </c>
       <c r="B248">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C248">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D248">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>mestreviniciusreviravolta</v>
+        <v>yamasakinhobjj</v>
       </c>
       <c r="B249">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C249">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D249">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="250">
@@ -6352,27 +6352,27 @@
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>cassiosants__</v>
+        <v>dudaadantass</v>
       </c>
       <c r="B426">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C426">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D426">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>rafaela_duaartee</v>
+        <v>cassiosants__</v>
       </c>
       <c r="B427">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C427">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D427">
         <v>0</v>
@@ -6380,13 +6380,13 @@
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>wagner_alexandre_w_a</v>
+        <v>rafaela_duaartee</v>
       </c>
       <c r="B428">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C428">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D428">
         <v>0</v>
@@ -6394,7 +6394,7 @@
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>andre.legendre.10</v>
+        <v>wagner_alexandre_w_a</v>
       </c>
       <c r="B429">
         <v>1</v>
@@ -6408,7 +6408,7 @@
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>phillipe.harry</v>
+        <v>andre.legendre.10</v>
       </c>
       <c r="B430">
         <v>1</v>
@@ -6422,7 +6422,7 @@
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>andrejetx</v>
+        <v>phillipe.harry</v>
       </c>
       <c r="B431">
         <v>1</v>
@@ -6436,7 +6436,7 @@
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>leandro_motiv4</v>
+        <v>andrejetx</v>
       </c>
       <c r="B432">
         <v>1</v>
@@ -6450,7 +6450,7 @@
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>olga.oliveira013</v>
+        <v>leandro_motiv4</v>
       </c>
       <c r="B433">
         <v>1</v>
@@ -6464,7 +6464,7 @@
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>vinyrodriguesoficial</v>
+        <v>olga.oliveira013</v>
       </c>
       <c r="B434">
         <v>1</v>
@@ -6478,7 +6478,7 @@
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>leosacraa</v>
+        <v>vinyrodriguesoficial</v>
       </c>
       <c r="B435">
         <v>1</v>
@@ -6492,7 +6492,7 @@
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>gutocriativo</v>
+        <v>leosacraa</v>
       </c>
       <c r="B436">
         <v>1</v>
@@ -6506,7 +6506,7 @@
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>igorfso_</v>
+        <v>gutocriativo</v>
       </c>
       <c r="B437">
         <v>1</v>
@@ -6520,7 +6520,7 @@
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>gabrielsilva_mma</v>
+        <v>igorfso_</v>
       </c>
       <c r="B438">
         <v>1</v>
@@ -6534,7 +6534,7 @@
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>lay_roqs</v>
+        <v>gabrielsilva_mma</v>
       </c>
       <c r="B439">
         <v>1</v>
@@ -6548,7 +6548,7 @@
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>bigjota.music</v>
+        <v>lay_roqs</v>
       </c>
       <c r="B440">
         <v>1</v>
@@ -6562,7 +6562,7 @@
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>jhoninhaoficial031</v>
+        <v>bigjota.music</v>
       </c>
       <c r="B441">
         <v>1</v>
@@ -6576,7 +6576,7 @@
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>mth_fernandes031</v>
+        <v>jhoninhaoficial031</v>
       </c>
       <c r="B442">
         <v>1</v>
@@ -6590,7 +6590,7 @@
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>cezary_oleksiejczuk</v>
+        <v>mth_fernandes031</v>
       </c>
       <c r="B443">
         <v>1</v>
@@ -6604,7 +6604,7 @@
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>_alcantara.bru</v>
+        <v>cezary_oleksiejczuk</v>
       </c>
       <c r="B444">
         <v>1</v>
@@ -6618,7 +6618,7 @@
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>_puroosso88</v>
+        <v>_alcantara.bru</v>
       </c>
       <c r="B445">
         <v>1</v>
@@ -6632,7 +6632,7 @@
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>_rayysp</v>
+        <v>_puroosso88</v>
       </c>
       <c r="B446">
         <v>1</v>
@@ -6646,7 +6646,7 @@
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>cami.terra_</v>
+        <v>_rayysp</v>
       </c>
       <c r="B447">
         <v>1</v>
@@ -6660,7 +6660,7 @@
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>gabicardoson</v>
+        <v>cami.terra_</v>
       </c>
       <c r="B448">
         <v>1</v>
@@ -6674,7 +6674,7 @@
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>pietroshz</v>
+        <v>gabicardoson</v>
       </c>
       <c r="B449">
         <v>1</v>
@@ -6688,7 +6688,7 @@
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>___neller</v>
+        <v>pietroshz</v>
       </c>
       <c r="B450">
         <v>1</v>
@@ -6702,7 +6702,7 @@
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>guilhermeefelix__</v>
+        <v>___neller</v>
       </c>
       <c r="B451">
         <v>1</v>
@@ -6716,7 +6716,7 @@
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>pativinisf</v>
+        <v>guilhermeefelix__</v>
       </c>
       <c r="B452">
         <v>1</v>
@@ -6730,7 +6730,7 @@
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>judadany</v>
+        <v>pativinisf</v>
       </c>
       <c r="B453">
         <v>1</v>
@@ -6744,7 +6744,7 @@
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>andre_alcausa</v>
+        <v>judadany</v>
       </c>
       <c r="B454">
         <v>1</v>
@@ -6758,7 +6758,7 @@
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>_fernunes</v>
+        <v>andre_alcausa</v>
       </c>
       <c r="B455">
         <v>1</v>
@@ -6772,7 +6772,7 @@
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>aloirmarcal</v>
+        <v>_fernunes</v>
       </c>
       <c r="B456">
         <v>1</v>
@@ -6786,7 +6786,7 @@
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>gilberto_7606</v>
+        <v>aloirmarcal</v>
       </c>
       <c r="B457">
         <v>1</v>
@@ -6800,7 +6800,7 @@
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>flazuera14</v>
+        <v>gilberto_7606</v>
       </c>
       <c r="B458">
         <v>1</v>
@@ -6814,7 +6814,7 @@
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>camii_bonfim</v>
+        <v>flazuera14</v>
       </c>
       <c r="B459">
         <v>1</v>
@@ -6828,7 +6828,7 @@
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>danlouiz.jj</v>
+        <v>camii_bonfim</v>
       </c>
       <c r="B460">
         <v>1</v>
@@ -6842,7 +6842,7 @@
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>gabriel_trevelin</v>
+        <v>danlouiz.jj</v>
       </c>
       <c r="B461">
         <v>1</v>
@@ -6856,7 +6856,7 @@
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>_lsanchess_</v>
+        <v>gabriel_trevelin</v>
       </c>
       <c r="B462">
         <v>1</v>
@@ -6870,7 +6870,7 @@
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>mr__rlk01</v>
+        <v>_lsanchess_</v>
       </c>
       <c r="B463">
         <v>1</v>
@@ -6884,7 +6884,7 @@
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>vitor_buck</v>
+        <v>mr__rlk01</v>
       </c>
       <c r="B464">
         <v>1</v>
@@ -6898,7 +6898,7 @@
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>fran.ruys</v>
+        <v>vitor_buck</v>
       </c>
       <c r="B465">
         <v>1</v>
@@ -6912,7 +6912,7 @@
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>arthurhenrique.sx</v>
+        <v>fran.ruys</v>
       </c>
       <c r="B466">
         <v>1</v>
@@ -6926,7 +6926,7 @@
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>draanapaulaponceano</v>
+        <v>arthurhenrique.sx</v>
       </c>
       <c r="B467">
         <v>1</v>
@@ -6940,7 +6940,7 @@
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>saj_photo_miami</v>
+        <v>draanapaulaponceano</v>
       </c>
       <c r="B468">
         <v>1</v>
@@ -6954,7 +6954,7 @@
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>alternativaremocoes</v>
+        <v>saj_photo_miami</v>
       </c>
       <c r="B469">
         <v>1</v>
@@ -6968,7 +6968,7 @@
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>benivalentinn</v>
+        <v>alternativaremocoes</v>
       </c>
       <c r="B470">
         <v>1</v>
@@ -6982,7 +6982,7 @@
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>miguelrodriguesbjj</v>
+        <v>benivalentinn</v>
       </c>
       <c r="B471">
         <v>1</v>
@@ -6996,7 +6996,7 @@
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>navarro_9430</v>
+        <v>miguelrodriguesbjj</v>
       </c>
       <c r="B472">
         <v>1</v>
@@ -7010,7 +7010,7 @@
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>charlesanthony2466</v>
+        <v>navarro_9430</v>
       </c>
       <c r="B473">
         <v>1</v>
@@ -7024,7 +7024,7 @@
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>xavyeroficial</v>
+        <v>charlesanthony2466</v>
       </c>
       <c r="B474">
         <v>1</v>
@@ -7038,7 +7038,7 @@
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>maryanagandra</v>
+        <v>xavyeroficial</v>
       </c>
       <c r="B475">
         <v>1</v>
@@ -7052,7 +7052,7 @@
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>katiaecarreraf</v>
+        <v>maryanagandra</v>
       </c>
       <c r="B476">
         <v>1</v>
@@ -7066,7 +7066,7 @@
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>geraldocnetomma</v>
+        <v>katiaecarreraf</v>
       </c>
       <c r="B477">
         <v>1</v>
@@ -7080,13 +7080,13 @@
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>marinealcausa</v>
+        <v>geraldocnetomma</v>
       </c>
       <c r="B478">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C478">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D478">
         <v>0</v>
@@ -7094,13 +7094,13 @@
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>artemio_bjj</v>
+        <v>marinealcausa</v>
       </c>
       <c r="B479">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C479">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D479">
         <v>0</v>
@@ -7108,7 +7108,7 @@
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>carolinne.xwp</v>
+        <v>artemio_bjj</v>
       </c>
       <c r="B480">
         <v>1</v>
@@ -7122,7 +7122,7 @@
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>isaac.bah_starinazzo</v>
+        <v>carolinne.xwp</v>
       </c>
       <c r="B481">
         <v>1</v>
@@ -7136,7 +7136,7 @@
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>lara.rpr</v>
+        <v>isaac.bah_starinazzo</v>
       </c>
       <c r="B482">
         <v>1</v>
@@ -7150,7 +7150,7 @@
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>codasqueves</v>
+        <v>lara.rpr</v>
       </c>
       <c r="B483">
         <v>1</v>
@@ -7164,7 +7164,7 @@
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>yan_touro_.7766</v>
+        <v>codasqueves</v>
       </c>
       <c r="B484">
         <v>1</v>
@@ -7178,7 +7178,7 @@
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>brothers_of_life</v>
+        <v>yan_touro_.7766</v>
       </c>
       <c r="B485">
         <v>1</v>
@@ -7192,7 +7192,7 @@
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>teacherthalesyouplus</v>
+        <v>brothers_of_life</v>
       </c>
       <c r="B486">
         <v>1</v>
@@ -7206,7 +7206,7 @@
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>minotaurinho</v>
+        <v>teacherthalesyouplus</v>
       </c>
       <c r="B487">
         <v>1</v>
@@ -7220,7 +7220,7 @@
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>anahangelica</v>
+        <v>minotaurinho</v>
       </c>
       <c r="B488">
         <v>1</v>
@@ -7234,7 +7234,7 @@
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>frankikolimabjj</v>
+        <v>anahangelica</v>
       </c>
       <c r="B489">
         <v>1</v>
@@ -7248,7 +7248,7 @@
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>tonketjudes</v>
+        <v>frankikolimabjj</v>
       </c>
       <c r="B490">
         <v>1</v>
@@ -7262,7 +7262,7 @@
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>_eliasffx</v>
+        <v>tonketjudes</v>
       </c>
       <c r="B491">
         <v>1</v>
@@ -7276,7 +7276,7 @@
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>pdfiv</v>
+        <v>_eliasffx</v>
       </c>
       <c r="B492">
         <v>1</v>
@@ -7290,7 +7290,7 @@
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>mariaraimundad940</v>
+        <v>pdfiv</v>
       </c>
       <c r="B493">
         <v>1</v>
@@ -7304,7 +7304,7 @@
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>gabesantos.13</v>
+        <v>mariaraimundad940</v>
       </c>
       <c r="B494">
         <v>1</v>
@@ -7318,7 +7318,7 @@
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>euvitormirandaa</v>
+        <v>gabesantos.13</v>
       </c>
       <c r="B495">
         <v>1</v>
@@ -7332,7 +7332,7 @@
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>gandra.julya</v>
+        <v>euvitormirandaa</v>
       </c>
       <c r="B496">
         <v>1</v>
@@ -7346,7 +7346,7 @@
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>espacomarcialino</v>
+        <v>gandra.julya</v>
       </c>
       <c r="B497">
         <v>1</v>
@@ -7360,7 +7360,7 @@
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>azulcapoeirabjj</v>
+        <v>espacomarcialino</v>
       </c>
       <c r="B498">
         <v>1</v>
@@ -7374,7 +7374,7 @@
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>andreiaatleta</v>
+        <v>azulcapoeirabjj</v>
       </c>
       <c r="B499">
         <v>1</v>
@@ -7388,7 +7388,7 @@
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>luhluhm</v>
+        <v>andreiaatleta</v>
       </c>
       <c r="B500">
         <v>1</v>
@@ -7402,7 +7402,7 @@
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>jack_hashimoto</v>
+        <v>luhluhm</v>
       </c>
       <c r="B501">
         <v>1</v>
@@ -7416,7 +7416,7 @@
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>do_caex_wandel</v>
+        <v>jack_hashimoto</v>
       </c>
       <c r="B502">
         <v>1</v>
@@ -7430,7 +7430,7 @@
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>eu_felipe_leite</v>
+        <v>do_caex_wandel</v>
       </c>
       <c r="B503">
         <v>1</v>
@@ -7444,7 +7444,7 @@
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>selma.ribeirotr</v>
+        <v>eu_felipe_leite</v>
       </c>
       <c r="B504">
         <v>1</v>
@@ -7458,7 +7458,7 @@
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>valqsm</v>
+        <v>selma.ribeirotr</v>
       </c>
       <c r="B505">
         <v>1</v>
@@ -7472,7 +7472,7 @@
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>nutrivan.alves</v>
+        <v>valqsm</v>
       </c>
       <c r="B506">
         <v>1</v>
@@ -7486,7 +7486,7 @@
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>allisonestuchi_fisioterapeuta</v>
+        <v>nutrivan.alves</v>
       </c>
       <c r="B507">
         <v>1</v>
@@ -7500,7 +7500,7 @@
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>sidneibabu</v>
+        <v>allisonestuchi_fisioterapeuta</v>
       </c>
       <c r="B508">
         <v>1</v>
@@ -7514,7 +7514,7 @@
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>muriloo__ferreira</v>
+        <v>sidneibabu</v>
       </c>
       <c r="B509">
         <v>1</v>
@@ -7528,7 +7528,7 @@
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>drfelipeoliveira_adv</v>
+        <v>muriloo__ferreira</v>
       </c>
       <c r="B510">
         <v>1</v>
@@ -7542,7 +7542,7 @@
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>turmanmma</v>
+        <v>drfelipeoliveira_adv</v>
       </c>
       <c r="B511">
         <v>1</v>
@@ -7556,7 +7556,7 @@
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>andre_luizdj</v>
+        <v>turmanmma</v>
       </c>
       <c r="B512">
         <v>1</v>
@@ -7570,7 +7570,7 @@
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>lumarasantosjj</v>
+        <v>andre_luizdj</v>
       </c>
       <c r="B513">
         <v>1</v>
@@ -7584,7 +7584,7 @@
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>donrey_42</v>
+        <v>lumarasantosjj</v>
       </c>
       <c r="B514">
         <v>1</v>
@@ -7598,7 +7598,7 @@
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>personalmaju</v>
+        <v>donrey_42</v>
       </c>
       <c r="B515">
         <v>1</v>
@@ -7612,7 +7612,7 @@
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>itsmayraregina</v>
+        <v>personalmaju</v>
       </c>
       <c r="B516">
         <v>1</v>
@@ -7626,7 +7626,7 @@
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>fototatico</v>
+        <v>itsmayraregina</v>
       </c>
       <c r="B517">
         <v>1</v>
@@ -7640,7 +7640,7 @@
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>michel.juliano.barbershop</v>
+        <v>fototatico</v>
       </c>
       <c r="B518">
         <v>1</v>
@@ -7654,7 +7654,7 @@
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>ruperto_696</v>
+        <v>michel.juliano.barbershop</v>
       </c>
       <c r="B519">
         <v>1</v>
@@ -7668,7 +7668,7 @@
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>diegomoisesribeiro</v>
+        <v>ruperto_696</v>
       </c>
       <c r="B520">
         <v>1</v>
@@ -7682,7 +7682,7 @@
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>lucca_bjj_01</v>
+        <v>diegomoisesribeiro</v>
       </c>
       <c r="B521">
         <v>1</v>
@@ -7696,7 +7696,7 @@
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>calebe1000grau</v>
+        <v>lucca_bjj_01</v>
       </c>
       <c r="B522">
         <v>1</v>
@@ -7710,7 +7710,7 @@
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>brunito_bernardo</v>
+        <v>calebe1000grau</v>
       </c>
       <c r="B523">
         <v>1</v>
@@ -7724,7 +7724,7 @@
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>clarianavillasboasoficial</v>
+        <v>brunito_bernardo</v>
       </c>
       <c r="B524">
         <v>1</v>
@@ -7738,7 +7738,7 @@
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>gladyador_do_asa</v>
+        <v>clarianavillasboasoficial</v>
       </c>
       <c r="B525">
         <v>1</v>
@@ -7752,7 +7752,7 @@
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>aureooficial</v>
+        <v>gladyador_do_asa</v>
       </c>
       <c r="B526">
         <v>1</v>
@@ -7766,7 +7766,7 @@
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>williamjanser</v>
+        <v>aureooficial</v>
       </c>
       <c r="B527">
         <v>1</v>
@@ -7780,7 +7780,7 @@
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>jeremyericjacobs</v>
+        <v>williamjanser</v>
       </c>
       <c r="B528">
         <v>1</v>
@@ -7794,7 +7794,7 @@
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>chicinvancity</v>
+        <v>jeremyericjacobs</v>
       </c>
       <c r="B529">
         <v>1</v>
@@ -7808,7 +7808,7 @@
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>susiemelchionda</v>
+        <v>chicinvancity</v>
       </c>
       <c r="B530">
         <v>1</v>
@@ -7822,7 +7822,7 @@
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>satsangbjj</v>
+        <v>susiemelchionda</v>
       </c>
       <c r="B531">
         <v>1</v>
@@ -7836,7 +7836,7 @@
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>gallupistrengthconditioning</v>
+        <v>satsangbjj</v>
       </c>
       <c r="B532">
         <v>1</v>
@@ -7850,7 +7850,7 @@
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>danibastiaan</v>
+        <v>gallupistrengthconditioning</v>
       </c>
       <c r="B533">
         <v>1</v>
@@ -7864,7 +7864,7 @@
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>gilcilenecristina</v>
+        <v>danibastiaan</v>
       </c>
       <c r="B534">
         <v>1</v>
@@ -7878,7 +7878,7 @@
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>andreaapurinaoficial</v>
+        <v>gilcilenecristina</v>
       </c>
       <c r="B535">
         <v>1</v>
@@ -7892,7 +7892,7 @@
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>alehh_novaes</v>
+        <v>andreaapurinaoficial</v>
       </c>
       <c r="B536">
         <v>1</v>
@@ -7906,7 +7906,7 @@
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>franklinamaral</v>
+        <v>alehh_novaes</v>
       </c>
       <c r="B537">
         <v>1</v>
@@ -7920,7 +7920,7 @@
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>valbersonsantoss</v>
+        <v>franklinamaral</v>
       </c>
       <c r="B538">
         <v>1</v>
@@ -7934,7 +7934,7 @@
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>j.borgespz</v>
+        <v>valbersonsantoss</v>
       </c>
       <c r="B539">
         <v>1</v>
@@ -7948,7 +7948,7 @@
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>gpedroza1</v>
+        <v>j.borgespz</v>
       </c>
       <c r="B540">
         <v>1</v>
@@ -7962,7 +7962,7 @@
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>almir_gdf</v>
+        <v>gpedroza1</v>
       </c>
       <c r="B541">
         <v>1</v>
@@ -7976,7 +7976,7 @@
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>renancarlini</v>
+        <v>almir_gdf</v>
       </c>
       <c r="B542">
         <v>1</v>
@@ -7990,7 +7990,7 @@
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>lucaswallaceftt</v>
+        <v>renancarlini</v>
       </c>
       <c r="B543">
         <v>1</v>
@@ -8004,7 +8004,7 @@
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>lilianvillaca_</v>
+        <v>lucaswallaceftt</v>
       </c>
       <c r="B544">
         <v>1</v>
@@ -8018,7 +8018,7 @@
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>jose_carlos_baixote</v>
+        <v>lilianvillaca_</v>
       </c>
       <c r="B545">
         <v>1</v>
@@ -8032,7 +8032,7 @@
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>projeto_amigos_de_ouro</v>
+        <v>jose_carlos_baixote</v>
       </c>
       <c r="B546">
         <v>1</v>
@@ -8046,7 +8046,7 @@
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>gratidao_jesus2026</v>
+        <v>projeto_amigos_de_ouro</v>
       </c>
       <c r="B547">
         <v>1</v>
@@ -8060,7 +8060,7 @@
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>sabe_de_uma_coisa2026</v>
+        <v>gratidao_jesus2026</v>
       </c>
       <c r="B548">
         <v>1</v>
@@ -8074,7 +8074,7 @@
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>alinedoprojeto</v>
+        <v>sabe_de_uma_coisa2026</v>
       </c>
       <c r="B549">
         <v>1</v>
@@ -8088,7 +8088,7 @@
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>dani120690</v>
+        <v>alinedoprojeto</v>
       </c>
       <c r="B550">
         <v>1</v>
@@ -8102,7 +8102,7 @@
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>raonasthai</v>
+        <v>dani120690</v>
       </c>
       <c r="B551">
         <v>1</v>
@@ -8116,7 +8116,7 @@
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>adonaibjj_grip</v>
+        <v>raonasthai</v>
       </c>
       <c r="B552">
         <v>1</v>
@@ -8130,7 +8130,7 @@
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>arturbambam</v>
+        <v>adonaibjj_grip</v>
       </c>
       <c r="B553">
         <v>1</v>
@@ -8144,7 +8144,7 @@
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>cebolajj167</v>
+        <v>arturbambam</v>
       </c>
       <c r="B554">
         <v>1</v>
@@ -8158,7 +8158,7 @@
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>danieljsantoss_</v>
+        <v>cebolajj167</v>
       </c>
       <c r="B555">
         <v>1</v>
@@ -8172,7 +8172,7 @@
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>hermaan10_</v>
+        <v>danieljsantoss_</v>
       </c>
       <c r="B556">
         <v>1</v>
@@ -8186,7 +8186,7 @@
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>markakasocks</v>
+        <v>hermaan10_</v>
       </c>
       <c r="B557">
         <v>1</v>
@@ -8200,7 +8200,7 @@
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>hunter.mccrary</v>
+        <v>markakasocks</v>
       </c>
       <c r="B558">
         <v>1</v>
@@ -8214,7 +8214,7 @@
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>davidpina_047</v>
+        <v>hunter.mccrary</v>
       </c>
       <c r="B559">
         <v>1</v>
@@ -8228,7 +8228,7 @@
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>odivaldo_lobo</v>
+        <v>davidpina_047</v>
       </c>
       <c r="B560">
         <v>1</v>
@@ -8242,7 +8242,7 @@
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>rodrigojansen_</v>
+        <v>odivaldo_lobo</v>
       </c>
       <c r="B561">
         <v>1</v>
@@ -8256,7 +8256,7 @@
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>flavia_gomes_29</v>
+        <v>rodrigojansen_</v>
       </c>
       <c r="B562">
         <v>1</v>
@@ -8270,7 +8270,7 @@
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>pelevermelha.uniformes</v>
+        <v>flavia_gomes_29</v>
       </c>
       <c r="B563">
         <v>1</v>
@@ -8284,7 +8284,7 @@
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>joao_lins_muaythai</v>
+        <v>pelevermelha.uniformes</v>
       </c>
       <c r="B564">
         <v>1</v>
@@ -8298,7 +8298,7 @@
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>omarcotomaz</v>
+        <v>joao_lins_muaythai</v>
       </c>
       <c r="B565">
         <v>1</v>
@@ -8312,7 +8312,7 @@
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>alphavillesup</v>
+        <v>omarcotomaz</v>
       </c>
       <c r="B566">
         <v>1</v>
@@ -8326,7 +8326,7 @@
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>ricieritonan</v>
+        <v>alphavillesup</v>
       </c>
       <c r="B567">
         <v>1</v>
@@ -8340,7 +8340,7 @@
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>lucasampaio</v>
+        <v>ricieritonan</v>
       </c>
       <c r="B568">
         <v>1</v>
@@ -8354,7 +8354,7 @@
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>manmoska</v>
+        <v>lucasampaio</v>
       </c>
       <c r="B569">
         <v>1</v>
@@ -8368,7 +8368,7 @@
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>renatoevangelistaa</v>
+        <v>manmoska</v>
       </c>
       <c r="B570">
         <v>1</v>
@@ -8382,7 +8382,7 @@
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>cassius.paula</v>
+        <v>renatoevangelistaa</v>
       </c>
       <c r="B571">
         <v>1</v>
@@ -8396,7 +8396,7 @@
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>ctt.casaestopteam</v>
+        <v>cassius.paula</v>
       </c>
       <c r="B572">
         <v>1</v>
@@ -8410,7 +8410,7 @@
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>moisespira</v>
+        <v>ctt.casaestopteam</v>
       </c>
       <c r="B573">
         <v>1</v>
@@ -8424,7 +8424,7 @@
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>rodrigolidiosales</v>
+        <v>moisespira</v>
       </c>
       <c r="B574">
         <v>1</v>
@@ -8438,7 +8438,7 @@
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>claudioribeiro_ufc</v>
+        <v>rodrigolidiosales</v>
       </c>
       <c r="B575">
         <v>1</v>
@@ -8452,7 +8452,7 @@
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>marciocatenacci</v>
+        <v>claudioribeiro_ufc</v>
       </c>
       <c r="B576">
         <v>1</v>
@@ -8466,7 +8466,7 @@
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>cristiane.c.santana</v>
+        <v>marciocatenacci</v>
       </c>
       <c r="B577">
         <v>1</v>
@@ -8480,7 +8480,7 @@
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>ariel_alvees</v>
+        <v>cristiane.c.santana</v>
       </c>
       <c r="B578">
         <v>1</v>
@@ -8494,7 +8494,7 @@
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>flahvinhotreinador</v>
+        <v>ariel_alvees</v>
       </c>
       <c r="B579">
         <v>1</v>
@@ -8508,7 +8508,7 @@
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>selma.oscar12</v>
+        <v>flahvinhotreinador</v>
       </c>
       <c r="B580">
         <v>1</v>
@@ -8522,7 +8522,7 @@
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>romulobelarmino</v>
+        <v>selma.oscar12</v>
       </c>
       <c r="B581">
         <v>1</v>
@@ -8536,7 +8536,7 @@
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>alberto_garcia_queiroz_junior</v>
+        <v>romulobelarmino</v>
       </c>
       <c r="B582">
         <v>1</v>
@@ -8550,7 +8550,7 @@
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>isasantos1404</v>
+        <v>alberto_garcia_queiroz_junior</v>
       </c>
       <c r="B583">
         <v>1</v>
@@ -8564,7 +8564,7 @@
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>fernandamourabjj</v>
+        <v>isasantos1404</v>
       </c>
       <c r="B584">
         <v>1</v>
@@ -8578,7 +8578,7 @@
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>larissamartinsbjj</v>
+        <v>fernandamourabjj</v>
       </c>
       <c r="B585">
         <v>1</v>
@@ -8592,7 +8592,7 @@
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>gabrielsoaresbjj</v>
+        <v>larissamartinsbjj</v>
       </c>
       <c r="B586">
         <v>1</v>
@@ -8606,7 +8606,7 @@
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>leitefelippez</v>
+        <v>gabrielsoaresbjj</v>
       </c>
       <c r="B587">
         <v>1</v>
@@ -8620,7 +8620,7 @@
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>israelbahiensebraz</v>
+        <v>leitefelippez</v>
       </c>
       <c r="B588">
         <v>1</v>
@@ -8634,7 +8634,7 @@
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>titosbjj</v>
+        <v>israelbahiensebraz</v>
       </c>
       <c r="B589">
         <v>1</v>
@@ -8648,7 +8648,7 @@
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>aldomanuel1994</v>
+        <v>titosbjj</v>
       </c>
       <c r="B590">
         <v>1</v>
@@ -8662,7 +8662,7 @@
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>x_xpatto</v>
+        <v>aldomanuel1994</v>
       </c>
       <c r="B591">
         <v>1</v>
@@ -8676,7 +8676,7 @@
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>keep.itpushinnn</v>
+        <v>x_xpatto</v>
       </c>
       <c r="B592">
         <v>1</v>
@@ -8690,7 +8690,7 @@
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>johnnydesinfluencer</v>
+        <v>keep.itpushinnn</v>
       </c>
       <c r="B593">
         <v>1</v>
@@ -8704,7 +8704,7 @@
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>ana.cristina.uno</v>
+        <v>johnnydesinfluencer</v>
       </c>
       <c r="B594">
         <v>1</v>
@@ -8718,7 +8718,7 @@
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>pbmoments_</v>
+        <v>ana.cristina.uno</v>
       </c>
       <c r="B595">
         <v>1</v>
@@ -8732,7 +8732,7 @@
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>rick.santosz</v>
+        <v>pbmoments_</v>
       </c>
       <c r="B596">
         <v>1</v>
@@ -8746,7 +8746,7 @@
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>eriikdossantoos</v>
+        <v>rick.santosz</v>
       </c>
       <c r="B597">
         <v>1</v>
@@ -8760,7 +8760,7 @@
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>sp__theus</v>
+        <v>eriikdossantoos</v>
       </c>
       <c r="B598">
         <v>1</v>
@@ -8774,7 +8774,7 @@
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>guihs_cardoso</v>
+        <v>sp__theus</v>
       </c>
       <c r="B599">
         <v>1</v>
@@ -8788,7 +8788,7 @@
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>jeffersonliu2022</v>
+        <v>guihs_cardoso</v>
       </c>
       <c r="B600">
         <v>1</v>
@@ -8802,7 +8802,7 @@
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>pettys2298</v>
+        <v>jeffersonliu2022</v>
       </c>
       <c r="B601">
         <v>1</v>
@@ -8816,7 +8816,7 @@
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>jhonny.2302_aritamma</v>
+        <v>pettys2298</v>
       </c>
       <c r="B602">
         <v>1</v>
@@ -8830,7 +8830,7 @@
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>ph_castroh</v>
+        <v>jhonny.2302_aritamma</v>
       </c>
       <c r="B603">
         <v>1</v>
@@ -8844,7 +8844,7 @@
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>paulokami.mma</v>
+        <v>ph_castroh</v>
       </c>
       <c r="B604">
         <v>1</v>
@@ -8858,7 +8858,7 @@
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>generaldantas</v>
+        <v>paulokami.mma</v>
       </c>
       <c r="B605">
         <v>1</v>
@@ -8872,7 +8872,7 @@
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>gi.liimaa_</v>
+        <v>generaldantas</v>
       </c>
       <c r="B606">
         <v>1</v>
@@ -8886,7 +8886,7 @@
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>_murilo_06</v>
+        <v>gi.liimaa_</v>
       </c>
       <c r="B607">
         <v>1</v>
@@ -8900,7 +8900,7 @@
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>biabezerra88</v>
+        <v>_murilo_06</v>
       </c>
       <c r="B608">
         <v>1</v>
@@ -8914,7 +8914,7 @@
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>geovannaalc_</v>
+        <v>biabezerra88</v>
       </c>
       <c r="B609">
         <v>1</v>
@@ -8928,7 +8928,7 @@
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>joselia_1980</v>
+        <v>geovannaalc_</v>
       </c>
       <c r="B610">
         <v>1</v>
@@ -8942,7 +8942,7 @@
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>silva_junior1979</v>
+        <v>joselia_1980</v>
       </c>
       <c r="B611">
         <v>1</v>
@@ -8956,7 +8956,7 @@
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>andreloliva12</v>
+        <v>silva_junior1979</v>
       </c>
       <c r="B612">
         <v>1</v>
@@ -8970,7 +8970,7 @@
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>soniarochaco</v>
+        <v>andreloliva12</v>
       </c>
       <c r="B613">
         <v>1</v>
@@ -8984,7 +8984,7 @@
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>leandro_pedro7</v>
+        <v>soniarochaco</v>
       </c>
       <c r="B614">
         <v>1</v>
@@ -8998,7 +8998,7 @@
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>camillinhamma</v>
+        <v>leandro_pedro7</v>
       </c>
       <c r="B615">
         <v>1</v>
@@ -9012,7 +9012,7 @@
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>martins.rauanee</v>
+        <v>camillinhamma</v>
       </c>
       <c r="B616">
         <v>1</v>
@@ -9026,7 +9026,7 @@
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>ever.soulson</v>
+        <v>martins.rauanee</v>
       </c>
       <c r="B617">
         <v>1</v>
@@ -9040,7 +9040,7 @@
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>mestrevascobento</v>
+        <v>ever.soulson</v>
       </c>
       <c r="B618">
         <v>1</v>
@@ -9054,7 +9054,7 @@
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>bernardocavalcanti1</v>
+        <v>mestrevascobento</v>
       </c>
       <c r="B619">
         <v>1</v>
@@ -9068,7 +9068,7 @@
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>terapeuta_moniquedias</v>
+        <v>bernardocavalcanti1</v>
       </c>
       <c r="B620">
         <v>1</v>
@@ -9082,7 +9082,7 @@
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>santos39roger</v>
+        <v>terapeuta_moniquedias</v>
       </c>
       <c r="B621">
         <v>1</v>
@@ -9096,7 +9096,7 @@
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>dcoops2</v>
+        <v>santos39roger</v>
       </c>
       <c r="B622">
         <v>1</v>
@@ -9110,7 +9110,7 @@
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>ricardosousa811</v>
+        <v>dcoops2</v>
       </c>
       <c r="B623">
         <v>1</v>
@@ -9124,7 +9124,7 @@
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>ludelmaraujo</v>
+        <v>ricardosousa811</v>
       </c>
       <c r="B624">
         <v>1</v>
@@ -9138,7 +9138,7 @@
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>homemdeita</v>
+        <v>ludelmaraujo</v>
       </c>
       <c r="B625">
         <v>1</v>
@@ -9152,7 +9152,7 @@
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>victorxferreira</v>
+        <v>homemdeita</v>
       </c>
       <c r="B626">
         <v>1</v>
@@ -9166,7 +9166,7 @@
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>eimysalazar</v>
+        <v>victorxferreira</v>
       </c>
       <c r="B627">
         <v>1</v>
@@ -9180,7 +9180,7 @@
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>oficialrichardsilva_ice_men</v>
+        <v>eimysalazar</v>
       </c>
       <c r="B628">
         <v>1</v>
@@ -9194,7 +9194,7 @@
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>axiaaly</v>
+        <v>oficialrichardsilva_ice_men</v>
       </c>
       <c r="B629">
         <v>1</v>
@@ -9208,7 +9208,7 @@
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>renatogomes769</v>
+        <v>axiaaly</v>
       </c>
       <c r="B630">
         <v>1</v>
@@ -9222,7 +9222,7 @@
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>adrianoblessed89</v>
+        <v>renatogomes769</v>
       </c>
       <c r="B631">
         <v>1</v>
@@ -9236,7 +9236,7 @@
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>dinhomoraisoficial</v>
+        <v>adrianoblessed89</v>
       </c>
       <c r="B632">
         <v>1</v>
@@ -9250,7 +9250,7 @@
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>santosriveiros18737383</v>
+        <v>dinhomoraisoficial</v>
       </c>
       <c r="B633">
         <v>1</v>
@@ -9264,7 +9264,7 @@
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>sr.dpaula10</v>
+        <v>santosriveiros18737383</v>
       </c>
       <c r="B634">
         <v>1</v>
@@ -9278,7 +9278,7 @@
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>pazzini__</v>
+        <v>sr.dpaula10</v>
       </c>
       <c r="B635">
         <v>1</v>
@@ -9292,7 +9292,7 @@
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>thiagomoisesmma</v>
+        <v>pazzini__</v>
       </c>
       <c r="B636">
         <v>1</v>
@@ -9306,7 +9306,7 @@
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>dobby_1968</v>
+        <v>thiagomoisesmma</v>
       </c>
       <c r="B637">
         <v>1</v>
@@ -9320,7 +9320,7 @@
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>ricardogabriel.sr</v>
+        <v>dobby_1968</v>
       </c>
       <c r="B638">
         <v>1</v>
@@ -9334,7 +9334,7 @@
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>indiopersonalfight</v>
+        <v>ricardogabriel.sr</v>
       </c>
       <c r="B639">
         <v>1</v>
@@ -9348,7 +9348,7 @@
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>_samu35</v>
+        <v>indiopersonalfight</v>
       </c>
       <c r="B640">
         <v>1</v>
@@ -9362,7 +9362,7 @@
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>1felipe.bjj</v>
+        <v>_samu35</v>
       </c>
       <c r="B641">
         <v>1</v>
@@ -9376,7 +9376,7 @@
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>odennismagalhaes</v>
+        <v>1felipe.bjj</v>
       </c>
       <c r="B642">
         <v>1</v>
@@ -9390,7 +9390,7 @@
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>remarchina</v>
+        <v>odennismagalhaes</v>
       </c>
       <c r="B643">
         <v>1</v>
@@ -9404,7 +9404,7 @@
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>blesed578</v>
+        <v>remarchina</v>
       </c>
       <c r="B644">
         <v>1</v>
@@ -9418,7 +9418,7 @@
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>yago_08k</v>
+        <v>blesed578</v>
       </c>
       <c r="B645">
         <v>1</v>
@@ -9432,7 +9432,7 @@
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>maribrittos22</v>
+        <v>yago_08k</v>
       </c>
       <c r="B646">
         <v>1</v>
@@ -9446,7 +9446,7 @@
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>grupoohplanooficial</v>
+        <v>maribrittos22</v>
       </c>
       <c r="B647">
         <v>1</v>
@@ -9460,7 +9460,7 @@
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>rxdi_mns</v>
+        <v>grupoohplanooficial</v>
       </c>
       <c r="B648">
         <v>1</v>
@@ -9474,7 +9474,7 @@
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>almeida_.e7</v>
+        <v>rxdi_mns</v>
       </c>
       <c r="B649">
         <v>1</v>
@@ -9488,7 +9488,7 @@
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>dyrodriguesohplano</v>
+        <v>almeida_.e7</v>
       </c>
       <c r="B650">
         <v>1</v>
@@ -9502,7 +9502,7 @@
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>lucianatpiccelli</v>
+        <v>dyrodriguesohplano</v>
       </c>
       <c r="B651">
         <v>1</v>
@@ -9516,7 +9516,7 @@
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>fe_.faggi</v>
+        <v>lucianatpiccelli</v>
       </c>
       <c r="B652">
         <v>1</v>
@@ -9530,7 +9530,7 @@
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>allves___46</v>
+        <v>fe_.faggi</v>
       </c>
       <c r="B653">
         <v>1</v>
@@ -9544,7 +9544,7 @@
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>ottoniisrael</v>
+        <v>allves___46</v>
       </c>
       <c r="B654">
         <v>1</v>
@@ -9558,7 +9558,7 @@
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>_.carlos.2x._</v>
+        <v>ottoniisrael</v>
       </c>
       <c r="B655">
         <v>1</v>
@@ -9572,7 +9572,7 @@
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>guilherme.duartesilva</v>
+        <v>_.carlos.2x._</v>
       </c>
       <c r="B656">
         <v>1</v>
@@ -9586,7 +9586,7 @@
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>davi.cb</v>
+        <v>guilherme.duartesilva</v>
       </c>
       <c r="B657">
         <v>1</v>
@@ -9600,7 +9600,7 @@
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>abbasrizvi2204</v>
+        <v>davi.cb</v>
       </c>
       <c r="B658">
         <v>1</v>
@@ -9614,7 +9614,7 @@
     </row>
     <row r="659">
       <c r="A659" t="str">
-        <v>nulife2day</v>
+        <v>abbasrizvi2204</v>
       </c>
       <c r="B659">
         <v>1</v>
@@ -9628,7 +9628,7 @@
     </row>
     <row r="660">
       <c r="A660" t="str">
-        <v>elnaggar_85</v>
+        <v>nulife2day</v>
       </c>
       <c r="B660">
         <v>1</v>
@@ -9642,7 +9642,7 @@
     </row>
     <row r="661">
       <c r="A661" t="str">
-        <v>bammer2026</v>
+        <v>elnaggar_85</v>
       </c>
       <c r="B661">
         <v>1</v>
@@ -9656,7 +9656,7 @@
     </row>
     <row r="662">
       <c r="A662" t="str">
-        <v>yon0sab0</v>
+        <v>bammer2026</v>
       </c>
       <c r="B662">
         <v>1</v>
@@ -9670,7 +9670,7 @@
     </row>
     <row r="663">
       <c r="A663" t="str">
-        <v>thizzlenik</v>
+        <v>yon0sab0</v>
       </c>
       <c r="B663">
         <v>1</v>
@@ -9684,7 +9684,7 @@
     </row>
     <row r="664">
       <c r="A664" t="str">
-        <v>dogodoy</v>
+        <v>thizzlenik</v>
       </c>
       <c r="B664">
         <v>1</v>
@@ -9698,7 +9698,7 @@
     </row>
     <row r="665">
       <c r="A665" t="str">
-        <v>cinemarianophoto</v>
+        <v>dogodoy</v>
       </c>
       <c r="B665">
         <v>1</v>
@@ -9712,7 +9712,7 @@
     </row>
     <row r="666">
       <c r="A666" t="str">
-        <v>nati.monteiro</v>
+        <v>cinemarianophoto</v>
       </c>
       <c r="B666">
         <v>1</v>
@@ -9726,7 +9726,7 @@
     </row>
     <row r="667">
       <c r="A667" t="str">
-        <v>boeno_rafael</v>
+        <v>nati.monteiro</v>
       </c>
       <c r="B667">
         <v>1</v>
@@ -9740,7 +9740,7 @@
     </row>
     <row r="668">
       <c r="A668" t="str">
-        <v>claudio_tikar</v>
+        <v>boeno_rafael</v>
       </c>
       <c r="B668">
         <v>1</v>
@@ -9754,7 +9754,7 @@
     </row>
     <row r="669">
       <c r="A669" t="str">
-        <v>mauricio_dutra_m</v>
+        <v>claudio_tikar</v>
       </c>
       <c r="B669">
         <v>1</v>
@@ -9768,7 +9768,7 @@
     </row>
     <row r="670">
       <c r="A670" t="str">
-        <v>s_giofe</v>
+        <v>mauricio_dutra_m</v>
       </c>
       <c r="B670">
         <v>1</v>
@@ -9782,7 +9782,7 @@
     </row>
     <row r="671">
       <c r="A671" t="str">
-        <v>1tiagomonteiro</v>
+        <v>s_giofe</v>
       </c>
       <c r="B671">
         <v>1</v>
@@ -9796,7 +9796,7 @@
     </row>
     <row r="672">
       <c r="A672" t="str">
-        <v>nautinhor7</v>
+        <v>1tiagomonteiro</v>
       </c>
       <c r="B672">
         <v>1</v>
@@ -9810,7 +9810,7 @@
     </row>
     <row r="673">
       <c r="A673" t="str">
-        <v>lucaspaes047</v>
+        <v>nautinhor7</v>
       </c>
       <c r="B673">
         <v>1</v>
@@ -9824,7 +9824,7 @@
     </row>
     <row r="674">
       <c r="A674" t="str">
-        <v>bmarinhorogerio</v>
+        <v>lucaspaes047</v>
       </c>
       <c r="B674">
         <v>1</v>
@@ -9838,7 +9838,7 @@
     </row>
     <row r="675">
       <c r="A675" t="str">
-        <v>klaiver.027xx</v>
+        <v>bmarinhorogerio</v>
       </c>
       <c r="B675">
         <v>1</v>
@@ -9852,7 +9852,7 @@
     </row>
     <row r="676">
       <c r="A676" t="str">
-        <v>jefte_jizreel</v>
+        <v>klaiver.027xx</v>
       </c>
       <c r="B676">
         <v>1</v>
@@ -9866,7 +9866,7 @@
     </row>
     <row r="677">
       <c r="A677" t="str">
-        <v>clinicaikiro</v>
+        <v>jefte_jizreel</v>
       </c>
       <c r="B677">
         <v>1</v>
@@ -9880,7 +9880,7 @@
     </row>
     <row r="678">
       <c r="A678" t="str">
-        <v>cabreuvamma</v>
+        <v>clinicaikiro</v>
       </c>
       <c r="B678">
         <v>1</v>
@@ -9894,7 +9894,7 @@
     </row>
     <row r="679">
       <c r="A679" t="str">
-        <v>use.ellasfit</v>
+        <v>cabreuvamma</v>
       </c>
       <c r="B679">
         <v>1</v>
@@ -9908,7 +9908,7 @@
     </row>
     <row r="680">
       <c r="A680" t="str">
-        <v>patriciarichteroficial</v>
+        <v>use.ellasfit</v>
       </c>
       <c r="B680">
         <v>1</v>
@@ -9922,7 +9922,7 @@
     </row>
     <row r="681">
       <c r="A681" t="str">
-        <v>kauan_mantas</v>
+        <v>patriciarichteroficial</v>
       </c>
       <c r="B681">
         <v>1</v>
@@ -9936,7 +9936,7 @@
     </row>
     <row r="682">
       <c r="A682" t="str">
-        <v>emersonapache</v>
+        <v>kauan_mantas</v>
       </c>
       <c r="B682">
         <v>1</v>
@@ -9950,7 +9950,7 @@
     </row>
     <row r="683">
       <c r="A683" t="str">
-        <v>nataliavidal965</v>
+        <v>emersonapache</v>
       </c>
       <c r="B683">
         <v>1</v>
@@ -9964,7 +9964,7 @@
     </row>
     <row r="684">
       <c r="A684" t="str">
-        <v>ruanpantojanutricionista</v>
+        <v>nataliavidal965</v>
       </c>
       <c r="B684">
         <v>1</v>
@@ -9978,7 +9978,7 @@
     </row>
     <row r="685">
       <c r="A685" t="str">
-        <v>luizpaulomma</v>
+        <v>ruanpantojanutricionista</v>
       </c>
       <c r="B685">
         <v>1</v>
@@ -9992,7 +9992,7 @@
     </row>
     <row r="686">
       <c r="A686" t="str">
-        <v>epicjoel2022</v>
+        <v>luizpaulomma</v>
       </c>
       <c r="B686">
         <v>1</v>
@@ -10006,7 +10006,7 @@
     </row>
     <row r="687">
       <c r="A687" t="str">
-        <v>tvlinsoficial</v>
+        <v>epicjoel2022</v>
       </c>
       <c r="B687">
         <v>1</v>
@@ -10020,7 +10020,7 @@
     </row>
     <row r="688">
       <c r="A688" t="str">
-        <v>_itamar_maximo</v>
+        <v>tvlinsoficial</v>
       </c>
       <c r="B688">
         <v>1</v>
@@ -10034,7 +10034,7 @@
     </row>
     <row r="689">
       <c r="A689" t="str">
-        <v>mg._silvaa_</v>
+        <v>_itamar_maximo</v>
       </c>
       <c r="B689">
         <v>1</v>
@@ -10048,7 +10048,7 @@
     </row>
     <row r="690">
       <c r="A690" t="str">
-        <v>desativado_no_off33</v>
+        <v>mg._silvaa_</v>
       </c>
       <c r="B690">
         <v>1</v>
@@ -10062,35 +10062,35 @@
     </row>
     <row r="691">
       <c r="A691" t="str">
-        <v>lucasbaddoure</v>
+        <v>desativado_no_off33</v>
       </c>
       <c r="B691">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C691">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D691">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="str">
-        <v>paulo_rafa_personal</v>
+        <v>lucasbaddoure</v>
       </c>
       <c r="B692">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C692">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D692">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="str">
-        <v>endurance_guia</v>
+        <v>paulo_rafa_personal</v>
       </c>
       <c r="B693">
         <v>1</v>
@@ -10104,7 +10104,7 @@
     </row>
     <row r="694">
       <c r="A694" t="str">
-        <v>cadupereirss</v>
+        <v>endurance_guia</v>
       </c>
       <c r="B694">
         <v>1</v>
@@ -10118,7 +10118,7 @@
     </row>
     <row r="695">
       <c r="A695" t="str">
-        <v>instrutorindiovs</v>
+        <v>cadupereirss</v>
       </c>
       <c r="B695">
         <v>1</v>
@@ -10132,7 +10132,7 @@
     </row>
     <row r="696">
       <c r="A696" t="str">
-        <v>lopes.felipe13</v>
+        <v>instrutorindiovs</v>
       </c>
       <c r="B696">
         <v>1</v>
@@ -10146,7 +10146,7 @@
     </row>
     <row r="697">
       <c r="A697" t="str">
-        <v>marchi_vinicius</v>
+        <v>lopes.felipe13</v>
       </c>
       <c r="B697">
         <v>1</v>
@@ -10160,7 +10160,7 @@
     </row>
     <row r="698">
       <c r="A698" t="str">
-        <v>rafa_speda</v>
+        <v>marchi_vinicius</v>
       </c>
       <c r="B698">
         <v>1</v>
@@ -10174,7 +10174,7 @@
     </row>
     <row r="699">
       <c r="A699" t="str">
-        <v>m1guelmolina</v>
+        <v>rafa_speda</v>
       </c>
       <c r="B699">
         <v>1</v>
@@ -10188,16 +10188,16 @@
     </row>
     <row r="700">
       <c r="A700" t="str">
-        <v>dudaadantass</v>
+        <v>m1guelmolina</v>
       </c>
       <c r="B700">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C700">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D700">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="701">
@@ -14115,7 +14115,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D97"/>
+  <dimension ref="A1:D100"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -14136,13 +14136,13 @@
         <v>peacegrappler</v>
       </c>
       <c r="B2">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>109</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3">
@@ -14181,7 +14181,7 @@
         <v>10</v>
       </c>
       <c r="C5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D5">
         <v>11</v>
@@ -14192,7 +14192,7 @@
         <v>pedr00jj</v>
       </c>
       <c r="B6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -14220,13 +14220,13 @@
         <v>sirleneferreiradiasdias</v>
       </c>
       <c r="B8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C8">
         <v>5</v>
       </c>
       <c r="D8">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -14237,10 +14237,10 @@
         <v>3</v>
       </c>
       <c r="C9">
+        <v>15</v>
+      </c>
+      <c r="D9">
         <v>13</v>
-      </c>
-      <c r="D9">
-        <v>11</v>
       </c>
     </row>
     <row r="10">
@@ -14399,21 +14399,21 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>propeace_fight</v>
+        <v>adriano.trator</v>
       </c>
       <c r="B21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D21">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>rm.nicki</v>
+        <v>propeace_fight</v>
       </c>
       <c r="B22">
         <v>2</v>
@@ -14427,7 +14427,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>lili.munix</v>
+        <v>rm.nicki</v>
       </c>
       <c r="B23">
         <v>2</v>
@@ -14441,7 +14441,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>rayn.avaro</v>
+        <v>lili.munix</v>
       </c>
       <c r="B24">
         <v>2</v>
@@ -14455,7 +14455,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>arafight_pesc</v>
+        <v>rayn.avaro</v>
       </c>
       <c r="B25">
         <v>2</v>
@@ -14469,7 +14469,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>kamile_oliveria_10</v>
+        <v>arafight_pesc</v>
       </c>
       <c r="B26">
         <v>2</v>
@@ -14483,7 +14483,7 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>malu832757</v>
+        <v>kamile_oliveria_10</v>
       </c>
       <c r="B27">
         <v>2</v>
@@ -14497,7 +14497,7 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>gdazuera</v>
+        <v>malu832757</v>
       </c>
       <c r="B28">
         <v>2</v>
@@ -14511,7 +14511,7 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>sueli_ferreira48</v>
+        <v>gdazuera</v>
       </c>
       <c r="B29">
         <v>2</v>
@@ -14520,21 +14520,21 @@
         <v>0</v>
       </c>
       <c r="D29">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>adriano.trator</v>
+        <v>sueli_ferreira48</v>
       </c>
       <c r="B30">
         <v>2</v>
       </c>
       <c r="C30">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -15225,27 +15225,27 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>leobahiamma</v>
+        <v>edebetim_</v>
       </c>
       <c r="B80">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C80">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D80">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>pedro_pavin_</v>
+        <v>leobahiamma</v>
       </c>
       <c r="B81">
         <v>0</v>
       </c>
       <c r="C81">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D81">
         <v>1</v>
@@ -15253,13 +15253,13 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>allan10adm</v>
+        <v>dudaadantass</v>
       </c>
       <c r="B82">
         <v>0</v>
       </c>
       <c r="C82">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D82">
         <v>1</v>
@@ -15267,7 +15267,7 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>ismael.marreta_ufc</v>
+        <v>pedro_pavin_</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -15281,7 +15281,7 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>joandersontubarao_ufc</v>
+        <v>allan10adm</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -15295,7 +15295,7 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>gaby_alves07</v>
+        <v>ismael.marreta_ufc</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -15309,7 +15309,7 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>diegosilvabjjoficial</v>
+        <v>joandersontubarao_ufc</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -15323,7 +15323,7 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>mvp_lutas</v>
+        <v>gaby_alves07</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -15337,7 +15337,7 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>dudaadantass</v>
+        <v>diegosilvabjjoficial</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -15351,7 +15351,7 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>pulsepro.nutrition</v>
+        <v>mvp_lutas</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -15360,12 +15360,12 @@
         <v>1</v>
       </c>
       <c r="D89">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>herbeth_indiomma</v>
+        <v>luis_pequeno_mma</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -15374,12 +15374,12 @@
         <v>1</v>
       </c>
       <c r="D90">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>danielbzk_</v>
+        <v>pulsepro.nutrition</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -15393,7 +15393,7 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>jp.mdc</v>
+        <v>herbeth_indiomma</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -15407,7 +15407,7 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>rosacostasousa36</v>
+        <v>danielbzk_</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -15421,7 +15421,7 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>cathya_ferreira</v>
+        <v>jp.mdc</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -15435,7 +15435,7 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>1210gi</v>
+        <v>rosacostasousa36</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -15449,7 +15449,7 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>juanx.pontes</v>
+        <v>cathya_ferreira</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -15463,21 +15463,63 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
+        <v>1210gi</v>
+      </c>
+      <c r="B97">
+        <v>0</v>
+      </c>
+      <c r="C97">
+        <v>1</v>
+      </c>
+      <c r="D97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>juanx.pontes</v>
+      </c>
+      <c r="B98">
+        <v>0</v>
+      </c>
+      <c r="C98">
+        <v>1</v>
+      </c>
+      <c r="D98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
         <v>_oliveira09_</v>
       </c>
-      <c r="B97">
-        <v>0</v>
-      </c>
-      <c r="C97">
-        <v>1</v>
-      </c>
-      <c r="D97">
+      <c r="B99">
+        <v>0</v>
+      </c>
+      <c r="C99">
+        <v>1</v>
+      </c>
+      <c r="D99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>mestreviniciusreviravolta</v>
+      </c>
+      <c r="B100">
+        <v>0</v>
+      </c>
+      <c r="C100">
+        <v>1</v>
+      </c>
+      <c r="D100">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D97"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D100"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Engagement Rankings 2026-07.xlsx
+++ b/Engagement Rankings 2026-07.xlsx
@@ -419,13 +419,13 @@
         <v>peacegrappler</v>
       </c>
       <c r="B2">
-        <v>13513</v>
+        <v>13518</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>12235</v>
+        <v>12240</v>
       </c>
     </row>
     <row r="3">
@@ -475,13 +475,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B6">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="C6">
         <v>16</v>
       </c>
       <c r="D6">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="7">
@@ -545,13 +545,13 @@
         <v>combintel</v>
       </c>
       <c r="B11">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="C11">
         <v>2</v>
       </c>
       <c r="D11">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12">
@@ -629,7 +629,7 @@
         <v>mmmarc20</v>
       </c>
       <c r="B17">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>johnmma9</v>
       </c>
       <c r="B18">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C18">
         <v>0</v>
       </c>
       <c r="D18">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="19">
@@ -657,7 +657,7 @@
         <v>masonharper_mma</v>
       </c>
       <c r="B19">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -842,10 +842,10 @@
         <v>41</v>
       </c>
       <c r="C32">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D32">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="33">
@@ -1178,10 +1178,10 @@
         <v>25</v>
       </c>
       <c r="C56">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D56">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="57">
@@ -14136,13 +14136,13 @@
         <v>peacegrappler</v>
       </c>
       <c r="B2">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>120</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3">
@@ -14150,13 +14150,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C3">
         <v>2</v>
       </c>
       <c r="D3">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4">
@@ -14181,10 +14181,10 @@
         <v>10</v>
       </c>
       <c r="C5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
@@ -14237,18 +14237,18 @@
         <v>3</v>
       </c>
       <c r="C9">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D9">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>ismaeldaniell</v>
+        <v>combintel</v>
       </c>
       <c r="B10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -14259,21 +14259,21 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>grapplerfight</v>
+        <v>ismaeldaniell</v>
       </c>
       <c r="B11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>galler_peace</v>
+        <v>grapplerfight</v>
       </c>
       <c r="B12">
         <v>3</v>
@@ -14287,7 +14287,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>thundergrapple</v>
+        <v>galler_peace</v>
       </c>
       <c r="B13">
         <v>3</v>
@@ -14301,7 +14301,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>figh_grappler</v>
+        <v>thundergrapple</v>
       </c>
       <c r="B14">
         <v>3</v>
@@ -14315,7 +14315,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>anayachiottoni</v>
+        <v>figh_grappler</v>
       </c>
       <c r="B15">
         <v>3</v>
@@ -14329,49 +14329,49 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>god.motivacao</v>
+        <v>anayachiottoni</v>
       </c>
       <c r="B16">
         <v>3</v>
       </c>
       <c r="C16">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D16">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>carlos_hm_iglesias</v>
+        <v>god.motivacao</v>
       </c>
       <c r="B17">
         <v>3</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D17">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>ninjatheorist</v>
+        <v>johnmma9</v>
       </c>
       <c r="B18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C18">
         <v>0</v>
       </c>
       <c r="D18">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>helenmacielmma</v>
+        <v>carlos_hm_iglesias</v>
       </c>
       <c r="B19">
         <v>3</v>
@@ -14385,10 +14385,10 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>wesleysepulveda__mma</v>
+        <v>ninjatheorist</v>
       </c>
       <c r="B20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -14399,21 +14399,21 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>adriano.trator</v>
+        <v>helenmacielmma</v>
       </c>
       <c r="B21">
         <v>3</v>
       </c>
       <c r="C21">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>propeace_fight</v>
+        <v>wesleysepulveda__mma</v>
       </c>
       <c r="B22">
         <v>2</v>
@@ -14427,35 +14427,35 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>rm.nicki</v>
+        <v>adriano.trator</v>
       </c>
       <c r="B23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D23">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>lili.munix</v>
+        <v>masonharper_mma</v>
       </c>
       <c r="B24">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C24">
         <v>0</v>
       </c>
       <c r="D24">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>rayn.avaro</v>
+        <v>propeace_fight</v>
       </c>
       <c r="B25">
         <v>2</v>
@@ -14469,7 +14469,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>arafight_pesc</v>
+        <v>rm.nicki</v>
       </c>
       <c r="B26">
         <v>2</v>
@@ -14483,7 +14483,7 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>kamile_oliveria_10</v>
+        <v>lili.munix</v>
       </c>
       <c r="B27">
         <v>2</v>
@@ -14497,7 +14497,7 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>malu832757</v>
+        <v>rayn.avaro</v>
       </c>
       <c r="B28">
         <v>2</v>
@@ -14511,7 +14511,7 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>gdazuera</v>
+        <v>arafight_pesc</v>
       </c>
       <c r="B29">
         <v>2</v>
@@ -14525,7 +14525,7 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>sueli_ferreira48</v>
+        <v>kamile_oliveria_10</v>
       </c>
       <c r="B30">
         <v>2</v>
@@ -14534,12 +14534,12 @@
         <v>0</v>
       </c>
       <c r="D30">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>combintel</v>
+        <v>malu832757</v>
       </c>
       <c r="B31">
         <v>2</v>
@@ -14548,12 +14548,12 @@
         <v>0</v>
       </c>
       <c r="D31">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>ottonimestre</v>
+        <v>gdazuera</v>
       </c>
       <c r="B32">
         <v>2</v>
@@ -14562,12 +14562,12 @@
         <v>0</v>
       </c>
       <c r="D32">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>canalgolpebaixo</v>
+        <v>sueli_ferreira48</v>
       </c>
       <c r="B33">
         <v>2</v>
@@ -14581,7 +14581,7 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>shawlinoficial</v>
+        <v>ottonimestre</v>
       </c>
       <c r="B34">
         <v>2</v>
@@ -14595,10 +14595,10 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>og.mthx</v>
+        <v>canalgolpebaixo</v>
       </c>
       <c r="B35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C35">
         <v>0</v>
@@ -14609,10 +14609,10 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>danielcarmonaconsultor</v>
+        <v>shawlinoficial</v>
       </c>
       <c r="B36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C36">
         <v>0</v>
@@ -14623,7 +14623,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>cristianpsicologo</v>
+        <v>og.mthx</v>
       </c>
       <c r="B37">
         <v>1</v>
@@ -14637,7 +14637,7 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>brcks4breakfast</v>
+        <v>danielcarmonaconsultor</v>
       </c>
       <c r="B38">
         <v>1</v>
@@ -14651,21 +14651,21 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>mma.idiot</v>
+        <v>mmmarc20</v>
       </c>
       <c r="B39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C39">
         <v>0</v>
       </c>
       <c r="D39">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>roger_santosmma</v>
+        <v>cristianpsicologo</v>
       </c>
       <c r="B40">
         <v>1</v>
@@ -14679,7 +14679,7 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>murata_profight</v>
+        <v>brcks4breakfast</v>
       </c>
       <c r="B41">
         <v>1</v>
@@ -14693,7 +14693,7 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>vndcardoso</v>
+        <v>mma.idiot</v>
       </c>
       <c r="B42">
         <v>1</v>
@@ -14707,21 +14707,21 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>jean_ferreira_br</v>
+        <v>roger_santosmma</v>
       </c>
       <c r="B43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C43">
         <v>0</v>
       </c>
       <c r="D43">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>zackdos</v>
+        <v>murata_profight</v>
       </c>
       <c r="B44">
         <v>1</v>
@@ -14735,7 +14735,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>npb.enterprise</v>
+        <v>vndcardoso</v>
       </c>
       <c r="B45">
         <v>1</v>
@@ -14749,21 +14749,21 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>david_sfc19</v>
+        <v>jean_ferreira_br</v>
       </c>
       <c r="B46">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C46">
         <v>0</v>
       </c>
       <c r="D46">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>danielrodrigues1000</v>
+        <v>zackdos</v>
       </c>
       <c r="B47">
         <v>1</v>
@@ -14777,7 +14777,7 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>laisrebeiro10</v>
+        <v>npb.enterprise</v>
       </c>
       <c r="B48">
         <v>1</v>
@@ -14791,7 +14791,7 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>claudineiscorrea</v>
+        <v>david_sfc19</v>
       </c>
       <c r="B49">
         <v>1</v>
@@ -14805,7 +14805,7 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>ottonianalivia</v>
+        <v>danielrodrigues1000</v>
       </c>
       <c r="B50">
         <v>1</v>
@@ -14819,21 +14819,21 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>cassiosants__</v>
+        <v>laisrebeiro10</v>
       </c>
       <c r="B51">
         <v>1</v>
       </c>
       <c r="C51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D51">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>masonharper_mma</v>
+        <v>claudineiscorrea</v>
       </c>
       <c r="B52">
         <v>1</v>
@@ -14842,12 +14842,12 @@
         <v>0</v>
       </c>
       <c r="D52">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>johnmma9</v>
+        <v>ottonianalivia</v>
       </c>
       <c r="B53">
         <v>1</v>
@@ -14856,18 +14856,18 @@
         <v>0</v>
       </c>
       <c r="D53">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>mmmarc20</v>
+        <v>cassiosants__</v>
       </c>
       <c r="B54">
         <v>1</v>
       </c>
       <c r="C54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D54">
         <v>0</v>

--- a/Engagement Rankings 2026-07.xlsx
+++ b/Engagement Rankings 2026-07.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D979"/>
+  <dimension ref="A1:D980"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -419,7 +419,7 @@
         <v>peacegrappler</v>
       </c>
       <c r="B2">
-        <v>13518</v>
+        <v>13519</v>
       </c>
       <c r="C2">
         <v>3</v>
@@ -475,13 +475,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B6">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="C6">
         <v>16</v>
       </c>
       <c r="D6">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="7">
@@ -657,7 +657,7 @@
         <v>masonharper_mma</v>
       </c>
       <c r="B19">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -3090,41 +3090,41 @@
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>cristianpsicologo</v>
+        <v>canalgolpebaixo</v>
       </c>
       <c r="B193">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C193">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D193">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>mah__vergueiro</v>
+        <v>cristianpsicologo</v>
       </c>
       <c r="B194">
+        <v>2</v>
+      </c>
+      <c r="C194">
+        <v>4</v>
+      </c>
+      <c r="D194">
         <v>3</v>
-      </c>
-      <c r="C194">
-        <v>0</v>
-      </c>
-      <c r="D194">
-        <v>0</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>pizzaria.bambina_</v>
+        <v>mah__vergueiro</v>
       </c>
       <c r="B195">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C195">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D195">
         <v>0</v>
@@ -3132,49 +3132,49 @@
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>h.codasqueves</v>
+        <v>pizzaria.bambina_</v>
       </c>
       <c r="B196">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C196">
         <v>1</v>
       </c>
       <c r="D196">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>pauloserrati</v>
+        <v>h.codasqueves</v>
       </c>
       <c r="B197">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C197">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D197">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>alexandreconsentino</v>
+        <v>pauloserrati</v>
       </c>
       <c r="B198">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C198">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D198">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>lipe.ftt</v>
+        <v>alexandreconsentino</v>
       </c>
       <c r="B199">
         <v>4</v>
@@ -3188,7 +3188,7 @@
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>fau_gfs</v>
+        <v>lipe.ftt</v>
       </c>
       <c r="B200">
         <v>4</v>
@@ -3202,21 +3202,21 @@
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>vitorpetrino</v>
+        <v>fau_gfs</v>
       </c>
       <c r="B201">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C201">
         <v>0</v>
       </c>
       <c r="D201">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>thompsonborralho</v>
+        <v>vitorpetrino</v>
       </c>
       <c r="B202">
         <v>3</v>
@@ -3230,7 +3230,7 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>devessonjj</v>
+        <v>thompsonborralho</v>
       </c>
       <c r="B203">
         <v>3</v>
@@ -3244,77 +3244,77 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>espaco_jhayoliveira</v>
+        <v>devessonjj</v>
       </c>
       <c r="B204">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C204">
         <v>0</v>
       </c>
       <c r="D204">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>artewebpersonalizados</v>
+        <v>espaco_jhayoliveira</v>
       </c>
       <c r="B205">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C205">
         <v>0</v>
       </c>
       <c r="D205">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>marcosferreira.ofc1</v>
+        <v>artewebpersonalizados</v>
       </c>
       <c r="B206">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C206">
         <v>0</v>
       </c>
       <c r="D206">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>dgswillian</v>
+        <v>marcosferreira.ofc1</v>
       </c>
       <c r="B207">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C207">
         <v>0</v>
       </c>
       <c r="D207">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>lili.munix</v>
+        <v>dgswillian</v>
       </c>
       <c r="B208">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C208">
         <v>0</v>
       </c>
       <c r="D208">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>victorhenriquebjj</v>
+        <v>lili.munix</v>
       </c>
       <c r="B209">
         <v>2</v>
@@ -3323,12 +3323,12 @@
         <v>0</v>
       </c>
       <c r="D209">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>eduardorobjj</v>
+        <v>victorhenriquebjj</v>
       </c>
       <c r="B210">
         <v>2</v>
@@ -3342,7 +3342,7 @@
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>diego.dieguito.3914</v>
+        <v>eduardorobjj</v>
       </c>
       <c r="B211">
         <v>2</v>
@@ -3356,7 +3356,7 @@
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>aerowellsports</v>
+        <v>diego.dieguito.3914</v>
       </c>
       <c r="B212">
         <v>2</v>
@@ -3370,7 +3370,7 @@
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>royrosiano</v>
+        <v>aerowellsports</v>
       </c>
       <c r="B213">
         <v>2</v>
@@ -3384,7 +3384,7 @@
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>febrancatti</v>
+        <v>royrosiano</v>
       </c>
       <c r="B214">
         <v>2</v>
@@ -3398,7 +3398,7 @@
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>sensei_rogerio_baltazar</v>
+        <v>febrancatti</v>
       </c>
       <c r="B215">
         <v>2</v>
@@ -3412,7 +3412,7 @@
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>jpaulo.mma</v>
+        <v>sensei_rogerio_baltazar</v>
       </c>
       <c r="B216">
         <v>2</v>
@@ -3426,7 +3426,7 @@
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>william_beckett12345</v>
+        <v>jpaulo.mma</v>
       </c>
       <c r="B217">
         <v>2</v>
@@ -3440,7 +3440,7 @@
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>_falcao95_</v>
+        <v>william_beckett12345</v>
       </c>
       <c r="B218">
         <v>2</v>
@@ -3454,7 +3454,7 @@
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>janyson.s</v>
+        <v>_falcao95_</v>
       </c>
       <c r="B219">
         <v>2</v>
@@ -3468,7 +3468,7 @@
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>rodrigo.personal.muaythai</v>
+        <v>janyson.s</v>
       </c>
       <c r="B220">
         <v>2</v>
@@ -3482,7 +3482,7 @@
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>andre_cr_daniel</v>
+        <v>rodrigo.personal.muaythai</v>
       </c>
       <c r="B221">
         <v>2</v>
@@ -3496,7 +3496,7 @@
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>wilsinho.campos</v>
+        <v>andre_cr_daniel</v>
       </c>
       <c r="B222">
         <v>2</v>
@@ -3510,7 +3510,7 @@
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>jheffzao</v>
+        <v>wilsinho.campos</v>
       </c>
       <c r="B223">
         <v>2</v>
@@ -3524,55 +3524,55 @@
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>joandersontubarao_ufc</v>
+        <v>jheffzao</v>
       </c>
       <c r="B224">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C224">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D224">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>felipedasilvalucas.bjj</v>
+        <v>joandersontubarao_ufc</v>
       </c>
       <c r="B225">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C225">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D225">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>motumbo_jr</v>
+        <v>felipedasilvalucas.bjj</v>
       </c>
       <c r="B226">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C226">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D226">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>julianoalicate</v>
+        <v>motumbo_jr</v>
       </c>
       <c r="B227">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C227">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D227">
         <v>1</v>
@@ -3580,16 +3580,16 @@
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>canalgolpebaixo</v>
+        <v>julianoalicate</v>
       </c>
       <c r="B228">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C228">
         <v>1</v>
       </c>
       <c r="D228">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="229">
@@ -5470,63 +5470,63 @@
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>marceloscorzato</v>
+        <v>djsagatoficial</v>
       </c>
       <c r="B363">
         <v>1</v>
       </c>
       <c r="C363">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D363">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>sergio_alves_bjj</v>
+        <v>marceloscorzato</v>
       </c>
       <c r="B364">
         <v>1</v>
       </c>
       <c r="C364">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D364">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>pedro_pavin_</v>
+        <v>sergio_alves_bjj</v>
       </c>
       <c r="B365">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C365">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D365">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>treinaadorrafael</v>
+        <v>pedro_pavin_</v>
       </c>
       <c r="B366">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C366">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D366">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>estevaotoledo</v>
+        <v>treinaadorrafael</v>
       </c>
       <c r="B367">
         <v>1</v>
@@ -5540,13 +5540,13 @@
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>djsagatoficial</v>
+        <v>estevaotoledo</v>
       </c>
       <c r="B368">
         <v>1</v>
       </c>
       <c r="C368">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D368">
         <v>0</v>
@@ -10482,35 +10482,35 @@
     </row>
     <row r="721">
       <c r="A721" t="str">
-        <v>luizcosta_mma</v>
+        <v>peacegrappler_podcast</v>
       </c>
       <c r="B721">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C721">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D721">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="722">
       <c r="A722" t="str">
-        <v>taylor_71kg</v>
+        <v>luizcosta_mma</v>
       </c>
       <c r="B722">
         <v>0</v>
       </c>
       <c r="C722">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D722">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="723">
       <c r="A723" t="str">
-        <v>_vpft</v>
+        <v>taylor_71kg</v>
       </c>
       <c r="B723">
         <v>0</v>
@@ -10524,21 +10524,21 @@
     </row>
     <row r="724">
       <c r="A724" t="str">
-        <v>viniciustbf</v>
+        <v>_vpft</v>
       </c>
       <c r="B724">
         <v>0</v>
       </c>
       <c r="C724">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D724">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="725">
       <c r="A725" t="str">
-        <v>dayanaa1511</v>
+        <v>viniciustbf</v>
       </c>
       <c r="B725">
         <v>0</v>
@@ -10547,40 +10547,40 @@
         <v>2</v>
       </c>
       <c r="D725">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="726">
       <c r="A726" t="str">
-        <v>danielfranzesilva</v>
+        <v>dayanaa1511</v>
       </c>
       <c r="B726">
         <v>0</v>
       </c>
       <c r="C726">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D726">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="727">
       <c r="A727" t="str">
-        <v>ednilsonkaicai</v>
+        <v>danielfranzesilva</v>
       </c>
       <c r="B727">
         <v>0</v>
       </c>
       <c r="C727">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D727">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="728">
       <c r="A728" t="str">
-        <v>vanessamelomma</v>
+        <v>ednilsonkaicai</v>
       </c>
       <c r="B728">
         <v>0</v>
@@ -10594,21 +10594,21 @@
     </row>
     <row r="729">
       <c r="A729" t="str">
-        <v>michelle_mirele</v>
+        <v>vanessamelomma</v>
       </c>
       <c r="B729">
         <v>0</v>
       </c>
       <c r="C729">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D729">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="730">
       <c r="A730" t="str">
-        <v>geyziellsouza</v>
+        <v>michelle_mirele</v>
       </c>
       <c r="B730">
         <v>0</v>
@@ -10622,21 +10622,21 @@
     </row>
     <row r="731">
       <c r="A731" t="str">
-        <v>guerreirammaofc</v>
+        <v>geyziellsouza</v>
       </c>
       <c r="B731">
         <v>0</v>
       </c>
       <c r="C731">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D731">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="732">
       <c r="A732" t="str">
-        <v>kalaga_vito</v>
+        <v>guerreirammaofc</v>
       </c>
       <c r="B732">
         <v>0</v>
@@ -10650,7 +10650,7 @@
     </row>
     <row r="733">
       <c r="A733" t="str">
-        <v>vitorshowman</v>
+        <v>kalaga_vito</v>
       </c>
       <c r="B733">
         <v>0</v>
@@ -10659,12 +10659,12 @@
         <v>2</v>
       </c>
       <c r="D733">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="734">
       <c r="A734" t="str">
-        <v>4lissson</v>
+        <v>vitorshowman</v>
       </c>
       <c r="B734">
         <v>0</v>
@@ -10678,21 +10678,21 @@
     </row>
     <row r="735">
       <c r="A735" t="str">
-        <v>danilofernandescf</v>
+        <v>4lissson</v>
       </c>
       <c r="B735">
         <v>0</v>
       </c>
       <c r="C735">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D735">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="736">
       <c r="A736" t="str">
-        <v>bryandazuera</v>
+        <v>danilofernandescf</v>
       </c>
       <c r="B736">
         <v>0</v>
@@ -10706,21 +10706,21 @@
     </row>
     <row r="737">
       <c r="A737" t="str">
-        <v>orlando_alfa09</v>
+        <v>bryandazuera</v>
       </c>
       <c r="B737">
         <v>0</v>
       </c>
       <c r="C737">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D737">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="738">
       <c r="A738" t="str">
-        <v>jhonnatanboxe_</v>
+        <v>orlando_alfa09</v>
       </c>
       <c r="B738">
         <v>0</v>
@@ -10734,7 +10734,7 @@
     </row>
     <row r="739">
       <c r="A739" t="str">
-        <v>manumito.oficial</v>
+        <v>jhonnatanboxe_</v>
       </c>
       <c r="B739">
         <v>0</v>
@@ -10748,63 +10748,63 @@
     </row>
     <row r="740">
       <c r="A740" t="str">
-        <v>coutz11</v>
+        <v>manumito.oficial</v>
       </c>
       <c r="B740">
         <v>0</v>
       </c>
       <c r="C740">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D740">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="741">
       <c r="A741" t="str">
-        <v>eglaudiomma</v>
+        <v>coutz11</v>
       </c>
       <c r="B741">
         <v>0</v>
       </c>
       <c r="C741">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D741">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="742">
       <c r="A742" t="str">
-        <v>lokomemo_protetores</v>
+        <v>eglaudiomma</v>
       </c>
       <c r="B742">
         <v>0</v>
       </c>
       <c r="C742">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D742">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="743">
       <c r="A743" t="str">
-        <v>carlosnoelblack</v>
+        <v>lokomemo_protetores</v>
       </c>
       <c r="B743">
         <v>0</v>
       </c>
       <c r="C743">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D743">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="744">
       <c r="A744" t="str">
-        <v>rafaelcmjj</v>
+        <v>carlosnoelblack</v>
       </c>
       <c r="B744">
         <v>0</v>
@@ -10818,21 +10818,21 @@
     </row>
     <row r="745">
       <c r="A745" t="str">
-        <v>rahikikhalid</v>
+        <v>rafaelcmjj</v>
       </c>
       <c r="B745">
         <v>0</v>
       </c>
       <c r="C745">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D745">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="746">
       <c r="A746" t="str">
-        <v>leonardopateira</v>
+        <v>rahikikhalid</v>
       </c>
       <c r="B746">
         <v>0</v>
@@ -10846,21 +10846,21 @@
     </row>
     <row r="747">
       <c r="A747" t="str">
-        <v>thalytabjj</v>
+        <v>leonardopateira</v>
       </c>
       <c r="B747">
         <v>0</v>
       </c>
       <c r="C747">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D747">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="748">
       <c r="A748" t="str">
-        <v>rafaelantonio.rj</v>
+        <v>thalytabjj</v>
       </c>
       <c r="B748">
         <v>0</v>
@@ -10874,35 +10874,35 @@
     </row>
     <row r="749">
       <c r="A749" t="str">
-        <v>yasminreis_oficiall</v>
+        <v>rafaelantonio.rj</v>
       </c>
       <c r="B749">
         <v>0</v>
       </c>
       <c r="C749">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D749">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="750">
       <c r="A750" t="str">
-        <v>dnoxsport</v>
+        <v>yasminreis_oficiall</v>
       </c>
       <c r="B750">
         <v>0</v>
       </c>
       <c r="C750">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D750">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="751">
       <c r="A751" t="str">
-        <v>armysenju</v>
+        <v>dnoxsport</v>
       </c>
       <c r="B751">
         <v>0</v>
@@ -10916,7 +10916,7 @@
     </row>
     <row r="752">
       <c r="A752" t="str">
-        <v>kamtalksmma</v>
+        <v>armysenju</v>
       </c>
       <c r="B752">
         <v>0</v>
@@ -10930,49 +10930,49 @@
     </row>
     <row r="753">
       <c r="A753" t="str">
-        <v>arleyleboss</v>
+        <v>kamtalksmma</v>
       </c>
       <c r="B753">
         <v>0</v>
       </c>
       <c r="C753">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D753">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="754">
       <c r="A754" t="str">
-        <v>jj_miguel05</v>
+        <v>arleyleboss</v>
       </c>
       <c r="B754">
         <v>0</v>
       </c>
       <c r="C754">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D754">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="755">
       <c r="A755" t="str">
-        <v>dra.izabeldelfino_</v>
+        <v>jj_miguel05</v>
       </c>
       <c r="B755">
         <v>0</v>
       </c>
       <c r="C755">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D755">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="756">
       <c r="A756" t="str">
-        <v>janjaovix</v>
+        <v>dra.izabeldelfino_</v>
       </c>
       <c r="B756">
         <v>0</v>
@@ -10986,7 +10986,7 @@
     </row>
     <row r="757">
       <c r="A757" t="str">
-        <v>joaolucasmma.rocha</v>
+        <v>janjaovix</v>
       </c>
       <c r="B757">
         <v>0</v>
@@ -11000,7 +11000,7 @@
     </row>
     <row r="758">
       <c r="A758" t="str">
-        <v>edsonbahienseb</v>
+        <v>joaolucasmma.rocha</v>
       </c>
       <c r="B758">
         <v>0</v>
@@ -11014,7 +11014,7 @@
     </row>
     <row r="759">
       <c r="A759" t="str">
-        <v>paulomartins.mma</v>
+        <v>edsonbahienseb</v>
       </c>
       <c r="B759">
         <v>0</v>
@@ -11028,27 +11028,27 @@
     </row>
     <row r="760">
       <c r="A760" t="str">
-        <v>daniel_natel</v>
+        <v>paulomartins.mma</v>
       </c>
       <c r="B760">
         <v>0</v>
       </c>
       <c r="C760">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D760">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="761">
       <c r="A761" t="str">
-        <v>dhuks11</v>
+        <v>daniel_natel</v>
       </c>
       <c r="B761">
         <v>0</v>
       </c>
       <c r="C761">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D761">
         <v>0</v>
@@ -11056,7 +11056,7 @@
     </row>
     <row r="762">
       <c r="A762" t="str">
-        <v>macksomlee</v>
+        <v>dhuks11</v>
       </c>
       <c r="B762">
         <v>0</v>
@@ -11065,40 +11065,40 @@
         <v>1</v>
       </c>
       <c r="D762">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="763">
       <c r="A763" t="str">
-        <v>y_nichimura</v>
+        <v>macksomlee</v>
       </c>
       <c r="B763">
         <v>0</v>
       </c>
       <c r="C763">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D763">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="764">
       <c r="A764" t="str">
-        <v>mayconzilli</v>
+        <v>y_nichimura</v>
       </c>
       <c r="B764">
         <v>0</v>
       </c>
       <c r="C764">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D764">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="765">
       <c r="A765" t="str">
-        <v>patascubo</v>
+        <v>mayconzilli</v>
       </c>
       <c r="B765">
         <v>0</v>
@@ -11112,7 +11112,7 @@
     </row>
     <row r="766">
       <c r="A766" t="str">
-        <v>jeffesonmeirelles</v>
+        <v>patascubo</v>
       </c>
       <c r="B766">
         <v>0</v>
@@ -11126,7 +11126,7 @@
     </row>
     <row r="767">
       <c r="A767" t="str">
-        <v>denilson.unit</v>
+        <v>jeffesonmeirelles</v>
       </c>
       <c r="B767">
         <v>0</v>
@@ -11140,7 +11140,7 @@
     </row>
     <row r="768">
       <c r="A768" t="str">
-        <v>vieirabjj____</v>
+        <v>denilson.unit</v>
       </c>
       <c r="B768">
         <v>0</v>
@@ -11154,7 +11154,7 @@
     </row>
     <row r="769">
       <c r="A769" t="str">
-        <v>leandro__parpinelli</v>
+        <v>vieirabjj____</v>
       </c>
       <c r="B769">
         <v>0</v>
@@ -11168,7 +11168,7 @@
     </row>
     <row r="770">
       <c r="A770" t="str">
-        <v>bruno_pontes1992</v>
+        <v>leandro__parpinelli</v>
       </c>
       <c r="B770">
         <v>0</v>
@@ -11182,7 +11182,7 @@
     </row>
     <row r="771">
       <c r="A771" t="str">
-        <v>allan10adm</v>
+        <v>bruno_pontes1992</v>
       </c>
       <c r="B771">
         <v>0</v>
@@ -11196,7 +11196,7 @@
     </row>
     <row r="772">
       <c r="A772" t="str">
-        <v>gaby_alves07</v>
+        <v>allan10adm</v>
       </c>
       <c r="B772">
         <v>0</v>
@@ -11210,7 +11210,7 @@
     </row>
     <row r="773">
       <c r="A773" t="str">
-        <v>mvp_lutas</v>
+        <v>gaby_alves07</v>
       </c>
       <c r="B773">
         <v>0</v>
@@ -11224,7 +11224,7 @@
     </row>
     <row r="774">
       <c r="A774" t="str">
-        <v>alineanne_</v>
+        <v>mvp_lutas</v>
       </c>
       <c r="B774">
         <v>0</v>
@@ -11233,12 +11233,12 @@
         <v>1</v>
       </c>
       <c r="D774">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="775">
       <c r="A775" t="str">
-        <v>julckreis</v>
+        <v>alineanne_</v>
       </c>
       <c r="B775">
         <v>0</v>
@@ -11252,7 +11252,7 @@
     </row>
     <row r="776">
       <c r="A776" t="str">
-        <v>andreza.thais.1</v>
+        <v>julckreis</v>
       </c>
       <c r="B776">
         <v>0</v>
@@ -11266,7 +11266,7 @@
     </row>
     <row r="777">
       <c r="A777" t="str">
-        <v>benicius_edu</v>
+        <v>andreza.thais.1</v>
       </c>
       <c r="B777">
         <v>0</v>
@@ -11280,7 +11280,7 @@
     </row>
     <row r="778">
       <c r="A778" t="str">
-        <v>nataliaemanuela.personal</v>
+        <v>benicius_edu</v>
       </c>
       <c r="B778">
         <v>0</v>
@@ -11294,7 +11294,7 @@
     </row>
     <row r="779">
       <c r="A779" t="str">
-        <v>michele_mixa</v>
+        <v>nataliaemanuela.personal</v>
       </c>
       <c r="B779">
         <v>0</v>
@@ -11308,7 +11308,7 @@
     </row>
     <row r="780">
       <c r="A780" t="str">
-        <v>joaolauar_</v>
+        <v>michele_mixa</v>
       </c>
       <c r="B780">
         <v>0</v>
@@ -11322,7 +11322,7 @@
     </row>
     <row r="781">
       <c r="A781" t="str">
-        <v>igorbrasileiro01</v>
+        <v>joaolauar_</v>
       </c>
       <c r="B781">
         <v>0</v>
@@ -11336,7 +11336,7 @@
     </row>
     <row r="782">
       <c r="A782" t="str">
-        <v>felipeocalmon</v>
+        <v>igorbrasileiro01</v>
       </c>
       <c r="B782">
         <v>0</v>
@@ -11350,7 +11350,7 @@
     </row>
     <row r="783">
       <c r="A783" t="str">
-        <v>rejr_mma</v>
+        <v>felipeocalmon</v>
       </c>
       <c r="B783">
         <v>0</v>
@@ -11364,7 +11364,7 @@
     </row>
     <row r="784">
       <c r="A784" t="str">
-        <v>deivssonmanin</v>
+        <v>rejr_mma</v>
       </c>
       <c r="B784">
         <v>0</v>
@@ -11378,7 +11378,7 @@
     </row>
     <row r="785">
       <c r="A785" t="str">
-        <v>andrey_m_s_</v>
+        <v>deivssonmanin</v>
       </c>
       <c r="B785">
         <v>0</v>
@@ -11392,7 +11392,7 @@
     </row>
     <row r="786">
       <c r="A786" t="str">
-        <v>vidaldanin</v>
+        <v>andrey_m_s_</v>
       </c>
       <c r="B786">
         <v>0</v>
@@ -11406,7 +11406,7 @@
     </row>
     <row r="787">
       <c r="A787" t="str">
-        <v>barbaracontadora</v>
+        <v>vidaldanin</v>
       </c>
       <c r="B787">
         <v>0</v>
@@ -11420,7 +11420,7 @@
     </row>
     <row r="788">
       <c r="A788" t="str">
-        <v>natalves5</v>
+        <v>barbaracontadora</v>
       </c>
       <c r="B788">
         <v>0</v>
@@ -11434,7 +11434,7 @@
     </row>
     <row r="789">
       <c r="A789" t="str">
-        <v>marlon_bodybuilding</v>
+        <v>natalves5</v>
       </c>
       <c r="B789">
         <v>0</v>
@@ -11448,7 +11448,7 @@
     </row>
     <row r="790">
       <c r="A790" t="str">
-        <v>boradepodcastoficial</v>
+        <v>marlon_bodybuilding</v>
       </c>
       <c r="B790">
         <v>0</v>
@@ -11462,7 +11462,7 @@
     </row>
     <row r="791">
       <c r="A791" t="str">
-        <v>audizioandrade</v>
+        <v>boradepodcastoficial</v>
       </c>
       <c r="B791">
         <v>0</v>
@@ -11476,7 +11476,7 @@
     </row>
     <row r="792">
       <c r="A792" t="str">
-        <v>isadoragolimpio</v>
+        <v>audizioandrade</v>
       </c>
       <c r="B792">
         <v>0</v>
@@ -11490,7 +11490,7 @@
     </row>
     <row r="793">
       <c r="A793" t="str">
-        <v>dudu.acabamentos</v>
+        <v>isadoragolimpio</v>
       </c>
       <c r="B793">
         <v>0</v>
@@ -11504,7 +11504,7 @@
     </row>
     <row r="794">
       <c r="A794" t="str">
-        <v>katlembrenda</v>
+        <v>dudu.acabamentos</v>
       </c>
       <c r="B794">
         <v>0</v>
@@ -11518,7 +11518,7 @@
     </row>
     <row r="795">
       <c r="A795" t="str">
-        <v>aline.amaral21</v>
+        <v>katlembrenda</v>
       </c>
       <c r="B795">
         <v>0</v>
@@ -11532,7 +11532,7 @@
     </row>
     <row r="796">
       <c r="A796" t="str">
-        <v>tamysregina</v>
+        <v>aline.amaral21</v>
       </c>
       <c r="B796">
         <v>0</v>
@@ -11546,7 +11546,7 @@
     </row>
     <row r="797">
       <c r="A797" t="str">
-        <v>guilhermews1994</v>
+        <v>tamysregina</v>
       </c>
       <c r="B797">
         <v>0</v>
@@ -11560,7 +11560,7 @@
     </row>
     <row r="798">
       <c r="A798" t="str">
-        <v>kevin.mota95</v>
+        <v>guilhermews1994</v>
       </c>
       <c r="B798">
         <v>0</v>
@@ -11574,7 +11574,7 @@
     </row>
     <row r="799">
       <c r="A799" t="str">
-        <v>douglas_vitor8</v>
+        <v>kevin.mota95</v>
       </c>
       <c r="B799">
         <v>0</v>
@@ -11588,7 +11588,7 @@
     </row>
     <row r="800">
       <c r="A800" t="str">
-        <v>gemeaslauraebrenda</v>
+        <v>douglas_vitor8</v>
       </c>
       <c r="B800">
         <v>0</v>
@@ -11602,7 +11602,7 @@
     </row>
     <row r="801">
       <c r="A801" t="str">
-        <v>raulcarvalho1010</v>
+        <v>gemeaslauraebrenda</v>
       </c>
       <c r="B801">
         <v>0</v>
@@ -11616,7 +11616,7 @@
     </row>
     <row r="802">
       <c r="A802" t="str">
-        <v>roginbrito</v>
+        <v>raulcarvalho1010</v>
       </c>
       <c r="B802">
         <v>0</v>
@@ -11630,7 +11630,7 @@
     </row>
     <row r="803">
       <c r="A803" t="str">
-        <v>romulerasilva</v>
+        <v>roginbrito</v>
       </c>
       <c r="B803">
         <v>0</v>
@@ -11644,7 +11644,7 @@
     </row>
     <row r="804">
       <c r="A804" t="str">
-        <v>higorsaantana</v>
+        <v>romulerasilva</v>
       </c>
       <c r="B804">
         <v>0</v>
@@ -11658,7 +11658,7 @@
     </row>
     <row r="805">
       <c r="A805" t="str">
-        <v>vitorcosta_mma</v>
+        <v>higorsaantana</v>
       </c>
       <c r="B805">
         <v>0</v>
@@ -11672,7 +11672,7 @@
     </row>
     <row r="806">
       <c r="A806" t="str">
-        <v>paulo.titoo</v>
+        <v>vitorcosta_mma</v>
       </c>
       <c r="B806">
         <v>0</v>
@@ -11686,7 +11686,7 @@
     </row>
     <row r="807">
       <c r="A807" t="str">
-        <v>1000ton_n</v>
+        <v>paulo.titoo</v>
       </c>
       <c r="B807">
         <v>0</v>
@@ -11700,7 +11700,7 @@
     </row>
     <row r="808">
       <c r="A808" t="str">
-        <v>strong_stg_oficial</v>
+        <v>1000ton_n</v>
       </c>
       <c r="B808">
         <v>0</v>
@@ -11714,7 +11714,7 @@
     </row>
     <row r="809">
       <c r="A809" t="str">
-        <v>ricardotofanello</v>
+        <v>strong_stg_oficial</v>
       </c>
       <c r="B809">
         <v>0</v>
@@ -11728,7 +11728,7 @@
     </row>
     <row r="810">
       <c r="A810" t="str">
-        <v>taporondebruno</v>
+        <v>ricardotofanello</v>
       </c>
       <c r="B810">
         <v>0</v>
@@ -11742,7 +11742,7 @@
     </row>
     <row r="811">
       <c r="A811" t="str">
-        <v>anamatias.m</v>
+        <v>taporondebruno</v>
       </c>
       <c r="B811">
         <v>0</v>
@@ -11756,7 +11756,7 @@
     </row>
     <row r="812">
       <c r="A812" t="str">
-        <v>claudio_marchese_7</v>
+        <v>anamatias.m</v>
       </c>
       <c r="B812">
         <v>0</v>
@@ -11770,7 +11770,7 @@
     </row>
     <row r="813">
       <c r="A813" t="str">
-        <v>caioparangole</v>
+        <v>claudio_marchese_7</v>
       </c>
       <c r="B813">
         <v>0</v>
@@ -11784,7 +11784,7 @@
     </row>
     <row r="814">
       <c r="A814" t="str">
-        <v>sabrinaalsilva</v>
+        <v>caioparangole</v>
       </c>
       <c r="B814">
         <v>0</v>
@@ -11798,7 +11798,7 @@
     </row>
     <row r="815">
       <c r="A815" t="str">
-        <v>nuncadesistir.nd</v>
+        <v>sabrinaalsilva</v>
       </c>
       <c r="B815">
         <v>0</v>
@@ -11812,7 +11812,7 @@
     </row>
     <row r="816">
       <c r="A816" t="str">
-        <v>marcilio.silva.71404</v>
+        <v>nuncadesistir.nd</v>
       </c>
       <c r="B816">
         <v>0</v>
@@ -11826,7 +11826,7 @@
     </row>
     <row r="817">
       <c r="A817" t="str">
-        <v>doraasivla</v>
+        <v>marcilio.silva.71404</v>
       </c>
       <c r="B817">
         <v>0</v>
@@ -11840,7 +11840,7 @@
     </row>
     <row r="818">
       <c r="A818" t="str">
-        <v>pe.mirandas</v>
+        <v>doraasivla</v>
       </c>
       <c r="B818">
         <v>0</v>
@@ -11854,7 +11854,7 @@
     </row>
     <row r="819">
       <c r="A819" t="str">
-        <v>leaoanaalice</v>
+        <v>pe.mirandas</v>
       </c>
       <c r="B819">
         <v>0</v>
@@ -11868,7 +11868,7 @@
     </row>
     <row r="820">
       <c r="A820" t="str">
-        <v>cristianomarcello</v>
+        <v>leaoanaalice</v>
       </c>
       <c r="B820">
         <v>0</v>
@@ -11882,7 +11882,7 @@
     </row>
     <row r="821">
       <c r="A821" t="str">
-        <v>dandraco_</v>
+        <v>cristianomarcello</v>
       </c>
       <c r="B821">
         <v>0</v>
@@ -11896,7 +11896,7 @@
     </row>
     <row r="822">
       <c r="A822" t="str">
-        <v>oliveiraandiarabjj</v>
+        <v>dandraco_</v>
       </c>
       <c r="B822">
         <v>0</v>
@@ -11910,7 +11910,7 @@
     </row>
     <row r="823">
       <c r="A823" t="str">
-        <v>sejamotivadorofc</v>
+        <v>oliveiraandiarabjj</v>
       </c>
       <c r="B823">
         <v>0</v>
@@ -11924,7 +11924,7 @@
     </row>
     <row r="824">
       <c r="A824" t="str">
-        <v>tpapereira</v>
+        <v>sejamotivadorofc</v>
       </c>
       <c r="B824">
         <v>0</v>
@@ -11938,7 +11938,7 @@
     </row>
     <row r="825">
       <c r="A825" t="str">
-        <v>kfcampeoes</v>
+        <v>tpapereira</v>
       </c>
       <c r="B825">
         <v>0</v>
@@ -11952,7 +11952,7 @@
     </row>
     <row r="826">
       <c r="A826" t="str">
-        <v>herrickmarinho</v>
+        <v>kfcampeoes</v>
       </c>
       <c r="B826">
         <v>0</v>
@@ -11966,7 +11966,7 @@
     </row>
     <row r="827">
       <c r="A827" t="str">
-        <v>geanne_franca_</v>
+        <v>herrickmarinho</v>
       </c>
       <c r="B827">
         <v>0</v>
@@ -11980,7 +11980,7 @@
     </row>
     <row r="828">
       <c r="A828" t="str">
-        <v>vanemessina</v>
+        <v>geanne_franca_</v>
       </c>
       <c r="B828">
         <v>0</v>
@@ -11994,7 +11994,7 @@
     </row>
     <row r="829">
       <c r="A829" t="str">
-        <v>dadwillians</v>
+        <v>vanemessina</v>
       </c>
       <c r="B829">
         <v>0</v>
@@ -12008,7 +12008,7 @@
     </row>
     <row r="830">
       <c r="A830" t="str">
-        <v>esteticaluharruda</v>
+        <v>dadwillians</v>
       </c>
       <c r="B830">
         <v>0</v>
@@ -12022,7 +12022,7 @@
     </row>
     <row r="831">
       <c r="A831" t="str">
-        <v>chubotaru_lilu</v>
+        <v>esteticaluharruda</v>
       </c>
       <c r="B831">
         <v>0</v>
@@ -12036,7 +12036,7 @@
     </row>
     <row r="832">
       <c r="A832" t="str">
-        <v>_kainanlima</v>
+        <v>chubotaru_lilu</v>
       </c>
       <c r="B832">
         <v>0</v>
@@ -12050,7 +12050,7 @@
     </row>
     <row r="833">
       <c r="A833" t="str">
-        <v>jimmy_indioap</v>
+        <v>_kainanlima</v>
       </c>
       <c r="B833">
         <v>0</v>
@@ -12064,7 +12064,7 @@
     </row>
     <row r="834">
       <c r="A834" t="str">
-        <v>omar_alneaimi</v>
+        <v>jimmy_indioap</v>
       </c>
       <c r="B834">
         <v>0</v>
@@ -12078,7 +12078,7 @@
     </row>
     <row r="835">
       <c r="A835" t="str">
-        <v>victor_brunopersonal</v>
+        <v>omar_alneaimi</v>
       </c>
       <c r="B835">
         <v>0</v>
@@ -12092,7 +12092,7 @@
     </row>
     <row r="836">
       <c r="A836" t="str">
-        <v>mariacleusa.lopes</v>
+        <v>victor_brunopersonal</v>
       </c>
       <c r="B836">
         <v>0</v>
@@ -12106,7 +12106,7 @@
     </row>
     <row r="837">
       <c r="A837" t="str">
-        <v>rafaelbipolarufc</v>
+        <v>mariacleusa.lopes</v>
       </c>
       <c r="B837">
         <v>0</v>
@@ -12120,7 +12120,7 @@
     </row>
     <row r="838">
       <c r="A838" t="str">
-        <v>martinpakciarz</v>
+        <v>rafaelbipolarufc</v>
       </c>
       <c r="B838">
         <v>0</v>
@@ -12134,7 +12134,7 @@
     </row>
     <row r="839">
       <c r="A839" t="str">
-        <v>andrearschack</v>
+        <v>martinpakciarz</v>
       </c>
       <c r="B839">
         <v>0</v>
@@ -12148,7 +12148,7 @@
     </row>
     <row r="840">
       <c r="A840" t="str">
-        <v>leziamorbeck50</v>
+        <v>andrearschack</v>
       </c>
       <c r="B840">
         <v>0</v>
@@ -12162,7 +12162,7 @@
     </row>
     <row r="841">
       <c r="A841" t="str">
-        <v>meirelesmma</v>
+        <v>leziamorbeck50</v>
       </c>
       <c r="B841">
         <v>0</v>
@@ -12176,7 +12176,7 @@
     </row>
     <row r="842">
       <c r="A842" t="str">
-        <v>teamsilverio</v>
+        <v>meirelesmma</v>
       </c>
       <c r="B842">
         <v>0</v>
@@ -12190,7 +12190,7 @@
     </row>
     <row r="843">
       <c r="A843" t="str">
-        <v>tatiaradias</v>
+        <v>teamsilverio</v>
       </c>
       <c r="B843">
         <v>0</v>
@@ -12204,7 +12204,7 @@
     </row>
     <row r="844">
       <c r="A844" t="str">
-        <v>daniloacordeon_oficial</v>
+        <v>tatiaradias</v>
       </c>
       <c r="B844">
         <v>0</v>
@@ -12218,7 +12218,7 @@
     </row>
     <row r="845">
       <c r="A845" t="str">
-        <v>thiagopssantos</v>
+        <v>daniloacordeon_oficial</v>
       </c>
       <c r="B845">
         <v>0</v>
@@ -12232,7 +12232,7 @@
     </row>
     <row r="846">
       <c r="A846" t="str">
-        <v>leafarlemos</v>
+        <v>thiagopssantos</v>
       </c>
       <c r="B846">
         <v>0</v>
@@ -12246,7 +12246,7 @@
     </row>
     <row r="847">
       <c r="A847" t="str">
-        <v>miltoncjr28</v>
+        <v>leafarlemos</v>
       </c>
       <c r="B847">
         <v>0</v>
@@ -12260,7 +12260,7 @@
     </row>
     <row r="848">
       <c r="A848" t="str">
-        <v>almeidajjwk</v>
+        <v>miltoncjr28</v>
       </c>
       <c r="B848">
         <v>0</v>
@@ -12274,7 +12274,7 @@
     </row>
     <row r="849">
       <c r="A849" t="str">
-        <v>soniarmurata</v>
+        <v>almeidajjwk</v>
       </c>
       <c r="B849">
         <v>0</v>
@@ -12288,7 +12288,7 @@
     </row>
     <row r="850">
       <c r="A850" t="str">
-        <v>foryousaudeespecializada</v>
+        <v>soniarmurata</v>
       </c>
       <c r="B850">
         <v>0</v>
@@ -12302,7 +12302,7 @@
     </row>
     <row r="851">
       <c r="A851" t="str">
-        <v>marques.__bjj</v>
+        <v>foryousaudeespecializada</v>
       </c>
       <c r="B851">
         <v>0</v>
@@ -12316,7 +12316,7 @@
     </row>
     <row r="852">
       <c r="A852" t="str">
-        <v>ryu_artes_marciais</v>
+        <v>marques.__bjj</v>
       </c>
       <c r="B852">
         <v>0</v>
@@ -12330,7 +12330,7 @@
     </row>
     <row r="853">
       <c r="A853" t="str">
-        <v>dorgivan13_bjj</v>
+        <v>ryu_artes_marciais</v>
       </c>
       <c r="B853">
         <v>0</v>
@@ -12344,7 +12344,7 @@
     </row>
     <row r="854">
       <c r="A854" t="str">
-        <v>ayman__falil_06</v>
+        <v>dorgivan13_bjj</v>
       </c>
       <c r="B854">
         <v>0</v>
@@ -12358,7 +12358,7 @@
     </row>
     <row r="855">
       <c r="A855" t="str">
-        <v>otaviocarneiromma</v>
+        <v>ayman__falil_06</v>
       </c>
       <c r="B855">
         <v>0</v>
@@ -12372,7 +12372,7 @@
     </row>
     <row r="856">
       <c r="A856" t="str">
-        <v>dvlucc2k26_</v>
+        <v>otaviocarneiromma</v>
       </c>
       <c r="B856">
         <v>0</v>
@@ -12386,7 +12386,7 @@
     </row>
     <row r="857">
       <c r="A857" t="str">
-        <v>thayanne_rodrigues_bjj</v>
+        <v>dvlucc2k26_</v>
       </c>
       <c r="B857">
         <v>0</v>
@@ -12400,7 +12400,7 @@
     </row>
     <row r="858">
       <c r="A858" t="str">
-        <v>lurochachef</v>
+        <v>thayanne_rodrigues_bjj</v>
       </c>
       <c r="B858">
         <v>0</v>
@@ -12414,7 +12414,7 @@
     </row>
     <row r="859">
       <c r="A859" t="str">
-        <v>viniciusmorais.bjj</v>
+        <v>lurochachef</v>
       </c>
       <c r="B859">
         <v>0</v>
@@ -12428,7 +12428,7 @@
     </row>
     <row r="860">
       <c r="A860" t="str">
-        <v>mauriciogeorge</v>
+        <v>viniciusmorais.bjj</v>
       </c>
       <c r="B860">
         <v>0</v>
@@ -12442,7 +12442,7 @@
     </row>
     <row r="861">
       <c r="A861" t="str">
-        <v>gisbedejose</v>
+        <v>mauriciogeorge</v>
       </c>
       <c r="B861">
         <v>0</v>
@@ -12456,7 +12456,7 @@
     </row>
     <row r="862">
       <c r="A862" t="str">
-        <v>laureanucalvo</v>
+        <v>gisbedejose</v>
       </c>
       <c r="B862">
         <v>0</v>
@@ -12470,7 +12470,7 @@
     </row>
     <row r="863">
       <c r="A863" t="str">
-        <v>galindofrontado</v>
+        <v>laureanucalvo</v>
       </c>
       <c r="B863">
         <v>0</v>
@@ -12484,7 +12484,7 @@
     </row>
     <row r="864">
       <c r="A864" t="str">
-        <v>chalakakavinda</v>
+        <v>galindofrontado</v>
       </c>
       <c r="B864">
         <v>0</v>
@@ -12498,7 +12498,7 @@
     </row>
     <row r="865">
       <c r="A865" t="str">
-        <v>gandrapaulino</v>
+        <v>chalakakavinda</v>
       </c>
       <c r="B865">
         <v>0</v>
@@ -12512,7 +12512,7 @@
     </row>
     <row r="866">
       <c r="A866" t="str">
-        <v>pgmarquesantos</v>
+        <v>gandrapaulino</v>
       </c>
       <c r="B866">
         <v>0</v>
@@ -12526,7 +12526,7 @@
     </row>
     <row r="867">
       <c r="A867" t="str">
-        <v>uluukyrgyz_tima</v>
+        <v>pgmarquesantos</v>
       </c>
       <c r="B867">
         <v>0</v>
@@ -12540,7 +12540,7 @@
     </row>
     <row r="868">
       <c r="A868" t="str">
-        <v>kells2vallone</v>
+        <v>uluukyrgyz_tima</v>
       </c>
       <c r="B868">
         <v>0</v>
@@ -12554,7 +12554,7 @@
     </row>
     <row r="869">
       <c r="A869" t="str">
-        <v>personaljakeline</v>
+        <v>kells2vallone</v>
       </c>
       <c r="B869">
         <v>0</v>
@@ -12568,7 +12568,7 @@
     </row>
     <row r="870">
       <c r="A870" t="str">
-        <v>bjjfalkenberg</v>
+        <v>personaljakeline</v>
       </c>
       <c r="B870">
         <v>0</v>
@@ -12582,7 +12582,7 @@
     </row>
     <row r="871">
       <c r="A871" t="str">
-        <v>sergiorenatocruz1</v>
+        <v>bjjfalkenberg</v>
       </c>
       <c r="B871">
         <v>0</v>
@@ -12596,7 +12596,7 @@
     </row>
     <row r="872">
       <c r="A872" t="str">
-        <v>marcaojudobjjmaster</v>
+        <v>sergiorenatocruz1</v>
       </c>
       <c r="B872">
         <v>0</v>
@@ -12610,7 +12610,7 @@
     </row>
     <row r="873">
       <c r="A873" t="str">
-        <v>indio_mma</v>
+        <v>marcaojudobjjmaster</v>
       </c>
       <c r="B873">
         <v>0</v>
@@ -12624,7 +12624,7 @@
     </row>
     <row r="874">
       <c r="A874" t="str">
-        <v>covil.045</v>
+        <v>indio_mma</v>
       </c>
       <c r="B874">
         <v>0</v>
@@ -12638,7 +12638,7 @@
     </row>
     <row r="875">
       <c r="A875" t="str">
-        <v>allandelano</v>
+        <v>covil.045</v>
       </c>
       <c r="B875">
         <v>0</v>
@@ -12652,7 +12652,7 @@
     </row>
     <row r="876">
       <c r="A876" t="str">
-        <v>alomaraujo</v>
+        <v>allandelano</v>
       </c>
       <c r="B876">
         <v>0</v>
@@ -12666,7 +12666,7 @@
     </row>
     <row r="877">
       <c r="A877" t="str">
-        <v>theanimallifemovement</v>
+        <v>alomaraujo</v>
       </c>
       <c r="B877">
         <v>0</v>
@@ -12680,7 +12680,7 @@
     </row>
     <row r="878">
       <c r="A878" t="str">
-        <v>tombg_64</v>
+        <v>theanimallifemovement</v>
       </c>
       <c r="B878">
         <v>0</v>
@@ -12694,7 +12694,7 @@
     </row>
     <row r="879">
       <c r="A879" t="str">
-        <v>michaeloliveiramma</v>
+        <v>tombg_64</v>
       </c>
       <c r="B879">
         <v>0</v>
@@ -12708,7 +12708,7 @@
     </row>
     <row r="880">
       <c r="A880" t="str">
-        <v>andreichubotaru94</v>
+        <v>michaeloliveiramma</v>
       </c>
       <c r="B880">
         <v>0</v>
@@ -12722,7 +12722,7 @@
     </row>
     <row r="881">
       <c r="A881" t="str">
-        <v>carinhakkz</v>
+        <v>andreichubotaru94</v>
       </c>
       <c r="B881">
         <v>0</v>
@@ -12736,7 +12736,7 @@
     </row>
     <row r="882">
       <c r="A882" t="str">
-        <v>helaynecrisl</v>
+        <v>carinhakkz</v>
       </c>
       <c r="B882">
         <v>0</v>
@@ -12750,7 +12750,7 @@
     </row>
     <row r="883">
       <c r="A883" t="str">
-        <v>oliveiraa_00.11</v>
+        <v>helaynecrisl</v>
       </c>
       <c r="B883">
         <v>0</v>
@@ -12764,7 +12764,7 @@
     </row>
     <row r="884">
       <c r="A884" t="str">
-        <v>udilimaheroi</v>
+        <v>oliveiraa_00.11</v>
       </c>
       <c r="B884">
         <v>0</v>
@@ -12778,7 +12778,7 @@
     </row>
     <row r="885">
       <c r="A885" t="str">
-        <v>mirnacaroline</v>
+        <v>udilimaheroi</v>
       </c>
       <c r="B885">
         <v>0</v>
@@ -12792,7 +12792,7 @@
     </row>
     <row r="886">
       <c r="A886" t="str">
-        <v>lmk_sport</v>
+        <v>mirnacaroline</v>
       </c>
       <c r="B886">
         <v>0</v>
@@ -12806,7 +12806,7 @@
     </row>
     <row r="887">
       <c r="A887" t="str">
-        <v>fher.nando_</v>
+        <v>lmk_sport</v>
       </c>
       <c r="B887">
         <v>0</v>
@@ -12820,7 +12820,7 @@
     </row>
     <row r="888">
       <c r="A888" t="str">
-        <v>cristiannogueira.vtt</v>
+        <v>fher.nando_</v>
       </c>
       <c r="B888">
         <v>0</v>
@@ -12834,7 +12834,7 @@
     </row>
     <row r="889">
       <c r="A889" t="str">
-        <v>adrianaramosalvesribeiro</v>
+        <v>cristiannogueira.vtt</v>
       </c>
       <c r="B889">
         <v>0</v>
@@ -12848,7 +12848,7 @@
     </row>
     <row r="890">
       <c r="A890" t="str">
-        <v>djuliaarianamma</v>
+        <v>adrianaramosalvesribeiro</v>
       </c>
       <c r="B890">
         <v>0</v>
@@ -12862,7 +12862,7 @@
     </row>
     <row r="891">
       <c r="A891" t="str">
-        <v>raulbasilioo</v>
+        <v>djuliaarianamma</v>
       </c>
       <c r="B891">
         <v>0</v>
@@ -12876,7 +12876,7 @@
     </row>
     <row r="892">
       <c r="A892" t="str">
-        <v>heloisa_elohim</v>
+        <v>raulbasilioo</v>
       </c>
       <c r="B892">
         <v>0</v>
@@ -12890,7 +12890,7 @@
     </row>
     <row r="893">
       <c r="A893" t="str">
-        <v>hostonhugo</v>
+        <v>heloisa_elohim</v>
       </c>
       <c r="B893">
         <v>0</v>
@@ -12904,7 +12904,7 @@
     </row>
     <row r="894">
       <c r="A894" t="str">
-        <v>ellida_guimaraes</v>
+        <v>hostonhugo</v>
       </c>
       <c r="B894">
         <v>0</v>
@@ -12918,7 +12918,7 @@
     </row>
     <row r="895">
       <c r="A895" t="str">
-        <v>massoterapeuta_bemestarr</v>
+        <v>ellida_guimaraes</v>
       </c>
       <c r="B895">
         <v>0</v>
@@ -12932,7 +12932,7 @@
     </row>
     <row r="896">
       <c r="A896" t="str">
-        <v>alexandrefideliis</v>
+        <v>massoterapeuta_bemestarr</v>
       </c>
       <c r="B896">
         <v>0</v>
@@ -12946,7 +12946,7 @@
     </row>
     <row r="897">
       <c r="A897" t="str">
-        <v>pammygaryo</v>
+        <v>alexandrefideliis</v>
       </c>
       <c r="B897">
         <v>0</v>
@@ -12960,7 +12960,7 @@
     </row>
     <row r="898">
       <c r="A898" t="str">
-        <v>beatrizosilveira</v>
+        <v>pammygaryo</v>
       </c>
       <c r="B898">
         <v>0</v>
@@ -12974,7 +12974,7 @@
     </row>
     <row r="899">
       <c r="A899" t="str">
-        <v>bastazinifilho</v>
+        <v>beatrizosilveira</v>
       </c>
       <c r="B899">
         <v>0</v>
@@ -12988,7 +12988,7 @@
     </row>
     <row r="900">
       <c r="A900" t="str">
-        <v>sem_saida.12</v>
+        <v>bastazinifilho</v>
       </c>
       <c r="B900">
         <v>0</v>
@@ -13002,7 +13002,7 @@
     </row>
     <row r="901">
       <c r="A901" t="str">
-        <v>sougustavorosa</v>
+        <v>sem_saida.12</v>
       </c>
       <c r="B901">
         <v>0</v>
@@ -13016,7 +13016,7 @@
     </row>
     <row r="902">
       <c r="A902" t="str">
-        <v>lincoln__puig77</v>
+        <v>sougustavorosa</v>
       </c>
       <c r="B902">
         <v>0</v>
@@ -13030,7 +13030,7 @@
     </row>
     <row r="903">
       <c r="A903" t="str">
-        <v>anselmo.azevedo</v>
+        <v>lincoln__puig77</v>
       </c>
       <c r="B903">
         <v>0</v>
@@ -13044,7 +13044,7 @@
     </row>
     <row r="904">
       <c r="A904" t="str">
-        <v>marcotulio_matuto</v>
+        <v>anselmo.azevedo</v>
       </c>
       <c r="B904">
         <v>0</v>
@@ -13058,7 +13058,7 @@
     </row>
     <row r="905">
       <c r="A905" t="str">
-        <v>ianrochaf</v>
+        <v>marcotulio_matuto</v>
       </c>
       <c r="B905">
         <v>0</v>
@@ -13072,7 +13072,7 @@
     </row>
     <row r="906">
       <c r="A906" t="str">
-        <v>ale.lagonegro</v>
+        <v>ianrochaf</v>
       </c>
       <c r="B906">
         <v>0</v>
@@ -13086,7 +13086,7 @@
     </row>
     <row r="907">
       <c r="A907" t="str">
-        <v>ganemfelipe</v>
+        <v>ale.lagonegro</v>
       </c>
       <c r="B907">
         <v>0</v>
@@ -13100,7 +13100,7 @@
     </row>
     <row r="908">
       <c r="A908" t="str">
-        <v>marcusvgsz</v>
+        <v>ganemfelipe</v>
       </c>
       <c r="B908">
         <v>0</v>
@@ -13114,7 +13114,7 @@
     </row>
     <row r="909">
       <c r="A909" t="str">
-        <v>fabio.sampaio.90260</v>
+        <v>marcusvgsz</v>
       </c>
       <c r="B909">
         <v>0</v>
@@ -13128,7 +13128,7 @@
     </row>
     <row r="910">
       <c r="A910" t="str">
-        <v>kaynankruschewsky_ufc</v>
+        <v>fabio.sampaio.90260</v>
       </c>
       <c r="B910">
         <v>0</v>
@@ -13142,7 +13142,7 @@
     </row>
     <row r="911">
       <c r="A911" t="str">
-        <v>vitorpaes_personalfight</v>
+        <v>kaynankruschewsky_ufc</v>
       </c>
       <c r="B911">
         <v>0</v>
@@ -13156,7 +13156,7 @@
     </row>
     <row r="912">
       <c r="A912" t="str">
-        <v>zeferinomma</v>
+        <v>vitorpaes_personalfight</v>
       </c>
       <c r="B912">
         <v>0</v>
@@ -13170,7 +13170,7 @@
     </row>
     <row r="913">
       <c r="A913" t="str">
-        <v>tavaresguu</v>
+        <v>zeferinomma</v>
       </c>
       <c r="B913">
         <v>0</v>
@@ -13184,7 +13184,7 @@
     </row>
     <row r="914">
       <c r="A914" t="str">
-        <v>ildemarmarajo</v>
+        <v>tavaresguu</v>
       </c>
       <c r="B914">
         <v>0</v>
@@ -13198,7 +13198,7 @@
     </row>
     <row r="915">
       <c r="A915" t="str">
-        <v>pepefightteam</v>
+        <v>ildemarmarajo</v>
       </c>
       <c r="B915">
         <v>0</v>
@@ -13212,7 +13212,7 @@
     </row>
     <row r="916">
       <c r="A916" t="str">
-        <v>danieldias7s</v>
+        <v>pepefightteam</v>
       </c>
       <c r="B916">
         <v>0</v>
@@ -13226,7 +13226,7 @@
     </row>
     <row r="917">
       <c r="A917" t="str">
-        <v>ohanna.anselmo</v>
+        <v>danieldias7s</v>
       </c>
       <c r="B917">
         <v>0</v>
@@ -13240,7 +13240,7 @@
     </row>
     <row r="918">
       <c r="A918" t="str">
-        <v>brun_oguerreiro</v>
+        <v>ohanna.anselmo</v>
       </c>
       <c r="B918">
         <v>0</v>
@@ -13254,7 +13254,7 @@
     </row>
     <row r="919">
       <c r="A919" t="str">
-        <v>helman_mma70</v>
+        <v>brun_oguerreiro</v>
       </c>
       <c r="B919">
         <v>0</v>
@@ -13268,7 +13268,7 @@
     </row>
     <row r="920">
       <c r="A920" t="str">
-        <v>macio.almeida_89</v>
+        <v>helman_mma70</v>
       </c>
       <c r="B920">
         <v>0</v>
@@ -13282,7 +13282,7 @@
     </row>
     <row r="921">
       <c r="A921" t="str">
-        <v>lyviaestherbjj</v>
+        <v>macio.almeida_89</v>
       </c>
       <c r="B921">
         <v>0</v>
@@ -13296,7 +13296,7 @@
     </row>
     <row r="922">
       <c r="A922" t="str">
-        <v>mma.fisio</v>
+        <v>lyviaestherbjj</v>
       </c>
       <c r="B922">
         <v>0</v>
@@ -13310,7 +13310,7 @@
     </row>
     <row r="923">
       <c r="A923" t="str">
-        <v>thaynara_victoria_</v>
+        <v>mma.fisio</v>
       </c>
       <c r="B923">
         <v>0</v>
@@ -13324,7 +13324,7 @@
     </row>
     <row r="924">
       <c r="A924" t="str">
-        <v>tamarapq</v>
+        <v>thaynara_victoria_</v>
       </c>
       <c r="B924">
         <v>0</v>
@@ -13338,7 +13338,7 @@
     </row>
     <row r="925">
       <c r="A925" t="str">
-        <v>wendel_bjj14</v>
+        <v>tamarapq</v>
       </c>
       <c r="B925">
         <v>0</v>
@@ -13352,7 +13352,7 @@
     </row>
     <row r="926">
       <c r="A926" t="str">
-        <v>karine_killer_ufc</v>
+        <v>wendel_bjj14</v>
       </c>
       <c r="B926">
         <v>0</v>
@@ -13366,7 +13366,7 @@
     </row>
     <row r="927">
       <c r="A927" t="str">
-        <v>andressa_bjj_</v>
+        <v>karine_killer_ufc</v>
       </c>
       <c r="B927">
         <v>0</v>
@@ -13380,7 +13380,7 @@
     </row>
     <row r="928">
       <c r="A928" t="str">
-        <v>dreamartpro</v>
+        <v>andressa_bjj_</v>
       </c>
       <c r="B928">
         <v>0</v>
@@ -13394,7 +13394,7 @@
     </row>
     <row r="929">
       <c r="A929" t="str">
-        <v>makelele_bjj</v>
+        <v>dreamartpro</v>
       </c>
       <c r="B929">
         <v>0</v>
@@ -13408,7 +13408,7 @@
     </row>
     <row r="930">
       <c r="A930" t="str">
-        <v>fdanieljj</v>
+        <v>makelele_bjj</v>
       </c>
       <c r="B930">
         <v>0</v>
@@ -13422,7 +13422,7 @@
     </row>
     <row r="931">
       <c r="A931" t="str">
-        <v>jeferson_tijolo1</v>
+        <v>fdanieljj</v>
       </c>
       <c r="B931">
         <v>0</v>
@@ -13436,7 +13436,7 @@
     </row>
     <row r="932">
       <c r="A932" t="str">
-        <v>caioleonjj</v>
+        <v>jeferson_tijolo1</v>
       </c>
       <c r="B932">
         <v>0</v>
@@ -13450,7 +13450,7 @@
     </row>
     <row r="933">
       <c r="A933" t="str">
-        <v>kevinlopes_bjj</v>
+        <v>caioleonjj</v>
       </c>
       <c r="B933">
         <v>0</v>
@@ -13464,7 +13464,7 @@
     </row>
     <row r="934">
       <c r="A934" t="str">
-        <v>malene_elleen</v>
+        <v>kevinlopes_bjj</v>
       </c>
       <c r="B934">
         <v>0</v>
@@ -13478,7 +13478,7 @@
     </row>
     <row r="935">
       <c r="A935" t="str">
-        <v>danielplayboymt</v>
+        <v>malene_elleen</v>
       </c>
       <c r="B935">
         <v>0</v>
@@ -13492,7 +13492,7 @@
     </row>
     <row r="936">
       <c r="A936" t="str">
-        <v>fix.pec</v>
+        <v>danielplayboymt</v>
       </c>
       <c r="B936">
         <v>0</v>
@@ -13506,7 +13506,7 @@
     </row>
     <row r="937">
       <c r="A937" t="str">
-        <v>chunco_424</v>
+        <v>fix.pec</v>
       </c>
       <c r="B937">
         <v>0</v>
@@ -13520,7 +13520,7 @@
     </row>
     <row r="938">
       <c r="A938" t="str">
-        <v>denisalagoanobjj</v>
+        <v>chunco_424</v>
       </c>
       <c r="B938">
         <v>0</v>
@@ -13534,7 +13534,7 @@
     </row>
     <row r="939">
       <c r="A939" t="str">
-        <v>priscilaapbatista</v>
+        <v>denisalagoanobjj</v>
       </c>
       <c r="B939">
         <v>0</v>
@@ -13548,7 +13548,7 @@
     </row>
     <row r="940">
       <c r="A940" t="str">
-        <v>josita_bjj</v>
+        <v>priscilaapbatista</v>
       </c>
       <c r="B940">
         <v>0</v>
@@ -13562,7 +13562,7 @@
     </row>
     <row r="941">
       <c r="A941" t="str">
-        <v>roxostrike</v>
+        <v>josita_bjj</v>
       </c>
       <c r="B941">
         <v>0</v>
@@ -13576,7 +13576,7 @@
     </row>
     <row r="942">
       <c r="A942" t="str">
-        <v>shirleypalestrina6</v>
+        <v>roxostrike</v>
       </c>
       <c r="B942">
         <v>0</v>
@@ -13590,7 +13590,7 @@
     </row>
     <row r="943">
       <c r="A943" t="str">
-        <v>flipebiano</v>
+        <v>shirleypalestrina6</v>
       </c>
       <c r="B943">
         <v>0</v>
@@ -13604,7 +13604,7 @@
     </row>
     <row r="944">
       <c r="A944" t="str">
-        <v>ruanmiqueias</v>
+        <v>flipebiano</v>
       </c>
       <c r="B944">
         <v>0</v>
@@ -13618,7 +13618,7 @@
     </row>
     <row r="945">
       <c r="A945" t="str">
-        <v>babimaciel1</v>
+        <v>ruanmiqueias</v>
       </c>
       <c r="B945">
         <v>0</v>
@@ -13632,7 +13632,7 @@
     </row>
     <row r="946">
       <c r="A946" t="str">
-        <v>manoel.brum</v>
+        <v>babimaciel1</v>
       </c>
       <c r="B946">
         <v>0</v>
@@ -13646,7 +13646,7 @@
     </row>
     <row r="947">
       <c r="A947" t="str">
-        <v>horadopower</v>
+        <v>manoel.brum</v>
       </c>
       <c r="B947">
         <v>0</v>
@@ -13660,7 +13660,7 @@
     </row>
     <row r="948">
       <c r="A948" t="str">
-        <v>lyvia_genuina</v>
+        <v>horadopower</v>
       </c>
       <c r="B948">
         <v>0</v>
@@ -13674,7 +13674,7 @@
     </row>
     <row r="949">
       <c r="A949" t="str">
-        <v>delariva_belem</v>
+        <v>lyvia_genuina</v>
       </c>
       <c r="B949">
         <v>0</v>
@@ -13688,7 +13688,7 @@
     </row>
     <row r="950">
       <c r="A950" t="str">
-        <v>juugxmes</v>
+        <v>delariva_belem</v>
       </c>
       <c r="B950">
         <v>0</v>
@@ -13702,7 +13702,7 @@
     </row>
     <row r="951">
       <c r="A951" t="str">
-        <v>gabrielsantosufc_</v>
+        <v>juugxmes</v>
       </c>
       <c r="B951">
         <v>0</v>
@@ -13716,7 +13716,7 @@
     </row>
     <row r="952">
       <c r="A952" t="str">
-        <v>_matheustiberio</v>
+        <v>gabrielsantosufc_</v>
       </c>
       <c r="B952">
         <v>0</v>
@@ -13730,7 +13730,7 @@
     </row>
     <row r="953">
       <c r="A953" t="str">
-        <v>sthefany_ochoao</v>
+        <v>_matheustiberio</v>
       </c>
       <c r="B953">
         <v>0</v>
@@ -13744,7 +13744,7 @@
     </row>
     <row r="954">
       <c r="A954" t="str">
-        <v>reynitaoblitasbustamante</v>
+        <v>sthefany_ochoao</v>
       </c>
       <c r="B954">
         <v>0</v>
@@ -13758,7 +13758,7 @@
     </row>
     <row r="955">
       <c r="A955" t="str">
-        <v>joseochoa.mma</v>
+        <v>reynitaoblitasbustamante</v>
       </c>
       <c r="B955">
         <v>0</v>
@@ -13772,7 +13772,7 @@
     </row>
     <row r="956">
       <c r="A956" t="str">
-        <v>gabriellb.andrade</v>
+        <v>joseochoa.mma</v>
       </c>
       <c r="B956">
         <v>0</v>
@@ -13786,7 +13786,7 @@
     </row>
     <row r="957">
       <c r="A957" t="str">
-        <v>romelluistro</v>
+        <v>gabriellb.andrade</v>
       </c>
       <c r="B957">
         <v>0</v>
@@ -13800,7 +13800,7 @@
     </row>
     <row r="958">
       <c r="A958" t="str">
-        <v>yuricapelasso</v>
+        <v>romelluistro</v>
       </c>
       <c r="B958">
         <v>0</v>
@@ -13814,7 +13814,7 @@
     </row>
     <row r="959">
       <c r="A959" t="str">
-        <v>lucasfenomeno_ufc</v>
+        <v>yuricapelasso</v>
       </c>
       <c r="B959">
         <v>0</v>
@@ -13828,7 +13828,7 @@
     </row>
     <row r="960">
       <c r="A960" t="str">
-        <v>gabriell_marcus</v>
+        <v>lucasfenomeno_ufc</v>
       </c>
       <c r="B960">
         <v>0</v>
@@ -13842,7 +13842,7 @@
     </row>
     <row r="961">
       <c r="A961" t="str">
-        <v>lazyboy.ufc</v>
+        <v>gabriell_marcus</v>
       </c>
       <c r="B961">
         <v>0</v>
@@ -13856,7 +13856,7 @@
     </row>
     <row r="962">
       <c r="A962" t="str">
-        <v>matheusdouradomma</v>
+        <v>lazyboy.ufc</v>
       </c>
       <c r="B962">
         <v>0</v>
@@ -13870,7 +13870,7 @@
     </row>
     <row r="963">
       <c r="A963" t="str">
-        <v>rafaelsouza7586</v>
+        <v>matheusdouradomma</v>
       </c>
       <c r="B963">
         <v>0</v>
@@ -13884,7 +13884,7 @@
     </row>
     <row r="964">
       <c r="A964" t="str">
-        <v>land_on_martelo_308</v>
+        <v>rafaelsouza7586</v>
       </c>
       <c r="B964">
         <v>0</v>
@@ -13898,7 +13898,7 @@
     </row>
     <row r="965">
       <c r="A965" t="str">
-        <v>dodge_big_johnson29</v>
+        <v>land_on_martelo_308</v>
       </c>
       <c r="B965">
         <v>0</v>
@@ -13912,7 +13912,7 @@
     </row>
     <row r="966">
       <c r="A966" t="str">
-        <v>dj__freckles</v>
+        <v>dodge_big_johnson29</v>
       </c>
       <c r="B966">
         <v>0</v>
@@ -13926,7 +13926,7 @@
     </row>
     <row r="967">
       <c r="A967" t="str">
-        <v>regis18vieira</v>
+        <v>dj__freckles</v>
       </c>
       <c r="B967">
         <v>0</v>
@@ -13940,7 +13940,7 @@
     </row>
     <row r="968">
       <c r="A968" t="str">
-        <v>andy.techera.12</v>
+        <v>regis18vieira</v>
       </c>
       <c r="B968">
         <v>0</v>
@@ -13954,7 +13954,7 @@
     </row>
     <row r="969">
       <c r="A969" t="str">
-        <v>celiogarcia6</v>
+        <v>andy.techera.12</v>
       </c>
       <c r="B969">
         <v>0</v>
@@ -13968,7 +13968,7 @@
     </row>
     <row r="970">
       <c r="A970" t="str">
-        <v>luluakio</v>
+        <v>celiogarcia6</v>
       </c>
       <c r="B970">
         <v>0</v>
@@ -13982,7 +13982,7 @@
     </row>
     <row r="971">
       <c r="A971" t="str">
-        <v>barreto.boxe</v>
+        <v>luluakio</v>
       </c>
       <c r="B971">
         <v>0</v>
@@ -13996,7 +13996,7 @@
     </row>
     <row r="972">
       <c r="A972" t="str">
-        <v>lusoaresjj</v>
+        <v>barreto.boxe</v>
       </c>
       <c r="B972">
         <v>0</v>
@@ -14010,7 +14010,7 @@
     </row>
     <row r="973">
       <c r="A973" t="str">
-        <v>sharingan_mma</v>
+        <v>lusoaresjj</v>
       </c>
       <c r="B973">
         <v>0</v>
@@ -14024,7 +14024,7 @@
     </row>
     <row r="974">
       <c r="A974" t="str">
-        <v>thaisadantas</v>
+        <v>sharingan_mma</v>
       </c>
       <c r="B974">
         <v>0</v>
@@ -14038,7 +14038,7 @@
     </row>
     <row r="975">
       <c r="A975" t="str">
-        <v>pulsepro.nutrition</v>
+        <v>thaisadantas</v>
       </c>
       <c r="B975">
         <v>0</v>
@@ -14052,7 +14052,7 @@
     </row>
     <row r="976">
       <c r="A976" t="str">
-        <v>herbeth_indiomma</v>
+        <v>pulsepro.nutrition</v>
       </c>
       <c r="B976">
         <v>0</v>
@@ -14066,7 +14066,7 @@
     </row>
     <row r="977">
       <c r="A977" t="str">
-        <v>danielbzk_</v>
+        <v>herbeth_indiomma</v>
       </c>
       <c r="B977">
         <v>0</v>
@@ -14080,7 +14080,7 @@
     </row>
     <row r="978">
       <c r="A978" t="str">
-        <v>jp.mdc</v>
+        <v>danielbzk_</v>
       </c>
       <c r="B978">
         <v>0</v>
@@ -14094,28 +14094,42 @@
     </row>
     <row r="979">
       <c r="A979" t="str">
+        <v>jp.mdc</v>
+      </c>
+      <c r="B979">
+        <v>0</v>
+      </c>
+      <c r="C979">
+        <v>1</v>
+      </c>
+      <c r="D979">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" t="str">
         <v>1210gi</v>
       </c>
-      <c r="B979">
-        <v>0</v>
-      </c>
-      <c r="C979">
-        <v>1</v>
-      </c>
-      <c r="D979">
+      <c r="B980">
+        <v>0</v>
+      </c>
+      <c r="C980">
+        <v>1</v>
+      </c>
+      <c r="D980">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D979"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D980"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D100"/>
+  <dimension ref="A1:D102"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -14136,7 +14150,7 @@
         <v>peacegrappler</v>
       </c>
       <c r="B2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -14150,13 +14164,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C3">
         <v>2</v>
       </c>
       <c r="D3">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4">
@@ -14357,35 +14371,35 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>johnmma9</v>
+        <v>masonharper_mma</v>
       </c>
       <c r="B18">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C18">
         <v>0</v>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>carlos_hm_iglesias</v>
+        <v>johnmma9</v>
       </c>
       <c r="B19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C19">
         <v>0</v>
       </c>
       <c r="D19">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>ninjatheorist</v>
+        <v>carlos_hm_iglesias</v>
       </c>
       <c r="B20">
         <v>3</v>
@@ -14399,7 +14413,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>helenmacielmma</v>
+        <v>ninjatheorist</v>
       </c>
       <c r="B21">
         <v>3</v>
@@ -14413,10 +14427,10 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>wesleysepulveda__mma</v>
+        <v>helenmacielmma</v>
       </c>
       <c r="B22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -14427,27 +14441,27 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>adriano.trator</v>
+        <v>wesleysepulveda__mma</v>
       </c>
       <c r="B23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>masonharper_mma</v>
+        <v>adriano.trator</v>
       </c>
       <c r="B24">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -14567,10 +14581,10 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>sueli_ferreira48</v>
+        <v>canalgolpebaixo</v>
       </c>
       <c r="B33">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C33">
         <v>0</v>
@@ -14581,7 +14595,7 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>ottonimestre</v>
+        <v>sueli_ferreira48</v>
       </c>
       <c r="B34">
         <v>2</v>
@@ -14595,7 +14609,7 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>canalgolpebaixo</v>
+        <v>ottonimestre</v>
       </c>
       <c r="B35">
         <v>2</v>
@@ -15239,21 +15253,21 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>leobahiamma</v>
+        <v>peacegrappler_podcast</v>
       </c>
       <c r="B81">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C81">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D81">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>dudaadantass</v>
+        <v>leobahiamma</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -15267,13 +15281,13 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>pedro_pavin_</v>
+        <v>dudaadantass</v>
       </c>
       <c r="B83">
         <v>0</v>
       </c>
       <c r="C83">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D83">
         <v>1</v>
@@ -15281,7 +15295,7 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>allan10adm</v>
+        <v>pedro_pavin_</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -15295,7 +15309,7 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>ismael.marreta_ufc</v>
+        <v>allan10adm</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -15309,7 +15323,7 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>joandersontubarao_ufc</v>
+        <v>ismael.marreta_ufc</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -15323,7 +15337,7 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>gaby_alves07</v>
+        <v>joandersontubarao_ufc</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -15337,7 +15351,7 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>diegosilvabjjoficial</v>
+        <v>gaby_alves07</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -15351,7 +15365,7 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>mvp_lutas</v>
+        <v>diegosilvabjjoficial</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -15365,7 +15379,7 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>luis_pequeno_mma</v>
+        <v>mvp_lutas</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -15379,7 +15393,7 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>pulsepro.nutrition</v>
+        <v>luis_pequeno_mma</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -15388,12 +15402,12 @@
         <v>1</v>
       </c>
       <c r="D91">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>herbeth_indiomma</v>
+        <v>pulsepro.nutrition</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -15407,7 +15421,7 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>danielbzk_</v>
+        <v>herbeth_indiomma</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -15421,7 +15435,7 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>jp.mdc</v>
+        <v>danielbzk_</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -15435,7 +15449,7 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>rosacostasousa36</v>
+        <v>jp.mdc</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -15449,7 +15463,7 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>cathya_ferreira</v>
+        <v>rosacostasousa36</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -15463,7 +15477,7 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>1210gi</v>
+        <v>cathya_ferreira</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -15477,7 +15491,7 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>juanx.pontes</v>
+        <v>1210gi</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -15491,7 +15505,7 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>_oliveira09_</v>
+        <v>juanx.pontes</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -15505,21 +15519,49 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
+        <v>_oliveira09_</v>
+      </c>
+      <c r="B100">
+        <v>0</v>
+      </c>
+      <c r="C100">
+        <v>1</v>
+      </c>
+      <c r="D100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
         <v>mestreviniciusreviravolta</v>
       </c>
-      <c r="B100">
-        <v>0</v>
-      </c>
-      <c r="C100">
-        <v>1</v>
-      </c>
-      <c r="D100">
+      <c r="B101">
+        <v>0</v>
+      </c>
+      <c r="C101">
+        <v>1</v>
+      </c>
+      <c r="D101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>djsagatoficial</v>
+      </c>
+      <c r="B102">
+        <v>0</v>
+      </c>
+      <c r="C102">
+        <v>1</v>
+      </c>
+      <c r="D102">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D100"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D102"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Engagement Rankings 2026-07.xlsx
+++ b/Engagement Rankings 2026-07.xlsx
@@ -475,13 +475,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B6">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="C6">
         <v>17</v>
       </c>
       <c r="D6">
-        <v>755</v>
+        <v>756</v>
       </c>
     </row>
     <row r="7">
@@ -14640,13 +14640,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C3">
         <v>3</v>
       </c>
       <c r="D3">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4">

--- a/Engagement Rankings 2026-07.xlsx
+++ b/Engagement Rankings 2026-07.xlsx
@@ -475,13 +475,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B6">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="C6">
         <v>17</v>
       </c>
       <c r="D6">
-        <v>756</v>
+        <v>757</v>
       </c>
     </row>
     <row r="7">
@@ -545,7 +545,7 @@
         <v>combintel</v>
       </c>
       <c r="B11">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C11">
         <v>2</v>
@@ -615,13 +615,13 @@
         <v>johnmma9</v>
       </c>
       <c r="B16">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
       <c r="D16">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17">
@@ -657,13 +657,13 @@
         <v>masonharper_mma</v>
       </c>
       <c r="B19">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C19">
         <v>0</v>
       </c>
       <c r="D19">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="20">
@@ -1102,58 +1102,58 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>arafight_pesc</v>
+        <v>kelly_ottoni</v>
       </c>
       <c r="B51">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C51">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="D51">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>grapplerfight</v>
+        <v>arafight_pesc</v>
       </c>
       <c r="B52">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C52">
         <v>0</v>
       </c>
       <c r="D52">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>enzoferrari680</v>
+        <v>grapplerfight</v>
       </c>
       <c r="B53">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="C53">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D53">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>kelly_ottoni</v>
+        <v>enzoferrari680</v>
       </c>
       <c r="B54">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="C54">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="D54">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55">
@@ -14640,13 +14640,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C3">
         <v>3</v>
       </c>
       <c r="D3">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4">
@@ -14671,10 +14671,10 @@
         <v>11</v>
       </c>
       <c r="C5">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D5">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6">
@@ -14693,58 +14693,58 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>natanborges001</v>
+        <v>johnmma9</v>
       </c>
       <c r="B7">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C7">
         <v>0</v>
       </c>
       <c r="D7">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>johnmma9</v>
+        <v>natanborges001</v>
       </c>
       <c r="B8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
       <c r="D8">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>combintel</v>
+        <v>masonharper_mma</v>
       </c>
       <c r="B9">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>masonharper_mma</v>
+        <v>combintel</v>
       </c>
       <c r="B10">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">

--- a/Engagement Rankings 2026-07.xlsx
+++ b/Engagement Rankings 2026-07.xlsx
@@ -419,13 +419,13 @@
         <v>peacegrappler</v>
       </c>
       <c r="B2">
-        <v>13573</v>
+        <v>13578</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>12284</v>
+        <v>12289</v>
       </c>
     </row>
     <row r="3">
@@ -433,7 +433,7 @@
         <v>pedr00jj</v>
       </c>
       <c r="B3">
-        <v>3679</v>
+        <v>3680</v>
       </c>
       <c r="C3">
         <v>6</v>
@@ -475,7 +475,7 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B6">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="C6">
         <v>17</v>
@@ -545,7 +545,7 @@
         <v>combintel</v>
       </c>
       <c r="B11">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C11">
         <v>2</v>
@@ -615,7 +615,7 @@
         <v>johnmma9</v>
       </c>
       <c r="B16">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -632,7 +632,7 @@
         <v>162</v>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17">
         <v>53</v>
@@ -657,7 +657,7 @@
         <v>masonharper_mma</v>
       </c>
       <c r="B19">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -1108,10 +1108,10 @@
         <v>26</v>
       </c>
       <c r="C51">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D51">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="52">
@@ -3006,49 +3006,49 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>fabinho_falcao_</v>
+        <v>mvp_lutas</v>
       </c>
       <c r="B187">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C187">
         <v>2</v>
       </c>
       <c r="D187">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>odeivisoncardoso</v>
+        <v>fabinho_falcao_</v>
       </c>
       <c r="B188">
         <v>2</v>
       </c>
       <c r="C188">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D188">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>fabiomarcelinopersonal</v>
+        <v>odeivisoncardoso</v>
       </c>
       <c r="B189">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C189">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D189">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>daniel_dias_214</v>
+        <v>fabiomarcelinopersonal</v>
       </c>
       <c r="B190">
         <v>3</v>
@@ -3062,21 +3062,21 @@
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>reifernandes</v>
+        <v>daniel_dias_214</v>
       </c>
       <c r="B191">
         <v>3</v>
       </c>
       <c r="C191">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D191">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>peacegrappler_archive</v>
+        <v>reifernandes</v>
       </c>
       <c r="B192">
         <v>3</v>
@@ -3090,13 +3090,13 @@
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>mauriciomouraprev</v>
+        <v>peacegrappler_archive</v>
       </c>
       <c r="B193">
         <v>3</v>
       </c>
       <c r="C193">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D193">
         <v>2</v>
@@ -3104,13 +3104,13 @@
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>canalgolpebaixo</v>
+        <v>mauriciomouraprev</v>
       </c>
       <c r="B194">
         <v>3</v>
       </c>
       <c r="C194">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D194">
         <v>2</v>
@@ -3118,41 +3118,41 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>cristianpsicologo</v>
+        <v>canalgolpebaixo</v>
       </c>
       <c r="B195">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C195">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D195">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>mah__vergueiro</v>
+        <v>cristianpsicologo</v>
       </c>
       <c r="B196">
+        <v>2</v>
+      </c>
+      <c r="C196">
+        <v>4</v>
+      </c>
+      <c r="D196">
         <v>3</v>
-      </c>
-      <c r="C196">
-        <v>0</v>
-      </c>
-      <c r="D196">
-        <v>0</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>pizzaria.bambina_</v>
+        <v>mah__vergueiro</v>
       </c>
       <c r="B197">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C197">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D197">
         <v>0</v>
@@ -3160,49 +3160,49 @@
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>h.codasqueves</v>
+        <v>pizzaria.bambina_</v>
       </c>
       <c r="B198">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C198">
         <v>1</v>
       </c>
       <c r="D198">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>pauloserrati</v>
+        <v>h.codasqueves</v>
       </c>
       <c r="B199">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C199">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D199">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>alexandreconsentino</v>
+        <v>pauloserrati</v>
       </c>
       <c r="B200">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C200">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D200">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>fau_gfs</v>
+        <v>alexandreconsentino</v>
       </c>
       <c r="B201">
         <v>4</v>
@@ -3216,7 +3216,7 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>lipe.ftt</v>
+        <v>fau_gfs</v>
       </c>
       <c r="B202">
         <v>4</v>
@@ -3230,21 +3230,21 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>vitorpetrino</v>
+        <v>lipe.ftt</v>
       </c>
       <c r="B203">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C203">
         <v>0</v>
       </c>
       <c r="D203">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>thompsonborralho</v>
+        <v>vitorpetrino</v>
       </c>
       <c r="B204">
         <v>3</v>
@@ -3258,7 +3258,7 @@
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>devessonjj</v>
+        <v>thompsonborralho</v>
       </c>
       <c r="B205">
         <v>3</v>
@@ -3272,77 +3272,77 @@
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>espaco_jhayoliveira</v>
+        <v>devessonjj</v>
       </c>
       <c r="B206">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C206">
         <v>0</v>
       </c>
       <c r="D206">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>artewebpersonalizados</v>
+        <v>espaco_jhayoliveira</v>
       </c>
       <c r="B207">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C207">
         <v>0</v>
       </c>
       <c r="D207">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>marcosferreira.ofc1</v>
+        <v>artewebpersonalizados</v>
       </c>
       <c r="B208">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C208">
         <v>0</v>
       </c>
       <c r="D208">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>dgswillian</v>
+        <v>marcosferreira.ofc1</v>
       </c>
       <c r="B209">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C209">
         <v>0</v>
       </c>
       <c r="D209">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>lili.munix</v>
+        <v>dgswillian</v>
       </c>
       <c r="B210">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C210">
         <v>0</v>
       </c>
       <c r="D210">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>victorhenriquebjj</v>
+        <v>lili.munix</v>
       </c>
       <c r="B211">
         <v>2</v>
@@ -3351,12 +3351,12 @@
         <v>0</v>
       </c>
       <c r="D211">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>diego.dieguito.3914</v>
+        <v>victorhenriquebjj</v>
       </c>
       <c r="B212">
         <v>2</v>
@@ -3370,7 +3370,7 @@
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>eduardorobjj</v>
+        <v>diego.dieguito.3914</v>
       </c>
       <c r="B213">
         <v>2</v>
@@ -3384,7 +3384,7 @@
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>aerowellsports</v>
+        <v>eduardorobjj</v>
       </c>
       <c r="B214">
         <v>2</v>
@@ -3398,7 +3398,7 @@
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>royrosiano</v>
+        <v>aerowellsports</v>
       </c>
       <c r="B215">
         <v>2</v>
@@ -3412,7 +3412,7 @@
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>febrancatti</v>
+        <v>royrosiano</v>
       </c>
       <c r="B216">
         <v>2</v>
@@ -3426,7 +3426,7 @@
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>sensei_rogerio_baltazar</v>
+        <v>febrancatti</v>
       </c>
       <c r="B217">
         <v>2</v>
@@ -3440,7 +3440,7 @@
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>jpaulo.mma</v>
+        <v>sensei_rogerio_baltazar</v>
       </c>
       <c r="B218">
         <v>2</v>
@@ -3454,7 +3454,7 @@
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>william_beckett12345</v>
+        <v>jpaulo.mma</v>
       </c>
       <c r="B219">
         <v>2</v>
@@ -3468,7 +3468,7 @@
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>janyson.s</v>
+        <v>william_beckett12345</v>
       </c>
       <c r="B220">
         <v>2</v>
@@ -3482,7 +3482,7 @@
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>_falcao95_</v>
+        <v>janyson.s</v>
       </c>
       <c r="B221">
         <v>2</v>
@@ -3496,7 +3496,7 @@
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>rodrigo.personal.muaythai</v>
+        <v>_falcao95_</v>
       </c>
       <c r="B222">
         <v>2</v>
@@ -3510,7 +3510,7 @@
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>andre_cr_daniel</v>
+        <v>rodrigo.personal.muaythai</v>
       </c>
       <c r="B223">
         <v>2</v>
@@ -3524,7 +3524,7 @@
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>wilsinho.campos</v>
+        <v>andre_cr_daniel</v>
       </c>
       <c r="B224">
         <v>2</v>
@@ -3538,7 +3538,7 @@
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>jheffzao</v>
+        <v>wilsinho.campos</v>
       </c>
       <c r="B225">
         <v>2</v>
@@ -3552,55 +3552,55 @@
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>joandersontubarao_ufc</v>
+        <v>jheffzao</v>
       </c>
       <c r="B226">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C226">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D226">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>felipedasilvalucas.bjj</v>
+        <v>joandersontubarao_ufc</v>
       </c>
       <c r="B227">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C227">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D227">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>motumbo_jr</v>
+        <v>felipedasilvalucas.bjj</v>
       </c>
       <c r="B228">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C228">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D228">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>julianoalicate</v>
+        <v>motumbo_jr</v>
       </c>
       <c r="B229">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C229">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D229">
         <v>1</v>
@@ -3608,13 +3608,13 @@
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>cairorochamma</v>
+        <v>julianoalicate</v>
       </c>
       <c r="B230">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C230">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D230">
         <v>1</v>
@@ -3622,41 +3622,41 @@
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>victus_torquatus</v>
+        <v>cairorochamma</v>
       </c>
       <c r="B231">
         <v>2</v>
       </c>
       <c r="C231">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D231">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>alexsandra_kairos</v>
+        <v>victus_torquatus</v>
       </c>
       <c r="B232">
         <v>2</v>
       </c>
       <c r="C232">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D232">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>tuizainocenciorodrigues</v>
+        <v>alexsandra_kairos</v>
       </c>
       <c r="B233">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C233">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D233">
         <v>0</v>
@@ -3664,7 +3664,7 @@
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>jocyrefan_bjj_mma</v>
+        <v>tuizainocenciorodrigues</v>
       </c>
       <c r="B234">
         <v>3</v>
@@ -3678,7 +3678,7 @@
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>multiplicaaba</v>
+        <v>jocyrefan_bjj_mma</v>
       </c>
       <c r="B235">
         <v>3</v>
@@ -3692,13 +3692,13 @@
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>disk_egg</v>
+        <v>multiplicaaba</v>
       </c>
       <c r="B236">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C236">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D236">
         <v>0</v>
@@ -3706,13 +3706,13 @@
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>mestreviniciusreviravolta</v>
+        <v>disk_egg</v>
       </c>
       <c r="B237">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C237">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D237">
         <v>0</v>
@@ -3720,55 +3720,55 @@
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>jose_luiz_thome</v>
+        <v>mestreviniciusreviravolta</v>
       </c>
       <c r="B238">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C238">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D238">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>efsantos.oficial</v>
+        <v>jose_luiz_thome</v>
       </c>
       <c r="B239">
         <v>1</v>
       </c>
       <c r="C239">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D239">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>ufc_paramountsports</v>
+        <v>efsantos.oficial</v>
       </c>
       <c r="B240">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C240">
         <v>1</v>
       </c>
       <c r="D240">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>mineirinho_jj</v>
+        <v>ufc_paramountsports</v>
       </c>
       <c r="B241">
         <v>2</v>
       </c>
       <c r="C241">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D241">
         <v>1</v>
@@ -3776,13 +3776,13 @@
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>marifferreirac</v>
+        <v>mineirinho_jj</v>
       </c>
       <c r="B242">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C242">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D242">
         <v>1</v>
@@ -3790,13 +3790,13 @@
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>juliochagasmma</v>
+        <v>marifferreirac</v>
       </c>
       <c r="B243">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C243">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D243">
         <v>1</v>
@@ -3804,35 +3804,35 @@
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>orafao1</v>
+        <v>juliochagasmma</v>
       </c>
       <c r="B244">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C244">
         <v>0</v>
       </c>
       <c r="D244">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>lopesbrunao</v>
+        <v>orafao1</v>
       </c>
       <c r="B245">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C245">
         <v>0</v>
       </c>
       <c r="D245">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>claudiaottoni19</v>
+        <v>lopesbrunao</v>
       </c>
       <c r="B246">
         <v>2</v>
@@ -3846,7 +3846,7 @@
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>sr.valter</v>
+        <v>claudiaottoni19</v>
       </c>
       <c r="B247">
         <v>2</v>
@@ -3860,7 +3860,7 @@
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>marcos.jordao.bjj</v>
+        <v>sr.valter</v>
       </c>
       <c r="B248">
         <v>2</v>
@@ -3874,77 +3874,77 @@
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>meol.socialmidia</v>
+        <v>marcos.jordao.bjj</v>
       </c>
       <c r="B249">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C249">
         <v>0</v>
       </c>
       <c r="D249">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>yamasakinhobjj</v>
+        <v>meol.socialmidia</v>
       </c>
       <c r="B250">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C250">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D250">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>cami28_l</v>
+        <v>yamasakinhobjj</v>
       </c>
       <c r="B251">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C251">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D251">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>chrislima____</v>
+        <v>cami28_l</v>
       </c>
       <c r="B252">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C252">
         <v>0</v>
       </c>
       <c r="D252">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>flaviakaena</v>
+        <v>chrislima____</v>
       </c>
       <c r="B253">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C253">
         <v>0</v>
       </c>
       <c r="D253">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>c.m_figth</v>
+        <v>flaviakaena</v>
       </c>
       <c r="B254">
         <v>3</v>
@@ -3958,35 +3958,35 @@
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>leo.ribeiro.bjj</v>
+        <v>c.m_figth</v>
       </c>
       <c r="B255">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C255">
         <v>0</v>
       </c>
       <c r="D255">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>e_car.doso</v>
+        <v>leo.ribeiro.bjj</v>
       </c>
       <c r="B256">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C256">
         <v>0</v>
       </c>
       <c r="D256">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>ellen.cristinaaa</v>
+        <v>e_car.doso</v>
       </c>
       <c r="B257">
         <v>3</v>
@@ -4000,77 +4000,77 @@
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>shawlinoficial</v>
+        <v>ellen.cristinaaa</v>
       </c>
       <c r="B258">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C258">
         <v>0</v>
       </c>
       <c r="D258">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>couragemma</v>
+        <v>shawlinoficial</v>
       </c>
       <c r="B259">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C259">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D259">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>kaua_limaofc</v>
+        <v>couragemma</v>
       </c>
       <c r="B260">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C260">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D260">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>ruangzk</v>
+        <v>kaua_limaofc</v>
       </c>
       <c r="B261">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C261">
         <v>0</v>
       </c>
       <c r="D261">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>emerson_lucaszx</v>
+        <v>ruangzk</v>
       </c>
       <c r="B262">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C262">
         <v>0</v>
       </c>
       <c r="D262">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>clouddhidden</v>
+        <v>emerson_lucaszx</v>
       </c>
       <c r="B263">
         <v>2</v>
@@ -4084,21 +4084,21 @@
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>_matheusifernandes</v>
+        <v>clouddhidden</v>
       </c>
       <c r="B264">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C264">
         <v>0</v>
       </c>
       <c r="D264">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>bryantank_</v>
+        <v>_matheusifernandes</v>
       </c>
       <c r="B265">
         <v>1</v>
@@ -4112,7 +4112,7 @@
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>ruan.arcanjo01</v>
+        <v>bryantank_</v>
       </c>
       <c r="B266">
         <v>1</v>
@@ -4126,7 +4126,7 @@
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>coyote_style_hair</v>
+        <v>ruan.arcanjo01</v>
       </c>
       <c r="B267">
         <v>1</v>
@@ -4140,7 +4140,7 @@
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>edsoncostateixeirabjj</v>
+        <v>coyote_style_hair</v>
       </c>
       <c r="B268">
         <v>1</v>
@@ -4154,16 +4154,16 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>mvp_lutas</v>
+        <v>edsoncostateixeirabjj</v>
       </c>
       <c r="B269">
         <v>1</v>
       </c>
       <c r="C269">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D269">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="270">
@@ -14626,13 +14626,13 @@
         <v>peacegrappler</v>
       </c>
       <c r="B2">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3">
@@ -14640,7 +14640,7 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C3">
         <v>3</v>
@@ -14671,10 +14671,10 @@
         <v>11</v>
       </c>
       <c r="C5">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D5">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6">
@@ -14682,7 +14682,7 @@
         <v>pedr00jj</v>
       </c>
       <c r="B6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -14696,7 +14696,7 @@
         <v>johnmma9</v>
       </c>
       <c r="B7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -14707,16 +14707,16 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>natanborges001</v>
+        <v>combintel</v>
       </c>
       <c r="B8">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
       <c r="D8">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -14724,7 +14724,7 @@
         <v>masonharper_mma</v>
       </c>
       <c r="B9">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -14735,16 +14735,16 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>combintel</v>
+        <v>natanborges001</v>
       </c>
       <c r="B10">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
@@ -14783,7 +14783,7 @@
         <v>6</v>
       </c>
       <c r="C13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13">
         <v>4</v>
@@ -15071,7 +15071,7 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>adriano.trator</v>
+        <v>mvp_lutas</v>
       </c>
       <c r="B34">
         <v>3</v>
@@ -15080,26 +15080,26 @@
         <v>2</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>lili.munix</v>
+        <v>adriano.trator</v>
       </c>
       <c r="B35">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D35">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>gdazuera</v>
+        <v>lili.munix</v>
       </c>
       <c r="B36">
         <v>2</v>
@@ -15113,35 +15113,35 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>canalgolpebaixo</v>
+        <v>gdazuera</v>
       </c>
       <c r="B37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C37">
         <v>0</v>
       </c>
       <c r="D37">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>pg_grappling</v>
+        <v>canalgolpebaixo</v>
       </c>
       <c r="B38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C38">
         <v>0</v>
       </c>
       <c r="D38">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>sueli_ferreira48</v>
+        <v>pg_grappling</v>
       </c>
       <c r="B39">
         <v>2</v>
@@ -15150,12 +15150,12 @@
         <v>0</v>
       </c>
       <c r="D39">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>ottonimestre</v>
+        <v>sueli_ferreira48</v>
       </c>
       <c r="B40">
         <v>2</v>
@@ -15169,7 +15169,7 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>shawlinoficial</v>
+        <v>ottonimestre</v>
       </c>
       <c r="B41">
         <v>2</v>
@@ -15183,16 +15183,16 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>mvp_lutas</v>
+        <v>shawlinoficial</v>
       </c>
       <c r="B42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C42">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D42">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">

--- a/Engagement Rankings 2026-07.xlsx
+++ b/Engagement Rankings 2026-07.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1014"/>
+  <dimension ref="A1:D1025"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -475,13 +475,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B6">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="C6">
         <v>17</v>
       </c>
       <c r="D6">
-        <v>757</v>
+        <v>758</v>
       </c>
     </row>
     <row r="7">
@@ -786,10 +786,10 @@
         <v>33</v>
       </c>
       <c r="C28">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D28">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="29">
@@ -1018,44 +1018,44 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>rayn.avaro</v>
+        <v>leonardomesquitamma</v>
       </c>
       <c r="B45">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C45">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D45">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>leonardomesquitamma</v>
+        <v>propeace_fight</v>
       </c>
       <c r="B46">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C46">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D46">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>propeace_fight</v>
+        <v>rayn.avaro</v>
       </c>
       <c r="B47">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C47">
         <v>1</v>
       </c>
       <c r="D47">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="48">
@@ -1088,30 +1088,30 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>rhuansales.mma</v>
+        <v>kelly_ottoni</v>
       </c>
       <c r="B50">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C50">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D50">
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>kelly_ottoni</v>
+        <v>rhuansales.mma</v>
       </c>
       <c r="B51">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C51">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="D51">
-        <v>26</v>
+        <v>17</v>
       </c>
     </row>
     <row r="52">
@@ -1242,35 +1242,35 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>shawlin13oficial</v>
+        <v>_cardoso_caio_</v>
       </c>
       <c r="B61">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="C61">
         <v>0</v>
       </c>
       <c r="D61">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>pedromadeira.s</v>
+        <v>shawlin13oficial</v>
       </c>
       <c r="B62">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C62">
         <v>0</v>
       </c>
       <c r="D62">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>_cardoso_caio_</v>
+        <v>pedromadeira.s</v>
       </c>
       <c r="B63">
         <v>31</v>
@@ -1279,7 +1279,7 @@
         <v>0</v>
       </c>
       <c r="D63">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="64">
@@ -1354,30 +1354,30 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>alvesmidih</v>
+        <v>marcelogabrielmma</v>
       </c>
       <c r="B69">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C69">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D69">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>marcelogabrielmma</v>
+        <v>alvesmidih</v>
       </c>
       <c r="B70">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C70">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D70">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="71">
@@ -1385,7 +1385,7 @@
         <v>vndcardoso</v>
       </c>
       <c r="B71">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C71">
         <v>0</v>
@@ -1410,21 +1410,21 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>laisrebeiro10</v>
+        <v>tiwifenixmma</v>
       </c>
       <c r="B73">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C73">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D73">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>docinhos26</v>
+        <v>laisrebeiro10</v>
       </c>
       <c r="B74">
         <v>19</v>
@@ -1433,21 +1433,21 @@
         <v>0</v>
       </c>
       <c r="D74">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>tiwifenixmma</v>
+        <v>docinhos26</v>
       </c>
       <c r="B75">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C75">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D75">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76">
@@ -1556,7 +1556,7 @@
         <v>9</v>
       </c>
       <c r="C83">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D83">
         <v>14</v>
@@ -2810,27 +2810,27 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>jean_ferreira_br</v>
+        <v>mestreviniciusreviravolta</v>
       </c>
       <c r="B173">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C173">
         <v>1</v>
       </c>
       <c r="D173">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>salost.ofc</v>
+        <v>jean_ferreira_br</v>
       </c>
       <c r="B174">
         <v>5</v>
       </c>
       <c r="C174">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D174">
         <v>0</v>
@@ -2838,49 +2838,49 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>gabrielsouzamma</v>
+        <v>salost.ofc</v>
       </c>
       <c r="B175">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C175">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D175">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>wilson_n_janjacomo</v>
+        <v>gabrielsouzamma</v>
       </c>
       <c r="B176">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C176">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D176">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>carlos_hm_iglesias</v>
+        <v>wilson_n_janjacomo</v>
       </c>
       <c r="B177">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C177">
         <v>0</v>
       </c>
       <c r="D177">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>helenmacielmma</v>
+        <v>carlos_hm_iglesias</v>
       </c>
       <c r="B178">
         <v>3</v>
@@ -2894,7 +2894,7 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>peacegrappler_podcast</v>
+        <v>helenmacielmma</v>
       </c>
       <c r="B179">
         <v>3</v>
@@ -2908,7 +2908,7 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>y.arthur_01</v>
+        <v>peacegrappler_podcast</v>
       </c>
       <c r="B180">
         <v>3</v>
@@ -2917,54 +2917,54 @@
         <v>0</v>
       </c>
       <c r="D180">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>s__simone__</v>
+        <v>y.arthur_01</v>
       </c>
       <c r="B181">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C181">
         <v>0</v>
       </c>
       <c r="D181">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>maxbjj_0</v>
+        <v>s__simone__</v>
       </c>
       <c r="B182">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C182">
         <v>0</v>
       </c>
       <c r="D182">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>vincenzo_pit_monster</v>
+        <v>maxbjj_0</v>
       </c>
       <c r="B183">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C183">
         <v>0</v>
       </c>
       <c r="D183">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>rian.vitorjj</v>
+        <v>vincenzo_pit_monster</v>
       </c>
       <c r="B184">
         <v>2</v>
@@ -2978,7 +2978,7 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>lonbradao__777</v>
+        <v>rian.vitorjj</v>
       </c>
       <c r="B185">
         <v>2</v>
@@ -2992,7 +2992,7 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>wesleysepulveda__mma</v>
+        <v>lonbradao__777</v>
       </c>
       <c r="B186">
         <v>2</v>
@@ -3006,63 +3006,63 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>mvp_lutas</v>
+        <v>wesleysepulveda__mma</v>
       </c>
       <c r="B187">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C187">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D187">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>fabinho_falcao_</v>
+        <v>mvp_lutas</v>
       </c>
       <c r="B188">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C188">
         <v>2</v>
       </c>
       <c r="D188">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>odeivisoncardoso</v>
+        <v>fabinho_falcao_</v>
       </c>
       <c r="B189">
         <v>2</v>
       </c>
       <c r="C189">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D189">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>fabiomarcelinopersonal</v>
+        <v>odeivisoncardoso</v>
       </c>
       <c r="B190">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C190">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D190">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>daniel_dias_214</v>
+        <v>fabiomarcelinopersonal</v>
       </c>
       <c r="B191">
         <v>3</v>
@@ -3076,21 +3076,21 @@
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>reifernandes</v>
+        <v>daniel_dias_214</v>
       </c>
       <c r="B192">
         <v>3</v>
       </c>
       <c r="C192">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D192">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>peacegrappler_archive</v>
+        <v>reifernandes</v>
       </c>
       <c r="B193">
         <v>3</v>
@@ -3104,13 +3104,13 @@
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>mauriciomouraprev</v>
+        <v>peacegrappler_archive</v>
       </c>
       <c r="B194">
         <v>3</v>
       </c>
       <c r="C194">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D194">
         <v>2</v>
@@ -3118,13 +3118,13 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>canalgolpebaixo</v>
+        <v>mauriciomouraprev</v>
       </c>
       <c r="B195">
         <v>3</v>
       </c>
       <c r="C195">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D195">
         <v>2</v>
@@ -3132,41 +3132,41 @@
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>cristianpsicologo</v>
+        <v>canalgolpebaixo</v>
       </c>
       <c r="B196">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C196">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D196">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>mah__vergueiro</v>
+        <v>cristianpsicologo</v>
       </c>
       <c r="B197">
+        <v>2</v>
+      </c>
+      <c r="C197">
+        <v>4</v>
+      </c>
+      <c r="D197">
         <v>3</v>
-      </c>
-      <c r="C197">
-        <v>0</v>
-      </c>
-      <c r="D197">
-        <v>0</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>pizzaria.bambina_</v>
+        <v>mah__vergueiro</v>
       </c>
       <c r="B198">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C198">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D198">
         <v>0</v>
@@ -3174,49 +3174,49 @@
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>h.codasqueves</v>
+        <v>pizzaria.bambina_</v>
       </c>
       <c r="B199">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C199">
         <v>1</v>
       </c>
       <c r="D199">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>pauloserrati</v>
+        <v>h.codasqueves</v>
       </c>
       <c r="B200">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C200">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D200">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>alexandreconsentino</v>
+        <v>pauloserrati</v>
       </c>
       <c r="B201">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C201">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D201">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>fau_gfs</v>
+        <v>alexandreconsentino</v>
       </c>
       <c r="B202">
         <v>4</v>
@@ -3230,7 +3230,7 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>lipe.ftt</v>
+        <v>fau_gfs</v>
       </c>
       <c r="B203">
         <v>4</v>
@@ -3244,21 +3244,21 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>vitorpetrino</v>
+        <v>lipe.ftt</v>
       </c>
       <c r="B204">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C204">
         <v>0</v>
       </c>
       <c r="D204">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>thompsonborralho</v>
+        <v>vitorpetrino</v>
       </c>
       <c r="B205">
         <v>3</v>
@@ -3272,7 +3272,7 @@
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>devessonjj</v>
+        <v>thompsonborralho</v>
       </c>
       <c r="B206">
         <v>3</v>
@@ -3286,77 +3286,77 @@
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>espaco_jhayoliveira</v>
+        <v>devessonjj</v>
       </c>
       <c r="B207">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C207">
         <v>0</v>
       </c>
       <c r="D207">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>artewebpersonalizados</v>
+        <v>espaco_jhayoliveira</v>
       </c>
       <c r="B208">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C208">
         <v>0</v>
       </c>
       <c r="D208">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>marcosferreira.ofc1</v>
+        <v>artewebpersonalizados</v>
       </c>
       <c r="B209">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C209">
         <v>0</v>
       </c>
       <c r="D209">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>dgswillian</v>
+        <v>marcosferreira.ofc1</v>
       </c>
       <c r="B210">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C210">
         <v>0</v>
       </c>
       <c r="D210">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>lili.munix</v>
+        <v>dgswillian</v>
       </c>
       <c r="B211">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C211">
         <v>0</v>
       </c>
       <c r="D211">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>victorhenriquebjj</v>
+        <v>lili.munix</v>
       </c>
       <c r="B212">
         <v>2</v>
@@ -3365,12 +3365,12 @@
         <v>0</v>
       </c>
       <c r="D212">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>diego.dieguito.3914</v>
+        <v>victorhenriquebjj</v>
       </c>
       <c r="B213">
         <v>2</v>
@@ -3384,7 +3384,7 @@
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>eduardorobjj</v>
+        <v>diego.dieguito.3914</v>
       </c>
       <c r="B214">
         <v>2</v>
@@ -3398,7 +3398,7 @@
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>aerowellsports</v>
+        <v>eduardorobjj</v>
       </c>
       <c r="B215">
         <v>2</v>
@@ -3412,7 +3412,7 @@
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>royrosiano</v>
+        <v>aerowellsports</v>
       </c>
       <c r="B216">
         <v>2</v>
@@ -3426,7 +3426,7 @@
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>febrancatti</v>
+        <v>royrosiano</v>
       </c>
       <c r="B217">
         <v>2</v>
@@ -3440,7 +3440,7 @@
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>sensei_rogerio_baltazar</v>
+        <v>febrancatti</v>
       </c>
       <c r="B218">
         <v>2</v>
@@ -3454,7 +3454,7 @@
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>jpaulo.mma</v>
+        <v>sensei_rogerio_baltazar</v>
       </c>
       <c r="B219">
         <v>2</v>
@@ -3468,7 +3468,7 @@
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>william_beckett12345</v>
+        <v>jpaulo.mma</v>
       </c>
       <c r="B220">
         <v>2</v>
@@ -3482,7 +3482,7 @@
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>janyson.s</v>
+        <v>william_beckett12345</v>
       </c>
       <c r="B221">
         <v>2</v>
@@ -3496,7 +3496,7 @@
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>_falcao95_</v>
+        <v>janyson.s</v>
       </c>
       <c r="B222">
         <v>2</v>
@@ -3510,7 +3510,7 @@
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>rodrigo.personal.muaythai</v>
+        <v>_falcao95_</v>
       </c>
       <c r="B223">
         <v>2</v>
@@ -3524,7 +3524,7 @@
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>andre_cr_daniel</v>
+        <v>rodrigo.personal.muaythai</v>
       </c>
       <c r="B224">
         <v>2</v>
@@ -3538,7 +3538,7 @@
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>wilsinho.campos</v>
+        <v>andre_cr_daniel</v>
       </c>
       <c r="B225">
         <v>2</v>
@@ -3552,7 +3552,7 @@
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>jheffzao</v>
+        <v>wilsinho.campos</v>
       </c>
       <c r="B226">
         <v>2</v>
@@ -3566,55 +3566,55 @@
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>joandersontubarao_ufc</v>
+        <v>jheffzao</v>
       </c>
       <c r="B227">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C227">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D227">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>felipedasilvalucas.bjj</v>
+        <v>joandersontubarao_ufc</v>
       </c>
       <c r="B228">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C228">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D228">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>motumbo_jr</v>
+        <v>felipedasilvalucas.bjj</v>
       </c>
       <c r="B229">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C229">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D229">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>julianoalicate</v>
+        <v>motumbo_jr</v>
       </c>
       <c r="B230">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C230">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D230">
         <v>1</v>
@@ -3622,13 +3622,13 @@
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>cairorochamma</v>
+        <v>julianoalicate</v>
       </c>
       <c r="B231">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C231">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D231">
         <v>1</v>
@@ -3636,41 +3636,41 @@
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>victus_torquatus</v>
+        <v>cairorochamma</v>
       </c>
       <c r="B232">
         <v>2</v>
       </c>
       <c r="C232">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D232">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>alexsandra_kairos</v>
+        <v>victus_torquatus</v>
       </c>
       <c r="B233">
         <v>2</v>
       </c>
       <c r="C233">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D233">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>tuizainocenciorodrigues</v>
+        <v>alexsandra_kairos</v>
       </c>
       <c r="B234">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C234">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D234">
         <v>0</v>
@@ -3678,7 +3678,7 @@
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>jocyrefan_bjj_mma</v>
+        <v>tuizainocenciorodrigues</v>
       </c>
       <c r="B235">
         <v>3</v>
@@ -3692,7 +3692,7 @@
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>multiplicaaba</v>
+        <v>jocyrefan_bjj_mma</v>
       </c>
       <c r="B236">
         <v>3</v>
@@ -3706,13 +3706,13 @@
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>disk_egg</v>
+        <v>multiplicaaba</v>
       </c>
       <c r="B237">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C237">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D237">
         <v>0</v>
@@ -3720,13 +3720,13 @@
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>mestreviniciusreviravolta</v>
+        <v>disk_egg</v>
       </c>
       <c r="B238">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C238">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D238">
         <v>0</v>
@@ -5484,105 +5484,105 @@
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>dr.daniloduartefisio</v>
+        <v>b.scarvalhooo</v>
       </c>
       <c r="B364">
         <v>1</v>
       </c>
       <c r="C364">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D364">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>pablo_bvg</v>
+        <v>dr.daniloduartefisio</v>
       </c>
       <c r="B365">
         <v>1</v>
       </c>
       <c r="C365">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D365">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>djsagatoficial</v>
+        <v>pablo_bvg</v>
       </c>
       <c r="B366">
         <v>1</v>
       </c>
       <c r="C366">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D366">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>marceloscorzato</v>
+        <v>djsagatoficial</v>
       </c>
       <c r="B367">
         <v>1</v>
       </c>
       <c r="C367">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D367">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>sergio_alves_bjj</v>
+        <v>marceloscorzato</v>
       </c>
       <c r="B368">
         <v>1</v>
       </c>
       <c r="C368">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D368">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>pedro_pavin_</v>
+        <v>sergio_alves_bjj</v>
       </c>
       <c r="B369">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C369">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D369">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>treinaadorrafael</v>
+        <v>pedro_pavin_</v>
       </c>
       <c r="B370">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C370">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D370">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>estevaotoledo</v>
+        <v>treinaadorrafael</v>
       </c>
       <c r="B371">
         <v>1</v>
@@ -5596,13 +5596,13 @@
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>kael_lyto</v>
+        <v>estevaotoledo</v>
       </c>
       <c r="B372">
         <v>1</v>
       </c>
       <c r="C372">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D372">
         <v>0</v>
@@ -5610,13 +5610,13 @@
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>yurimartins1_</v>
+        <v>kael_lyto</v>
       </c>
       <c r="B373">
         <v>1</v>
       </c>
       <c r="C373">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D373">
         <v>0</v>
@@ -5624,7 +5624,7 @@
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>maria.pereiradeoliveira.5283</v>
+        <v>yurimartins1_</v>
       </c>
       <c r="B374">
         <v>1</v>
@@ -5638,7 +5638,7 @@
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>matheusteodoro_1</v>
+        <v>maria.pereiradeoliveira.5283</v>
       </c>
       <c r="B375">
         <v>1</v>
@@ -5652,7 +5652,7 @@
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>kawannsenaboxe</v>
+        <v>matheusteodoro_1</v>
       </c>
       <c r="B376">
         <v>1</v>
@@ -5666,7 +5666,7 @@
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>guiiviieira_</v>
+        <v>kawannsenaboxe</v>
       </c>
       <c r="B377">
         <v>1</v>
@@ -5680,7 +5680,7 @@
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>cshigueo</v>
+        <v>guiiviieira_</v>
       </c>
       <c r="B378">
         <v>1</v>
@@ -5694,7 +5694,7 @@
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>vitorhugo_vtr</v>
+        <v>cshigueo</v>
       </c>
       <c r="B379">
         <v>1</v>
@@ -5708,7 +5708,7 @@
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>danni_goncalves12</v>
+        <v>vitorhugo_vtr</v>
       </c>
       <c r="B380">
         <v>1</v>
@@ -5722,7 +5722,7 @@
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>mttsm._</v>
+        <v>danni_goncalves12</v>
       </c>
       <c r="B381">
         <v>1</v>
@@ -5736,7 +5736,7 @@
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>andrealvess02</v>
+        <v>mttsm._</v>
       </c>
       <c r="B382">
         <v>1</v>
@@ -5750,7 +5750,7 @@
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>gildojiu</v>
+        <v>andrealvess02</v>
       </c>
       <c r="B383">
         <v>1</v>
@@ -5764,13 +5764,13 @@
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>fagnerosensei</v>
+        <v>gildojiu</v>
       </c>
       <c r="B384">
         <v>1</v>
       </c>
       <c r="C384">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D384">
         <v>0</v>
@@ -5778,7 +5778,7 @@
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>flavio.dequeiroz</v>
+        <v>fagnerosensei</v>
       </c>
       <c r="B385">
         <v>1</v>
@@ -5792,13 +5792,13 @@
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>030sami</v>
+        <v>flavio.dequeiroz</v>
       </c>
       <c r="B386">
         <v>1</v>
       </c>
       <c r="C386">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D386">
         <v>0</v>
@@ -5806,35 +5806,35 @@
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>giulia.fasolato</v>
+        <v>030sami</v>
       </c>
       <c r="B387">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C387">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D387">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>selipereirapereira</v>
+        <v>giulia.fasolato</v>
       </c>
       <c r="B388">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C388">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D388">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>d.silvamma</v>
+        <v>selipereirapereira</v>
       </c>
       <c r="B389">
         <v>1</v>
@@ -5848,7 +5848,7 @@
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>kalindrafaria</v>
+        <v>d.silvamma</v>
       </c>
       <c r="B390">
         <v>1</v>
@@ -5862,35 +5862,35 @@
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>igorsiqueiramma57</v>
+        <v>kalindrafaria</v>
       </c>
       <c r="B391">
         <v>1</v>
       </c>
       <c r="C391">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D391">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>oniszczuk_ko</v>
+        <v>igorsiqueiramma57</v>
       </c>
       <c r="B392">
         <v>1</v>
       </c>
       <c r="C392">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D392">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>andreibjj</v>
+        <v>oniszczuk_ko</v>
       </c>
       <c r="B393">
         <v>1</v>
@@ -5904,7 +5904,7 @@
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>manoelwilliamdejesus</v>
+        <v>andreibjj</v>
       </c>
       <c r="B394">
         <v>1</v>
@@ -5918,7 +5918,7 @@
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>killemquick</v>
+        <v>manoelwilliamdejesus</v>
       </c>
       <c r="B395">
         <v>1</v>
@@ -5932,7 +5932,7 @@
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>chuck_tlp</v>
+        <v>killemquick</v>
       </c>
       <c r="B396">
         <v>1</v>
@@ -5946,7 +5946,7 @@
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>henriquemmunhoz</v>
+        <v>chuck_tlp</v>
       </c>
       <c r="B397">
         <v>1</v>
@@ -5960,7 +5960,7 @@
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>flavio_tuba8</v>
+        <v>henriquemmunhoz</v>
       </c>
       <c r="B398">
         <v>1</v>
@@ -5974,13 +5974,13 @@
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>koliseu.br</v>
+        <v>flavio_tuba8</v>
       </c>
       <c r="B399">
         <v>1</v>
       </c>
       <c r="C399">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D399">
         <v>0</v>
@@ -5988,41 +5988,41 @@
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>aida_dos_sonhos</v>
+        <v>koliseu.br</v>
       </c>
       <c r="B400">
         <v>1</v>
       </c>
       <c r="C400">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D400">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>marianappedro</v>
+        <v>aida_dos_sonhos</v>
       </c>
       <c r="B401">
         <v>1</v>
       </c>
       <c r="C401">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D401">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>cathya_ferreira</v>
+        <v>marianappedro</v>
       </c>
       <c r="B402">
         <v>1</v>
       </c>
       <c r="C402">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D402">
         <v>0</v>
@@ -6030,13 +6030,13 @@
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>plmoreiraz</v>
+        <v>cathya_ferreira</v>
       </c>
       <c r="B403">
         <v>1</v>
       </c>
       <c r="C403">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D403">
         <v>0</v>
@@ -6044,7 +6044,7 @@
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>morena_ramos</v>
+        <v>plmoreiraz</v>
       </c>
       <c r="B404">
         <v>1</v>
@@ -6058,21 +6058,21 @@
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>_pedro0h</v>
+        <v>morena_ramos</v>
       </c>
       <c r="B405">
         <v>1</v>
       </c>
       <c r="C405">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D405">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>percepcar</v>
+        <v>_pedro0h</v>
       </c>
       <c r="B406">
         <v>1</v>
@@ -6081,12 +6081,12 @@
         <v>1</v>
       </c>
       <c r="D406">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>ojaimerocha</v>
+        <v>percepcar</v>
       </c>
       <c r="B407">
         <v>1</v>
@@ -6100,7 +6100,7 @@
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>yeslifeacademia</v>
+        <v>ojaimerocha</v>
       </c>
       <c r="B408">
         <v>1</v>
@@ -6114,7 +6114,7 @@
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>edergama.mma</v>
+        <v>yeslifeacademia</v>
       </c>
       <c r="B409">
         <v>1</v>
@@ -6128,7 +6128,7 @@
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>eliandropires</v>
+        <v>edergama.mma</v>
       </c>
       <c r="B410">
         <v>1</v>
@@ -6142,7 +6142,7 @@
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>_gabrielpego</v>
+        <v>eliandropires</v>
       </c>
       <c r="B411">
         <v>1</v>
@@ -6156,7 +6156,7 @@
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>eusoufernandosaito</v>
+        <v>_gabrielpego</v>
       </c>
       <c r="B412">
         <v>1</v>
@@ -6170,7 +6170,7 @@
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>motumbo_team</v>
+        <v>eusoufernandosaito</v>
       </c>
       <c r="B413">
         <v>1</v>
@@ -6184,7 +6184,7 @@
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>beabmendes_</v>
+        <v>motumbo_team</v>
       </c>
       <c r="B414">
         <v>1</v>
@@ -6198,7 +6198,7 @@
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>jenifer.ciborg</v>
+        <v>beabmendes_</v>
       </c>
       <c r="B415">
         <v>1</v>
@@ -6212,7 +6212,7 @@
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>felipefrancoufc</v>
+        <v>jenifer.ciborg</v>
       </c>
       <c r="B416">
         <v>1</v>
@@ -6226,7 +6226,7 @@
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>leonardoo_paixao</v>
+        <v>felipefrancoufc</v>
       </c>
       <c r="B417">
         <v>1</v>
@@ -6240,35 +6240,35 @@
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>antonioemanuel.13</v>
+        <v>leonardoo_paixao</v>
       </c>
       <c r="B418">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C418">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D418">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>gasparjr1983</v>
+        <v>antonioemanuel.13</v>
       </c>
       <c r="B419">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C419">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D419">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>magnoddias</v>
+        <v>gasparjr1983</v>
       </c>
       <c r="B420">
         <v>1</v>
@@ -6282,7 +6282,7 @@
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>ballestarbosa</v>
+        <v>magnoddias</v>
       </c>
       <c r="B421">
         <v>1</v>
@@ -6296,7 +6296,7 @@
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>marcioticotobarbosa</v>
+        <v>ballestarbosa</v>
       </c>
       <c r="B422">
         <v>1</v>
@@ -6310,7 +6310,7 @@
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>renan.dniz</v>
+        <v>marcioticotobarbosa</v>
       </c>
       <c r="B423">
         <v>1</v>
@@ -6324,7 +6324,7 @@
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>nunesjanjacomo</v>
+        <v>renan.dniz</v>
       </c>
       <c r="B424">
         <v>1</v>
@@ -6338,7 +6338,7 @@
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>eumarianojr</v>
+        <v>nunesjanjacomo</v>
       </c>
       <c r="B425">
         <v>1</v>
@@ -6352,7 +6352,7 @@
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>mmapalpitex</v>
+        <v>eumarianojr</v>
       </c>
       <c r="B426">
         <v>1</v>
@@ -6366,7 +6366,7 @@
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>chillyfit007</v>
+        <v>mmapalpitex</v>
       </c>
       <c r="B427">
         <v>1</v>
@@ -6380,7 +6380,7 @@
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>george.laroque</v>
+        <v>chillyfit007</v>
       </c>
       <c r="B428">
         <v>1</v>
@@ -6394,41 +6394,41 @@
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>dudaadantass</v>
+        <v>george.laroque</v>
       </c>
       <c r="B429">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C429">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D429">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>cassiosants__</v>
+        <v>dudaadantass</v>
       </c>
       <c r="B430">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C430">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D430">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>mth_fernandes031</v>
+        <v>cassiosants__</v>
       </c>
       <c r="B431">
         <v>1</v>
       </c>
       <c r="C431">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D431">
         <v>0</v>
@@ -6436,7 +6436,7 @@
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>jhoninhaoficial031</v>
+        <v>mth_fernandes031</v>
       </c>
       <c r="B432">
         <v>1</v>
@@ -6450,7 +6450,7 @@
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>bigjota.music</v>
+        <v>jhoninhaoficial031</v>
       </c>
       <c r="B433">
         <v>1</v>
@@ -6464,7 +6464,7 @@
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>lay_roqs</v>
+        <v>bigjota.music</v>
       </c>
       <c r="B434">
         <v>1</v>
@@ -6478,7 +6478,7 @@
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>gabrielsilva_mma</v>
+        <v>lay_roqs</v>
       </c>
       <c r="B435">
         <v>1</v>
@@ -6492,7 +6492,7 @@
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>igorfso_</v>
+        <v>gabrielsilva_mma</v>
       </c>
       <c r="B436">
         <v>1</v>
@@ -6506,7 +6506,7 @@
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>gutocriativo</v>
+        <v>igorfso_</v>
       </c>
       <c r="B437">
         <v>1</v>
@@ -6520,7 +6520,7 @@
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>leosacraa</v>
+        <v>gutocriativo</v>
       </c>
       <c r="B438">
         <v>1</v>
@@ -6534,7 +6534,7 @@
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>vinyrodriguesoficial</v>
+        <v>leosacraa</v>
       </c>
       <c r="B439">
         <v>1</v>
@@ -6548,7 +6548,7 @@
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>olga.oliveira013</v>
+        <v>vinyrodriguesoficial</v>
       </c>
       <c r="B440">
         <v>1</v>
@@ -6562,7 +6562,7 @@
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>leandro_motiv4</v>
+        <v>olga.oliveira013</v>
       </c>
       <c r="B441">
         <v>1</v>
@@ -6576,7 +6576,7 @@
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>andrejetx</v>
+        <v>leandro_motiv4</v>
       </c>
       <c r="B442">
         <v>1</v>
@@ -6590,7 +6590,7 @@
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>phillipe.harry</v>
+        <v>andrejetx</v>
       </c>
       <c r="B443">
         <v>1</v>
@@ -6604,7 +6604,7 @@
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>andre.legendre.10</v>
+        <v>phillipe.harry</v>
       </c>
       <c r="B444">
         <v>1</v>
@@ -6618,7 +6618,7 @@
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>wagner_alexandre_w_a</v>
+        <v>andre.legendre.10</v>
       </c>
       <c r="B445">
         <v>1</v>
@@ -6632,13 +6632,13 @@
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>rafaela_duaartee</v>
+        <v>wagner_alexandre_w_a</v>
       </c>
       <c r="B446">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C446">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D446">
         <v>0</v>
@@ -6646,13 +6646,13 @@
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>cezary_oleksiejczuk</v>
+        <v>rafaela_duaartee</v>
       </c>
       <c r="B447">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C447">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D447">
         <v>0</v>
@@ -6660,7 +6660,7 @@
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>_alcantara.bru</v>
+        <v>cezary_oleksiejczuk</v>
       </c>
       <c r="B448">
         <v>1</v>
@@ -6674,7 +6674,7 @@
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>arthurhenrique.sx</v>
+        <v>_alcantara.bru</v>
       </c>
       <c r="B449">
         <v>1</v>
@@ -6688,7 +6688,7 @@
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>fran.ruys</v>
+        <v>arthurhenrique.sx</v>
       </c>
       <c r="B450">
         <v>1</v>
@@ -6702,7 +6702,7 @@
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>vitor_buck</v>
+        <v>fran.ruys</v>
       </c>
       <c r="B451">
         <v>1</v>
@@ -6716,7 +6716,7 @@
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>mr__rlk01</v>
+        <v>vitor_buck</v>
       </c>
       <c r="B452">
         <v>1</v>
@@ -6730,7 +6730,7 @@
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>_lsanchess_</v>
+        <v>mr__rlk01</v>
       </c>
       <c r="B453">
         <v>1</v>
@@ -6744,7 +6744,7 @@
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>gabriel_trevelin</v>
+        <v>_lsanchess_</v>
       </c>
       <c r="B454">
         <v>1</v>
@@ -6758,7 +6758,7 @@
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>danlouiz.jj</v>
+        <v>gabriel_trevelin</v>
       </c>
       <c r="B455">
         <v>1</v>
@@ -6772,7 +6772,7 @@
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>camii_bonfim</v>
+        <v>danlouiz.jj</v>
       </c>
       <c r="B456">
         <v>1</v>
@@ -6786,7 +6786,7 @@
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>flazuera14</v>
+        <v>camii_bonfim</v>
       </c>
       <c r="B457">
         <v>1</v>
@@ -6800,7 +6800,7 @@
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>gilberto_7606</v>
+        <v>flazuera14</v>
       </c>
       <c r="B458">
         <v>1</v>
@@ -6814,7 +6814,7 @@
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>aloirmarcal</v>
+        <v>gilberto_7606</v>
       </c>
       <c r="B459">
         <v>1</v>
@@ -6828,7 +6828,7 @@
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>_fernunes</v>
+        <v>aloirmarcal</v>
       </c>
       <c r="B460">
         <v>1</v>
@@ -6842,7 +6842,7 @@
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>andre_alcausa</v>
+        <v>_fernunes</v>
       </c>
       <c r="B461">
         <v>1</v>
@@ -6856,7 +6856,7 @@
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>judadany</v>
+        <v>andre_alcausa</v>
       </c>
       <c r="B462">
         <v>1</v>
@@ -6870,7 +6870,7 @@
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>pativinisf</v>
+        <v>judadany</v>
       </c>
       <c r="B463">
         <v>1</v>
@@ -6884,7 +6884,7 @@
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>guilhermeefelix__</v>
+        <v>pativinisf</v>
       </c>
       <c r="B464">
         <v>1</v>
@@ -6898,7 +6898,7 @@
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>___neller</v>
+        <v>guilhermeefelix__</v>
       </c>
       <c r="B465">
         <v>1</v>
@@ -6912,7 +6912,7 @@
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>pietroshz</v>
+        <v>___neller</v>
       </c>
       <c r="B466">
         <v>1</v>
@@ -6926,7 +6926,7 @@
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>gabicardoson</v>
+        <v>pietroshz</v>
       </c>
       <c r="B467">
         <v>1</v>
@@ -6940,7 +6940,7 @@
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>cami.terra_</v>
+        <v>gabicardoson</v>
       </c>
       <c r="B468">
         <v>1</v>
@@ -6954,7 +6954,7 @@
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>_rayysp</v>
+        <v>cami.terra_</v>
       </c>
       <c r="B469">
         <v>1</v>
@@ -6968,7 +6968,7 @@
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>_puroosso88</v>
+        <v>_rayysp</v>
       </c>
       <c r="B470">
         <v>1</v>
@@ -6982,7 +6982,7 @@
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>navarro_9430</v>
+        <v>_puroosso88</v>
       </c>
       <c r="B471">
         <v>1</v>
@@ -6996,7 +6996,7 @@
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>miguelrodriguesbjj</v>
+        <v>navarro_9430</v>
       </c>
       <c r="B472">
         <v>1</v>
@@ -7010,7 +7010,7 @@
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>benivalentinn</v>
+        <v>miguelrodriguesbjj</v>
       </c>
       <c r="B473">
         <v>1</v>
@@ -7024,7 +7024,7 @@
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>alternativaremocoes</v>
+        <v>benivalentinn</v>
       </c>
       <c r="B474">
         <v>1</v>
@@ -7038,7 +7038,7 @@
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>saj_photo_miami</v>
+        <v>alternativaremocoes</v>
       </c>
       <c r="B475">
         <v>1</v>
@@ -7052,7 +7052,7 @@
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>draanapaulaponceano</v>
+        <v>saj_photo_miami</v>
       </c>
       <c r="B476">
         <v>1</v>
@@ -7066,7 +7066,7 @@
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>charlesanthony2466</v>
+        <v>draanapaulaponceano</v>
       </c>
       <c r="B477">
         <v>1</v>
@@ -7080,7 +7080,7 @@
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>maryanagandra</v>
+        <v>charlesanthony2466</v>
       </c>
       <c r="B478">
         <v>1</v>
@@ -7094,7 +7094,7 @@
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>xavyeroficial</v>
+        <v>maryanagandra</v>
       </c>
       <c r="B479">
         <v>1</v>
@@ -7108,7 +7108,7 @@
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>geraldocnetomma</v>
+        <v>xavyeroficial</v>
       </c>
       <c r="B480">
         <v>1</v>
@@ -7122,7 +7122,7 @@
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>katiaecarreraf</v>
+        <v>geraldocnetomma</v>
       </c>
       <c r="B481">
         <v>1</v>
@@ -7136,13 +7136,13 @@
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>marinealcausa</v>
+        <v>katiaecarreraf</v>
       </c>
       <c r="B482">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C482">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D482">
         <v>0</v>
@@ -7150,13 +7150,13 @@
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>artemio_bjj</v>
+        <v>marinealcausa</v>
       </c>
       <c r="B483">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C483">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D483">
         <v>0</v>
@@ -7164,7 +7164,7 @@
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>isaac.bah_starinazzo</v>
+        <v>artemio_bjj</v>
       </c>
       <c r="B484">
         <v>1</v>
@@ -7178,7 +7178,7 @@
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>carolinne.xwp</v>
+        <v>isaac.bah_starinazzo</v>
       </c>
       <c r="B485">
         <v>1</v>
@@ -7192,7 +7192,7 @@
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>yan_touro_.7766</v>
+        <v>carolinne.xwp</v>
       </c>
       <c r="B486">
         <v>1</v>
@@ -7206,7 +7206,7 @@
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>codasqueves</v>
+        <v>yan_touro_.7766</v>
       </c>
       <c r="B487">
         <v>1</v>
@@ -7220,7 +7220,7 @@
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>lara.rpr</v>
+        <v>codasqueves</v>
       </c>
       <c r="B488">
         <v>1</v>
@@ -7234,7 +7234,7 @@
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>brothers_of_life</v>
+        <v>lara.rpr</v>
       </c>
       <c r="B489">
         <v>1</v>
@@ -7248,7 +7248,7 @@
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>minotaurinho</v>
+        <v>brothers_of_life</v>
       </c>
       <c r="B490">
         <v>1</v>
@@ -7262,7 +7262,7 @@
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>teacherthalesyouplus</v>
+        <v>minotaurinho</v>
       </c>
       <c r="B491">
         <v>1</v>
@@ -7276,7 +7276,7 @@
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>anahangelica</v>
+        <v>teacherthalesyouplus</v>
       </c>
       <c r="B492">
         <v>1</v>
@@ -7290,7 +7290,7 @@
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>frankikolimabjj</v>
+        <v>anahangelica</v>
       </c>
       <c r="B493">
         <v>1</v>
@@ -7304,7 +7304,7 @@
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>euvitormirandaa</v>
+        <v>frankikolimabjj</v>
       </c>
       <c r="B494">
         <v>1</v>
@@ -7318,7 +7318,7 @@
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>gabesantos.13</v>
+        <v>euvitormirandaa</v>
       </c>
       <c r="B495">
         <v>1</v>
@@ -7332,7 +7332,7 @@
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>mariaraimundad940</v>
+        <v>gabesantos.13</v>
       </c>
       <c r="B496">
         <v>1</v>
@@ -7346,7 +7346,7 @@
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>pdfiv</v>
+        <v>mariaraimundad940</v>
       </c>
       <c r="B497">
         <v>1</v>
@@ -7360,7 +7360,7 @@
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>_eliasffx</v>
+        <v>pdfiv</v>
       </c>
       <c r="B498">
         <v>1</v>
@@ -7374,7 +7374,7 @@
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>tonketjudes</v>
+        <v>_eliasffx</v>
       </c>
       <c r="B499">
         <v>1</v>
@@ -7388,7 +7388,7 @@
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>gandra.julya</v>
+        <v>tonketjudes</v>
       </c>
       <c r="B500">
         <v>1</v>
@@ -7402,7 +7402,7 @@
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>azulcapoeirabjj</v>
+        <v>gandra.julya</v>
       </c>
       <c r="B501">
         <v>1</v>
@@ -7416,7 +7416,7 @@
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>espacomarcialino</v>
+        <v>azulcapoeirabjj</v>
       </c>
       <c r="B502">
         <v>1</v>
@@ -7430,7 +7430,7 @@
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>andreiaatleta</v>
+        <v>espacomarcialino</v>
       </c>
       <c r="B503">
         <v>1</v>
@@ -7444,7 +7444,7 @@
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>turmanmma</v>
+        <v>andreiaatleta</v>
       </c>
       <c r="B504">
         <v>1</v>
@@ -7458,7 +7458,7 @@
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>drfelipeoliveira_adv</v>
+        <v>turmanmma</v>
       </c>
       <c r="B505">
         <v>1</v>
@@ -7472,7 +7472,7 @@
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>muriloo__ferreira</v>
+        <v>drfelipeoliveira_adv</v>
       </c>
       <c r="B506">
         <v>1</v>
@@ -7486,7 +7486,7 @@
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>sidneibabu</v>
+        <v>muriloo__ferreira</v>
       </c>
       <c r="B507">
         <v>1</v>
@@ -7500,7 +7500,7 @@
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>allisonestuchi_fisioterapeuta</v>
+        <v>sidneibabu</v>
       </c>
       <c r="B508">
         <v>1</v>
@@ -7514,7 +7514,7 @@
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>nutrivan.alves</v>
+        <v>allisonestuchi_fisioterapeuta</v>
       </c>
       <c r="B509">
         <v>1</v>
@@ -7528,7 +7528,7 @@
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>valqsm</v>
+        <v>nutrivan.alves</v>
       </c>
       <c r="B510">
         <v>1</v>
@@ -7542,7 +7542,7 @@
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>selma.ribeirotr</v>
+        <v>valqsm</v>
       </c>
       <c r="B511">
         <v>1</v>
@@ -7556,7 +7556,7 @@
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>eu_felipe_leite</v>
+        <v>selma.ribeirotr</v>
       </c>
       <c r="B512">
         <v>1</v>
@@ -7570,7 +7570,7 @@
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>do_caex_wandel</v>
+        <v>eu_felipe_leite</v>
       </c>
       <c r="B513">
         <v>1</v>
@@ -7584,7 +7584,7 @@
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>jack_hashimoto</v>
+        <v>do_caex_wandel</v>
       </c>
       <c r="B514">
         <v>1</v>
@@ -7598,7 +7598,7 @@
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>luhluhm</v>
+        <v>jack_hashimoto</v>
       </c>
       <c r="B515">
         <v>1</v>
@@ -7612,7 +7612,7 @@
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>donrey_42</v>
+        <v>luhluhm</v>
       </c>
       <c r="B516">
         <v>1</v>
@@ -7626,7 +7626,7 @@
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>lumarasantosjj</v>
+        <v>donrey_42</v>
       </c>
       <c r="B517">
         <v>1</v>
@@ -7640,7 +7640,7 @@
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>andre_luizdj</v>
+        <v>lumarasantosjj</v>
       </c>
       <c r="B518">
         <v>1</v>
@@ -7654,7 +7654,7 @@
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>itsmayraregina</v>
+        <v>andre_luizdj</v>
       </c>
       <c r="B519">
         <v>1</v>
@@ -7668,7 +7668,7 @@
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>personalmaju</v>
+        <v>itsmayraregina</v>
       </c>
       <c r="B520">
         <v>1</v>
@@ -7682,7 +7682,7 @@
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>fototatico</v>
+        <v>personalmaju</v>
       </c>
       <c r="B521">
         <v>1</v>
@@ -7696,7 +7696,7 @@
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>michel.juliano.barbershop</v>
+        <v>fototatico</v>
       </c>
       <c r="B522">
         <v>1</v>
@@ -7710,7 +7710,7 @@
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>diegomoisesribeiro</v>
+        <v>michel.juliano.barbershop</v>
       </c>
       <c r="B523">
         <v>1</v>
@@ -7724,7 +7724,7 @@
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>ruperto_696</v>
+        <v>diegomoisesribeiro</v>
       </c>
       <c r="B524">
         <v>1</v>
@@ -7738,7 +7738,7 @@
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>brunito_bernardo</v>
+        <v>ruperto_696</v>
       </c>
       <c r="B525">
         <v>1</v>
@@ -7752,7 +7752,7 @@
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>calebe1000grau</v>
+        <v>brunito_bernardo</v>
       </c>
       <c r="B526">
         <v>1</v>
@@ -7766,7 +7766,7 @@
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>lucca_bjj_01</v>
+        <v>calebe1000grau</v>
       </c>
       <c r="B527">
         <v>1</v>
@@ -7780,7 +7780,7 @@
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>clarianavillasboasoficial</v>
+        <v>lucca_bjj_01</v>
       </c>
       <c r="B528">
         <v>1</v>
@@ -7794,7 +7794,7 @@
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>williamjanser</v>
+        <v>clarianavillasboasoficial</v>
       </c>
       <c r="B529">
         <v>1</v>
@@ -7808,7 +7808,7 @@
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>aureooficial</v>
+        <v>williamjanser</v>
       </c>
       <c r="B530">
         <v>1</v>
@@ -7822,7 +7822,7 @@
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>gladyador_do_asa</v>
+        <v>aureooficial</v>
       </c>
       <c r="B531">
         <v>1</v>
@@ -7836,7 +7836,7 @@
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>chicinvancity</v>
+        <v>gladyador_do_asa</v>
       </c>
       <c r="B532">
         <v>1</v>
@@ -7850,7 +7850,7 @@
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>jeremyericjacobs</v>
+        <v>chicinvancity</v>
       </c>
       <c r="B533">
         <v>1</v>
@@ -7864,7 +7864,7 @@
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>gallupistrengthconditioning</v>
+        <v>jeremyericjacobs</v>
       </c>
       <c r="B534">
         <v>1</v>
@@ -7878,7 +7878,7 @@
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>satsangbjj</v>
+        <v>gallupistrengthconditioning</v>
       </c>
       <c r="B535">
         <v>1</v>
@@ -7892,7 +7892,7 @@
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>susiemelchionda</v>
+        <v>satsangbjj</v>
       </c>
       <c r="B536">
         <v>1</v>
@@ -7906,7 +7906,7 @@
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>alehh_novaes</v>
+        <v>susiemelchionda</v>
       </c>
       <c r="B537">
         <v>1</v>
@@ -7920,7 +7920,7 @@
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>andreaapurinaoficial</v>
+        <v>alehh_novaes</v>
       </c>
       <c r="B538">
         <v>1</v>
@@ -7934,7 +7934,7 @@
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>gilcilenecristina</v>
+        <v>andreaapurinaoficial</v>
       </c>
       <c r="B539">
         <v>1</v>
@@ -7948,7 +7948,7 @@
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>danibastiaan</v>
+        <v>gilcilenecristina</v>
       </c>
       <c r="B540">
         <v>1</v>
@@ -7962,7 +7962,7 @@
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>valbersonsantoss</v>
+        <v>danibastiaan</v>
       </c>
       <c r="B541">
         <v>1</v>
@@ -7976,7 +7976,7 @@
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>franklinamaral</v>
+        <v>valbersonsantoss</v>
       </c>
       <c r="B542">
         <v>1</v>
@@ -7990,7 +7990,7 @@
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>j.borgespz</v>
+        <v>franklinamaral</v>
       </c>
       <c r="B543">
         <v>1</v>
@@ -8004,7 +8004,7 @@
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>lucaswallaceftt</v>
+        <v>j.borgespz</v>
       </c>
       <c r="B544">
         <v>1</v>
@@ -8018,7 +8018,7 @@
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>renancarlini</v>
+        <v>lucaswallaceftt</v>
       </c>
       <c r="B545">
         <v>1</v>
@@ -8032,7 +8032,7 @@
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>almir_gdf</v>
+        <v>renancarlini</v>
       </c>
       <c r="B546">
         <v>1</v>
@@ -8046,7 +8046,7 @@
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>gpedroza1</v>
+        <v>almir_gdf</v>
       </c>
       <c r="B547">
         <v>1</v>
@@ -8060,7 +8060,7 @@
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>lilianvillaca_</v>
+        <v>gpedroza1</v>
       </c>
       <c r="B548">
         <v>1</v>
@@ -8074,7 +8074,7 @@
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>alinedoprojeto</v>
+        <v>lilianvillaca_</v>
       </c>
       <c r="B549">
         <v>1</v>
@@ -8088,7 +8088,7 @@
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>sabe_de_uma_coisa2026</v>
+        <v>alinedoprojeto</v>
       </c>
       <c r="B550">
         <v>1</v>
@@ -8102,7 +8102,7 @@
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>gratidao_jesus2026</v>
+        <v>sabe_de_uma_coisa2026</v>
       </c>
       <c r="B551">
         <v>1</v>
@@ -8116,7 +8116,7 @@
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>projeto_amigos_de_ouro</v>
+        <v>gratidao_jesus2026</v>
       </c>
       <c r="B552">
         <v>1</v>
@@ -8130,7 +8130,7 @@
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>jose_carlos_baixote</v>
+        <v>projeto_amigos_de_ouro</v>
       </c>
       <c r="B553">
         <v>1</v>
@@ -8144,7 +8144,7 @@
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>dani120690</v>
+        <v>jose_carlos_baixote</v>
       </c>
       <c r="B554">
         <v>1</v>
@@ -8158,7 +8158,7 @@
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>raonasthai</v>
+        <v>dani120690</v>
       </c>
       <c r="B555">
         <v>1</v>
@@ -8172,7 +8172,7 @@
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>adonaibjj_grip</v>
+        <v>raonasthai</v>
       </c>
       <c r="B556">
         <v>1</v>
@@ -8186,7 +8186,7 @@
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>arturbambam</v>
+        <v>adonaibjj_grip</v>
       </c>
       <c r="B557">
         <v>1</v>
@@ -8200,7 +8200,7 @@
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>cebolajj167</v>
+        <v>arturbambam</v>
       </c>
       <c r="B558">
         <v>1</v>
@@ -8214,7 +8214,7 @@
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>danieljsantoss_</v>
+        <v>cebolajj167</v>
       </c>
       <c r="B559">
         <v>1</v>
@@ -8228,7 +8228,7 @@
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>hermaan10_</v>
+        <v>danieljsantoss_</v>
       </c>
       <c r="B560">
         <v>1</v>
@@ -8242,7 +8242,7 @@
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>hunter.mccrary</v>
+        <v>hermaan10_</v>
       </c>
       <c r="B561">
         <v>1</v>
@@ -8256,7 +8256,7 @@
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>markakasocks</v>
+        <v>hunter.mccrary</v>
       </c>
       <c r="B562">
         <v>1</v>
@@ -8270,7 +8270,7 @@
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>rodrigojansen_</v>
+        <v>markakasocks</v>
       </c>
       <c r="B563">
         <v>1</v>
@@ -8284,7 +8284,7 @@
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>odivaldo_lobo</v>
+        <v>rodrigojansen_</v>
       </c>
       <c r="B564">
         <v>1</v>
@@ -8298,7 +8298,7 @@
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>davidpina_047</v>
+        <v>odivaldo_lobo</v>
       </c>
       <c r="B565">
         <v>1</v>
@@ -8312,7 +8312,7 @@
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>selma.oscar12</v>
+        <v>davidpina_047</v>
       </c>
       <c r="B566">
         <v>1</v>
@@ -8326,7 +8326,7 @@
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>flahvinhotreinador</v>
+        <v>selma.oscar12</v>
       </c>
       <c r="B567">
         <v>1</v>
@@ -8340,7 +8340,7 @@
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>ariel_alvees</v>
+        <v>flahvinhotreinador</v>
       </c>
       <c r="B568">
         <v>1</v>
@@ -8354,7 +8354,7 @@
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>cristiane.c.santana</v>
+        <v>ariel_alvees</v>
       </c>
       <c r="B569">
         <v>1</v>
@@ -8368,7 +8368,7 @@
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>marciocatenacci</v>
+        <v>cristiane.c.santana</v>
       </c>
       <c r="B570">
         <v>1</v>
@@ -8382,7 +8382,7 @@
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>claudioribeiro_ufc</v>
+        <v>marciocatenacci</v>
       </c>
       <c r="B571">
         <v>1</v>
@@ -8396,7 +8396,7 @@
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>rodrigolidiosales</v>
+        <v>claudioribeiro_ufc</v>
       </c>
       <c r="B572">
         <v>1</v>
@@ -8410,7 +8410,7 @@
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>moisespira</v>
+        <v>rodrigolidiosales</v>
       </c>
       <c r="B573">
         <v>1</v>
@@ -8424,7 +8424,7 @@
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>ctt.casaestopteam</v>
+        <v>moisespira</v>
       </c>
       <c r="B574">
         <v>1</v>
@@ -8438,7 +8438,7 @@
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>cassius.paula</v>
+        <v>ctt.casaestopteam</v>
       </c>
       <c r="B575">
         <v>1</v>
@@ -8452,7 +8452,7 @@
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>renatoevangelistaa</v>
+        <v>cassius.paula</v>
       </c>
       <c r="B576">
         <v>1</v>
@@ -8466,7 +8466,7 @@
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>manmoska</v>
+        <v>renatoevangelistaa</v>
       </c>
       <c r="B577">
         <v>1</v>
@@ -8480,7 +8480,7 @@
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>lucasampaio</v>
+        <v>manmoska</v>
       </c>
       <c r="B578">
         <v>1</v>
@@ -8494,7 +8494,7 @@
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>ricieritonan</v>
+        <v>lucasampaio</v>
       </c>
       <c r="B579">
         <v>1</v>
@@ -8508,7 +8508,7 @@
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>alphavillesup</v>
+        <v>ricieritonan</v>
       </c>
       <c r="B580">
         <v>1</v>
@@ -8522,7 +8522,7 @@
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>omarcotomaz</v>
+        <v>alphavillesup</v>
       </c>
       <c r="B581">
         <v>1</v>
@@ -8536,7 +8536,7 @@
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>joao_lins_muaythai</v>
+        <v>omarcotomaz</v>
       </c>
       <c r="B582">
         <v>1</v>
@@ -8550,7 +8550,7 @@
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>pelevermelha.uniformes</v>
+        <v>joao_lins_muaythai</v>
       </c>
       <c r="B583">
         <v>1</v>
@@ -8564,7 +8564,7 @@
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>flavia_gomes_29</v>
+        <v>pelevermelha.uniformes</v>
       </c>
       <c r="B584">
         <v>1</v>
@@ -8578,7 +8578,7 @@
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>romulobelarmino</v>
+        <v>flavia_gomes_29</v>
       </c>
       <c r="B585">
         <v>1</v>
@@ -8592,7 +8592,7 @@
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>israelbahiensebraz</v>
+        <v>romulobelarmino</v>
       </c>
       <c r="B586">
         <v>1</v>
@@ -8606,7 +8606,7 @@
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>leitefelippez</v>
+        <v>israelbahiensebraz</v>
       </c>
       <c r="B587">
         <v>1</v>
@@ -8620,7 +8620,7 @@
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>gabrielsoaresbjj</v>
+        <v>leitefelippez</v>
       </c>
       <c r="B588">
         <v>1</v>
@@ -8634,7 +8634,7 @@
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>larissamartinsbjj</v>
+        <v>gabrielsoaresbjj</v>
       </c>
       <c r="B589">
         <v>1</v>
@@ -8648,7 +8648,7 @@
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>fernandamourabjj</v>
+        <v>larissamartinsbjj</v>
       </c>
       <c r="B590">
         <v>1</v>
@@ -8662,7 +8662,7 @@
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>isasantos1404</v>
+        <v>fernandamourabjj</v>
       </c>
       <c r="B591">
         <v>1</v>
@@ -8676,7 +8676,7 @@
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>alberto_garcia_queiroz_junior</v>
+        <v>isasantos1404</v>
       </c>
       <c r="B592">
         <v>1</v>
@@ -8690,7 +8690,7 @@
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>titosbjj</v>
+        <v>alberto_garcia_queiroz_junior</v>
       </c>
       <c r="B593">
         <v>1</v>
@@ -8704,7 +8704,7 @@
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>johnnydesinfluencer</v>
+        <v>titosbjj</v>
       </c>
       <c r="B594">
         <v>1</v>
@@ -8718,7 +8718,7 @@
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>keep.itpushinnn</v>
+        <v>johnnydesinfluencer</v>
       </c>
       <c r="B595">
         <v>1</v>
@@ -8732,7 +8732,7 @@
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>x_xpatto</v>
+        <v>keep.itpushinnn</v>
       </c>
       <c r="B596">
         <v>1</v>
@@ -8746,7 +8746,7 @@
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>aldomanuel1994</v>
+        <v>x_xpatto</v>
       </c>
       <c r="B597">
         <v>1</v>
@@ -8760,7 +8760,7 @@
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>joselia_1980</v>
+        <v>aldomanuel1994</v>
       </c>
       <c r="B598">
         <v>1</v>
@@ -8774,7 +8774,7 @@
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>geovannaalc_</v>
+        <v>joselia_1980</v>
       </c>
       <c r="B599">
         <v>1</v>
@@ -8788,7 +8788,7 @@
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>biabezerra88</v>
+        <v>geovannaalc_</v>
       </c>
       <c r="B600">
         <v>1</v>
@@ -8802,7 +8802,7 @@
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>_murilo_06</v>
+        <v>biabezerra88</v>
       </c>
       <c r="B601">
         <v>1</v>
@@ -8816,7 +8816,7 @@
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>gi.liimaa_</v>
+        <v>_murilo_06</v>
       </c>
       <c r="B602">
         <v>1</v>
@@ -8830,7 +8830,7 @@
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>generaldantas</v>
+        <v>gi.liimaa_</v>
       </c>
       <c r="B603">
         <v>1</v>
@@ -8844,7 +8844,7 @@
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>paulokami.mma</v>
+        <v>generaldantas</v>
       </c>
       <c r="B604">
         <v>1</v>
@@ -8858,7 +8858,7 @@
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>ph_castroh</v>
+        <v>paulokami.mma</v>
       </c>
       <c r="B605">
         <v>1</v>
@@ -8872,7 +8872,7 @@
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>jhonny.2302_aritamma</v>
+        <v>ph_castroh</v>
       </c>
       <c r="B606">
         <v>1</v>
@@ -8886,7 +8886,7 @@
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>pettys2298</v>
+        <v>jhonny.2302_aritamma</v>
       </c>
       <c r="B607">
         <v>1</v>
@@ -8900,7 +8900,7 @@
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>jeffersonliu2022</v>
+        <v>pettys2298</v>
       </c>
       <c r="B608">
         <v>1</v>
@@ -8914,7 +8914,7 @@
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>guihs_cardoso</v>
+        <v>jeffersonliu2022</v>
       </c>
       <c r="B609">
         <v>1</v>
@@ -8928,7 +8928,7 @@
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>sp__theus</v>
+        <v>guihs_cardoso</v>
       </c>
       <c r="B610">
         <v>1</v>
@@ -8942,7 +8942,7 @@
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>eriikdossantoos</v>
+        <v>sp__theus</v>
       </c>
       <c r="B611">
         <v>1</v>
@@ -8956,7 +8956,7 @@
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>rick.santosz</v>
+        <v>eriikdossantoos</v>
       </c>
       <c r="B612">
         <v>1</v>
@@ -8970,7 +8970,7 @@
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>pbmoments_</v>
+        <v>rick.santosz</v>
       </c>
       <c r="B613">
         <v>1</v>
@@ -8984,7 +8984,7 @@
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>ana.cristina.uno</v>
+        <v>pbmoments_</v>
       </c>
       <c r="B614">
         <v>1</v>
@@ -8998,7 +8998,7 @@
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>silva_junior1979</v>
+        <v>ana.cristina.uno</v>
       </c>
       <c r="B615">
         <v>1</v>
@@ -9012,7 +9012,7 @@
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>santos39roger</v>
+        <v>silva_junior1979</v>
       </c>
       <c r="B616">
         <v>1</v>
@@ -9026,7 +9026,7 @@
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>terapeuta_moniquedias</v>
+        <v>santos39roger</v>
       </c>
       <c r="B617">
         <v>1</v>
@@ -9040,7 +9040,7 @@
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>bernardocavalcanti1</v>
+        <v>terapeuta_moniquedias</v>
       </c>
       <c r="B618">
         <v>1</v>
@@ -9054,7 +9054,7 @@
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>mestrevascobento</v>
+        <v>bernardocavalcanti1</v>
       </c>
       <c r="B619">
         <v>1</v>
@@ -9068,7 +9068,7 @@
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>ever.soulson</v>
+        <v>mestrevascobento</v>
       </c>
       <c r="B620">
         <v>1</v>
@@ -9082,7 +9082,7 @@
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>martins.rauanee</v>
+        <v>ever.soulson</v>
       </c>
       <c r="B621">
         <v>1</v>
@@ -9096,7 +9096,7 @@
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>camillinhamma</v>
+        <v>martins.rauanee</v>
       </c>
       <c r="B622">
         <v>1</v>
@@ -9110,7 +9110,7 @@
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>leandro_pedro7</v>
+        <v>camillinhamma</v>
       </c>
       <c r="B623">
         <v>1</v>
@@ -9124,7 +9124,7 @@
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>soniarochaco</v>
+        <v>leandro_pedro7</v>
       </c>
       <c r="B624">
         <v>1</v>
@@ -9138,7 +9138,7 @@
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>andreloliva12</v>
+        <v>soniarochaco</v>
       </c>
       <c r="B625">
         <v>1</v>
@@ -9152,7 +9152,7 @@
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>dcoops2</v>
+        <v>andreloliva12</v>
       </c>
       <c r="B626">
         <v>1</v>
@@ -9166,7 +9166,7 @@
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>homemdeita</v>
+        <v>dcoops2</v>
       </c>
       <c r="B627">
         <v>1</v>
@@ -9180,7 +9180,7 @@
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>ludelmaraujo</v>
+        <v>homemdeita</v>
       </c>
       <c r="B628">
         <v>1</v>
@@ -9194,7 +9194,7 @@
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>ricardosousa811</v>
+        <v>ludelmaraujo</v>
       </c>
       <c r="B629">
         <v>1</v>
@@ -9208,7 +9208,7 @@
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>axiaaly</v>
+        <v>ricardosousa811</v>
       </c>
       <c r="B630">
         <v>1</v>
@@ -9222,7 +9222,7 @@
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>oficialrichardsilva_ice_men</v>
+        <v>axiaaly</v>
       </c>
       <c r="B631">
         <v>1</v>
@@ -9236,7 +9236,7 @@
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>eimysalazar</v>
+        <v>oficialrichardsilva_ice_men</v>
       </c>
       <c r="B632">
         <v>1</v>
@@ -9250,7 +9250,7 @@
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>victorxferreira</v>
+        <v>eimysalazar</v>
       </c>
       <c r="B633">
         <v>1</v>
@@ -9264,7 +9264,7 @@
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>renatogomes769</v>
+        <v>victorxferreira</v>
       </c>
       <c r="B634">
         <v>1</v>
@@ -9278,7 +9278,7 @@
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>thiagomoisesmma</v>
+        <v>renatogomes769</v>
       </c>
       <c r="B635">
         <v>1</v>
@@ -9292,7 +9292,7 @@
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>pazzini__</v>
+        <v>thiagomoisesmma</v>
       </c>
       <c r="B636">
         <v>1</v>
@@ -9306,7 +9306,7 @@
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>sr.dpaula10</v>
+        <v>pazzini__</v>
       </c>
       <c r="B637">
         <v>1</v>
@@ -9320,7 +9320,7 @@
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>santosriveiros18737383</v>
+        <v>sr.dpaula10</v>
       </c>
       <c r="B638">
         <v>1</v>
@@ -9334,7 +9334,7 @@
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>dinhomoraisoficial</v>
+        <v>santosriveiros18737383</v>
       </c>
       <c r="B639">
         <v>1</v>
@@ -9348,7 +9348,7 @@
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>adrianoblessed89</v>
+        <v>dinhomoraisoficial</v>
       </c>
       <c r="B640">
         <v>1</v>
@@ -9362,7 +9362,7 @@
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>dobby_1968</v>
+        <v>adrianoblessed89</v>
       </c>
       <c r="B641">
         <v>1</v>
@@ -9376,7 +9376,7 @@
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>ricardogabriel.sr</v>
+        <v>dobby_1968</v>
       </c>
       <c r="B642">
         <v>1</v>
@@ -9390,7 +9390,7 @@
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>ottoniisrael</v>
+        <v>ricardogabriel.sr</v>
       </c>
       <c r="B643">
         <v>1</v>
@@ -9404,7 +9404,7 @@
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>allves___46</v>
+        <v>ottoniisrael</v>
       </c>
       <c r="B644">
         <v>1</v>
@@ -9418,7 +9418,7 @@
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>fe_.faggi</v>
+        <v>allves___46</v>
       </c>
       <c r="B645">
         <v>1</v>
@@ -9432,7 +9432,7 @@
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>lucianatpiccelli</v>
+        <v>fe_.faggi</v>
       </c>
       <c r="B646">
         <v>1</v>
@@ -9446,7 +9446,7 @@
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>dyrodriguesohplano</v>
+        <v>lucianatpiccelli</v>
       </c>
       <c r="B647">
         <v>1</v>
@@ -9460,7 +9460,7 @@
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>almeida_.e7</v>
+        <v>dyrodriguesohplano</v>
       </c>
       <c r="B648">
         <v>1</v>
@@ -9474,7 +9474,7 @@
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>rxdi_mns</v>
+        <v>almeida_.e7</v>
       </c>
       <c r="B649">
         <v>1</v>
@@ -9488,7 +9488,7 @@
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>grupoohplanooficial</v>
+        <v>rxdi_mns</v>
       </c>
       <c r="B650">
         <v>1</v>
@@ -9502,7 +9502,7 @@
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>maribrittos22</v>
+        <v>grupoohplanooficial</v>
       </c>
       <c r="B651">
         <v>1</v>
@@ -9516,7 +9516,7 @@
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>yago_08k</v>
+        <v>maribrittos22</v>
       </c>
       <c r="B652">
         <v>1</v>
@@ -9530,7 +9530,7 @@
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>blesed578</v>
+        <v>yago_08k</v>
       </c>
       <c r="B653">
         <v>1</v>
@@ -9544,7 +9544,7 @@
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>remarchina</v>
+        <v>blesed578</v>
       </c>
       <c r="B654">
         <v>1</v>
@@ -9558,7 +9558,7 @@
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>odennismagalhaes</v>
+        <v>remarchina</v>
       </c>
       <c r="B655">
         <v>1</v>
@@ -9572,7 +9572,7 @@
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>1felipe.bjj</v>
+        <v>odennismagalhaes</v>
       </c>
       <c r="B656">
         <v>1</v>
@@ -9586,7 +9586,7 @@
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>_samu35</v>
+        <v>1felipe.bjj</v>
       </c>
       <c r="B657">
         <v>1</v>
@@ -9600,7 +9600,7 @@
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>indiopersonalfight</v>
+        <v>_samu35</v>
       </c>
       <c r="B658">
         <v>1</v>
@@ -9614,7 +9614,7 @@
     </row>
     <row r="659">
       <c r="A659" t="str">
-        <v>davi.cb</v>
+        <v>indiopersonalfight</v>
       </c>
       <c r="B659">
         <v>1</v>
@@ -9628,7 +9628,7 @@
     </row>
     <row r="660">
       <c r="A660" t="str">
-        <v>guilherme.duartesilva</v>
+        <v>davi.cb</v>
       </c>
       <c r="B660">
         <v>1</v>
@@ -9642,7 +9642,7 @@
     </row>
     <row r="661">
       <c r="A661" t="str">
-        <v>_.carlos.2x._</v>
+        <v>guilherme.duartesilva</v>
       </c>
       <c r="B661">
         <v>1</v>
@@ -9656,7 +9656,7 @@
     </row>
     <row r="662">
       <c r="A662" t="str">
-        <v>thizzlenik</v>
+        <v>_.carlos.2x._</v>
       </c>
       <c r="B662">
         <v>1</v>
@@ -9670,7 +9670,7 @@
     </row>
     <row r="663">
       <c r="A663" t="str">
-        <v>yon0sab0</v>
+        <v>thizzlenik</v>
       </c>
       <c r="B663">
         <v>1</v>
@@ -9684,7 +9684,7 @@
     </row>
     <row r="664">
       <c r="A664" t="str">
-        <v>bammer2026</v>
+        <v>yon0sab0</v>
       </c>
       <c r="B664">
         <v>1</v>
@@ -9698,7 +9698,7 @@
     </row>
     <row r="665">
       <c r="A665" t="str">
-        <v>elnaggar_85</v>
+        <v>bammer2026</v>
       </c>
       <c r="B665">
         <v>1</v>
@@ -9712,7 +9712,7 @@
     </row>
     <row r="666">
       <c r="A666" t="str">
-        <v>nulife2day</v>
+        <v>elnaggar_85</v>
       </c>
       <c r="B666">
         <v>1</v>
@@ -9726,7 +9726,7 @@
     </row>
     <row r="667">
       <c r="A667" t="str">
-        <v>abbasrizvi2204</v>
+        <v>nulife2day</v>
       </c>
       <c r="B667">
         <v>1</v>
@@ -9740,7 +9740,7 @@
     </row>
     <row r="668">
       <c r="A668" t="str">
-        <v>dogodoy</v>
+        <v>abbasrizvi2204</v>
       </c>
       <c r="B668">
         <v>1</v>
@@ -9754,7 +9754,7 @@
     </row>
     <row r="669">
       <c r="A669" t="str">
-        <v>cabreuvamma</v>
+        <v>dogodoy</v>
       </c>
       <c r="B669">
         <v>1</v>
@@ -9768,7 +9768,7 @@
     </row>
     <row r="670">
       <c r="A670" t="str">
-        <v>clinicaikiro</v>
+        <v>cabreuvamma</v>
       </c>
       <c r="B670">
         <v>1</v>
@@ -9782,7 +9782,7 @@
     </row>
     <row r="671">
       <c r="A671" t="str">
-        <v>jefte_jizreel</v>
+        <v>clinicaikiro</v>
       </c>
       <c r="B671">
         <v>1</v>
@@ -9796,7 +9796,7 @@
     </row>
     <row r="672">
       <c r="A672" t="str">
-        <v>klaiver.027xx</v>
+        <v>jefte_jizreel</v>
       </c>
       <c r="B672">
         <v>1</v>
@@ -9810,7 +9810,7 @@
     </row>
     <row r="673">
       <c r="A673" t="str">
-        <v>bmarinhorogerio</v>
+        <v>klaiver.027xx</v>
       </c>
       <c r="B673">
         <v>1</v>
@@ -9824,7 +9824,7 @@
     </row>
     <row r="674">
       <c r="A674" t="str">
-        <v>lucaspaes047</v>
+        <v>bmarinhorogerio</v>
       </c>
       <c r="B674">
         <v>1</v>
@@ -9838,7 +9838,7 @@
     </row>
     <row r="675">
       <c r="A675" t="str">
-        <v>nautinhor7</v>
+        <v>lucaspaes047</v>
       </c>
       <c r="B675">
         <v>1</v>
@@ -9852,7 +9852,7 @@
     </row>
     <row r="676">
       <c r="A676" t="str">
-        <v>1tiagomonteiro</v>
+        <v>nautinhor7</v>
       </c>
       <c r="B676">
         <v>1</v>
@@ -9866,7 +9866,7 @@
     </row>
     <row r="677">
       <c r="A677" t="str">
-        <v>s_giofe</v>
+        <v>1tiagomonteiro</v>
       </c>
       <c r="B677">
         <v>1</v>
@@ -9880,7 +9880,7 @@
     </row>
     <row r="678">
       <c r="A678" t="str">
-        <v>mauricio_dutra_m</v>
+        <v>s_giofe</v>
       </c>
       <c r="B678">
         <v>1</v>
@@ -9894,7 +9894,7 @@
     </row>
     <row r="679">
       <c r="A679" t="str">
-        <v>claudio_tikar</v>
+        <v>mauricio_dutra_m</v>
       </c>
       <c r="B679">
         <v>1</v>
@@ -9908,7 +9908,7 @@
     </row>
     <row r="680">
       <c r="A680" t="str">
-        <v>boeno_rafael</v>
+        <v>claudio_tikar</v>
       </c>
       <c r="B680">
         <v>1</v>
@@ -9922,7 +9922,7 @@
     </row>
     <row r="681">
       <c r="A681" t="str">
-        <v>nati.monteiro</v>
+        <v>boeno_rafael</v>
       </c>
       <c r="B681">
         <v>1</v>
@@ -9936,7 +9936,7 @@
     </row>
     <row r="682">
       <c r="A682" t="str">
-        <v>cinemarianophoto</v>
+        <v>nati.monteiro</v>
       </c>
       <c r="B682">
         <v>1</v>
@@ -9950,7 +9950,7 @@
     </row>
     <row r="683">
       <c r="A683" t="str">
-        <v>patriciarichteroficial</v>
+        <v>cinemarianophoto</v>
       </c>
       <c r="B683">
         <v>1</v>
@@ -9964,7 +9964,7 @@
     </row>
     <row r="684">
       <c r="A684" t="str">
-        <v>use.ellasfit</v>
+        <v>patriciarichteroficial</v>
       </c>
       <c r="B684">
         <v>1</v>
@@ -9978,7 +9978,7 @@
     </row>
     <row r="685">
       <c r="A685" t="str">
-        <v>kauan_mantas</v>
+        <v>use.ellasfit</v>
       </c>
       <c r="B685">
         <v>1</v>
@@ -9992,7 +9992,7 @@
     </row>
     <row r="686">
       <c r="A686" t="str">
-        <v>emersonapache</v>
+        <v>kauan_mantas</v>
       </c>
       <c r="B686">
         <v>1</v>
@@ -10006,7 +10006,7 @@
     </row>
     <row r="687">
       <c r="A687" t="str">
-        <v>nataliavidal965</v>
+        <v>emersonapache</v>
       </c>
       <c r="B687">
         <v>1</v>
@@ -10020,7 +10020,7 @@
     </row>
     <row r="688">
       <c r="A688" t="str">
-        <v>ruanpantojanutricionista</v>
+        <v>nataliavidal965</v>
       </c>
       <c r="B688">
         <v>1</v>
@@ -10034,7 +10034,7 @@
     </row>
     <row r="689">
       <c r="A689" t="str">
-        <v>luizpaulomma</v>
+        <v>ruanpantojanutricionista</v>
       </c>
       <c r="B689">
         <v>1</v>
@@ -10048,7 +10048,7 @@
     </row>
     <row r="690">
       <c r="A690" t="str">
-        <v>tvlinsoficial</v>
+        <v>luizpaulomma</v>
       </c>
       <c r="B690">
         <v>1</v>
@@ -10062,7 +10062,7 @@
     </row>
     <row r="691">
       <c r="A691" t="str">
-        <v>epicjoel2022</v>
+        <v>tvlinsoficial</v>
       </c>
       <c r="B691">
         <v>1</v>
@@ -10076,7 +10076,7 @@
     </row>
     <row r="692">
       <c r="A692" t="str">
-        <v>paulo_rafa_personal</v>
+        <v>epicjoel2022</v>
       </c>
       <c r="B692">
         <v>1</v>
@@ -10090,35 +10090,35 @@
     </row>
     <row r="693">
       <c r="A693" t="str">
-        <v>lucasbaddoure</v>
+        <v>paulo_rafa_personal</v>
       </c>
       <c r="B693">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C693">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D693">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="str">
-        <v>desativado_no_off33</v>
+        <v>lucasbaddoure</v>
       </c>
       <c r="B694">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C694">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D694">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="str">
-        <v>mg._silvaa_</v>
+        <v>desativado_no_off33</v>
       </c>
       <c r="B695">
         <v>1</v>
@@ -10132,7 +10132,7 @@
     </row>
     <row r="696">
       <c r="A696" t="str">
-        <v>_itamar_maximo</v>
+        <v>mg._silvaa_</v>
       </c>
       <c r="B696">
         <v>1</v>
@@ -10146,7 +10146,7 @@
     </row>
     <row r="697">
       <c r="A697" t="str">
-        <v>lopes.felipe13</v>
+        <v>_itamar_maximo</v>
       </c>
       <c r="B697">
         <v>1</v>
@@ -10160,7 +10160,7 @@
     </row>
     <row r="698">
       <c r="A698" t="str">
-        <v>instrutorindiovs</v>
+        <v>lopes.felipe13</v>
       </c>
       <c r="B698">
         <v>1</v>
@@ -10174,7 +10174,7 @@
     </row>
     <row r="699">
       <c r="A699" t="str">
-        <v>cadupereirss</v>
+        <v>instrutorindiovs</v>
       </c>
       <c r="B699">
         <v>1</v>
@@ -10188,7 +10188,7 @@
     </row>
     <row r="700">
       <c r="A700" t="str">
-        <v>endurance_guia</v>
+        <v>cadupereirss</v>
       </c>
       <c r="B700">
         <v>1</v>
@@ -10202,7 +10202,7 @@
     </row>
     <row r="701">
       <c r="A701" t="str">
-        <v>m1guelmolina</v>
+        <v>endurance_guia</v>
       </c>
       <c r="B701">
         <v>1</v>
@@ -10216,7 +10216,7 @@
     </row>
     <row r="702">
       <c r="A702" t="str">
-        <v>rafa_speda</v>
+        <v>m1guelmolina</v>
       </c>
       <c r="B702">
         <v>1</v>
@@ -10230,7 +10230,7 @@
     </row>
     <row r="703">
       <c r="A703" t="str">
-        <v>marchi_vinicius</v>
+        <v>rafa_speda</v>
       </c>
       <c r="B703">
         <v>1</v>
@@ -10244,7 +10244,7 @@
     </row>
     <row r="704">
       <c r="A704" t="str">
-        <v>perninhakickboxing</v>
+        <v>marchi_vinicius</v>
       </c>
       <c r="B704">
         <v>1</v>
@@ -10258,7 +10258,7 @@
     </row>
     <row r="705">
       <c r="A705" t="str">
-        <v>alissonlayza</v>
+        <v>perninhakickboxing</v>
       </c>
       <c r="B705">
         <v>1</v>
@@ -10272,7 +10272,7 @@
     </row>
     <row r="706">
       <c r="A706" t="str">
-        <v>cotty_bigmonster</v>
+        <v>alissonlayza</v>
       </c>
       <c r="B706">
         <v>1</v>
@@ -10286,7 +10286,7 @@
     </row>
     <row r="707">
       <c r="A707" t="str">
-        <v>programaparadois</v>
+        <v>cotty_bigmonster</v>
       </c>
       <c r="B707">
         <v>1</v>
@@ -10300,7 +10300,7 @@
     </row>
     <row r="708">
       <c r="A708" t="str">
-        <v>alinefurlann</v>
+        <v>programaparadois</v>
       </c>
       <c r="B708">
         <v>1</v>
@@ -10314,7 +10314,7 @@
     </row>
     <row r="709">
       <c r="A709" t="str">
-        <v>cassiolee013</v>
+        <v>alinefurlann</v>
       </c>
       <c r="B709">
         <v>1</v>
@@ -10328,7 +10328,7 @@
     </row>
     <row r="710">
       <c r="A710" t="str">
-        <v>caiogoularts</v>
+        <v>cassiolee013</v>
       </c>
       <c r="B710">
         <v>1</v>
@@ -10342,7 +10342,7 @@
     </row>
     <row r="711">
       <c r="A711" t="str">
-        <v>rosantos83</v>
+        <v>caiogoularts</v>
       </c>
       <c r="B711">
         <v>1</v>
@@ -10356,7 +10356,7 @@
     </row>
     <row r="712">
       <c r="A712" t="str">
-        <v>rodrigo.nsx</v>
+        <v>rosantos83</v>
       </c>
       <c r="B712">
         <v>1</v>
@@ -10370,7 +10370,7 @@
     </row>
     <row r="713">
       <c r="A713" t="str">
-        <v>lorenzojjts</v>
+        <v>rodrigo.nsx</v>
       </c>
       <c r="B713">
         <v>1</v>
@@ -10384,7 +10384,7 @@
     </row>
     <row r="714">
       <c r="A714" t="str">
-        <v>enzorkbjj</v>
+        <v>lorenzojjts</v>
       </c>
       <c r="B714">
         <v>1</v>
@@ -10398,7 +10398,7 @@
     </row>
     <row r="715">
       <c r="A715" t="str">
-        <v>_hygor.soares</v>
+        <v>enzorkbjj</v>
       </c>
       <c r="B715">
         <v>1</v>
@@ -10412,7 +10412,7 @@
     </row>
     <row r="716">
       <c r="A716" t="str">
-        <v>k_costa68</v>
+        <v>_hygor.soares</v>
       </c>
       <c r="B716">
         <v>1</v>
@@ -10426,7 +10426,7 @@
     </row>
     <row r="717">
       <c r="A717" t="str">
-        <v>808.chaz</v>
+        <v>k_costa68</v>
       </c>
       <c r="B717">
         <v>1</v>
@@ -10440,7 +10440,7 @@
     </row>
     <row r="718">
       <c r="A718" t="str">
-        <v>i_am_mauispunjahchick</v>
+        <v>808.chaz</v>
       </c>
       <c r="B718">
         <v>1</v>
@@ -10454,7 +10454,7 @@
     </row>
     <row r="719">
       <c r="A719" t="str">
-        <v>leomvgomes</v>
+        <v>i_am_mauispunjahchick</v>
       </c>
       <c r="B719">
         <v>1</v>
@@ -10468,7 +10468,7 @@
     </row>
     <row r="720">
       <c r="A720" t="str">
-        <v>luizguilhermepaiva_</v>
+        <v>leomvgomes</v>
       </c>
       <c r="B720">
         <v>1</v>
@@ -10482,7 +10482,7 @@
     </row>
     <row r="721">
       <c r="A721" t="str">
-        <v>wagnermeneguelll</v>
+        <v>luizguilhermepaiva_</v>
       </c>
       <c r="B721">
         <v>1</v>
@@ -10496,7 +10496,7 @@
     </row>
     <row r="722">
       <c r="A722" t="str">
-        <v>marcos_indio._</v>
+        <v>wagnermeneguelll</v>
       </c>
       <c r="B722">
         <v>1</v>
@@ -10510,7 +10510,7 @@
     </row>
     <row r="723">
       <c r="A723" t="str">
-        <v>corullapedro</v>
+        <v>marcos_indio._</v>
       </c>
       <c r="B723">
         <v>1</v>
@@ -10524,7 +10524,7 @@
     </row>
     <row r="724">
       <c r="A724" t="str">
-        <v>wanderley_silva081</v>
+        <v>corullapedro</v>
       </c>
       <c r="B724">
         <v>1</v>
@@ -10538,7 +10538,7 @@
     </row>
     <row r="725">
       <c r="A725" t="str">
-        <v>kakaa_ranch</v>
+        <v>wanderley_silva081</v>
       </c>
       <c r="B725">
         <v>1</v>
@@ -10552,7 +10552,7 @@
     </row>
     <row r="726">
       <c r="A726" t="str">
-        <v>lorenzo.klippel</v>
+        <v>kakaa_ranch</v>
       </c>
       <c r="B726">
         <v>1</v>
@@ -10566,7 +10566,7 @@
     </row>
     <row r="727">
       <c r="A727" t="str">
-        <v>luana8324</v>
+        <v>lorenzo.klippel</v>
       </c>
       <c r="B727">
         <v>1</v>
@@ -10580,7 +10580,7 @@
     </row>
     <row r="728">
       <c r="A728" t="str">
-        <v>paidepef</v>
+        <v>luana8324</v>
       </c>
       <c r="B728">
         <v>1</v>
@@ -10594,7 +10594,7 @@
     </row>
     <row r="729">
       <c r="A729" t="str">
-        <v>malhadinho_ufc</v>
+        <v>paidepef</v>
       </c>
       <c r="B729">
         <v>1</v>
@@ -10608,7 +10608,7 @@
     </row>
     <row r="730">
       <c r="A730" t="str">
-        <v>juan.lboxe_</v>
+        <v>malhadinho_ufc</v>
       </c>
       <c r="B730">
         <v>1</v>
@@ -10622,35 +10622,35 @@
     </row>
     <row r="731">
       <c r="A731" t="str">
-        <v>pedroriela</v>
+        <v>juan.lboxe_</v>
       </c>
       <c r="B731">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C731">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D731">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="732">
       <c r="A732" t="str">
-        <v>andradeoficiaal</v>
+        <v>pedroriela</v>
       </c>
       <c r="B732">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C732">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D732">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="733">
       <c r="A733" t="str">
-        <v>netinho_souzas</v>
+        <v>andradeoficiaal</v>
       </c>
       <c r="B733">
         <v>1</v>
@@ -10664,7 +10664,7 @@
     </row>
     <row r="734">
       <c r="A734" t="str">
-        <v>katharinelopes</v>
+        <v>netinho_souzas</v>
       </c>
       <c r="B734">
         <v>1</v>
@@ -10678,7 +10678,7 @@
     </row>
     <row r="735">
       <c r="A735" t="str">
-        <v>__dias_07_</v>
+        <v>katharinelopes</v>
       </c>
       <c r="B735">
         <v>1</v>
@@ -10692,7 +10692,7 @@
     </row>
     <row r="736">
       <c r="A736" t="str">
-        <v>igorsbessa</v>
+        <v>__dias_07_</v>
       </c>
       <c r="B736">
         <v>1</v>
@@ -10706,7 +10706,7 @@
     </row>
     <row r="737">
       <c r="A737" t="str">
-        <v>themarcosalves</v>
+        <v>igorsbessa</v>
       </c>
       <c r="B737">
         <v>1</v>
@@ -10720,7 +10720,7 @@
     </row>
     <row r="738">
       <c r="A738" t="str">
-        <v>deni_jesus_shalom</v>
+        <v>themarcosalves</v>
       </c>
       <c r="B738">
         <v>1</v>
@@ -10734,7 +10734,7 @@
     </row>
     <row r="739">
       <c r="A739" t="str">
-        <v>george.bjj_</v>
+        <v>deni_jesus_shalom</v>
       </c>
       <c r="B739">
         <v>1</v>
@@ -10748,7 +10748,7 @@
     </row>
     <row r="740">
       <c r="A740" t="str">
-        <v>carlosshenn</v>
+        <v>george.bjj_</v>
       </c>
       <c r="B740">
         <v>1</v>
@@ -10762,7 +10762,7 @@
     </row>
     <row r="741">
       <c r="A741" t="str">
-        <v>almeida.nyara</v>
+        <v>carlosshenn</v>
       </c>
       <c r="B741">
         <v>1</v>
@@ -10776,83 +10776,83 @@
     </row>
     <row r="742">
       <c r="A742" t="str">
-        <v>luizcosta_mma</v>
+        <v>almeida.nyara</v>
       </c>
       <c r="B742">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C742">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D742">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="743">
       <c r="A743" t="str">
-        <v>taylor_71kg</v>
+        <v>biazon87</v>
       </c>
       <c r="B743">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C743">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D743">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="744">
       <c r="A744" t="str">
-        <v>_vpft</v>
+        <v>dubernardo37</v>
       </c>
       <c r="B744">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C744">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D744">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="745">
       <c r="A745" t="str">
-        <v>viniciustbf</v>
+        <v>sadraquesantana</v>
       </c>
       <c r="B745">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C745">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D745">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="746">
       <c r="A746" t="str">
-        <v>dayanaa1511</v>
+        <v>rogerio.maga</v>
       </c>
       <c r="B746">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C746">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D746">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="747">
       <c r="A747" t="str">
-        <v>danielfranzesilva</v>
+        <v>roblesbastosalfredo</v>
       </c>
       <c r="B747">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C747">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D747">
         <v>0</v>
@@ -10860,7 +10860,7 @@
     </row>
     <row r="748">
       <c r="A748" t="str">
-        <v>ednilsonkaicai</v>
+        <v>luizcosta_mma</v>
       </c>
       <c r="B748">
         <v>0</v>
@@ -10869,18 +10869,18 @@
         <v>2</v>
       </c>
       <c r="D748">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="749">
       <c r="A749" t="str">
-        <v>vanessamelomma</v>
+        <v>taylor_71kg</v>
       </c>
       <c r="B749">
         <v>0</v>
       </c>
       <c r="C749">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D749">
         <v>1</v>
@@ -10888,7 +10888,7 @@
     </row>
     <row r="750">
       <c r="A750" t="str">
-        <v>michelle_mirele</v>
+        <v>_vpft</v>
       </c>
       <c r="B750">
         <v>0</v>
@@ -10897,26 +10897,26 @@
         <v>3</v>
       </c>
       <c r="D750">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="751">
       <c r="A751" t="str">
-        <v>geyziellsouza</v>
+        <v>viniciustbf</v>
       </c>
       <c r="B751">
         <v>0</v>
       </c>
       <c r="C751">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D751">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="752">
       <c r="A752" t="str">
-        <v>guerreirammaofc</v>
+        <v>dayanaa1511</v>
       </c>
       <c r="B752">
         <v>0</v>
@@ -10930,27 +10930,27 @@
     </row>
     <row r="753">
       <c r="A753" t="str">
-        <v>kalaga_vito</v>
+        <v>danielfranzesilva</v>
       </c>
       <c r="B753">
         <v>0</v>
       </c>
       <c r="C753">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D753">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="754">
       <c r="A754" t="str">
-        <v>bryandazuera</v>
+        <v>ednilsonkaicai</v>
       </c>
       <c r="B754">
         <v>0</v>
       </c>
       <c r="C754">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D754">
         <v>1</v>
@@ -10958,13 +10958,13 @@
     </row>
     <row r="755">
       <c r="A755" t="str">
-        <v>danilofernandescf</v>
+        <v>vanessamelomma</v>
       </c>
       <c r="B755">
         <v>0</v>
       </c>
       <c r="C755">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D755">
         <v>1</v>
@@ -10972,13 +10972,13 @@
     </row>
     <row r="756">
       <c r="A756" t="str">
-        <v>4lissson</v>
+        <v>michelle_mirele</v>
       </c>
       <c r="B756">
         <v>0</v>
       </c>
       <c r="C756">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D756">
         <v>0</v>
@@ -10986,13 +10986,13 @@
     </row>
     <row r="757">
       <c r="A757" t="str">
-        <v>vitorshowman</v>
+        <v>geyziellsouza</v>
       </c>
       <c r="B757">
         <v>0</v>
       </c>
       <c r="C757">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D757">
         <v>0</v>
@@ -11000,7 +11000,7 @@
     </row>
     <row r="758">
       <c r="A758" t="str">
-        <v>orlando_alfa09</v>
+        <v>guerreirammaofc</v>
       </c>
       <c r="B758">
         <v>0</v>
@@ -11009,12 +11009,12 @@
         <v>2</v>
       </c>
       <c r="D758">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="759">
       <c r="A759" t="str">
-        <v>jhonnatanboxe_</v>
+        <v>kalaga_vito</v>
       </c>
       <c r="B759">
         <v>0</v>
@@ -11023,26 +11023,26 @@
         <v>2</v>
       </c>
       <c r="D759">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="760">
       <c r="A760" t="str">
-        <v>manumito.oficial</v>
+        <v>bryandazuera</v>
       </c>
       <c r="B760">
         <v>0</v>
       </c>
       <c r="C760">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D760">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="761">
       <c r="A761" t="str">
-        <v>coutz11</v>
+        <v>danilofernandescf</v>
       </c>
       <c r="B761">
         <v>0</v>
@@ -11056,7 +11056,7 @@
     </row>
     <row r="762">
       <c r="A762" t="str">
-        <v>eglaudiomma</v>
+        <v>4lissson</v>
       </c>
       <c r="B762">
         <v>0</v>
@@ -11070,21 +11070,21 @@
     </row>
     <row r="763">
       <c r="A763" t="str">
-        <v>lokomemo_protetores</v>
+        <v>vitorshowman</v>
       </c>
       <c r="B763">
         <v>0</v>
       </c>
       <c r="C763">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D763">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="764">
       <c r="A764" t="str">
-        <v>carlosnoelblack</v>
+        <v>orlando_alfa09</v>
       </c>
       <c r="B764">
         <v>0</v>
@@ -11098,7 +11098,7 @@
     </row>
     <row r="765">
       <c r="A765" t="str">
-        <v>rafaelcmjj</v>
+        <v>jhonnatanboxe_</v>
       </c>
       <c r="B765">
         <v>0</v>
@@ -11112,21 +11112,21 @@
     </row>
     <row r="766">
       <c r="A766" t="str">
-        <v>rahikikhalid</v>
+        <v>manumito.oficial</v>
       </c>
       <c r="B766">
         <v>0</v>
       </c>
       <c r="C766">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D766">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="767">
       <c r="A767" t="str">
-        <v>leonardopateira</v>
+        <v>coutz11</v>
       </c>
       <c r="B767">
         <v>0</v>
@@ -11140,7 +11140,7 @@
     </row>
     <row r="768">
       <c r="A768" t="str">
-        <v>tpapereira</v>
+        <v>eglaudiomma</v>
       </c>
       <c r="B768">
         <v>0</v>
@@ -11154,21 +11154,21 @@
     </row>
     <row r="769">
       <c r="A769" t="str">
-        <v>thalytabjj</v>
+        <v>lokomemo_protetores</v>
       </c>
       <c r="B769">
         <v>0</v>
       </c>
       <c r="C769">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D769">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="770">
       <c r="A770" t="str">
-        <v>rafaelantonio.rj</v>
+        <v>carlosnoelblack</v>
       </c>
       <c r="B770">
         <v>0</v>
@@ -11182,49 +11182,49 @@
     </row>
     <row r="771">
       <c r="A771" t="str">
-        <v>yasminreis_oficiall</v>
+        <v>rafaelcmjj</v>
       </c>
       <c r="B771">
         <v>0</v>
       </c>
       <c r="C771">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D771">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="772">
       <c r="A772" t="str">
-        <v>armysenju</v>
+        <v>rahikikhalid</v>
       </c>
       <c r="B772">
         <v>0</v>
       </c>
       <c r="C772">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D772">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="773">
       <c r="A773" t="str">
-        <v>dnoxsport</v>
+        <v>leonardopateira</v>
       </c>
       <c r="B773">
         <v>0</v>
       </c>
       <c r="C773">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D773">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="774">
       <c r="A774" t="str">
-        <v>kamtalksmma</v>
+        <v>tpapereira</v>
       </c>
       <c r="B774">
         <v>0</v>
@@ -11238,35 +11238,35 @@
     </row>
     <row r="775">
       <c r="A775" t="str">
-        <v>arleyleboss</v>
+        <v>thalytabjj</v>
       </c>
       <c r="B775">
         <v>0</v>
       </c>
       <c r="C775">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D775">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="776">
       <c r="A776" t="str">
-        <v>janjaovix</v>
+        <v>rafaelantonio.rj</v>
       </c>
       <c r="B776">
         <v>0</v>
       </c>
       <c r="C776">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D776">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="777">
       <c r="A777" t="str">
-        <v>dra.izabeldelfino_</v>
+        <v>yasminreis_oficiall</v>
       </c>
       <c r="B777">
         <v>0</v>
@@ -11280,7 +11280,7 @@
     </row>
     <row r="778">
       <c r="A778" t="str">
-        <v>jj_miguel05</v>
+        <v>armysenju</v>
       </c>
       <c r="B778">
         <v>0</v>
@@ -11294,35 +11294,35 @@
     </row>
     <row r="779">
       <c r="A779" t="str">
-        <v>joaolucasmma.rocha</v>
+        <v>dnoxsport</v>
       </c>
       <c r="B779">
         <v>0</v>
       </c>
       <c r="C779">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D779">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="780">
       <c r="A780" t="str">
-        <v>edsonbahienseb</v>
+        <v>kamtalksmma</v>
       </c>
       <c r="B780">
         <v>0</v>
       </c>
       <c r="C780">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D780">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="781">
       <c r="A781" t="str">
-        <v>paulomartins.mma</v>
+        <v>arleyleboss</v>
       </c>
       <c r="B781">
         <v>0</v>
@@ -11336,21 +11336,21 @@
     </row>
     <row r="782">
       <c r="A782" t="str">
-        <v>daniel_natel</v>
+        <v>janjaovix</v>
       </c>
       <c r="B782">
         <v>0</v>
       </c>
       <c r="C782">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D782">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="783">
       <c r="A783" t="str">
-        <v>dhuks11</v>
+        <v>dra.izabeldelfino_</v>
       </c>
       <c r="B783">
         <v>0</v>
@@ -11359,40 +11359,40 @@
         <v>1</v>
       </c>
       <c r="D783">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="784">
       <c r="A784" t="str">
-        <v>macksomlee</v>
+        <v>jj_miguel05</v>
       </c>
       <c r="B784">
         <v>0</v>
       </c>
       <c r="C784">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D784">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="785">
       <c r="A785" t="str">
-        <v>y_nichimura</v>
+        <v>joaolucasmma.rocha</v>
       </c>
       <c r="B785">
         <v>0</v>
       </c>
       <c r="C785">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D785">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="786">
       <c r="A786" t="str">
-        <v>patascubo</v>
+        <v>edsonbahienseb</v>
       </c>
       <c r="B786">
         <v>0</v>
@@ -11406,7 +11406,7 @@
     </row>
     <row r="787">
       <c r="A787" t="str">
-        <v>mayconzilli</v>
+        <v>paulomartins.mma</v>
       </c>
       <c r="B787">
         <v>0</v>
@@ -11420,21 +11420,21 @@
     </row>
     <row r="788">
       <c r="A788" t="str">
-        <v>jeffesonmeirelles</v>
+        <v>daniel_natel</v>
       </c>
       <c r="B788">
         <v>0</v>
       </c>
       <c r="C788">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D788">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="789">
       <c r="A789" t="str">
-        <v>denilson.unit</v>
+        <v>dhuks11</v>
       </c>
       <c r="B789">
         <v>0</v>
@@ -11443,12 +11443,12 @@
         <v>1</v>
       </c>
       <c r="D789">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="790">
       <c r="A790" t="str">
-        <v>vieirabjj____</v>
+        <v>macksomlee</v>
       </c>
       <c r="B790">
         <v>0</v>
@@ -11462,21 +11462,21 @@
     </row>
     <row r="791">
       <c r="A791" t="str">
-        <v>bruno_pontes1992</v>
+        <v>y_nichimura</v>
       </c>
       <c r="B791">
         <v>0</v>
       </c>
       <c r="C791">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D791">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="792">
       <c r="A792" t="str">
-        <v>leandro__parpinelli</v>
+        <v>patascubo</v>
       </c>
       <c r="B792">
         <v>0</v>
@@ -11490,7 +11490,7 @@
     </row>
     <row r="793">
       <c r="A793" t="str">
-        <v>allan10adm</v>
+        <v>mayconzilli</v>
       </c>
       <c r="B793">
         <v>0</v>
@@ -11504,7 +11504,7 @@
     </row>
     <row r="794">
       <c r="A794" t="str">
-        <v>gaby_alves07</v>
+        <v>jeffesonmeirelles</v>
       </c>
       <c r="B794">
         <v>0</v>
@@ -11518,7 +11518,7 @@
     </row>
     <row r="795">
       <c r="A795" t="str">
-        <v>roginbrito</v>
+        <v>denilson.unit</v>
       </c>
       <c r="B795">
         <v>0</v>
@@ -11527,12 +11527,12 @@
         <v>1</v>
       </c>
       <c r="D795">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="796">
       <c r="A796" t="str">
-        <v>raulcarvalho1010</v>
+        <v>vieirabjj____</v>
       </c>
       <c r="B796">
         <v>0</v>
@@ -11541,12 +11541,12 @@
         <v>1</v>
       </c>
       <c r="D796">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="797">
       <c r="A797" t="str">
-        <v>gemeaslauraebrenda</v>
+        <v>bruno_pontes1992</v>
       </c>
       <c r="B797">
         <v>0</v>
@@ -11555,12 +11555,12 @@
         <v>1</v>
       </c>
       <c r="D797">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="798">
       <c r="A798" t="str">
-        <v>douglas_vitor8</v>
+        <v>leandro__parpinelli</v>
       </c>
       <c r="B798">
         <v>0</v>
@@ -11569,12 +11569,12 @@
         <v>1</v>
       </c>
       <c r="D798">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="799">
       <c r="A799" t="str">
-        <v>kevin.mota95</v>
+        <v>allan10adm</v>
       </c>
       <c r="B799">
         <v>0</v>
@@ -11583,12 +11583,12 @@
         <v>1</v>
       </c>
       <c r="D799">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="800">
       <c r="A800" t="str">
-        <v>guilhermews1994</v>
+        <v>gaby_alves07</v>
       </c>
       <c r="B800">
         <v>0</v>
@@ -11597,12 +11597,12 @@
         <v>1</v>
       </c>
       <c r="D800">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="801">
       <c r="A801" t="str">
-        <v>tamysregina</v>
+        <v>roginbrito</v>
       </c>
       <c r="B801">
         <v>0</v>
@@ -11616,7 +11616,7 @@
     </row>
     <row r="802">
       <c r="A802" t="str">
-        <v>aline.amaral21</v>
+        <v>raulcarvalho1010</v>
       </c>
       <c r="B802">
         <v>0</v>
@@ -11630,7 +11630,7 @@
     </row>
     <row r="803">
       <c r="A803" t="str">
-        <v>katlembrenda</v>
+        <v>gemeaslauraebrenda</v>
       </c>
       <c r="B803">
         <v>0</v>
@@ -11644,7 +11644,7 @@
     </row>
     <row r="804">
       <c r="A804" t="str">
-        <v>dudu.acabamentos</v>
+        <v>douglas_vitor8</v>
       </c>
       <c r="B804">
         <v>0</v>
@@ -11658,7 +11658,7 @@
     </row>
     <row r="805">
       <c r="A805" t="str">
-        <v>isadoragolimpio</v>
+        <v>kevin.mota95</v>
       </c>
       <c r="B805">
         <v>0</v>
@@ -11672,7 +11672,7 @@
     </row>
     <row r="806">
       <c r="A806" t="str">
-        <v>audizioandrade</v>
+        <v>guilhermews1994</v>
       </c>
       <c r="B806">
         <v>0</v>
@@ -11686,7 +11686,7 @@
     </row>
     <row r="807">
       <c r="A807" t="str">
-        <v>boradepodcastoficial</v>
+        <v>tamysregina</v>
       </c>
       <c r="B807">
         <v>0</v>
@@ -11700,7 +11700,7 @@
     </row>
     <row r="808">
       <c r="A808" t="str">
-        <v>marlon_bodybuilding</v>
+        <v>aline.amaral21</v>
       </c>
       <c r="B808">
         <v>0</v>
@@ -11714,7 +11714,7 @@
     </row>
     <row r="809">
       <c r="A809" t="str">
-        <v>natalves5</v>
+        <v>katlembrenda</v>
       </c>
       <c r="B809">
         <v>0</v>
@@ -11728,7 +11728,7 @@
     </row>
     <row r="810">
       <c r="A810" t="str">
-        <v>barbaracontadora</v>
+        <v>dudu.acabamentos</v>
       </c>
       <c r="B810">
         <v>0</v>
@@ -11742,7 +11742,7 @@
     </row>
     <row r="811">
       <c r="A811" t="str">
-        <v>vidaldanin</v>
+        <v>isadoragolimpio</v>
       </c>
       <c r="B811">
         <v>0</v>
@@ -11756,7 +11756,7 @@
     </row>
     <row r="812">
       <c r="A812" t="str">
-        <v>andrey_m_s_</v>
+        <v>audizioandrade</v>
       </c>
       <c r="B812">
         <v>0</v>
@@ -11770,7 +11770,7 @@
     </row>
     <row r="813">
       <c r="A813" t="str">
-        <v>deivssonmanin</v>
+        <v>boradepodcastoficial</v>
       </c>
       <c r="B813">
         <v>0</v>
@@ -11784,7 +11784,7 @@
     </row>
     <row r="814">
       <c r="A814" t="str">
-        <v>rejr_mma</v>
+        <v>marlon_bodybuilding</v>
       </c>
       <c r="B814">
         <v>0</v>
@@ -11798,7 +11798,7 @@
     </row>
     <row r="815">
       <c r="A815" t="str">
-        <v>felipeocalmon</v>
+        <v>natalves5</v>
       </c>
       <c r="B815">
         <v>0</v>
@@ -11812,7 +11812,7 @@
     </row>
     <row r="816">
       <c r="A816" t="str">
-        <v>igorbrasileiro01</v>
+        <v>barbaracontadora</v>
       </c>
       <c r="B816">
         <v>0</v>
@@ -11826,7 +11826,7 @@
     </row>
     <row r="817">
       <c r="A817" t="str">
-        <v>joaolauar_</v>
+        <v>vidaldanin</v>
       </c>
       <c r="B817">
         <v>0</v>
@@ -11840,7 +11840,7 @@
     </row>
     <row r="818">
       <c r="A818" t="str">
-        <v>michele_mixa</v>
+        <v>andrey_m_s_</v>
       </c>
       <c r="B818">
         <v>0</v>
@@ -11854,7 +11854,7 @@
     </row>
     <row r="819">
       <c r="A819" t="str">
-        <v>nataliaemanuela.personal</v>
+        <v>deivssonmanin</v>
       </c>
       <c r="B819">
         <v>0</v>
@@ -11868,7 +11868,7 @@
     </row>
     <row r="820">
       <c r="A820" t="str">
-        <v>benicius_edu</v>
+        <v>rejr_mma</v>
       </c>
       <c r="B820">
         <v>0</v>
@@ -11882,7 +11882,7 @@
     </row>
     <row r="821">
       <c r="A821" t="str">
-        <v>andreza.thais.1</v>
+        <v>felipeocalmon</v>
       </c>
       <c r="B821">
         <v>0</v>
@@ -11896,7 +11896,7 @@
     </row>
     <row r="822">
       <c r="A822" t="str">
-        <v>julckreis</v>
+        <v>igorbrasileiro01</v>
       </c>
       <c r="B822">
         <v>0</v>
@@ -11910,7 +11910,7 @@
     </row>
     <row r="823">
       <c r="A823" t="str">
-        <v>alineanne_</v>
+        <v>joaolauar_</v>
       </c>
       <c r="B823">
         <v>0</v>
@@ -11924,7 +11924,7 @@
     </row>
     <row r="824">
       <c r="A824" t="str">
-        <v>romulerasilva</v>
+        <v>michele_mixa</v>
       </c>
       <c r="B824">
         <v>0</v>
@@ -11938,7 +11938,7 @@
     </row>
     <row r="825">
       <c r="A825" t="str">
-        <v>higorsaantana</v>
+        <v>nataliaemanuela.personal</v>
       </c>
       <c r="B825">
         <v>0</v>
@@ -11952,7 +11952,7 @@
     </row>
     <row r="826">
       <c r="A826" t="str">
-        <v>vitorcosta_mma</v>
+        <v>benicius_edu</v>
       </c>
       <c r="B826">
         <v>0</v>
@@ -11966,7 +11966,7 @@
     </row>
     <row r="827">
       <c r="A827" t="str">
-        <v>paulo.titoo</v>
+        <v>andreza.thais.1</v>
       </c>
       <c r="B827">
         <v>0</v>
@@ -11980,7 +11980,7 @@
     </row>
     <row r="828">
       <c r="A828" t="str">
-        <v>1000ton_n</v>
+        <v>julckreis</v>
       </c>
       <c r="B828">
         <v>0</v>
@@ -11994,7 +11994,7 @@
     </row>
     <row r="829">
       <c r="A829" t="str">
-        <v>claudio_marchese_7</v>
+        <v>alineanne_</v>
       </c>
       <c r="B829">
         <v>0</v>
@@ -12008,7 +12008,7 @@
     </row>
     <row r="830">
       <c r="A830" t="str">
-        <v>anamatias.m</v>
+        <v>romulerasilva</v>
       </c>
       <c r="B830">
         <v>0</v>
@@ -12022,7 +12022,7 @@
     </row>
     <row r="831">
       <c r="A831" t="str">
-        <v>taporondebruno</v>
+        <v>higorsaantana</v>
       </c>
       <c r="B831">
         <v>0</v>
@@ -12036,7 +12036,7 @@
     </row>
     <row r="832">
       <c r="A832" t="str">
-        <v>ricardotofanello</v>
+        <v>vitorcosta_mma</v>
       </c>
       <c r="B832">
         <v>0</v>
@@ -12050,7 +12050,7 @@
     </row>
     <row r="833">
       <c r="A833" t="str">
-        <v>strong_stg_oficial</v>
+        <v>paulo.titoo</v>
       </c>
       <c r="B833">
         <v>0</v>
@@ -12064,7 +12064,7 @@
     </row>
     <row r="834">
       <c r="A834" t="str">
-        <v>nuncadesistir.nd</v>
+        <v>1000ton_n</v>
       </c>
       <c r="B834">
         <v>0</v>
@@ -12078,7 +12078,7 @@
     </row>
     <row r="835">
       <c r="A835" t="str">
-        <v>sabrinaalsilva</v>
+        <v>claudio_marchese_7</v>
       </c>
       <c r="B835">
         <v>0</v>
@@ -12092,7 +12092,7 @@
     </row>
     <row r="836">
       <c r="A836" t="str">
-        <v>caioparangole</v>
+        <v>anamatias.m</v>
       </c>
       <c r="B836">
         <v>0</v>
@@ -12106,7 +12106,7 @@
     </row>
     <row r="837">
       <c r="A837" t="str">
-        <v>leaoanaalice</v>
+        <v>taporondebruno</v>
       </c>
       <c r="B837">
         <v>0</v>
@@ -12120,7 +12120,7 @@
     </row>
     <row r="838">
       <c r="A838" t="str">
-        <v>pe.mirandas</v>
+        <v>ricardotofanello</v>
       </c>
       <c r="B838">
         <v>0</v>
@@ -12134,7 +12134,7 @@
     </row>
     <row r="839">
       <c r="A839" t="str">
-        <v>doraasivla</v>
+        <v>strong_stg_oficial</v>
       </c>
       <c r="B839">
         <v>0</v>
@@ -12148,7 +12148,7 @@
     </row>
     <row r="840">
       <c r="A840" t="str">
-        <v>marcilio.silva.71404</v>
+        <v>nuncadesistir.nd</v>
       </c>
       <c r="B840">
         <v>0</v>
@@ -12162,7 +12162,7 @@
     </row>
     <row r="841">
       <c r="A841" t="str">
-        <v>cristianomarcello</v>
+        <v>sabrinaalsilva</v>
       </c>
       <c r="B841">
         <v>0</v>
@@ -12176,7 +12176,7 @@
     </row>
     <row r="842">
       <c r="A842" t="str">
-        <v>herrickmarinho</v>
+        <v>caioparangole</v>
       </c>
       <c r="B842">
         <v>0</v>
@@ -12190,7 +12190,7 @@
     </row>
     <row r="843">
       <c r="A843" t="str">
-        <v>kfcampeoes</v>
+        <v>leaoanaalice</v>
       </c>
       <c r="B843">
         <v>0</v>
@@ -12204,7 +12204,7 @@
     </row>
     <row r="844">
       <c r="A844" t="str">
-        <v>sejamotivadorofc</v>
+        <v>pe.mirandas</v>
       </c>
       <c r="B844">
         <v>0</v>
@@ -12218,7 +12218,7 @@
     </row>
     <row r="845">
       <c r="A845" t="str">
-        <v>oliveiraandiarabjj</v>
+        <v>doraasivla</v>
       </c>
       <c r="B845">
         <v>0</v>
@@ -12232,7 +12232,7 @@
     </row>
     <row r="846">
       <c r="A846" t="str">
-        <v>dandraco_</v>
+        <v>marcilio.silva.71404</v>
       </c>
       <c r="B846">
         <v>0</v>
@@ -12246,7 +12246,7 @@
     </row>
     <row r="847">
       <c r="A847" t="str">
-        <v>chubotaru_lilu</v>
+        <v>cristianomarcello</v>
       </c>
       <c r="B847">
         <v>0</v>
@@ -12260,7 +12260,7 @@
     </row>
     <row r="848">
       <c r="A848" t="str">
-        <v>esteticaluharruda</v>
+        <v>herrickmarinho</v>
       </c>
       <c r="B848">
         <v>0</v>
@@ -12274,7 +12274,7 @@
     </row>
     <row r="849">
       <c r="A849" t="str">
-        <v>dadwillians</v>
+        <v>kfcampeoes</v>
       </c>
       <c r="B849">
         <v>0</v>
@@ -12288,7 +12288,7 @@
     </row>
     <row r="850">
       <c r="A850" t="str">
-        <v>vanemessina</v>
+        <v>sejamotivadorofc</v>
       </c>
       <c r="B850">
         <v>0</v>
@@ -12302,7 +12302,7 @@
     </row>
     <row r="851">
       <c r="A851" t="str">
-        <v>geanne_franca_</v>
+        <v>oliveiraandiarabjj</v>
       </c>
       <c r="B851">
         <v>0</v>
@@ -12316,7 +12316,7 @@
     </row>
     <row r="852">
       <c r="A852" t="str">
-        <v>victor_brunopersonal</v>
+        <v>dandraco_</v>
       </c>
       <c r="B852">
         <v>0</v>
@@ -12330,7 +12330,7 @@
     </row>
     <row r="853">
       <c r="A853" t="str">
-        <v>omar_alneaimi</v>
+        <v>chubotaru_lilu</v>
       </c>
       <c r="B853">
         <v>0</v>
@@ -12344,7 +12344,7 @@
     </row>
     <row r="854">
       <c r="A854" t="str">
-        <v>jimmy_indioap</v>
+        <v>esteticaluharruda</v>
       </c>
       <c r="B854">
         <v>0</v>
@@ -12358,7 +12358,7 @@
     </row>
     <row r="855">
       <c r="A855" t="str">
-        <v>_kainanlima</v>
+        <v>dadwillians</v>
       </c>
       <c r="B855">
         <v>0</v>
@@ -12372,7 +12372,7 @@
     </row>
     <row r="856">
       <c r="A856" t="str">
-        <v>mariacleusa.lopes</v>
+        <v>vanemessina</v>
       </c>
       <c r="B856">
         <v>0</v>
@@ -12386,7 +12386,7 @@
     </row>
     <row r="857">
       <c r="A857" t="str">
-        <v>leziamorbeck50</v>
+        <v>geanne_franca_</v>
       </c>
       <c r="B857">
         <v>0</v>
@@ -12400,7 +12400,7 @@
     </row>
     <row r="858">
       <c r="A858" t="str">
-        <v>andrearschack</v>
+        <v>victor_brunopersonal</v>
       </c>
       <c r="B858">
         <v>0</v>
@@ -12414,7 +12414,7 @@
     </row>
     <row r="859">
       <c r="A859" t="str">
-        <v>martinpakciarz</v>
+        <v>omar_alneaimi</v>
       </c>
       <c r="B859">
         <v>0</v>
@@ -12428,7 +12428,7 @@
     </row>
     <row r="860">
       <c r="A860" t="str">
-        <v>rafaelbipolarufc</v>
+        <v>jimmy_indioap</v>
       </c>
       <c r="B860">
         <v>0</v>
@@ -12442,7 +12442,7 @@
     </row>
     <row r="861">
       <c r="A861" t="str">
-        <v>meirelesmma</v>
+        <v>_kainanlima</v>
       </c>
       <c r="B861">
         <v>0</v>
@@ -12456,7 +12456,7 @@
     </row>
     <row r="862">
       <c r="A862" t="str">
-        <v>teamsilverio</v>
+        <v>mariacleusa.lopes</v>
       </c>
       <c r="B862">
         <v>0</v>
@@ -12470,7 +12470,7 @@
     </row>
     <row r="863">
       <c r="A863" t="str">
-        <v>tatiaradias</v>
+        <v>leziamorbeck50</v>
       </c>
       <c r="B863">
         <v>0</v>
@@ -12484,7 +12484,7 @@
     </row>
     <row r="864">
       <c r="A864" t="str">
-        <v>miltoncjr28</v>
+        <v>andrearschack</v>
       </c>
       <c r="B864">
         <v>0</v>
@@ -12498,7 +12498,7 @@
     </row>
     <row r="865">
       <c r="A865" t="str">
-        <v>leafarlemos</v>
+        <v>martinpakciarz</v>
       </c>
       <c r="B865">
         <v>0</v>
@@ -12512,7 +12512,7 @@
     </row>
     <row r="866">
       <c r="A866" t="str">
-        <v>thiagopssantos</v>
+        <v>rafaelbipolarufc</v>
       </c>
       <c r="B866">
         <v>0</v>
@@ -12526,7 +12526,7 @@
     </row>
     <row r="867">
       <c r="A867" t="str">
-        <v>daniloacordeon_oficial</v>
+        <v>meirelesmma</v>
       </c>
       <c r="B867">
         <v>0</v>
@@ -12540,7 +12540,7 @@
     </row>
     <row r="868">
       <c r="A868" t="str">
-        <v>dorgivan13_bjj</v>
+        <v>teamsilverio</v>
       </c>
       <c r="B868">
         <v>0</v>
@@ -12554,7 +12554,7 @@
     </row>
     <row r="869">
       <c r="A869" t="str">
-        <v>ryu_artes_marciais</v>
+        <v>tatiaradias</v>
       </c>
       <c r="B869">
         <v>0</v>
@@ -12568,7 +12568,7 @@
     </row>
     <row r="870">
       <c r="A870" t="str">
-        <v>marques.__bjj</v>
+        <v>miltoncjr28</v>
       </c>
       <c r="B870">
         <v>0</v>
@@ -12582,7 +12582,7 @@
     </row>
     <row r="871">
       <c r="A871" t="str">
-        <v>foryousaudeespecializada</v>
+        <v>leafarlemos</v>
       </c>
       <c r="B871">
         <v>0</v>
@@ -12596,7 +12596,7 @@
     </row>
     <row r="872">
       <c r="A872" t="str">
-        <v>soniarmurata</v>
+        <v>thiagopssantos</v>
       </c>
       <c r="B872">
         <v>0</v>
@@ -12610,7 +12610,7 @@
     </row>
     <row r="873">
       <c r="A873" t="str">
-        <v>almeidajjwk</v>
+        <v>daniloacordeon_oficial</v>
       </c>
       <c r="B873">
         <v>0</v>
@@ -12624,7 +12624,7 @@
     </row>
     <row r="874">
       <c r="A874" t="str">
-        <v>dvlucc2k26_</v>
+        <v>dorgivan13_bjj</v>
       </c>
       <c r="B874">
         <v>0</v>
@@ -12638,7 +12638,7 @@
     </row>
     <row r="875">
       <c r="A875" t="str">
-        <v>otaviocarneiromma</v>
+        <v>ryu_artes_marciais</v>
       </c>
       <c r="B875">
         <v>0</v>
@@ -12652,7 +12652,7 @@
     </row>
     <row r="876">
       <c r="A876" t="str">
-        <v>ayman__falil_06</v>
+        <v>marques.__bjj</v>
       </c>
       <c r="B876">
         <v>0</v>
@@ -12666,7 +12666,7 @@
     </row>
     <row r="877">
       <c r="A877" t="str">
-        <v>lurochachef</v>
+        <v>foryousaudeespecializada</v>
       </c>
       <c r="B877">
         <v>0</v>
@@ -12680,7 +12680,7 @@
     </row>
     <row r="878">
       <c r="A878" t="str">
-        <v>thayanne_rodrigues_bjj</v>
+        <v>soniarmurata</v>
       </c>
       <c r="B878">
         <v>0</v>
@@ -12694,7 +12694,7 @@
     </row>
     <row r="879">
       <c r="A879" t="str">
-        <v>galindofrontado</v>
+        <v>almeidajjwk</v>
       </c>
       <c r="B879">
         <v>0</v>
@@ -12708,7 +12708,7 @@
     </row>
     <row r="880">
       <c r="A880" t="str">
-        <v>laureanucalvo</v>
+        <v>dvlucc2k26_</v>
       </c>
       <c r="B880">
         <v>0</v>
@@ -12722,7 +12722,7 @@
     </row>
     <row r="881">
       <c r="A881" t="str">
-        <v>gisbedejose</v>
+        <v>otaviocarneiromma</v>
       </c>
       <c r="B881">
         <v>0</v>
@@ -12736,7 +12736,7 @@
     </row>
     <row r="882">
       <c r="A882" t="str">
-        <v>mauriciogeorge</v>
+        <v>ayman__falil_06</v>
       </c>
       <c r="B882">
         <v>0</v>
@@ -12750,7 +12750,7 @@
     </row>
     <row r="883">
       <c r="A883" t="str">
-        <v>viniciusmorais.bjj</v>
+        <v>lurochachef</v>
       </c>
       <c r="B883">
         <v>0</v>
@@ -12764,7 +12764,7 @@
     </row>
     <row r="884">
       <c r="A884" t="str">
-        <v>gandrapaulino</v>
+        <v>thayanne_rodrigues_bjj</v>
       </c>
       <c r="B884">
         <v>0</v>
@@ -12778,7 +12778,7 @@
     </row>
     <row r="885">
       <c r="A885" t="str">
-        <v>chalakakavinda</v>
+        <v>galindofrontado</v>
       </c>
       <c r="B885">
         <v>0</v>
@@ -12792,7 +12792,7 @@
     </row>
     <row r="886">
       <c r="A886" t="str">
-        <v>pgmarquesantos</v>
+        <v>laureanucalvo</v>
       </c>
       <c r="B886">
         <v>0</v>
@@ -12806,7 +12806,7 @@
     </row>
     <row r="887">
       <c r="A887" t="str">
-        <v>uluukyrgyz_tima</v>
+        <v>gisbedejose</v>
       </c>
       <c r="B887">
         <v>0</v>
@@ -12820,7 +12820,7 @@
     </row>
     <row r="888">
       <c r="A888" t="str">
-        <v>kells2vallone</v>
+        <v>mauriciogeorge</v>
       </c>
       <c r="B888">
         <v>0</v>
@@ -12834,7 +12834,7 @@
     </row>
     <row r="889">
       <c r="A889" t="str">
-        <v>personaljakeline</v>
+        <v>viniciusmorais.bjj</v>
       </c>
       <c r="B889">
         <v>0</v>
@@ -12848,7 +12848,7 @@
     </row>
     <row r="890">
       <c r="A890" t="str">
-        <v>marcaojudobjjmaster</v>
+        <v>gandrapaulino</v>
       </c>
       <c r="B890">
         <v>0</v>
@@ -12862,7 +12862,7 @@
     </row>
     <row r="891">
       <c r="A891" t="str">
-        <v>sergiorenatocruz1</v>
+        <v>chalakakavinda</v>
       </c>
       <c r="B891">
         <v>0</v>
@@ -12876,7 +12876,7 @@
     </row>
     <row r="892">
       <c r="A892" t="str">
-        <v>bjjfalkenberg</v>
+        <v>pgmarquesantos</v>
       </c>
       <c r="B892">
         <v>0</v>
@@ -12890,7 +12890,7 @@
     </row>
     <row r="893">
       <c r="A893" t="str">
-        <v>covil.045</v>
+        <v>uluukyrgyz_tima</v>
       </c>
       <c r="B893">
         <v>0</v>
@@ -12904,7 +12904,7 @@
     </row>
     <row r="894">
       <c r="A894" t="str">
-        <v>indio_mma</v>
+        <v>kells2vallone</v>
       </c>
       <c r="B894">
         <v>0</v>
@@ -12918,7 +12918,7 @@
     </row>
     <row r="895">
       <c r="A895" t="str">
-        <v>alomaraujo</v>
+        <v>personaljakeline</v>
       </c>
       <c r="B895">
         <v>0</v>
@@ -12932,7 +12932,7 @@
     </row>
     <row r="896">
       <c r="A896" t="str">
-        <v>allandelano</v>
+        <v>marcaojudobjjmaster</v>
       </c>
       <c r="B896">
         <v>0</v>
@@ -12946,7 +12946,7 @@
     </row>
     <row r="897">
       <c r="A897" t="str">
-        <v>theanimallifemovement</v>
+        <v>sergiorenatocruz1</v>
       </c>
       <c r="B897">
         <v>0</v>
@@ -12960,7 +12960,7 @@
     </row>
     <row r="898">
       <c r="A898" t="str">
-        <v>tombg_64</v>
+        <v>bjjfalkenberg</v>
       </c>
       <c r="B898">
         <v>0</v>
@@ -12974,7 +12974,7 @@
     </row>
     <row r="899">
       <c r="A899" t="str">
-        <v>andreichubotaru94</v>
+        <v>covil.045</v>
       </c>
       <c r="B899">
         <v>0</v>
@@ -12988,7 +12988,7 @@
     </row>
     <row r="900">
       <c r="A900" t="str">
-        <v>michaeloliveiramma</v>
+        <v>indio_mma</v>
       </c>
       <c r="B900">
         <v>0</v>
@@ -13002,7 +13002,7 @@
     </row>
     <row r="901">
       <c r="A901" t="str">
-        <v>helaynecrisl</v>
+        <v>alomaraujo</v>
       </c>
       <c r="B901">
         <v>0</v>
@@ -13016,7 +13016,7 @@
     </row>
     <row r="902">
       <c r="A902" t="str">
-        <v>carinhakkz</v>
+        <v>allandelano</v>
       </c>
       <c r="B902">
         <v>0</v>
@@ -13030,7 +13030,7 @@
     </row>
     <row r="903">
       <c r="A903" t="str">
-        <v>lmk_sport</v>
+        <v>theanimallifemovement</v>
       </c>
       <c r="B903">
         <v>0</v>
@@ -13044,7 +13044,7 @@
     </row>
     <row r="904">
       <c r="A904" t="str">
-        <v>mirnacaroline</v>
+        <v>tombg_64</v>
       </c>
       <c r="B904">
         <v>0</v>
@@ -13058,7 +13058,7 @@
     </row>
     <row r="905">
       <c r="A905" t="str">
-        <v>udilimaheroi</v>
+        <v>andreichubotaru94</v>
       </c>
       <c r="B905">
         <v>0</v>
@@ -13072,7 +13072,7 @@
     </row>
     <row r="906">
       <c r="A906" t="str">
-        <v>oliveiraa_00.11</v>
+        <v>michaeloliveiramma</v>
       </c>
       <c r="B906">
         <v>0</v>
@@ -13086,7 +13086,7 @@
     </row>
     <row r="907">
       <c r="A907" t="str">
-        <v>cristiannogueira.vtt</v>
+        <v>helaynecrisl</v>
       </c>
       <c r="B907">
         <v>0</v>
@@ -13100,7 +13100,7 @@
     </row>
     <row r="908">
       <c r="A908" t="str">
-        <v>fher.nando_</v>
+        <v>carinhakkz</v>
       </c>
       <c r="B908">
         <v>0</v>
@@ -13114,7 +13114,7 @@
     </row>
     <row r="909">
       <c r="A909" t="str">
-        <v>heloisa_elohim</v>
+        <v>lmk_sport</v>
       </c>
       <c r="B909">
         <v>0</v>
@@ -13128,7 +13128,7 @@
     </row>
     <row r="910">
       <c r="A910" t="str">
-        <v>raulbasilioo</v>
+        <v>mirnacaroline</v>
       </c>
       <c r="B910">
         <v>0</v>
@@ -13142,7 +13142,7 @@
     </row>
     <row r="911">
       <c r="A911" t="str">
-        <v>djuliaarianamma</v>
+        <v>udilimaheroi</v>
       </c>
       <c r="B911">
         <v>0</v>
@@ -13156,7 +13156,7 @@
     </row>
     <row r="912">
       <c r="A912" t="str">
-        <v>adrianaramosalvesribeiro</v>
+        <v>oliveiraa_00.11</v>
       </c>
       <c r="B912">
         <v>0</v>
@@ -13170,7 +13170,7 @@
     </row>
     <row r="913">
       <c r="A913" t="str">
-        <v>alexandrefideliis</v>
+        <v>cristiannogueira.vtt</v>
       </c>
       <c r="B913">
         <v>0</v>
@@ -13184,7 +13184,7 @@
     </row>
     <row r="914">
       <c r="A914" t="str">
-        <v>massoterapeuta_bemestarr</v>
+        <v>fher.nando_</v>
       </c>
       <c r="B914">
         <v>0</v>
@@ -13198,7 +13198,7 @@
     </row>
     <row r="915">
       <c r="A915" t="str">
-        <v>ellida_guimaraes</v>
+        <v>heloisa_elohim</v>
       </c>
       <c r="B915">
         <v>0</v>
@@ -13212,7 +13212,7 @@
     </row>
     <row r="916">
       <c r="A916" t="str">
-        <v>hostonhugo</v>
+        <v>raulbasilioo</v>
       </c>
       <c r="B916">
         <v>0</v>
@@ -13226,7 +13226,7 @@
     </row>
     <row r="917">
       <c r="A917" t="str">
-        <v>pammygaryo</v>
+        <v>djuliaarianamma</v>
       </c>
       <c r="B917">
         <v>0</v>
@@ -13240,7 +13240,7 @@
     </row>
     <row r="918">
       <c r="A918" t="str">
-        <v>bastazinifilho</v>
+        <v>adrianaramosalvesribeiro</v>
       </c>
       <c r="B918">
         <v>0</v>
@@ -13254,7 +13254,7 @@
     </row>
     <row r="919">
       <c r="A919" t="str">
-        <v>beatrizosilveira</v>
+        <v>alexandrefideliis</v>
       </c>
       <c r="B919">
         <v>0</v>
@@ -13268,7 +13268,7 @@
     </row>
     <row r="920">
       <c r="A920" t="str">
-        <v>danieldias7s</v>
+        <v>massoterapeuta_bemestarr</v>
       </c>
       <c r="B920">
         <v>0</v>
@@ -13282,7 +13282,7 @@
     </row>
     <row r="921">
       <c r="A921" t="str">
-        <v>pepefightteam</v>
+        <v>ellida_guimaraes</v>
       </c>
       <c r="B921">
         <v>0</v>
@@ -13296,7 +13296,7 @@
     </row>
     <row r="922">
       <c r="A922" t="str">
-        <v>ildemarmarajo</v>
+        <v>hostonhugo</v>
       </c>
       <c r="B922">
         <v>0</v>
@@ -13310,7 +13310,7 @@
     </row>
     <row r="923">
       <c r="A923" t="str">
-        <v>tavaresguu</v>
+        <v>pammygaryo</v>
       </c>
       <c r="B923">
         <v>0</v>
@@ -13324,7 +13324,7 @@
     </row>
     <row r="924">
       <c r="A924" t="str">
-        <v>zeferinomma</v>
+        <v>bastazinifilho</v>
       </c>
       <c r="B924">
         <v>0</v>
@@ -13338,7 +13338,7 @@
     </row>
     <row r="925">
       <c r="A925" t="str">
-        <v>vitorpaes_personalfight</v>
+        <v>beatrizosilveira</v>
       </c>
       <c r="B925">
         <v>0</v>
@@ -13352,7 +13352,7 @@
     </row>
     <row r="926">
       <c r="A926" t="str">
-        <v>kaynankruschewsky_ufc</v>
+        <v>danieldias7s</v>
       </c>
       <c r="B926">
         <v>0</v>
@@ -13366,7 +13366,7 @@
     </row>
     <row r="927">
       <c r="A927" t="str">
-        <v>fabio.sampaio.90260</v>
+        <v>pepefightteam</v>
       </c>
       <c r="B927">
         <v>0</v>
@@ -13380,7 +13380,7 @@
     </row>
     <row r="928">
       <c r="A928" t="str">
-        <v>marcusvgsz</v>
+        <v>ildemarmarajo</v>
       </c>
       <c r="B928">
         <v>0</v>
@@ -13394,7 +13394,7 @@
     </row>
     <row r="929">
       <c r="A929" t="str">
-        <v>ganemfelipe</v>
+        <v>tavaresguu</v>
       </c>
       <c r="B929">
         <v>0</v>
@@ -13408,7 +13408,7 @@
     </row>
     <row r="930">
       <c r="A930" t="str">
-        <v>ale.lagonegro</v>
+        <v>zeferinomma</v>
       </c>
       <c r="B930">
         <v>0</v>
@@ -13422,7 +13422,7 @@
     </row>
     <row r="931">
       <c r="A931" t="str">
-        <v>ianrochaf</v>
+        <v>vitorpaes_personalfight</v>
       </c>
       <c r="B931">
         <v>0</v>
@@ -13436,7 +13436,7 @@
     </row>
     <row r="932">
       <c r="A932" t="str">
-        <v>marcotulio_matuto</v>
+        <v>kaynankruschewsky_ufc</v>
       </c>
       <c r="B932">
         <v>0</v>
@@ -13450,7 +13450,7 @@
     </row>
     <row r="933">
       <c r="A933" t="str">
-        <v>anselmo.azevedo</v>
+        <v>fabio.sampaio.90260</v>
       </c>
       <c r="B933">
         <v>0</v>
@@ -13464,7 +13464,7 @@
     </row>
     <row r="934">
       <c r="A934" t="str">
-        <v>lincoln__puig77</v>
+        <v>marcusvgsz</v>
       </c>
       <c r="B934">
         <v>0</v>
@@ -13478,7 +13478,7 @@
     </row>
     <row r="935">
       <c r="A935" t="str">
-        <v>sougustavorosa</v>
+        <v>ganemfelipe</v>
       </c>
       <c r="B935">
         <v>0</v>
@@ -13492,7 +13492,7 @@
     </row>
     <row r="936">
       <c r="A936" t="str">
-        <v>sem_saida.12</v>
+        <v>ale.lagonegro</v>
       </c>
       <c r="B936">
         <v>0</v>
@@ -13506,7 +13506,7 @@
     </row>
     <row r="937">
       <c r="A937" t="str">
-        <v>lyviaestherbjj</v>
+        <v>ianrochaf</v>
       </c>
       <c r="B937">
         <v>0</v>
@@ -13520,7 +13520,7 @@
     </row>
     <row r="938">
       <c r="A938" t="str">
-        <v>macio.almeida_89</v>
+        <v>marcotulio_matuto</v>
       </c>
       <c r="B938">
         <v>0</v>
@@ -13534,7 +13534,7 @@
     </row>
     <row r="939">
       <c r="A939" t="str">
-        <v>helman_mma70</v>
+        <v>anselmo.azevedo</v>
       </c>
       <c r="B939">
         <v>0</v>
@@ -13548,7 +13548,7 @@
     </row>
     <row r="940">
       <c r="A940" t="str">
-        <v>brun_oguerreiro</v>
+        <v>lincoln__puig77</v>
       </c>
       <c r="B940">
         <v>0</v>
@@ -13562,7 +13562,7 @@
     </row>
     <row r="941">
       <c r="A941" t="str">
-        <v>ohanna.anselmo</v>
+        <v>sougustavorosa</v>
       </c>
       <c r="B941">
         <v>0</v>
@@ -13576,7 +13576,7 @@
     </row>
     <row r="942">
       <c r="A942" t="str">
-        <v>malene_elleen</v>
+        <v>sem_saida.12</v>
       </c>
       <c r="B942">
         <v>0</v>
@@ -13590,7 +13590,7 @@
     </row>
     <row r="943">
       <c r="A943" t="str">
-        <v>kevinlopes_bjj</v>
+        <v>lyviaestherbjj</v>
       </c>
       <c r="B943">
         <v>0</v>
@@ -13604,7 +13604,7 @@
     </row>
     <row r="944">
       <c r="A944" t="str">
-        <v>caioleonjj</v>
+        <v>macio.almeida_89</v>
       </c>
       <c r="B944">
         <v>0</v>
@@ -13618,7 +13618,7 @@
     </row>
     <row r="945">
       <c r="A945" t="str">
-        <v>jeferson_tijolo1</v>
+        <v>helman_mma70</v>
       </c>
       <c r="B945">
         <v>0</v>
@@ -13632,7 +13632,7 @@
     </row>
     <row r="946">
       <c r="A946" t="str">
-        <v>fdanieljj</v>
+        <v>brun_oguerreiro</v>
       </c>
       <c r="B946">
         <v>0</v>
@@ -13646,7 +13646,7 @@
     </row>
     <row r="947">
       <c r="A947" t="str">
-        <v>makelele_bjj</v>
+        <v>ohanna.anselmo</v>
       </c>
       <c r="B947">
         <v>0</v>
@@ -13660,7 +13660,7 @@
     </row>
     <row r="948">
       <c r="A948" t="str">
-        <v>dreamartpro</v>
+        <v>malene_elleen</v>
       </c>
       <c r="B948">
         <v>0</v>
@@ -13674,7 +13674,7 @@
     </row>
     <row r="949">
       <c r="A949" t="str">
-        <v>andressa_bjj_</v>
+        <v>kevinlopes_bjj</v>
       </c>
       <c r="B949">
         <v>0</v>
@@ -13688,7 +13688,7 @@
     </row>
     <row r="950">
       <c r="A950" t="str">
-        <v>karine_killer_ufc</v>
+        <v>caioleonjj</v>
       </c>
       <c r="B950">
         <v>0</v>
@@ -13702,7 +13702,7 @@
     </row>
     <row r="951">
       <c r="A951" t="str">
-        <v>wendel_bjj14</v>
+        <v>jeferson_tijolo1</v>
       </c>
       <c r="B951">
         <v>0</v>
@@ -13716,7 +13716,7 @@
     </row>
     <row r="952">
       <c r="A952" t="str">
-        <v>tamarapq</v>
+        <v>fdanieljj</v>
       </c>
       <c r="B952">
         <v>0</v>
@@ -13730,7 +13730,7 @@
     </row>
     <row r="953">
       <c r="A953" t="str">
-        <v>thaynara_victoria_</v>
+        <v>makelele_bjj</v>
       </c>
       <c r="B953">
         <v>0</v>
@@ -13744,7 +13744,7 @@
     </row>
     <row r="954">
       <c r="A954" t="str">
-        <v>mma.fisio</v>
+        <v>dreamartpro</v>
       </c>
       <c r="B954">
         <v>0</v>
@@ -13758,7 +13758,7 @@
     </row>
     <row r="955">
       <c r="A955" t="str">
-        <v>danielplayboymt</v>
+        <v>andressa_bjj_</v>
       </c>
       <c r="B955">
         <v>0</v>
@@ -13772,7 +13772,7 @@
     </row>
     <row r="956">
       <c r="A956" t="str">
-        <v>chunco_424</v>
+        <v>karine_killer_ufc</v>
       </c>
       <c r="B956">
         <v>0</v>
@@ -13786,7 +13786,7 @@
     </row>
     <row r="957">
       <c r="A957" t="str">
-        <v>fix.pec</v>
+        <v>wendel_bjj14</v>
       </c>
       <c r="B957">
         <v>0</v>
@@ -13800,7 +13800,7 @@
     </row>
     <row r="958">
       <c r="A958" t="str">
-        <v>roxostrike</v>
+        <v>tamarapq</v>
       </c>
       <c r="B958">
         <v>0</v>
@@ -13814,7 +13814,7 @@
     </row>
     <row r="959">
       <c r="A959" t="str">
-        <v>josita_bjj</v>
+        <v>thaynara_victoria_</v>
       </c>
       <c r="B959">
         <v>0</v>
@@ -13828,7 +13828,7 @@
     </row>
     <row r="960">
       <c r="A960" t="str">
-        <v>priscilaapbatista</v>
+        <v>mma.fisio</v>
       </c>
       <c r="B960">
         <v>0</v>
@@ -13842,7 +13842,7 @@
     </row>
     <row r="961">
       <c r="A961" t="str">
-        <v>denisalagoanobjj</v>
+        <v>danielplayboymt</v>
       </c>
       <c r="B961">
         <v>0</v>
@@ -13856,7 +13856,7 @@
     </row>
     <row r="962">
       <c r="A962" t="str">
-        <v>shirleypalestrina6</v>
+        <v>chunco_424</v>
       </c>
       <c r="B962">
         <v>0</v>
@@ -13870,7 +13870,7 @@
     </row>
     <row r="963">
       <c r="A963" t="str">
-        <v>flipebiano</v>
+        <v>fix.pec</v>
       </c>
       <c r="B963">
         <v>0</v>
@@ -13884,7 +13884,7 @@
     </row>
     <row r="964">
       <c r="A964" t="str">
-        <v>lyvia_genuina</v>
+        <v>roxostrike</v>
       </c>
       <c r="B964">
         <v>0</v>
@@ -13898,7 +13898,7 @@
     </row>
     <row r="965">
       <c r="A965" t="str">
-        <v>horadopower</v>
+        <v>josita_bjj</v>
       </c>
       <c r="B965">
         <v>0</v>
@@ -13912,7 +13912,7 @@
     </row>
     <row r="966">
       <c r="A966" t="str">
-        <v>manoel.brum</v>
+        <v>priscilaapbatista</v>
       </c>
       <c r="B966">
         <v>0</v>
@@ -13926,7 +13926,7 @@
     </row>
     <row r="967">
       <c r="A967" t="str">
-        <v>babimaciel1</v>
+        <v>denisalagoanobjj</v>
       </c>
       <c r="B967">
         <v>0</v>
@@ -13940,7 +13940,7 @@
     </row>
     <row r="968">
       <c r="A968" t="str">
-        <v>ruanmiqueias</v>
+        <v>shirleypalestrina6</v>
       </c>
       <c r="B968">
         <v>0</v>
@@ -13954,7 +13954,7 @@
     </row>
     <row r="969">
       <c r="A969" t="str">
-        <v>delariva_belem</v>
+        <v>flipebiano</v>
       </c>
       <c r="B969">
         <v>0</v>
@@ -13968,7 +13968,7 @@
     </row>
     <row r="970">
       <c r="A970" t="str">
-        <v>joseochoa.mma</v>
+        <v>lyvia_genuina</v>
       </c>
       <c r="B970">
         <v>0</v>
@@ -13982,7 +13982,7 @@
     </row>
     <row r="971">
       <c r="A971" t="str">
-        <v>reynitaoblitasbustamante</v>
+        <v>horadopower</v>
       </c>
       <c r="B971">
         <v>0</v>
@@ -13996,7 +13996,7 @@
     </row>
     <row r="972">
       <c r="A972" t="str">
-        <v>sthefany_ochoao</v>
+        <v>manoel.brum</v>
       </c>
       <c r="B972">
         <v>0</v>
@@ -14010,7 +14010,7 @@
     </row>
     <row r="973">
       <c r="A973" t="str">
-        <v>_matheustiberio</v>
+        <v>babimaciel1</v>
       </c>
       <c r="B973">
         <v>0</v>
@@ -14024,7 +14024,7 @@
     </row>
     <row r="974">
       <c r="A974" t="str">
-        <v>gabrielsantosufc_</v>
+        <v>ruanmiqueias</v>
       </c>
       <c r="B974">
         <v>0</v>
@@ -14038,7 +14038,7 @@
     </row>
     <row r="975">
       <c r="A975" t="str">
-        <v>juugxmes</v>
+        <v>delariva_belem</v>
       </c>
       <c r="B975">
         <v>0</v>
@@ -14052,7 +14052,7 @@
     </row>
     <row r="976">
       <c r="A976" t="str">
-        <v>gabriellb.andrade</v>
+        <v>joseochoa.mma</v>
       </c>
       <c r="B976">
         <v>0</v>
@@ -14066,7 +14066,7 @@
     </row>
     <row r="977">
       <c r="A977" t="str">
-        <v>romelluistro</v>
+        <v>reynitaoblitasbustamante</v>
       </c>
       <c r="B977">
         <v>0</v>
@@ -14080,7 +14080,7 @@
     </row>
     <row r="978">
       <c r="A978" t="str">
-        <v>yuricapelasso</v>
+        <v>sthefany_ochoao</v>
       </c>
       <c r="B978">
         <v>0</v>
@@ -14094,7 +14094,7 @@
     </row>
     <row r="979">
       <c r="A979" t="str">
-        <v>lucasfenomeno_ufc</v>
+        <v>_matheustiberio</v>
       </c>
       <c r="B979">
         <v>0</v>
@@ -14108,7 +14108,7 @@
     </row>
     <row r="980">
       <c r="A980" t="str">
-        <v>matheusdouradomma</v>
+        <v>gabrielsantosufc_</v>
       </c>
       <c r="B980">
         <v>0</v>
@@ -14122,7 +14122,7 @@
     </row>
     <row r="981">
       <c r="A981" t="str">
-        <v>lazyboy.ufc</v>
+        <v>juugxmes</v>
       </c>
       <c r="B981">
         <v>0</v>
@@ -14136,7 +14136,7 @@
     </row>
     <row r="982">
       <c r="A982" t="str">
-        <v>gabriell_marcus</v>
+        <v>gabriellb.andrade</v>
       </c>
       <c r="B982">
         <v>0</v>
@@ -14150,7 +14150,7 @@
     </row>
     <row r="983">
       <c r="A983" t="str">
-        <v>rafaelsouza7586</v>
+        <v>romelluistro</v>
       </c>
       <c r="B983">
         <v>0</v>
@@ -14164,7 +14164,7 @@
     </row>
     <row r="984">
       <c r="A984" t="str">
-        <v>dodge_big_johnson29</v>
+        <v>yuricapelasso</v>
       </c>
       <c r="B984">
         <v>0</v>
@@ -14178,7 +14178,7 @@
     </row>
     <row r="985">
       <c r="A985" t="str">
-        <v>land_on_martelo_308</v>
+        <v>lucasfenomeno_ufc</v>
       </c>
       <c r="B985">
         <v>0</v>
@@ -14192,7 +14192,7 @@
     </row>
     <row r="986">
       <c r="A986" t="str">
-        <v>dj__freckles</v>
+        <v>matheusdouradomma</v>
       </c>
       <c r="B986">
         <v>0</v>
@@ -14206,7 +14206,7 @@
     </row>
     <row r="987">
       <c r="A987" t="str">
-        <v>regis18vieira</v>
+        <v>lazyboy.ufc</v>
       </c>
       <c r="B987">
         <v>0</v>
@@ -14220,7 +14220,7 @@
     </row>
     <row r="988">
       <c r="A988" t="str">
-        <v>andy.techera.12</v>
+        <v>gabriell_marcus</v>
       </c>
       <c r="B988">
         <v>0</v>
@@ -14234,7 +14234,7 @@
     </row>
     <row r="989">
       <c r="A989" t="str">
-        <v>celiogarcia6</v>
+        <v>rafaelsouza7586</v>
       </c>
       <c r="B989">
         <v>0</v>
@@ -14248,7 +14248,7 @@
     </row>
     <row r="990">
       <c r="A990" t="str">
-        <v>luluakio</v>
+        <v>dodge_big_johnson29</v>
       </c>
       <c r="B990">
         <v>0</v>
@@ -14262,7 +14262,7 @@
     </row>
     <row r="991">
       <c r="A991" t="str">
-        <v>lusoaresjj</v>
+        <v>land_on_martelo_308</v>
       </c>
       <c r="B991">
         <v>0</v>
@@ -14276,7 +14276,7 @@
     </row>
     <row r="992">
       <c r="A992" t="str">
-        <v>barreto.boxe</v>
+        <v>dj__freckles</v>
       </c>
       <c r="B992">
         <v>0</v>
@@ -14290,7 +14290,7 @@
     </row>
     <row r="993">
       <c r="A993" t="str">
-        <v>sharingan_mma</v>
+        <v>regis18vieira</v>
       </c>
       <c r="B993">
         <v>0</v>
@@ -14304,7 +14304,7 @@
     </row>
     <row r="994">
       <c r="A994" t="str">
-        <v>thaisadantas</v>
+        <v>andy.techera.12</v>
       </c>
       <c r="B994">
         <v>0</v>
@@ -14318,7 +14318,7 @@
     </row>
     <row r="995">
       <c r="A995" t="str">
-        <v>jp.mdc</v>
+        <v>celiogarcia6</v>
       </c>
       <c r="B995">
         <v>0</v>
@@ -14332,7 +14332,7 @@
     </row>
     <row r="996">
       <c r="A996" t="str">
-        <v>danielbzk_</v>
+        <v>luluakio</v>
       </c>
       <c r="B996">
         <v>0</v>
@@ -14346,7 +14346,7 @@
     </row>
     <row r="997">
       <c r="A997" t="str">
-        <v>herbeth_indiomma</v>
+        <v>lusoaresjj</v>
       </c>
       <c r="B997">
         <v>0</v>
@@ -14360,7 +14360,7 @@
     </row>
     <row r="998">
       <c r="A998" t="str">
-        <v>pulsepro.nutrition</v>
+        <v>barreto.boxe</v>
       </c>
       <c r="B998">
         <v>0</v>
@@ -14374,7 +14374,7 @@
     </row>
     <row r="999">
       <c r="A999" t="str">
-        <v>1210gi</v>
+        <v>sharingan_mma</v>
       </c>
       <c r="B999">
         <v>0</v>
@@ -14388,7 +14388,7 @@
     </row>
     <row r="1000">
       <c r="A1000" t="str">
-        <v>maicon_mamute_</v>
+        <v>thaisadantas</v>
       </c>
       <c r="B1000">
         <v>0</v>
@@ -14402,7 +14402,7 @@
     </row>
     <row r="1001">
       <c r="A1001" t="str">
-        <v>wildler_borriello</v>
+        <v>jp.mdc</v>
       </c>
       <c r="B1001">
         <v>0</v>
@@ -14416,7 +14416,7 @@
     </row>
     <row r="1002">
       <c r="A1002" t="str">
-        <v>esmeraldasales</v>
+        <v>danielbzk_</v>
       </c>
       <c r="B1002">
         <v>0</v>
@@ -14430,7 +14430,7 @@
     </row>
     <row r="1003">
       <c r="A1003" t="str">
-        <v>raffaelcerqueira_ufc</v>
+        <v>herbeth_indiomma</v>
       </c>
       <c r="B1003">
         <v>0</v>
@@ -14444,7 +14444,7 @@
     </row>
     <row r="1004">
       <c r="A1004" t="str">
-        <v>jhonnydavid</v>
+        <v>pulsepro.nutrition</v>
       </c>
       <c r="B1004">
         <v>0</v>
@@ -14458,7 +14458,7 @@
     </row>
     <row r="1005">
       <c r="A1005" t="str">
-        <v>dannielvieira</v>
+        <v>1210gi</v>
       </c>
       <c r="B1005">
         <v>0</v>
@@ -14472,7 +14472,7 @@
     </row>
     <row r="1006">
       <c r="A1006" t="str">
-        <v>guilherme.leandromma</v>
+        <v>maicon_mamute_</v>
       </c>
       <c r="B1006">
         <v>0</v>
@@ -14486,7 +14486,7 @@
     </row>
     <row r="1007">
       <c r="A1007" t="str">
-        <v>siinho</v>
+        <v>wildler_borriello</v>
       </c>
       <c r="B1007">
         <v>0</v>
@@ -14500,7 +14500,7 @@
     </row>
     <row r="1008">
       <c r="A1008" t="str">
-        <v>rnn.neves</v>
+        <v>esmeraldasales</v>
       </c>
       <c r="B1008">
         <v>0</v>
@@ -14514,7 +14514,7 @@
     </row>
     <row r="1009">
       <c r="A1009" t="str">
-        <v>sulafotografia</v>
+        <v>raffaelcerqueira_ufc</v>
       </c>
       <c r="B1009">
         <v>0</v>
@@ -14528,7 +14528,7 @@
     </row>
     <row r="1010">
       <c r="A1010" t="str">
-        <v>luisfendt</v>
+        <v>jhonnydavid</v>
       </c>
       <c r="B1010">
         <v>0</v>
@@ -14542,7 +14542,7 @@
     </row>
     <row r="1011">
       <c r="A1011" t="str">
-        <v>cipobr</v>
+        <v>dannielvieira</v>
       </c>
       <c r="B1011">
         <v>0</v>
@@ -14556,7 +14556,7 @@
     </row>
     <row r="1012">
       <c r="A1012" t="str">
-        <v>contadoraison</v>
+        <v>guilherme.leandromma</v>
       </c>
       <c r="B1012">
         <v>0</v>
@@ -14570,7 +14570,7 @@
     </row>
     <row r="1013">
       <c r="A1013" t="str">
-        <v>guerreira.doasfalto</v>
+        <v>siinho</v>
       </c>
       <c r="B1013">
         <v>0</v>
@@ -14584,28 +14584,182 @@
     </row>
     <row r="1014">
       <c r="A1014" t="str">
+        <v>rnn.neves</v>
+      </c>
+      <c r="B1014">
+        <v>0</v>
+      </c>
+      <c r="C1014">
+        <v>1</v>
+      </c>
+      <c r="D1014">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" t="str">
+        <v>sulafotografia</v>
+      </c>
+      <c r="B1015">
+        <v>0</v>
+      </c>
+      <c r="C1015">
+        <v>1</v>
+      </c>
+      <c r="D1015">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="str">
+        <v>luisfendt</v>
+      </c>
+      <c r="B1016">
+        <v>0</v>
+      </c>
+      <c r="C1016">
+        <v>1</v>
+      </c>
+      <c r="D1016">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" t="str">
+        <v>cipobr</v>
+      </c>
+      <c r="B1017">
+        <v>0</v>
+      </c>
+      <c r="C1017">
+        <v>1</v>
+      </c>
+      <c r="D1017">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" t="str">
+        <v>contadoraison</v>
+      </c>
+      <c r="B1018">
+        <v>0</v>
+      </c>
+      <c r="C1018">
+        <v>1</v>
+      </c>
+      <c r="D1018">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="str">
+        <v>guerreira.doasfalto</v>
+      </c>
+      <c r="B1019">
+        <v>0</v>
+      </c>
+      <c r="C1019">
+        <v>1</v>
+      </c>
+      <c r="D1019">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" t="str">
         <v>jlheitor</v>
       </c>
-      <c r="B1014">
-        <v>0</v>
-      </c>
-      <c r="C1014">
-        <v>1</v>
-      </c>
-      <c r="D1014">
+      <c r="B1020">
+        <v>0</v>
+      </c>
+      <c r="C1020">
+        <v>1</v>
+      </c>
+      <c r="D1020">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" t="str">
+        <v>nostalgia_npt</v>
+      </c>
+      <c r="B1021">
+        <v>0</v>
+      </c>
+      <c r="C1021">
+        <v>1</v>
+      </c>
+      <c r="D1021">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" t="str">
+        <v>rapaduracapoeira</v>
+      </c>
+      <c r="B1022">
+        <v>0</v>
+      </c>
+      <c r="C1022">
+        <v>1</v>
+      </c>
+      <c r="D1022">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" t="str">
+        <v>cdmurilorossi</v>
+      </c>
+      <c r="B1023">
+        <v>0</v>
+      </c>
+      <c r="C1023">
+        <v>1</v>
+      </c>
+      <c r="D1023">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="str">
+        <v>marciosil7</v>
+      </c>
+      <c r="B1024">
+        <v>0</v>
+      </c>
+      <c r="C1024">
+        <v>1</v>
+      </c>
+      <c r="D1024">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="str">
+        <v>s.rodrigobernardoda</v>
+      </c>
+      <c r="B1025">
+        <v>0</v>
+      </c>
+      <c r="C1025">
+        <v>1</v>
+      </c>
+      <c r="D1025">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D1014"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D1025"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D140"/>
+  <dimension ref="A1:D155"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -14640,13 +14794,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C3">
         <v>3</v>
       </c>
       <c r="D3">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4">
@@ -14671,10 +14825,10 @@
         <v>11</v>
       </c>
       <c r="C5">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D5">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
@@ -14864,13 +15018,13 @@
         <v>propeace_fight</v>
       </c>
       <c r="B19">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C19">
         <v>0</v>
       </c>
       <c r="D19">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -14909,10 +15063,10 @@
         <v>3</v>
       </c>
       <c r="C22">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D22">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23">
@@ -15091,7 +15245,7 @@
         <v>3</v>
       </c>
       <c r="C35">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -15169,7 +15323,7 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>ottonimestre</v>
+        <v>vndcardoso</v>
       </c>
       <c r="B41">
         <v>2</v>
@@ -15183,7 +15337,7 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>shawlinoficial</v>
+        <v>ottonimestre</v>
       </c>
       <c r="B42">
         <v>2</v>
@@ -15197,10 +15351,10 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>og.mthx</v>
+        <v>shawlinoficial</v>
       </c>
       <c r="B43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C43">
         <v>0</v>
@@ -15211,7 +15365,7 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>danielcarmonaconsultor</v>
+        <v>og.mthx</v>
       </c>
       <c r="B44">
         <v>1</v>
@@ -15225,7 +15379,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>brcks4breakfast</v>
+        <v>danielcarmonaconsultor</v>
       </c>
       <c r="B45">
         <v>1</v>
@@ -15239,13 +15393,13 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>cristianpsicologo</v>
+        <v>mestreviniciusreviravolta</v>
       </c>
       <c r="B46">
         <v>1</v>
       </c>
       <c r="C46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D46">
         <v>1</v>
@@ -15253,7 +15407,7 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>mma.idiot</v>
+        <v>brcks4breakfast</v>
       </c>
       <c r="B47">
         <v>1</v>
@@ -15267,7 +15421,7 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>vndcardoso</v>
+        <v>cristianpsicologo</v>
       </c>
       <c r="B48">
         <v>1</v>
@@ -15281,7 +15435,7 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>murata_profight</v>
+        <v>mma.idiot</v>
       </c>
       <c r="B49">
         <v>1</v>
@@ -15295,7 +15449,7 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>roger_santosmma</v>
+        <v>murata_profight</v>
       </c>
       <c r="B50">
         <v>1</v>
@@ -15309,35 +15463,35 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>jean_ferreira_br</v>
+        <v>roger_santosmma</v>
       </c>
       <c r="B51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C51">
         <v>0</v>
       </c>
       <c r="D51">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>zackdos</v>
+        <v>jean_ferreira_br</v>
       </c>
       <c r="B52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C52">
         <v>0</v>
       </c>
       <c r="D52">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>david_sfc19</v>
+        <v>zackdos</v>
       </c>
       <c r="B53">
         <v>1</v>
@@ -15351,7 +15505,7 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>danielrodrigues1000</v>
+        <v>david_sfc19</v>
       </c>
       <c r="B54">
         <v>1</v>
@@ -15365,7 +15519,7 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>claudineiscorrea</v>
+        <v>danielrodrigues1000</v>
       </c>
       <c r="B55">
         <v>1</v>
@@ -15379,7 +15533,7 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>laisrebeiro10</v>
+        <v>claudineiscorrea</v>
       </c>
       <c r="B56">
         <v>1</v>
@@ -15393,7 +15547,7 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>klebiofernando</v>
+        <v>laisrebeiro10</v>
       </c>
       <c r="B57">
         <v>1</v>
@@ -15407,35 +15561,35 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>cassiosants__</v>
+        <v>klebiofernando</v>
       </c>
       <c r="B58">
         <v>1</v>
       </c>
       <c r="C58">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D58">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>aj_mma_</v>
+        <v>_cardoso_caio_</v>
       </c>
       <c r="B59">
         <v>1</v>
       </c>
       <c r="C59">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D59">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>pablofiorindi</v>
+        <v>b.scarvalhooo</v>
       </c>
       <c r="B60">
         <v>1</v>
@@ -15444,12 +15598,12 @@
         <v>0</v>
       </c>
       <c r="D60">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>erickdiaseds</v>
+        <v>tiwifenixmma</v>
       </c>
       <c r="B61">
         <v>1</v>
@@ -15458,12 +15612,12 @@
         <v>0</v>
       </c>
       <c r="D61">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>_jullianadacruz</v>
+        <v>marcelogabrielmma</v>
       </c>
       <c r="B62">
         <v>1</v>
@@ -15472,18 +15626,18 @@
         <v>0</v>
       </c>
       <c r="D62">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>albertoleandromoco</v>
+        <v>cassiosants__</v>
       </c>
       <c r="B63">
         <v>1</v>
       </c>
       <c r="C63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D63">
         <v>0</v>
@@ -15491,13 +15645,13 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>ellen.cristinaaa</v>
+        <v>aj_mma_</v>
       </c>
       <c r="B64">
         <v>1</v>
       </c>
       <c r="C64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D64">
         <v>0</v>
@@ -15505,7 +15659,7 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>thiagoauper</v>
+        <v>pablofiorindi</v>
       </c>
       <c r="B65">
         <v>1</v>
@@ -15519,7 +15673,7 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>karen.ottoni</v>
+        <v>erickdiaseds</v>
       </c>
       <c r="B66">
         <v>1</v>
@@ -15533,7 +15687,7 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>pauloserrati</v>
+        <v>_jullianadacruz</v>
       </c>
       <c r="B67">
         <v>1</v>
@@ -15547,7 +15701,7 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>lorenzojjts</v>
+        <v>albertoleandromoco</v>
       </c>
       <c r="B68">
         <v>1</v>
@@ -15561,7 +15715,7 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>_pedro0h</v>
+        <v>ellen.cristinaaa</v>
       </c>
       <c r="B69">
         <v>1</v>
@@ -15575,7 +15729,7 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>emersonriosmma</v>
+        <v>thiagoauper</v>
       </c>
       <c r="B70">
         <v>1</v>
@@ -15589,7 +15743,7 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>enzorkbjj</v>
+        <v>karen.ottoni</v>
       </c>
       <c r="B71">
         <v>1</v>
@@ -15603,7 +15757,7 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>_hygor.soares</v>
+        <v>pauloserrati</v>
       </c>
       <c r="B72">
         <v>1</v>
@@ -15617,7 +15771,7 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>adrianoams7</v>
+        <v>lorenzojjts</v>
       </c>
       <c r="B73">
         <v>1</v>
@@ -15631,7 +15785,7 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>k_costa68</v>
+        <v>_pedro0h</v>
       </c>
       <c r="B74">
         <v>1</v>
@@ -15645,7 +15799,7 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>808.chaz</v>
+        <v>emersonriosmma</v>
       </c>
       <c r="B75">
         <v>1</v>
@@ -15659,7 +15813,7 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>i_am_mauispunjahchick</v>
+        <v>enzorkbjj</v>
       </c>
       <c r="B76">
         <v>1</v>
@@ -15673,7 +15827,7 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>leomvgomes</v>
+        <v>_hygor.soares</v>
       </c>
       <c r="B77">
         <v>1</v>
@@ -15687,7 +15841,7 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>eliassilverio</v>
+        <v>adrianoams7</v>
       </c>
       <c r="B78">
         <v>1</v>
@@ -15701,7 +15855,7 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>luizguilhermepaiva_</v>
+        <v>k_costa68</v>
       </c>
       <c r="B79">
         <v>1</v>
@@ -15715,7 +15869,7 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>wagnermeneguelll</v>
+        <v>808.chaz</v>
       </c>
       <c r="B80">
         <v>1</v>
@@ -15729,7 +15883,7 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>marcos_indio._</v>
+        <v>i_am_mauispunjahchick</v>
       </c>
       <c r="B81">
         <v>1</v>
@@ -15743,7 +15897,7 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>corullapedro</v>
+        <v>leomvgomes</v>
       </c>
       <c r="B82">
         <v>1</v>
@@ -15757,7 +15911,7 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>dgswillian</v>
+        <v>eliassilverio</v>
       </c>
       <c r="B83">
         <v>1</v>
@@ -15771,7 +15925,7 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>edebetim_</v>
+        <v>luizguilhermepaiva_</v>
       </c>
       <c r="B84">
         <v>1</v>
@@ -15785,7 +15939,7 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>wanderley_silva081</v>
+        <v>wagnermeneguelll</v>
       </c>
       <c r="B85">
         <v>1</v>
@@ -15799,7 +15953,7 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>kakaa_ranch</v>
+        <v>marcos_indio._</v>
       </c>
       <c r="B86">
         <v>1</v>
@@ -15813,7 +15967,7 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>lorenzo.klippel</v>
+        <v>corullapedro</v>
       </c>
       <c r="B87">
         <v>1</v>
@@ -15827,7 +15981,7 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>luana8324</v>
+        <v>dgswillian</v>
       </c>
       <c r="B88">
         <v>1</v>
@@ -15841,7 +15995,7 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>paidepef</v>
+        <v>edebetim_</v>
       </c>
       <c r="B89">
         <v>1</v>
@@ -15855,7 +16009,7 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>malhadinho_ufc</v>
+        <v>wanderley_silva081</v>
       </c>
       <c r="B90">
         <v>1</v>
@@ -15869,7 +16023,7 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>juan.lboxe_</v>
+        <v>kakaa_ranch</v>
       </c>
       <c r="B91">
         <v>1</v>
@@ -15883,21 +16037,21 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>pedroriela</v>
+        <v>lorenzo.klippel</v>
       </c>
       <c r="B92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C92">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D92">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>andradeoficiaal</v>
+        <v>luana8324</v>
       </c>
       <c r="B93">
         <v>1</v>
@@ -15911,7 +16065,7 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>netinho_souzas</v>
+        <v>paidepef</v>
       </c>
       <c r="B94">
         <v>1</v>
@@ -15925,7 +16079,7 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>katharinelopes</v>
+        <v>malhadinho_ufc</v>
       </c>
       <c r="B95">
         <v>1</v>
@@ -15939,7 +16093,7 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>__dias_07_</v>
+        <v>juan.lboxe_</v>
       </c>
       <c r="B96">
         <v>1</v>
@@ -15953,21 +16107,21 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>igorsbessa</v>
+        <v>pedroriela</v>
       </c>
       <c r="B97">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C97">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D97">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>themarcosalves</v>
+        <v>andradeoficiaal</v>
       </c>
       <c r="B98">
         <v>1</v>
@@ -15981,7 +16135,7 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>deni_jesus_shalom</v>
+        <v>netinho_souzas</v>
       </c>
       <c r="B99">
         <v>1</v>
@@ -15995,7 +16149,7 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>george.bjj_</v>
+        <v>katharinelopes</v>
       </c>
       <c r="B100">
         <v>1</v>
@@ -16009,7 +16163,7 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>carlosshenn</v>
+        <v>__dias_07_</v>
       </c>
       <c r="B101">
         <v>1</v>
@@ -16023,7 +16177,7 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>almeida.nyara</v>
+        <v>igorsbessa</v>
       </c>
       <c r="B102">
         <v>1</v>
@@ -16037,7 +16191,7 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>ryangandraufc</v>
+        <v>themarcosalves</v>
       </c>
       <c r="B103">
         <v>1</v>
@@ -16051,153 +16205,153 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>leobahiamma</v>
+        <v>deni_jesus_shalom</v>
       </c>
       <c r="B104">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C104">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D104">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>dudaadantass</v>
+        <v>george.bjj_</v>
       </c>
       <c r="B105">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C105">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D105">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>joandersontubarao_ufc</v>
+        <v>carlosshenn</v>
       </c>
       <c r="B106">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C106">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D106">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>ismael.marreta_ufc</v>
+        <v>almeida.nyara</v>
       </c>
       <c r="B107">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C107">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D107">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>allan10adm</v>
+        <v>ryangandraufc</v>
       </c>
       <c r="B108">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C108">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D108">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>pedro_pavin_</v>
+        <v>biazon87</v>
       </c>
       <c r="B109">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C109">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D109">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>gaby_alves07</v>
+        <v>dubernardo37</v>
       </c>
       <c r="B110">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C110">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D110">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>diegosilvabjjoficial</v>
+        <v>sadraquesantana</v>
       </c>
       <c r="B111">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C111">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D111">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>luis_pequeno_mma</v>
+        <v>leonardomesquitamma</v>
       </c>
       <c r="B112">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C112">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D112">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>italothearcher</v>
+        <v>rogerio.maga</v>
       </c>
       <c r="B113">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C113">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D113">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>cathya_ferreira</v>
+        <v>roblesbastosalfredo</v>
       </c>
       <c r="B114">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C114">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D114">
         <v>0</v>
@@ -16205,35 +16359,35 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>rosacostasousa36</v>
+        <v>leobahiamma</v>
       </c>
       <c r="B115">
         <v>0</v>
       </c>
       <c r="C115">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D115">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>jp.mdc</v>
+        <v>dudaadantass</v>
       </c>
       <c r="B116">
         <v>0</v>
       </c>
       <c r="C116">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D116">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>danielbzk_</v>
+        <v>joandersontubarao_ufc</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -16242,12 +16396,12 @@
         <v>1</v>
       </c>
       <c r="D117">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>herbeth_indiomma</v>
+        <v>ismael.marreta_ufc</v>
       </c>
       <c r="B118">
         <v>0</v>
@@ -16256,12 +16410,12 @@
         <v>1</v>
       </c>
       <c r="D118">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>pulsepro.nutrition</v>
+        <v>allan10adm</v>
       </c>
       <c r="B119">
         <v>0</v>
@@ -16270,12 +16424,12 @@
         <v>1</v>
       </c>
       <c r="D119">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>1210gi</v>
+        <v>pedro_pavin_</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -16284,12 +16438,12 @@
         <v>1</v>
       </c>
       <c r="D120">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>juanx.pontes</v>
+        <v>gaby_alves07</v>
       </c>
       <c r="B121">
         <v>0</v>
@@ -16298,12 +16452,12 @@
         <v>1</v>
       </c>
       <c r="D121">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>_oliveira09_</v>
+        <v>diegosilvabjjoficial</v>
       </c>
       <c r="B122">
         <v>0</v>
@@ -16312,12 +16466,12 @@
         <v>1</v>
       </c>
       <c r="D122">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>mestreviniciusreviravolta</v>
+        <v>luis_pequeno_mma</v>
       </c>
       <c r="B123">
         <v>0</v>
@@ -16326,12 +16480,12 @@
         <v>1</v>
       </c>
       <c r="D123">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>djsagatoficial</v>
+        <v>italothearcher</v>
       </c>
       <c r="B124">
         <v>0</v>
@@ -16340,12 +16494,12 @@
         <v>1</v>
       </c>
       <c r="D124">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>maicon_mamute_</v>
+        <v>cathya_ferreira</v>
       </c>
       <c r="B125">
         <v>0</v>
@@ -16359,7 +16513,7 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>wildler_borriello</v>
+        <v>rosacostasousa36</v>
       </c>
       <c r="B126">
         <v>0</v>
@@ -16373,7 +16527,7 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>esmeraldasales</v>
+        <v>jp.mdc</v>
       </c>
       <c r="B127">
         <v>0</v>
@@ -16387,7 +16541,7 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>raffaelcerqueira_ufc</v>
+        <v>danielbzk_</v>
       </c>
       <c r="B128">
         <v>0</v>
@@ -16401,7 +16555,7 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>jhonnydavid</v>
+        <v>herbeth_indiomma</v>
       </c>
       <c r="B129">
         <v>0</v>
@@ -16415,7 +16569,7 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>dannielvieira</v>
+        <v>pulsepro.nutrition</v>
       </c>
       <c r="B130">
         <v>0</v>
@@ -16429,7 +16583,7 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>guilherme.leandromma</v>
+        <v>1210gi</v>
       </c>
       <c r="B131">
         <v>0</v>
@@ -16443,7 +16597,7 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>siinho</v>
+        <v>juanx.pontes</v>
       </c>
       <c r="B132">
         <v>0</v>
@@ -16457,7 +16611,7 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>rnn.neves</v>
+        <v>_oliveira09_</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -16471,7 +16625,7 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>tpapereira</v>
+        <v>djsagatoficial</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -16485,7 +16639,7 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>sulafotografia</v>
+        <v>maicon_mamute_</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -16499,7 +16653,7 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>luisfendt</v>
+        <v>wildler_borriello</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -16513,7 +16667,7 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>cipobr</v>
+        <v>esmeraldasales</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -16527,7 +16681,7 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>contadoraison</v>
+        <v>raffaelcerqueira_ufc</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -16541,7 +16695,7 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>guerreira.doasfalto</v>
+        <v>jhonnydavid</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -16555,21 +16709,231 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
+        <v>dannielvieira</v>
+      </c>
+      <c r="B140">
+        <v>0</v>
+      </c>
+      <c r="C140">
+        <v>1</v>
+      </c>
+      <c r="D140">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>guilherme.leandromma</v>
+      </c>
+      <c r="B141">
+        <v>0</v>
+      </c>
+      <c r="C141">
+        <v>1</v>
+      </c>
+      <c r="D141">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>siinho</v>
+      </c>
+      <c r="B142">
+        <v>0</v>
+      </c>
+      <c r="C142">
+        <v>1</v>
+      </c>
+      <c r="D142">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>rnn.neves</v>
+      </c>
+      <c r="B143">
+        <v>0</v>
+      </c>
+      <c r="C143">
+        <v>1</v>
+      </c>
+      <c r="D143">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>tpapereira</v>
+      </c>
+      <c r="B144">
+        <v>0</v>
+      </c>
+      <c r="C144">
+        <v>1</v>
+      </c>
+      <c r="D144">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>sulafotografia</v>
+      </c>
+      <c r="B145">
+        <v>0</v>
+      </c>
+      <c r="C145">
+        <v>1</v>
+      </c>
+      <c r="D145">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>luisfendt</v>
+      </c>
+      <c r="B146">
+        <v>0</v>
+      </c>
+      <c r="C146">
+        <v>1</v>
+      </c>
+      <c r="D146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>cipobr</v>
+      </c>
+      <c r="B147">
+        <v>0</v>
+      </c>
+      <c r="C147">
+        <v>1</v>
+      </c>
+      <c r="D147">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>contadoraison</v>
+      </c>
+      <c r="B148">
+        <v>0</v>
+      </c>
+      <c r="C148">
+        <v>1</v>
+      </c>
+      <c r="D148">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>guerreira.doasfalto</v>
+      </c>
+      <c r="B149">
+        <v>0</v>
+      </c>
+      <c r="C149">
+        <v>1</v>
+      </c>
+      <c r="D149">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
         <v>jlheitor</v>
       </c>
-      <c r="B140">
-        <v>0</v>
-      </c>
-      <c r="C140">
-        <v>1</v>
-      </c>
-      <c r="D140">
+      <c r="B150">
+        <v>0</v>
+      </c>
+      <c r="C150">
+        <v>1</v>
+      </c>
+      <c r="D150">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>nostalgia_npt</v>
+      </c>
+      <c r="B151">
+        <v>0</v>
+      </c>
+      <c r="C151">
+        <v>1</v>
+      </c>
+      <c r="D151">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>rapaduracapoeira</v>
+      </c>
+      <c r="B152">
+        <v>0</v>
+      </c>
+      <c r="C152">
+        <v>1</v>
+      </c>
+      <c r="D152">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>cdmurilorossi</v>
+      </c>
+      <c r="B153">
+        <v>0</v>
+      </c>
+      <c r="C153">
+        <v>1</v>
+      </c>
+      <c r="D153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>marciosil7</v>
+      </c>
+      <c r="B154">
+        <v>0</v>
+      </c>
+      <c r="C154">
+        <v>1</v>
+      </c>
+      <c r="D154">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>s.rodrigobernardoda</v>
+      </c>
+      <c r="B155">
+        <v>0</v>
+      </c>
+      <c r="C155">
+        <v>1</v>
+      </c>
+      <c r="D155">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D140"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D155"/>
   </ignoredErrors>
 </worksheet>
 </file>